--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="3">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="4">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="5">
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="6">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="7">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="8">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="9">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="10">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="11">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="12">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="13">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="14">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="15">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="16">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="17">
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="18">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="19">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="20">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="21">
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="22">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="23">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="24">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="25">
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="26">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="27">
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="28">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="29">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="30">
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="31">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="32">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="33">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="34">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="35">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="36">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="37">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="38">
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="39">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="40">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="41">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="42">
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="43">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="44">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="45">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="46">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="47">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="48">
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="49">
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="50">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
       </c>
     </row>
     <row r="51">
@@ -2423,10 +2423,1960 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46094.25622588059</v>
+        <v>46094.25622587963</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>e715895a-7a8a-47c1-857c-e87a64fb2118</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6054.19</v>
+      </c>
+      <c r="D52" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>c6d56985-5a6a-49e6-b8e8-860c6dc07e10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1679.02</v>
+      </c>
+      <c r="D53" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1a23d3a8-52b9-437e-913e-581a97eee8cc</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>9186.139999999999</v>
+      </c>
+      <c r="D54" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>f6081d35-4bc5-4f01-b297-da420817bf42</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2389.02</v>
+      </c>
+      <c r="D55" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>162938ad-c468-4930-b7f5-9496fa97cb6d</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2878.77</v>
+      </c>
+      <c r="D56" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>d55b4bf2-8aac-4f8e-a876-3066518f442f</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3181.6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>91.17</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9588dd77-b44f-4bf3-99f6-007d91bcf8be</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5369.93</v>
+      </c>
+      <c r="D58" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20af1d8a-3d5b-492a-a2ce-1c385c06bfef</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>6670.76</v>
+      </c>
+      <c r="D59" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6877568a-cbe1-48be-a8ae-9a2912009768</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9205.940000000001</v>
+      </c>
+      <c r="D60" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>100f9133-3187-40ff-95f7-3381c810ecbe</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2065.45</v>
+      </c>
+      <c r="D61" t="n">
+        <v>85.06999999999999</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>59668d0a-3955-4b53-ba0f-e278e92dd3eb</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2501.3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3b1ea915-a4cb-46f3-8469-42dee4357ff4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>8921.280000000001</v>
+      </c>
+      <c r="D63" t="n">
+        <v>87.31999999999999</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>70e66201-db63-4fa9-ae20-29c7b57463de</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>8679.780000000001</v>
+      </c>
+      <c r="D64" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0e7ff1a5-67ac-475b-9d7d-0009a21dd50f</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6043.45</v>
+      </c>
+      <c r="D65" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>71c0efec-c333-4ff7-a09b-e7e4545e8f93</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1530.11</v>
+      </c>
+      <c r="D66" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1e194daa-45ea-4822-b8a8-8e7937ff95bd</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>8436.969999999999</v>
+      </c>
+      <c r="D67" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>a2b02321-c657-4cf4-a44c-696320598cbc</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4347.47</v>
+      </c>
+      <c r="D68" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>75b2ee11-1a96-4125-82e6-3bed8b18d3ec</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5357.75</v>
+      </c>
+      <c r="D69" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6c69de8b-13ff-49d1-b8e8-fb733d1441fd</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4243.73</v>
+      </c>
+      <c r="D70" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>b4b087ef-560f-41de-b9df-394e0ccecbd5</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>7321.8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>dd10f970-adb3-439b-a7c0-f782639e5b91</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>6341.3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20f0ca84-badc-4dd4-91e0-ea426296dc34</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5864.18</v>
+      </c>
+      <c r="D73" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>061a5d8d-db2c-4eb2-8dab-0d3022a37074</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6326.55</v>
+      </c>
+      <c r="D74" t="n">
+        <v>87.27</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>bb339521-073d-415c-8193-35cd41b24a8a</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3944.61</v>
+      </c>
+      <c r="D75" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>a8eb50ee-b5ff-4191-a0a6-cd163a09d918</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3243.46</v>
+      </c>
+      <c r="D76" t="n">
+        <v>99.78</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>066a0461-853e-4d63-8876-8fb3d41a1f54</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2249.65</v>
+      </c>
+      <c r="D77" t="n">
+        <v>89.06</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>995349d6-0520-40f2-b77d-5734b81dcf25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1735.02</v>
+      </c>
+      <c r="D78" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fe29a209-e7d6-4290-a402-cc0050182210</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3437.88</v>
+      </c>
+      <c r="D79" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>a9d59163-e9e3-4602-8f6f-d8ee471fc731</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4410</v>
+      </c>
+      <c r="D80" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>98f4be1e-4f41-44ad-84f8-4993472c4f92</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7621.06</v>
+      </c>
+      <c r="D81" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>72c9447c-5584-4d93-ac79-04097139e5cd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>7667.47</v>
+      </c>
+      <c r="D82" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>84730c28-9465-4801-8092-05f9cd78cc5b</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>8073.79</v>
+      </c>
+      <c r="D83" t="n">
+        <v>97.45999999999999</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>fd499e9e-741b-4826-848a-b0360d2d2cad</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3132.79</v>
+      </c>
+      <c r="D84" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8a7ebb39-c7f9-40fd-a82f-3b4057d25bda</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>7747.28</v>
+      </c>
+      <c r="D85" t="n">
+        <v>95.29000000000001</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14e8167e-ccf0-4e6a-9c33-3a9f6ecc1a79</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4860.53</v>
+      </c>
+      <c r="D86" t="n">
+        <v>95.87</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>24a73fe1-4c8d-4d08-b850-e07a3c653910</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>8192.809999999999</v>
+      </c>
+      <c r="D87" t="n">
+        <v>92.95999999999999</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>97556e77-3a71-4e0e-9b49-d84af964b598</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>8240.459999999999</v>
+      </c>
+      <c r="D88" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cbee731f-b14d-4743-9b87-fb5aeddf7d84</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>6569.96</v>
+      </c>
+      <c r="D89" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>baed2d45-70d0-467a-a088-f25779fdae91</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>4471.71</v>
+      </c>
+      <c r="D90" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>aeba1ce1-3306-4f81-acb0-b81b4e30925f</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2790.71</v>
+      </c>
+      <c r="D91" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1a6a020a-171d-4bfe-b6ab-348ae858d2ec</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>7693.11</v>
+      </c>
+      <c r="D92" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>61a36c48-8a6b-44e8-9d99-91cb11828130</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1637.05</v>
+      </c>
+      <c r="D93" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ff77c13e-e11d-47b0-a19e-83a916c763ae</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>8854.280000000001</v>
+      </c>
+      <c r="D94" t="n">
+        <v>97.87</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>34d2e99c-8962-49cb-85a3-f0480403d7e4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>5207.09</v>
+      </c>
+      <c r="D95" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3df449ec-e9f5-4939-9471-b3ba82db3d19</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>8858.85</v>
+      </c>
+      <c r="D96" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>5a2ba8e5-04e6-47d2-93a9-d27736a0a1a4</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5018.74</v>
+      </c>
+      <c r="D97" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>e13a4ded-3395-4fc7-81e8-dc16bcc5f87e</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2060.9</v>
+      </c>
+      <c r="D98" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>32be64a1-f03c-482a-a52b-4efc49632624</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5189.53</v>
+      </c>
+      <c r="D99" t="n">
+        <v>88.83</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>c44bcb78-1735-4a9d-b5fb-862fef33f1f9</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>9179.92</v>
+      </c>
+      <c r="D100" t="n">
+        <v>90.72</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>46094.26884123853</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>a93c4311-1888-4651-827e-20c3b73c9cd4</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>5390.86</v>
+      </c>
+      <c r="D101" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>46094.26884123853</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:I551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46074.27338435522</v>
+        <v>46074.27338435185</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46079.27338435522</v>
+        <v>46079.27338435185</v>
       </c>
     </row>
     <row r="3">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46085.2733843597</v>
+        <v>46085.27338436343</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46090.2733843597</v>
+        <v>46090.27338436343</v>
       </c>
     </row>
     <row r="4">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46085.2733843631</v>
+        <v>46085.27338436343</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46090.2733843631</v>
+        <v>46090.27338436343</v>
       </c>
     </row>
     <row r="5">
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46075.27338436617</v>
+        <v>46075.27338436343</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46080.27338436617</v>
+        <v>46080.27338436343</v>
       </c>
     </row>
     <row r="6">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46071.27338436958</v>
+        <v>46071.273384375</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46076.27338436958</v>
+        <v>46076.273384375</v>
       </c>
     </row>
     <row r="7">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46069.27338437267</v>
+        <v>46069.273384375</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46074.27338437267</v>
+        <v>46074.273384375</v>
       </c>
     </row>
     <row r="8">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46073.27338437577</v>
+        <v>46073.273384375</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46078.27338437577</v>
+        <v>46078.273384375</v>
       </c>
     </row>
     <row r="9">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46087.27338437885</v>
+        <v>46087.273384375</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46092.27338437885</v>
+        <v>46092.273384375</v>
       </c>
     </row>
     <row r="10">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46075.27338438256</v>
+        <v>46075.27338438657</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46080.27338438256</v>
+        <v>46080.27338438657</v>
       </c>
     </row>
     <row r="11">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46075.27338438571</v>
+        <v>46075.27338438657</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46080.27338438571</v>
+        <v>46080.27338438657</v>
       </c>
     </row>
     <row r="12">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46067.27338438889</v>
+        <v>46067.27338438657</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46072.27338438889</v>
+        <v>46072.27338438657</v>
       </c>
     </row>
     <row r="13">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46070.27338439228</v>
+        <v>46070.27338438657</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46075.27338439228</v>
+        <v>46075.27338438657</v>
       </c>
     </row>
     <row r="14">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46073.27338439552</v>
+        <v>46073.27338439815</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46078.27338439552</v>
+        <v>46078.27338439815</v>
       </c>
     </row>
     <row r="15">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46066.27338439874</v>
+        <v>46066.27338439815</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46071.27338439874</v>
+        <v>46071.27338439815</v>
       </c>
     </row>
     <row r="16">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46060.27338440189</v>
+        <v>46060.27338439815</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46065.27338440189</v>
+        <v>46065.27338439815</v>
       </c>
     </row>
     <row r="17">
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46067.27338440515</v>
+        <v>46067.27338440972</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46072.27338440515</v>
+        <v>46072.27338440972</v>
       </c>
     </row>
     <row r="18">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46074.27338440831</v>
+        <v>46074.27338440972</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46079.27338440831</v>
+        <v>46079.27338440972</v>
       </c>
     </row>
     <row r="19">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46078.27338441137</v>
+        <v>46078.27338440972</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46083.27338441137</v>
+        <v>46083.27338440972</v>
       </c>
     </row>
     <row r="20">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46088.27338441468</v>
+        <v>46088.27338440972</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46093.27338441468</v>
+        <v>46093.27338440972</v>
       </c>
     </row>
     <row r="21">
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>46067.27338441776</v>
+        <v>46067.2733844213</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46072.27338441776</v>
+        <v>46072.2733844213</v>
       </c>
     </row>
     <row r="22">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>46069.27338442076</v>
+        <v>46069.2733844213</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46074.27338442076</v>
+        <v>46074.2733844213</v>
       </c>
     </row>
     <row r="23">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46064.2733844238</v>
+        <v>46064.2733844213</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46069.2733844238</v>
+        <v>46069.2733844213</v>
       </c>
     </row>
     <row r="24">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46073.2733844274</v>
+        <v>46073.27338443287</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46078.2733844274</v>
+        <v>46078.27338443287</v>
       </c>
     </row>
     <row r="25">
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46066.27338443044</v>
+        <v>46066.27338443287</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46071.27338443044</v>
+        <v>46071.27338443287</v>
       </c>
     </row>
     <row r="26">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46084.27338443367</v>
+        <v>46084.27338443287</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46089.27338443367</v>
+        <v>46089.27338443287</v>
       </c>
     </row>
     <row r="27">
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46062.27338443667</v>
+        <v>46062.27338443287</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46067.27338443667</v>
+        <v>46067.27338443287</v>
       </c>
     </row>
     <row r="28">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46076.27338444004</v>
+        <v>46076.27338444444</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46081.27338444004</v>
+        <v>46081.27338444444</v>
       </c>
     </row>
     <row r="29">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46083.27338444308</v>
+        <v>46083.27338444444</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46088.27338444308</v>
+        <v>46088.27338444444</v>
       </c>
     </row>
     <row r="30">
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46060.27338444629</v>
+        <v>46060.27338444444</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46065.27338444629</v>
+        <v>46065.27338444444</v>
       </c>
     </row>
     <row r="31">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46086.27338444969</v>
+        <v>46086.27338444444</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46091.27338444969</v>
+        <v>46091.27338444444</v>
       </c>
     </row>
     <row r="32">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46076.27338445273</v>
+        <v>46076.27338445602</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46081.27338445273</v>
+        <v>46081.27338445602</v>
       </c>
     </row>
     <row r="33">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46069.27338445574</v>
+        <v>46069.27338445602</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46074.27338445574</v>
+        <v>46074.27338445602</v>
       </c>
     </row>
     <row r="34">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46062.27338445879</v>
+        <v>46062.27338445602</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46067.27338445879</v>
+        <v>46067.27338445602</v>
       </c>
     </row>
     <row r="35">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46075.27338446208</v>
+        <v>46075.27338446759</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46080.27338446208</v>
+        <v>46080.27338446759</v>
       </c>
     </row>
     <row r="36">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46062.27338446513</v>
+        <v>46062.27338446759</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46067.27338446513</v>
+        <v>46067.27338446759</v>
       </c>
     </row>
     <row r="37">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46065.27338446827</v>
+        <v>46065.27338446759</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46070.27338446827</v>
+        <v>46070.27338446759</v>
       </c>
     </row>
     <row r="38">
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46066.27338447125</v>
+        <v>46066.27338446759</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46071.27338447125</v>
+        <v>46071.27338446759</v>
       </c>
     </row>
     <row r="39">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46059.27338447501</v>
+        <v>46059.27338447917</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46064.27338447501</v>
+        <v>46064.27338447917</v>
       </c>
     </row>
     <row r="40">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46078.27338447809</v>
+        <v>46078.27338447917</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46083.27338447809</v>
+        <v>46083.27338447917</v>
       </c>
     </row>
     <row r="41">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46084.27338448114</v>
+        <v>46084.27338447917</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46089.27338448114</v>
+        <v>46089.27338447917</v>
       </c>
     </row>
     <row r="42">
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>46087.27338448448</v>
+        <v>46087.27338447917</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46092.27338448448</v>
+        <v>46092.27338447917</v>
       </c>
     </row>
     <row r="43">
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46069.2733844875</v>
+        <v>46069.27338449074</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46074.2733844875</v>
+        <v>46074.27338449074</v>
       </c>
     </row>
     <row r="44">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46077.27338449075</v>
+        <v>46077.27338449074</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46082.27338449075</v>
+        <v>46082.27338449074</v>
       </c>
     </row>
     <row r="45">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46067.27338449394</v>
+        <v>46067.27338449074</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46072.27338449394</v>
+        <v>46072.27338449074</v>
       </c>
     </row>
     <row r="46">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46068.27338449729</v>
+        <v>46068.27338450232</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46073.27338449729</v>
+        <v>46073.27338450232</v>
       </c>
     </row>
     <row r="47">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46087.27338450032</v>
+        <v>46087.27338450232</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46092.27338450032</v>
+        <v>46092.27338450232</v>
       </c>
     </row>
     <row r="48">
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46079.27338450334</v>
+        <v>46079.27338450232</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46084.27338450334</v>
+        <v>46084.27338450232</v>
       </c>
     </row>
     <row r="49">
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46071.27338450641</v>
+        <v>46071.27338450232</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46076.27338450641</v>
+        <v>46076.27338450232</v>
       </c>
     </row>
     <row r="50">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46068.27338450967</v>
+        <v>46068.27338451389</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46073.27338450967</v>
+        <v>46073.27338451389</v>
       </c>
     </row>
     <row r="51">
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46078.27338451269</v>
+        <v>46078.27338451389</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46083.27338451269</v>
+        <v>46083.27338451389</v>
       </c>
     </row>
     <row r="52">
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46086.27338451582</v>
+        <v>46086.27338451389</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46091.27338451582</v>
+        <v>46091.27338451389</v>
       </c>
     </row>
     <row r="53">
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46078.27338451966</v>
+        <v>46078.27338451389</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46083.27338451966</v>
+        <v>46083.27338451389</v>
       </c>
     </row>
     <row r="54">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46081.27338452276</v>
+        <v>46081.27338452546</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46086.27338452276</v>
+        <v>46086.27338452546</v>
       </c>
     </row>
     <row r="55">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46067.27338452591</v>
+        <v>46067.27338452546</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46072.27338452591</v>
+        <v>46072.27338452546</v>
       </c>
     </row>
     <row r="56">
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46069.27338452911</v>
+        <v>46069.27338452546</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46074.27338452911</v>
+        <v>46074.27338452546</v>
       </c>
     </row>
     <row r="57">
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46067.27338453226</v>
+        <v>46067.27338453704</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46072.27338453226</v>
+        <v>46072.27338453704</v>
       </c>
     </row>
     <row r="58">
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46085.2733845353</v>
+        <v>46085.27338453704</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46090.2733845353</v>
+        <v>46090.27338453704</v>
       </c>
     </row>
     <row r="59">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46078.27338453836</v>
+        <v>46078.27338453704</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46083.27338453836</v>
+        <v>46083.27338453704</v>
       </c>
     </row>
     <row r="60">
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46062.27338454135</v>
+        <v>46062.27338453704</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46067.27338454135</v>
+        <v>46067.27338453704</v>
       </c>
     </row>
     <row r="61">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46071.2733845446</v>
+        <v>46071.27338454861</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46076.2733845446</v>
+        <v>46076.27338454861</v>
       </c>
     </row>
     <row r="62">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46074.27338454758</v>
+        <v>46074.27338454861</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46079.27338454758</v>
+        <v>46079.27338454861</v>
       </c>
     </row>
     <row r="63">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>46073.27338455062</v>
+        <v>46073.27338454861</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46078.27338455062</v>
+        <v>46078.27338454861</v>
       </c>
     </row>
     <row r="64">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>46059.27338455387</v>
+        <v>46059.27338454861</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46064.27338455387</v>
+        <v>46064.27338454861</v>
       </c>
     </row>
     <row r="65">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46066.27338455687</v>
+        <v>46066.27338456018</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46071.27338455687</v>
+        <v>46071.27338456018</v>
       </c>
     </row>
     <row r="66">
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46075.27338455992</v>
+        <v>46075.27338456018</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46080.27338455992</v>
+        <v>46080.27338456018</v>
       </c>
     </row>
     <row r="67">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46081.273384563</v>
+        <v>46081.27338456018</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46086.273384563</v>
+        <v>46086.27338456018</v>
       </c>
     </row>
     <row r="68">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46066.27338456657</v>
+        <v>46066.27338457176</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46071.27338456657</v>
+        <v>46071.27338457176</v>
       </c>
     </row>
     <row r="69">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46065.27338457005</v>
+        <v>46065.27338457176</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46070.27338457005</v>
+        <v>46070.27338457176</v>
       </c>
     </row>
     <row r="70">
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46078.27338457308</v>
+        <v>46078.27338457176</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46083.27338457308</v>
+        <v>46083.27338457176</v>
       </c>
     </row>
     <row r="71">
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46059.27338457853</v>
+        <v>46059.27338458334</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46064.27338457853</v>
+        <v>46064.27338458334</v>
       </c>
     </row>
     <row r="72">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46080.27338458171</v>
+        <v>46080.27338458334</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46085.27338458171</v>
+        <v>46085.27338458334</v>
       </c>
     </row>
     <row r="73">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46084.27338458481</v>
+        <v>46084.27338458334</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46089.27338458481</v>
+        <v>46089.27338458334</v>
       </c>
     </row>
     <row r="74">
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46077.27338458824</v>
+        <v>46077.27338458334</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46082.27338458824</v>
+        <v>46082.27338458334</v>
       </c>
     </row>
     <row r="75">
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46078.27338459133</v>
+        <v>46078.2733845949</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46083.27338459133</v>
+        <v>46083.2733845949</v>
       </c>
     </row>
     <row r="76">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46080.27338459431</v>
+        <v>46080.2733845949</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46085.27338459431</v>
+        <v>46085.2733845949</v>
       </c>
     </row>
     <row r="77">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46061.27338459737</v>
+        <v>46061.2733845949</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46066.27338459737</v>
+        <v>46066.2733845949</v>
       </c>
     </row>
     <row r="78">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46060.27338460072</v>
+        <v>46060.27338460648</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46065.27338460072</v>
+        <v>46065.27338460648</v>
       </c>
     </row>
     <row r="79">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46059.2733846038</v>
+        <v>46059.27338460648</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46064.2733846038</v>
+        <v>46064.27338460648</v>
       </c>
     </row>
     <row r="80">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46086.27338460687</v>
+        <v>46086.27338460648</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46091.27338460687</v>
+        <v>46091.27338460648</v>
       </c>
     </row>
     <row r="81">
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46085.27338461</v>
+        <v>46085.27338460648</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46090.27338461</v>
+        <v>46090.27338460648</v>
       </c>
     </row>
     <row r="82">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46085.27338461322</v>
+        <v>46085.27338461806</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46090.27338461322</v>
+        <v>46090.27338461806</v>
       </c>
     </row>
     <row r="83">
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46065.27338461625</v>
+        <v>46065.27338461806</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46070.27338461625</v>
+        <v>46070.27338461806</v>
       </c>
     </row>
     <row r="84">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46077.27338461937</v>
+        <v>46077.27338461806</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46082.27338461937</v>
+        <v>46082.27338461806</v>
       </c>
     </row>
     <row r="85">
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46060.27338462249</v>
+        <v>46060.27338461806</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46065.27338462249</v>
+        <v>46065.27338461806</v>
       </c>
     </row>
     <row r="86">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46066.27338462568</v>
+        <v>46066.27338462963</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46071.27338462568</v>
+        <v>46071.27338462963</v>
       </c>
     </row>
     <row r="87">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46081.27338462888</v>
+        <v>46081.27338462963</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46086.27338462888</v>
+        <v>46086.27338462963</v>
       </c>
     </row>
     <row r="88">
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46073.2733846319</v>
+        <v>46073.27338462963</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46078.2733846319</v>
+        <v>46078.27338462963</v>
       </c>
     </row>
     <row r="89">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46068.27338463524</v>
+        <v>46068.27338462963</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46073.27338463524</v>
+        <v>46073.27338462963</v>
       </c>
     </row>
     <row r="90">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46076.27338463837</v>
+        <v>46076.2733846412</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46081.27338463837</v>
+        <v>46081.2733846412</v>
       </c>
     </row>
     <row r="91">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46059.27338464149</v>
+        <v>46059.2733846412</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46064.27338464149</v>
+        <v>46064.2733846412</v>
       </c>
     </row>
     <row r="92">
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>46085.27338464457</v>
+        <v>46085.2733846412</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46090.27338464457</v>
+        <v>46090.2733846412</v>
       </c>
     </row>
     <row r="93">
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46074.27338464774</v>
+        <v>46074.27338465278</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46079.27338464774</v>
+        <v>46079.27338465278</v>
       </c>
     </row>
     <row r="94">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46061.27338465104</v>
+        <v>46061.27338465278</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46066.27338465104</v>
+        <v>46066.27338465278</v>
       </c>
     </row>
     <row r="95">
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46082.27338465423</v>
+        <v>46082.27338465278</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46087.27338465423</v>
+        <v>46087.27338465278</v>
       </c>
     </row>
     <row r="96">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46066.27338465724</v>
+        <v>46066.27338465278</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46071.27338465724</v>
+        <v>46071.27338465278</v>
       </c>
     </row>
     <row r="97">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>46077.27338466064</v>
+        <v>46077.27338466435</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46082.27338466064</v>
+        <v>46082.27338466435</v>
       </c>
     </row>
     <row r="98">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46063.27338466371</v>
+        <v>46063.27338466435</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46068.27338466371</v>
+        <v>46068.27338466435</v>
       </c>
     </row>
     <row r="99">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46065.2733846669</v>
+        <v>46065.27338466435</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46070.2733846669</v>
+        <v>46070.27338466435</v>
       </c>
     </row>
     <row r="100">
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46085.27338467008</v>
+        <v>46085.27338466435</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46090.27338467008</v>
+        <v>46090.27338466435</v>
       </c>
     </row>
     <row r="101">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46083.27338467317</v>
+        <v>46083.27338467593</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46088.27338467317</v>
+        <v>46088.27338467593</v>
       </c>
     </row>
     <row r="102">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46088.27338467625</v>
+        <v>46088.27338467593</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46093.27338467625</v>
+        <v>46093.27338467593</v>
       </c>
     </row>
     <row r="103">
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46067.27338467928</v>
+        <v>46067.27338467593</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46072.27338467928</v>
+        <v>46072.27338467593</v>
       </c>
     </row>
     <row r="104">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46072.27338468272</v>
+        <v>46072.2733846875</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46077.27338468272</v>
+        <v>46077.2733846875</v>
       </c>
     </row>
     <row r="105">
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46087.27338468585</v>
+        <v>46087.2733846875</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46092.27338468585</v>
+        <v>46092.2733846875</v>
       </c>
     </row>
     <row r="106">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46071.273384689</v>
+        <v>46071.2733846875</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46076.273384689</v>
+        <v>46076.2733846875</v>
       </c>
     </row>
     <row r="107">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46066.273384692</v>
+        <v>46066.2733846875</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46071.273384692</v>
+        <v>46071.2733846875</v>
       </c>
     </row>
     <row r="108">
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46063.2733846952</v>
+        <v>46063.27338469907</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46068.2733846952</v>
+        <v>46068.27338469907</v>
       </c>
     </row>
     <row r="109">
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46067.27338469839</v>
+        <v>46067.27338469907</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46072.27338469839</v>
+        <v>46072.27338469907</v>
       </c>
     </row>
     <row r="110">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46086.27338470152</v>
+        <v>46086.27338469907</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46091.27338470152</v>
+        <v>46091.27338469907</v>
       </c>
     </row>
     <row r="111">
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46084.27338470478</v>
+        <v>46084.27338469907</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46089.27338470478</v>
+        <v>46089.27338469907</v>
       </c>
     </row>
     <row r="112">
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46060.27338470781</v>
+        <v>46060.27338471065</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46065.27338470781</v>
+        <v>46065.27338471065</v>
       </c>
     </row>
     <row r="113">
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46085.27338471083</v>
+        <v>46085.27338471065</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46090.27338471083</v>
+        <v>46090.27338471065</v>
       </c>
     </row>
     <row r="114">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46063.27338471399</v>
+        <v>46063.27338471065</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46068.27338471399</v>
+        <v>46068.27338471065</v>
       </c>
     </row>
     <row r="115">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46087.27338471733</v>
+        <v>46087.27338472222</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46092.27338471733</v>
+        <v>46092.27338472222</v>
       </c>
     </row>
     <row r="116">
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46061.27338472043</v>
+        <v>46061.27338472222</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46066.27338472043</v>
+        <v>46066.27338472222</v>
       </c>
     </row>
     <row r="117">
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46088.27338472347</v>
+        <v>46088.27338472222</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46093.27338472347</v>
+        <v>46093.27338472222</v>
       </c>
     </row>
     <row r="118">
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46068.27338472652</v>
+        <v>46068.27338472222</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46073.27338472652</v>
+        <v>46073.27338472222</v>
       </c>
     </row>
     <row r="119">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46066.2733847297</v>
+        <v>46066.27338473379</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46071.2733847297</v>
+        <v>46071.27338473379</v>
       </c>
     </row>
     <row r="120">
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>46060.27338473285</v>
+        <v>46060.27338473379</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46065.27338473285</v>
+        <v>46065.27338473379</v>
       </c>
     </row>
     <row r="121">
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46063.27338473588</v>
+        <v>46063.27338473379</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46068.27338473588</v>
+        <v>46068.27338473379</v>
       </c>
     </row>
     <row r="122">
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46084.27338473911</v>
+        <v>46084.27338473379</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46089.27338473911</v>
+        <v>46089.27338473379</v>
       </c>
     </row>
     <row r="123">
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46075.27338474216</v>
+        <v>46075.27338474537</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46080.27338474216</v>
+        <v>46080.27338474537</v>
       </c>
     </row>
     <row r="124">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46076.27338474516</v>
+        <v>46076.27338474537</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46081.27338474516</v>
+        <v>46081.27338474537</v>
       </c>
     </row>
     <row r="125">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46078.27338474819</v>
+        <v>46078.27338474537</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46083.27338474819</v>
+        <v>46083.27338474537</v>
       </c>
     </row>
     <row r="126">
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46077.27338475158</v>
+        <v>46077.27338475695</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46082.27338475158</v>
+        <v>46082.27338475695</v>
       </c>
     </row>
     <row r="127">
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46076.27338475458</v>
+        <v>46076.27338475695</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46081.27338475458</v>
+        <v>46081.27338475695</v>
       </c>
     </row>
     <row r="128">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="H128" s="2" t="n">
-        <v>46079.27338475785</v>
+        <v>46079.27338475695</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46084.27338475785</v>
+        <v>46084.27338475695</v>
       </c>
     </row>
     <row r="129">
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="H129" s="2" t="n">
-        <v>46074.27338476091</v>
+        <v>46074.27338475695</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46079.27338476091</v>
+        <v>46079.27338475695</v>
       </c>
     </row>
     <row r="130">
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="H130" s="2" t="n">
-        <v>46078.27338476406</v>
+        <v>46078.27338476852</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46083.27338476406</v>
+        <v>46083.27338476852</v>
       </c>
     </row>
     <row r="131">
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46060.27338476727</v>
+        <v>46060.27338476852</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46065.27338476727</v>
+        <v>46065.27338476852</v>
       </c>
     </row>
     <row r="132">
@@ -5582,10 +5582,10 @@
         </is>
       </c>
       <c r="H132" s="2" t="n">
-        <v>46059.27338477036</v>
+        <v>46059.27338476852</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46064.27338477036</v>
+        <v>46064.27338476852</v>
       </c>
     </row>
     <row r="133">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="H133" s="2" t="n">
-        <v>46070.27338477359</v>
+        <v>46070.27338476852</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46075.27338477359</v>
+        <v>46075.27338476852</v>
       </c>
     </row>
     <row r="134">
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="H134" s="2" t="n">
-        <v>46077.2733847766</v>
+        <v>46077.27338478009</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46082.2733847766</v>
+        <v>46082.27338478009</v>
       </c>
     </row>
     <row r="135">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="H135" s="2" t="n">
-        <v>46087.27338477968</v>
+        <v>46087.27338478009</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46092.27338477968</v>
+        <v>46092.27338478009</v>
       </c>
     </row>
     <row r="136">
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="H136" s="2" t="n">
-        <v>46060.27338478278</v>
+        <v>46060.27338478009</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46065.27338478278</v>
+        <v>46065.27338478009</v>
       </c>
     </row>
     <row r="137">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="H137" s="2" t="n">
-        <v>46065.27338478607</v>
+        <v>46065.27338479167</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46070.27338478607</v>
+        <v>46070.27338479167</v>
       </c>
     </row>
     <row r="138">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="H138" s="2" t="n">
-        <v>46075.27338478912</v>
+        <v>46075.27338479167</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46080.27338478912</v>
+        <v>46080.27338479167</v>
       </c>
     </row>
     <row r="139">
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="H139" s="2" t="n">
-        <v>46074.27338479216</v>
+        <v>46074.27338479167</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46079.27338479216</v>
+        <v>46079.27338479167</v>
       </c>
     </row>
     <row r="140">
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="H140" s="2" t="n">
-        <v>46061.27338479521</v>
+        <v>46061.27338479167</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46066.27338479521</v>
+        <v>46066.27338479167</v>
       </c>
     </row>
     <row r="141">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="H141" s="2" t="n">
-        <v>46066.27338479837</v>
+        <v>46066.27338480324</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46071.27338479837</v>
+        <v>46071.27338480324</v>
       </c>
     </row>
     <row r="142">
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="H142" s="2" t="n">
-        <v>46086.27338480143</v>
+        <v>46086.27338480324</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46091.27338480143</v>
+        <v>46091.27338480324</v>
       </c>
     </row>
     <row r="143">
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="H143" s="2" t="n">
-        <v>46071.27338480449</v>
+        <v>46071.27338480324</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46076.27338480449</v>
+        <v>46076.27338480324</v>
       </c>
     </row>
     <row r="144">
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="H144" s="2" t="n">
-        <v>46079.2733848076</v>
+        <v>46079.27338480324</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46084.2733848076</v>
+        <v>46084.27338480324</v>
       </c>
     </row>
     <row r="145">
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="H145" s="2" t="n">
-        <v>46062.27338481087</v>
+        <v>46062.27338481481</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46067.27338481087</v>
+        <v>46067.27338481481</v>
       </c>
     </row>
     <row r="146">
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="H146" s="2" t="n">
-        <v>46073.27338481397</v>
+        <v>46073.27338481481</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>46078.27338481397</v>
+        <v>46078.27338481481</v>
       </c>
     </row>
     <row r="147">
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="H147" s="2" t="n">
-        <v>46088.273384817</v>
+        <v>46088.27338481481</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>46093.273384817</v>
+        <v>46093.27338481481</v>
       </c>
     </row>
     <row r="148">
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="H148" s="2" t="n">
-        <v>46086.27338482049</v>
+        <v>46086.27338481481</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>46091.27338482049</v>
+        <v>46091.27338481481</v>
       </c>
     </row>
     <row r="149">
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="H149" s="2" t="n">
-        <v>46088.27338482362</v>
+        <v>46088.27338482639</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>46093.27338482362</v>
+        <v>46093.27338482639</v>
       </c>
     </row>
     <row r="150">
@@ -6284,10 +6284,10 @@
         </is>
       </c>
       <c r="H150" s="2" t="n">
-        <v>46081.27338482685</v>
+        <v>46081.27338482639</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>46086.27338482685</v>
+        <v>46086.27338482639</v>
       </c>
     </row>
     <row r="151">
@@ -6323,10 +6323,10 @@
         </is>
       </c>
       <c r="H151" s="2" t="n">
-        <v>46064.27338483003</v>
+        <v>46064.27338482639</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>46069.27338483003</v>
+        <v>46069.27338482639</v>
       </c>
     </row>
     <row r="152">
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="H152" s="2" t="n">
-        <v>46083.27338483315</v>
+        <v>46083.27338483796</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>46088.27338483315</v>
+        <v>46088.27338483796</v>
       </c>
     </row>
     <row r="153">
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="H153" s="2" t="n">
-        <v>46076.27338483638</v>
+        <v>46076.27338483796</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>46081.27338483638</v>
+        <v>46081.27338483796</v>
       </c>
     </row>
     <row r="154">
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="H154" s="2" t="n">
-        <v>46072.27338484034</v>
+        <v>46072.27338483796</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>46077.27338484034</v>
+        <v>46077.27338483796</v>
       </c>
     </row>
     <row r="155">
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="H155" s="2" t="n">
-        <v>46067.27338484353</v>
+        <v>46067.27338483796</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>46072.27338484353</v>
+        <v>46072.27338483796</v>
       </c>
     </row>
     <row r="156">
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="H156" s="2" t="n">
-        <v>46078.27338484659</v>
+        <v>46078.27338484953</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>46083.27338484659</v>
+        <v>46083.27338484953</v>
       </c>
     </row>
     <row r="157">
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="H157" s="2" t="n">
-        <v>46073.27338484964</v>
+        <v>46073.27338484953</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>46078.27338484964</v>
+        <v>46078.27338484953</v>
       </c>
     </row>
     <row r="158">
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="H158" s="2" t="n">
-        <v>46087.27338485274</v>
+        <v>46087.27338484953</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>46092.27338485274</v>
+        <v>46092.27338484953</v>
       </c>
     </row>
     <row r="159">
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="H159" s="2" t="n">
-        <v>46087.2733848559</v>
+        <v>46087.27338486111</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>46092.2733848559</v>
+        <v>46092.27338486111</v>
       </c>
     </row>
     <row r="160">
@@ -6674,10 +6674,10 @@
         </is>
       </c>
       <c r="H160" s="2" t="n">
-        <v>46086.27338485909</v>
+        <v>46086.27338486111</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>46091.27338485909</v>
+        <v>46091.27338486111</v>
       </c>
     </row>
     <row r="161">
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="H161" s="2" t="n">
-        <v>46080.27338486214</v>
+        <v>46080.27338486111</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>46085.27338486214</v>
+        <v>46085.27338486111</v>
       </c>
     </row>
     <row r="162">
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="H162" s="2" t="n">
-        <v>46087.27338486532</v>
+        <v>46087.27338486111</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>46092.27338486532</v>
+        <v>46092.27338486111</v>
       </c>
     </row>
     <row r="163">
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="H163" s="2" t="n">
-        <v>46073.27338486865</v>
+        <v>46073.27338487269</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>46078.27338486865</v>
+        <v>46078.27338487269</v>
       </c>
     </row>
     <row r="164">
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="H164" s="2" t="n">
-        <v>46060.27338487169</v>
+        <v>46060.27338487269</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>46065.27338487169</v>
+        <v>46065.27338487269</v>
       </c>
     </row>
     <row r="165">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="H165" s="2" t="n">
-        <v>46070.27338487473</v>
+        <v>46070.27338487269</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>46075.27338487473</v>
+        <v>46075.27338487269</v>
       </c>
     </row>
     <row r="166">
@@ -6908,10 +6908,10 @@
         </is>
       </c>
       <c r="H166" s="2" t="n">
-        <v>46086.27338487795</v>
+        <v>46086.27338487269</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>46091.27338487795</v>
+        <v>46091.27338487269</v>
       </c>
     </row>
     <row r="167">
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="H167" s="2" t="n">
-        <v>46068.27338488098</v>
+        <v>46068.27338488426</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>46073.27338488098</v>
+        <v>46073.27338488426</v>
       </c>
     </row>
     <row r="168">
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="H168" s="2" t="n">
-        <v>46059.27338488404</v>
+        <v>46059.27338488426</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>46064.27338488404</v>
+        <v>46064.27338488426</v>
       </c>
     </row>
     <row r="169">
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="H169" s="2" t="n">
-        <v>46061.27338488706</v>
+        <v>46061.27338488426</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>46066.27338488706</v>
+        <v>46066.27338488426</v>
       </c>
     </row>
     <row r="170">
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="H170" s="2" t="n">
-        <v>46085.27338489032</v>
+        <v>46085.27338489583</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>46090.27338489032</v>
+        <v>46090.27338489583</v>
       </c>
     </row>
     <row r="171">
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H171" s="2" t="n">
-        <v>46072.27338489333</v>
+        <v>46072.27338489583</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>46077.27338489333</v>
+        <v>46077.27338489583</v>
       </c>
     </row>
     <row r="172">
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>46064.27338489651</v>
+        <v>46064.27338489583</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>46069.27338489651</v>
+        <v>46069.27338489583</v>
       </c>
     </row>
     <row r="173">
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="H173" s="2" t="n">
-        <v>46086.27338489959</v>
+        <v>46086.27338489583</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>46091.27338489959</v>
+        <v>46091.27338489583</v>
       </c>
     </row>
     <row r="174">
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="H174" s="2" t="n">
-        <v>46060.27338490276</v>
+        <v>46060.27338490741</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>46065.27338490276</v>
+        <v>46065.27338490741</v>
       </c>
     </row>
     <row r="175">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="H175" s="2" t="n">
-        <v>46071.27338490596</v>
+        <v>46071.27338490741</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>46076.27338490596</v>
+        <v>46076.27338490741</v>
       </c>
     </row>
     <row r="176">
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="H176" s="2" t="n">
-        <v>46082.27338490923</v>
+        <v>46082.27338490741</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>46087.27338490923</v>
+        <v>46087.27338490741</v>
       </c>
     </row>
     <row r="177">
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="H177" s="2" t="n">
-        <v>46073.27338491259</v>
+        <v>46073.27338490741</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>46078.27338491259</v>
+        <v>46078.27338490741</v>
       </c>
     </row>
     <row r="178">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="H178" s="2" t="n">
-        <v>46074.27338491573</v>
+        <v>46074.27338491898</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>46079.27338491573</v>
+        <v>46079.27338491898</v>
       </c>
     </row>
     <row r="179">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="H179" s="2" t="n">
-        <v>46086.27338491873</v>
+        <v>46086.27338491898</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>46091.27338491873</v>
+        <v>46091.27338491898</v>
       </c>
     </row>
     <row r="180">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="H180" s="2" t="n">
-        <v>46061.2733849219</v>
+        <v>46061.27338491898</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>46066.2733849219</v>
+        <v>46066.27338491898</v>
       </c>
     </row>
     <row r="181">
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="H181" s="2" t="n">
-        <v>46081.27338492509</v>
+        <v>46081.27338493056</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>46086.27338492509</v>
+        <v>46086.27338493056</v>
       </c>
     </row>
     <row r="182">
@@ -7532,10 +7532,10 @@
         </is>
       </c>
       <c r="H182" s="2" t="n">
-        <v>46088.27338492814</v>
+        <v>46088.27338493056</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>46093.27338492814</v>
+        <v>46093.27338493056</v>
       </c>
     </row>
     <row r="183">
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="H183" s="2" t="n">
-        <v>46069.27338493121</v>
+        <v>46069.27338493056</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>46074.27338493121</v>
+        <v>46074.27338493056</v>
       </c>
     </row>
     <row r="184">
@@ -7610,10 +7610,10 @@
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>46063.2733849342</v>
+        <v>46063.27338493056</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>46068.2733849342</v>
+        <v>46068.27338493056</v>
       </c>
     </row>
     <row r="185">
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="H185" s="2" t="n">
-        <v>46081.27338493785</v>
+        <v>46081.27338494213</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>46086.27338493785</v>
+        <v>46086.27338494213</v>
       </c>
     </row>
     <row r="186">
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="H186" s="2" t="n">
-        <v>46067.27338494105</v>
+        <v>46067.27338494213</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>46072.27338494105</v>
+        <v>46072.27338494213</v>
       </c>
     </row>
     <row r="187">
@@ -7727,10 +7727,10 @@
         </is>
       </c>
       <c r="H187" s="2" t="n">
-        <v>46079.27338494424</v>
+        <v>46079.27338494213</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>46084.27338494424</v>
+        <v>46084.27338494213</v>
       </c>
     </row>
     <row r="188">
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="H188" s="2" t="n">
-        <v>46079.27338494758</v>
+        <v>46079.27338494213</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>46084.27338494758</v>
+        <v>46084.27338494213</v>
       </c>
     </row>
     <row r="189">
@@ -7805,10 +7805,10 @@
         </is>
       </c>
       <c r="H189" s="2" t="n">
-        <v>46080.27338495065</v>
+        <v>46080.2733849537</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>46085.27338495065</v>
+        <v>46085.2733849537</v>
       </c>
     </row>
     <row r="190">
@@ -7844,10 +7844,10 @@
         </is>
       </c>
       <c r="H190" s="2" t="n">
-        <v>46063.27338495386</v>
+        <v>46063.2733849537</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>46068.27338495386</v>
+        <v>46068.2733849537</v>
       </c>
     </row>
     <row r="191">
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="H191" s="2" t="n">
-        <v>46066.273384957</v>
+        <v>46066.2733849537</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>46071.273384957</v>
+        <v>46071.2733849537</v>
       </c>
     </row>
     <row r="192">
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="H192" s="2" t="n">
-        <v>46085.27338496036</v>
+        <v>46085.27338496528</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>46090.27338496036</v>
+        <v>46090.27338496528</v>
       </c>
     </row>
     <row r="193">
@@ -7961,10 +7961,10 @@
         </is>
       </c>
       <c r="H193" s="2" t="n">
-        <v>46070.27338496348</v>
+        <v>46070.27338496528</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>46075.27338496348</v>
+        <v>46075.27338496528</v>
       </c>
     </row>
     <row r="194">
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="H194" s="2" t="n">
-        <v>46074.27338496669</v>
+        <v>46074.27338496528</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>46079.27338496669</v>
+        <v>46079.27338496528</v>
       </c>
     </row>
     <row r="195">
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="H195" s="2" t="n">
-        <v>46066.27338496994</v>
+        <v>46066.27338496528</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>46071.27338496994</v>
+        <v>46071.27338496528</v>
       </c>
     </row>
     <row r="196">
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="H196" s="2" t="n">
-        <v>46078.27338497298</v>
+        <v>46078.27338497685</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>46083.27338497298</v>
+        <v>46083.27338497685</v>
       </c>
     </row>
     <row r="197">
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="H197" s="2" t="n">
-        <v>46088.27338497622</v>
+        <v>46088.27338497685</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>46093.27338497622</v>
+        <v>46093.27338497685</v>
       </c>
     </row>
     <row r="198">
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="H198" s="2" t="n">
-        <v>46062.27338497937</v>
+        <v>46062.27338497685</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>46067.27338497937</v>
+        <v>46067.27338497685</v>
       </c>
     </row>
     <row r="199">
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="H199" s="2" t="n">
-        <v>46084.27338498276</v>
+        <v>46084.27338498842</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>46089.27338498276</v>
+        <v>46089.27338498842</v>
       </c>
     </row>
     <row r="200">
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="H200" s="2" t="n">
-        <v>46078.27338498595</v>
+        <v>46078.27338498842</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>46083.27338498595</v>
+        <v>46083.27338498842</v>
       </c>
     </row>
     <row r="201">
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="H201" s="2" t="n">
-        <v>46076.27338498909</v>
+        <v>46076.27338498842</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>46081.27338498909</v>
+        <v>46081.27338498842</v>
       </c>
     </row>
     <row r="202">
@@ -8312,10 +8312,10 @@
         </is>
       </c>
       <c r="H202" s="2" t="n">
-        <v>46066.27338499224</v>
+        <v>46066.27338498842</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>46071.27338499224</v>
+        <v>46071.27338498842</v>
       </c>
     </row>
     <row r="203">
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="H203" s="2" t="n">
-        <v>46067.27338499543</v>
+        <v>46067.273385</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>46072.27338499543</v>
+        <v>46072.273385</v>
       </c>
     </row>
     <row r="204">
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="H204" s="2" t="n">
-        <v>46068.27338499867</v>
+        <v>46068.273385</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>46073.27338499867</v>
+        <v>46073.273385</v>
       </c>
     </row>
     <row r="205">
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="H205" s="2" t="n">
-        <v>46077.27338500168</v>
+        <v>46077.273385</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>46082.27338500168</v>
+        <v>46082.273385</v>
       </c>
     </row>
     <row r="206">
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="H206" s="2" t="n">
-        <v>46081.2733850049</v>
+        <v>46081.273385</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>46086.2733850049</v>
+        <v>46086.273385</v>
       </c>
     </row>
     <row r="207">
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="H207" s="2" t="n">
-        <v>46088.27338500804</v>
+        <v>46088.27338501158</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>46093.27338500804</v>
+        <v>46093.27338501158</v>
       </c>
     </row>
     <row r="208">
@@ -8546,10 +8546,10 @@
         </is>
       </c>
       <c r="H208" s="2" t="n">
-        <v>46083.27338501107</v>
+        <v>46083.27338501158</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>46088.27338501107</v>
+        <v>46088.27338501158</v>
       </c>
     </row>
     <row r="209">
@@ -8585,10 +8585,10 @@
         </is>
       </c>
       <c r="H209" s="2" t="n">
-        <v>46063.27338501429</v>
+        <v>46063.27338501158</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>46068.27338501429</v>
+        <v>46068.27338501158</v>
       </c>
     </row>
     <row r="210">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="H210" s="2" t="n">
-        <v>46080.27338501746</v>
+        <v>46080.27338502315</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>46085.27338501746</v>
+        <v>46085.27338502315</v>
       </c>
     </row>
     <row r="211">
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="H211" s="2" t="n">
-        <v>46071.27338502064</v>
+        <v>46071.27338502315</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>46076.27338502064</v>
+        <v>46076.27338502315</v>
       </c>
     </row>
     <row r="212">
@@ -8702,10 +8702,10 @@
         </is>
       </c>
       <c r="H212" s="2" t="n">
-        <v>46069.27338502379</v>
+        <v>46069.27338502315</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>46074.27338502379</v>
+        <v>46074.27338502315</v>
       </c>
     </row>
     <row r="213">
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="H213" s="2" t="n">
-        <v>46083.27338502691</v>
+        <v>46083.27338502315</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>46088.27338502691</v>
+        <v>46088.27338502315</v>
       </c>
     </row>
     <row r="214">
@@ -8780,10 +8780,10 @@
         </is>
       </c>
       <c r="H214" s="2" t="n">
-        <v>46070.27338503033</v>
+        <v>46070.27338503472</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>46075.27338503033</v>
+        <v>46075.27338503472</v>
       </c>
     </row>
     <row r="215">
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="H215" s="2" t="n">
-        <v>46084.27338503335</v>
+        <v>46084.27338503472</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>46089.27338503335</v>
+        <v>46089.27338503472</v>
       </c>
     </row>
     <row r="216">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="H216" s="2" t="n">
-        <v>46087.27338503638</v>
+        <v>46087.27338503472</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>46092.27338503638</v>
+        <v>46092.27338503472</v>
       </c>
     </row>
     <row r="217">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="H217" s="2" t="n">
-        <v>46060.2733850396</v>
+        <v>46060.27338503472</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>46065.2733850396</v>
+        <v>46065.27338503472</v>
       </c>
     </row>
     <row r="218">
@@ -8936,10 +8936,10 @@
         </is>
       </c>
       <c r="H218" s="2" t="n">
-        <v>46059.27338504278</v>
+        <v>46059.2733850463</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>46064.27338504278</v>
+        <v>46064.2733850463</v>
       </c>
     </row>
     <row r="219">
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="H219" s="2" t="n">
-        <v>46062.27338504589</v>
+        <v>46062.2733850463</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>46067.27338504589</v>
+        <v>46067.2733850463</v>
       </c>
     </row>
     <row r="220">
@@ -9014,10 +9014,10 @@
         </is>
       </c>
       <c r="H220" s="2" t="n">
-        <v>46067.27338504892</v>
+        <v>46067.2733850463</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>46072.27338504892</v>
+        <v>46072.2733850463</v>
       </c>
     </row>
     <row r="221">
@@ -9053,10 +9053,10 @@
         </is>
       </c>
       <c r="H221" s="2" t="n">
-        <v>46078.27338505227</v>
+        <v>46078.27338505787</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>46083.27338505227</v>
+        <v>46083.27338505787</v>
       </c>
     </row>
     <row r="222">
@@ -9092,10 +9092,10 @@
         </is>
       </c>
       <c r="H222" s="2" t="n">
-        <v>46066.2733850553</v>
+        <v>46066.27338505787</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>46071.2733850553</v>
+        <v>46071.27338505787</v>
       </c>
     </row>
     <row r="223">
@@ -9131,10 +9131,10 @@
         </is>
       </c>
       <c r="H223" s="2" t="n">
-        <v>46085.2733850583</v>
+        <v>46085.27338505787</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>46090.2733850583</v>
+        <v>46090.27338505787</v>
       </c>
     </row>
     <row r="224">
@@ -9170,10 +9170,10 @@
         </is>
       </c>
       <c r="H224" s="2" t="n">
-        <v>46074.27338506135</v>
+        <v>46074.27338505787</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>46079.27338506135</v>
+        <v>46079.27338505787</v>
       </c>
     </row>
     <row r="225">
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="H225" s="2" t="n">
-        <v>46074.27338506468</v>
+        <v>46074.27338506944</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>46079.27338506468</v>
+        <v>46079.27338506944</v>
       </c>
     </row>
     <row r="226">
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="H226" s="2" t="n">
-        <v>46077.27338506793</v>
+        <v>46077.27338506944</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>46082.27338506793</v>
+        <v>46082.27338506944</v>
       </c>
     </row>
     <row r="227">
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="H227" s="2" t="n">
-        <v>46071.27338507105</v>
+        <v>46071.27338506944</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>46076.27338507105</v>
+        <v>46076.27338506944</v>
       </c>
     </row>
     <row r="228">
@@ -9326,10 +9326,10 @@
         </is>
       </c>
       <c r="H228" s="2" t="n">
-        <v>46088.27338507432</v>
+        <v>46088.27338506944</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>46093.27338507432</v>
+        <v>46093.27338506944</v>
       </c>
     </row>
     <row r="229">
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="H229" s="2" t="n">
-        <v>46062.27338507743</v>
+        <v>46062.27338508102</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>46067.27338507743</v>
+        <v>46067.27338508102</v>
       </c>
     </row>
     <row r="230">
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="H230" s="2" t="n">
-        <v>46066.27338508043</v>
+        <v>46066.27338508102</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>46071.27338508043</v>
+        <v>46071.27338508102</v>
       </c>
     </row>
     <row r="231">
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="H231" s="2" t="n">
-        <v>46064.27338508346</v>
+        <v>46064.27338508102</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>46069.27338508346</v>
+        <v>46069.27338508102</v>
       </c>
     </row>
     <row r="232">
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="H232" s="2" t="n">
-        <v>46081.2733850868</v>
+        <v>46081.27338508102</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>46086.2733850868</v>
+        <v>46086.27338508102</v>
       </c>
     </row>
     <row r="233">
@@ -9521,10 +9521,10 @@
         </is>
       </c>
       <c r="H233" s="2" t="n">
-        <v>46067.27338509</v>
+        <v>46067.27338509259</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>46072.27338509</v>
+        <v>46072.27338509259</v>
       </c>
     </row>
     <row r="234">
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="H234" s="2" t="n">
-        <v>46071.27338509307</v>
+        <v>46071.27338509259</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>46076.27338509307</v>
+        <v>46076.27338509259</v>
       </c>
     </row>
     <row r="235">
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="H235" s="2" t="n">
-        <v>46079.27338509616</v>
+        <v>46079.27338509259</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>46084.27338509616</v>
+        <v>46084.27338509259</v>
       </c>
     </row>
     <row r="236">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="H236" s="2" t="n">
-        <v>46073.27338509941</v>
+        <v>46073.27338510417</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>46078.27338509941</v>
+        <v>46078.27338510417</v>
       </c>
     </row>
     <row r="237">
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="H237" s="2" t="n">
-        <v>46060.27338510251</v>
+        <v>46060.27338510417</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>46065.27338510251</v>
+        <v>46065.27338510417</v>
       </c>
     </row>
     <row r="238">
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="H238" s="2" t="n">
-        <v>46077.27338510558</v>
+        <v>46077.27338510417</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>46082.27338510558</v>
+        <v>46082.27338510417</v>
       </c>
     </row>
     <row r="239">
@@ -9755,10 +9755,10 @@
         </is>
       </c>
       <c r="H239" s="2" t="n">
-        <v>46067.27338510856</v>
+        <v>46067.27338510417</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>46072.27338510856</v>
+        <v>46072.27338510417</v>
       </c>
     </row>
     <row r="240">
@@ -9794,10 +9794,10 @@
         </is>
       </c>
       <c r="H240" s="2" t="n">
-        <v>46080.27338511192</v>
+        <v>46080.27338511574</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>46085.27338511192</v>
+        <v>46085.27338511574</v>
       </c>
     </row>
     <row r="241">
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="H241" s="2" t="n">
-        <v>46081.27338511511</v>
+        <v>46081.27338511574</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>46086.27338511511</v>
+        <v>46086.27338511574</v>
       </c>
     </row>
     <row r="242">
@@ -9872,10 +9872,10 @@
         </is>
       </c>
       <c r="H242" s="2" t="n">
-        <v>46065.27338511809</v>
+        <v>46065.27338511574</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>46070.27338511809</v>
+        <v>46070.27338511574</v>
       </c>
     </row>
     <row r="243">
@@ -9911,10 +9911,10 @@
         </is>
       </c>
       <c r="H243" s="2" t="n">
-        <v>46068.27338512147</v>
+        <v>46068.27338511574</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>46073.27338512147</v>
+        <v>46073.27338511574</v>
       </c>
     </row>
     <row r="244">
@@ -9950,10 +9950,10 @@
         </is>
       </c>
       <c r="H244" s="2" t="n">
-        <v>46060.27338512448</v>
+        <v>46060.27338512732</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>46065.27338512448</v>
+        <v>46065.27338512732</v>
       </c>
     </row>
     <row r="245">
@@ -9989,10 +9989,10 @@
         </is>
       </c>
       <c r="H245" s="2" t="n">
-        <v>46063.27338512751</v>
+        <v>46063.27338512732</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>46068.27338512751</v>
+        <v>46068.27338512732</v>
       </c>
     </row>
     <row r="246">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="H246" s="2" t="n">
-        <v>46079.27338513055</v>
+        <v>46079.27338512732</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>46084.27338513055</v>
+        <v>46084.27338512732</v>
       </c>
     </row>
     <row r="247">
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="H247" s="2" t="n">
-        <v>46080.27338513376</v>
+        <v>46080.27338513889</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>46085.27338513376</v>
+        <v>46085.27338513889</v>
       </c>
     </row>
     <row r="248">
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="H248" s="2" t="n">
-        <v>46063.27338513682</v>
+        <v>46063.27338513889</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>46068.27338513682</v>
+        <v>46068.27338513889</v>
       </c>
     </row>
     <row r="249">
@@ -10145,10 +10145,10 @@
         </is>
       </c>
       <c r="H249" s="2" t="n">
-        <v>46060.27338513995</v>
+        <v>46060.27338513889</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>46065.27338513995</v>
+        <v>46065.27338513889</v>
       </c>
     </row>
     <row r="250">
@@ -10184,10 +10184,10 @@
         </is>
       </c>
       <c r="H250" s="2" t="n">
-        <v>46066.27338514305</v>
+        <v>46066.27338513889</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>46071.27338514305</v>
+        <v>46071.27338513889</v>
       </c>
     </row>
     <row r="251">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="H251" s="2" t="n">
-        <v>46067.27338514624</v>
+        <v>46067.27338515046</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>46072.27338514624</v>
+        <v>46072.27338515046</v>
       </c>
     </row>
     <row r="252">
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="H252" s="2" t="n">
-        <v>46067.27338514926</v>
+        <v>46067.27338515046</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>46072.27338514926</v>
+        <v>46072.27338515046</v>
       </c>
     </row>
     <row r="253">
@@ -10301,10 +10301,10 @@
         </is>
       </c>
       <c r="H253" s="2" t="n">
-        <v>46078.2733851523</v>
+        <v>46078.27338515046</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>46083.2733851523</v>
+        <v>46083.27338515046</v>
       </c>
     </row>
     <row r="254">
@@ -10340,10 +10340,10 @@
         </is>
       </c>
       <c r="H254" s="2" t="n">
-        <v>46079.27338515559</v>
+        <v>46079.27338515046</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>46084.27338515559</v>
+        <v>46084.27338515046</v>
       </c>
     </row>
     <row r="255">
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="H255" s="2" t="n">
-        <v>46087.27338515866</v>
+        <v>46087.27338516204</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>46092.27338515866</v>
+        <v>46092.27338516204</v>
       </c>
     </row>
     <row r="256">
@@ -10418,10 +10418,10 @@
         </is>
       </c>
       <c r="H256" s="2" t="n">
-        <v>46066.27338516166</v>
+        <v>46066.27338516204</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>46071.27338516166</v>
+        <v>46071.27338516204</v>
       </c>
     </row>
     <row r="257">
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="H257" s="2" t="n">
-        <v>46070.27338516464</v>
+        <v>46070.27338516204</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>46075.27338516464</v>
+        <v>46075.27338516204</v>
       </c>
     </row>
     <row r="258">
@@ -10496,10 +10496,10 @@
         </is>
       </c>
       <c r="H258" s="2" t="n">
-        <v>46071.27338516799</v>
+        <v>46071.27338517361</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>46076.27338516799</v>
+        <v>46076.27338517361</v>
       </c>
     </row>
     <row r="259">
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="H259" s="2" t="n">
-        <v>46071.27338517116</v>
+        <v>46071.27338517361</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>46076.27338517116</v>
+        <v>46076.27338517361</v>
       </c>
     </row>
     <row r="260">
@@ -10574,10 +10574,10 @@
         </is>
       </c>
       <c r="H260" s="2" t="n">
-        <v>46065.27338517434</v>
+        <v>46065.27338517361</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>46070.27338517434</v>
+        <v>46070.27338517361</v>
       </c>
     </row>
     <row r="261">
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="H261" s="2" t="n">
-        <v>46065.27338517747</v>
+        <v>46065.27338517361</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>46070.27338517747</v>
+        <v>46070.27338517361</v>
       </c>
     </row>
     <row r="262">
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="H262" s="2" t="n">
-        <v>46080.27338518075</v>
+        <v>46080.27338518519</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>46085.27338518075</v>
+        <v>46085.27338518519</v>
       </c>
     </row>
     <row r="263">
@@ -10691,10 +10691,10 @@
         </is>
       </c>
       <c r="H263" s="2" t="n">
-        <v>46066.27338518508</v>
+        <v>46066.27338518519</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>46071.27338518508</v>
+        <v>46071.27338518519</v>
       </c>
     </row>
     <row r="264">
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="H264" s="2" t="n">
-        <v>46061.27338518827</v>
+        <v>46061.27338518519</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>46066.27338518827</v>
+        <v>46066.27338518519</v>
       </c>
     </row>
     <row r="265">
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="H265" s="2" t="n">
-        <v>46082.27338519215</v>
+        <v>46082.27338519676</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>46087.27338519215</v>
+        <v>46087.27338519676</v>
       </c>
     </row>
     <row r="266">
@@ -10808,10 +10808,10 @@
         </is>
       </c>
       <c r="H266" s="2" t="n">
-        <v>46080.27338519534</v>
+        <v>46080.27338519676</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>46085.27338519534</v>
+        <v>46085.27338519676</v>
       </c>
     </row>
     <row r="267">
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="H267" s="2" t="n">
-        <v>46061.27338519838</v>
+        <v>46061.27338519676</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>46066.27338519838</v>
+        <v>46066.27338519676</v>
       </c>
     </row>
     <row r="268">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="H268" s="2" t="n">
-        <v>46082.27338520168</v>
+        <v>46082.27338519676</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>46087.27338520168</v>
+        <v>46087.27338519676</v>
       </c>
     </row>
     <row r="269">
@@ -10925,10 +10925,10 @@
         </is>
       </c>
       <c r="H269" s="2" t="n">
-        <v>46063.27338520473</v>
+        <v>46063.27338520833</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>46068.27338520473</v>
+        <v>46068.27338520833</v>
       </c>
     </row>
     <row r="270">
@@ -10964,10 +10964,10 @@
         </is>
       </c>
       <c r="H270" s="2" t="n">
-        <v>46066.27338520788</v>
+        <v>46066.27338520833</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>46071.27338520788</v>
+        <v>46071.27338520833</v>
       </c>
     </row>
     <row r="271">
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="H271" s="2" t="n">
-        <v>46059.27338521123</v>
+        <v>46059.27338520833</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>46064.27338521123</v>
+        <v>46064.27338520833</v>
       </c>
     </row>
     <row r="272">
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="H272" s="2" t="n">
-        <v>46064.2733852145</v>
+        <v>46064.27338521991</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>46069.2733852145</v>
+        <v>46069.27338521991</v>
       </c>
     </row>
     <row r="273">
@@ -11081,10 +11081,10 @@
         </is>
       </c>
       <c r="H273" s="2" t="n">
-        <v>46068.27338521754</v>
+        <v>46068.27338521991</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>46073.27338521754</v>
+        <v>46073.27338521991</v>
       </c>
     </row>
     <row r="274">
@@ -11120,10 +11120,10 @@
         </is>
       </c>
       <c r="H274" s="2" t="n">
-        <v>46084.27338522072</v>
+        <v>46084.27338521991</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>46089.27338522072</v>
+        <v>46089.27338521991</v>
       </c>
     </row>
     <row r="275">
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="H275" s="2" t="n">
-        <v>46073.27338522377</v>
+        <v>46073.27338521991</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>46078.27338522377</v>
+        <v>46078.27338521991</v>
       </c>
     </row>
     <row r="276">
@@ -11198,10 +11198,10 @@
         </is>
       </c>
       <c r="H276" s="2" t="n">
-        <v>46082.27338522718</v>
+        <v>46082.27338523149</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>46087.27338522718</v>
+        <v>46087.27338523149</v>
       </c>
     </row>
     <row r="277">
@@ -11237,10 +11237,10 @@
         </is>
       </c>
       <c r="H277" s="2" t="n">
-        <v>46084.27338523039</v>
+        <v>46084.27338523149</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>46089.27338523039</v>
+        <v>46089.27338523149</v>
       </c>
     </row>
     <row r="278">
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="H278" s="2" t="n">
-        <v>46066.27338523365</v>
+        <v>46066.27338523149</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>46071.27338523365</v>
+        <v>46071.27338523149</v>
       </c>
     </row>
     <row r="279">
@@ -11315,10 +11315,10 @@
         </is>
       </c>
       <c r="H279" s="2" t="n">
-        <v>46081.27338523684</v>
+        <v>46081.27338523149</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>46086.27338523684</v>
+        <v>46086.27338523149</v>
       </c>
     </row>
     <row r="280">
@@ -11354,10 +11354,10 @@
         </is>
       </c>
       <c r="H280" s="2" t="n">
-        <v>46061.27338523992</v>
+        <v>46061.27338524305</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>46066.27338523992</v>
+        <v>46066.27338524305</v>
       </c>
     </row>
     <row r="281">
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="H281" s="2" t="n">
-        <v>46071.27338524309</v>
+        <v>46071.27338524305</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>46076.27338524309</v>
+        <v>46076.27338524305</v>
       </c>
     </row>
     <row r="282">
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="H282" s="2" t="n">
-        <v>46066.27338524616</v>
+        <v>46066.27338524305</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>46071.27338524616</v>
+        <v>46071.27338524305</v>
       </c>
     </row>
     <row r="283">
@@ -11471,10 +11471,10 @@
         </is>
       </c>
       <c r="H283" s="2" t="n">
-        <v>46060.27338524933</v>
+        <v>46060.27338525463</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>46065.27338524933</v>
+        <v>46065.27338525463</v>
       </c>
     </row>
     <row r="284">
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="H284" s="2" t="n">
-        <v>46085.27338525236</v>
+        <v>46085.27338525463</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>46090.27338525236</v>
+        <v>46090.27338525463</v>
       </c>
     </row>
     <row r="285">
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="H285" s="2" t="n">
-        <v>46082.27338525549</v>
+        <v>46082.27338525463</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>46087.27338525549</v>
+        <v>46087.27338525463</v>
       </c>
     </row>
     <row r="286">
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="H286" s="2" t="n">
-        <v>46059.27338525849</v>
+        <v>46059.27338525463</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>46064.27338525849</v>
+        <v>46064.27338525463</v>
       </c>
     </row>
     <row r="287">
@@ -11627,10 +11627,10 @@
         </is>
       </c>
       <c r="H287" s="2" t="n">
-        <v>46084.27338526186</v>
+        <v>46084.27338526621</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>46089.27338526186</v>
+        <v>46089.27338526621</v>
       </c>
     </row>
     <row r="288">
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="H288" s="2" t="n">
-        <v>46060.27338526488</v>
+        <v>46060.27338526621</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>46065.27338526488</v>
+        <v>46065.27338526621</v>
       </c>
     </row>
     <row r="289">
@@ -11705,10 +11705,10 @@
         </is>
       </c>
       <c r="H289" s="2" t="n">
-        <v>46085.27338526789</v>
+        <v>46085.27338526621</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>46090.27338526789</v>
+        <v>46090.27338526621</v>
       </c>
     </row>
     <row r="290">
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="H290" s="2" t="n">
-        <v>46066.2733852711</v>
+        <v>46066.27338526621</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>46071.2733852711</v>
+        <v>46071.27338526621</v>
       </c>
     </row>
     <row r="291">
@@ -11783,10 +11783,10 @@
         </is>
       </c>
       <c r="H291" s="2" t="n">
-        <v>46076.27338527414</v>
+        <v>46076.27338527777</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>46081.27338527414</v>
+        <v>46081.27338527777</v>
       </c>
     </row>
     <row r="292">
@@ -11822,10 +11822,10 @@
         </is>
       </c>
       <c r="H292" s="2" t="n">
-        <v>46060.27338527722</v>
+        <v>46060.27338527777</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>46065.27338527722</v>
+        <v>46065.27338527777</v>
       </c>
     </row>
     <row r="293">
@@ -11861,10 +11861,10 @@
         </is>
       </c>
       <c r="H293" s="2" t="n">
-        <v>46065.27338528029</v>
+        <v>46065.27338527777</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>46070.27338528029</v>
+        <v>46070.27338527777</v>
       </c>
     </row>
     <row r="294">
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="H294" s="2" t="n">
-        <v>46060.27338528349</v>
+        <v>46060.27338527777</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>46065.27338528349</v>
+        <v>46065.27338527777</v>
       </c>
     </row>
     <row r="295">
@@ -11939,10 +11939,10 @@
         </is>
       </c>
       <c r="H295" s="2" t="n">
-        <v>46079.27338528657</v>
+        <v>46079.27338528935</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>46084.27338528657</v>
+        <v>46084.27338528935</v>
       </c>
     </row>
     <row r="296">
@@ -11978,10 +11978,10 @@
         </is>
       </c>
       <c r="H296" s="2" t="n">
-        <v>46066.27338528957</v>
+        <v>46066.27338528935</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>46071.27338528957</v>
+        <v>46071.27338528935</v>
       </c>
     </row>
     <row r="297">
@@ -12017,10 +12017,10 @@
         </is>
       </c>
       <c r="H297" s="2" t="n">
-        <v>46079.27338529281</v>
+        <v>46079.27338528935</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>46084.27338529281</v>
+        <v>46084.27338528935</v>
       </c>
     </row>
     <row r="298">
@@ -12056,10 +12056,10 @@
         </is>
       </c>
       <c r="H298" s="2" t="n">
-        <v>46080.27338529602</v>
+        <v>46080.27338530093</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>46085.27338529602</v>
+        <v>46085.27338530093</v>
       </c>
     </row>
     <row r="299">
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="H299" s="2" t="n">
-        <v>46065.2733852993</v>
+        <v>46065.27338530093</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>46070.2733852993</v>
+        <v>46070.27338530093</v>
       </c>
     </row>
     <row r="300">
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="H300" s="2" t="n">
-        <v>46076.27338530245</v>
+        <v>46076.27338530093</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>46081.27338530245</v>
+        <v>46081.27338530093</v>
       </c>
     </row>
     <row r="301">
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="H301" s="2" t="n">
-        <v>46072.27338530582</v>
+        <v>46072.27338530093</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>46077.27338530582</v>
+        <v>46077.27338530093</v>
       </c>
     </row>
     <row r="302">
@@ -12212,10 +12212,10 @@
         </is>
       </c>
       <c r="H302" s="2" t="n">
-        <v>46077.27338530904</v>
+        <v>46077.2733853125</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>46082.27338530904</v>
+        <v>46082.2733853125</v>
       </c>
     </row>
     <row r="303">
@@ -12251,10 +12251,10 @@
         </is>
       </c>
       <c r="H303" s="2" t="n">
-        <v>46061.27338531227</v>
+        <v>46061.2733853125</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>46066.27338531227</v>
+        <v>46066.2733853125</v>
       </c>
     </row>
     <row r="304">
@@ -12290,10 +12290,10 @@
         </is>
       </c>
       <c r="H304" s="2" t="n">
-        <v>46063.27338531531</v>
+        <v>46063.2733853125</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>46068.27338531531</v>
+        <v>46068.2733853125</v>
       </c>
     </row>
     <row r="305">
@@ -12329,10 +12329,10 @@
         </is>
       </c>
       <c r="H305" s="2" t="n">
-        <v>46082.27338531856</v>
+        <v>46082.27338532407</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>46087.27338531856</v>
+        <v>46087.27338532407</v>
       </c>
     </row>
     <row r="306">
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="H306" s="2" t="n">
-        <v>46067.27338532171</v>
+        <v>46067.27338532407</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>46072.27338532171</v>
+        <v>46072.27338532407</v>
       </c>
     </row>
     <row r="307">
@@ -12407,10 +12407,10 @@
         </is>
       </c>
       <c r="H307" s="2" t="n">
-        <v>46082.27338532489</v>
+        <v>46082.27338532407</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>46087.27338532489</v>
+        <v>46087.27338532407</v>
       </c>
     </row>
     <row r="308">
@@ -12446,10 +12446,10 @@
         </is>
       </c>
       <c r="H308" s="2" t="n">
-        <v>46066.27338532791</v>
+        <v>46066.27338532407</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>46071.27338532791</v>
+        <v>46071.27338532407</v>
       </c>
     </row>
     <row r="309">
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="H309" s="2" t="n">
-        <v>46087.2733853313</v>
+        <v>46087.27338533565</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>46092.2733853313</v>
+        <v>46092.27338533565</v>
       </c>
     </row>
     <row r="310">
@@ -12524,10 +12524,10 @@
         </is>
       </c>
       <c r="H310" s="2" t="n">
-        <v>46071.27338533432</v>
+        <v>46071.27338533565</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>46076.27338533432</v>
+        <v>46076.27338533565</v>
       </c>
     </row>
     <row r="311">
@@ -12563,10 +12563,10 @@
         </is>
       </c>
       <c r="H311" s="2" t="n">
-        <v>46077.27338533768</v>
+        <v>46077.27338533565</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>46082.27338533768</v>
+        <v>46082.27338533565</v>
       </c>
     </row>
     <row r="312">
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="H312" s="2" t="n">
-        <v>46067.27338534082</v>
+        <v>46067.27338533565</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>46072.27338534082</v>
+        <v>46072.27338533565</v>
       </c>
     </row>
     <row r="313">
@@ -12641,10 +12641,10 @@
         </is>
       </c>
       <c r="H313" s="2" t="n">
-        <v>46059.27338534386</v>
+        <v>46059.27338534722</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>46064.27338534386</v>
+        <v>46064.27338534722</v>
       </c>
     </row>
     <row r="314">
@@ -12680,10 +12680,10 @@
         </is>
       </c>
       <c r="H314" s="2" t="n">
-        <v>46083.27338534707</v>
+        <v>46083.27338534722</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>46088.27338534707</v>
+        <v>46088.27338534722</v>
       </c>
     </row>
     <row r="315">
@@ -12719,10 +12719,10 @@
         </is>
       </c>
       <c r="H315" s="2" t="n">
-        <v>46067.27338535023</v>
+        <v>46067.27338534722</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>46072.27338535023</v>
+        <v>46072.27338534722</v>
       </c>
     </row>
     <row r="316">
@@ -12758,10 +12758,10 @@
         </is>
       </c>
       <c r="H316" s="2" t="n">
-        <v>46085.27338535359</v>
+        <v>46085.2733853588</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>46090.27338535359</v>
+        <v>46090.2733853588</v>
       </c>
     </row>
     <row r="317">
@@ -12797,10 +12797,10 @@
         </is>
       </c>
       <c r="H317" s="2" t="n">
-        <v>46073.27338535673</v>
+        <v>46073.2733853588</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>46078.27338535673</v>
+        <v>46078.2733853588</v>
       </c>
     </row>
     <row r="318">
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="H318" s="2" t="n">
-        <v>46067.27338535972</v>
+        <v>46067.2733853588</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>46072.27338535972</v>
+        <v>46072.2733853588</v>
       </c>
     </row>
     <row r="319">
@@ -12875,10 +12875,10 @@
         </is>
       </c>
       <c r="H319" s="2" t="n">
-        <v>46084.27338536282</v>
+        <v>46084.2733853588</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>46089.27338536282</v>
+        <v>46089.2733853588</v>
       </c>
     </row>
     <row r="320">
@@ -12914,10 +12914,10 @@
         </is>
       </c>
       <c r="H320" s="2" t="n">
-        <v>46081.27338536603</v>
+        <v>46081.27338537037</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>46086.27338536603</v>
+        <v>46086.27338537037</v>
       </c>
     </row>
     <row r="321">
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="H321" s="2" t="n">
-        <v>46086.27338536912</v>
+        <v>46086.27338537037</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>46091.27338536912</v>
+        <v>46091.27338537037</v>
       </c>
     </row>
     <row r="322">
@@ -12992,10 +12992,10 @@
         </is>
       </c>
       <c r="H322" s="2" t="n">
-        <v>46073.2733853722</v>
+        <v>46073.27338537037</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>46078.2733853722</v>
+        <v>46078.27338537037</v>
       </c>
     </row>
     <row r="323">
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="H323" s="2" t="n">
-        <v>46064.27338537537</v>
+        <v>46064.27338537037</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>46069.27338537537</v>
+        <v>46069.27338537037</v>
       </c>
     </row>
     <row r="324">
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="H324" s="2" t="n">
-        <v>46078.27338537854</v>
+        <v>46078.27338538194</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>46083.27338537854</v>
+        <v>46083.27338538194</v>
       </c>
     </row>
     <row r="325">
@@ -13109,10 +13109,10 @@
         </is>
       </c>
       <c r="H325" s="2" t="n">
-        <v>46084.2733853817</v>
+        <v>46084.27338538194</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>46089.2733853817</v>
+        <v>46089.27338538194</v>
       </c>
     </row>
     <row r="326">
@@ -13148,10 +13148,10 @@
         </is>
       </c>
       <c r="H326" s="2" t="n">
-        <v>46068.27338538492</v>
+        <v>46068.27338538194</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>46073.27338538492</v>
+        <v>46073.27338538194</v>
       </c>
     </row>
     <row r="327">
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="H327" s="2" t="n">
-        <v>46079.27338538808</v>
+        <v>46079.27338539352</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>46084.27338538808</v>
+        <v>46084.27338539352</v>
       </c>
     </row>
     <row r="328">
@@ -13226,10 +13226,10 @@
         </is>
       </c>
       <c r="H328" s="2" t="n">
-        <v>46085.27338539127</v>
+        <v>46085.27338539352</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>46090.27338539127</v>
+        <v>46090.27338539352</v>
       </c>
     </row>
     <row r="329">
@@ -13265,10 +13265,10 @@
         </is>
       </c>
       <c r="H329" s="2" t="n">
-        <v>46064.27338539435</v>
+        <v>46064.27338539352</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>46069.27338539435</v>
+        <v>46069.27338539352</v>
       </c>
     </row>
     <row r="330">
@@ -13304,10 +13304,10 @@
         </is>
       </c>
       <c r="H330" s="2" t="n">
-        <v>46088.2733853973</v>
+        <v>46088.27338539352</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>46093.2733853973</v>
+        <v>46093.27338539352</v>
       </c>
     </row>
     <row r="331">
@@ -13343,10 +13343,10 @@
         </is>
       </c>
       <c r="H331" s="2" t="n">
-        <v>46069.27338540064</v>
+        <v>46069.27338540509</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>46074.27338540064</v>
+        <v>46074.27338540509</v>
       </c>
     </row>
     <row r="332">
@@ -13382,10 +13382,10 @@
         </is>
       </c>
       <c r="H332" s="2" t="n">
-        <v>46062.27338540367</v>
+        <v>46062.27338540509</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>46067.27338540367</v>
+        <v>46067.27338540509</v>
       </c>
     </row>
     <row r="333">
@@ -13421,10 +13421,10 @@
         </is>
       </c>
       <c r="H333" s="2" t="n">
-        <v>46072.27338540673</v>
+        <v>46072.27338540509</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>46077.27338540673</v>
+        <v>46077.27338540509</v>
       </c>
     </row>
     <row r="334">
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="H334" s="2" t="n">
-        <v>46082.27338541006</v>
+        <v>46082.27338540509</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>46087.27338541006</v>
+        <v>46087.27338540509</v>
       </c>
     </row>
     <row r="335">
@@ -13499,10 +13499,10 @@
         </is>
       </c>
       <c r="H335" s="2" t="n">
-        <v>46077.27338541315</v>
+        <v>46077.27338541667</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>46082.27338541315</v>
+        <v>46082.27338541667</v>
       </c>
     </row>
     <row r="336">
@@ -13538,10 +13538,10 @@
         </is>
       </c>
       <c r="H336" s="2" t="n">
-        <v>46079.27338541641</v>
+        <v>46079.27338541667</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>46084.27338541641</v>
+        <v>46084.27338541667</v>
       </c>
     </row>
     <row r="337">
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="H337" s="2" t="n">
-        <v>46065.27338541944</v>
+        <v>46065.27338541667</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>46070.27338541944</v>
+        <v>46070.27338541667</v>
       </c>
     </row>
     <row r="338">
@@ -13616,10 +13616,10 @@
         </is>
       </c>
       <c r="H338" s="2" t="n">
-        <v>46066.2733854228</v>
+        <v>46066.27338542824</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>46071.2733854228</v>
+        <v>46071.27338542824</v>
       </c>
     </row>
     <row r="339">
@@ -13655,10 +13655,10 @@
         </is>
       </c>
       <c r="H339" s="2" t="n">
-        <v>46084.27338542591</v>
+        <v>46084.27338542824</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>46089.27338542591</v>
+        <v>46089.27338542824</v>
       </c>
     </row>
     <row r="340">
@@ -13694,10 +13694,10 @@
         </is>
       </c>
       <c r="H340" s="2" t="n">
-        <v>46079.27338542897</v>
+        <v>46079.27338542824</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>46084.27338542897</v>
+        <v>46084.27338542824</v>
       </c>
     </row>
     <row r="341">
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="H341" s="2" t="n">
-        <v>46069.27338543216</v>
+        <v>46069.27338542824</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>46074.27338543216</v>
+        <v>46074.27338542824</v>
       </c>
     </row>
     <row r="342">
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="H342" s="2" t="n">
-        <v>46085.2733854355</v>
+        <v>46085.27338543982</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>46090.2733854355</v>
+        <v>46090.27338543982</v>
       </c>
     </row>
     <row r="343">
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="H343" s="2" t="n">
-        <v>46072.27338543857</v>
+        <v>46072.27338543982</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>46077.27338543857</v>
+        <v>46077.27338543982</v>
       </c>
     </row>
     <row r="344">
@@ -13850,10 +13850,10 @@
         </is>
       </c>
       <c r="H344" s="2" t="n">
-        <v>46069.27338544155</v>
+        <v>46069.27338543982</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>46074.27338544155</v>
+        <v>46074.27338543982</v>
       </c>
     </row>
     <row r="345">
@@ -13889,10 +13889,10 @@
         </is>
       </c>
       <c r="H345" s="2" t="n">
-        <v>46079.2733854449</v>
+        <v>46079.27338543982</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>46084.2733854449</v>
+        <v>46084.27338543982</v>
       </c>
     </row>
     <row r="346">
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="H346" s="2" t="n">
-        <v>46088.27338544797</v>
+        <v>46088.27338545139</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>46093.27338544797</v>
+        <v>46093.27338545139</v>
       </c>
     </row>
     <row r="347">
@@ -13967,10 +13967,10 @@
         </is>
       </c>
       <c r="H347" s="2" t="n">
-        <v>46059.27338545102</v>
+        <v>46059.27338545139</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>46064.27338545102</v>
+        <v>46064.27338545139</v>
       </c>
     </row>
     <row r="348">
@@ -14006,10 +14006,10 @@
         </is>
       </c>
       <c r="H348" s="2" t="n">
-        <v>46087.27338545422</v>
+        <v>46087.27338545139</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>46092.27338545422</v>
+        <v>46092.27338545139</v>
       </c>
     </row>
     <row r="349">
@@ -14045,10 +14045,10 @@
         </is>
       </c>
       <c r="H349" s="2" t="n">
-        <v>46073.27338545902</v>
+        <v>46073.27338546296</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>46078.27338545902</v>
+        <v>46078.27338546296</v>
       </c>
     </row>
     <row r="350">
@@ -14084,10 +14084,10 @@
         </is>
       </c>
       <c r="H350" s="2" t="n">
-        <v>46084.27338546223</v>
+        <v>46084.27338546296</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>46089.27338546223</v>
+        <v>46089.27338546296</v>
       </c>
     </row>
     <row r="351">
@@ -14123,10 +14123,10 @@
         </is>
       </c>
       <c r="H351" s="2" t="n">
-        <v>46062.27338546528</v>
+        <v>46062.27338546296</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>46067.27338546528</v>
+        <v>46067.27338546296</v>
       </c>
     </row>
     <row r="352">
@@ -14162,10 +14162,10 @@
         </is>
       </c>
       <c r="H352" s="2" t="n">
-        <v>46077.2733854686</v>
+        <v>46077.27338546296</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>46082.2733854686</v>
+        <v>46082.27338546296</v>
       </c>
     </row>
     <row r="353">
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="H353" s="2" t="n">
-        <v>46082.2733854717</v>
+        <v>46082.27338547454</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>46087.2733854717</v>
+        <v>46087.27338547454</v>
       </c>
     </row>
     <row r="354">
@@ -14240,10 +14240,10 @@
         </is>
       </c>
       <c r="H354" s="2" t="n">
-        <v>46075.27338547476</v>
+        <v>46075.27338547454</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>46080.27338547476</v>
+        <v>46080.27338547454</v>
       </c>
     </row>
     <row r="355">
@@ -14279,10 +14279,10 @@
         </is>
       </c>
       <c r="H355" s="2" t="n">
-        <v>46078.27338547802</v>
+        <v>46078.27338547454</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>46083.27338547802</v>
+        <v>46083.27338547454</v>
       </c>
     </row>
     <row r="356">
@@ -14318,10 +14318,10 @@
         </is>
       </c>
       <c r="H356" s="2" t="n">
-        <v>46071.27338548119</v>
+        <v>46071.27338548611</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>46076.27338548119</v>
+        <v>46076.27338548611</v>
       </c>
     </row>
     <row r="357">
@@ -14357,10 +14357,10 @@
         </is>
       </c>
       <c r="H357" s="2" t="n">
-        <v>46077.27338548433</v>
+        <v>46077.27338548611</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>46082.27338548433</v>
+        <v>46082.27338548611</v>
       </c>
     </row>
     <row r="358">
@@ -14396,10 +14396,10 @@
         </is>
       </c>
       <c r="H358" s="2" t="n">
-        <v>46063.27338548753</v>
+        <v>46063.27338548611</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>46068.27338548753</v>
+        <v>46068.27338548611</v>
       </c>
     </row>
     <row r="359">
@@ -14435,10 +14435,10 @@
         </is>
       </c>
       <c r="H359" s="2" t="n">
-        <v>46063.27338549082</v>
+        <v>46063.27338548611</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>46068.27338549082</v>
+        <v>46068.27338548611</v>
       </c>
     </row>
     <row r="360">
@@ -14474,10 +14474,10 @@
         </is>
       </c>
       <c r="H360" s="2" t="n">
-        <v>46063.27338549398</v>
+        <v>46063.27338549768</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>46068.27338549398</v>
+        <v>46068.27338549768</v>
       </c>
     </row>
     <row r="361">
@@ -14513,10 +14513,10 @@
         </is>
       </c>
       <c r="H361" s="2" t="n">
-        <v>46083.27338549703</v>
+        <v>46083.27338549768</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>46088.27338549703</v>
+        <v>46088.27338549768</v>
       </c>
     </row>
     <row r="362">
@@ -14552,10 +14552,10 @@
         </is>
       </c>
       <c r="H362" s="2" t="n">
-        <v>46075.27338550008</v>
+        <v>46075.27338549768</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>46080.27338550008</v>
+        <v>46080.27338549768</v>
       </c>
     </row>
     <row r="363">
@@ -14591,10 +14591,10 @@
         </is>
       </c>
       <c r="H363" s="2" t="n">
-        <v>46066.27338550336</v>
+        <v>46066.27338549768</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>46071.27338550336</v>
+        <v>46071.27338549768</v>
       </c>
     </row>
     <row r="364">
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="H364" s="2" t="n">
-        <v>46067.27338550641</v>
+        <v>46067.27338550926</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>46072.27338550641</v>
+        <v>46072.27338550926</v>
       </c>
     </row>
     <row r="365">
@@ -14669,10 +14669,10 @@
         </is>
       </c>
       <c r="H365" s="2" t="n">
-        <v>46070.27338550953</v>
+        <v>46070.27338550926</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>46075.27338550953</v>
+        <v>46075.27338550926</v>
       </c>
     </row>
     <row r="366">
@@ -14708,10 +14708,10 @@
         </is>
       </c>
       <c r="H366" s="2" t="n">
-        <v>46080.27338551251</v>
+        <v>46080.27338550926</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>46085.27338551251</v>
+        <v>46085.27338550926</v>
       </c>
     </row>
     <row r="367">
@@ -14747,10 +14747,10 @@
         </is>
       </c>
       <c r="H367" s="2" t="n">
-        <v>46070.27338551587</v>
+        <v>46070.27338552084</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>46075.27338551587</v>
+        <v>46075.27338552084</v>
       </c>
     </row>
     <row r="368">
@@ -14786,10 +14786,10 @@
         </is>
       </c>
       <c r="H368" s="2" t="n">
-        <v>46064.27338551888</v>
+        <v>46064.27338552084</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>46069.27338551888</v>
+        <v>46069.27338552084</v>
       </c>
     </row>
     <row r="369">
@@ -14825,10 +14825,10 @@
         </is>
       </c>
       <c r="H369" s="2" t="n">
-        <v>46065.27338552188</v>
+        <v>46065.27338552084</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>46070.27338552188</v>
+        <v>46070.27338552084</v>
       </c>
     </row>
     <row r="370">
@@ -14864,10 +14864,10 @@
         </is>
       </c>
       <c r="H370" s="2" t="n">
-        <v>46068.27338552497</v>
+        <v>46068.27338552084</v>
       </c>
       <c r="I370" s="2" t="n">
-        <v>46073.27338552497</v>
+        <v>46073.27338552084</v>
       </c>
     </row>
     <row r="371">
@@ -14903,10 +14903,10 @@
         </is>
       </c>
       <c r="H371" s="2" t="n">
-        <v>46072.27338552813</v>
+        <v>46072.2733855324</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>46077.27338552813</v>
+        <v>46077.2733855324</v>
       </c>
     </row>
     <row r="372">
@@ -14942,10 +14942,10 @@
         </is>
       </c>
       <c r="H372" s="2" t="n">
-        <v>46070.27338553128</v>
+        <v>46070.2733855324</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>46075.27338553128</v>
+        <v>46075.2733855324</v>
       </c>
     </row>
     <row r="373">
@@ -14981,10 +14981,10 @@
         </is>
       </c>
       <c r="H373" s="2" t="n">
-        <v>46061.27338553428</v>
+        <v>46061.2733855324</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>46066.27338553428</v>
+        <v>46066.2733855324</v>
       </c>
     </row>
     <row r="374">
@@ -15020,10 +15020,10 @@
         </is>
       </c>
       <c r="H374" s="2" t="n">
-        <v>46077.27338553743</v>
+        <v>46077.2733855324</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>46082.27338553743</v>
+        <v>46082.2733855324</v>
       </c>
     </row>
     <row r="375">
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="H375" s="2" t="n">
-        <v>46088.27338554053</v>
+        <v>46088.27338554398</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>46093.27338554053</v>
+        <v>46093.27338554398</v>
       </c>
     </row>
     <row r="376">
@@ -15098,10 +15098,10 @@
         </is>
       </c>
       <c r="H376" s="2" t="n">
-        <v>46081.27338554369</v>
+        <v>46081.27338554398</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>46086.27338554369</v>
+        <v>46086.27338554398</v>
       </c>
     </row>
     <row r="377">
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="H377" s="2" t="n">
-        <v>46076.27338554677</v>
+        <v>46076.27338554398</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>46081.27338554677</v>
+        <v>46081.27338554398</v>
       </c>
     </row>
     <row r="378">
@@ -15176,10 +15176,10 @@
         </is>
       </c>
       <c r="H378" s="2" t="n">
-        <v>46069.27338555005</v>
+        <v>46069.27338555556</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>46074.27338555005</v>
+        <v>46074.27338555556</v>
       </c>
     </row>
     <row r="379">
@@ -15215,10 +15215,10 @@
         </is>
       </c>
       <c r="H379" s="2" t="n">
-        <v>46075.27338555313</v>
+        <v>46075.27338555556</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>46080.27338555313</v>
+        <v>46080.27338555556</v>
       </c>
     </row>
     <row r="380">
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="H380" s="2" t="n">
-        <v>46065.27338555619</v>
+        <v>46065.27338555556</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>46070.27338555619</v>
+        <v>46070.27338555556</v>
       </c>
     </row>
     <row r="381">
@@ -15293,10 +15293,10 @@
         </is>
       </c>
       <c r="H381" s="2" t="n">
-        <v>46067.27338555941</v>
+        <v>46067.27338555556</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>46072.27338555941</v>
+        <v>46072.27338555556</v>
       </c>
     </row>
     <row r="382">
@@ -15332,10 +15332,10 @@
         </is>
       </c>
       <c r="H382" s="2" t="n">
-        <v>46072.27338556272</v>
+        <v>46072.27338556713</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>46077.27338556272</v>
+        <v>46077.27338556713</v>
       </c>
     </row>
     <row r="383">
@@ -15371,10 +15371,10 @@
         </is>
       </c>
       <c r="H383" s="2" t="n">
-        <v>46061.27338556587</v>
+        <v>46061.27338556713</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>46066.27338556587</v>
+        <v>46066.27338556713</v>
       </c>
     </row>
     <row r="384">
@@ -15410,10 +15410,10 @@
         </is>
       </c>
       <c r="H384" s="2" t="n">
-        <v>46069.27338556896</v>
+        <v>46069.27338556713</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>46074.27338556896</v>
+        <v>46074.27338556713</v>
       </c>
     </row>
     <row r="385">
@@ -15449,10 +15449,10 @@
         </is>
       </c>
       <c r="H385" s="2" t="n">
-        <v>46075.27338557212</v>
+        <v>46075.27338556713</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>46080.27338557212</v>
+        <v>46080.27338556713</v>
       </c>
     </row>
     <row r="386">
@@ -15488,10 +15488,10 @@
         </is>
       </c>
       <c r="H386" s="2" t="n">
-        <v>46066.27338557515</v>
+        <v>46066.2733855787</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>46071.27338557515</v>
+        <v>46071.2733855787</v>
       </c>
     </row>
     <row r="387">
@@ -15527,10 +15527,10 @@
         </is>
       </c>
       <c r="H387" s="2" t="n">
-        <v>46075.27338557821</v>
+        <v>46075.2733855787</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>46080.27338557821</v>
+        <v>46080.2733855787</v>
       </c>
     </row>
     <row r="388">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="H388" s="2" t="n">
-        <v>46078.27338558131</v>
+        <v>46078.2733855787</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>46083.27338558131</v>
+        <v>46083.2733855787</v>
       </c>
     </row>
     <row r="389">
@@ -15605,10 +15605,10 @@
         </is>
       </c>
       <c r="H389" s="2" t="n">
-        <v>46076.27338558457</v>
+        <v>46076.27338559028</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>46081.27338558457</v>
+        <v>46081.27338559028</v>
       </c>
     </row>
     <row r="390">
@@ -15644,10 +15644,10 @@
         </is>
       </c>
       <c r="H390" s="2" t="n">
-        <v>46060.27338558766</v>
+        <v>46060.27338559028</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>46065.27338558766</v>
+        <v>46065.27338559028</v>
       </c>
     </row>
     <row r="391">
@@ -15683,10 +15683,10 @@
         </is>
       </c>
       <c r="H391" s="2" t="n">
-        <v>46073.27338559068</v>
+        <v>46073.27338559028</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>46078.27338559068</v>
+        <v>46078.27338559028</v>
       </c>
     </row>
     <row r="392">
@@ -15722,10 +15722,10 @@
         </is>
       </c>
       <c r="H392" s="2" t="n">
-        <v>46074.27338559375</v>
+        <v>46074.27338559028</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>46079.27338559375</v>
+        <v>46079.27338559028</v>
       </c>
     </row>
     <row r="393">
@@ -15761,10 +15761,10 @@
         </is>
       </c>
       <c r="H393" s="2" t="n">
-        <v>46063.27338559704</v>
+        <v>46063.27338560185</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>46068.27338559704</v>
+        <v>46068.27338560185</v>
       </c>
     </row>
     <row r="394">
@@ -15800,10 +15800,10 @@
         </is>
       </c>
       <c r="H394" s="2" t="n">
-        <v>46061.27338560009</v>
+        <v>46061.27338560185</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>46066.27338560009</v>
+        <v>46066.27338560185</v>
       </c>
     </row>
     <row r="395">
@@ -15839,10 +15839,10 @@
         </is>
       </c>
       <c r="H395" s="2" t="n">
-        <v>46069.27338560327</v>
+        <v>46069.27338560185</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>46074.27338560327</v>
+        <v>46074.27338560185</v>
       </c>
     </row>
     <row r="396">
@@ -15878,10 +15878,10 @@
         </is>
       </c>
       <c r="H396" s="2" t="n">
-        <v>46070.27338560624</v>
+        <v>46070.27338560185</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>46075.27338560624</v>
+        <v>46075.27338560185</v>
       </c>
     </row>
     <row r="397">
@@ -15917,10 +15917,10 @@
         </is>
       </c>
       <c r="H397" s="2" t="n">
-        <v>46061.2733856095</v>
+        <v>46061.27338561343</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>46066.2733856095</v>
+        <v>46066.27338561343</v>
       </c>
     </row>
     <row r="398">
@@ -15956,10 +15956,10 @@
         </is>
       </c>
       <c r="H398" s="2" t="n">
-        <v>46069.27338561265</v>
+        <v>46069.27338561343</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>46074.27338561265</v>
+        <v>46074.27338561343</v>
       </c>
     </row>
     <row r="399">
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="H399" s="2" t="n">
-        <v>46070.27338561569</v>
+        <v>46070.27338561343</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>46075.27338561569</v>
+        <v>46075.27338561343</v>
       </c>
     </row>
     <row r="400">
@@ -16034,10 +16034,10 @@
         </is>
       </c>
       <c r="H400" s="2" t="n">
-        <v>46077.2733856189</v>
+        <v>46077.27338561343</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>46082.2733856189</v>
+        <v>46082.27338561343</v>
       </c>
     </row>
     <row r="401">
@@ -16073,10 +16073,10 @@
         </is>
       </c>
       <c r="H401" s="2" t="n">
-        <v>46059.27338562201</v>
+        <v>46059.273385625</v>
       </c>
       <c r="I401" s="2" t="n">
-        <v>46064.27338562201</v>
+        <v>46064.273385625</v>
       </c>
     </row>
     <row r="402">
@@ -16112,10 +16112,10 @@
         </is>
       </c>
       <c r="H402" s="2" t="n">
-        <v>46082.27338562506</v>
+        <v>46082.273385625</v>
       </c>
       <c r="I402" s="2" t="n">
-        <v>46087.27338562506</v>
+        <v>46087.273385625</v>
       </c>
     </row>
     <row r="403">
@@ -16151,10 +16151,10 @@
         </is>
       </c>
       <c r="H403" s="2" t="n">
-        <v>46061.27338562808</v>
+        <v>46061.273385625</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>46066.27338562808</v>
+        <v>46066.273385625</v>
       </c>
     </row>
     <row r="404">
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="H404" s="2" t="n">
-        <v>46073.27338563131</v>
+        <v>46073.27338563657</v>
       </c>
       <c r="I404" s="2" t="n">
-        <v>46078.27338563131</v>
+        <v>46078.27338563657</v>
       </c>
     </row>
     <row r="405">
@@ -16229,10 +16229,10 @@
         </is>
       </c>
       <c r="H405" s="2" t="n">
-        <v>46084.27338563434</v>
+        <v>46084.27338563657</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>46089.27338563434</v>
+        <v>46089.27338563657</v>
       </c>
     </row>
     <row r="406">
@@ -16268,10 +16268,10 @@
         </is>
       </c>
       <c r="H406" s="2" t="n">
-        <v>46059.27338563747</v>
+        <v>46059.27338563657</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>46064.27338563747</v>
+        <v>46064.27338563657</v>
       </c>
     </row>
     <row r="407">
@@ -16307,10 +16307,10 @@
         </is>
       </c>
       <c r="H407" s="2" t="n">
-        <v>46075.27338564061</v>
+        <v>46075.27338563657</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>46080.27338564061</v>
+        <v>46080.27338563657</v>
       </c>
     </row>
     <row r="408">
@@ -16346,10 +16346,10 @@
         </is>
       </c>
       <c r="H408" s="2" t="n">
-        <v>46084.27338564388</v>
+        <v>46084.27338564815</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>46089.27338564388</v>
+        <v>46089.27338564815</v>
       </c>
     </row>
     <row r="409">
@@ -16385,10 +16385,10 @@
         </is>
       </c>
       <c r="H409" s="2" t="n">
-        <v>46065.27338564718</v>
+        <v>46065.27338564815</v>
       </c>
       <c r="I409" s="2" t="n">
-        <v>46070.27338564718</v>
+        <v>46070.27338564815</v>
       </c>
     </row>
     <row r="410">
@@ -16424,10 +16424,10 @@
         </is>
       </c>
       <c r="H410" s="2" t="n">
-        <v>46088.27338565017</v>
+        <v>46088.27338564815</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>46093.27338565017</v>
+        <v>46093.27338564815</v>
       </c>
     </row>
     <row r="411">
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="H411" s="2" t="n">
-        <v>46060.27338565344</v>
+        <v>46060.27338564815</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>46065.27338565344</v>
+        <v>46065.27338564815</v>
       </c>
     </row>
     <row r="412">
@@ -16502,10 +16502,10 @@
         </is>
       </c>
       <c r="H412" s="2" t="n">
-        <v>46087.27338565647</v>
+        <v>46087.27338565972</v>
       </c>
       <c r="I412" s="2" t="n">
-        <v>46092.27338565647</v>
+        <v>46092.27338565972</v>
       </c>
     </row>
     <row r="413">
@@ -16541,10 +16541,10 @@
         </is>
       </c>
       <c r="H413" s="2" t="n">
-        <v>46078.27338565941</v>
+        <v>46078.27338565972</v>
       </c>
       <c r="I413" s="2" t="n">
-        <v>46083.27338565941</v>
+        <v>46083.27338565972</v>
       </c>
     </row>
     <row r="414">
@@ -16580,10 +16580,10 @@
         </is>
       </c>
       <c r="H414" s="2" t="n">
-        <v>46068.27338566261</v>
+        <v>46068.27338565972</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>46073.27338566261</v>
+        <v>46073.27338565972</v>
       </c>
     </row>
     <row r="415">
@@ -16619,10 +16619,10 @@
         </is>
       </c>
       <c r="H415" s="2" t="n">
-        <v>46061.27338566577</v>
+        <v>46061.27338567129</v>
       </c>
       <c r="I415" s="2" t="n">
-        <v>46066.27338566577</v>
+        <v>46066.27338567129</v>
       </c>
     </row>
     <row r="416">
@@ -16658,10 +16658,10 @@
         </is>
       </c>
       <c r="H416" s="2" t="n">
-        <v>46063.27338566884</v>
+        <v>46063.27338567129</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>46068.27338566884</v>
+        <v>46068.27338567129</v>
       </c>
     </row>
     <row r="417">
@@ -16697,10 +16697,10 @@
         </is>
       </c>
       <c r="H417" s="2" t="n">
-        <v>46088.27338567198</v>
+        <v>46088.27338567129</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>46093.27338567198</v>
+        <v>46093.27338567129</v>
       </c>
     </row>
     <row r="418">
@@ -16736,10 +16736,10 @@
         </is>
       </c>
       <c r="H418" s="2" t="n">
-        <v>46068.27338567578</v>
+        <v>46068.27338567129</v>
       </c>
       <c r="I418" s="2" t="n">
-        <v>46073.27338567578</v>
+        <v>46073.27338567129</v>
       </c>
     </row>
     <row r="419">
@@ -16775,10 +16775,10 @@
         </is>
       </c>
       <c r="H419" s="2" t="n">
-        <v>46085.27338567901</v>
+        <v>46085.27338568287</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>46090.27338567901</v>
+        <v>46090.27338568287</v>
       </c>
     </row>
     <row r="420">
@@ -16814,10 +16814,10 @@
         </is>
       </c>
       <c r="H420" s="2" t="n">
-        <v>46063.27338568201</v>
+        <v>46063.27338568287</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>46068.27338568201</v>
+        <v>46068.27338568287</v>
       </c>
     </row>
     <row r="421">
@@ -16853,10 +16853,10 @@
         </is>
       </c>
       <c r="H421" s="2" t="n">
-        <v>46067.27338568516</v>
+        <v>46067.27338568287</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>46072.27338568516</v>
+        <v>46072.27338568287</v>
       </c>
     </row>
     <row r="422">
@@ -16892,10 +16892,10 @@
         </is>
       </c>
       <c r="H422" s="2" t="n">
-        <v>46076.27338568861</v>
+        <v>46076.27338568287</v>
       </c>
       <c r="I422" s="2" t="n">
-        <v>46081.27338568861</v>
+        <v>46081.27338568287</v>
       </c>
     </row>
     <row r="423">
@@ -16931,10 +16931,10 @@
         </is>
       </c>
       <c r="H423" s="2" t="n">
-        <v>46064.27338569181</v>
+        <v>46064.27338569445</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>46069.27338569181</v>
+        <v>46069.27338569445</v>
       </c>
     </row>
     <row r="424">
@@ -16970,10 +16970,10 @@
         </is>
       </c>
       <c r="H424" s="2" t="n">
-        <v>46080.27338569484</v>
+        <v>46080.27338569445</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>46085.27338569484</v>
+        <v>46085.27338569445</v>
       </c>
     </row>
     <row r="425">
@@ -17009,10 +17009,10 @@
         </is>
       </c>
       <c r="H425" s="2" t="n">
-        <v>46074.27338569798</v>
+        <v>46074.27338569445</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>46079.27338569798</v>
+        <v>46079.27338569445</v>
       </c>
     </row>
     <row r="426">
@@ -17048,10 +17048,10 @@
         </is>
       </c>
       <c r="H426" s="2" t="n">
-        <v>46082.27338570207</v>
+        <v>46082.27338570602</v>
       </c>
       <c r="I426" s="2" t="n">
-        <v>46087.27338570207</v>
+        <v>46087.27338570602</v>
       </c>
     </row>
     <row r="427">
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="H427" s="2" t="n">
-        <v>46072.27338570528</v>
+        <v>46072.27338570602</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>46077.27338570528</v>
+        <v>46077.27338570602</v>
       </c>
     </row>
     <row r="428">
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="H428" s="2" t="n">
-        <v>46088.27338570838</v>
+        <v>46088.27338570602</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>46093.27338570838</v>
+        <v>46093.27338570602</v>
       </c>
     </row>
     <row r="429">
@@ -17165,10 +17165,10 @@
         </is>
       </c>
       <c r="H429" s="2" t="n">
-        <v>46077.2733857116</v>
+        <v>46077.27338570602</v>
       </c>
       <c r="I429" s="2" t="n">
-        <v>46082.2733857116</v>
+        <v>46082.27338570602</v>
       </c>
     </row>
     <row r="430">
@@ -17204,10 +17204,10 @@
         </is>
       </c>
       <c r="H430" s="2" t="n">
-        <v>46072.27338571467</v>
+        <v>46072.27338571759</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>46077.27338571467</v>
+        <v>46077.27338571759</v>
       </c>
     </row>
     <row r="431">
@@ -17243,10 +17243,10 @@
         </is>
       </c>
       <c r="H431" s="2" t="n">
-        <v>46088.27338571779</v>
+        <v>46088.27338571759</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>46093.27338571779</v>
+        <v>46093.27338571759</v>
       </c>
     </row>
     <row r="432">
@@ -17282,10 +17282,10 @@
         </is>
       </c>
       <c r="H432" s="2" t="n">
-        <v>46066.27338572087</v>
+        <v>46066.27338571759</v>
       </c>
       <c r="I432" s="2" t="n">
-        <v>46071.27338572087</v>
+        <v>46071.27338571759</v>
       </c>
     </row>
     <row r="433">
@@ -17321,10 +17321,10 @@
         </is>
       </c>
       <c r="H433" s="2" t="n">
-        <v>46075.27338572413</v>
+        <v>46075.27338572917</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>46080.27338572413</v>
+        <v>46080.27338572917</v>
       </c>
     </row>
     <row r="434">
@@ -17360,10 +17360,10 @@
         </is>
       </c>
       <c r="H434" s="2" t="n">
-        <v>46069.27338572729</v>
+        <v>46069.27338572917</v>
       </c>
       <c r="I434" s="2" t="n">
-        <v>46074.27338572729</v>
+        <v>46074.27338572917</v>
       </c>
     </row>
     <row r="435">
@@ -17399,10 +17399,10 @@
         </is>
       </c>
       <c r="H435" s="2" t="n">
-        <v>46066.27338573028</v>
+        <v>46066.27338572917</v>
       </c>
       <c r="I435" s="2" t="n">
-        <v>46071.27338573028</v>
+        <v>46071.27338572917</v>
       </c>
     </row>
     <row r="436">
@@ -17438,10 +17438,10 @@
         </is>
       </c>
       <c r="H436" s="2" t="n">
-        <v>46078.27338573334</v>
+        <v>46078.27338572917</v>
       </c>
       <c r="I436" s="2" t="n">
-        <v>46083.27338573334</v>
+        <v>46083.27338572917</v>
       </c>
     </row>
     <row r="437">
@@ -17477,10 +17477,10 @@
         </is>
       </c>
       <c r="H437" s="2" t="n">
-        <v>46064.27338573664</v>
+        <v>46064.27338574074</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>46069.27338573664</v>
+        <v>46069.27338574074</v>
       </c>
     </row>
     <row r="438">
@@ -17516,10 +17516,10 @@
         </is>
       </c>
       <c r="H438" s="2" t="n">
-        <v>46082.27338573973</v>
+        <v>46082.27338574074</v>
       </c>
       <c r="I438" s="2" t="n">
-        <v>46087.27338573973</v>
+        <v>46087.27338574074</v>
       </c>
     </row>
     <row r="439">
@@ -17555,10 +17555,10 @@
         </is>
       </c>
       <c r="H439" s="2" t="n">
-        <v>46071.27338574269</v>
+        <v>46071.27338574074</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>46076.27338574269</v>
+        <v>46076.27338574074</v>
       </c>
     </row>
     <row r="440">
@@ -17594,10 +17594,10 @@
         </is>
       </c>
       <c r="H440" s="2" t="n">
-        <v>46062.273385746</v>
+        <v>46062.27338574074</v>
       </c>
       <c r="I440" s="2" t="n">
-        <v>46067.273385746</v>
+        <v>46067.27338574074</v>
       </c>
     </row>
     <row r="441">
@@ -17633,10 +17633,10 @@
         </is>
       </c>
       <c r="H441" s="2" t="n">
-        <v>46088.27338574929</v>
+        <v>46088.27338575231</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>46093.27338574929</v>
+        <v>46093.27338575231</v>
       </c>
     </row>
     <row r="442">
@@ -17672,10 +17672,10 @@
         </is>
       </c>
       <c r="H442" s="2" t="n">
-        <v>46087.27338575255</v>
+        <v>46087.27338575231</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>46092.27338575255</v>
+        <v>46092.27338575231</v>
       </c>
     </row>
     <row r="443">
@@ -17711,10 +17711,10 @@
         </is>
       </c>
       <c r="H443" s="2" t="n">
-        <v>46076.27338575554</v>
+        <v>46076.27338575231</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>46081.27338575554</v>
+        <v>46081.27338575231</v>
       </c>
     </row>
     <row r="444">
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="H444" s="2" t="n">
-        <v>46071.27338575873</v>
+        <v>46071.27338576389</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>46076.27338575873</v>
+        <v>46076.27338576389</v>
       </c>
     </row>
     <row r="445">
@@ -17789,10 +17789,10 @@
         </is>
       </c>
       <c r="H445" s="2" t="n">
-        <v>46073.27338576193</v>
+        <v>46073.27338576389</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>46078.27338576193</v>
+        <v>46078.27338576389</v>
       </c>
     </row>
     <row r="446">
@@ -17828,10 +17828,10 @@
         </is>
       </c>
       <c r="H446" s="2" t="n">
-        <v>46088.27338576509</v>
+        <v>46088.27338576389</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>46093.27338576509</v>
+        <v>46093.27338576389</v>
       </c>
     </row>
     <row r="447">
@@ -17867,10 +17867,10 @@
         </is>
       </c>
       <c r="H447" s="2" t="n">
-        <v>46079.27338576828</v>
+        <v>46079.27338576389</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>46084.27338576828</v>
+        <v>46084.27338576389</v>
       </c>
     </row>
     <row r="448">
@@ -17906,10 +17906,10 @@
         </is>
       </c>
       <c r="H448" s="2" t="n">
-        <v>46068.27338577151</v>
+        <v>46068.27338577546</v>
       </c>
       <c r="I448" s="2" t="n">
-        <v>46073.27338577151</v>
+        <v>46073.27338577546</v>
       </c>
     </row>
     <row r="449">
@@ -17945,10 +17945,10 @@
         </is>
       </c>
       <c r="H449" s="2" t="n">
-        <v>46071.27338577453</v>
+        <v>46071.27338577546</v>
       </c>
       <c r="I449" s="2" t="n">
-        <v>46076.27338577453</v>
+        <v>46076.27338577546</v>
       </c>
     </row>
     <row r="450">
@@ -17984,10 +17984,10 @@
         </is>
       </c>
       <c r="H450" s="2" t="n">
-        <v>46083.2733857777</v>
+        <v>46083.27338577546</v>
       </c>
       <c r="I450" s="2" t="n">
-        <v>46088.2733857777</v>
+        <v>46088.27338577546</v>
       </c>
     </row>
     <row r="451">
@@ -18023,10 +18023,10 @@
         </is>
       </c>
       <c r="H451" s="2" t="n">
-        <v>46084.27338578107</v>
+        <v>46084.27338577546</v>
       </c>
       <c r="I451" s="2" t="n">
-        <v>46089.27338578107</v>
+        <v>46089.27338577546</v>
       </c>
     </row>
     <row r="452">
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="H452" s="2" t="n">
-        <v>46068.27338578409</v>
+        <v>46068.27338578703</v>
       </c>
       <c r="I452" s="2" t="n">
-        <v>46073.27338578409</v>
+        <v>46073.27338578703</v>
       </c>
     </row>
     <row r="453">
@@ -18101,10 +18101,10 @@
         </is>
       </c>
       <c r="H453" s="2" t="n">
-        <v>46077.27338578716</v>
+        <v>46077.27338578703</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>46082.27338578716</v>
+        <v>46082.27338578703</v>
       </c>
     </row>
     <row r="454">
@@ -18140,10 +18140,10 @@
         </is>
       </c>
       <c r="H454" s="2" t="n">
-        <v>46085.27338579018</v>
+        <v>46085.27338578703</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>46090.27338579018</v>
+        <v>46090.27338578703</v>
       </c>
     </row>
     <row r="455">
@@ -18179,10 +18179,10 @@
         </is>
       </c>
       <c r="H455" s="2" t="n">
-        <v>46065.27338579338</v>
+        <v>46065.27338579861</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>46070.27338579338</v>
+        <v>46070.27338579861</v>
       </c>
     </row>
     <row r="456">
@@ -18218,10 +18218,10 @@
         </is>
       </c>
       <c r="H456" s="2" t="n">
-        <v>46075.27338579653</v>
+        <v>46075.27338579861</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>46080.27338579653</v>
+        <v>46080.27338579861</v>
       </c>
     </row>
     <row r="457">
@@ -18257,10 +18257,10 @@
         </is>
       </c>
       <c r="H457" s="2" t="n">
-        <v>46065.27338579959</v>
+        <v>46065.27338579861</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>46070.27338579959</v>
+        <v>46070.27338579861</v>
       </c>
     </row>
     <row r="458">
@@ -18296,10 +18296,10 @@
         </is>
       </c>
       <c r="H458" s="2" t="n">
-        <v>46083.27338580263</v>
+        <v>46083.27338579861</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>46088.27338580263</v>
+        <v>46088.27338579861</v>
       </c>
     </row>
     <row r="459">
@@ -18335,10 +18335,10 @@
         </is>
       </c>
       <c r="H459" s="2" t="n">
-        <v>46075.27338580583</v>
+        <v>46075.27338581019</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>46080.27338580583</v>
+        <v>46080.27338581019</v>
       </c>
     </row>
     <row r="460">
@@ -18374,10 +18374,10 @@
         </is>
       </c>
       <c r="H460" s="2" t="n">
-        <v>46087.27338580904</v>
+        <v>46087.27338581019</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>46092.27338580904</v>
+        <v>46092.27338581019</v>
       </c>
     </row>
     <row r="461">
@@ -18413,10 +18413,10 @@
         </is>
       </c>
       <c r="H461" s="2" t="n">
-        <v>46081.27338581206</v>
+        <v>46081.27338581019</v>
       </c>
       <c r="I461" s="2" t="n">
-        <v>46086.27338581206</v>
+        <v>46086.27338581019</v>
       </c>
     </row>
     <row r="462">
@@ -18452,10 +18452,10 @@
         </is>
       </c>
       <c r="H462" s="2" t="n">
-        <v>46081.27338581526</v>
+        <v>46081.27338581019</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>46086.27338581526</v>
+        <v>46086.27338581019</v>
       </c>
     </row>
     <row r="463">
@@ -18491,10 +18491,10 @@
         </is>
       </c>
       <c r="H463" s="2" t="n">
-        <v>46072.27338581848</v>
+        <v>46072.27338582176</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>46077.27338581848</v>
+        <v>46077.27338582176</v>
       </c>
     </row>
     <row r="464">
@@ -18530,10 +18530,10 @@
         </is>
       </c>
       <c r="H464" s="2" t="n">
-        <v>46078.27338582161</v>
+        <v>46078.27338582176</v>
       </c>
       <c r="I464" s="2" t="n">
-        <v>46083.27338582161</v>
+        <v>46083.27338582176</v>
       </c>
     </row>
     <row r="465">
@@ -18569,10 +18569,10 @@
         </is>
       </c>
       <c r="H465" s="2" t="n">
-        <v>46075.27338582482</v>
+        <v>46075.27338582176</v>
       </c>
       <c r="I465" s="2" t="n">
-        <v>46080.27338582482</v>
+        <v>46080.27338582176</v>
       </c>
     </row>
     <row r="466">
@@ -18608,10 +18608,10 @@
         </is>
       </c>
       <c r="H466" s="2" t="n">
-        <v>46078.27338582811</v>
+        <v>46078.27338583333</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>46083.27338582811</v>
+        <v>46083.27338583333</v>
       </c>
     </row>
     <row r="467">
@@ -18647,10 +18647,10 @@
         </is>
       </c>
       <c r="H467" s="2" t="n">
-        <v>46074.27338583134</v>
+        <v>46074.27338583333</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>46079.27338583134</v>
+        <v>46079.27338583333</v>
       </c>
     </row>
     <row r="468">
@@ -18686,10 +18686,10 @@
         </is>
       </c>
       <c r="H468" s="2" t="n">
-        <v>46063.27338583438</v>
+        <v>46063.27338583333</v>
       </c>
       <c r="I468" s="2" t="n">
-        <v>46068.27338583438</v>
+        <v>46068.27338583333</v>
       </c>
     </row>
     <row r="469">
@@ -18725,10 +18725,10 @@
         </is>
       </c>
       <c r="H469" s="2" t="n">
-        <v>46073.27338583751</v>
+        <v>46073.27338583333</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>46078.27338583751</v>
+        <v>46078.27338583333</v>
       </c>
     </row>
     <row r="470">
@@ -18764,10 +18764,10 @@
         </is>
       </c>
       <c r="H470" s="2" t="n">
-        <v>46072.27338584072</v>
+        <v>46072.27338584491</v>
       </c>
       <c r="I470" s="2" t="n">
-        <v>46077.27338584072</v>
+        <v>46077.27338584491</v>
       </c>
     </row>
     <row r="471">
@@ -18803,10 +18803,10 @@
         </is>
       </c>
       <c r="H471" s="2" t="n">
-        <v>46082.27338584371</v>
+        <v>46082.27338584491</v>
       </c>
       <c r="I471" s="2" t="n">
-        <v>46087.27338584371</v>
+        <v>46087.27338584491</v>
       </c>
     </row>
     <row r="472">
@@ -18842,10 +18842,10 @@
         </is>
       </c>
       <c r="H472" s="2" t="n">
-        <v>46073.27338584681</v>
+        <v>46073.27338584491</v>
       </c>
       <c r="I472" s="2" t="n">
-        <v>46078.27338584681</v>
+        <v>46078.27338584491</v>
       </c>
     </row>
     <row r="473">
@@ -18881,10 +18881,10 @@
         </is>
       </c>
       <c r="H473" s="2" t="n">
-        <v>46087.27338584996</v>
+        <v>46087.27338584491</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>46092.27338584996</v>
+        <v>46092.27338584491</v>
       </c>
     </row>
     <row r="474">
@@ -18920,10 +18920,10 @@
         </is>
       </c>
       <c r="H474" s="2" t="n">
-        <v>46062.27338585298</v>
+        <v>46062.27338585648</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>46067.27338585298</v>
+        <v>46067.27338585648</v>
       </c>
     </row>
     <row r="475">
@@ -18959,10 +18959,10 @@
         </is>
       </c>
       <c r="H475" s="2" t="n">
-        <v>46065.27338585602</v>
+        <v>46065.27338585648</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>46070.27338585602</v>
+        <v>46070.27338585648</v>
       </c>
     </row>
     <row r="476">
@@ -18998,10 +18998,10 @@
         </is>
       </c>
       <c r="H476" s="2" t="n">
-        <v>46077.2733858592</v>
+        <v>46077.27338585648</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>46082.2733858592</v>
+        <v>46082.27338585648</v>
       </c>
     </row>
     <row r="477">
@@ -19037,10 +19037,10 @@
         </is>
       </c>
       <c r="H477" s="2" t="n">
-        <v>46086.27338586249</v>
+        <v>46086.27338586806</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>46091.27338586249</v>
+        <v>46091.27338586806</v>
       </c>
     </row>
     <row r="478">
@@ -19076,10 +19076,10 @@
         </is>
       </c>
       <c r="H478" s="2" t="n">
-        <v>46065.2733858655</v>
+        <v>46065.27338586806</v>
       </c>
       <c r="I478" s="2" t="n">
-        <v>46070.2733858655</v>
+        <v>46070.27338586806</v>
       </c>
     </row>
     <row r="479">
@@ -19115,10 +19115,10 @@
         </is>
       </c>
       <c r="H479" s="2" t="n">
-        <v>46074.27338586863</v>
+        <v>46074.27338586806</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>46079.27338586863</v>
+        <v>46079.27338586806</v>
       </c>
     </row>
     <row r="480">
@@ -19154,10 +19154,10 @@
         </is>
       </c>
       <c r="H480" s="2" t="n">
-        <v>46081.27338587165</v>
+        <v>46081.27338586806</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>46086.27338587165</v>
+        <v>46086.27338586806</v>
       </c>
     </row>
     <row r="481">
@@ -19193,10 +19193,10 @@
         </is>
       </c>
       <c r="H481" s="2" t="n">
-        <v>46066.27338587499</v>
+        <v>46066.27338587963</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>46071.27338587499</v>
+        <v>46071.27338587963</v>
       </c>
     </row>
     <row r="482">
@@ -19232,10 +19232,10 @@
         </is>
       </c>
       <c r="H482" s="2" t="n">
-        <v>46078.27338587823</v>
+        <v>46078.27338587963</v>
       </c>
       <c r="I482" s="2" t="n">
-        <v>46083.27338587823</v>
+        <v>46083.27338587963</v>
       </c>
     </row>
     <row r="483">
@@ -19271,10 +19271,10 @@
         </is>
       </c>
       <c r="H483" s="2" t="n">
-        <v>46083.27338588129</v>
+        <v>46083.27338587963</v>
       </c>
       <c r="I483" s="2" t="n">
-        <v>46088.27338588129</v>
+        <v>46088.27338587963</v>
       </c>
     </row>
     <row r="484">
@@ -19310,10 +19310,10 @@
         </is>
       </c>
       <c r="H484" s="2" t="n">
-        <v>46078.2733858845</v>
+        <v>46078.27338587963</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>46083.2733858845</v>
+        <v>46083.27338587963</v>
       </c>
     </row>
     <row r="485">
@@ -19349,10 +19349,10 @@
         </is>
       </c>
       <c r="H485" s="2" t="n">
-        <v>46088.27338588757</v>
+        <v>46088.2733858912</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>46093.27338588757</v>
+        <v>46093.2733858912</v>
       </c>
     </row>
     <row r="486">
@@ -19388,10 +19388,10 @@
         </is>
       </c>
       <c r="H486" s="2" t="n">
-        <v>46073.27338589061</v>
+        <v>46073.2733858912</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>46078.27338589061</v>
+        <v>46078.2733858912</v>
       </c>
     </row>
     <row r="487">
@@ -19427,10 +19427,10 @@
         </is>
       </c>
       <c r="H487" s="2" t="n">
-        <v>46087.27338589379</v>
+        <v>46087.2733858912</v>
       </c>
       <c r="I487" s="2" t="n">
-        <v>46092.27338589379</v>
+        <v>46092.2733858912</v>
       </c>
     </row>
     <row r="488">
@@ -19466,10 +19466,10 @@
         </is>
       </c>
       <c r="H488" s="2" t="n">
-        <v>46065.27338589696</v>
+        <v>46065.2733858912</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>46070.27338589696</v>
+        <v>46070.2733858912</v>
       </c>
     </row>
     <row r="489">
@@ -19505,10 +19505,10 @@
         </is>
       </c>
       <c r="H489" s="2" t="n">
-        <v>46063.27338589999</v>
+        <v>46063.27338590278</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>46068.27338589999</v>
+        <v>46068.27338590278</v>
       </c>
     </row>
     <row r="490">
@@ -19544,10 +19544,10 @@
         </is>
       </c>
       <c r="H490" s="2" t="n">
-        <v>46085.27338590302</v>
+        <v>46085.27338590278</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>46090.27338590302</v>
+        <v>46090.27338590278</v>
       </c>
     </row>
     <row r="491">
@@ -19583,10 +19583,10 @@
         </is>
       </c>
       <c r="H491" s="2" t="n">
-        <v>46083.27338590602</v>
+        <v>46083.27338590278</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>46088.27338590602</v>
+        <v>46088.27338590278</v>
       </c>
     </row>
     <row r="492">
@@ -19622,10 +19622,10 @@
         </is>
       </c>
       <c r="H492" s="2" t="n">
-        <v>46073.27338590936</v>
+        <v>46073.27338591436</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>46078.27338590936</v>
+        <v>46078.27338591436</v>
       </c>
     </row>
     <row r="493">
@@ -19661,10 +19661,10 @@
         </is>
       </c>
       <c r="H493" s="2" t="n">
-        <v>46085.27338591238</v>
+        <v>46085.27338591436</v>
       </c>
       <c r="I493" s="2" t="n">
-        <v>46090.27338591238</v>
+        <v>46090.27338591436</v>
       </c>
     </row>
     <row r="494">
@@ -19700,10 +19700,10 @@
         </is>
       </c>
       <c r="H494" s="2" t="n">
-        <v>46079.27338591542</v>
+        <v>46079.27338591436</v>
       </c>
       <c r="I494" s="2" t="n">
-        <v>46084.27338591542</v>
+        <v>46084.27338591436</v>
       </c>
     </row>
     <row r="495">
@@ -19739,10 +19739,10 @@
         </is>
       </c>
       <c r="H495" s="2" t="n">
-        <v>46066.27338591854</v>
+        <v>46066.27338591436</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>46071.27338591854</v>
+        <v>46071.27338591436</v>
       </c>
     </row>
     <row r="496">
@@ -19778,10 +19778,10 @@
         </is>
       </c>
       <c r="H496" s="2" t="n">
-        <v>46084.27338592173</v>
+        <v>46084.27338592592</v>
       </c>
       <c r="I496" s="2" t="n">
-        <v>46089.27338592173</v>
+        <v>46089.27338592592</v>
       </c>
     </row>
     <row r="497">
@@ -19817,10 +19817,10 @@
         </is>
       </c>
       <c r="H497" s="2" t="n">
-        <v>46086.27338592478</v>
+        <v>46086.27338592592</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>46091.27338592478</v>
+        <v>46091.27338592592</v>
       </c>
     </row>
     <row r="498">
@@ -19856,10 +19856,10 @@
         </is>
       </c>
       <c r="H498" s="2" t="n">
-        <v>46070.2733859278</v>
+        <v>46070.27338592592</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>46075.2733859278</v>
+        <v>46075.27338592592</v>
       </c>
     </row>
     <row r="499">
@@ -19895,10 +19895,10 @@
         </is>
       </c>
       <c r="H499" s="2" t="n">
-        <v>46086.273385931</v>
+        <v>46086.27338592592</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>46091.273385931</v>
+        <v>46091.27338592592</v>
       </c>
     </row>
     <row r="500">
@@ -19934,10 +19934,10 @@
         </is>
       </c>
       <c r="H500" s="2" t="n">
-        <v>46062.27338593402</v>
+        <v>46062.2733859375</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>46067.27338593402</v>
+        <v>46067.2733859375</v>
       </c>
     </row>
     <row r="501">
@@ -19973,10 +19973,1960 @@
         </is>
       </c>
       <c r="H501" s="2" t="n">
-        <v>46067.27338593706</v>
+        <v>46067.2733859375</v>
       </c>
       <c r="I501" s="2" t="n">
-        <v>46072.27338593706</v>
+        <v>46072.2733859375</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>b08c82bb-4677-4021-8bab-7788d0a276c8</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>2271.97</v>
+      </c>
+      <c r="D502" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="n">
+        <v>46087.28937713445</v>
+      </c>
+      <c r="I502" s="2" t="n">
+        <v>46092.28937713445</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>30b0cfb4-420c-4cd9-9570-0a8fe1893aef</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>8897.360000000001</v>
+      </c>
+      <c r="D503" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H503" s="2" t="n">
+        <v>46088.28937713874</v>
+      </c>
+      <c r="I503" s="2" t="n">
+        <v>46093.28937713874</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>536c7b76-0b35-47fe-8090-e94300839e5d</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>4044.71</v>
+      </c>
+      <c r="D504" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H504" s="2" t="n">
+        <v>46064.28937714201</v>
+      </c>
+      <c r="I504" s="2" t="n">
+        <v>46069.28937714201</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>9ea37706-10e4-4525-b363-9770dde6d763</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>4362.87</v>
+      </c>
+      <c r="D505" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H505" s="2" t="n">
+        <v>46065.2893771453</v>
+      </c>
+      <c r="I505" s="2" t="n">
+        <v>46070.2893771453</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>1c8ecd1c-d0bb-4630-a2e4-2655f6bdaca3</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>1963.5</v>
+      </c>
+      <c r="D506" t="n">
+        <v>95</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H506" s="2" t="n">
+        <v>46070.28937714858</v>
+      </c>
+      <c r="I506" s="2" t="n">
+        <v>46075.28937714858</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>47faa697-70a8-413d-abe3-16d329f90f21</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>8359.559999999999</v>
+      </c>
+      <c r="D507" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="n">
+        <v>46059.28937715171</v>
+      </c>
+      <c r="I507" s="2" t="n">
+        <v>46064.28937715171</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>acc5d158-3c79-45e9-859f-592a1dee32c3</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>2440.64</v>
+      </c>
+      <c r="D508" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="n">
+        <v>46070.28937715492</v>
+      </c>
+      <c r="I508" s="2" t="n">
+        <v>46075.28937715492</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>61cf9ef7-621e-42d9-8fd9-dcfdf569ac33</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>2448.6</v>
+      </c>
+      <c r="D509" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H509" s="2" t="n">
+        <v>46061.28937715817</v>
+      </c>
+      <c r="I509" s="2" t="n">
+        <v>46066.28937715817</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>aebbfc87-2e57-4bd8-8b84-8d979a122de3</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>7307.09</v>
+      </c>
+      <c r="D510" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H510" s="2" t="n">
+        <v>46088.28937716169</v>
+      </c>
+      <c r="I510" s="2" t="n">
+        <v>46093.28937716169</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>caf94a38-e5b1-4a09-ad6a-263e2bdfb05d</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>4171.26</v>
+      </c>
+      <c r="D511" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H511" s="2" t="n">
+        <v>46081.28937716501</v>
+      </c>
+      <c r="I511" s="2" t="n">
+        <v>46086.28937716501</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>9aabe525-6ec2-4c92-b084-1be588dfa603</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>9101.98</v>
+      </c>
+      <c r="D512" t="n">
+        <v>96</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="n">
+        <v>46065.2893771681</v>
+      </c>
+      <c r="I512" s="2" t="n">
+        <v>46070.2893771681</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>e342557d-a276-4f10-955b-ec102abce62b</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>1948.11</v>
+      </c>
+      <c r="D513" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H513" s="2" t="n">
+        <v>46085.28937717142</v>
+      </c>
+      <c r="I513" s="2" t="n">
+        <v>46090.28937717142</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>45edb267-a2bd-4af4-998f-c10c8084c51d</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>5040.25</v>
+      </c>
+      <c r="D514" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H514" s="2" t="n">
+        <v>46067.28937717469</v>
+      </c>
+      <c r="I514" s="2" t="n">
+        <v>46072.28937717469</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2bd70b43-a67f-4fb4-9462-f7266685bf22</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>5668.23</v>
+      </c>
+      <c r="D515" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H515" s="2" t="n">
+        <v>46088.28937717786</v>
+      </c>
+      <c r="I515" s="2" t="n">
+        <v>46093.28937717786</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>8df11d50-da85-471b-92ef-0e551f2a2ae9</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>3813.08</v>
+      </c>
+      <c r="D516" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H516" s="2" t="n">
+        <v>46076.28937718103</v>
+      </c>
+      <c r="I516" s="2" t="n">
+        <v>46081.28937718103</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>595d25cd-8e49-4b59-bb7f-535414497cdf</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>8440.07</v>
+      </c>
+      <c r="D517" t="n">
+        <v>90.84</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H517" s="2" t="n">
+        <v>46075.28937718428</v>
+      </c>
+      <c r="I517" s="2" t="n">
+        <v>46080.28937718428</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>802ce0b6-6807-430d-8d5f-2f61d3e51bb1</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>3991.62</v>
+      </c>
+      <c r="D518" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H518" s="2" t="n">
+        <v>46066.28937718735</v>
+      </c>
+      <c r="I518" s="2" t="n">
+        <v>46071.28937718735</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>6bd4d6f9-d830-4412-be07-f12d9656d121</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>6868.86</v>
+      </c>
+      <c r="D519" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H519" s="2" t="n">
+        <v>46067.28937719043</v>
+      </c>
+      <c r="I519" s="2" t="n">
+        <v>46072.28937719043</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>ba9b0064-d2c9-4366-88ea-6ee7f5f70bb0</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>6608.99</v>
+      </c>
+      <c r="D520" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H520" s="2" t="n">
+        <v>46059.28937719367</v>
+      </c>
+      <c r="I520" s="2" t="n">
+        <v>46064.28937719367</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>85e55dc1-c799-4492-8a6a-fe9bd72323b1</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>7916.26</v>
+      </c>
+      <c r="D521" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="n">
+        <v>46064.28937719674</v>
+      </c>
+      <c r="I521" s="2" t="n">
+        <v>46069.28937719674</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>ee509a87-34e6-493e-8d00-529ef4fd0759</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>1389.44</v>
+      </c>
+      <c r="D522" t="n">
+        <v>85.98</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="n">
+        <v>46082.28937719977</v>
+      </c>
+      <c r="I522" s="2" t="n">
+        <v>46087.28937719977</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>ca327c3c-9a1b-41af-b66f-99d9a0d22cbf</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>3292.74</v>
+      </c>
+      <c r="D523" t="n">
+        <v>99.17</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H523" s="2" t="n">
+        <v>46076.2893772028</v>
+      </c>
+      <c r="I523" s="2" t="n">
+        <v>46081.2893772028</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>f98000d5-f06a-4f64-b173-0a4e45a69242</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>7789.41</v>
+      </c>
+      <c r="D524" t="n">
+        <v>87.34999999999999</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H524" s="2" t="n">
+        <v>46071.28937720609</v>
+      </c>
+      <c r="I524" s="2" t="n">
+        <v>46076.28937720609</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>a0ec6fe9-ad94-40e0-bf94-9d4ce7d7ebcc</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>2877.99</v>
+      </c>
+      <c r="D525" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H525" s="2" t="n">
+        <v>46077.28937720925</v>
+      </c>
+      <c r="I525" s="2" t="n">
+        <v>46082.28937720925</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>526c8661-27be-4a19-9b0d-f1806a1b4929</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>9591.65</v>
+      </c>
+      <c r="D526" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H526" s="2" t="n">
+        <v>46088.28937721228</v>
+      </c>
+      <c r="I526" s="2" t="n">
+        <v>46093.28937721228</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>7bb684f9-d4e1-4d65-8b5b-fd5a72597f68</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>9251.32</v>
+      </c>
+      <c r="D527" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H527" s="2" t="n">
+        <v>46085.28937721553</v>
+      </c>
+      <c r="I527" s="2" t="n">
+        <v>46090.28937721553</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>a1617060-221e-4ace-863f-814a4f7df61f</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>4056.4</v>
+      </c>
+      <c r="D528" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H528" s="2" t="n">
+        <v>46079.28937721903</v>
+      </c>
+      <c r="I528" s="2" t="n">
+        <v>46084.28937721903</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>53748711-6386-4b79-a899-33fb7f1790d6</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>6842.25</v>
+      </c>
+      <c r="D529" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H529" s="2" t="n">
+        <v>46084.28937722214</v>
+      </c>
+      <c r="I529" s="2" t="n">
+        <v>46089.28937722214</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>c8bfd8e2-fc2d-4a1d-88dd-6385d1e56223</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>4226.75</v>
+      </c>
+      <c r="D530" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H530" s="2" t="n">
+        <v>46061.28937722528</v>
+      </c>
+      <c r="I530" s="2" t="n">
+        <v>46066.28937722528</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>92093c53-a175-4a9f-a1d3-c47dc1f5f59c</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>3200.23</v>
+      </c>
+      <c r="D531" t="n">
+        <v>85.08</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H531" s="2" t="n">
+        <v>46078.28937722873</v>
+      </c>
+      <c r="I531" s="2" t="n">
+        <v>46083.28937722873</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>3f6a66f6-0cc4-4faf-9a9a-a6ca6da5f49e</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>9140.030000000001</v>
+      </c>
+      <c r="D532" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="n">
+        <v>46061.28937723182</v>
+      </c>
+      <c r="I532" s="2" t="n">
+        <v>46066.28937723182</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>6c74d833-67e4-4ba1-9201-e106355fa46a</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>9165.49</v>
+      </c>
+      <c r="D533" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="n">
+        <v>46069.28937723486</v>
+      </c>
+      <c r="I533" s="2" t="n">
+        <v>46074.28937723486</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>847c524c-b2f1-4938-a7f4-8bd5798ed010</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>5605.12</v>
+      </c>
+      <c r="D534" t="n">
+        <v>97.89</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="n">
+        <v>46076.28937723796</v>
+      </c>
+      <c r="I534" s="2" t="n">
+        <v>46081.28937723796</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>9774cb84-086c-40db-865b-c976b64475a2</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>4467.2</v>
+      </c>
+      <c r="D535" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="n">
+        <v>46071.28937724121</v>
+      </c>
+      <c r="I535" s="2" t="n">
+        <v>46076.28937724121</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>0d779aa8-c4f0-45da-8844-f567af0f8547</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>1880.18</v>
+      </c>
+      <c r="D536" t="n">
+        <v>85.31</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="n">
+        <v>46082.28937724436</v>
+      </c>
+      <c r="I536" s="2" t="n">
+        <v>46087.28937724436</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>726a1bdc-4d06-41fb-a09e-4a3d8c5e7e2d</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>4028.68</v>
+      </c>
+      <c r="D537" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="n">
+        <v>46062.28937724741</v>
+      </c>
+      <c r="I537" s="2" t="n">
+        <v>46067.28937724741</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>908ff0e0-f310-40fe-8b84-bcb2d57ad229</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>3441.17</v>
+      </c>
+      <c r="D538" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="n">
+        <v>46068.28937725046</v>
+      </c>
+      <c r="I538" s="2" t="n">
+        <v>46073.28937725046</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>135ff89b-d2fc-4935-9b2e-93553ce79319</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>3307.46</v>
+      </c>
+      <c r="D539" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="n">
+        <v>46061.28937725391</v>
+      </c>
+      <c r="I539" s="2" t="n">
+        <v>46066.28937725391</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1e969486-84aa-4a88-b040-ac5139d7e23a</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>9384.780000000001</v>
+      </c>
+      <c r="D540" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="n">
+        <v>46064.2893772571</v>
+      </c>
+      <c r="I540" s="2" t="n">
+        <v>46069.2893772571</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>f033f3d2-1684-411f-86ff-0d627471bfc3</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>8833.99</v>
+      </c>
+      <c r="D541" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="n">
+        <v>46073.28937726014</v>
+      </c>
+      <c r="I541" s="2" t="n">
+        <v>46078.28937726014</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>8a90a5d8-615a-414d-b948-ef092bb3d01f</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>8386.700000000001</v>
+      </c>
+      <c r="D542" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="n">
+        <v>46072.28937726333</v>
+      </c>
+      <c r="I542" s="2" t="n">
+        <v>46077.28937726333</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>8bc3055e-1d7a-470f-939d-71683953f6c2</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>7151.21</v>
+      </c>
+      <c r="D543" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="n">
+        <v>46078.28937726654</v>
+      </c>
+      <c r="I543" s="2" t="n">
+        <v>46083.28937726654</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>42c94772-d4d2-48c3-a8ad-338a048d326e</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>3728.78</v>
+      </c>
+      <c r="D544" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="n">
+        <v>46070.2893772696</v>
+      </c>
+      <c r="I544" s="2" t="n">
+        <v>46075.2893772696</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>aa2007bf-5feb-46c8-94fe-bc80c14947be</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>1418.33</v>
+      </c>
+      <c r="D545" t="n">
+        <v>95.98</v>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="n">
+        <v>46070.28937727264</v>
+      </c>
+      <c r="I545" s="2" t="n">
+        <v>46075.28937727264</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>c4175400-89a6-4a00-83d2-a5b72a96bb72</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>1958.55</v>
+      </c>
+      <c r="D546" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="n">
+        <v>46060.28937727593</v>
+      </c>
+      <c r="I546" s="2" t="n">
+        <v>46065.28937727593</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>01e09385-4abb-4812-b1ea-404f354439d1</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>3245.63</v>
+      </c>
+      <c r="D547" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="n">
+        <v>46071.28937727897</v>
+      </c>
+      <c r="I547" s="2" t="n">
+        <v>46076.28937727897</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>7fa8ff52-3eee-464e-8f49-19665668962a</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>4393.23</v>
+      </c>
+      <c r="D548" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="n">
+        <v>46080.28937728214</v>
+      </c>
+      <c r="I548" s="2" t="n">
+        <v>46085.28937728214</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>c5e5ec90-e2a0-4736-9a78-a7a000a7d918</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>5843.58</v>
+      </c>
+      <c r="D549" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="n">
+        <v>46084.28937728524</v>
+      </c>
+      <c r="I549" s="2" t="n">
+        <v>46089.28937728524</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>0bb29069-9141-4a52-b71b-a2f6cae240de</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>8998.34</v>
+      </c>
+      <c r="D550" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="n">
+        <v>46066.28937728846</v>
+      </c>
+      <c r="I550" s="2" t="n">
+        <v>46071.28937728846</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>e79ed416-2b36-485d-b7a8-c2747f1b5ebb</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>6541.12</v>
+      </c>
+      <c r="D551" t="n">
+        <v>91.03</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="n">
+        <v>46061.28937729153</v>
+      </c>
+      <c r="I551" s="2" t="n">
+        <v>46066.28937729153</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I551"/>
+  <dimension ref="A1:I601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20012,10 +20012,10 @@
         </is>
       </c>
       <c r="H502" s="2" t="n">
-        <v>46087.28937713445</v>
+        <v>46087.28937712963</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>46092.28937713445</v>
+        <v>46092.28937712963</v>
       </c>
     </row>
     <row r="503">
@@ -20051,10 +20051,10 @@
         </is>
       </c>
       <c r="H503" s="2" t="n">
-        <v>46088.28937713874</v>
+        <v>46088.28937714121</v>
       </c>
       <c r="I503" s="2" t="n">
-        <v>46093.28937713874</v>
+        <v>46093.28937714121</v>
       </c>
     </row>
     <row r="504">
@@ -20090,10 +20090,10 @@
         </is>
       </c>
       <c r="H504" s="2" t="n">
-        <v>46064.28937714201</v>
+        <v>46064.28937714121</v>
       </c>
       <c r="I504" s="2" t="n">
-        <v>46069.28937714201</v>
+        <v>46069.28937714121</v>
       </c>
     </row>
     <row r="505">
@@ -20129,10 +20129,10 @@
         </is>
       </c>
       <c r="H505" s="2" t="n">
-        <v>46065.2893771453</v>
+        <v>46065.28937714121</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>46070.2893771453</v>
+        <v>46070.28937714121</v>
       </c>
     </row>
     <row r="506">
@@ -20168,10 +20168,10 @@
         </is>
       </c>
       <c r="H506" s="2" t="n">
-        <v>46070.28937714858</v>
+        <v>46070.28937715277</v>
       </c>
       <c r="I506" s="2" t="n">
-        <v>46075.28937714858</v>
+        <v>46075.28937715277</v>
       </c>
     </row>
     <row r="507">
@@ -20207,10 +20207,10 @@
         </is>
       </c>
       <c r="H507" s="2" t="n">
-        <v>46059.28937715171</v>
+        <v>46059.28937715277</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>46064.28937715171</v>
+        <v>46064.28937715277</v>
       </c>
     </row>
     <row r="508">
@@ -20246,10 +20246,10 @@
         </is>
       </c>
       <c r="H508" s="2" t="n">
-        <v>46070.28937715492</v>
+        <v>46070.28937715277</v>
       </c>
       <c r="I508" s="2" t="n">
-        <v>46075.28937715492</v>
+        <v>46075.28937715277</v>
       </c>
     </row>
     <row r="509">
@@ -20285,10 +20285,10 @@
         </is>
       </c>
       <c r="H509" s="2" t="n">
-        <v>46061.28937715817</v>
+        <v>46061.28937715277</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>46066.28937715817</v>
+        <v>46066.28937715277</v>
       </c>
     </row>
     <row r="510">
@@ -20324,10 +20324,10 @@
         </is>
       </c>
       <c r="H510" s="2" t="n">
-        <v>46088.28937716169</v>
+        <v>46088.28937716435</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>46093.28937716169</v>
+        <v>46093.28937716435</v>
       </c>
     </row>
     <row r="511">
@@ -20363,10 +20363,10 @@
         </is>
       </c>
       <c r="H511" s="2" t="n">
-        <v>46081.28937716501</v>
+        <v>46081.28937716435</v>
       </c>
       <c r="I511" s="2" t="n">
-        <v>46086.28937716501</v>
+        <v>46086.28937716435</v>
       </c>
     </row>
     <row r="512">
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="H512" s="2" t="n">
-        <v>46065.2893771681</v>
+        <v>46065.28937716435</v>
       </c>
       <c r="I512" s="2" t="n">
-        <v>46070.2893771681</v>
+        <v>46070.28937716435</v>
       </c>
     </row>
     <row r="513">
@@ -20441,10 +20441,10 @@
         </is>
       </c>
       <c r="H513" s="2" t="n">
-        <v>46085.28937717142</v>
+        <v>46085.28937717593</v>
       </c>
       <c r="I513" s="2" t="n">
-        <v>46090.28937717142</v>
+        <v>46090.28937717593</v>
       </c>
     </row>
     <row r="514">
@@ -20480,10 +20480,10 @@
         </is>
       </c>
       <c r="H514" s="2" t="n">
-        <v>46067.28937717469</v>
+        <v>46067.28937717593</v>
       </c>
       <c r="I514" s="2" t="n">
-        <v>46072.28937717469</v>
+        <v>46072.28937717593</v>
       </c>
     </row>
     <row r="515">
@@ -20519,10 +20519,10 @@
         </is>
       </c>
       <c r="H515" s="2" t="n">
-        <v>46088.28937717786</v>
+        <v>46088.28937717593</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>46093.28937717786</v>
+        <v>46093.28937717593</v>
       </c>
     </row>
     <row r="516">
@@ -20558,10 +20558,10 @@
         </is>
       </c>
       <c r="H516" s="2" t="n">
-        <v>46076.28937718103</v>
+        <v>46076.28937717593</v>
       </c>
       <c r="I516" s="2" t="n">
-        <v>46081.28937718103</v>
+        <v>46081.28937717593</v>
       </c>
     </row>
     <row r="517">
@@ -20597,10 +20597,10 @@
         </is>
       </c>
       <c r="H517" s="2" t="n">
-        <v>46075.28937718428</v>
+        <v>46075.2893771875</v>
       </c>
       <c r="I517" s="2" t="n">
-        <v>46080.28937718428</v>
+        <v>46080.2893771875</v>
       </c>
     </row>
     <row r="518">
@@ -20636,10 +20636,10 @@
         </is>
       </c>
       <c r="H518" s="2" t="n">
-        <v>46066.28937718735</v>
+        <v>46066.2893771875</v>
       </c>
       <c r="I518" s="2" t="n">
-        <v>46071.28937718735</v>
+        <v>46071.2893771875</v>
       </c>
     </row>
     <row r="519">
@@ -20675,10 +20675,10 @@
         </is>
       </c>
       <c r="H519" s="2" t="n">
-        <v>46067.28937719043</v>
+        <v>46067.2893771875</v>
       </c>
       <c r="I519" s="2" t="n">
-        <v>46072.28937719043</v>
+        <v>46072.2893771875</v>
       </c>
     </row>
     <row r="520">
@@ -20714,10 +20714,10 @@
         </is>
       </c>
       <c r="H520" s="2" t="n">
-        <v>46059.28937719367</v>
+        <v>46059.28937719907</v>
       </c>
       <c r="I520" s="2" t="n">
-        <v>46064.28937719367</v>
+        <v>46064.28937719907</v>
       </c>
     </row>
     <row r="521">
@@ -20753,10 +20753,10 @@
         </is>
       </c>
       <c r="H521" s="2" t="n">
-        <v>46064.28937719674</v>
+        <v>46064.28937719907</v>
       </c>
       <c r="I521" s="2" t="n">
-        <v>46069.28937719674</v>
+        <v>46069.28937719907</v>
       </c>
     </row>
     <row r="522">
@@ -20792,10 +20792,10 @@
         </is>
       </c>
       <c r="H522" s="2" t="n">
-        <v>46082.28937719977</v>
+        <v>46082.28937719907</v>
       </c>
       <c r="I522" s="2" t="n">
-        <v>46087.28937719977</v>
+        <v>46087.28937719907</v>
       </c>
     </row>
     <row r="523">
@@ -20831,10 +20831,10 @@
         </is>
       </c>
       <c r="H523" s="2" t="n">
-        <v>46076.2893772028</v>
+        <v>46076.28937719907</v>
       </c>
       <c r="I523" s="2" t="n">
-        <v>46081.2893772028</v>
+        <v>46081.28937719907</v>
       </c>
     </row>
     <row r="524">
@@ -20870,10 +20870,10 @@
         </is>
       </c>
       <c r="H524" s="2" t="n">
-        <v>46071.28937720609</v>
+        <v>46071.28937721065</v>
       </c>
       <c r="I524" s="2" t="n">
-        <v>46076.28937720609</v>
+        <v>46076.28937721065</v>
       </c>
     </row>
     <row r="525">
@@ -20909,10 +20909,10 @@
         </is>
       </c>
       <c r="H525" s="2" t="n">
-        <v>46077.28937720925</v>
+        <v>46077.28937721065</v>
       </c>
       <c r="I525" s="2" t="n">
-        <v>46082.28937720925</v>
+        <v>46082.28937721065</v>
       </c>
     </row>
     <row r="526">
@@ -20948,10 +20948,10 @@
         </is>
       </c>
       <c r="H526" s="2" t="n">
-        <v>46088.28937721228</v>
+        <v>46088.28937721065</v>
       </c>
       <c r="I526" s="2" t="n">
-        <v>46093.28937721228</v>
+        <v>46093.28937721065</v>
       </c>
     </row>
     <row r="527">
@@ -20987,10 +20987,10 @@
         </is>
       </c>
       <c r="H527" s="2" t="n">
-        <v>46085.28937721553</v>
+        <v>46085.28937721065</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>46090.28937721553</v>
+        <v>46090.28937721065</v>
       </c>
     </row>
     <row r="528">
@@ -21026,10 +21026,10 @@
         </is>
       </c>
       <c r="H528" s="2" t="n">
-        <v>46079.28937721903</v>
+        <v>46079.28937722222</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>46084.28937721903</v>
+        <v>46084.28937722222</v>
       </c>
     </row>
     <row r="529">
@@ -21065,10 +21065,10 @@
         </is>
       </c>
       <c r="H529" s="2" t="n">
-        <v>46084.28937722214</v>
+        <v>46084.28937722222</v>
       </c>
       <c r="I529" s="2" t="n">
-        <v>46089.28937722214</v>
+        <v>46089.28937722222</v>
       </c>
     </row>
     <row r="530">
@@ -21104,10 +21104,10 @@
         </is>
       </c>
       <c r="H530" s="2" t="n">
-        <v>46061.28937722528</v>
+        <v>46061.28937722222</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>46066.28937722528</v>
+        <v>46066.28937722222</v>
       </c>
     </row>
     <row r="531">
@@ -21143,10 +21143,10 @@
         </is>
       </c>
       <c r="H531" s="2" t="n">
-        <v>46078.28937722873</v>
+        <v>46078.2893772338</v>
       </c>
       <c r="I531" s="2" t="n">
-        <v>46083.28937722873</v>
+        <v>46083.2893772338</v>
       </c>
     </row>
     <row r="532">
@@ -21182,10 +21182,10 @@
         </is>
       </c>
       <c r="H532" s="2" t="n">
-        <v>46061.28937723182</v>
+        <v>46061.2893772338</v>
       </c>
       <c r="I532" s="2" t="n">
-        <v>46066.28937723182</v>
+        <v>46066.2893772338</v>
       </c>
     </row>
     <row r="533">
@@ -21221,10 +21221,10 @@
         </is>
       </c>
       <c r="H533" s="2" t="n">
-        <v>46069.28937723486</v>
+        <v>46069.2893772338</v>
       </c>
       <c r="I533" s="2" t="n">
-        <v>46074.28937723486</v>
+        <v>46074.2893772338</v>
       </c>
     </row>
     <row r="534">
@@ -21260,10 +21260,10 @@
         </is>
       </c>
       <c r="H534" s="2" t="n">
-        <v>46076.28937723796</v>
+        <v>46076.2893772338</v>
       </c>
       <c r="I534" s="2" t="n">
-        <v>46081.28937723796</v>
+        <v>46081.2893772338</v>
       </c>
     </row>
     <row r="535">
@@ -21299,10 +21299,10 @@
         </is>
       </c>
       <c r="H535" s="2" t="n">
-        <v>46071.28937724121</v>
+        <v>46071.28937724537</v>
       </c>
       <c r="I535" s="2" t="n">
-        <v>46076.28937724121</v>
+        <v>46076.28937724537</v>
       </c>
     </row>
     <row r="536">
@@ -21338,10 +21338,10 @@
         </is>
       </c>
       <c r="H536" s="2" t="n">
-        <v>46082.28937724436</v>
+        <v>46082.28937724537</v>
       </c>
       <c r="I536" s="2" t="n">
-        <v>46087.28937724436</v>
+        <v>46087.28937724537</v>
       </c>
     </row>
     <row r="537">
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="H537" s="2" t="n">
-        <v>46062.28937724741</v>
+        <v>46062.28937724537</v>
       </c>
       <c r="I537" s="2" t="n">
-        <v>46067.28937724741</v>
+        <v>46067.28937724537</v>
       </c>
     </row>
     <row r="538">
@@ -21416,10 +21416,10 @@
         </is>
       </c>
       <c r="H538" s="2" t="n">
-        <v>46068.28937725046</v>
+        <v>46068.28937724537</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>46073.28937725046</v>
+        <v>46073.28937724537</v>
       </c>
     </row>
     <row r="539">
@@ -21455,10 +21455,10 @@
         </is>
       </c>
       <c r="H539" s="2" t="n">
-        <v>46061.28937725391</v>
+        <v>46061.28937725694</v>
       </c>
       <c r="I539" s="2" t="n">
-        <v>46066.28937725391</v>
+        <v>46066.28937725694</v>
       </c>
     </row>
     <row r="540">
@@ -21494,10 +21494,10 @@
         </is>
       </c>
       <c r="H540" s="2" t="n">
-        <v>46064.2893772571</v>
+        <v>46064.28937725694</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>46069.2893772571</v>
+        <v>46069.28937725694</v>
       </c>
     </row>
     <row r="541">
@@ -21533,10 +21533,10 @@
         </is>
       </c>
       <c r="H541" s="2" t="n">
-        <v>46073.28937726014</v>
+        <v>46073.28937725694</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>46078.28937726014</v>
+        <v>46078.28937725694</v>
       </c>
     </row>
     <row r="542">
@@ -21572,10 +21572,10 @@
         </is>
       </c>
       <c r="H542" s="2" t="n">
-        <v>46072.28937726333</v>
+        <v>46072.28937726852</v>
       </c>
       <c r="I542" s="2" t="n">
-        <v>46077.28937726333</v>
+        <v>46077.28937726852</v>
       </c>
     </row>
     <row r="543">
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="H543" s="2" t="n">
-        <v>46078.28937726654</v>
+        <v>46078.28937726852</v>
       </c>
       <c r="I543" s="2" t="n">
-        <v>46083.28937726654</v>
+        <v>46083.28937726852</v>
       </c>
     </row>
     <row r="544">
@@ -21650,10 +21650,10 @@
         </is>
       </c>
       <c r="H544" s="2" t="n">
-        <v>46070.2893772696</v>
+        <v>46070.28937726852</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>46075.2893772696</v>
+        <v>46075.28937726852</v>
       </c>
     </row>
     <row r="545">
@@ -21689,10 +21689,10 @@
         </is>
       </c>
       <c r="H545" s="2" t="n">
-        <v>46070.28937727264</v>
+        <v>46070.28937726852</v>
       </c>
       <c r="I545" s="2" t="n">
-        <v>46075.28937727264</v>
+        <v>46075.28937726852</v>
       </c>
     </row>
     <row r="546">
@@ -21728,10 +21728,10 @@
         </is>
       </c>
       <c r="H546" s="2" t="n">
-        <v>46060.28937727593</v>
+        <v>46060.28937728009</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>46065.28937727593</v>
+        <v>46065.28937728009</v>
       </c>
     </row>
     <row r="547">
@@ -21767,10 +21767,10 @@
         </is>
       </c>
       <c r="H547" s="2" t="n">
-        <v>46071.28937727897</v>
+        <v>46071.28937728009</v>
       </c>
       <c r="I547" s="2" t="n">
-        <v>46076.28937727897</v>
+        <v>46076.28937728009</v>
       </c>
     </row>
     <row r="548">
@@ -21806,10 +21806,10 @@
         </is>
       </c>
       <c r="H548" s="2" t="n">
-        <v>46080.28937728214</v>
+        <v>46080.28937728009</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>46085.28937728214</v>
+        <v>46085.28937728009</v>
       </c>
     </row>
     <row r="549">
@@ -21845,10 +21845,10 @@
         </is>
       </c>
       <c r="H549" s="2" t="n">
-        <v>46084.28937728524</v>
+        <v>46084.28937728009</v>
       </c>
       <c r="I549" s="2" t="n">
-        <v>46089.28937728524</v>
+        <v>46089.28937728009</v>
       </c>
     </row>
     <row r="550">
@@ -21884,10 +21884,10 @@
         </is>
       </c>
       <c r="H550" s="2" t="n">
-        <v>46066.28937728846</v>
+        <v>46066.28937729167</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>46071.28937728846</v>
+        <v>46071.28937729167</v>
       </c>
     </row>
     <row r="551">
@@ -21923,10 +21923,1960 @@
         </is>
       </c>
       <c r="H551" s="2" t="n">
-        <v>46061.28937729153</v>
+        <v>46061.28937729167</v>
       </c>
       <c r="I551" s="2" t="n">
-        <v>46066.28937729153</v>
+        <v>46066.28937729167</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>857d0806-0f10-4330-b2ed-de37b27b20a9</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>2194.09</v>
+      </c>
+      <c r="D552" t="n">
+        <v>91.11</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="n">
+        <v>46060.54629734754</v>
+      </c>
+      <c r="I552" s="2" t="n">
+        <v>46065.54629734754</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>eb4f135f-8fa3-4324-93b0-bf69a241c5ac</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>4432.97</v>
+      </c>
+      <c r="D553" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="n">
+        <v>46081.54629735218</v>
+      </c>
+      <c r="I553" s="2" t="n">
+        <v>46086.54629735218</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>6c633a38-fa58-48b4-84a9-cde12968c4af</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>2714.3</v>
+      </c>
+      <c r="D554" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="n">
+        <v>46067.54629735544</v>
+      </c>
+      <c r="I554" s="2" t="n">
+        <v>46072.54629735544</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>d7f36b98-11ed-4cbb-bb59-667f7df12f6a</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>1595.72</v>
+      </c>
+      <c r="D555" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="n">
+        <v>46069.54629735871</v>
+      </c>
+      <c r="I555" s="2" t="n">
+        <v>46074.54629735871</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>b74b4d9e-99cc-49de-9026-9be19d543019</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>9142.43</v>
+      </c>
+      <c r="D556" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="n">
+        <v>46079.5462973621</v>
+      </c>
+      <c r="I556" s="2" t="n">
+        <v>46084.5462973621</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>9445f8fd-7161-4c7f-8fea-4db374579ad8</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>6989.15</v>
+      </c>
+      <c r="D557" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="n">
+        <v>46064.5462973658</v>
+      </c>
+      <c r="I557" s="2" t="n">
+        <v>46069.5462973658</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>f6fed973-70e2-4efe-a175-86f338d5d1b4</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>1033.1</v>
+      </c>
+      <c r="D558" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="n">
+        <v>46076.54629736891</v>
+      </c>
+      <c r="I558" s="2" t="n">
+        <v>46081.54629736891</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>51628fa4-128b-42ab-9dfa-66d55d3213f1</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>9540.4</v>
+      </c>
+      <c r="D559" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="n">
+        <v>46077.54629737206</v>
+      </c>
+      <c r="I559" s="2" t="n">
+        <v>46082.54629737206</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>b1c8d170-cc99-40af-a96d-6635ca9be7d2</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>3836.56</v>
+      </c>
+      <c r="D560" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="n">
+        <v>46088.54629737534</v>
+      </c>
+      <c r="I560" s="2" t="n">
+        <v>46093.54629737534</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>61360ffd-a88c-4ad0-a464-3a300c2c0aab</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>9766.76</v>
+      </c>
+      <c r="D561" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="n">
+        <v>46069.54629737847</v>
+      </c>
+      <c r="I561" s="2" t="n">
+        <v>46074.54629737847</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>09a58def-7756-4ede-9f0a-af3b60374bd7</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>3769.89</v>
+      </c>
+      <c r="D562" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="n">
+        <v>46077.54629738196</v>
+      </c>
+      <c r="I562" s="2" t="n">
+        <v>46082.54629738196</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>c0bb005f-031d-45b9-ae7b-7849d437915c</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>7855.33</v>
+      </c>
+      <c r="D563" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="n">
+        <v>46059.54629738504</v>
+      </c>
+      <c r="I563" s="2" t="n">
+        <v>46064.54629738504</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>71bad39d-82c4-4838-8ba5-50e0e33b7f01</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>7828.02</v>
+      </c>
+      <c r="D564" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="n">
+        <v>46071.54629738865</v>
+      </c>
+      <c r="I564" s="2" t="n">
+        <v>46076.54629738865</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>b875e5c8-7728-412d-9b81-f2e669aa7ff0</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>8120.27</v>
+      </c>
+      <c r="D565" t="n">
+        <v>96.73999999999999</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="n">
+        <v>46079.54629739174</v>
+      </c>
+      <c r="I565" s="2" t="n">
+        <v>46084.54629739174</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>fa40a6ee-08f8-417d-a633-a760fad3092b</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>4569.46</v>
+      </c>
+      <c r="D566" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="n">
+        <v>46087.5462973949</v>
+      </c>
+      <c r="I566" s="2" t="n">
+        <v>46092.5462973949</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>e4333b0f-b2a4-4be8-9efb-44e28f82761e</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>9642.459999999999</v>
+      </c>
+      <c r="D567" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="n">
+        <v>46067.54629739834</v>
+      </c>
+      <c r="I567" s="2" t="n">
+        <v>46072.54629739834</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>f88ba1b0-f075-43ff-8aa2-4f366bf9b2eb</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>9165.690000000001</v>
+      </c>
+      <c r="D568" t="n">
+        <v>88.72</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="n">
+        <v>46084.54629740229</v>
+      </c>
+      <c r="I568" s="2" t="n">
+        <v>46089.54629740229</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>fd95471f-48b8-4311-a108-ed46dca8e2b2</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>9787.15</v>
+      </c>
+      <c r="D569" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="n">
+        <v>46073.5462974054</v>
+      </c>
+      <c r="I569" s="2" t="n">
+        <v>46078.5462974054</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>11e37fbf-706a-4ad0-b9bd-134a2bbdcf03</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>6667.18</v>
+      </c>
+      <c r="D570" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="n">
+        <v>46075.54629740853</v>
+      </c>
+      <c r="I570" s="2" t="n">
+        <v>46080.54629740853</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>050659a0-ca13-4690-bd39-f6d0fe86ccbc</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>4667.99</v>
+      </c>
+      <c r="D571" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="n">
+        <v>46059.54629741182</v>
+      </c>
+      <c r="I571" s="2" t="n">
+        <v>46064.54629741182</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>3decbe6f-feb8-4242-9aac-1efb05f7a6ed</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>6592.52</v>
+      </c>
+      <c r="D572" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="n">
+        <v>46071.54629741496</v>
+      </c>
+      <c r="I572" s="2" t="n">
+        <v>46076.54629741496</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>75620955-b8a1-4cfd-b93d-3737aa4e4ca1</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>4302.68</v>
+      </c>
+      <c r="D573" t="n">
+        <v>98.31999999999999</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="n">
+        <v>46084.54629741821</v>
+      </c>
+      <c r="I573" s="2" t="n">
+        <v>46089.54629741821</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>cf99d64b-36dd-4621-9f62-d18c7be066c1</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>2608.84</v>
+      </c>
+      <c r="D574" t="n">
+        <v>89.45999999999999</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="n">
+        <v>46083.54629742145</v>
+      </c>
+      <c r="I574" s="2" t="n">
+        <v>46088.54629742145</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>43351dfe-fa9b-4f09-be50-a716542d3a47</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>7007.58</v>
+      </c>
+      <c r="D575" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="n">
+        <v>46067.54629742468</v>
+      </c>
+      <c r="I575" s="2" t="n">
+        <v>46072.54629742468</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>0be1c8d4-3702-47dd-a82d-9014c688e352</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>8274.1</v>
+      </c>
+      <c r="D576" t="n">
+        <v>94.14</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="n">
+        <v>46069.54629742775</v>
+      </c>
+      <c r="I576" s="2" t="n">
+        <v>46074.54629742775</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>352bc9c0-e473-4f44-9c4e-34e92f74c107</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>7824.75</v>
+      </c>
+      <c r="D577" t="n">
+        <v>98.39</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="n">
+        <v>46079.54629743101</v>
+      </c>
+      <c r="I577" s="2" t="n">
+        <v>46084.54629743101</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>c1353d4a-e856-4a88-98f9-f735cab6e869</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>4838.27</v>
+      </c>
+      <c r="D578" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="n">
+        <v>46071.54629743465</v>
+      </c>
+      <c r="I578" s="2" t="n">
+        <v>46076.54629743465</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>87626a0e-0c5e-4d23-8538-1eb671eaa3a7</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>9399.27</v>
+      </c>
+      <c r="D579" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="n">
+        <v>46067.54629743786</v>
+      </c>
+      <c r="I579" s="2" t="n">
+        <v>46072.54629743786</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>5e2d5d1c-9749-4099-829b-fcf41f7754cb</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>3140.55</v>
+      </c>
+      <c r="D580" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="n">
+        <v>46086.54629744092</v>
+      </c>
+      <c r="I580" s="2" t="n">
+        <v>46091.54629744092</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>7a3042fb-ac42-468c-ae74-471addfd3050</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>8020.4</v>
+      </c>
+      <c r="D581" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="n">
+        <v>46066.54629744399</v>
+      </c>
+      <c r="I581" s="2" t="n">
+        <v>46071.54629744399</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>a2b947cd-5653-42d6-933d-dd5fdecb4f6c</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>3753.61</v>
+      </c>
+      <c r="D582" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="n">
+        <v>46088.5462974475</v>
+      </c>
+      <c r="I582" s="2" t="n">
+        <v>46093.5462974475</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>642f472d-2963-4870-a708-3e6cfe013157</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>4219.66</v>
+      </c>
+      <c r="D583" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="n">
+        <v>46076.54629745054</v>
+      </c>
+      <c r="I583" s="2" t="n">
+        <v>46081.54629745054</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>d78c8701-5c91-491d-960e-fa7e50fc5f95</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>8384.799999999999</v>
+      </c>
+      <c r="D584" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="n">
+        <v>46067.54629745373</v>
+      </c>
+      <c r="I584" s="2" t="n">
+        <v>46072.54629745373</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>3c4bda8b-4d61-470f-81bc-ac3410ffb05a</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>1464.9</v>
+      </c>
+      <c r="D585" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="n">
+        <v>46073.54629745705</v>
+      </c>
+      <c r="I585" s="2" t="n">
+        <v>46078.54629745705</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>b39f60fd-2d5e-4745-a505-349e3c08912b</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>7308.09</v>
+      </c>
+      <c r="D586" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="n">
+        <v>46075.54629746026</v>
+      </c>
+      <c r="I586" s="2" t="n">
+        <v>46080.54629746026</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>3bad2eb8-0e7a-4958-a82e-45ee1cfa3e75</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>4141.77</v>
+      </c>
+      <c r="D587" t="n">
+        <v>85.62</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="n">
+        <v>46062.54629746337</v>
+      </c>
+      <c r="I587" s="2" t="n">
+        <v>46067.54629746337</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>4c0c5e7f-1307-49b9-a3fc-37bafcd1ec64</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>2710.12</v>
+      </c>
+      <c r="D588" t="n">
+        <v>88.72</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="n">
+        <v>46069.5462974664</v>
+      </c>
+      <c r="I588" s="2" t="n">
+        <v>46074.5462974664</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>fc1bb941-e2a7-434a-86fb-c9d476559f3f</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>9913.25</v>
+      </c>
+      <c r="D589" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="n">
+        <v>46074.54629746974</v>
+      </c>
+      <c r="I589" s="2" t="n">
+        <v>46079.54629746974</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2743224a-c38b-45fe-b4af-bd238ef77cdb</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>3647.8</v>
+      </c>
+      <c r="D590" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="n">
+        <v>46088.54629747287</v>
+      </c>
+      <c r="I590" s="2" t="n">
+        <v>46093.54629747287</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>0d34b840-4a4b-42cc-8f1a-25de96dc0458</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>3512.64</v>
+      </c>
+      <c r="D591" t="n">
+        <v>88.66</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="n">
+        <v>46075.54629747595</v>
+      </c>
+      <c r="I591" s="2" t="n">
+        <v>46080.54629747595</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>953f8dd7-1efc-4020-bbc7-4f1fab2a68ee</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>2240.89</v>
+      </c>
+      <c r="D592" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="n">
+        <v>46083.54629747938</v>
+      </c>
+      <c r="I592" s="2" t="n">
+        <v>46088.54629747938</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>55744d16-dd40-4b24-a479-2241a1e83a67</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>4129.37</v>
+      </c>
+      <c r="D593" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="n">
+        <v>46062.54629748264</v>
+      </c>
+      <c r="I593" s="2" t="n">
+        <v>46067.54629748264</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>77beae8d-b1ff-449c-9e6c-ee5fe115b020</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>7015.71</v>
+      </c>
+      <c r="D594" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="n">
+        <v>46073.54629748569</v>
+      </c>
+      <c r="I594" s="2" t="n">
+        <v>46078.54629748569</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>cc659dc5-0296-485a-979d-074e4b27294d</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>9016.08</v>
+      </c>
+      <c r="D595" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="n">
+        <v>46075.54629748885</v>
+      </c>
+      <c r="I595" s="2" t="n">
+        <v>46080.54629748885</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>669b8b1a-0341-428d-97a3-b4e7169f7cd0</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>9127.860000000001</v>
+      </c>
+      <c r="D596" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="n">
+        <v>46078.54629749214</v>
+      </c>
+      <c r="I596" s="2" t="n">
+        <v>46083.54629749214</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>4524f329-85e0-4838-99ef-063f2d97aec9</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>7845.17</v>
+      </c>
+      <c r="D597" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="n">
+        <v>46077.54629749537</v>
+      </c>
+      <c r="I597" s="2" t="n">
+        <v>46082.54629749537</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>7e358781-1a40-4444-a375-286af92691c0</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>8789.07</v>
+      </c>
+      <c r="D598" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="n">
+        <v>46087.54629749839</v>
+      </c>
+      <c r="I598" s="2" t="n">
+        <v>46092.54629749839</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>0e3b467c-d658-4c4d-ab9b-f395d55ef1f8</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>3958.84</v>
+      </c>
+      <c r="D599" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="n">
+        <v>46064.5462975016</v>
+      </c>
+      <c r="I599" s="2" t="n">
+        <v>46069.5462975016</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>d328b2dc-a7de-4b46-83f1-1808496a8d0c</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>7384.35</v>
+      </c>
+      <c r="D600" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="n">
+        <v>46065.54629750497</v>
+      </c>
+      <c r="I600" s="2" t="n">
+        <v>46070.54629750497</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>a2b32d8e-f6fb-4f74-bd5d-9ea01cf17cdb</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>7363.76</v>
+      </c>
+      <c r="D601" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="n">
+        <v>46079.54629750804</v>
+      </c>
+      <c r="I601" s="2" t="n">
+        <v>46084.54629750804</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I601"/>
+  <dimension ref="A1:I651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="H552" s="2" t="n">
-        <v>46060.54629734754</v>
+        <v>46060.54629734954</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>46065.54629734754</v>
+        <v>46065.54629734954</v>
       </c>
     </row>
     <row r="553">
@@ -22001,10 +22001,10 @@
         </is>
       </c>
       <c r="H553" s="2" t="n">
-        <v>46081.54629735218</v>
+        <v>46081.54629734954</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>46086.54629735218</v>
+        <v>46086.54629734954</v>
       </c>
     </row>
     <row r="554">
@@ -22040,10 +22040,10 @@
         </is>
       </c>
       <c r="H554" s="2" t="n">
-        <v>46067.54629735544</v>
+        <v>46067.54629736111</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>46072.54629735544</v>
+        <v>46072.54629736111</v>
       </c>
     </row>
     <row r="555">
@@ -22079,10 +22079,10 @@
         </is>
       </c>
       <c r="H555" s="2" t="n">
-        <v>46069.54629735871</v>
+        <v>46069.54629736111</v>
       </c>
       <c r="I555" s="2" t="n">
-        <v>46074.54629735871</v>
+        <v>46074.54629736111</v>
       </c>
     </row>
     <row r="556">
@@ -22118,10 +22118,10 @@
         </is>
       </c>
       <c r="H556" s="2" t="n">
-        <v>46079.5462973621</v>
+        <v>46079.54629736111</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>46084.5462973621</v>
+        <v>46084.54629736111</v>
       </c>
     </row>
     <row r="557">
@@ -22157,10 +22157,10 @@
         </is>
       </c>
       <c r="H557" s="2" t="n">
-        <v>46064.5462973658</v>
+        <v>46064.54629736111</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>46069.5462973658</v>
+        <v>46069.54629736111</v>
       </c>
     </row>
     <row r="558">
@@ -22196,10 +22196,10 @@
         </is>
       </c>
       <c r="H558" s="2" t="n">
-        <v>46076.54629736891</v>
+        <v>46076.54629737268</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>46081.54629736891</v>
+        <v>46081.54629737268</v>
       </c>
     </row>
     <row r="559">
@@ -22235,10 +22235,10 @@
         </is>
       </c>
       <c r="H559" s="2" t="n">
-        <v>46077.54629737206</v>
+        <v>46077.54629737268</v>
       </c>
       <c r="I559" s="2" t="n">
-        <v>46082.54629737206</v>
+        <v>46082.54629737268</v>
       </c>
     </row>
     <row r="560">
@@ -22274,10 +22274,10 @@
         </is>
       </c>
       <c r="H560" s="2" t="n">
-        <v>46088.54629737534</v>
+        <v>46088.54629737268</v>
       </c>
       <c r="I560" s="2" t="n">
-        <v>46093.54629737534</v>
+        <v>46093.54629737268</v>
       </c>
     </row>
     <row r="561">
@@ -22313,10 +22313,10 @@
         </is>
       </c>
       <c r="H561" s="2" t="n">
-        <v>46069.54629737847</v>
+        <v>46069.54629737268</v>
       </c>
       <c r="I561" s="2" t="n">
-        <v>46074.54629737847</v>
+        <v>46074.54629737268</v>
       </c>
     </row>
     <row r="562">
@@ -22352,10 +22352,10 @@
         </is>
       </c>
       <c r="H562" s="2" t="n">
-        <v>46077.54629738196</v>
+        <v>46077.54629738426</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>46082.54629738196</v>
+        <v>46082.54629738426</v>
       </c>
     </row>
     <row r="563">
@@ -22391,10 +22391,10 @@
         </is>
       </c>
       <c r="H563" s="2" t="n">
-        <v>46059.54629738504</v>
+        <v>46059.54629738426</v>
       </c>
       <c r="I563" s="2" t="n">
-        <v>46064.54629738504</v>
+        <v>46064.54629738426</v>
       </c>
     </row>
     <row r="564">
@@ -22430,10 +22430,10 @@
         </is>
       </c>
       <c r="H564" s="2" t="n">
-        <v>46071.54629738865</v>
+        <v>46071.54629738426</v>
       </c>
       <c r="I564" s="2" t="n">
-        <v>46076.54629738865</v>
+        <v>46076.54629738426</v>
       </c>
     </row>
     <row r="565">
@@ -22469,10 +22469,10 @@
         </is>
       </c>
       <c r="H565" s="2" t="n">
-        <v>46079.54629739174</v>
+        <v>46079.54629739583</v>
       </c>
       <c r="I565" s="2" t="n">
-        <v>46084.54629739174</v>
+        <v>46084.54629739583</v>
       </c>
     </row>
     <row r="566">
@@ -22508,10 +22508,10 @@
         </is>
       </c>
       <c r="H566" s="2" t="n">
-        <v>46087.5462973949</v>
+        <v>46087.54629739583</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>46092.5462973949</v>
+        <v>46092.54629739583</v>
       </c>
     </row>
     <row r="567">
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="H567" s="2" t="n">
-        <v>46067.54629739834</v>
+        <v>46067.54629739583</v>
       </c>
       <c r="I567" s="2" t="n">
-        <v>46072.54629739834</v>
+        <v>46072.54629739583</v>
       </c>
     </row>
     <row r="568">
@@ -22586,10 +22586,10 @@
         </is>
       </c>
       <c r="H568" s="2" t="n">
-        <v>46084.54629740229</v>
+        <v>46084.54629740741</v>
       </c>
       <c r="I568" s="2" t="n">
-        <v>46089.54629740229</v>
+        <v>46089.54629740741</v>
       </c>
     </row>
     <row r="569">
@@ -22625,10 +22625,10 @@
         </is>
       </c>
       <c r="H569" s="2" t="n">
-        <v>46073.5462974054</v>
+        <v>46073.54629740741</v>
       </c>
       <c r="I569" s="2" t="n">
-        <v>46078.5462974054</v>
+        <v>46078.54629740741</v>
       </c>
     </row>
     <row r="570">
@@ -22664,10 +22664,10 @@
         </is>
       </c>
       <c r="H570" s="2" t="n">
-        <v>46075.54629740853</v>
+        <v>46075.54629740741</v>
       </c>
       <c r="I570" s="2" t="n">
-        <v>46080.54629740853</v>
+        <v>46080.54629740741</v>
       </c>
     </row>
     <row r="571">
@@ -22703,10 +22703,10 @@
         </is>
       </c>
       <c r="H571" s="2" t="n">
-        <v>46059.54629741182</v>
+        <v>46059.54629740741</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>46064.54629741182</v>
+        <v>46064.54629740741</v>
       </c>
     </row>
     <row r="572">
@@ -22742,10 +22742,10 @@
         </is>
       </c>
       <c r="H572" s="2" t="n">
-        <v>46071.54629741496</v>
+        <v>46071.54629741898</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>46076.54629741496</v>
+        <v>46076.54629741898</v>
       </c>
     </row>
     <row r="573">
@@ -22781,10 +22781,10 @@
         </is>
       </c>
       <c r="H573" s="2" t="n">
-        <v>46084.54629741821</v>
+        <v>46084.54629741898</v>
       </c>
       <c r="I573" s="2" t="n">
-        <v>46089.54629741821</v>
+        <v>46089.54629741898</v>
       </c>
     </row>
     <row r="574">
@@ -22820,10 +22820,10 @@
         </is>
       </c>
       <c r="H574" s="2" t="n">
-        <v>46083.54629742145</v>
+        <v>46083.54629741898</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>46088.54629742145</v>
+        <v>46088.54629741898</v>
       </c>
     </row>
     <row r="575">
@@ -22859,10 +22859,10 @@
         </is>
       </c>
       <c r="H575" s="2" t="n">
-        <v>46067.54629742468</v>
+        <v>46067.54629741898</v>
       </c>
       <c r="I575" s="2" t="n">
-        <v>46072.54629742468</v>
+        <v>46072.54629741898</v>
       </c>
     </row>
     <row r="576">
@@ -22898,10 +22898,10 @@
         </is>
       </c>
       <c r="H576" s="2" t="n">
-        <v>46069.54629742775</v>
+        <v>46069.54629743056</v>
       </c>
       <c r="I576" s="2" t="n">
-        <v>46074.54629742775</v>
+        <v>46074.54629743056</v>
       </c>
     </row>
     <row r="577">
@@ -22937,10 +22937,10 @@
         </is>
       </c>
       <c r="H577" s="2" t="n">
-        <v>46079.54629743101</v>
+        <v>46079.54629743056</v>
       </c>
       <c r="I577" s="2" t="n">
-        <v>46084.54629743101</v>
+        <v>46084.54629743056</v>
       </c>
     </row>
     <row r="578">
@@ -22976,10 +22976,10 @@
         </is>
       </c>
       <c r="H578" s="2" t="n">
-        <v>46071.54629743465</v>
+        <v>46071.54629743056</v>
       </c>
       <c r="I578" s="2" t="n">
-        <v>46076.54629743465</v>
+        <v>46076.54629743056</v>
       </c>
     </row>
     <row r="579">
@@ -23015,10 +23015,10 @@
         </is>
       </c>
       <c r="H579" s="2" t="n">
-        <v>46067.54629743786</v>
+        <v>46067.54629744213</v>
       </c>
       <c r="I579" s="2" t="n">
-        <v>46072.54629743786</v>
+        <v>46072.54629744213</v>
       </c>
     </row>
     <row r="580">
@@ -23054,10 +23054,10 @@
         </is>
       </c>
       <c r="H580" s="2" t="n">
-        <v>46086.54629744092</v>
+        <v>46086.54629744213</v>
       </c>
       <c r="I580" s="2" t="n">
-        <v>46091.54629744092</v>
+        <v>46091.54629744213</v>
       </c>
     </row>
     <row r="581">
@@ -23093,10 +23093,10 @@
         </is>
       </c>
       <c r="H581" s="2" t="n">
-        <v>46066.54629744399</v>
+        <v>46066.54629744213</v>
       </c>
       <c r="I581" s="2" t="n">
-        <v>46071.54629744399</v>
+        <v>46071.54629744213</v>
       </c>
     </row>
     <row r="582">
@@ -23132,10 +23132,10 @@
         </is>
       </c>
       <c r="H582" s="2" t="n">
-        <v>46088.5462974475</v>
+        <v>46088.54629744213</v>
       </c>
       <c r="I582" s="2" t="n">
-        <v>46093.5462974475</v>
+        <v>46093.54629744213</v>
       </c>
     </row>
     <row r="583">
@@ -23171,10 +23171,10 @@
         </is>
       </c>
       <c r="H583" s="2" t="n">
-        <v>46076.54629745054</v>
+        <v>46076.5462974537</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>46081.54629745054</v>
+        <v>46081.5462974537</v>
       </c>
     </row>
     <row r="584">
@@ -23210,10 +23210,10 @@
         </is>
       </c>
       <c r="H584" s="2" t="n">
-        <v>46067.54629745373</v>
+        <v>46067.5462974537</v>
       </c>
       <c r="I584" s="2" t="n">
-        <v>46072.54629745373</v>
+        <v>46072.5462974537</v>
       </c>
     </row>
     <row r="585">
@@ -23249,10 +23249,10 @@
         </is>
       </c>
       <c r="H585" s="2" t="n">
-        <v>46073.54629745705</v>
+        <v>46073.5462974537</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>46078.54629745705</v>
+        <v>46078.5462974537</v>
       </c>
     </row>
     <row r="586">
@@ -23288,10 +23288,10 @@
         </is>
       </c>
       <c r="H586" s="2" t="n">
-        <v>46075.54629746026</v>
+        <v>46075.54629746528</v>
       </c>
       <c r="I586" s="2" t="n">
-        <v>46080.54629746026</v>
+        <v>46080.54629746528</v>
       </c>
     </row>
     <row r="587">
@@ -23327,10 +23327,10 @@
         </is>
       </c>
       <c r="H587" s="2" t="n">
-        <v>46062.54629746337</v>
+        <v>46062.54629746528</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>46067.54629746337</v>
+        <v>46067.54629746528</v>
       </c>
     </row>
     <row r="588">
@@ -23366,10 +23366,10 @@
         </is>
       </c>
       <c r="H588" s="2" t="n">
-        <v>46069.5462974664</v>
+        <v>46069.54629746528</v>
       </c>
       <c r="I588" s="2" t="n">
-        <v>46074.5462974664</v>
+        <v>46074.54629746528</v>
       </c>
     </row>
     <row r="589">
@@ -23405,10 +23405,10 @@
         </is>
       </c>
       <c r="H589" s="2" t="n">
-        <v>46074.54629746974</v>
+        <v>46074.54629746528</v>
       </c>
       <c r="I589" s="2" t="n">
-        <v>46079.54629746974</v>
+        <v>46079.54629746528</v>
       </c>
     </row>
     <row r="590">
@@ -23444,10 +23444,10 @@
         </is>
       </c>
       <c r="H590" s="2" t="n">
-        <v>46088.54629747287</v>
+        <v>46088.54629747685</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>46093.54629747287</v>
+        <v>46093.54629747685</v>
       </c>
     </row>
     <row r="591">
@@ -23483,10 +23483,10 @@
         </is>
       </c>
       <c r="H591" s="2" t="n">
-        <v>46075.54629747595</v>
+        <v>46075.54629747685</v>
       </c>
       <c r="I591" s="2" t="n">
-        <v>46080.54629747595</v>
+        <v>46080.54629747685</v>
       </c>
     </row>
     <row r="592">
@@ -23522,10 +23522,10 @@
         </is>
       </c>
       <c r="H592" s="2" t="n">
-        <v>46083.54629747938</v>
+        <v>46083.54629747685</v>
       </c>
       <c r="I592" s="2" t="n">
-        <v>46088.54629747938</v>
+        <v>46088.54629747685</v>
       </c>
     </row>
     <row r="593">
@@ -23561,10 +23561,10 @@
         </is>
       </c>
       <c r="H593" s="2" t="n">
-        <v>46062.54629748264</v>
+        <v>46062.54629747685</v>
       </c>
       <c r="I593" s="2" t="n">
-        <v>46067.54629748264</v>
+        <v>46067.54629747685</v>
       </c>
     </row>
     <row r="594">
@@ -23600,10 +23600,10 @@
         </is>
       </c>
       <c r="H594" s="2" t="n">
-        <v>46073.54629748569</v>
+        <v>46073.54629748843</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>46078.54629748569</v>
+        <v>46078.54629748843</v>
       </c>
     </row>
     <row r="595">
@@ -23639,10 +23639,10 @@
         </is>
       </c>
       <c r="H595" s="2" t="n">
-        <v>46075.54629748885</v>
+        <v>46075.54629748843</v>
       </c>
       <c r="I595" s="2" t="n">
-        <v>46080.54629748885</v>
+        <v>46080.54629748843</v>
       </c>
     </row>
     <row r="596">
@@ -23678,10 +23678,10 @@
         </is>
       </c>
       <c r="H596" s="2" t="n">
-        <v>46078.54629749214</v>
+        <v>46078.54629748843</v>
       </c>
       <c r="I596" s="2" t="n">
-        <v>46083.54629749214</v>
+        <v>46083.54629748843</v>
       </c>
     </row>
     <row r="597">
@@ -23717,10 +23717,10 @@
         </is>
       </c>
       <c r="H597" s="2" t="n">
-        <v>46077.54629749537</v>
+        <v>46077.5462975</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>46082.54629749537</v>
+        <v>46082.5462975</v>
       </c>
     </row>
     <row r="598">
@@ -23756,10 +23756,10 @@
         </is>
       </c>
       <c r="H598" s="2" t="n">
-        <v>46087.54629749839</v>
+        <v>46087.5462975</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>46092.54629749839</v>
+        <v>46092.5462975</v>
       </c>
     </row>
     <row r="599">
@@ -23795,10 +23795,10 @@
         </is>
       </c>
       <c r="H599" s="2" t="n">
-        <v>46064.5462975016</v>
+        <v>46064.5462975</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>46069.5462975016</v>
+        <v>46069.5462975</v>
       </c>
     </row>
     <row r="600">
@@ -23834,10 +23834,10 @@
         </is>
       </c>
       <c r="H600" s="2" t="n">
-        <v>46065.54629750497</v>
+        <v>46065.5462975</v>
       </c>
       <c r="I600" s="2" t="n">
-        <v>46070.54629750497</v>
+        <v>46070.5462975</v>
       </c>
     </row>
     <row r="601">
@@ -23873,10 +23873,1960 @@
         </is>
       </c>
       <c r="H601" s="2" t="n">
-        <v>46079.54629750804</v>
+        <v>46079.54629751157</v>
       </c>
       <c r="I601" s="2" t="n">
-        <v>46084.54629750804</v>
+        <v>46084.54629751157</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>baa7ed4a-8c68-4e77-aa14-524f47a81a93</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>6485.32</v>
+      </c>
+      <c r="D602" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="n">
+        <v>46066.59608732769</v>
+      </c>
+      <c r="I602" s="2" t="n">
+        <v>46071.59608732769</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>4c59bf3e-035d-4908-9763-6d5ec796f45c</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>2827.35</v>
+      </c>
+      <c r="D603" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="n">
+        <v>46079.5960873319</v>
+      </c>
+      <c r="I603" s="2" t="n">
+        <v>46084.5960873319</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>29f2432f-2ed0-4ba2-b0b6-7b4a407aeb59</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>7957.68</v>
+      </c>
+      <c r="D604" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="n">
+        <v>46081.5960873353</v>
+      </c>
+      <c r="I604" s="2" t="n">
+        <v>46086.5960873353</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>61e7dcd8-aeb7-4992-9db3-d06e9ab7cf61</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>3529.59</v>
+      </c>
+      <c r="D605" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="n">
+        <v>46063.59608733867</v>
+      </c>
+      <c r="I605" s="2" t="n">
+        <v>46068.59608733867</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>41107f68-3a74-4c9c-823c-daeeca3f891a</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>4645.27</v>
+      </c>
+      <c r="D606" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="n">
+        <v>46085.59608734177</v>
+      </c>
+      <c r="I606" s="2" t="n">
+        <v>46090.59608734177</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>b0976afb-6758-4dd8-a226-184be379d329</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>2423.21</v>
+      </c>
+      <c r="D607" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="n">
+        <v>46062.5960873451</v>
+      </c>
+      <c r="I607" s="2" t="n">
+        <v>46067.5960873451</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>68ada10e-146b-4b24-889a-e9d0b30756cb</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>9444.77</v>
+      </c>
+      <c r="D608" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="n">
+        <v>46072.59608734838</v>
+      </c>
+      <c r="I608" s="2" t="n">
+        <v>46077.59608734838</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>dcd2491e-29ba-4405-981d-8df9b2ecb71b</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>5363.95</v>
+      </c>
+      <c r="D609" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="n">
+        <v>46081.59608735154</v>
+      </c>
+      <c r="I609" s="2" t="n">
+        <v>46086.59608735154</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>f1de66b3-f38c-43fa-bead-8cff6084d01c</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>5448.39</v>
+      </c>
+      <c r="D610" t="n">
+        <v>90.41</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="n">
+        <v>46060.59608735476</v>
+      </c>
+      <c r="I610" s="2" t="n">
+        <v>46065.59608735476</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>a33344f8-d610-43c2-a475-fd55e64ccfb4</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>2293.63</v>
+      </c>
+      <c r="D611" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="n">
+        <v>46067.59608735793</v>
+      </c>
+      <c r="I611" s="2" t="n">
+        <v>46072.59608735793</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>9d88e637-9ff3-4fd6-874c-0aba4f9b3275</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>7118.3</v>
+      </c>
+      <c r="D612" t="n">
+        <v>88.79000000000001</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="n">
+        <v>46086.59608736123</v>
+      </c>
+      <c r="I612" s="2" t="n">
+        <v>46091.59608736123</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>adcdabae-b7cf-4d5b-9f69-52978aeef469</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>3806.53</v>
+      </c>
+      <c r="D613" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="n">
+        <v>46077.59608736446</v>
+      </c>
+      <c r="I613" s="2" t="n">
+        <v>46082.59608736446</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>4ba1722b-390e-4c3d-9142-1b8f5755a988</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>5936.52</v>
+      </c>
+      <c r="D614" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="n">
+        <v>46070.59608736759</v>
+      </c>
+      <c r="I614" s="2" t="n">
+        <v>46075.59608736759</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>ac0483b3-194a-4dfc-8079-85023b436f98</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>6609.05</v>
+      </c>
+      <c r="D615" t="n">
+        <v>88.56999999999999</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="n">
+        <v>46060.59608737077</v>
+      </c>
+      <c r="I615" s="2" t="n">
+        <v>46065.59608737077</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>fb96b029-8c21-4453-b234-a0276c3a8a59</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>5644.59</v>
+      </c>
+      <c r="D616" t="n">
+        <v>88.06</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="n">
+        <v>46088.59608737432</v>
+      </c>
+      <c r="I616" s="2" t="n">
+        <v>46093.59608737432</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>c0609d05-9aef-4938-9534-6d10ba871786</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>8416.27</v>
+      </c>
+      <c r="D617" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="n">
+        <v>46068.59608737735</v>
+      </c>
+      <c r="I617" s="2" t="n">
+        <v>46073.59608737735</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>7370c5a6-8f21-41ad-a2ee-ab44036e761f</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>5359.48</v>
+      </c>
+      <c r="D618" t="n">
+        <v>98.73999999999999</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="n">
+        <v>46085.59608738041</v>
+      </c>
+      <c r="I618" s="2" t="n">
+        <v>46090.59608738041</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>72bf69ad-02ae-4718-8921-564c5b8037d4</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>1411.99</v>
+      </c>
+      <c r="D619" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="n">
+        <v>46075.59608738368</v>
+      </c>
+      <c r="I619" s="2" t="n">
+        <v>46080.59608738368</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>97f693f5-f0d1-403d-8a52-890a47f47cf4</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>5726.16</v>
+      </c>
+      <c r="D620" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="n">
+        <v>46066.59608738678</v>
+      </c>
+      <c r="I620" s="2" t="n">
+        <v>46071.59608738678</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>22d307d5-d678-4305-bdf6-f4ae79d29b68</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>3474.37</v>
+      </c>
+      <c r="D621" t="n">
+        <v>89.36</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="n">
+        <v>46067.59608738997</v>
+      </c>
+      <c r="I621" s="2" t="n">
+        <v>46072.59608738997</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>7af6b38f-e383-48d6-8ad7-71aeb4ebef90</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>8587.07</v>
+      </c>
+      <c r="D622" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="n">
+        <v>46084.59608739295</v>
+      </c>
+      <c r="I622" s="2" t="n">
+        <v>46089.59608739295</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>5d6c6746-0f34-430c-b84a-6b2575338f46</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>2931.79</v>
+      </c>
+      <c r="D623" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="n">
+        <v>46087.59608739618</v>
+      </c>
+      <c r="I623" s="2" t="n">
+        <v>46092.59608739618</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>82ecfcad-7a3a-4a83-a42a-443cd817740c</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>8997.35</v>
+      </c>
+      <c r="D624" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="n">
+        <v>46060.59608739933</v>
+      </c>
+      <c r="I624" s="2" t="n">
+        <v>46065.59608739933</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>1165e8f2-28ab-43bd-b674-fae44f057c04</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>8294.629999999999</v>
+      </c>
+      <c r="D625" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="n">
+        <v>46085.59608740231</v>
+      </c>
+      <c r="I625" s="2" t="n">
+        <v>46090.59608740231</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>26af686a-b539-47c3-abb2-f355aecd3e82</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>8979.200000000001</v>
+      </c>
+      <c r="D626" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="n">
+        <v>46072.59608740543</v>
+      </c>
+      <c r="I626" s="2" t="n">
+        <v>46077.59608740543</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>81f276ed-7123-4305-97f9-69112175e560</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>5621.92</v>
+      </c>
+      <c r="D627" t="n">
+        <v>85.47</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="n">
+        <v>46078.5960874088</v>
+      </c>
+      <c r="I627" s="2" t="n">
+        <v>46083.5960874088</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>d61729d3-61ce-421c-a487-8fad73eed802</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>2730.4</v>
+      </c>
+      <c r="D628" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="n">
+        <v>46069.59608741204</v>
+      </c>
+      <c r="I628" s="2" t="n">
+        <v>46074.59608741204</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>c35738d5-c36d-4f1b-a63c-0316fc7f54c3</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>7152.97</v>
+      </c>
+      <c r="D629" t="n">
+        <v>90.78</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="n">
+        <v>46066.59608741507</v>
+      </c>
+      <c r="I629" s="2" t="n">
+        <v>46071.59608741507</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>b44b84a0-2a4a-446a-85e3-e9876384cf05</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>1051.13</v>
+      </c>
+      <c r="D630" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="n">
+        <v>46081.59608741837</v>
+      </c>
+      <c r="I630" s="2" t="n">
+        <v>46086.59608741837</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>97ec28a1-4680-48f2-9f72-04d3b3d0b9fe</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>9372.1</v>
+      </c>
+      <c r="D631" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="n">
+        <v>46062.59608742173</v>
+      </c>
+      <c r="I631" s="2" t="n">
+        <v>46067.59608742173</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>3dfe2580-5fd7-48ff-8b31-71433ae784c8</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>8356.389999999999</v>
+      </c>
+      <c r="D632" t="n">
+        <v>97.89</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="n">
+        <v>46066.59608742501</v>
+      </c>
+      <c r="I632" s="2" t="n">
+        <v>46071.59608742501</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>0e0173eb-459d-43ed-bca7-c54dc8c9bcef</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>8483.93</v>
+      </c>
+      <c r="D633" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="n">
+        <v>46083.59608742806</v>
+      </c>
+      <c r="I633" s="2" t="n">
+        <v>46088.59608742806</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>ae59944b-181d-4187-b886-a1e6b05df5a8</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>7629.34</v>
+      </c>
+      <c r="D634" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="n">
+        <v>46065.59608743135</v>
+      </c>
+      <c r="I634" s="2" t="n">
+        <v>46070.59608743135</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>523cf0a8-0e7c-4952-afa2-d2314c99fa35</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>9906.68</v>
+      </c>
+      <c r="D635" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="n">
+        <v>46074.59608743447</v>
+      </c>
+      <c r="I635" s="2" t="n">
+        <v>46079.59608743447</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>c1e06220-dba5-4cef-9a7d-f0e6a18b86c8</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>5693.51</v>
+      </c>
+      <c r="D636" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="n">
+        <v>46084.5960874376</v>
+      </c>
+      <c r="I636" s="2" t="n">
+        <v>46089.5960874376</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>fa700996-3763-4bdc-b464-bee1e3fff5b4</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>8873.610000000001</v>
+      </c>
+      <c r="D637" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="n">
+        <v>46080.59608744081</v>
+      </c>
+      <c r="I637" s="2" t="n">
+        <v>46085.59608744081</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>22212b79-aa1e-49f8-bac3-84feebe30114</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>6356.44</v>
+      </c>
+      <c r="D638" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="n">
+        <v>46079.59608744404</v>
+      </c>
+      <c r="I638" s="2" t="n">
+        <v>46084.59608744404</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>a648b3b3-ea19-48ff-824d-8c137a79086d</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>3891.46</v>
+      </c>
+      <c r="D639" t="n">
+        <v>86.87</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="n">
+        <v>46074.5960874472</v>
+      </c>
+      <c r="I639" s="2" t="n">
+        <v>46079.5960874472</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>c92240f0-3e68-424c-8f73-01df622bbb1e</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>1314.08</v>
+      </c>
+      <c r="D640" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="n">
+        <v>46085.59608745036</v>
+      </c>
+      <c r="I640" s="2" t="n">
+        <v>46090.59608745036</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>6909372d-c959-4d73-a0aa-7c4129adc2a7</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>5706.67</v>
+      </c>
+      <c r="D641" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="n">
+        <v>46060.59608745373</v>
+      </c>
+      <c r="I641" s="2" t="n">
+        <v>46065.59608745373</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>25114fce-f940-4e56-b657-c9c19741a6ce</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>2976.34</v>
+      </c>
+      <c r="D642" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="n">
+        <v>46068.59608745688</v>
+      </c>
+      <c r="I642" s="2" t="n">
+        <v>46073.59608745688</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>5fe61a1f-f21e-4469-9717-1f6f45471fb5</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>3713.92</v>
+      </c>
+      <c r="D643" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="n">
+        <v>46059.59608745999</v>
+      </c>
+      <c r="I643" s="2" t="n">
+        <v>46064.59608745999</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>51e0b758-950f-4a4a-ab93-0835fe84b9f8</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>1547.92</v>
+      </c>
+      <c r="D644" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="n">
+        <v>46064.5960874631</v>
+      </c>
+      <c r="I644" s="2" t="n">
+        <v>46069.5960874631</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>b8d917ff-d52f-461b-9dac-b93d845ec257</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>3852.08</v>
+      </c>
+      <c r="D645" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="n">
+        <v>46088.59608746633</v>
+      </c>
+      <c r="I645" s="2" t="n">
+        <v>46093.59608746633</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>6c80f053-815c-4aca-9f83-31f1b2d0e592</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>5018.6</v>
+      </c>
+      <c r="D646" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="n">
+        <v>46076.59608746944</v>
+      </c>
+      <c r="I646" s="2" t="n">
+        <v>46081.59608746944</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>8a8b9b44-f54f-4413-8c50-8ceb0ea9abdc</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>2408.27</v>
+      </c>
+      <c r="D647" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="n">
+        <v>46080.59608747246</v>
+      </c>
+      <c r="I647" s="2" t="n">
+        <v>46085.59608747246</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>bdf75d57-ba5d-4d13-914a-bc8398b6de57</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>9512.870000000001</v>
+      </c>
+      <c r="D648" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="n">
+        <v>46085.59608747566</v>
+      </c>
+      <c r="I648" s="2" t="n">
+        <v>46090.59608747566</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>e306753e-620e-4d67-a040-73c65dca1210</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>7149.72</v>
+      </c>
+      <c r="D649" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="n">
+        <v>46074.59608747887</v>
+      </c>
+      <c r="I649" s="2" t="n">
+        <v>46079.59608747887</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>0a5e8503-5cd4-4982-86ef-ecd8f50fcd98</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>9985.290000000001</v>
+      </c>
+      <c r="D650" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="n">
+        <v>46075.59608748208</v>
+      </c>
+      <c r="I650" s="2" t="n">
+        <v>46080.59608748208</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>c0829025-9725-4f56-ba50-d752ed12d42b</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>4704.9</v>
+      </c>
+      <c r="D651" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="n">
+        <v>46062.59608748528</v>
+      </c>
+      <c r="I651" s="2" t="n">
+        <v>46067.59608748528</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I651"/>
+  <dimension ref="A1:I701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23912,10 +23912,10 @@
         </is>
       </c>
       <c r="H602" s="2" t="n">
-        <v>46066.59608732769</v>
+        <v>46066.59608732639</v>
       </c>
       <c r="I602" s="2" t="n">
-        <v>46071.59608732769</v>
+        <v>46071.59608732639</v>
       </c>
     </row>
     <row r="603">
@@ -23951,10 +23951,10 @@
         </is>
       </c>
       <c r="H603" s="2" t="n">
-        <v>46079.5960873319</v>
+        <v>46079.59608732639</v>
       </c>
       <c r="I603" s="2" t="n">
-        <v>46084.5960873319</v>
+        <v>46084.59608732639</v>
       </c>
     </row>
     <row r="604">
@@ -23990,10 +23990,10 @@
         </is>
       </c>
       <c r="H604" s="2" t="n">
-        <v>46081.5960873353</v>
+        <v>46081.59608733797</v>
       </c>
       <c r="I604" s="2" t="n">
-        <v>46086.5960873353</v>
+        <v>46086.59608733797</v>
       </c>
     </row>
     <row r="605">
@@ -24029,10 +24029,10 @@
         </is>
       </c>
       <c r="H605" s="2" t="n">
-        <v>46063.59608733867</v>
+        <v>46063.59608733797</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>46068.59608733867</v>
+        <v>46068.59608733797</v>
       </c>
     </row>
     <row r="606">
@@ -24068,10 +24068,10 @@
         </is>
       </c>
       <c r="H606" s="2" t="n">
-        <v>46085.59608734177</v>
+        <v>46085.59608733797</v>
       </c>
       <c r="I606" s="2" t="n">
-        <v>46090.59608734177</v>
+        <v>46090.59608733797</v>
       </c>
     </row>
     <row r="607">
@@ -24107,10 +24107,10 @@
         </is>
       </c>
       <c r="H607" s="2" t="n">
-        <v>46062.5960873451</v>
+        <v>46062.59608734954</v>
       </c>
       <c r="I607" s="2" t="n">
-        <v>46067.5960873451</v>
+        <v>46067.59608734954</v>
       </c>
     </row>
     <row r="608">
@@ -24146,10 +24146,10 @@
         </is>
       </c>
       <c r="H608" s="2" t="n">
-        <v>46072.59608734838</v>
+        <v>46072.59608734954</v>
       </c>
       <c r="I608" s="2" t="n">
-        <v>46077.59608734838</v>
+        <v>46077.59608734954</v>
       </c>
     </row>
     <row r="609">
@@ -24185,10 +24185,10 @@
         </is>
       </c>
       <c r="H609" s="2" t="n">
-        <v>46081.59608735154</v>
+        <v>46081.59608734954</v>
       </c>
       <c r="I609" s="2" t="n">
-        <v>46086.59608735154</v>
+        <v>46086.59608734954</v>
       </c>
     </row>
     <row r="610">
@@ -24224,10 +24224,10 @@
         </is>
       </c>
       <c r="H610" s="2" t="n">
-        <v>46060.59608735476</v>
+        <v>46060.59608734954</v>
       </c>
       <c r="I610" s="2" t="n">
-        <v>46065.59608735476</v>
+        <v>46065.59608734954</v>
       </c>
     </row>
     <row r="611">
@@ -24263,10 +24263,10 @@
         </is>
       </c>
       <c r="H611" s="2" t="n">
-        <v>46067.59608735793</v>
+        <v>46067.59608736111</v>
       </c>
       <c r="I611" s="2" t="n">
-        <v>46072.59608735793</v>
+        <v>46072.59608736111</v>
       </c>
     </row>
     <row r="612">
@@ -24302,10 +24302,10 @@
         </is>
       </c>
       <c r="H612" s="2" t="n">
-        <v>46086.59608736123</v>
+        <v>46086.59608736111</v>
       </c>
       <c r="I612" s="2" t="n">
-        <v>46091.59608736123</v>
+        <v>46091.59608736111</v>
       </c>
     </row>
     <row r="613">
@@ -24341,10 +24341,10 @@
         </is>
       </c>
       <c r="H613" s="2" t="n">
-        <v>46077.59608736446</v>
+        <v>46077.59608736111</v>
       </c>
       <c r="I613" s="2" t="n">
-        <v>46082.59608736446</v>
+        <v>46082.59608736111</v>
       </c>
     </row>
     <row r="614">
@@ -24380,10 +24380,10 @@
         </is>
       </c>
       <c r="H614" s="2" t="n">
-        <v>46070.59608736759</v>
+        <v>46070.59608737269</v>
       </c>
       <c r="I614" s="2" t="n">
-        <v>46075.59608736759</v>
+        <v>46075.59608737269</v>
       </c>
     </row>
     <row r="615">
@@ -24419,10 +24419,10 @@
         </is>
       </c>
       <c r="H615" s="2" t="n">
-        <v>46060.59608737077</v>
+        <v>46060.59608737269</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>46065.59608737077</v>
+        <v>46065.59608737269</v>
       </c>
     </row>
     <row r="616">
@@ -24458,10 +24458,10 @@
         </is>
       </c>
       <c r="H616" s="2" t="n">
-        <v>46088.59608737432</v>
+        <v>46088.59608737269</v>
       </c>
       <c r="I616" s="2" t="n">
-        <v>46093.59608737432</v>
+        <v>46093.59608737269</v>
       </c>
     </row>
     <row r="617">
@@ -24497,10 +24497,10 @@
         </is>
       </c>
       <c r="H617" s="2" t="n">
-        <v>46068.59608737735</v>
+        <v>46068.59608737269</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>46073.59608737735</v>
+        <v>46073.59608737269</v>
       </c>
     </row>
     <row r="618">
@@ -24536,10 +24536,10 @@
         </is>
       </c>
       <c r="H618" s="2" t="n">
-        <v>46085.59608738041</v>
+        <v>46085.59608738426</v>
       </c>
       <c r="I618" s="2" t="n">
-        <v>46090.59608738041</v>
+        <v>46090.59608738426</v>
       </c>
     </row>
     <row r="619">
@@ -24575,10 +24575,10 @@
         </is>
       </c>
       <c r="H619" s="2" t="n">
-        <v>46075.59608738368</v>
+        <v>46075.59608738426</v>
       </c>
       <c r="I619" s="2" t="n">
-        <v>46080.59608738368</v>
+        <v>46080.59608738426</v>
       </c>
     </row>
     <row r="620">
@@ -24614,10 +24614,10 @@
         </is>
       </c>
       <c r="H620" s="2" t="n">
-        <v>46066.59608738678</v>
+        <v>46066.59608738426</v>
       </c>
       <c r="I620" s="2" t="n">
-        <v>46071.59608738678</v>
+        <v>46071.59608738426</v>
       </c>
     </row>
     <row r="621">
@@ -24653,10 +24653,10 @@
         </is>
       </c>
       <c r="H621" s="2" t="n">
-        <v>46067.59608738997</v>
+        <v>46067.59608738426</v>
       </c>
       <c r="I621" s="2" t="n">
-        <v>46072.59608738997</v>
+        <v>46072.59608738426</v>
       </c>
     </row>
     <row r="622">
@@ -24692,10 +24692,10 @@
         </is>
       </c>
       <c r="H622" s="2" t="n">
-        <v>46084.59608739295</v>
+        <v>46084.59608739583</v>
       </c>
       <c r="I622" s="2" t="n">
-        <v>46089.59608739295</v>
+        <v>46089.59608739583</v>
       </c>
     </row>
     <row r="623">
@@ -24731,10 +24731,10 @@
         </is>
       </c>
       <c r="H623" s="2" t="n">
-        <v>46087.59608739618</v>
+        <v>46087.59608739583</v>
       </c>
       <c r="I623" s="2" t="n">
-        <v>46092.59608739618</v>
+        <v>46092.59608739583</v>
       </c>
     </row>
     <row r="624">
@@ -24770,10 +24770,10 @@
         </is>
       </c>
       <c r="H624" s="2" t="n">
-        <v>46060.59608739933</v>
+        <v>46060.59608739583</v>
       </c>
       <c r="I624" s="2" t="n">
-        <v>46065.59608739933</v>
+        <v>46065.59608739583</v>
       </c>
     </row>
     <row r="625">
@@ -24809,10 +24809,10 @@
         </is>
       </c>
       <c r="H625" s="2" t="n">
-        <v>46085.59608740231</v>
+        <v>46085.59608740741</v>
       </c>
       <c r="I625" s="2" t="n">
-        <v>46090.59608740231</v>
+        <v>46090.59608740741</v>
       </c>
     </row>
     <row r="626">
@@ -24848,10 +24848,10 @@
         </is>
       </c>
       <c r="H626" s="2" t="n">
-        <v>46072.59608740543</v>
+        <v>46072.59608740741</v>
       </c>
       <c r="I626" s="2" t="n">
-        <v>46077.59608740543</v>
+        <v>46077.59608740741</v>
       </c>
     </row>
     <row r="627">
@@ -24887,10 +24887,10 @@
         </is>
       </c>
       <c r="H627" s="2" t="n">
-        <v>46078.5960874088</v>
+        <v>46078.59608740741</v>
       </c>
       <c r="I627" s="2" t="n">
-        <v>46083.5960874088</v>
+        <v>46083.59608740741</v>
       </c>
     </row>
     <row r="628">
@@ -24926,10 +24926,10 @@
         </is>
       </c>
       <c r="H628" s="2" t="n">
-        <v>46069.59608741204</v>
+        <v>46069.59608740741</v>
       </c>
       <c r="I628" s="2" t="n">
-        <v>46074.59608741204</v>
+        <v>46074.59608740741</v>
       </c>
     </row>
     <row r="629">
@@ -24965,10 +24965,10 @@
         </is>
       </c>
       <c r="H629" s="2" t="n">
-        <v>46066.59608741507</v>
+        <v>46066.59608741898</v>
       </c>
       <c r="I629" s="2" t="n">
-        <v>46071.59608741507</v>
+        <v>46071.59608741898</v>
       </c>
     </row>
     <row r="630">
@@ -25004,10 +25004,10 @@
         </is>
       </c>
       <c r="H630" s="2" t="n">
-        <v>46081.59608741837</v>
+        <v>46081.59608741898</v>
       </c>
       <c r="I630" s="2" t="n">
-        <v>46086.59608741837</v>
+        <v>46086.59608741898</v>
       </c>
     </row>
     <row r="631">
@@ -25043,10 +25043,10 @@
         </is>
       </c>
       <c r="H631" s="2" t="n">
-        <v>46062.59608742173</v>
+        <v>46062.59608741898</v>
       </c>
       <c r="I631" s="2" t="n">
-        <v>46067.59608742173</v>
+        <v>46067.59608741898</v>
       </c>
     </row>
     <row r="632">
@@ -25082,10 +25082,10 @@
         </is>
       </c>
       <c r="H632" s="2" t="n">
-        <v>46066.59608742501</v>
+        <v>46066.59608743055</v>
       </c>
       <c r="I632" s="2" t="n">
-        <v>46071.59608742501</v>
+        <v>46071.59608743055</v>
       </c>
     </row>
     <row r="633">
@@ -25121,10 +25121,10 @@
         </is>
       </c>
       <c r="H633" s="2" t="n">
-        <v>46083.59608742806</v>
+        <v>46083.59608743055</v>
       </c>
       <c r="I633" s="2" t="n">
-        <v>46088.59608742806</v>
+        <v>46088.59608743055</v>
       </c>
     </row>
     <row r="634">
@@ -25160,10 +25160,10 @@
         </is>
       </c>
       <c r="H634" s="2" t="n">
-        <v>46065.59608743135</v>
+        <v>46065.59608743055</v>
       </c>
       <c r="I634" s="2" t="n">
-        <v>46070.59608743135</v>
+        <v>46070.59608743055</v>
       </c>
     </row>
     <row r="635">
@@ -25199,10 +25199,10 @@
         </is>
       </c>
       <c r="H635" s="2" t="n">
-        <v>46074.59608743447</v>
+        <v>46074.59608743055</v>
       </c>
       <c r="I635" s="2" t="n">
-        <v>46079.59608743447</v>
+        <v>46079.59608743055</v>
       </c>
     </row>
     <row r="636">
@@ -25238,10 +25238,10 @@
         </is>
       </c>
       <c r="H636" s="2" t="n">
-        <v>46084.5960874376</v>
+        <v>46084.59608744213</v>
       </c>
       <c r="I636" s="2" t="n">
-        <v>46089.5960874376</v>
+        <v>46089.59608744213</v>
       </c>
     </row>
     <row r="637">
@@ -25277,10 +25277,10 @@
         </is>
       </c>
       <c r="H637" s="2" t="n">
-        <v>46080.59608744081</v>
+        <v>46080.59608744213</v>
       </c>
       <c r="I637" s="2" t="n">
-        <v>46085.59608744081</v>
+        <v>46085.59608744213</v>
       </c>
     </row>
     <row r="638">
@@ -25316,10 +25316,10 @@
         </is>
       </c>
       <c r="H638" s="2" t="n">
-        <v>46079.59608744404</v>
+        <v>46079.59608744213</v>
       </c>
       <c r="I638" s="2" t="n">
-        <v>46084.59608744404</v>
+        <v>46084.59608744213</v>
       </c>
     </row>
     <row r="639">
@@ -25355,10 +25355,10 @@
         </is>
       </c>
       <c r="H639" s="2" t="n">
-        <v>46074.5960874472</v>
+        <v>46074.59608744213</v>
       </c>
       <c r="I639" s="2" t="n">
-        <v>46079.5960874472</v>
+        <v>46079.59608744213</v>
       </c>
     </row>
     <row r="640">
@@ -25394,10 +25394,10 @@
         </is>
       </c>
       <c r="H640" s="2" t="n">
-        <v>46085.59608745036</v>
+        <v>46085.5960874537</v>
       </c>
       <c r="I640" s="2" t="n">
-        <v>46090.59608745036</v>
+        <v>46090.5960874537</v>
       </c>
     </row>
     <row r="641">
@@ -25433,10 +25433,10 @@
         </is>
       </c>
       <c r="H641" s="2" t="n">
-        <v>46060.59608745373</v>
+        <v>46060.5960874537</v>
       </c>
       <c r="I641" s="2" t="n">
-        <v>46065.59608745373</v>
+        <v>46065.5960874537</v>
       </c>
     </row>
     <row r="642">
@@ -25472,10 +25472,10 @@
         </is>
       </c>
       <c r="H642" s="2" t="n">
-        <v>46068.59608745688</v>
+        <v>46068.5960874537</v>
       </c>
       <c r="I642" s="2" t="n">
-        <v>46073.59608745688</v>
+        <v>46073.5960874537</v>
       </c>
     </row>
     <row r="643">
@@ -25511,10 +25511,10 @@
         </is>
       </c>
       <c r="H643" s="2" t="n">
-        <v>46059.59608745999</v>
+        <v>46059.59608746528</v>
       </c>
       <c r="I643" s="2" t="n">
-        <v>46064.59608745999</v>
+        <v>46064.59608746528</v>
       </c>
     </row>
     <row r="644">
@@ -25550,10 +25550,10 @@
         </is>
       </c>
       <c r="H644" s="2" t="n">
-        <v>46064.5960874631</v>
+        <v>46064.59608746528</v>
       </c>
       <c r="I644" s="2" t="n">
-        <v>46069.5960874631</v>
+        <v>46069.59608746528</v>
       </c>
     </row>
     <row r="645">
@@ -25589,10 +25589,10 @@
         </is>
       </c>
       <c r="H645" s="2" t="n">
-        <v>46088.59608746633</v>
+        <v>46088.59608746528</v>
       </c>
       <c r="I645" s="2" t="n">
-        <v>46093.59608746633</v>
+        <v>46093.59608746528</v>
       </c>
     </row>
     <row r="646">
@@ -25628,10 +25628,10 @@
         </is>
       </c>
       <c r="H646" s="2" t="n">
-        <v>46076.59608746944</v>
+        <v>46076.59608746528</v>
       </c>
       <c r="I646" s="2" t="n">
-        <v>46081.59608746944</v>
+        <v>46081.59608746528</v>
       </c>
     </row>
     <row r="647">
@@ -25667,10 +25667,10 @@
         </is>
       </c>
       <c r="H647" s="2" t="n">
-        <v>46080.59608747246</v>
+        <v>46080.59608747685</v>
       </c>
       <c r="I647" s="2" t="n">
-        <v>46085.59608747246</v>
+        <v>46085.59608747685</v>
       </c>
     </row>
     <row r="648">
@@ -25706,10 +25706,10 @@
         </is>
       </c>
       <c r="H648" s="2" t="n">
-        <v>46085.59608747566</v>
+        <v>46085.59608747685</v>
       </c>
       <c r="I648" s="2" t="n">
-        <v>46090.59608747566</v>
+        <v>46090.59608747685</v>
       </c>
     </row>
     <row r="649">
@@ -25745,10 +25745,10 @@
         </is>
       </c>
       <c r="H649" s="2" t="n">
-        <v>46074.59608747887</v>
+        <v>46074.59608747685</v>
       </c>
       <c r="I649" s="2" t="n">
-        <v>46079.59608747887</v>
+        <v>46079.59608747685</v>
       </c>
     </row>
     <row r="650">
@@ -25784,10 +25784,10 @@
         </is>
       </c>
       <c r="H650" s="2" t="n">
-        <v>46075.59608748208</v>
+        <v>46075.59608747685</v>
       </c>
       <c r="I650" s="2" t="n">
-        <v>46080.59608748208</v>
+        <v>46080.59608747685</v>
       </c>
     </row>
     <row r="651">
@@ -25823,10 +25823,1960 @@
         </is>
       </c>
       <c r="H651" s="2" t="n">
-        <v>46062.59608748528</v>
+        <v>46062.59608748843</v>
       </c>
       <c r="I651" s="2" t="n">
-        <v>46067.59608748528</v>
+        <v>46067.59608748843</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>50b7255d-476e-4238-9d70-2c720e2eaeef</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>6611.64</v>
+      </c>
+      <c r="D652" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="n">
+        <v>46075.61179396173</v>
+      </c>
+      <c r="I652" s="2" t="n">
+        <v>46080.61179396173</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>d016f671-bfe6-44da-9864-f40b52009548</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>6951.08</v>
+      </c>
+      <c r="D653" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="n">
+        <v>46073.61179396624</v>
+      </c>
+      <c r="I653" s="2" t="n">
+        <v>46078.61179396624</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>d0493c70-feee-44b3-904a-c2d49a899a65</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>2255.73</v>
+      </c>
+      <c r="D654" t="n">
+        <v>94.72</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="n">
+        <v>46063.61179396943</v>
+      </c>
+      <c r="I654" s="2" t="n">
+        <v>46068.61179396943</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>58eaca07-7f6e-469e-82ee-ef26f1d55147</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>8107.54</v>
+      </c>
+      <c r="D655" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="n">
+        <v>46069.61179397273</v>
+      </c>
+      <c r="I655" s="2" t="n">
+        <v>46074.61179397273</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>64cb6a25-ce39-44de-b7dd-1aea65360e0a</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>7622.29</v>
+      </c>
+      <c r="D656" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="n">
+        <v>46060.61179397591</v>
+      </c>
+      <c r="I656" s="2" t="n">
+        <v>46065.61179397591</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>7b45770b-97a7-4f27-acd7-b0a83f233805</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>3301.44</v>
+      </c>
+      <c r="D657" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="n">
+        <v>46069.61179397925</v>
+      </c>
+      <c r="I657" s="2" t="n">
+        <v>46074.61179397925</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>ae8d9832-1820-4576-88fb-7c759e1304a6</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>4806.3</v>
+      </c>
+      <c r="D658" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="n">
+        <v>46059.61179398235</v>
+      </c>
+      <c r="I658" s="2" t="n">
+        <v>46064.61179398235</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>837840d4-088d-4771-8ed8-80e491829998</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>1903.96</v>
+      </c>
+      <c r="D659" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="n">
+        <v>46065.61179398542</v>
+      </c>
+      <c r="I659" s="2" t="n">
+        <v>46070.61179398542</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>53658452-c234-44ab-96c8-521fb8f20a1f</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>9325.719999999999</v>
+      </c>
+      <c r="D660" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="n">
+        <v>46065.61179398852</v>
+      </c>
+      <c r="I660" s="2" t="n">
+        <v>46070.61179398852</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>e82d9af5-b28e-4046-b142-278d1dedb31b</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>2073.67</v>
+      </c>
+      <c r="D661" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="n">
+        <v>46066.61179399218</v>
+      </c>
+      <c r="I661" s="2" t="n">
+        <v>46071.61179399218</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>7faad09f-5b0e-4eb1-9823-f094399c0bdd</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>7192.87</v>
+      </c>
+      <c r="D662" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="n">
+        <v>46063.61179399538</v>
+      </c>
+      <c r="I662" s="2" t="n">
+        <v>46068.61179399538</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>55a27469-0140-4719-935f-d997cea4de36</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>5180.88</v>
+      </c>
+      <c r="D663" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="n">
+        <v>46068.61179399846</v>
+      </c>
+      <c r="I663" s="2" t="n">
+        <v>46073.61179399846</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>e452e18f-55b0-4a77-b265-679a6f1068b9</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>6752.85</v>
+      </c>
+      <c r="D664" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H664" s="2" t="n">
+        <v>46073.61179400211</v>
+      </c>
+      <c r="I664" s="2" t="n">
+        <v>46078.61179400211</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>89f8d0ff-245a-4035-ac17-001d9714ef1f</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>3122.6</v>
+      </c>
+      <c r="D665" t="n">
+        <v>89.70999999999999</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H665" s="2" t="n">
+        <v>46060.61179400529</v>
+      </c>
+      <c r="I665" s="2" t="n">
+        <v>46065.61179400529</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>4285c4d1-fdac-4a52-ae33-79cb4da4b3c2</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>3102.78</v>
+      </c>
+      <c r="D666" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H666" s="2" t="n">
+        <v>46077.61179400842</v>
+      </c>
+      <c r="I666" s="2" t="n">
+        <v>46082.61179400842</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>37a7dcb1-7521-4007-a711-357c1f1adb77</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>8444.799999999999</v>
+      </c>
+      <c r="D667" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H667" s="2" t="n">
+        <v>46079.61179401147</v>
+      </c>
+      <c r="I667" s="2" t="n">
+        <v>46084.61179401147</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>6f81e737-1bd6-4d70-95e2-2e2f7a796e33</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>4897.92</v>
+      </c>
+      <c r="D668" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="n">
+        <v>46059.61179401483</v>
+      </c>
+      <c r="I668" s="2" t="n">
+        <v>46064.61179401483</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>b6676b5d-9e7e-4dad-a651-a4c11c1ee04a</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>7647.55</v>
+      </c>
+      <c r="D669" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="n">
+        <v>46063.61179401798</v>
+      </c>
+      <c r="I669" s="2" t="n">
+        <v>46068.61179401798</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>7eed7d97-ca1c-4408-90d9-a0e0d45a8cea</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>7832.34</v>
+      </c>
+      <c r="D670" t="n">
+        <v>86.97</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="n">
+        <v>46082.61179402109</v>
+      </c>
+      <c r="I670" s="2" t="n">
+        <v>46087.61179402109</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>31f9bf89-f3bb-468e-b22c-d99c6352888f</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>4506.44</v>
+      </c>
+      <c r="D671" t="n">
+        <v>91.72</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="n">
+        <v>46088.61179402428</v>
+      </c>
+      <c r="I671" s="2" t="n">
+        <v>46093.61179402428</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>3d31031a-5fce-42ad-a7f6-0b8f60b8368a</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>2901.86</v>
+      </c>
+      <c r="D672" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="n">
+        <v>46075.61179402744</v>
+      </c>
+      <c r="I672" s="2" t="n">
+        <v>46080.61179402744</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>ffe2d4d6-7edc-442f-a591-2adb63399103</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>6068.07</v>
+      </c>
+      <c r="D673" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="n">
+        <v>46086.61179403054</v>
+      </c>
+      <c r="I673" s="2" t="n">
+        <v>46091.61179403054</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>7b11a2c9-c127-430c-aba9-874b0d7d60a1</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>7156.52</v>
+      </c>
+      <c r="D674" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="n">
+        <v>46070.61179403355</v>
+      </c>
+      <c r="I674" s="2" t="n">
+        <v>46075.61179403355</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>d8af2d27-ffd6-400f-9909-8bca54261334</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>6338.37</v>
+      </c>
+      <c r="D675" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="n">
+        <v>46080.61179403673</v>
+      </c>
+      <c r="I675" s="2" t="n">
+        <v>46085.61179403673</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>a5f4bb36-2e0b-40ee-9979-2836680e6bf3</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>9879.57</v>
+      </c>
+      <c r="D676" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="n">
+        <v>46079.61179403979</v>
+      </c>
+      <c r="I676" s="2" t="n">
+        <v>46084.61179403979</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>d3445bbe-07e6-4b31-afa2-f316de4e88bd</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>2978.58</v>
+      </c>
+      <c r="D677" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H677" s="2" t="n">
+        <v>46081.61179404286</v>
+      </c>
+      <c r="I677" s="2" t="n">
+        <v>46086.61179404286</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>a786efb3-2d5e-4338-bb26-aa2c6b07e303</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>1829.47</v>
+      </c>
+      <c r="D678" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H678" s="2" t="n">
+        <v>46064.61179404601</v>
+      </c>
+      <c r="I678" s="2" t="n">
+        <v>46069.61179404601</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>ab35d860-c8ba-42ff-b36e-8c5b4712c812</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>3933.9</v>
+      </c>
+      <c r="D679" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="n">
+        <v>46067.6117940496</v>
+      </c>
+      <c r="I679" s="2" t="n">
+        <v>46072.6117940496</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>24c1f530-8b3a-4895-a21f-f1baacf639d1</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>8316.280000000001</v>
+      </c>
+      <c r="D680" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="n">
+        <v>46083.61179405285</v>
+      </c>
+      <c r="I680" s="2" t="n">
+        <v>46088.61179405285</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>caee9bdb-f0ed-41bc-b363-1679b4bf92b4</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>3772.03</v>
+      </c>
+      <c r="D681" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="n">
+        <v>46084.61179405617</v>
+      </c>
+      <c r="I681" s="2" t="n">
+        <v>46089.61179405617</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>3fc6c417-6242-4987-a29f-f0816aac8cdb</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>4209.71</v>
+      </c>
+      <c r="D682" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H682" s="2" t="n">
+        <v>46067.61179405943</v>
+      </c>
+      <c r="I682" s="2" t="n">
+        <v>46072.61179405943</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>722acc51-a7ad-4e31-a890-834bf2b52348</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>4020.85</v>
+      </c>
+      <c r="D683" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="n">
+        <v>46085.61179406247</v>
+      </c>
+      <c r="I683" s="2" t="n">
+        <v>46090.61179406247</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>dc4c3c5a-6a72-4c80-b014-1db0d28b8ab3</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>1369.82</v>
+      </c>
+      <c r="D684" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="n">
+        <v>46083.61179406563</v>
+      </c>
+      <c r="I684" s="2" t="n">
+        <v>46088.61179406563</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>d6e1ae04-ef81-4183-9c0c-0410a911b306</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>1227.65</v>
+      </c>
+      <c r="D685" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="n">
+        <v>46073.61179406888</v>
+      </c>
+      <c r="I685" s="2" t="n">
+        <v>46078.61179406888</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>50a27a7b-9ff6-4da6-8ade-41375578fa90</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>6374.86</v>
+      </c>
+      <c r="D686" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="n">
+        <v>46081.61179407204</v>
+      </c>
+      <c r="I686" s="2" t="n">
+        <v>46086.61179407204</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>4f058fa4-0986-4766-a63e-5854c724ce2e</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>8886.030000000001</v>
+      </c>
+      <c r="D687" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="n">
+        <v>46076.61179407528</v>
+      </c>
+      <c r="I687" s="2" t="n">
+        <v>46081.61179407528</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>b5abcdaa-8f1d-405e-bc26-e8539c96a86f</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>3609.77</v>
+      </c>
+      <c r="D688" t="n">
+        <v>92.01000000000001</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H688" s="2" t="n">
+        <v>46083.61179407842</v>
+      </c>
+      <c r="I688" s="2" t="n">
+        <v>46088.61179407842</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>095b74d7-13d1-432f-ae1f-1210cc566b7d</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2740.34</v>
+      </c>
+      <c r="D689" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="n">
+        <v>46087.61179408162</v>
+      </c>
+      <c r="I689" s="2" t="n">
+        <v>46092.61179408162</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>c2811e74-9dd6-4c43-8775-2445557a6d14</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>2524.55</v>
+      </c>
+      <c r="D690" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="n">
+        <v>46060.61179408475</v>
+      </c>
+      <c r="I690" s="2" t="n">
+        <v>46065.61179408475</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>7639bc2c-b8d2-4908-a6e3-4e43360c06b9</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>2801.25</v>
+      </c>
+      <c r="D691" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="n">
+        <v>46076.61179408788</v>
+      </c>
+      <c r="I691" s="2" t="n">
+        <v>46081.61179408788</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>adf08da6-1507-48f4-985b-6428905f5d80</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>9037.200000000001</v>
+      </c>
+      <c r="D692" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="n">
+        <v>46077.61179409098</v>
+      </c>
+      <c r="I692" s="2" t="n">
+        <v>46082.61179409098</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>3a24274c-68c3-4368-a7d4-f93885bfc531</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>4902.75</v>
+      </c>
+      <c r="D693" t="n">
+        <v>89.81</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="n">
+        <v>46070.61179409466</v>
+      </c>
+      <c r="I693" s="2" t="n">
+        <v>46075.61179409466</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>af50c5b4-88d4-472d-8dfc-c2c700b7ca8a</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>9483.379999999999</v>
+      </c>
+      <c r="D694" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="n">
+        <v>46059.61179409815</v>
+      </c>
+      <c r="I694" s="2" t="n">
+        <v>46064.61179409815</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>165e8d0a-3ac1-45d7-a734-af1eed6bfd95</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>6591.52</v>
+      </c>
+      <c r="D695" t="n">
+        <v>99.29000000000001</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="n">
+        <v>46070.61179410118</v>
+      </c>
+      <c r="I695" s="2" t="n">
+        <v>46075.61179410118</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>3cc9a3a8-c5dd-49f9-8dbb-dd3fed0c405e</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>4883.7</v>
+      </c>
+      <c r="D696" t="n">
+        <v>88.64</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="n">
+        <v>46062.61179410419</v>
+      </c>
+      <c r="I696" s="2" t="n">
+        <v>46067.61179410419</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>c90d96ca-e9ab-40ff-b2af-ed3144a590a5</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>1082.63</v>
+      </c>
+      <c r="D697" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="n">
+        <v>46082.61179410746</v>
+      </c>
+      <c r="I697" s="2" t="n">
+        <v>46087.61179410746</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>da65f702-8f71-46a3-9eb8-c03e65c831ee</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>6432.53</v>
+      </c>
+      <c r="D698" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="n">
+        <v>46073.61179411066</v>
+      </c>
+      <c r="I698" s="2" t="n">
+        <v>46078.61179411066</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>042d8ec2-dfe2-4a2a-a566-e46a10688be8</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>9775.6</v>
+      </c>
+      <c r="D699" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="n">
+        <v>46069.61179411387</v>
+      </c>
+      <c r="I699" s="2" t="n">
+        <v>46074.61179411387</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>e3bf582c-17ef-4b04-8385-194b5152b866</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2119.23</v>
+      </c>
+      <c r="D700" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="n">
+        <v>46072.61179411702</v>
+      </c>
+      <c r="I700" s="2" t="n">
+        <v>46077.61179411702</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>0e84fbd8-daa6-46f4-b937-24dc76d64f61</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>6271.52</v>
+      </c>
+      <c r="D701" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="n">
+        <v>46076.6117941203</v>
+      </c>
+      <c r="I701" s="2" t="n">
+        <v>46081.6117941203</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I701"/>
+  <dimension ref="A1:I751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25862,10 +25862,10 @@
         </is>
       </c>
       <c r="H652" s="2" t="n">
-        <v>46075.61179396173</v>
+        <v>46075.61179395833</v>
       </c>
       <c r="I652" s="2" t="n">
-        <v>46080.61179396173</v>
+        <v>46080.61179395833</v>
       </c>
     </row>
     <row r="653">
@@ -25901,10 +25901,10 @@
         </is>
       </c>
       <c r="H653" s="2" t="n">
-        <v>46073.61179396624</v>
+        <v>46073.61179396991</v>
       </c>
       <c r="I653" s="2" t="n">
-        <v>46078.61179396624</v>
+        <v>46078.61179396991</v>
       </c>
     </row>
     <row r="654">
@@ -25940,10 +25940,10 @@
         </is>
       </c>
       <c r="H654" s="2" t="n">
-        <v>46063.61179396943</v>
+        <v>46063.61179396991</v>
       </c>
       <c r="I654" s="2" t="n">
-        <v>46068.61179396943</v>
+        <v>46068.61179396991</v>
       </c>
     </row>
     <row r="655">
@@ -25979,10 +25979,10 @@
         </is>
       </c>
       <c r="H655" s="2" t="n">
-        <v>46069.61179397273</v>
+        <v>46069.61179396991</v>
       </c>
       <c r="I655" s="2" t="n">
-        <v>46074.61179397273</v>
+        <v>46074.61179396991</v>
       </c>
     </row>
     <row r="656">
@@ -26018,10 +26018,10 @@
         </is>
       </c>
       <c r="H656" s="2" t="n">
-        <v>46060.61179397591</v>
+        <v>46060.61179398148</v>
       </c>
       <c r="I656" s="2" t="n">
-        <v>46065.61179397591</v>
+        <v>46065.61179398148</v>
       </c>
     </row>
     <row r="657">
@@ -26057,10 +26057,10 @@
         </is>
       </c>
       <c r="H657" s="2" t="n">
-        <v>46069.61179397925</v>
+        <v>46069.61179398148</v>
       </c>
       <c r="I657" s="2" t="n">
-        <v>46074.61179397925</v>
+        <v>46074.61179398148</v>
       </c>
     </row>
     <row r="658">
@@ -26096,10 +26096,10 @@
         </is>
       </c>
       <c r="H658" s="2" t="n">
-        <v>46059.61179398235</v>
+        <v>46059.61179398148</v>
       </c>
       <c r="I658" s="2" t="n">
-        <v>46064.61179398235</v>
+        <v>46064.61179398148</v>
       </c>
     </row>
     <row r="659">
@@ -26135,10 +26135,10 @@
         </is>
       </c>
       <c r="H659" s="2" t="n">
-        <v>46065.61179398542</v>
+        <v>46065.61179398148</v>
       </c>
       <c r="I659" s="2" t="n">
-        <v>46070.61179398542</v>
+        <v>46070.61179398148</v>
       </c>
     </row>
     <row r="660">
@@ -26174,10 +26174,10 @@
         </is>
       </c>
       <c r="H660" s="2" t="n">
-        <v>46065.61179398852</v>
+        <v>46065.61179399306</v>
       </c>
       <c r="I660" s="2" t="n">
-        <v>46070.61179398852</v>
+        <v>46070.61179399306</v>
       </c>
     </row>
     <row r="661">
@@ -26213,10 +26213,10 @@
         </is>
       </c>
       <c r="H661" s="2" t="n">
-        <v>46066.61179399218</v>
+        <v>46066.61179399306</v>
       </c>
       <c r="I661" s="2" t="n">
-        <v>46071.61179399218</v>
+        <v>46071.61179399306</v>
       </c>
     </row>
     <row r="662">
@@ -26252,10 +26252,10 @@
         </is>
       </c>
       <c r="H662" s="2" t="n">
-        <v>46063.61179399538</v>
+        <v>46063.61179399306</v>
       </c>
       <c r="I662" s="2" t="n">
-        <v>46068.61179399538</v>
+        <v>46068.61179399306</v>
       </c>
     </row>
     <row r="663">
@@ -26291,10 +26291,10 @@
         </is>
       </c>
       <c r="H663" s="2" t="n">
-        <v>46068.61179399846</v>
+        <v>46068.61179399306</v>
       </c>
       <c r="I663" s="2" t="n">
-        <v>46073.61179399846</v>
+        <v>46073.61179399306</v>
       </c>
     </row>
     <row r="664">
@@ -26330,10 +26330,10 @@
         </is>
       </c>
       <c r="H664" s="2" t="n">
-        <v>46073.61179400211</v>
+        <v>46073.61179400463</v>
       </c>
       <c r="I664" s="2" t="n">
-        <v>46078.61179400211</v>
+        <v>46078.61179400463</v>
       </c>
     </row>
     <row r="665">
@@ -26369,10 +26369,10 @@
         </is>
       </c>
       <c r="H665" s="2" t="n">
-        <v>46060.61179400529</v>
+        <v>46060.61179400463</v>
       </c>
       <c r="I665" s="2" t="n">
-        <v>46065.61179400529</v>
+        <v>46065.61179400463</v>
       </c>
     </row>
     <row r="666">
@@ -26408,10 +26408,10 @@
         </is>
       </c>
       <c r="H666" s="2" t="n">
-        <v>46077.61179400842</v>
+        <v>46077.61179400463</v>
       </c>
       <c r="I666" s="2" t="n">
-        <v>46082.61179400842</v>
+        <v>46082.61179400463</v>
       </c>
     </row>
     <row r="667">
@@ -26447,10 +26447,10 @@
         </is>
       </c>
       <c r="H667" s="2" t="n">
-        <v>46079.61179401147</v>
+        <v>46079.6117940162</v>
       </c>
       <c r="I667" s="2" t="n">
-        <v>46084.61179401147</v>
+        <v>46084.6117940162</v>
       </c>
     </row>
     <row r="668">
@@ -26486,10 +26486,10 @@
         </is>
       </c>
       <c r="H668" s="2" t="n">
-        <v>46059.61179401483</v>
+        <v>46059.6117940162</v>
       </c>
       <c r="I668" s="2" t="n">
-        <v>46064.61179401483</v>
+        <v>46064.6117940162</v>
       </c>
     </row>
     <row r="669">
@@ -26525,10 +26525,10 @@
         </is>
       </c>
       <c r="H669" s="2" t="n">
-        <v>46063.61179401798</v>
+        <v>46063.6117940162</v>
       </c>
       <c r="I669" s="2" t="n">
-        <v>46068.61179401798</v>
+        <v>46068.6117940162</v>
       </c>
     </row>
     <row r="670">
@@ -26564,10 +26564,10 @@
         </is>
       </c>
       <c r="H670" s="2" t="n">
-        <v>46082.61179402109</v>
+        <v>46082.6117940162</v>
       </c>
       <c r="I670" s="2" t="n">
-        <v>46087.61179402109</v>
+        <v>46087.6117940162</v>
       </c>
     </row>
     <row r="671">
@@ -26603,10 +26603,10 @@
         </is>
       </c>
       <c r="H671" s="2" t="n">
-        <v>46088.61179402428</v>
+        <v>46088.61179402778</v>
       </c>
       <c r="I671" s="2" t="n">
-        <v>46093.61179402428</v>
+        <v>46093.61179402778</v>
       </c>
     </row>
     <row r="672">
@@ -26642,10 +26642,10 @@
         </is>
       </c>
       <c r="H672" s="2" t="n">
-        <v>46075.61179402744</v>
+        <v>46075.61179402778</v>
       </c>
       <c r="I672" s="2" t="n">
-        <v>46080.61179402744</v>
+        <v>46080.61179402778</v>
       </c>
     </row>
     <row r="673">
@@ -26681,10 +26681,10 @@
         </is>
       </c>
       <c r="H673" s="2" t="n">
-        <v>46086.61179403054</v>
+        <v>46086.61179402778</v>
       </c>
       <c r="I673" s="2" t="n">
-        <v>46091.61179403054</v>
+        <v>46091.61179402778</v>
       </c>
     </row>
     <row r="674">
@@ -26720,10 +26720,10 @@
         </is>
       </c>
       <c r="H674" s="2" t="n">
-        <v>46070.61179403355</v>
+        <v>46070.61179402778</v>
       </c>
       <c r="I674" s="2" t="n">
-        <v>46075.61179403355</v>
+        <v>46075.61179402778</v>
       </c>
     </row>
     <row r="675">
@@ -26759,10 +26759,10 @@
         </is>
       </c>
       <c r="H675" s="2" t="n">
-        <v>46080.61179403673</v>
+        <v>46080.61179403935</v>
       </c>
       <c r="I675" s="2" t="n">
-        <v>46085.61179403673</v>
+        <v>46085.61179403935</v>
       </c>
     </row>
     <row r="676">
@@ -26798,10 +26798,10 @@
         </is>
       </c>
       <c r="H676" s="2" t="n">
-        <v>46079.61179403979</v>
+        <v>46079.61179403935</v>
       </c>
       <c r="I676" s="2" t="n">
-        <v>46084.61179403979</v>
+        <v>46084.61179403935</v>
       </c>
     </row>
     <row r="677">
@@ -26837,10 +26837,10 @@
         </is>
       </c>
       <c r="H677" s="2" t="n">
-        <v>46081.61179404286</v>
+        <v>46081.61179403935</v>
       </c>
       <c r="I677" s="2" t="n">
-        <v>46086.61179404286</v>
+        <v>46086.61179403935</v>
       </c>
     </row>
     <row r="678">
@@ -26876,10 +26876,10 @@
         </is>
       </c>
       <c r="H678" s="2" t="n">
-        <v>46064.61179404601</v>
+        <v>46064.61179405093</v>
       </c>
       <c r="I678" s="2" t="n">
-        <v>46069.61179404601</v>
+        <v>46069.61179405093</v>
       </c>
     </row>
     <row r="679">
@@ -26915,10 +26915,10 @@
         </is>
       </c>
       <c r="H679" s="2" t="n">
-        <v>46067.6117940496</v>
+        <v>46067.61179405093</v>
       </c>
       <c r="I679" s="2" t="n">
-        <v>46072.6117940496</v>
+        <v>46072.61179405093</v>
       </c>
     </row>
     <row r="680">
@@ -26954,10 +26954,10 @@
         </is>
       </c>
       <c r="H680" s="2" t="n">
-        <v>46083.61179405285</v>
+        <v>46083.61179405093</v>
       </c>
       <c r="I680" s="2" t="n">
-        <v>46088.61179405285</v>
+        <v>46088.61179405093</v>
       </c>
     </row>
     <row r="681">
@@ -26993,10 +26993,10 @@
         </is>
       </c>
       <c r="H681" s="2" t="n">
-        <v>46084.61179405617</v>
+        <v>46084.61179405093</v>
       </c>
       <c r="I681" s="2" t="n">
-        <v>46089.61179405617</v>
+        <v>46089.61179405093</v>
       </c>
     </row>
     <row r="682">
@@ -27032,10 +27032,10 @@
         </is>
       </c>
       <c r="H682" s="2" t="n">
-        <v>46067.61179405943</v>
+        <v>46067.6117940625</v>
       </c>
       <c r="I682" s="2" t="n">
-        <v>46072.61179405943</v>
+        <v>46072.6117940625</v>
       </c>
     </row>
     <row r="683">
@@ -27071,10 +27071,10 @@
         </is>
       </c>
       <c r="H683" s="2" t="n">
-        <v>46085.61179406247</v>
+        <v>46085.6117940625</v>
       </c>
       <c r="I683" s="2" t="n">
-        <v>46090.61179406247</v>
+        <v>46090.6117940625</v>
       </c>
     </row>
     <row r="684">
@@ -27110,10 +27110,10 @@
         </is>
       </c>
       <c r="H684" s="2" t="n">
-        <v>46083.61179406563</v>
+        <v>46083.6117940625</v>
       </c>
       <c r="I684" s="2" t="n">
-        <v>46088.61179406563</v>
+        <v>46088.6117940625</v>
       </c>
     </row>
     <row r="685">
@@ -27149,10 +27149,10 @@
         </is>
       </c>
       <c r="H685" s="2" t="n">
-        <v>46073.61179406888</v>
+        <v>46073.61179407407</v>
       </c>
       <c r="I685" s="2" t="n">
-        <v>46078.61179406888</v>
+        <v>46078.61179407407</v>
       </c>
     </row>
     <row r="686">
@@ -27188,10 +27188,10 @@
         </is>
       </c>
       <c r="H686" s="2" t="n">
-        <v>46081.61179407204</v>
+        <v>46081.61179407407</v>
       </c>
       <c r="I686" s="2" t="n">
-        <v>46086.61179407204</v>
+        <v>46086.61179407407</v>
       </c>
     </row>
     <row r="687">
@@ -27227,10 +27227,10 @@
         </is>
       </c>
       <c r="H687" s="2" t="n">
-        <v>46076.61179407528</v>
+        <v>46076.61179407407</v>
       </c>
       <c r="I687" s="2" t="n">
-        <v>46081.61179407528</v>
+        <v>46081.61179407407</v>
       </c>
     </row>
     <row r="688">
@@ -27266,10 +27266,10 @@
         </is>
       </c>
       <c r="H688" s="2" t="n">
-        <v>46083.61179407842</v>
+        <v>46083.61179407407</v>
       </c>
       <c r="I688" s="2" t="n">
-        <v>46088.61179407842</v>
+        <v>46088.61179407407</v>
       </c>
     </row>
     <row r="689">
@@ -27305,10 +27305,10 @@
         </is>
       </c>
       <c r="H689" s="2" t="n">
-        <v>46087.61179408162</v>
+        <v>46087.61179408565</v>
       </c>
       <c r="I689" s="2" t="n">
-        <v>46092.61179408162</v>
+        <v>46092.61179408565</v>
       </c>
     </row>
     <row r="690">
@@ -27344,10 +27344,10 @@
         </is>
       </c>
       <c r="H690" s="2" t="n">
-        <v>46060.61179408475</v>
+        <v>46060.61179408565</v>
       </c>
       <c r="I690" s="2" t="n">
-        <v>46065.61179408475</v>
+        <v>46065.61179408565</v>
       </c>
     </row>
     <row r="691">
@@ -27383,10 +27383,10 @@
         </is>
       </c>
       <c r="H691" s="2" t="n">
-        <v>46076.61179408788</v>
+        <v>46076.61179408565</v>
       </c>
       <c r="I691" s="2" t="n">
-        <v>46081.61179408788</v>
+        <v>46081.61179408565</v>
       </c>
     </row>
     <row r="692">
@@ -27422,10 +27422,10 @@
         </is>
       </c>
       <c r="H692" s="2" t="n">
-        <v>46077.61179409098</v>
+        <v>46077.61179408565</v>
       </c>
       <c r="I692" s="2" t="n">
-        <v>46082.61179409098</v>
+        <v>46082.61179408565</v>
       </c>
     </row>
     <row r="693">
@@ -27461,10 +27461,10 @@
         </is>
       </c>
       <c r="H693" s="2" t="n">
-        <v>46070.61179409466</v>
+        <v>46070.61179409723</v>
       </c>
       <c r="I693" s="2" t="n">
-        <v>46075.61179409466</v>
+        <v>46075.61179409723</v>
       </c>
     </row>
     <row r="694">
@@ -27500,10 +27500,10 @@
         </is>
       </c>
       <c r="H694" s="2" t="n">
-        <v>46059.61179409815</v>
+        <v>46059.61179409723</v>
       </c>
       <c r="I694" s="2" t="n">
-        <v>46064.61179409815</v>
+        <v>46064.61179409723</v>
       </c>
     </row>
     <row r="695">
@@ -27539,10 +27539,10 @@
         </is>
       </c>
       <c r="H695" s="2" t="n">
-        <v>46070.61179410118</v>
+        <v>46070.61179409723</v>
       </c>
       <c r="I695" s="2" t="n">
-        <v>46075.61179410118</v>
+        <v>46075.61179409723</v>
       </c>
     </row>
     <row r="696">
@@ -27578,10 +27578,10 @@
         </is>
       </c>
       <c r="H696" s="2" t="n">
-        <v>46062.61179410419</v>
+        <v>46062.61179410879</v>
       </c>
       <c r="I696" s="2" t="n">
-        <v>46067.61179410419</v>
+        <v>46067.61179410879</v>
       </c>
     </row>
     <row r="697">
@@ -27617,10 +27617,10 @@
         </is>
       </c>
       <c r="H697" s="2" t="n">
-        <v>46082.61179410746</v>
+        <v>46082.61179410879</v>
       </c>
       <c r="I697" s="2" t="n">
-        <v>46087.61179410746</v>
+        <v>46087.61179410879</v>
       </c>
     </row>
     <row r="698">
@@ -27656,10 +27656,10 @@
         </is>
       </c>
       <c r="H698" s="2" t="n">
-        <v>46073.61179411066</v>
+        <v>46073.61179410879</v>
       </c>
       <c r="I698" s="2" t="n">
-        <v>46078.61179411066</v>
+        <v>46078.61179410879</v>
       </c>
     </row>
     <row r="699">
@@ -27695,10 +27695,10 @@
         </is>
       </c>
       <c r="H699" s="2" t="n">
-        <v>46069.61179411387</v>
+        <v>46069.61179410879</v>
       </c>
       <c r="I699" s="2" t="n">
-        <v>46074.61179411387</v>
+        <v>46074.61179410879</v>
       </c>
     </row>
     <row r="700">
@@ -27734,10 +27734,10 @@
         </is>
       </c>
       <c r="H700" s="2" t="n">
-        <v>46072.61179411702</v>
+        <v>46072.61179412037</v>
       </c>
       <c r="I700" s="2" t="n">
-        <v>46077.61179411702</v>
+        <v>46077.61179412037</v>
       </c>
     </row>
     <row r="701">
@@ -27773,10 +27773,1960 @@
         </is>
       </c>
       <c r="H701" s="2" t="n">
-        <v>46076.6117941203</v>
+        <v>46076.61179412037</v>
       </c>
       <c r="I701" s="2" t="n">
-        <v>46081.6117941203</v>
+        <v>46081.61179412037</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>35aa2688-4610-4dac-8329-49519fb81a39</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>4250.54</v>
+      </c>
+      <c r="D702" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="n">
+        <v>46076.63651467322</v>
+      </c>
+      <c r="I702" s="2" t="n">
+        <v>46081.63651467322</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>5b89f551-babc-4982-8875-556751dc288e</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>4523.52</v>
+      </c>
+      <c r="D703" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="n">
+        <v>46083.63651467743</v>
+      </c>
+      <c r="I703" s="2" t="n">
+        <v>46088.63651467743</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>5786831b-8a66-44f2-aa16-e7492c82926b</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>2423.46</v>
+      </c>
+      <c r="D704" t="n">
+        <v>90.51000000000001</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="n">
+        <v>46087.63651468074</v>
+      </c>
+      <c r="I704" s="2" t="n">
+        <v>46092.63651468074</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>8fdb9fdb-afef-437f-a2cd-08565e8a0480</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>3164.12</v>
+      </c>
+      <c r="D705" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="n">
+        <v>46069.63651468396</v>
+      </c>
+      <c r="I705" s="2" t="n">
+        <v>46074.63651468396</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>b35949de-3dfb-4ba6-821e-ea840ebe883a</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>2809.74</v>
+      </c>
+      <c r="D706" t="n">
+        <v>88.61</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="n">
+        <v>46086.6365146868</v>
+      </c>
+      <c r="I706" s="2" t="n">
+        <v>46091.6365146868</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>f7c6ebe6-e509-497f-9cbe-7b705b7272b5</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>5271.9</v>
+      </c>
+      <c r="D707" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="n">
+        <v>46077.63651468976</v>
+      </c>
+      <c r="I707" s="2" t="n">
+        <v>46082.63651468976</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>f79ad350-2ad4-495a-9723-309aa26a9a56</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>1069.76</v>
+      </c>
+      <c r="D708" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="n">
+        <v>46081.63651469274</v>
+      </c>
+      <c r="I708" s="2" t="n">
+        <v>46086.63651469274</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>6cfc439b-196e-4a2d-a26f-27d348483dd3</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>4173.8</v>
+      </c>
+      <c r="D709" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="n">
+        <v>46062.6365146957</v>
+      </c>
+      <c r="I709" s="2" t="n">
+        <v>46067.6365146957</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>ade4dfbf-d42b-40f7-99a5-a1d5b733f301</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>5137.84</v>
+      </c>
+      <c r="D710" t="n">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="n">
+        <v>46061.63651469882</v>
+      </c>
+      <c r="I710" s="2" t="n">
+        <v>46066.63651469882</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>7eb34511-5578-4724-b6fa-49fb9727f7f8</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>4235.72</v>
+      </c>
+      <c r="D711" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="n">
+        <v>46069.63651470173</v>
+      </c>
+      <c r="I711" s="2" t="n">
+        <v>46074.63651470173</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>e8d84f66-4034-44c4-8d21-6de99927041d</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>2503.03</v>
+      </c>
+      <c r="D712" t="n">
+        <v>96.29000000000001</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="n">
+        <v>46069.63651470489</v>
+      </c>
+      <c r="I712" s="2" t="n">
+        <v>46074.63651470489</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2a1bc2c5-77cd-4203-9045-38933e5efd81</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>7955.84</v>
+      </c>
+      <c r="D713" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="n">
+        <v>46060.63651470779</v>
+      </c>
+      <c r="I713" s="2" t="n">
+        <v>46065.63651470779</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>01677c6b-8d51-43d1-863d-0619175f13fa</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>9898.93</v>
+      </c>
+      <c r="D714" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="n">
+        <v>46066.63651471069</v>
+      </c>
+      <c r="I714" s="2" t="n">
+        <v>46071.63651471069</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>628714d0-ef00-4a6b-a2d0-30c82040a3e4</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>5925.82</v>
+      </c>
+      <c r="D715" t="n">
+        <v>99.14</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="n">
+        <v>46061.6365147136</v>
+      </c>
+      <c r="I715" s="2" t="n">
+        <v>46066.6365147136</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>f7a5e412-964d-47c8-b1bd-9d705a0018c6</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>5384.86</v>
+      </c>
+      <c r="D716" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="n">
+        <v>46084.63651471637</v>
+      </c>
+      <c r="I716" s="2" t="n">
+        <v>46089.63651471637</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>a5baf645-5c6a-47dd-be45-4b96104ee25b</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>7003.65</v>
+      </c>
+      <c r="D717" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="n">
+        <v>46068.6365147192</v>
+      </c>
+      <c r="I717" s="2" t="n">
+        <v>46073.6365147192</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>d9ba2d5c-e81d-4dda-959f-8da6cf67c3e2</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>5091.15</v>
+      </c>
+      <c r="D718" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="n">
+        <v>46088.63651472214</v>
+      </c>
+      <c r="I718" s="2" t="n">
+        <v>46093.63651472214</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>ad575945-0ffb-4bcc-8d2b-98ee38a0753e</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>7876.43</v>
+      </c>
+      <c r="D719" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="n">
+        <v>46063.63651472513</v>
+      </c>
+      <c r="I719" s="2" t="n">
+        <v>46068.63651472513</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>6eb031f5-7aad-44b8-8e09-3111ccad9cd5</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>9642.1</v>
+      </c>
+      <c r="D720" t="n">
+        <v>91.38</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="n">
+        <v>46079.63651472817</v>
+      </c>
+      <c r="I720" s="2" t="n">
+        <v>46084.63651472817</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>52f04c7f-62b1-4b1f-bcb1-6cdfd5196825</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>1302.38</v>
+      </c>
+      <c r="D721" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H721" s="2" t="n">
+        <v>46077.63651473104</v>
+      </c>
+      <c r="I721" s="2" t="n">
+        <v>46082.63651473104</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>20cf546d-c0cd-4544-bc1f-5141b26749ef</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>9907.190000000001</v>
+      </c>
+      <c r="D722" t="n">
+        <v>90.72</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H722" s="2" t="n">
+        <v>46075.63651473385</v>
+      </c>
+      <c r="I722" s="2" t="n">
+        <v>46080.63651473385</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>3332f984-c78d-43c4-a9f6-d8ccd68f975b</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>7021.08</v>
+      </c>
+      <c r="D723" t="n">
+        <v>91.45999999999999</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H723" s="2" t="n">
+        <v>46078.63651473675</v>
+      </c>
+      <c r="I723" s="2" t="n">
+        <v>46083.63651473675</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>c75a6c59-e493-4467-b660-dad12e3401ac</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>4638.43</v>
+      </c>
+      <c r="D724" t="n">
+        <v>87.69</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H724" s="2" t="n">
+        <v>46080.63651473955</v>
+      </c>
+      <c r="I724" s="2" t="n">
+        <v>46085.63651473955</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>e940d1e4-0acf-4d9e-b5e1-d8b10596b24a</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>9746.559999999999</v>
+      </c>
+      <c r="D725" t="n">
+        <v>89.95999999999999</v>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="n">
+        <v>46082.63651474248</v>
+      </c>
+      <c r="I725" s="2" t="n">
+        <v>46087.63651474248</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>c9028daa-5f41-4c46-b87b-9cc5609f5b31</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>9029.5</v>
+      </c>
+      <c r="D726" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H726" s="2" t="n">
+        <v>46073.63651474538</v>
+      </c>
+      <c r="I726" s="2" t="n">
+        <v>46078.63651474538</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>079105b9-cef6-453e-88f8-2bf4491273ce</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D727" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H727" s="2" t="n">
+        <v>46059.63651474838</v>
+      </c>
+      <c r="I727" s="2" t="n">
+        <v>46064.63651474838</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>facfe198-cdd9-4503-829e-39fa06644086</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>5046.57</v>
+      </c>
+      <c r="D728" t="n">
+        <v>91.97</v>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H728" s="2" t="n">
+        <v>46080.6365147514</v>
+      </c>
+      <c r="I728" s="2" t="n">
+        <v>46085.6365147514</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>8760a690-8a67-4ee4-bcbd-52aa87117a45</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>8146.62</v>
+      </c>
+      <c r="D729" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="n">
+        <v>46081.63651475419</v>
+      </c>
+      <c r="I729" s="2" t="n">
+        <v>46086.63651475419</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>f574277e-a113-41ef-9013-10321d51cf7c</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>8741.6</v>
+      </c>
+      <c r="D730" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H730" s="2" t="n">
+        <v>46064.63651475698</v>
+      </c>
+      <c r="I730" s="2" t="n">
+        <v>46069.63651475698</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>c537c210-f6ad-4224-bdd3-4a8f57e1f605</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>3211.42</v>
+      </c>
+      <c r="D731" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="n">
+        <v>46086.63651476</v>
+      </c>
+      <c r="I731" s="2" t="n">
+        <v>46091.63651476</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>ad5afe57-d10d-4e1d-9073-4b427096c69e</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>6610.28</v>
+      </c>
+      <c r="D732" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H732" s="2" t="n">
+        <v>46080.63651476288</v>
+      </c>
+      <c r="I732" s="2" t="n">
+        <v>46085.63651476288</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>298f2a77-ae3d-4bd9-a39f-1fa781eb3261</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>7432.78</v>
+      </c>
+      <c r="D733" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H733" s="2" t="n">
+        <v>46077.63651476572</v>
+      </c>
+      <c r="I733" s="2" t="n">
+        <v>46082.63651476572</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>eb60a40c-d999-428e-b81a-3c9737a07930</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>7836.48</v>
+      </c>
+      <c r="D734" t="n">
+        <v>87.72</v>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H734" s="2" t="n">
+        <v>46075.63651476859</v>
+      </c>
+      <c r="I734" s="2" t="n">
+        <v>46080.63651476859</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>fe2f7ddf-c47f-4b59-85d9-cc1be9488a26</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>8148.37</v>
+      </c>
+      <c r="D735" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H735" s="2" t="n">
+        <v>46077.63651477166</v>
+      </c>
+      <c r="I735" s="2" t="n">
+        <v>46082.63651477166</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>81e9aba8-d0af-4dbc-af74-e25b3e84817e</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>6561.17</v>
+      </c>
+      <c r="D736" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H736" s="2" t="n">
+        <v>46087.63651477442</v>
+      </c>
+      <c r="I736" s="2" t="n">
+        <v>46092.63651477442</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>ece9f276-5821-4901-b49d-2f942b3471f8</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>9975.43</v>
+      </c>
+      <c r="D737" t="n">
+        <v>98.64</v>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="n">
+        <v>46077.63651477727</v>
+      </c>
+      <c r="I737" s="2" t="n">
+        <v>46082.63651477727</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>5d7787cb-7f5f-45f1-942d-a99b6564d550</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>2573.85</v>
+      </c>
+      <c r="D738" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="n">
+        <v>46081.63651478009</v>
+      </c>
+      <c r="I738" s="2" t="n">
+        <v>46086.63651478009</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>fec6a825-caf6-44df-bfce-d992e57deaf6</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>7122.35</v>
+      </c>
+      <c r="D739" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H739" s="2" t="n">
+        <v>46070.63651478312</v>
+      </c>
+      <c r="I739" s="2" t="n">
+        <v>46075.63651478312</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>dde62b51-867f-4cae-b258-d99052e21b62</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>2485.63</v>
+      </c>
+      <c r="D740" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H740" s="2" t="n">
+        <v>46082.63651478589</v>
+      </c>
+      <c r="I740" s="2" t="n">
+        <v>46087.63651478589</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>06d2f2d5-9c46-49eb-819c-6fa3c6cac829</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>9678.32</v>
+      </c>
+      <c r="D741" t="n">
+        <v>85.66</v>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H741" s="2" t="n">
+        <v>46067.63651478873</v>
+      </c>
+      <c r="I741" s="2" t="n">
+        <v>46072.63651478873</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>cf047088-b027-4b5e-ba75-59a492210609</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>3765.51</v>
+      </c>
+      <c r="D742" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H742" s="2" t="n">
+        <v>46077.63651479153</v>
+      </c>
+      <c r="I742" s="2" t="n">
+        <v>46082.63651479153</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>0a09acdd-3439-413f-9023-581788539b59</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>7021.57</v>
+      </c>
+      <c r="D743" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H743" s="2" t="n">
+        <v>46072.63651479437</v>
+      </c>
+      <c r="I743" s="2" t="n">
+        <v>46077.63651479437</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>41d345fe-73b0-4957-979b-7e6d1892a6dc</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>7376.2</v>
+      </c>
+      <c r="D744" t="n">
+        <v>90.05</v>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H744" s="2" t="n">
+        <v>46085.6365147976</v>
+      </c>
+      <c r="I744" s="2" t="n">
+        <v>46090.6365147976</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>71b3478f-44d1-4729-aef1-4795e2514d29</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>5610.38</v>
+      </c>
+      <c r="D745" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="n">
+        <v>46059.6365148004</v>
+      </c>
+      <c r="I745" s="2" t="n">
+        <v>46064.6365148004</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>c3679b77-77d2-45f1-8375-d8741acce97a</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>6477.52</v>
+      </c>
+      <c r="D746" t="n">
+        <v>90.06999999999999</v>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="n">
+        <v>46084.63651480322</v>
+      </c>
+      <c r="I746" s="2" t="n">
+        <v>46089.63651480322</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>e1ad3d75-e7fa-4904-823d-a69a086b704e</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>2893.05</v>
+      </c>
+      <c r="D747" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="n">
+        <v>46063.63651480608</v>
+      </c>
+      <c r="I747" s="2" t="n">
+        <v>46068.63651480608</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>bbf6d2c2-5c02-474e-acce-1fa06ac68ada</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>2928.8</v>
+      </c>
+      <c r="D748" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="n">
+        <v>46071.636514809</v>
+      </c>
+      <c r="I748" s="2" t="n">
+        <v>46076.636514809</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>e1efef48-47b6-4a2e-9fad-571b4cab21ea</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>4264.69</v>
+      </c>
+      <c r="D749" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H749" s="2" t="n">
+        <v>46071.63651481193</v>
+      </c>
+      <c r="I749" s="2" t="n">
+        <v>46076.63651481193</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>1f18f7f9-09ea-4e33-835d-5889fb7739f4</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>2828.76</v>
+      </c>
+      <c r="D750" t="n">
+        <v>90.54000000000001</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="n">
+        <v>46071.6365148147</v>
+      </c>
+      <c r="I750" s="2" t="n">
+        <v>46076.6365148147</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>c571bdcd-200b-4cda-8f28-8c1f4e4ec856</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>7232.81</v>
+      </c>
+      <c r="D751" t="n">
+        <v>94.63</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="n">
+        <v>46071.63651481755</v>
+      </c>
+      <c r="I751" s="2" t="n">
+        <v>46076.63651481755</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I751"/>
+  <dimension ref="A1:I801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27812,10 +27812,10 @@
         </is>
       </c>
       <c r="H702" s="2" t="n">
-        <v>46076.63651467322</v>
+        <v>46076.63651467593</v>
       </c>
       <c r="I702" s="2" t="n">
-        <v>46081.63651467322</v>
+        <v>46081.63651467593</v>
       </c>
     </row>
     <row r="703">
@@ -27851,10 +27851,10 @@
         </is>
       </c>
       <c r="H703" s="2" t="n">
-        <v>46083.63651467743</v>
+        <v>46083.63651467593</v>
       </c>
       <c r="I703" s="2" t="n">
-        <v>46088.63651467743</v>
+        <v>46088.63651467593</v>
       </c>
     </row>
     <row r="704">
@@ -27890,10 +27890,10 @@
         </is>
       </c>
       <c r="H704" s="2" t="n">
-        <v>46087.63651468074</v>
+        <v>46087.63651467593</v>
       </c>
       <c r="I704" s="2" t="n">
-        <v>46092.63651468074</v>
+        <v>46092.63651467593</v>
       </c>
     </row>
     <row r="705">
@@ -27929,10 +27929,10 @@
         </is>
       </c>
       <c r="H705" s="2" t="n">
-        <v>46069.63651468396</v>
+        <v>46069.6365146875</v>
       </c>
       <c r="I705" s="2" t="n">
-        <v>46074.63651468396</v>
+        <v>46074.6365146875</v>
       </c>
     </row>
     <row r="706">
@@ -27968,10 +27968,10 @@
         </is>
       </c>
       <c r="H706" s="2" t="n">
-        <v>46086.6365146868</v>
+        <v>46086.6365146875</v>
       </c>
       <c r="I706" s="2" t="n">
-        <v>46091.6365146868</v>
+        <v>46091.6365146875</v>
       </c>
     </row>
     <row r="707">
@@ -28007,10 +28007,10 @@
         </is>
       </c>
       <c r="H707" s="2" t="n">
-        <v>46077.63651468976</v>
+        <v>46077.6365146875</v>
       </c>
       <c r="I707" s="2" t="n">
-        <v>46082.63651468976</v>
+        <v>46082.6365146875</v>
       </c>
     </row>
     <row r="708">
@@ -28046,10 +28046,10 @@
         </is>
       </c>
       <c r="H708" s="2" t="n">
-        <v>46081.63651469274</v>
+        <v>46081.6365146875</v>
       </c>
       <c r="I708" s="2" t="n">
-        <v>46086.63651469274</v>
+        <v>46086.6365146875</v>
       </c>
     </row>
     <row r="709">
@@ -28085,10 +28085,10 @@
         </is>
       </c>
       <c r="H709" s="2" t="n">
-        <v>46062.6365146957</v>
+        <v>46062.63651469907</v>
       </c>
       <c r="I709" s="2" t="n">
-        <v>46067.6365146957</v>
+        <v>46067.63651469907</v>
       </c>
     </row>
     <row r="710">
@@ -28124,10 +28124,10 @@
         </is>
       </c>
       <c r="H710" s="2" t="n">
-        <v>46061.63651469882</v>
+        <v>46061.63651469907</v>
       </c>
       <c r="I710" s="2" t="n">
-        <v>46066.63651469882</v>
+        <v>46066.63651469907</v>
       </c>
     </row>
     <row r="711">
@@ -28163,10 +28163,10 @@
         </is>
       </c>
       <c r="H711" s="2" t="n">
-        <v>46069.63651470173</v>
+        <v>46069.63651469907</v>
       </c>
       <c r="I711" s="2" t="n">
-        <v>46074.63651470173</v>
+        <v>46074.63651469907</v>
       </c>
     </row>
     <row r="712">
@@ -28202,10 +28202,10 @@
         </is>
       </c>
       <c r="H712" s="2" t="n">
-        <v>46069.63651470489</v>
+        <v>46069.63651471065</v>
       </c>
       <c r="I712" s="2" t="n">
-        <v>46074.63651470489</v>
+        <v>46074.63651471065</v>
       </c>
     </row>
     <row r="713">
@@ -28241,10 +28241,10 @@
         </is>
       </c>
       <c r="H713" s="2" t="n">
-        <v>46060.63651470779</v>
+        <v>46060.63651471065</v>
       </c>
       <c r="I713" s="2" t="n">
-        <v>46065.63651470779</v>
+        <v>46065.63651471065</v>
       </c>
     </row>
     <row r="714">
@@ -28280,10 +28280,10 @@
         </is>
       </c>
       <c r="H714" s="2" t="n">
-        <v>46066.63651471069</v>
+        <v>46066.63651471065</v>
       </c>
       <c r="I714" s="2" t="n">
-        <v>46071.63651471069</v>
+        <v>46071.63651471065</v>
       </c>
     </row>
     <row r="715">
@@ -28319,10 +28319,10 @@
         </is>
       </c>
       <c r="H715" s="2" t="n">
-        <v>46061.6365147136</v>
+        <v>46061.63651471065</v>
       </c>
       <c r="I715" s="2" t="n">
-        <v>46066.6365147136</v>
+        <v>46066.63651471065</v>
       </c>
     </row>
     <row r="716">
@@ -28358,10 +28358,10 @@
         </is>
       </c>
       <c r="H716" s="2" t="n">
-        <v>46084.63651471637</v>
+        <v>46084.63651471065</v>
       </c>
       <c r="I716" s="2" t="n">
-        <v>46089.63651471637</v>
+        <v>46089.63651471065</v>
       </c>
     </row>
     <row r="717">
@@ -28397,10 +28397,10 @@
         </is>
       </c>
       <c r="H717" s="2" t="n">
-        <v>46068.6365147192</v>
+        <v>46068.63651472222</v>
       </c>
       <c r="I717" s="2" t="n">
-        <v>46073.6365147192</v>
+        <v>46073.63651472222</v>
       </c>
     </row>
     <row r="718">
@@ -28436,10 +28436,10 @@
         </is>
       </c>
       <c r="H718" s="2" t="n">
-        <v>46088.63651472214</v>
+        <v>46088.63651472222</v>
       </c>
       <c r="I718" s="2" t="n">
-        <v>46093.63651472214</v>
+        <v>46093.63651472222</v>
       </c>
     </row>
     <row r="719">
@@ -28475,10 +28475,10 @@
         </is>
       </c>
       <c r="H719" s="2" t="n">
-        <v>46063.63651472513</v>
+        <v>46063.63651472222</v>
       </c>
       <c r="I719" s="2" t="n">
-        <v>46068.63651472513</v>
+        <v>46068.63651472222</v>
       </c>
     </row>
     <row r="720">
@@ -28514,10 +28514,10 @@
         </is>
       </c>
       <c r="H720" s="2" t="n">
-        <v>46079.63651472817</v>
+        <v>46079.63651473379</v>
       </c>
       <c r="I720" s="2" t="n">
-        <v>46084.63651472817</v>
+        <v>46084.63651473379</v>
       </c>
     </row>
     <row r="721">
@@ -28553,10 +28553,10 @@
         </is>
       </c>
       <c r="H721" s="2" t="n">
-        <v>46077.63651473104</v>
+        <v>46077.63651473379</v>
       </c>
       <c r="I721" s="2" t="n">
-        <v>46082.63651473104</v>
+        <v>46082.63651473379</v>
       </c>
     </row>
     <row r="722">
@@ -28592,10 +28592,10 @@
         </is>
       </c>
       <c r="H722" s="2" t="n">
-        <v>46075.63651473385</v>
+        <v>46075.63651473379</v>
       </c>
       <c r="I722" s="2" t="n">
-        <v>46080.63651473385</v>
+        <v>46080.63651473379</v>
       </c>
     </row>
     <row r="723">
@@ -28631,10 +28631,10 @@
         </is>
       </c>
       <c r="H723" s="2" t="n">
-        <v>46078.63651473675</v>
+        <v>46078.63651473379</v>
       </c>
       <c r="I723" s="2" t="n">
-        <v>46083.63651473675</v>
+        <v>46083.63651473379</v>
       </c>
     </row>
     <row r="724">
@@ -28670,10 +28670,10 @@
         </is>
       </c>
       <c r="H724" s="2" t="n">
-        <v>46080.63651473955</v>
+        <v>46080.63651473379</v>
       </c>
       <c r="I724" s="2" t="n">
-        <v>46085.63651473955</v>
+        <v>46085.63651473379</v>
       </c>
     </row>
     <row r="725">
@@ -28709,10 +28709,10 @@
         </is>
       </c>
       <c r="H725" s="2" t="n">
-        <v>46082.63651474248</v>
+        <v>46082.63651474537</v>
       </c>
       <c r="I725" s="2" t="n">
-        <v>46087.63651474248</v>
+        <v>46087.63651474537</v>
       </c>
     </row>
     <row r="726">
@@ -28748,10 +28748,10 @@
         </is>
       </c>
       <c r="H726" s="2" t="n">
-        <v>46073.63651474538</v>
+        <v>46073.63651474537</v>
       </c>
       <c r="I726" s="2" t="n">
-        <v>46078.63651474538</v>
+        <v>46078.63651474537</v>
       </c>
     </row>
     <row r="727">
@@ -28787,10 +28787,10 @@
         </is>
       </c>
       <c r="H727" s="2" t="n">
-        <v>46059.63651474838</v>
+        <v>46059.63651474537</v>
       </c>
       <c r="I727" s="2" t="n">
-        <v>46064.63651474838</v>
+        <v>46064.63651474537</v>
       </c>
     </row>
     <row r="728">
@@ -28826,10 +28826,10 @@
         </is>
       </c>
       <c r="H728" s="2" t="n">
-        <v>46080.6365147514</v>
+        <v>46080.63651475694</v>
       </c>
       <c r="I728" s="2" t="n">
-        <v>46085.6365147514</v>
+        <v>46085.63651475694</v>
       </c>
     </row>
     <row r="729">
@@ -28865,10 +28865,10 @@
         </is>
       </c>
       <c r="H729" s="2" t="n">
-        <v>46081.63651475419</v>
+        <v>46081.63651475694</v>
       </c>
       <c r="I729" s="2" t="n">
-        <v>46086.63651475419</v>
+        <v>46086.63651475694</v>
       </c>
     </row>
     <row r="730">
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="H730" s="2" t="n">
-        <v>46064.63651475698</v>
+        <v>46064.63651475694</v>
       </c>
       <c r="I730" s="2" t="n">
-        <v>46069.63651475698</v>
+        <v>46069.63651475694</v>
       </c>
     </row>
     <row r="731">
@@ -28943,10 +28943,10 @@
         </is>
       </c>
       <c r="H731" s="2" t="n">
-        <v>46086.63651476</v>
+        <v>46086.63651475694</v>
       </c>
       <c r="I731" s="2" t="n">
-        <v>46091.63651476</v>
+        <v>46091.63651475694</v>
       </c>
     </row>
     <row r="732">
@@ -28982,10 +28982,10 @@
         </is>
       </c>
       <c r="H732" s="2" t="n">
-        <v>46080.63651476288</v>
+        <v>46080.63651476852</v>
       </c>
       <c r="I732" s="2" t="n">
-        <v>46085.63651476288</v>
+        <v>46085.63651476852</v>
       </c>
     </row>
     <row r="733">
@@ -29021,10 +29021,10 @@
         </is>
       </c>
       <c r="H733" s="2" t="n">
-        <v>46077.63651476572</v>
+        <v>46077.63651476852</v>
       </c>
       <c r="I733" s="2" t="n">
-        <v>46082.63651476572</v>
+        <v>46082.63651476852</v>
       </c>
     </row>
     <row r="734">
@@ -29060,10 +29060,10 @@
         </is>
       </c>
       <c r="H734" s="2" t="n">
-        <v>46075.63651476859</v>
+        <v>46075.63651476852</v>
       </c>
       <c r="I734" s="2" t="n">
-        <v>46080.63651476859</v>
+        <v>46080.63651476852</v>
       </c>
     </row>
     <row r="735">
@@ -29099,10 +29099,10 @@
         </is>
       </c>
       <c r="H735" s="2" t="n">
-        <v>46077.63651477166</v>
+        <v>46077.63651476852</v>
       </c>
       <c r="I735" s="2" t="n">
-        <v>46082.63651477166</v>
+        <v>46082.63651476852</v>
       </c>
     </row>
     <row r="736">
@@ -29138,10 +29138,10 @@
         </is>
       </c>
       <c r="H736" s="2" t="n">
-        <v>46087.63651477442</v>
+        <v>46087.63651478009</v>
       </c>
       <c r="I736" s="2" t="n">
-        <v>46092.63651477442</v>
+        <v>46092.63651478009</v>
       </c>
     </row>
     <row r="737">
@@ -29177,10 +29177,10 @@
         </is>
       </c>
       <c r="H737" s="2" t="n">
-        <v>46077.63651477727</v>
+        <v>46077.63651478009</v>
       </c>
       <c r="I737" s="2" t="n">
-        <v>46082.63651477727</v>
+        <v>46082.63651478009</v>
       </c>
     </row>
     <row r="738">
@@ -29255,10 +29255,10 @@
         </is>
       </c>
       <c r="H739" s="2" t="n">
-        <v>46070.63651478312</v>
+        <v>46070.63651478009</v>
       </c>
       <c r="I739" s="2" t="n">
-        <v>46075.63651478312</v>
+        <v>46075.63651478009</v>
       </c>
     </row>
     <row r="740">
@@ -29294,10 +29294,10 @@
         </is>
       </c>
       <c r="H740" s="2" t="n">
-        <v>46082.63651478589</v>
+        <v>46082.63651479167</v>
       </c>
       <c r="I740" s="2" t="n">
-        <v>46087.63651478589</v>
+        <v>46087.63651479167</v>
       </c>
     </row>
     <row r="741">
@@ -29333,10 +29333,10 @@
         </is>
       </c>
       <c r="H741" s="2" t="n">
-        <v>46067.63651478873</v>
+        <v>46067.63651479167</v>
       </c>
       <c r="I741" s="2" t="n">
-        <v>46072.63651478873</v>
+        <v>46072.63651479167</v>
       </c>
     </row>
     <row r="742">
@@ -29372,10 +29372,10 @@
         </is>
       </c>
       <c r="H742" s="2" t="n">
-        <v>46077.63651479153</v>
+        <v>46077.63651479167</v>
       </c>
       <c r="I742" s="2" t="n">
-        <v>46082.63651479153</v>
+        <v>46082.63651479167</v>
       </c>
     </row>
     <row r="743">
@@ -29411,10 +29411,10 @@
         </is>
       </c>
       <c r="H743" s="2" t="n">
-        <v>46072.63651479437</v>
+        <v>46072.63651479167</v>
       </c>
       <c r="I743" s="2" t="n">
-        <v>46077.63651479437</v>
+        <v>46077.63651479167</v>
       </c>
     </row>
     <row r="744">
@@ -29450,10 +29450,10 @@
         </is>
       </c>
       <c r="H744" s="2" t="n">
-        <v>46085.6365147976</v>
+        <v>46085.63651480324</v>
       </c>
       <c r="I744" s="2" t="n">
-        <v>46090.6365147976</v>
+        <v>46090.63651480324</v>
       </c>
     </row>
     <row r="745">
@@ -29489,10 +29489,10 @@
         </is>
       </c>
       <c r="H745" s="2" t="n">
-        <v>46059.6365148004</v>
+        <v>46059.63651480324</v>
       </c>
       <c r="I745" s="2" t="n">
-        <v>46064.6365148004</v>
+        <v>46064.63651480324</v>
       </c>
     </row>
     <row r="746">
@@ -29528,10 +29528,10 @@
         </is>
       </c>
       <c r="H746" s="2" t="n">
-        <v>46084.63651480322</v>
+        <v>46084.63651480324</v>
       </c>
       <c r="I746" s="2" t="n">
-        <v>46089.63651480322</v>
+        <v>46089.63651480324</v>
       </c>
     </row>
     <row r="747">
@@ -29567,10 +29567,10 @@
         </is>
       </c>
       <c r="H747" s="2" t="n">
-        <v>46063.63651480608</v>
+        <v>46063.63651480324</v>
       </c>
       <c r="I747" s="2" t="n">
-        <v>46068.63651480608</v>
+        <v>46068.63651480324</v>
       </c>
     </row>
     <row r="748">
@@ -29606,10 +29606,10 @@
         </is>
       </c>
       <c r="H748" s="2" t="n">
-        <v>46071.636514809</v>
+        <v>46071.63651480324</v>
       </c>
       <c r="I748" s="2" t="n">
-        <v>46076.636514809</v>
+        <v>46076.63651480324</v>
       </c>
     </row>
     <row r="749">
@@ -29645,10 +29645,10 @@
         </is>
       </c>
       <c r="H749" s="2" t="n">
-        <v>46071.63651481193</v>
+        <v>46071.63651481482</v>
       </c>
       <c r="I749" s="2" t="n">
-        <v>46076.63651481193</v>
+        <v>46076.63651481482</v>
       </c>
     </row>
     <row r="750">
@@ -29684,10 +29684,10 @@
         </is>
       </c>
       <c r="H750" s="2" t="n">
-        <v>46071.6365148147</v>
+        <v>46071.63651481482</v>
       </c>
       <c r="I750" s="2" t="n">
-        <v>46076.6365148147</v>
+        <v>46076.63651481482</v>
       </c>
     </row>
     <row r="751">
@@ -29723,10 +29723,1960 @@
         </is>
       </c>
       <c r="H751" s="2" t="n">
-        <v>46071.63651481755</v>
+        <v>46071.63651481482</v>
       </c>
       <c r="I751" s="2" t="n">
-        <v>46076.63651481755</v>
+        <v>46076.63651481482</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>def882b6-def6-42c6-938c-1495d06a3c3c</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>3664.81</v>
+      </c>
+      <c r="D752" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="n">
+        <v>46068.67981566994</v>
+      </c>
+      <c r="I752" s="2" t="n">
+        <v>46073.67981566994</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>c92629df-3759-41d5-9132-d27d52263f12</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>6472.84</v>
+      </c>
+      <c r="D753" t="n">
+        <v>91.37</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H753" s="2" t="n">
+        <v>46083.67981567408</v>
+      </c>
+      <c r="I753" s="2" t="n">
+        <v>46088.67981567408</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>948c1d3d-efdb-40fc-bf6e-f4b39a551456</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>6973.17</v>
+      </c>
+      <c r="D754" t="n">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H754" s="2" t="n">
+        <v>46067.67981567739</v>
+      </c>
+      <c r="I754" s="2" t="n">
+        <v>46072.67981567739</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>061a9842-e334-492e-9e57-10f6a9533380</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>4354.28</v>
+      </c>
+      <c r="D755" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="n">
+        <v>46061.67981568087</v>
+      </c>
+      <c r="I755" s="2" t="n">
+        <v>46066.67981568087</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>e39f1e89-dc85-4722-a75c-334d615ebb78</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>2602.89</v>
+      </c>
+      <c r="D756" t="n">
+        <v>93.56999999999999</v>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H756" s="2" t="n">
+        <v>46063.67981568407</v>
+      </c>
+      <c r="I756" s="2" t="n">
+        <v>46068.67981568407</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>17229131-e051-4a61-b82a-9f83bc45863e</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>9198.6</v>
+      </c>
+      <c r="D757" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="n">
+        <v>46068.67981568717</v>
+      </c>
+      <c r="I757" s="2" t="n">
+        <v>46073.67981568717</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>da2964a6-47c4-40ed-8ab2-5d7da5806f08</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>6304.82</v>
+      </c>
+      <c r="D758" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="n">
+        <v>46060.67981569034</v>
+      </c>
+      <c r="I758" s="2" t="n">
+        <v>46065.67981569034</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>dd9508fa-da1a-4b66-b2f7-dfb81cc98eaf</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>7821.22</v>
+      </c>
+      <c r="D759" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="n">
+        <v>46068.67981569363</v>
+      </c>
+      <c r="I759" s="2" t="n">
+        <v>46073.67981569363</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>d24cf199-935a-44d4-ada6-a3a992c8c71c</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>4898.48</v>
+      </c>
+      <c r="D760" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="n">
+        <v>46082.67981569669</v>
+      </c>
+      <c r="I760" s="2" t="n">
+        <v>46087.67981569669</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>1d1ef314-52f0-4082-9862-13108c87437b</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>3055.01</v>
+      </c>
+      <c r="D761" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="n">
+        <v>46076.67981569986</v>
+      </c>
+      <c r="I761" s="2" t="n">
+        <v>46081.67981569986</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>4ae48d55-eb7f-4c10-a390-9dd89386963c</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>3613.32</v>
+      </c>
+      <c r="D762" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="n">
+        <v>46062.67981570315</v>
+      </c>
+      <c r="I762" s="2" t="n">
+        <v>46067.67981570315</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>b9fcfad8-fdeb-457a-a843-8df49df72a02</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>2650.97</v>
+      </c>
+      <c r="D763" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="n">
+        <v>46068.67981570633</v>
+      </c>
+      <c r="I763" s="2" t="n">
+        <v>46073.67981570633</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>bcd1dd37-a81a-4eb5-80a3-554f841982a2</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>8320.780000000001</v>
+      </c>
+      <c r="D764" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="n">
+        <v>46077.67981570937</v>
+      </c>
+      <c r="I764" s="2" t="n">
+        <v>46082.67981570937</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>53ff8292-39e0-42be-b2cd-674b6c8237c0</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>5443.74</v>
+      </c>
+      <c r="D765" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="n">
+        <v>46072.67981571238</v>
+      </c>
+      <c r="I765" s="2" t="n">
+        <v>46077.67981571238</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>ee5bd2f6-4903-4311-bb1d-bfc80a97cc86</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>3162.01</v>
+      </c>
+      <c r="D766" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="n">
+        <v>46085.67981571573</v>
+      </c>
+      <c r="I766" s="2" t="n">
+        <v>46090.67981571573</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>e683cdb2-169d-427f-9988-a1882ec49376</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>8762.129999999999</v>
+      </c>
+      <c r="D767" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="n">
+        <v>46082.67981571893</v>
+      </c>
+      <c r="I767" s="2" t="n">
+        <v>46087.67981571893</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>ee252fdb-4dab-44ae-a49d-a9f0ecfeafa0</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>6601.72</v>
+      </c>
+      <c r="D768" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H768" s="2" t="n">
+        <v>46085.67981572195</v>
+      </c>
+      <c r="I768" s="2" t="n">
+        <v>46090.67981572195</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>48f1e553-b8bf-4462-833e-a9143dd2553c</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>9979.42</v>
+      </c>
+      <c r="D769" t="n">
+        <v>90.79000000000001</v>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="n">
+        <v>46072.67981572494</v>
+      </c>
+      <c r="I769" s="2" t="n">
+        <v>46077.67981572494</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>a5121bc6-b739-4ca2-8f6f-35d6f2615db4</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>6957.42</v>
+      </c>
+      <c r="D770" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H770" s="2" t="n">
+        <v>46063.67981572814</v>
+      </c>
+      <c r="I770" s="2" t="n">
+        <v>46068.67981572814</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>eb1f00ff-1fe1-4943-9f2f-d5743c621a19</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>7611.05</v>
+      </c>
+      <c r="D771" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="n">
+        <v>46065.67981573135</v>
+      </c>
+      <c r="I771" s="2" t="n">
+        <v>46070.67981573135</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>ec102bf8-b99f-42c4-a6ab-1216097b7d19</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>7218.9</v>
+      </c>
+      <c r="D772" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="n">
+        <v>46062.67981573454</v>
+      </c>
+      <c r="I772" s="2" t="n">
+        <v>46067.67981573454</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>0173642e-3ca4-45f9-b7b3-e7a8252f38cd</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>4492.31</v>
+      </c>
+      <c r="D773" t="n">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="n">
+        <v>46064.67981573772</v>
+      </c>
+      <c r="I773" s="2" t="n">
+        <v>46069.67981573772</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>8183ea22-9000-4f57-b3da-a02cebc5b2ea</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>7566.6</v>
+      </c>
+      <c r="D774" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="n">
+        <v>46071.6798157408</v>
+      </c>
+      <c r="I774" s="2" t="n">
+        <v>46076.6798157408</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>639a7382-e74b-47f4-b1f7-d3f037edde05</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>6469.33</v>
+      </c>
+      <c r="D775" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="n">
+        <v>46067.67981574377</v>
+      </c>
+      <c r="I775" s="2" t="n">
+        <v>46072.67981574377</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>d8006394-103b-4106-9a7c-fce11b677073</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>9198.790000000001</v>
+      </c>
+      <c r="D776" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="n">
+        <v>46079.67981574679</v>
+      </c>
+      <c r="I776" s="2" t="n">
+        <v>46084.67981574679</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>88f6f350-56b4-4456-b412-2b48c8714cf3</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>7370.42</v>
+      </c>
+      <c r="D777" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="n">
+        <v>46066.6798157502</v>
+      </c>
+      <c r="I777" s="2" t="n">
+        <v>46071.6798157502</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>e4889755-bad3-44fd-a814-2ba395fff6ef</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>1004.83</v>
+      </c>
+      <c r="D778" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="n">
+        <v>46080.6798157534</v>
+      </c>
+      <c r="I778" s="2" t="n">
+        <v>46085.6798157534</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>429319d8-196b-4125-af5c-a90afd03818d</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>2418.75</v>
+      </c>
+      <c r="D779" t="n">
+        <v>92.69</v>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="n">
+        <v>46074.67981575647</v>
+      </c>
+      <c r="I779" s="2" t="n">
+        <v>46079.67981575647</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>aeaef3db-23e4-4af5-9d22-85653f916edb</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>6190.87</v>
+      </c>
+      <c r="D780" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="n">
+        <v>46060.67981575961</v>
+      </c>
+      <c r="I780" s="2" t="n">
+        <v>46065.67981575961</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>67483aeb-f661-433a-8026-dc1a19d04a40</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>6616.34</v>
+      </c>
+      <c r="D781" t="n">
+        <v>94.23999999999999</v>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="n">
+        <v>46084.67981576294</v>
+      </c>
+      <c r="I781" s="2" t="n">
+        <v>46089.67981576294</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>95d456b7-4823-4913-970a-8967073748d1</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>6377.72</v>
+      </c>
+      <c r="D782" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="n">
+        <v>46084.6798157663</v>
+      </c>
+      <c r="I782" s="2" t="n">
+        <v>46089.6798157663</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>0418ae8f-6703-4a6c-b83e-b0fe9fd037e4</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>3220.28</v>
+      </c>
+      <c r="D783" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="n">
+        <v>46068.67981576944</v>
+      </c>
+      <c r="I783" s="2" t="n">
+        <v>46073.67981576944</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>5b41e7cc-006e-4c63-8a1d-85dfff1cc10e</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>5844</v>
+      </c>
+      <c r="D784" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="n">
+        <v>46083.67981577278</v>
+      </c>
+      <c r="I784" s="2" t="n">
+        <v>46088.67981577278</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>04395110-3b3d-4b75-8f8b-6502f948c986</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>6824.96</v>
+      </c>
+      <c r="D785" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="n">
+        <v>46077.67981577582</v>
+      </c>
+      <c r="I785" s="2" t="n">
+        <v>46082.67981577582</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>784d086b-aa3b-4aa0-8ad9-4d8f0e1c4d5a</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>7788.24</v>
+      </c>
+      <c r="D786" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="n">
+        <v>46061.67981577884</v>
+      </c>
+      <c r="I786" s="2" t="n">
+        <v>46066.67981577884</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>9d772244-7f72-4a63-93d9-b46f6536dfbd</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>7188.04</v>
+      </c>
+      <c r="D787" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="n">
+        <v>46075.67981578207</v>
+      </c>
+      <c r="I787" s="2" t="n">
+        <v>46080.67981578207</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>1752cca5-ce66-48aa-8ad0-b583c45e3cf4</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>3792.53</v>
+      </c>
+      <c r="D788" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="n">
+        <v>46064.67981578535</v>
+      </c>
+      <c r="I788" s="2" t="n">
+        <v>46069.67981578535</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>92a43823-016b-4402-9f11-123ef62af4f9</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>1804.65</v>
+      </c>
+      <c r="D789" t="n">
+        <v>87.69</v>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="n">
+        <v>46074.67981578839</v>
+      </c>
+      <c r="I789" s="2" t="n">
+        <v>46079.67981578839</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>d03a8487-3061-4bc7-b510-eff9d3910d1d</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>7488.97</v>
+      </c>
+      <c r="D790" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="n">
+        <v>46082.6798157914</v>
+      </c>
+      <c r="I790" s="2" t="n">
+        <v>46087.6798157914</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>a06ded3f-56ec-457e-aa98-750bbd584cf7</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>2901.13</v>
+      </c>
+      <c r="D791" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="n">
+        <v>46071.67981579489</v>
+      </c>
+      <c r="I791" s="2" t="n">
+        <v>46076.67981579489</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>fa8bc42b-413a-444f-953c-1e8e954d680c</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>4864.29</v>
+      </c>
+      <c r="D792" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="n">
+        <v>46079.67981579797</v>
+      </c>
+      <c r="I792" s="2" t="n">
+        <v>46084.67981579797</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2a30d9c7-fe48-47a5-b02c-62036ea6212a</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>3488.4</v>
+      </c>
+      <c r="D793" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="n">
+        <v>46085.679815801</v>
+      </c>
+      <c r="I793" s="2" t="n">
+        <v>46090.679815801</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>dc2dcf9c-646c-4875-800f-75faf2c477af</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>4031.56</v>
+      </c>
+      <c r="D794" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="n">
+        <v>46086.67981580406</v>
+      </c>
+      <c r="I794" s="2" t="n">
+        <v>46091.67981580406</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>3a17ede1-b206-455b-9cf9-2c400522dcb6</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>5423.83</v>
+      </c>
+      <c r="D795" t="n">
+        <v>85.81</v>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="n">
+        <v>46076.67981580735</v>
+      </c>
+      <c r="I795" s="2" t="n">
+        <v>46081.67981580735</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>21b19f56-3bea-46b9-af6a-58e810292df8</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>6763.35</v>
+      </c>
+      <c r="D796" t="n">
+        <v>92.52</v>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H796" s="2" t="n">
+        <v>46060.67981581039</v>
+      </c>
+      <c r="I796" s="2" t="n">
+        <v>46065.67981581039</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>98621bb2-d51c-4362-83d6-8fb319ee80da</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>5779.75</v>
+      </c>
+      <c r="D797" t="n">
+        <v>90.94</v>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="n">
+        <v>46088.67981581359</v>
+      </c>
+      <c r="I797" s="2" t="n">
+        <v>46093.67981581359</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>7b041b20-4548-4d01-9dea-f30c710ef3da</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>5529.67</v>
+      </c>
+      <c r="D798" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H798" s="2" t="n">
+        <v>46084.67981581675</v>
+      </c>
+      <c r="I798" s="2" t="n">
+        <v>46089.67981581675</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>559699cf-6ee3-4045-a124-0f566ce5a841</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>8646.860000000001</v>
+      </c>
+      <c r="D799" t="n">
+        <v>97</v>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="n">
+        <v>46065.67981582</v>
+      </c>
+      <c r="I799" s="2" t="n">
+        <v>46070.67981582</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>b84a2a61-3d0c-4680-b66b-e827f4dd39de</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>4096.83</v>
+      </c>
+      <c r="D800" t="n">
+        <v>88.69</v>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="n">
+        <v>46068.67981582315</v>
+      </c>
+      <c r="I800" s="2" t="n">
+        <v>46073.67981582315</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>ca46c94f-9fa0-4bb3-b7dc-a9726f10abce</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>8236.83</v>
+      </c>
+      <c r="D801" t="n">
+        <v>96.70999999999999</v>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="n">
+        <v>46083.67981582624</v>
+      </c>
+      <c r="I801" s="2" t="n">
+        <v>46088.67981582624</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I801"/>
+  <dimension ref="A1:I851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29762,10 +29762,10 @@
         </is>
       </c>
       <c r="H752" s="2" t="n">
-        <v>46068.67981566994</v>
+        <v>46068.6798156713</v>
       </c>
       <c r="I752" s="2" t="n">
-        <v>46073.67981566994</v>
+        <v>46073.6798156713</v>
       </c>
     </row>
     <row r="753">
@@ -29801,10 +29801,10 @@
         </is>
       </c>
       <c r="H753" s="2" t="n">
-        <v>46083.67981567408</v>
+        <v>46083.6798156713</v>
       </c>
       <c r="I753" s="2" t="n">
-        <v>46088.67981567408</v>
+        <v>46088.6798156713</v>
       </c>
     </row>
     <row r="754">
@@ -29840,10 +29840,10 @@
         </is>
       </c>
       <c r="H754" s="2" t="n">
-        <v>46067.67981567739</v>
+        <v>46067.67981568287</v>
       </c>
       <c r="I754" s="2" t="n">
-        <v>46072.67981567739</v>
+        <v>46072.67981568287</v>
       </c>
     </row>
     <row r="755">
@@ -29879,10 +29879,10 @@
         </is>
       </c>
       <c r="H755" s="2" t="n">
-        <v>46061.67981568087</v>
+        <v>46061.67981568287</v>
       </c>
       <c r="I755" s="2" t="n">
-        <v>46066.67981568087</v>
+        <v>46066.67981568287</v>
       </c>
     </row>
     <row r="756">
@@ -29918,10 +29918,10 @@
         </is>
       </c>
       <c r="H756" s="2" t="n">
-        <v>46063.67981568407</v>
+        <v>46063.67981568287</v>
       </c>
       <c r="I756" s="2" t="n">
-        <v>46068.67981568407</v>
+        <v>46068.67981568287</v>
       </c>
     </row>
     <row r="757">
@@ -29957,10 +29957,10 @@
         </is>
       </c>
       <c r="H757" s="2" t="n">
-        <v>46068.67981568717</v>
+        <v>46068.67981568287</v>
       </c>
       <c r="I757" s="2" t="n">
-        <v>46073.67981568717</v>
+        <v>46073.67981568287</v>
       </c>
     </row>
     <row r="758">
@@ -29996,10 +29996,10 @@
         </is>
       </c>
       <c r="H758" s="2" t="n">
-        <v>46060.67981569034</v>
+        <v>46060.67981569444</v>
       </c>
       <c r="I758" s="2" t="n">
-        <v>46065.67981569034</v>
+        <v>46065.67981569444</v>
       </c>
     </row>
     <row r="759">
@@ -30035,10 +30035,10 @@
         </is>
       </c>
       <c r="H759" s="2" t="n">
-        <v>46068.67981569363</v>
+        <v>46068.67981569444</v>
       </c>
       <c r="I759" s="2" t="n">
-        <v>46073.67981569363</v>
+        <v>46073.67981569444</v>
       </c>
     </row>
     <row r="760">
@@ -30074,10 +30074,10 @@
         </is>
       </c>
       <c r="H760" s="2" t="n">
-        <v>46082.67981569669</v>
+        <v>46082.67981569444</v>
       </c>
       <c r="I760" s="2" t="n">
-        <v>46087.67981569669</v>
+        <v>46087.67981569444</v>
       </c>
     </row>
     <row r="761">
@@ -30113,10 +30113,10 @@
         </is>
       </c>
       <c r="H761" s="2" t="n">
-        <v>46076.67981569986</v>
+        <v>46076.67981569444</v>
       </c>
       <c r="I761" s="2" t="n">
-        <v>46081.67981569986</v>
+        <v>46081.67981569444</v>
       </c>
     </row>
     <row r="762">
@@ -30152,10 +30152,10 @@
         </is>
       </c>
       <c r="H762" s="2" t="n">
-        <v>46062.67981570315</v>
+        <v>46062.67981570602</v>
       </c>
       <c r="I762" s="2" t="n">
-        <v>46067.67981570315</v>
+        <v>46067.67981570602</v>
       </c>
     </row>
     <row r="763">
@@ -30191,10 +30191,10 @@
         </is>
       </c>
       <c r="H763" s="2" t="n">
-        <v>46068.67981570633</v>
+        <v>46068.67981570602</v>
       </c>
       <c r="I763" s="2" t="n">
-        <v>46073.67981570633</v>
+        <v>46073.67981570602</v>
       </c>
     </row>
     <row r="764">
@@ -30230,10 +30230,10 @@
         </is>
       </c>
       <c r="H764" s="2" t="n">
-        <v>46077.67981570937</v>
+        <v>46077.67981570602</v>
       </c>
       <c r="I764" s="2" t="n">
-        <v>46082.67981570937</v>
+        <v>46082.67981570602</v>
       </c>
     </row>
     <row r="765">
@@ -30269,10 +30269,10 @@
         </is>
       </c>
       <c r="H765" s="2" t="n">
-        <v>46072.67981571238</v>
+        <v>46072.67981571759</v>
       </c>
       <c r="I765" s="2" t="n">
-        <v>46077.67981571238</v>
+        <v>46077.67981571759</v>
       </c>
     </row>
     <row r="766">
@@ -30308,10 +30308,10 @@
         </is>
       </c>
       <c r="H766" s="2" t="n">
-        <v>46085.67981571573</v>
+        <v>46085.67981571759</v>
       </c>
       <c r="I766" s="2" t="n">
-        <v>46090.67981571573</v>
+        <v>46090.67981571759</v>
       </c>
     </row>
     <row r="767">
@@ -30347,10 +30347,10 @@
         </is>
       </c>
       <c r="H767" s="2" t="n">
-        <v>46082.67981571893</v>
+        <v>46082.67981571759</v>
       </c>
       <c r="I767" s="2" t="n">
-        <v>46087.67981571893</v>
+        <v>46087.67981571759</v>
       </c>
     </row>
     <row r="768">
@@ -30386,10 +30386,10 @@
         </is>
       </c>
       <c r="H768" s="2" t="n">
-        <v>46085.67981572195</v>
+        <v>46085.67981571759</v>
       </c>
       <c r="I768" s="2" t="n">
-        <v>46090.67981572195</v>
+        <v>46090.67981571759</v>
       </c>
     </row>
     <row r="769">
@@ -30425,10 +30425,10 @@
         </is>
       </c>
       <c r="H769" s="2" t="n">
-        <v>46072.67981572494</v>
+        <v>46072.67981572916</v>
       </c>
       <c r="I769" s="2" t="n">
-        <v>46077.67981572494</v>
+        <v>46077.67981572916</v>
       </c>
     </row>
     <row r="770">
@@ -30464,10 +30464,10 @@
         </is>
       </c>
       <c r="H770" s="2" t="n">
-        <v>46063.67981572814</v>
+        <v>46063.67981572916</v>
       </c>
       <c r="I770" s="2" t="n">
-        <v>46068.67981572814</v>
+        <v>46068.67981572916</v>
       </c>
     </row>
     <row r="771">
@@ -30503,10 +30503,10 @@
         </is>
       </c>
       <c r="H771" s="2" t="n">
-        <v>46065.67981573135</v>
+        <v>46065.67981572916</v>
       </c>
       <c r="I771" s="2" t="n">
-        <v>46070.67981573135</v>
+        <v>46070.67981572916</v>
       </c>
     </row>
     <row r="772">
@@ -30542,10 +30542,10 @@
         </is>
       </c>
       <c r="H772" s="2" t="n">
-        <v>46062.67981573454</v>
+        <v>46062.67981572916</v>
       </c>
       <c r="I772" s="2" t="n">
-        <v>46067.67981573454</v>
+        <v>46067.67981572916</v>
       </c>
     </row>
     <row r="773">
@@ -30581,10 +30581,10 @@
         </is>
       </c>
       <c r="H773" s="2" t="n">
-        <v>46064.67981573772</v>
+        <v>46064.67981574074</v>
       </c>
       <c r="I773" s="2" t="n">
-        <v>46069.67981573772</v>
+        <v>46069.67981574074</v>
       </c>
     </row>
     <row r="774">
@@ -30620,10 +30620,10 @@
         </is>
       </c>
       <c r="H774" s="2" t="n">
-        <v>46071.6798157408</v>
+        <v>46071.67981574074</v>
       </c>
       <c r="I774" s="2" t="n">
-        <v>46076.6798157408</v>
+        <v>46076.67981574074</v>
       </c>
     </row>
     <row r="775">
@@ -30659,10 +30659,10 @@
         </is>
       </c>
       <c r="H775" s="2" t="n">
-        <v>46067.67981574377</v>
+        <v>46067.67981574074</v>
       </c>
       <c r="I775" s="2" t="n">
-        <v>46072.67981574377</v>
+        <v>46072.67981574074</v>
       </c>
     </row>
     <row r="776">
@@ -30698,10 +30698,10 @@
         </is>
       </c>
       <c r="H776" s="2" t="n">
-        <v>46079.67981574679</v>
+        <v>46079.67981575232</v>
       </c>
       <c r="I776" s="2" t="n">
-        <v>46084.67981574679</v>
+        <v>46084.67981575232</v>
       </c>
     </row>
     <row r="777">
@@ -30737,10 +30737,10 @@
         </is>
       </c>
       <c r="H777" s="2" t="n">
-        <v>46066.6798157502</v>
+        <v>46066.67981575232</v>
       </c>
       <c r="I777" s="2" t="n">
-        <v>46071.6798157502</v>
+        <v>46071.67981575232</v>
       </c>
     </row>
     <row r="778">
@@ -30776,10 +30776,10 @@
         </is>
       </c>
       <c r="H778" s="2" t="n">
-        <v>46080.6798157534</v>
+        <v>46080.67981575232</v>
       </c>
       <c r="I778" s="2" t="n">
-        <v>46085.6798157534</v>
+        <v>46085.67981575232</v>
       </c>
     </row>
     <row r="779">
@@ -30815,10 +30815,10 @@
         </is>
       </c>
       <c r="H779" s="2" t="n">
-        <v>46074.67981575647</v>
+        <v>46074.67981575232</v>
       </c>
       <c r="I779" s="2" t="n">
-        <v>46079.67981575647</v>
+        <v>46079.67981575232</v>
       </c>
     </row>
     <row r="780">
@@ -30854,10 +30854,10 @@
         </is>
       </c>
       <c r="H780" s="2" t="n">
-        <v>46060.67981575961</v>
+        <v>46060.67981576389</v>
       </c>
       <c r="I780" s="2" t="n">
-        <v>46065.67981575961</v>
+        <v>46065.67981576389</v>
       </c>
     </row>
     <row r="781">
@@ -30893,10 +30893,10 @@
         </is>
       </c>
       <c r="H781" s="2" t="n">
-        <v>46084.67981576294</v>
+        <v>46084.67981576389</v>
       </c>
       <c r="I781" s="2" t="n">
-        <v>46089.67981576294</v>
+        <v>46089.67981576389</v>
       </c>
     </row>
     <row r="782">
@@ -30932,10 +30932,10 @@
         </is>
       </c>
       <c r="H782" s="2" t="n">
-        <v>46084.6798157663</v>
+        <v>46084.67981576389</v>
       </c>
       <c r="I782" s="2" t="n">
-        <v>46089.6798157663</v>
+        <v>46089.67981576389</v>
       </c>
     </row>
     <row r="783">
@@ -30971,10 +30971,10 @@
         </is>
       </c>
       <c r="H783" s="2" t="n">
-        <v>46068.67981576944</v>
+        <v>46068.67981576389</v>
       </c>
       <c r="I783" s="2" t="n">
-        <v>46073.67981576944</v>
+        <v>46073.67981576389</v>
       </c>
     </row>
     <row r="784">
@@ -31010,10 +31010,10 @@
         </is>
       </c>
       <c r="H784" s="2" t="n">
-        <v>46083.67981577278</v>
+        <v>46083.67981577546</v>
       </c>
       <c r="I784" s="2" t="n">
-        <v>46088.67981577278</v>
+        <v>46088.67981577546</v>
       </c>
     </row>
     <row r="785">
@@ -31049,10 +31049,10 @@
         </is>
       </c>
       <c r="H785" s="2" t="n">
-        <v>46077.67981577582</v>
+        <v>46077.67981577546</v>
       </c>
       <c r="I785" s="2" t="n">
-        <v>46082.67981577582</v>
+        <v>46082.67981577546</v>
       </c>
     </row>
     <row r="786">
@@ -31088,10 +31088,10 @@
         </is>
       </c>
       <c r="H786" s="2" t="n">
-        <v>46061.67981577884</v>
+        <v>46061.67981577546</v>
       </c>
       <c r="I786" s="2" t="n">
-        <v>46066.67981577884</v>
+        <v>46066.67981577546</v>
       </c>
     </row>
     <row r="787">
@@ -31127,10 +31127,10 @@
         </is>
       </c>
       <c r="H787" s="2" t="n">
-        <v>46075.67981578207</v>
+        <v>46075.67981578704</v>
       </c>
       <c r="I787" s="2" t="n">
-        <v>46080.67981578207</v>
+        <v>46080.67981578704</v>
       </c>
     </row>
     <row r="788">
@@ -31166,10 +31166,10 @@
         </is>
       </c>
       <c r="H788" s="2" t="n">
-        <v>46064.67981578535</v>
+        <v>46064.67981578704</v>
       </c>
       <c r="I788" s="2" t="n">
-        <v>46069.67981578535</v>
+        <v>46069.67981578704</v>
       </c>
     </row>
     <row r="789">
@@ -31205,10 +31205,10 @@
         </is>
       </c>
       <c r="H789" s="2" t="n">
-        <v>46074.67981578839</v>
+        <v>46074.67981578704</v>
       </c>
       <c r="I789" s="2" t="n">
-        <v>46079.67981578839</v>
+        <v>46079.67981578704</v>
       </c>
     </row>
     <row r="790">
@@ -31244,10 +31244,10 @@
         </is>
       </c>
       <c r="H790" s="2" t="n">
-        <v>46082.6798157914</v>
+        <v>46082.67981578704</v>
       </c>
       <c r="I790" s="2" t="n">
-        <v>46087.6798157914</v>
+        <v>46087.67981578704</v>
       </c>
     </row>
     <row r="791">
@@ -31283,10 +31283,10 @@
         </is>
       </c>
       <c r="H791" s="2" t="n">
-        <v>46071.67981579489</v>
+        <v>46071.67981579861</v>
       </c>
       <c r="I791" s="2" t="n">
-        <v>46076.67981579489</v>
+        <v>46076.67981579861</v>
       </c>
     </row>
     <row r="792">
@@ -31322,10 +31322,10 @@
         </is>
       </c>
       <c r="H792" s="2" t="n">
-        <v>46079.67981579797</v>
+        <v>46079.67981579861</v>
       </c>
       <c r="I792" s="2" t="n">
-        <v>46084.67981579797</v>
+        <v>46084.67981579861</v>
       </c>
     </row>
     <row r="793">
@@ -31361,10 +31361,10 @@
         </is>
       </c>
       <c r="H793" s="2" t="n">
-        <v>46085.679815801</v>
+        <v>46085.67981579861</v>
       </c>
       <c r="I793" s="2" t="n">
-        <v>46090.679815801</v>
+        <v>46090.67981579861</v>
       </c>
     </row>
     <row r="794">
@@ -31400,10 +31400,10 @@
         </is>
       </c>
       <c r="H794" s="2" t="n">
-        <v>46086.67981580406</v>
+        <v>46086.67981579861</v>
       </c>
       <c r="I794" s="2" t="n">
-        <v>46091.67981580406</v>
+        <v>46091.67981579861</v>
       </c>
     </row>
     <row r="795">
@@ -31439,10 +31439,10 @@
         </is>
       </c>
       <c r="H795" s="2" t="n">
-        <v>46076.67981580735</v>
+        <v>46076.67981581019</v>
       </c>
       <c r="I795" s="2" t="n">
-        <v>46081.67981580735</v>
+        <v>46081.67981581019</v>
       </c>
     </row>
     <row r="796">
@@ -31478,10 +31478,10 @@
         </is>
       </c>
       <c r="H796" s="2" t="n">
-        <v>46060.67981581039</v>
+        <v>46060.67981581019</v>
       </c>
       <c r="I796" s="2" t="n">
-        <v>46065.67981581039</v>
+        <v>46065.67981581019</v>
       </c>
     </row>
     <row r="797">
@@ -31517,10 +31517,10 @@
         </is>
       </c>
       <c r="H797" s="2" t="n">
-        <v>46088.67981581359</v>
+        <v>46088.67981581019</v>
       </c>
       <c r="I797" s="2" t="n">
-        <v>46093.67981581359</v>
+        <v>46093.67981581019</v>
       </c>
     </row>
     <row r="798">
@@ -31556,10 +31556,10 @@
         </is>
       </c>
       <c r="H798" s="2" t="n">
-        <v>46084.67981581675</v>
+        <v>46084.67981582176</v>
       </c>
       <c r="I798" s="2" t="n">
-        <v>46089.67981581675</v>
+        <v>46089.67981582176</v>
       </c>
     </row>
     <row r="799">
@@ -31595,10 +31595,10 @@
         </is>
       </c>
       <c r="H799" s="2" t="n">
-        <v>46065.67981582</v>
+        <v>46065.67981582176</v>
       </c>
       <c r="I799" s="2" t="n">
-        <v>46070.67981582</v>
+        <v>46070.67981582176</v>
       </c>
     </row>
     <row r="800">
@@ -31634,10 +31634,10 @@
         </is>
       </c>
       <c r="H800" s="2" t="n">
-        <v>46068.67981582315</v>
+        <v>46068.67981582176</v>
       </c>
       <c r="I800" s="2" t="n">
-        <v>46073.67981582315</v>
+        <v>46073.67981582176</v>
       </c>
     </row>
     <row r="801">
@@ -31673,10 +31673,1960 @@
         </is>
       </c>
       <c r="H801" s="2" t="n">
-        <v>46083.67981582624</v>
+        <v>46083.67981582176</v>
       </c>
       <c r="I801" s="2" t="n">
-        <v>46088.67981582624</v>
+        <v>46088.67981582176</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>b1280636-e3ce-4fd4-83fb-2003c154a453</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>7709.2</v>
+      </c>
+      <c r="D802" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="n">
+        <v>46061.72017556887</v>
+      </c>
+      <c r="I802" s="2" t="n">
+        <v>46066.72017556887</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>c6a4dbc1-f752-41da-8749-21a410731bfa</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>2223.59</v>
+      </c>
+      <c r="D803" t="n">
+        <v>89.93000000000001</v>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="n">
+        <v>46079.72017557322</v>
+      </c>
+      <c r="I803" s="2" t="n">
+        <v>46084.72017557322</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>6b719db8-d872-4401-b8b7-cff1f1a8cbdc</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>1282.77</v>
+      </c>
+      <c r="D804" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H804" s="2" t="n">
+        <v>46084.7201755766</v>
+      </c>
+      <c r="I804" s="2" t="n">
+        <v>46089.7201755766</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>37cdf58e-e19b-43f7-a2e2-b68fa6a4e9f3</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>6650.2</v>
+      </c>
+      <c r="D805" t="n">
+        <v>88.54000000000001</v>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="n">
+        <v>46082.72017557982</v>
+      </c>
+      <c r="I805" s="2" t="n">
+        <v>46087.72017557982</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>7934b399-37d5-45b6-a6b9-88ab62284696</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>4087.11</v>
+      </c>
+      <c r="D806" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H806" s="2" t="n">
+        <v>46082.72017558294</v>
+      </c>
+      <c r="I806" s="2" t="n">
+        <v>46087.72017558294</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>215dac92-3b8a-4048-9492-afcbb38b6741</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>1849.63</v>
+      </c>
+      <c r="D807" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="n">
+        <v>46077.72017558666</v>
+      </c>
+      <c r="I807" s="2" t="n">
+        <v>46082.72017558666</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>03185e8e-1460-4bf0-94e5-ac5bef028002</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>3146.13</v>
+      </c>
+      <c r="D808" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="n">
+        <v>46072.72017558973</v>
+      </c>
+      <c r="I808" s="2" t="n">
+        <v>46077.72017558973</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>09a00b98-2a99-482d-bf63-db20b449c231</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>6808.64</v>
+      </c>
+      <c r="D809" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="n">
+        <v>46072.72017559287</v>
+      </c>
+      <c r="I809" s="2" t="n">
+        <v>46077.72017559287</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>db0bb19c-1b2b-466e-a2e7-fb1fcbdfa089</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>7818.93</v>
+      </c>
+      <c r="D810" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="n">
+        <v>46062.72017559685</v>
+      </c>
+      <c r="I810" s="2" t="n">
+        <v>46067.72017559685</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>0a62276d-a1a8-477a-9b9e-4e36075570d4</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>2938.89</v>
+      </c>
+      <c r="D811" t="n">
+        <v>97.01000000000001</v>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="n">
+        <v>46063.72017560013</v>
+      </c>
+      <c r="I811" s="2" t="n">
+        <v>46068.72017560013</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>bece8b1d-7d8e-4589-a5e7-66a1213fa737</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>6272.91</v>
+      </c>
+      <c r="D812" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="n">
+        <v>46066.72017560348</v>
+      </c>
+      <c r="I812" s="2" t="n">
+        <v>46071.72017560348</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>79dffc75-b06a-49a7-938f-65f7da965b17</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>6829.1</v>
+      </c>
+      <c r="D813" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="n">
+        <v>46082.72017560693</v>
+      </c>
+      <c r="I813" s="2" t="n">
+        <v>46087.72017560693</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>da953338-d740-4e2e-9aec-31ca59b1f3b1</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>7806.62</v>
+      </c>
+      <c r="D814" t="n">
+        <v>95.37</v>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="n">
+        <v>46076.72017561011</v>
+      </c>
+      <c r="I814" s="2" t="n">
+        <v>46081.72017561011</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2e0fb77e-5499-421b-996d-2aea1fe4ae10</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>3230.5</v>
+      </c>
+      <c r="D815" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="n">
+        <v>46070.72017561316</v>
+      </c>
+      <c r="I815" s="2" t="n">
+        <v>46075.72017561316</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>40a698cc-ad4b-48a2-8242-35f0dea4083c</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>6803.05</v>
+      </c>
+      <c r="D816" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="n">
+        <v>46066.72017561622</v>
+      </c>
+      <c r="I816" s="2" t="n">
+        <v>46071.72017561622</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>de3df5c4-c47e-4a7c-8c62-10124aba11bb</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>5706.24</v>
+      </c>
+      <c r="D817" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="n">
+        <v>46075.72017561949</v>
+      </c>
+      <c r="I817" s="2" t="n">
+        <v>46080.72017561949</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>c5ea309c-4537-438f-8cd8-cdbc21cd9ddd</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>5655.19</v>
+      </c>
+      <c r="D818" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H818" s="2" t="n">
+        <v>46087.72017562253</v>
+      </c>
+      <c r="I818" s="2" t="n">
+        <v>46092.72017562253</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>0f0fd362-0345-4d85-9d1a-8b0c18e939e0</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>6738.84</v>
+      </c>
+      <c r="D819" t="n">
+        <v>86.58</v>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="n">
+        <v>46072.72017562575</v>
+      </c>
+      <c r="I819" s="2" t="n">
+        <v>46077.72017562575</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>b49bcc59-b5e9-4a3e-ba45-2e6e8c077cc0</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>7268.32</v>
+      </c>
+      <c r="D820" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H820" s="2" t="n">
+        <v>46072.72017562882</v>
+      </c>
+      <c r="I820" s="2" t="n">
+        <v>46077.72017562882</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>4dfd08ec-de9e-4737-86af-8fbda7edc363</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>8384.41</v>
+      </c>
+      <c r="D821" t="n">
+        <v>91.03</v>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="n">
+        <v>46082.72017563219</v>
+      </c>
+      <c r="I821" s="2" t="n">
+        <v>46087.72017563219</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>bd09e1c4-7972-47bd-ad09-d707e6358385</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>4125.57</v>
+      </c>
+      <c r="D822" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="n">
+        <v>46070.72017563524</v>
+      </c>
+      <c r="I822" s="2" t="n">
+        <v>46075.72017563524</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>deea15e2-8f12-4453-b6d1-8de07a91dd81</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>3562.56</v>
+      </c>
+      <c r="D823" t="n">
+        <v>98.77</v>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="n">
+        <v>46077.72017563834</v>
+      </c>
+      <c r="I823" s="2" t="n">
+        <v>46082.72017563834</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>1a9d9071-6d5b-4907-b755-30980f2aa9ea</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>8653.34</v>
+      </c>
+      <c r="D824" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="n">
+        <v>46074.72017564187</v>
+      </c>
+      <c r="I824" s="2" t="n">
+        <v>46079.72017564187</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>7918a951-f712-43d8-82da-29c50f53b2d4</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>8465.879999999999</v>
+      </c>
+      <c r="D825" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="n">
+        <v>46067.72017564498</v>
+      </c>
+      <c r="I825" s="2" t="n">
+        <v>46072.72017564498</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>aa0d1ca4-0bdd-40e3-916d-4c8ccd6263da</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>7161.97</v>
+      </c>
+      <c r="D826" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="n">
+        <v>46082.72017564815</v>
+      </c>
+      <c r="I826" s="2" t="n">
+        <v>46087.72017564815</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>04b4622d-0934-4bde-ad68-378e5cba3bee</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>5703.3</v>
+      </c>
+      <c r="D827" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="n">
+        <v>46063.72017565139</v>
+      </c>
+      <c r="I827" s="2" t="n">
+        <v>46068.72017565139</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>7d55820e-b500-4be6-aba6-6e1b54e699f2</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>5638.54</v>
+      </c>
+      <c r="D828" t="n">
+        <v>87.59</v>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="n">
+        <v>46065.7201756546</v>
+      </c>
+      <c r="I828" s="2" t="n">
+        <v>46070.7201756546</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>6cc32273-1b7f-462c-8b65-057dbdda68f0</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>3348.39</v>
+      </c>
+      <c r="D829" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="n">
+        <v>46083.72017565771</v>
+      </c>
+      <c r="I829" s="2" t="n">
+        <v>46088.72017565771</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>acf20933-63e8-438e-835c-c9ca7c2630b2</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>5971.8</v>
+      </c>
+      <c r="D830" t="n">
+        <v>97.27</v>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="n">
+        <v>46084.72017566072</v>
+      </c>
+      <c r="I830" s="2" t="n">
+        <v>46089.72017566072</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>60f472af-3772-4903-a82f-dbd7aa94ff17</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>8176.68</v>
+      </c>
+      <c r="D831" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="n">
+        <v>46076.72017566382</v>
+      </c>
+      <c r="I831" s="2" t="n">
+        <v>46081.72017566382</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>40af0366-d9ad-4dd8-b8c6-929bdea9de0e</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>9425.25</v>
+      </c>
+      <c r="D832" t="n">
+        <v>85.01000000000001</v>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="n">
+        <v>46088.72017566721</v>
+      </c>
+      <c r="I832" s="2" t="n">
+        <v>46093.72017566721</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>a67911c6-8945-43ce-90b8-254bb38e13d8</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>6455.15</v>
+      </c>
+      <c r="D833" t="n">
+        <v>90.01000000000001</v>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="n">
+        <v>46086.72017567028</v>
+      </c>
+      <c r="I833" s="2" t="n">
+        <v>46091.72017567028</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>d93f8dd0-5fd0-4035-b2ec-18e9a72a6db4</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>7740.08</v>
+      </c>
+      <c r="D834" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="n">
+        <v>46079.72017567351</v>
+      </c>
+      <c r="I834" s="2" t="n">
+        <v>46084.72017567351</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>410d510e-bd75-4122-9725-f0f4f426d478</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>9816.9</v>
+      </c>
+      <c r="D835" t="n">
+        <v>86.14</v>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="n">
+        <v>46084.72017567686</v>
+      </c>
+      <c r="I835" s="2" t="n">
+        <v>46089.72017567686</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>fcc520fd-a135-41ba-a89b-ef711524ac6b</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>4368.76</v>
+      </c>
+      <c r="D836" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="n">
+        <v>46081.72017567982</v>
+      </c>
+      <c r="I836" s="2" t="n">
+        <v>46086.72017567982</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>4e9d9df4-65ac-4cbc-97e5-d95bce1106a2</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>3191.03</v>
+      </c>
+      <c r="D837" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="n">
+        <v>46084.72017568293</v>
+      </c>
+      <c r="I837" s="2" t="n">
+        <v>46089.72017568293</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>7e764c48-99d5-4fe8-bb41-74f0455719ff</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>8505.290000000001</v>
+      </c>
+      <c r="D838" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="n">
+        <v>46075.72017568597</v>
+      </c>
+      <c r="I838" s="2" t="n">
+        <v>46080.72017568597</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>3dfb7c84-20de-41bd-a508-c1ec5f108d6a</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>2299.72</v>
+      </c>
+      <c r="D839" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="n">
+        <v>46067.7201756896</v>
+      </c>
+      <c r="I839" s="2" t="n">
+        <v>46072.7201756896</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>83db7dae-edd6-46b6-9a59-ea31a80cec6c</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>1403.94</v>
+      </c>
+      <c r="D840" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="n">
+        <v>46068.72017569275</v>
+      </c>
+      <c r="I840" s="2" t="n">
+        <v>46073.72017569275</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>50409910-90a5-40ef-8968-8132feff19ac</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>5744.89</v>
+      </c>
+      <c r="D841" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="n">
+        <v>46068.72017569585</v>
+      </c>
+      <c r="I841" s="2" t="n">
+        <v>46073.72017569585</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>8a589903-e137-4a60-82d7-fc0b1da76393</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>7872.63</v>
+      </c>
+      <c r="D842" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="n">
+        <v>46084.720175699</v>
+      </c>
+      <c r="I842" s="2" t="n">
+        <v>46089.720175699</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>94c8fcd4-f6cc-403f-b81d-2c34859f3312</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>2599.86</v>
+      </c>
+      <c r="D843" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="n">
+        <v>46062.72017570234</v>
+      </c>
+      <c r="I843" s="2" t="n">
+        <v>46067.72017570234</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>fb82b25e-5718-4a9f-bb2c-8e97185fec6f</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>7325.57</v>
+      </c>
+      <c r="D844" t="n">
+        <v>96.44</v>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="n">
+        <v>46066.72017570541</v>
+      </c>
+      <c r="I844" s="2" t="n">
+        <v>46071.72017570541</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>e21d4a4a-d2fb-4d97-a357-22cae8ddf31f</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>2714.26</v>
+      </c>
+      <c r="D845" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="n">
+        <v>46069.72017570846</v>
+      </c>
+      <c r="I845" s="2" t="n">
+        <v>46074.72017570846</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>59c74d3e-af1c-4cc5-be6a-be9b340d2fc5</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>5997.1</v>
+      </c>
+      <c r="D846" t="n">
+        <v>97</v>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="n">
+        <v>46081.72017571172</v>
+      </c>
+      <c r="I846" s="2" t="n">
+        <v>46086.72017571172</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>c3d88499-ee91-486f-8905-9ab7d20ac1aa</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>6770.85</v>
+      </c>
+      <c r="D847" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="n">
+        <v>46082.72017571703</v>
+      </c>
+      <c r="I847" s="2" t="n">
+        <v>46087.72017571703</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>85601bfa-b688-4964-8b0b-a7f8115652ef</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>2510.12</v>
+      </c>
+      <c r="D848" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="n">
+        <v>46068.72017572085</v>
+      </c>
+      <c r="I848" s="2" t="n">
+        <v>46073.72017572085</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>bce2ac2a-7daa-446e-9388-63b75860ecac</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>7979.08</v>
+      </c>
+      <c r="D849" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="n">
+        <v>46065.72017572461</v>
+      </c>
+      <c r="I849" s="2" t="n">
+        <v>46070.72017572461</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>68169296-4328-41f4-a64a-1665ecca8a70</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>3100.82</v>
+      </c>
+      <c r="D850" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="n">
+        <v>46084.72017572765</v>
+      </c>
+      <c r="I850" s="2" t="n">
+        <v>46089.72017572765</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>3ab75ca7-e7fd-418d-9e7b-80f4bbc48ce4</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>4338.01</v>
+      </c>
+      <c r="D851" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="n">
+        <v>46074.7201757307</v>
+      </c>
+      <c r="I851" s="2" t="n">
+        <v>46079.7201757307</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I851"/>
+  <dimension ref="A1:I901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31712,10 +31712,10 @@
         </is>
       </c>
       <c r="H802" s="2" t="n">
-        <v>46061.72017556887</v>
+        <v>46061.72017556713</v>
       </c>
       <c r="I802" s="2" t="n">
-        <v>46066.72017556887</v>
+        <v>46066.72017556713</v>
       </c>
     </row>
     <row r="803">
@@ -31751,10 +31751,10 @@
         </is>
       </c>
       <c r="H803" s="2" t="n">
-        <v>46079.72017557322</v>
+        <v>46079.7201755787</v>
       </c>
       <c r="I803" s="2" t="n">
-        <v>46084.72017557322</v>
+        <v>46084.7201755787</v>
       </c>
     </row>
     <row r="804">
@@ -31790,10 +31790,10 @@
         </is>
       </c>
       <c r="H804" s="2" t="n">
-        <v>46084.7201755766</v>
+        <v>46084.7201755787</v>
       </c>
       <c r="I804" s="2" t="n">
-        <v>46089.7201755766</v>
+        <v>46089.7201755787</v>
       </c>
     </row>
     <row r="805">
@@ -31829,10 +31829,10 @@
         </is>
       </c>
       <c r="H805" s="2" t="n">
-        <v>46082.72017557982</v>
+        <v>46082.7201755787</v>
       </c>
       <c r="I805" s="2" t="n">
-        <v>46087.72017557982</v>
+        <v>46087.7201755787</v>
       </c>
     </row>
     <row r="806">
@@ -31868,10 +31868,10 @@
         </is>
       </c>
       <c r="H806" s="2" t="n">
-        <v>46082.72017558294</v>
+        <v>46082.7201755787</v>
       </c>
       <c r="I806" s="2" t="n">
-        <v>46087.72017558294</v>
+        <v>46087.7201755787</v>
       </c>
     </row>
     <row r="807">
@@ -31907,10 +31907,10 @@
         </is>
       </c>
       <c r="H807" s="2" t="n">
-        <v>46077.72017558666</v>
+        <v>46077.72017559028</v>
       </c>
       <c r="I807" s="2" t="n">
-        <v>46082.72017558666</v>
+        <v>46082.72017559028</v>
       </c>
     </row>
     <row r="808">
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="H808" s="2" t="n">
-        <v>46072.72017558973</v>
+        <v>46072.72017559028</v>
       </c>
       <c r="I808" s="2" t="n">
-        <v>46077.72017558973</v>
+        <v>46077.72017559028</v>
       </c>
     </row>
     <row r="809">
@@ -31985,10 +31985,10 @@
         </is>
       </c>
       <c r="H809" s="2" t="n">
-        <v>46072.72017559287</v>
+        <v>46072.72017559028</v>
       </c>
       <c r="I809" s="2" t="n">
-        <v>46077.72017559287</v>
+        <v>46077.72017559028</v>
       </c>
     </row>
     <row r="810">
@@ -32024,10 +32024,10 @@
         </is>
       </c>
       <c r="H810" s="2" t="n">
-        <v>46062.72017559685</v>
+        <v>46062.72017560185</v>
       </c>
       <c r="I810" s="2" t="n">
-        <v>46067.72017559685</v>
+        <v>46067.72017560185</v>
       </c>
     </row>
     <row r="811">
@@ -32063,10 +32063,10 @@
         </is>
       </c>
       <c r="H811" s="2" t="n">
-        <v>46063.72017560013</v>
+        <v>46063.72017560185</v>
       </c>
       <c r="I811" s="2" t="n">
-        <v>46068.72017560013</v>
+        <v>46068.72017560185</v>
       </c>
     </row>
     <row r="812">
@@ -32102,10 +32102,10 @@
         </is>
       </c>
       <c r="H812" s="2" t="n">
-        <v>46066.72017560348</v>
+        <v>46066.72017560185</v>
       </c>
       <c r="I812" s="2" t="n">
-        <v>46071.72017560348</v>
+        <v>46071.72017560185</v>
       </c>
     </row>
     <row r="813">
@@ -32141,10 +32141,10 @@
         </is>
       </c>
       <c r="H813" s="2" t="n">
-        <v>46082.72017560693</v>
+        <v>46082.72017560185</v>
       </c>
       <c r="I813" s="2" t="n">
-        <v>46087.72017560693</v>
+        <v>46087.72017560185</v>
       </c>
     </row>
     <row r="814">
@@ -32180,10 +32180,10 @@
         </is>
       </c>
       <c r="H814" s="2" t="n">
-        <v>46076.72017561011</v>
+        <v>46076.72017561342</v>
       </c>
       <c r="I814" s="2" t="n">
-        <v>46081.72017561011</v>
+        <v>46081.72017561342</v>
       </c>
     </row>
     <row r="815">
@@ -32219,10 +32219,10 @@
         </is>
       </c>
       <c r="H815" s="2" t="n">
-        <v>46070.72017561316</v>
+        <v>46070.72017561342</v>
       </c>
       <c r="I815" s="2" t="n">
-        <v>46075.72017561316</v>
+        <v>46075.72017561342</v>
       </c>
     </row>
     <row r="816">
@@ -32258,10 +32258,10 @@
         </is>
       </c>
       <c r="H816" s="2" t="n">
-        <v>46066.72017561622</v>
+        <v>46066.72017561342</v>
       </c>
       <c r="I816" s="2" t="n">
-        <v>46071.72017561622</v>
+        <v>46071.72017561342</v>
       </c>
     </row>
     <row r="817">
@@ -32297,10 +32297,10 @@
         </is>
       </c>
       <c r="H817" s="2" t="n">
-        <v>46075.72017561949</v>
+        <v>46075.720175625</v>
       </c>
       <c r="I817" s="2" t="n">
-        <v>46080.72017561949</v>
+        <v>46080.720175625</v>
       </c>
     </row>
     <row r="818">
@@ -32336,10 +32336,10 @@
         </is>
       </c>
       <c r="H818" s="2" t="n">
-        <v>46087.72017562253</v>
+        <v>46087.720175625</v>
       </c>
       <c r="I818" s="2" t="n">
-        <v>46092.72017562253</v>
+        <v>46092.720175625</v>
       </c>
     </row>
     <row r="819">
@@ -32375,10 +32375,10 @@
         </is>
       </c>
       <c r="H819" s="2" t="n">
-        <v>46072.72017562575</v>
+        <v>46072.720175625</v>
       </c>
       <c r="I819" s="2" t="n">
-        <v>46077.72017562575</v>
+        <v>46077.720175625</v>
       </c>
     </row>
     <row r="820">
@@ -32414,10 +32414,10 @@
         </is>
       </c>
       <c r="H820" s="2" t="n">
-        <v>46072.72017562882</v>
+        <v>46072.720175625</v>
       </c>
       <c r="I820" s="2" t="n">
-        <v>46077.72017562882</v>
+        <v>46077.720175625</v>
       </c>
     </row>
     <row r="821">
@@ -32453,10 +32453,10 @@
         </is>
       </c>
       <c r="H821" s="2" t="n">
-        <v>46082.72017563219</v>
+        <v>46082.72017563658</v>
       </c>
       <c r="I821" s="2" t="n">
-        <v>46087.72017563219</v>
+        <v>46087.72017563658</v>
       </c>
     </row>
     <row r="822">
@@ -32492,10 +32492,10 @@
         </is>
       </c>
       <c r="H822" s="2" t="n">
-        <v>46070.72017563524</v>
+        <v>46070.72017563658</v>
       </c>
       <c r="I822" s="2" t="n">
-        <v>46075.72017563524</v>
+        <v>46075.72017563658</v>
       </c>
     </row>
     <row r="823">
@@ -32531,10 +32531,10 @@
         </is>
       </c>
       <c r="H823" s="2" t="n">
-        <v>46077.72017563834</v>
+        <v>46077.72017563658</v>
       </c>
       <c r="I823" s="2" t="n">
-        <v>46082.72017563834</v>
+        <v>46082.72017563658</v>
       </c>
     </row>
     <row r="824">
@@ -32570,10 +32570,10 @@
         </is>
       </c>
       <c r="H824" s="2" t="n">
-        <v>46074.72017564187</v>
+        <v>46074.72017563658</v>
       </c>
       <c r="I824" s="2" t="n">
-        <v>46079.72017564187</v>
+        <v>46079.72017563658</v>
       </c>
     </row>
     <row r="825">
@@ -32609,10 +32609,10 @@
         </is>
       </c>
       <c r="H825" s="2" t="n">
-        <v>46067.72017564498</v>
+        <v>46067.72017564815</v>
       </c>
       <c r="I825" s="2" t="n">
-        <v>46072.72017564498</v>
+        <v>46072.72017564815</v>
       </c>
     </row>
     <row r="826">
@@ -32687,10 +32687,10 @@
         </is>
       </c>
       <c r="H827" s="2" t="n">
-        <v>46063.72017565139</v>
+        <v>46063.72017564815</v>
       </c>
       <c r="I827" s="2" t="n">
-        <v>46068.72017565139</v>
+        <v>46068.72017564815</v>
       </c>
     </row>
     <row r="828">
@@ -32726,10 +32726,10 @@
         </is>
       </c>
       <c r="H828" s="2" t="n">
-        <v>46065.7201756546</v>
+        <v>46065.72017565972</v>
       </c>
       <c r="I828" s="2" t="n">
-        <v>46070.7201756546</v>
+        <v>46070.72017565972</v>
       </c>
     </row>
     <row r="829">
@@ -32765,10 +32765,10 @@
         </is>
       </c>
       <c r="H829" s="2" t="n">
-        <v>46083.72017565771</v>
+        <v>46083.72017565972</v>
       </c>
       <c r="I829" s="2" t="n">
-        <v>46088.72017565771</v>
+        <v>46088.72017565972</v>
       </c>
     </row>
     <row r="830">
@@ -32804,10 +32804,10 @@
         </is>
       </c>
       <c r="H830" s="2" t="n">
-        <v>46084.72017566072</v>
+        <v>46084.72017565972</v>
       </c>
       <c r="I830" s="2" t="n">
-        <v>46089.72017566072</v>
+        <v>46089.72017565972</v>
       </c>
     </row>
     <row r="831">
@@ -32843,10 +32843,10 @@
         </is>
       </c>
       <c r="H831" s="2" t="n">
-        <v>46076.72017566382</v>
+        <v>46076.72017565972</v>
       </c>
       <c r="I831" s="2" t="n">
-        <v>46081.72017566382</v>
+        <v>46081.72017565972</v>
       </c>
     </row>
     <row r="832">
@@ -32882,10 +32882,10 @@
         </is>
       </c>
       <c r="H832" s="2" t="n">
-        <v>46088.72017566721</v>
+        <v>46088.7201756713</v>
       </c>
       <c r="I832" s="2" t="n">
-        <v>46093.72017566721</v>
+        <v>46093.7201756713</v>
       </c>
     </row>
     <row r="833">
@@ -32921,10 +32921,10 @@
         </is>
       </c>
       <c r="H833" s="2" t="n">
-        <v>46086.72017567028</v>
+        <v>46086.7201756713</v>
       </c>
       <c r="I833" s="2" t="n">
-        <v>46091.72017567028</v>
+        <v>46091.7201756713</v>
       </c>
     </row>
     <row r="834">
@@ -32960,10 +32960,10 @@
         </is>
       </c>
       <c r="H834" s="2" t="n">
-        <v>46079.72017567351</v>
+        <v>46079.7201756713</v>
       </c>
       <c r="I834" s="2" t="n">
-        <v>46084.72017567351</v>
+        <v>46084.7201756713</v>
       </c>
     </row>
     <row r="835">
@@ -32999,10 +32999,10 @@
         </is>
       </c>
       <c r="H835" s="2" t="n">
-        <v>46084.72017567686</v>
+        <v>46084.7201756713</v>
       </c>
       <c r="I835" s="2" t="n">
-        <v>46089.72017567686</v>
+        <v>46089.7201756713</v>
       </c>
     </row>
     <row r="836">
@@ -33038,10 +33038,10 @@
         </is>
       </c>
       <c r="H836" s="2" t="n">
-        <v>46081.72017567982</v>
+        <v>46081.72017568287</v>
       </c>
       <c r="I836" s="2" t="n">
-        <v>46086.72017567982</v>
+        <v>46086.72017568287</v>
       </c>
     </row>
     <row r="837">
@@ -33077,10 +33077,10 @@
         </is>
       </c>
       <c r="H837" s="2" t="n">
-        <v>46084.72017568293</v>
+        <v>46084.72017568287</v>
       </c>
       <c r="I837" s="2" t="n">
-        <v>46089.72017568293</v>
+        <v>46089.72017568287</v>
       </c>
     </row>
     <row r="838">
@@ -33116,10 +33116,10 @@
         </is>
       </c>
       <c r="H838" s="2" t="n">
-        <v>46075.72017568597</v>
+        <v>46075.72017568287</v>
       </c>
       <c r="I838" s="2" t="n">
-        <v>46080.72017568597</v>
+        <v>46080.72017568287</v>
       </c>
     </row>
     <row r="839">
@@ -33155,10 +33155,10 @@
         </is>
       </c>
       <c r="H839" s="2" t="n">
-        <v>46067.7201756896</v>
+        <v>46067.72017569444</v>
       </c>
       <c r="I839" s="2" t="n">
-        <v>46072.7201756896</v>
+        <v>46072.72017569444</v>
       </c>
     </row>
     <row r="840">
@@ -33194,10 +33194,10 @@
         </is>
       </c>
       <c r="H840" s="2" t="n">
-        <v>46068.72017569275</v>
+        <v>46068.72017569444</v>
       </c>
       <c r="I840" s="2" t="n">
-        <v>46073.72017569275</v>
+        <v>46073.72017569444</v>
       </c>
     </row>
     <row r="841">
@@ -33233,10 +33233,10 @@
         </is>
       </c>
       <c r="H841" s="2" t="n">
-        <v>46068.72017569585</v>
+        <v>46068.72017569444</v>
       </c>
       <c r="I841" s="2" t="n">
-        <v>46073.72017569585</v>
+        <v>46073.72017569444</v>
       </c>
     </row>
     <row r="842">
@@ -33272,10 +33272,10 @@
         </is>
       </c>
       <c r="H842" s="2" t="n">
-        <v>46084.720175699</v>
+        <v>46084.72017569444</v>
       </c>
       <c r="I842" s="2" t="n">
-        <v>46089.720175699</v>
+        <v>46089.72017569444</v>
       </c>
     </row>
     <row r="843">
@@ -33311,10 +33311,10 @@
         </is>
       </c>
       <c r="H843" s="2" t="n">
-        <v>46062.72017570234</v>
+        <v>46062.72017570602</v>
       </c>
       <c r="I843" s="2" t="n">
-        <v>46067.72017570234</v>
+        <v>46067.72017570602</v>
       </c>
     </row>
     <row r="844">
@@ -33350,10 +33350,10 @@
         </is>
       </c>
       <c r="H844" s="2" t="n">
-        <v>46066.72017570541</v>
+        <v>46066.72017570602</v>
       </c>
       <c r="I844" s="2" t="n">
-        <v>46071.72017570541</v>
+        <v>46071.72017570602</v>
       </c>
     </row>
     <row r="845">
@@ -33389,10 +33389,10 @@
         </is>
       </c>
       <c r="H845" s="2" t="n">
-        <v>46069.72017570846</v>
+        <v>46069.72017570602</v>
       </c>
       <c r="I845" s="2" t="n">
-        <v>46074.72017570846</v>
+        <v>46074.72017570602</v>
       </c>
     </row>
     <row r="846">
@@ -33428,10 +33428,10 @@
         </is>
       </c>
       <c r="H846" s="2" t="n">
-        <v>46081.72017571172</v>
+        <v>46081.72017570602</v>
       </c>
       <c r="I846" s="2" t="n">
-        <v>46086.72017571172</v>
+        <v>46086.72017570602</v>
       </c>
     </row>
     <row r="847">
@@ -33467,10 +33467,10 @@
         </is>
       </c>
       <c r="H847" s="2" t="n">
-        <v>46082.72017571703</v>
+        <v>46082.72017571759</v>
       </c>
       <c r="I847" s="2" t="n">
-        <v>46087.72017571703</v>
+        <v>46087.72017571759</v>
       </c>
     </row>
     <row r="848">
@@ -33506,10 +33506,10 @@
         </is>
       </c>
       <c r="H848" s="2" t="n">
-        <v>46068.72017572085</v>
+        <v>46068.72017571759</v>
       </c>
       <c r="I848" s="2" t="n">
-        <v>46073.72017572085</v>
+        <v>46073.72017571759</v>
       </c>
     </row>
     <row r="849">
@@ -33545,10 +33545,10 @@
         </is>
       </c>
       <c r="H849" s="2" t="n">
-        <v>46065.72017572461</v>
+        <v>46065.72017572917</v>
       </c>
       <c r="I849" s="2" t="n">
-        <v>46070.72017572461</v>
+        <v>46070.72017572917</v>
       </c>
     </row>
     <row r="850">
@@ -33584,10 +33584,10 @@
         </is>
       </c>
       <c r="H850" s="2" t="n">
-        <v>46084.72017572765</v>
+        <v>46084.72017572917</v>
       </c>
       <c r="I850" s="2" t="n">
-        <v>46089.72017572765</v>
+        <v>46089.72017572917</v>
       </c>
     </row>
     <row r="851">
@@ -33623,10 +33623,1960 @@
         </is>
       </c>
       <c r="H851" s="2" t="n">
-        <v>46074.7201757307</v>
+        <v>46074.72017572917</v>
       </c>
       <c r="I851" s="2" t="n">
-        <v>46079.7201757307</v>
+        <v>46079.72017572917</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>93668fa5-91f9-4fbd-945f-71f23ce3b2ca</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>8738.469999999999</v>
+      </c>
+      <c r="D852" t="n">
+        <v>95.11</v>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="n">
+        <v>46072.76571767292</v>
+      </c>
+      <c r="I852" s="2" t="n">
+        <v>46077.76571767292</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>4d8b9348-02ef-4ca3-b880-fd5c9170d4b1</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>7378.37</v>
+      </c>
+      <c r="D853" t="n">
+        <v>88.66</v>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="n">
+        <v>46085.76571767736</v>
+      </c>
+      <c r="I853" s="2" t="n">
+        <v>46090.76571767736</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>8c51aa49-b13d-4c72-8707-9d7877b32082</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>7339.35</v>
+      </c>
+      <c r="D854" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H854" s="2" t="n">
+        <v>46074.76571768057</v>
+      </c>
+      <c r="I854" s="2" t="n">
+        <v>46079.76571768057</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>22e49c19-5e98-4b93-985c-aaac85522b33</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>8002.37</v>
+      </c>
+      <c r="D855" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="n">
+        <v>46086.76571768389</v>
+      </c>
+      <c r="I855" s="2" t="n">
+        <v>46091.76571768389</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>bb47010d-05d2-41f9-96f0-bb1398fcd8a6</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>9856.540000000001</v>
+      </c>
+      <c r="D856" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="n">
+        <v>46080.76571768698</v>
+      </c>
+      <c r="I856" s="2" t="n">
+        <v>46085.76571768698</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>bac3db48-92c3-4b37-8bdf-18c85c77f64d</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>7949.67</v>
+      </c>
+      <c r="D857" t="n">
+        <v>87.37</v>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="n">
+        <v>46062.76571769036</v>
+      </c>
+      <c r="I857" s="2" t="n">
+        <v>46067.76571769036</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>70e4f9f8-888d-4677-a074-e4ec5cbd24de</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>5453.1</v>
+      </c>
+      <c r="D858" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="n">
+        <v>46081.76571769344</v>
+      </c>
+      <c r="I858" s="2" t="n">
+        <v>46086.76571769344</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2f9f8ba5-ea34-44f1-bf03-9f9610a4a3a3</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>9171.23</v>
+      </c>
+      <c r="D859" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="n">
+        <v>46062.76571769665</v>
+      </c>
+      <c r="I859" s="2" t="n">
+        <v>46067.76571769665</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>adf072be-aa9c-4b75-b361-a2deb1c68e3a</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>1849.07</v>
+      </c>
+      <c r="D860" t="n">
+        <v>85.31999999999999</v>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="n">
+        <v>46074.7657177001</v>
+      </c>
+      <c r="I860" s="2" t="n">
+        <v>46079.7657177001</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2822993d-b582-4212-9052-61dcba6a5fd7</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>4952.45</v>
+      </c>
+      <c r="D861" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="n">
+        <v>46065.76571770341</v>
+      </c>
+      <c r="I861" s="2" t="n">
+        <v>46070.76571770341</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>8d5c1327-c2bf-448f-9715-c6af231009a9</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>1449.15</v>
+      </c>
+      <c r="D862" t="n">
+        <v>86.76000000000001</v>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="n">
+        <v>46082.76571770653</v>
+      </c>
+      <c r="I862" s="2" t="n">
+        <v>46087.76571770653</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>4ee5deb4-c40a-4db2-9037-d166971fc2f5</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>9143.5</v>
+      </c>
+      <c r="D863" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="n">
+        <v>46063.76571770968</v>
+      </c>
+      <c r="I863" s="2" t="n">
+        <v>46068.76571770968</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>0e5b1f8e-4c02-43d8-87de-7ccf21a6fd01</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>6457.41</v>
+      </c>
+      <c r="D864" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="n">
+        <v>46059.76571771291</v>
+      </c>
+      <c r="I864" s="2" t="n">
+        <v>46064.76571771291</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>c8d8740b-92fd-4cc8-bf7c-fbc94e8b1aed</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>6267.14</v>
+      </c>
+      <c r="D865" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="n">
+        <v>46070.76571771603</v>
+      </c>
+      <c r="I865" s="2" t="n">
+        <v>46075.76571771603</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>1f76e152-f8dd-41e8-9cbe-b641309c7665</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>9791.1</v>
+      </c>
+      <c r="D866" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="n">
+        <v>46064.7657177192</v>
+      </c>
+      <c r="I866" s="2" t="n">
+        <v>46069.7657177192</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>d5ca044a-b92a-40ab-8be4-b5550db9ef3d</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>2550.13</v>
+      </c>
+      <c r="D867" t="n">
+        <v>94.73</v>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="n">
+        <v>46081.7657177223</v>
+      </c>
+      <c r="I867" s="2" t="n">
+        <v>46086.7657177223</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>d15ab7b6-a885-42ef-b999-58cf8bcd720f</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>5899.17</v>
+      </c>
+      <c r="D868" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="n">
+        <v>46076.76571772561</v>
+      </c>
+      <c r="I868" s="2" t="n">
+        <v>46081.76571772561</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>859bccbb-3738-499d-a559-c907174e29f2</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>3631.53</v>
+      </c>
+      <c r="D869" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="n">
+        <v>46071.76571772878</v>
+      </c>
+      <c r="I869" s="2" t="n">
+        <v>46076.76571772878</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>fa383ea1-aa85-4241-8259-e6c5ec39316f</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>1999.37</v>
+      </c>
+      <c r="D870" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="n">
+        <v>46088.76571773209</v>
+      </c>
+      <c r="I870" s="2" t="n">
+        <v>46093.76571773209</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>15f2fe6f-23b3-4aa7-8317-29a90be625ca</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>9636.530000000001</v>
+      </c>
+      <c r="D871" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="n">
+        <v>46076.76571773543</v>
+      </c>
+      <c r="I871" s="2" t="n">
+        <v>46081.76571773543</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>7d01bdb8-2b6f-4993-acd1-d2fe9c427d29</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>1384.79</v>
+      </c>
+      <c r="D872" t="n">
+        <v>94.72</v>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="n">
+        <v>46073.7657177385</v>
+      </c>
+      <c r="I872" s="2" t="n">
+        <v>46078.7657177385</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>3ce0ea1a-7bc7-4a29-8446-49643ce3befd</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>7567.16</v>
+      </c>
+      <c r="D873" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="n">
+        <v>46077.76571774167</v>
+      </c>
+      <c r="I873" s="2" t="n">
+        <v>46082.76571774167</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>9c640618-38e5-4498-a62b-476e6cc2baf4</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>9931.809999999999</v>
+      </c>
+      <c r="D874" t="n">
+        <v>90.20999999999999</v>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="n">
+        <v>46074.76571774475</v>
+      </c>
+      <c r="I874" s="2" t="n">
+        <v>46079.76571774475</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>1396f573-b493-4000-8639-0639db89579b</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>5869.78</v>
+      </c>
+      <c r="D875" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="n">
+        <v>46082.76571774812</v>
+      </c>
+      <c r="I875" s="2" t="n">
+        <v>46087.76571774812</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>dde0639a-19e2-4378-96a4-878adfb5231d</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>7284.51</v>
+      </c>
+      <c r="D876" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="n">
+        <v>46062.76571775116</v>
+      </c>
+      <c r="I876" s="2" t="n">
+        <v>46067.76571775116</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>8bfd4ec0-fa09-4d9f-bfc4-f1d35a9b754c</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>6098.96</v>
+      </c>
+      <c r="D877" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="n">
+        <v>46085.76571775427</v>
+      </c>
+      <c r="I877" s="2" t="n">
+        <v>46090.76571775427</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>28c2f6c1-244a-4737-95c3-cbdab592de14</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>9560.33</v>
+      </c>
+      <c r="D878" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="n">
+        <v>46087.76571775743</v>
+      </c>
+      <c r="I878" s="2" t="n">
+        <v>46092.76571775743</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>6efcc097-1e3e-4397-82bc-75515e7c1806</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>3308.57</v>
+      </c>
+      <c r="D879" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="n">
+        <v>46079.7657177607</v>
+      </c>
+      <c r="I879" s="2" t="n">
+        <v>46084.7657177607</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>f3e7d1ad-2cb8-448d-90af-3006b02cf41f</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>6359.02</v>
+      </c>
+      <c r="D880" t="n">
+        <v>94.77</v>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="n">
+        <v>46077.76571776376</v>
+      </c>
+      <c r="I880" s="2" t="n">
+        <v>46082.76571776376</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>b33a2863-e166-4891-b579-c2023352f1ee</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>9484.700000000001</v>
+      </c>
+      <c r="D881" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="n">
+        <v>46060.76571776681</v>
+      </c>
+      <c r="I881" s="2" t="n">
+        <v>46065.76571776681</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>191fe4b7-5573-4747-b498-4e2581d7e30c</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>8166.17</v>
+      </c>
+      <c r="D882" t="n">
+        <v>92.89</v>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="n">
+        <v>46075.76571777018</v>
+      </c>
+      <c r="I882" s="2" t="n">
+        <v>46080.76571777018</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2fdfeff1-05b7-4bbb-8824-96d8e84187a7</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>2176.08</v>
+      </c>
+      <c r="D883" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="n">
+        <v>46062.76571777336</v>
+      </c>
+      <c r="I883" s="2" t="n">
+        <v>46067.76571777336</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>068ae17a-d416-4013-b953-9e16fc556ee5</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>8534.98</v>
+      </c>
+      <c r="D884" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="n">
+        <v>46079.76571777655</v>
+      </c>
+      <c r="I884" s="2" t="n">
+        <v>46084.76571777655</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>bfa5aa0e-1a5d-4bc6-82e0-ce9bbdf6061e</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>7013.74</v>
+      </c>
+      <c r="D885" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="n">
+        <v>46069.76571778015</v>
+      </c>
+      <c r="I885" s="2" t="n">
+        <v>46074.76571778015</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2beed69d-35c1-4546-a31f-4229ddecc147</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>9503.67</v>
+      </c>
+      <c r="D886" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="n">
+        <v>46075.76571778338</v>
+      </c>
+      <c r="I886" s="2" t="n">
+        <v>46080.76571778338</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>aa6a2c46-ed3a-4048-a634-311b21bf6e9e</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>4972.4</v>
+      </c>
+      <c r="D887" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="n">
+        <v>46085.7657177864</v>
+      </c>
+      <c r="I887" s="2" t="n">
+        <v>46090.7657177864</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>6d72c8f9-867a-4322-8ef0-68fe741a411c</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>6508.66</v>
+      </c>
+      <c r="D888" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="n">
+        <v>46081.76571778941</v>
+      </c>
+      <c r="I888" s="2" t="n">
+        <v>46086.76571778941</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>8c87d06b-52c1-463d-9147-99e2638a174c</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>5058.64</v>
+      </c>
+      <c r="D889" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="n">
+        <v>46084.76571779263</v>
+      </c>
+      <c r="I889" s="2" t="n">
+        <v>46089.76571779263</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>c8e6f612-589f-4d79-897e-c57d4d81506c</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>7969.99</v>
+      </c>
+      <c r="D890" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="n">
+        <v>46072.76571779569</v>
+      </c>
+      <c r="I890" s="2" t="n">
+        <v>46077.76571779569</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>c7cd60f3-2608-4c7a-bf34-0245032684a9</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>8658.690000000001</v>
+      </c>
+      <c r="D891" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="n">
+        <v>46087.76571779873</v>
+      </c>
+      <c r="I891" s="2" t="n">
+        <v>46092.76571779873</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>c01171f0-ce05-4ae4-88db-2392f58aecac</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>3956.66</v>
+      </c>
+      <c r="D892" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="n">
+        <v>46064.76571780185</v>
+      </c>
+      <c r="I892" s="2" t="n">
+        <v>46069.76571780185</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>b6d8c20c-91c8-4b1f-afaa-83e5ddb8900f</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>7097.11</v>
+      </c>
+      <c r="D893" t="n">
+        <v>85.31999999999999</v>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="n">
+        <v>46075.7657178052</v>
+      </c>
+      <c r="I893" s="2" t="n">
+        <v>46080.7657178052</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>80dcd774-783e-4909-b51f-571d70f7b635</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>1848.39</v>
+      </c>
+      <c r="D894" t="n">
+        <v>96.45999999999999</v>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="n">
+        <v>46076.76571780822</v>
+      </c>
+      <c r="I894" s="2" t="n">
+        <v>46081.76571780822</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>42792fb1-b396-404e-95a9-db12a2e833f6</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>2924.76</v>
+      </c>
+      <c r="D895" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="n">
+        <v>46063.76571781141</v>
+      </c>
+      <c r="I895" s="2" t="n">
+        <v>46068.76571781141</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>5e355f22-61bc-4fca-a051-894897e522fd</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>6483.18</v>
+      </c>
+      <c r="D896" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="n">
+        <v>46073.7657178146</v>
+      </c>
+      <c r="I896" s="2" t="n">
+        <v>46078.7657178146</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>aed45ccf-bfdb-42db-9d6b-0a21456cfd21</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>4909.64</v>
+      </c>
+      <c r="D897" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="n">
+        <v>46067.76571781791</v>
+      </c>
+      <c r="I897" s="2" t="n">
+        <v>46072.76571781791</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>c485f3c2-4b42-4bfa-98ed-a7d9e16f8e75</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>4930</v>
+      </c>
+      <c r="D898" t="n">
+        <v>85.17</v>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="n">
+        <v>46064.76571782095</v>
+      </c>
+      <c r="I898" s="2" t="n">
+        <v>46069.76571782095</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>e0fef902-3f0a-4795-a65b-90575ccd6f3c</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>6930.28</v>
+      </c>
+      <c r="D899" t="n">
+        <v>85.17</v>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="n">
+        <v>46062.76571782405</v>
+      </c>
+      <c r="I899" s="2" t="n">
+        <v>46067.76571782405</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>40b123b9-bfba-47d6-a6b0-cf70b4c9e259</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>5644.32</v>
+      </c>
+      <c r="D900" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="n">
+        <v>46080.76571782719</v>
+      </c>
+      <c r="I900" s="2" t="n">
+        <v>46085.76571782719</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>ad841e60-97c5-40a6-8bc3-d950b61f54f6</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>7679.85</v>
+      </c>
+      <c r="D901" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="n">
+        <v>46085.76571783039</v>
+      </c>
+      <c r="I901" s="2" t="n">
+        <v>46090.76571783039</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I901"/>
+  <dimension ref="A1:I951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33662,10 +33662,10 @@
         </is>
       </c>
       <c r="H852" s="2" t="n">
-        <v>46072.76571767292</v>
+        <v>46072.76571767361</v>
       </c>
       <c r="I852" s="2" t="n">
-        <v>46077.76571767292</v>
+        <v>46077.76571767361</v>
       </c>
     </row>
     <row r="853">
@@ -33701,10 +33701,10 @@
         </is>
       </c>
       <c r="H853" s="2" t="n">
-        <v>46085.76571767736</v>
+        <v>46085.76571767361</v>
       </c>
       <c r="I853" s="2" t="n">
-        <v>46090.76571767736</v>
+        <v>46090.76571767361</v>
       </c>
     </row>
     <row r="854">
@@ -33740,10 +33740,10 @@
         </is>
       </c>
       <c r="H854" s="2" t="n">
-        <v>46074.76571768057</v>
+        <v>46074.76571768519</v>
       </c>
       <c r="I854" s="2" t="n">
-        <v>46079.76571768057</v>
+        <v>46079.76571768519</v>
       </c>
     </row>
     <row r="855">
@@ -33779,10 +33779,10 @@
         </is>
       </c>
       <c r="H855" s="2" t="n">
-        <v>46086.76571768389</v>
+        <v>46086.76571768519</v>
       </c>
       <c r="I855" s="2" t="n">
-        <v>46091.76571768389</v>
+        <v>46091.76571768519</v>
       </c>
     </row>
     <row r="856">
@@ -33818,10 +33818,10 @@
         </is>
       </c>
       <c r="H856" s="2" t="n">
-        <v>46080.76571768698</v>
+        <v>46080.76571768519</v>
       </c>
       <c r="I856" s="2" t="n">
-        <v>46085.76571768698</v>
+        <v>46085.76571768519</v>
       </c>
     </row>
     <row r="857">
@@ -33857,10 +33857,10 @@
         </is>
       </c>
       <c r="H857" s="2" t="n">
-        <v>46062.76571769036</v>
+        <v>46062.76571768519</v>
       </c>
       <c r="I857" s="2" t="n">
-        <v>46067.76571769036</v>
+        <v>46067.76571768519</v>
       </c>
     </row>
     <row r="858">
@@ -33896,10 +33896,10 @@
         </is>
       </c>
       <c r="H858" s="2" t="n">
-        <v>46081.76571769344</v>
+        <v>46081.76571769676</v>
       </c>
       <c r="I858" s="2" t="n">
-        <v>46086.76571769344</v>
+        <v>46086.76571769676</v>
       </c>
     </row>
     <row r="859">
@@ -33935,10 +33935,10 @@
         </is>
       </c>
       <c r="H859" s="2" t="n">
-        <v>46062.76571769665</v>
+        <v>46062.76571769676</v>
       </c>
       <c r="I859" s="2" t="n">
-        <v>46067.76571769665</v>
+        <v>46067.76571769676</v>
       </c>
     </row>
     <row r="860">
@@ -33974,10 +33974,10 @@
         </is>
       </c>
       <c r="H860" s="2" t="n">
-        <v>46074.7657177001</v>
+        <v>46074.76571769676</v>
       </c>
       <c r="I860" s="2" t="n">
-        <v>46079.7657177001</v>
+        <v>46079.76571769676</v>
       </c>
     </row>
     <row r="861">
@@ -34013,10 +34013,10 @@
         </is>
       </c>
       <c r="H861" s="2" t="n">
-        <v>46065.76571770341</v>
+        <v>46065.76571770833</v>
       </c>
       <c r="I861" s="2" t="n">
-        <v>46070.76571770341</v>
+        <v>46070.76571770833</v>
       </c>
     </row>
     <row r="862">
@@ -34052,10 +34052,10 @@
         </is>
       </c>
       <c r="H862" s="2" t="n">
-        <v>46082.76571770653</v>
+        <v>46082.76571770833</v>
       </c>
       <c r="I862" s="2" t="n">
-        <v>46087.76571770653</v>
+        <v>46087.76571770833</v>
       </c>
     </row>
     <row r="863">
@@ -34091,10 +34091,10 @@
         </is>
       </c>
       <c r="H863" s="2" t="n">
-        <v>46063.76571770968</v>
+        <v>46063.76571770833</v>
       </c>
       <c r="I863" s="2" t="n">
-        <v>46068.76571770968</v>
+        <v>46068.76571770833</v>
       </c>
     </row>
     <row r="864">
@@ -34130,10 +34130,10 @@
         </is>
       </c>
       <c r="H864" s="2" t="n">
-        <v>46059.76571771291</v>
+        <v>46059.76571770833</v>
       </c>
       <c r="I864" s="2" t="n">
-        <v>46064.76571771291</v>
+        <v>46064.76571770833</v>
       </c>
     </row>
     <row r="865">
@@ -34169,10 +34169,10 @@
         </is>
       </c>
       <c r="H865" s="2" t="n">
-        <v>46070.76571771603</v>
+        <v>46070.76571771991</v>
       </c>
       <c r="I865" s="2" t="n">
-        <v>46075.76571771603</v>
+        <v>46075.76571771991</v>
       </c>
     </row>
     <row r="866">
@@ -34208,10 +34208,10 @@
         </is>
       </c>
       <c r="H866" s="2" t="n">
-        <v>46064.7657177192</v>
+        <v>46064.76571771991</v>
       </c>
       <c r="I866" s="2" t="n">
-        <v>46069.7657177192</v>
+        <v>46069.76571771991</v>
       </c>
     </row>
     <row r="867">
@@ -34247,10 +34247,10 @@
         </is>
       </c>
       <c r="H867" s="2" t="n">
-        <v>46081.7657177223</v>
+        <v>46081.76571771991</v>
       </c>
       <c r="I867" s="2" t="n">
-        <v>46086.7657177223</v>
+        <v>46086.76571771991</v>
       </c>
     </row>
     <row r="868">
@@ -34286,10 +34286,10 @@
         </is>
       </c>
       <c r="H868" s="2" t="n">
-        <v>46076.76571772561</v>
+        <v>46076.76571771991</v>
       </c>
       <c r="I868" s="2" t="n">
-        <v>46081.76571772561</v>
+        <v>46081.76571771991</v>
       </c>
     </row>
     <row r="869">
@@ -34325,10 +34325,10 @@
         </is>
       </c>
       <c r="H869" s="2" t="n">
-        <v>46071.76571772878</v>
+        <v>46071.76571773148</v>
       </c>
       <c r="I869" s="2" t="n">
-        <v>46076.76571772878</v>
+        <v>46076.76571773148</v>
       </c>
     </row>
     <row r="870">
@@ -34364,10 +34364,10 @@
         </is>
       </c>
       <c r="H870" s="2" t="n">
-        <v>46088.76571773209</v>
+        <v>46088.76571773148</v>
       </c>
       <c r="I870" s="2" t="n">
-        <v>46093.76571773209</v>
+        <v>46093.76571773148</v>
       </c>
     </row>
     <row r="871">
@@ -34403,10 +34403,10 @@
         </is>
       </c>
       <c r="H871" s="2" t="n">
-        <v>46076.76571773543</v>
+        <v>46076.76571773148</v>
       </c>
       <c r="I871" s="2" t="n">
-        <v>46081.76571773543</v>
+        <v>46081.76571773148</v>
       </c>
     </row>
     <row r="872">
@@ -34442,10 +34442,10 @@
         </is>
       </c>
       <c r="H872" s="2" t="n">
-        <v>46073.7657177385</v>
+        <v>46073.76571774305</v>
       </c>
       <c r="I872" s="2" t="n">
-        <v>46078.7657177385</v>
+        <v>46078.76571774305</v>
       </c>
     </row>
     <row r="873">
@@ -34481,10 +34481,10 @@
         </is>
       </c>
       <c r="H873" s="2" t="n">
-        <v>46077.76571774167</v>
+        <v>46077.76571774305</v>
       </c>
       <c r="I873" s="2" t="n">
-        <v>46082.76571774167</v>
+        <v>46082.76571774305</v>
       </c>
     </row>
     <row r="874">
@@ -34520,10 +34520,10 @@
         </is>
       </c>
       <c r="H874" s="2" t="n">
-        <v>46074.76571774475</v>
+        <v>46074.76571774305</v>
       </c>
       <c r="I874" s="2" t="n">
-        <v>46079.76571774475</v>
+        <v>46079.76571774305</v>
       </c>
     </row>
     <row r="875">
@@ -34559,10 +34559,10 @@
         </is>
       </c>
       <c r="H875" s="2" t="n">
-        <v>46082.76571774812</v>
+        <v>46082.76571774305</v>
       </c>
       <c r="I875" s="2" t="n">
-        <v>46087.76571774812</v>
+        <v>46087.76571774305</v>
       </c>
     </row>
     <row r="876">
@@ -34598,10 +34598,10 @@
         </is>
       </c>
       <c r="H876" s="2" t="n">
-        <v>46062.76571775116</v>
+        <v>46062.76571775463</v>
       </c>
       <c r="I876" s="2" t="n">
-        <v>46067.76571775116</v>
+        <v>46067.76571775463</v>
       </c>
     </row>
     <row r="877">
@@ -34637,10 +34637,10 @@
         </is>
       </c>
       <c r="H877" s="2" t="n">
-        <v>46085.76571775427</v>
+        <v>46085.76571775463</v>
       </c>
       <c r="I877" s="2" t="n">
-        <v>46090.76571775427</v>
+        <v>46090.76571775463</v>
       </c>
     </row>
     <row r="878">
@@ -34676,10 +34676,10 @@
         </is>
       </c>
       <c r="H878" s="2" t="n">
-        <v>46087.76571775743</v>
+        <v>46087.76571775463</v>
       </c>
       <c r="I878" s="2" t="n">
-        <v>46092.76571775743</v>
+        <v>46092.76571775463</v>
       </c>
     </row>
     <row r="879">
@@ -34715,10 +34715,10 @@
         </is>
       </c>
       <c r="H879" s="2" t="n">
-        <v>46079.7657177607</v>
+        <v>46079.7657177662</v>
       </c>
       <c r="I879" s="2" t="n">
-        <v>46084.7657177607</v>
+        <v>46084.7657177662</v>
       </c>
     </row>
     <row r="880">
@@ -34754,10 +34754,10 @@
         </is>
       </c>
       <c r="H880" s="2" t="n">
-        <v>46077.76571776376</v>
+        <v>46077.7657177662</v>
       </c>
       <c r="I880" s="2" t="n">
-        <v>46082.76571776376</v>
+        <v>46082.7657177662</v>
       </c>
     </row>
     <row r="881">
@@ -34793,10 +34793,10 @@
         </is>
       </c>
       <c r="H881" s="2" t="n">
-        <v>46060.76571776681</v>
+        <v>46060.7657177662</v>
       </c>
       <c r="I881" s="2" t="n">
-        <v>46065.76571776681</v>
+        <v>46065.7657177662</v>
       </c>
     </row>
     <row r="882">
@@ -34832,10 +34832,10 @@
         </is>
       </c>
       <c r="H882" s="2" t="n">
-        <v>46075.76571777018</v>
+        <v>46075.7657177662</v>
       </c>
       <c r="I882" s="2" t="n">
-        <v>46080.76571777018</v>
+        <v>46080.7657177662</v>
       </c>
     </row>
     <row r="883">
@@ -34871,10 +34871,10 @@
         </is>
       </c>
       <c r="H883" s="2" t="n">
-        <v>46062.76571777336</v>
+        <v>46062.76571777778</v>
       </c>
       <c r="I883" s="2" t="n">
-        <v>46067.76571777336</v>
+        <v>46067.76571777778</v>
       </c>
     </row>
     <row r="884">
@@ -34910,10 +34910,10 @@
         </is>
       </c>
       <c r="H884" s="2" t="n">
-        <v>46079.76571777655</v>
+        <v>46079.76571777778</v>
       </c>
       <c r="I884" s="2" t="n">
-        <v>46084.76571777655</v>
+        <v>46084.76571777778</v>
       </c>
     </row>
     <row r="885">
@@ -34949,10 +34949,10 @@
         </is>
       </c>
       <c r="H885" s="2" t="n">
-        <v>46069.76571778015</v>
+        <v>46069.76571777778</v>
       </c>
       <c r="I885" s="2" t="n">
-        <v>46074.76571778015</v>
+        <v>46074.76571777778</v>
       </c>
     </row>
     <row r="886">
@@ -34988,10 +34988,10 @@
         </is>
       </c>
       <c r="H886" s="2" t="n">
-        <v>46075.76571778338</v>
+        <v>46075.76571777778</v>
       </c>
       <c r="I886" s="2" t="n">
-        <v>46080.76571778338</v>
+        <v>46080.76571777778</v>
       </c>
     </row>
     <row r="887">
@@ -35027,10 +35027,10 @@
         </is>
       </c>
       <c r="H887" s="2" t="n">
-        <v>46085.7657177864</v>
+        <v>46085.76571778935</v>
       </c>
       <c r="I887" s="2" t="n">
-        <v>46090.7657177864</v>
+        <v>46090.76571778935</v>
       </c>
     </row>
     <row r="888">
@@ -35066,10 +35066,10 @@
         </is>
       </c>
       <c r="H888" s="2" t="n">
-        <v>46081.76571778941</v>
+        <v>46081.76571778935</v>
       </c>
       <c r="I888" s="2" t="n">
-        <v>46086.76571778941</v>
+        <v>46086.76571778935</v>
       </c>
     </row>
     <row r="889">
@@ -35105,10 +35105,10 @@
         </is>
       </c>
       <c r="H889" s="2" t="n">
-        <v>46084.76571779263</v>
+        <v>46084.76571778935</v>
       </c>
       <c r="I889" s="2" t="n">
-        <v>46089.76571779263</v>
+        <v>46089.76571778935</v>
       </c>
     </row>
     <row r="890">
@@ -35144,10 +35144,10 @@
         </is>
       </c>
       <c r="H890" s="2" t="n">
-        <v>46072.76571779569</v>
+        <v>46072.76571780092</v>
       </c>
       <c r="I890" s="2" t="n">
-        <v>46077.76571779569</v>
+        <v>46077.76571780092</v>
       </c>
     </row>
     <row r="891">
@@ -35183,10 +35183,10 @@
         </is>
       </c>
       <c r="H891" s="2" t="n">
-        <v>46087.76571779873</v>
+        <v>46087.76571780092</v>
       </c>
       <c r="I891" s="2" t="n">
-        <v>46092.76571779873</v>
+        <v>46092.76571780092</v>
       </c>
     </row>
     <row r="892">
@@ -35222,10 +35222,10 @@
         </is>
       </c>
       <c r="H892" s="2" t="n">
-        <v>46064.76571780185</v>
+        <v>46064.76571780092</v>
       </c>
       <c r="I892" s="2" t="n">
-        <v>46069.76571780185</v>
+        <v>46069.76571780092</v>
       </c>
     </row>
     <row r="893">
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="H893" s="2" t="n">
-        <v>46075.7657178052</v>
+        <v>46075.76571780092</v>
       </c>
       <c r="I893" s="2" t="n">
-        <v>46080.7657178052</v>
+        <v>46080.76571780092</v>
       </c>
     </row>
     <row r="894">
@@ -35300,10 +35300,10 @@
         </is>
       </c>
       <c r="H894" s="2" t="n">
-        <v>46076.76571780822</v>
+        <v>46076.7657178125</v>
       </c>
       <c r="I894" s="2" t="n">
-        <v>46081.76571780822</v>
+        <v>46081.7657178125</v>
       </c>
     </row>
     <row r="895">
@@ -35339,10 +35339,10 @@
         </is>
       </c>
       <c r="H895" s="2" t="n">
-        <v>46063.76571781141</v>
+        <v>46063.7657178125</v>
       </c>
       <c r="I895" s="2" t="n">
-        <v>46068.76571781141</v>
+        <v>46068.7657178125</v>
       </c>
     </row>
     <row r="896">
@@ -35378,10 +35378,10 @@
         </is>
       </c>
       <c r="H896" s="2" t="n">
-        <v>46073.7657178146</v>
+        <v>46073.7657178125</v>
       </c>
       <c r="I896" s="2" t="n">
-        <v>46078.7657178146</v>
+        <v>46078.7657178125</v>
       </c>
     </row>
     <row r="897">
@@ -35417,10 +35417,10 @@
         </is>
       </c>
       <c r="H897" s="2" t="n">
-        <v>46067.76571781791</v>
+        <v>46067.7657178125</v>
       </c>
       <c r="I897" s="2" t="n">
-        <v>46072.76571781791</v>
+        <v>46072.7657178125</v>
       </c>
     </row>
     <row r="898">
@@ -35456,10 +35456,10 @@
         </is>
       </c>
       <c r="H898" s="2" t="n">
-        <v>46064.76571782095</v>
+        <v>46064.76571782408</v>
       </c>
       <c r="I898" s="2" t="n">
-        <v>46069.76571782095</v>
+        <v>46069.76571782408</v>
       </c>
     </row>
     <row r="899">
@@ -35495,10 +35495,10 @@
         </is>
       </c>
       <c r="H899" s="2" t="n">
-        <v>46062.76571782405</v>
+        <v>46062.76571782408</v>
       </c>
       <c r="I899" s="2" t="n">
-        <v>46067.76571782405</v>
+        <v>46067.76571782408</v>
       </c>
     </row>
     <row r="900">
@@ -35534,10 +35534,10 @@
         </is>
       </c>
       <c r="H900" s="2" t="n">
-        <v>46080.76571782719</v>
+        <v>46080.76571782408</v>
       </c>
       <c r="I900" s="2" t="n">
-        <v>46085.76571782719</v>
+        <v>46085.76571782408</v>
       </c>
     </row>
     <row r="901">
@@ -35573,10 +35573,1960 @@
         </is>
       </c>
       <c r="H901" s="2" t="n">
-        <v>46085.76571783039</v>
+        <v>46085.76571783565</v>
       </c>
       <c r="I901" s="2" t="n">
-        <v>46090.76571783039</v>
+        <v>46090.76571783565</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>faee317d-6923-4612-8d8a-988b09c13bef</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>8159.75</v>
+      </c>
+      <c r="D902" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="n">
+        <v>46086.80440636374</v>
+      </c>
+      <c r="I902" s="2" t="n">
+        <v>46091.80440636374</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>66a1fa9b-36e4-4c86-9863-e5ee6997ca94</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>2680.03</v>
+      </c>
+      <c r="D903" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="n">
+        <v>46074.80440636795</v>
+      </c>
+      <c r="I903" s="2" t="n">
+        <v>46079.80440636795</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>f36f0b64-f83e-4f26-95d6-b2fedc4e3b6c</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>9810.09</v>
+      </c>
+      <c r="D904" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="n">
+        <v>46059.80440637137</v>
+      </c>
+      <c r="I904" s="2" t="n">
+        <v>46064.80440637137</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>b8c15e58-e7ec-49af-a166-4cea197fd8b6</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>4816.69</v>
+      </c>
+      <c r="D905" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="n">
+        <v>46064.8044063749</v>
+      </c>
+      <c r="I905" s="2" t="n">
+        <v>46069.8044063749</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>7652c18e-722d-4640-8301-6948d24fb23d</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>7541.59</v>
+      </c>
+      <c r="D906" t="n">
+        <v>97.87</v>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="n">
+        <v>46081.80440637823</v>
+      </c>
+      <c r="I906" s="2" t="n">
+        <v>46086.80440637823</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>79ca0b75-f950-4059-9c37-eb170fc83240</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>5873.96</v>
+      </c>
+      <c r="D907" t="n">
+        <v>90.58</v>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="n">
+        <v>46060.8044063816</v>
+      </c>
+      <c r="I907" s="2" t="n">
+        <v>46065.8044063816</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>96547d68-e41b-47d2-9756-7d0769b43924</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>2460.84</v>
+      </c>
+      <c r="D908" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="n">
+        <v>46063.80440638468</v>
+      </c>
+      <c r="I908" s="2" t="n">
+        <v>46068.80440638468</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>a53df51c-a547-4ebe-9807-1555247cc5f1</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>5439.06</v>
+      </c>
+      <c r="D909" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="n">
+        <v>46088.80440638823</v>
+      </c>
+      <c r="I909" s="2" t="n">
+        <v>46093.80440638823</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>3c8fb256-6a9d-49ea-8646-32ce0d81e579</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>4939.29</v>
+      </c>
+      <c r="D910" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="n">
+        <v>46075.80440639157</v>
+      </c>
+      <c r="I910" s="2" t="n">
+        <v>46080.80440639157</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>22df145d-4831-4d54-88a5-e8b583c14286</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>3162.41</v>
+      </c>
+      <c r="D911" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="n">
+        <v>46083.80440639487</v>
+      </c>
+      <c r="I911" s="2" t="n">
+        <v>46088.80440639487</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>902bcfe6-d7f2-4e96-9655-4cc9010bcb4f</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>2114.32</v>
+      </c>
+      <c r="D912" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="n">
+        <v>46085.80440639866</v>
+      </c>
+      <c r="I912" s="2" t="n">
+        <v>46090.80440639866</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>8c871962-2965-4819-9753-2ba6ff553a98</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>4137.55</v>
+      </c>
+      <c r="D913" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="n">
+        <v>46069.80440640193</v>
+      </c>
+      <c r="I913" s="2" t="n">
+        <v>46074.80440640193</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>227c6139-b6a5-437f-ad06-7f41241e2965</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>8530.57</v>
+      </c>
+      <c r="D914" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H914" s="2" t="n">
+        <v>46072.80440640528</v>
+      </c>
+      <c r="I914" s="2" t="n">
+        <v>46077.80440640528</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>a114eb37-6b79-4a3d-9482-37b9402bd77e</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>7626.21</v>
+      </c>
+      <c r="D915" t="n">
+        <v>99.88</v>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="n">
+        <v>46064.80440640861</v>
+      </c>
+      <c r="I915" s="2" t="n">
+        <v>46069.80440640861</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>c9da8397-2620-4d0b-b0b1-74e91520491c</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>2308.97</v>
+      </c>
+      <c r="D916" t="n">
+        <v>85.22</v>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H916" s="2" t="n">
+        <v>46060.80440641173</v>
+      </c>
+      <c r="I916" s="2" t="n">
+        <v>46065.80440641173</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>327fe8d7-1088-40e5-8cdb-c3d45b511ec7</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>5062.5</v>
+      </c>
+      <c r="D917" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="n">
+        <v>46087.80440641504</v>
+      </c>
+      <c r="I917" s="2" t="n">
+        <v>46092.80440641504</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>b8d6314f-b5bc-4647-8d3d-86fbdf91f497</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>3597.97</v>
+      </c>
+      <c r="D918" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H918" s="2" t="n">
+        <v>46085.8044064183</v>
+      </c>
+      <c r="I918" s="2" t="n">
+        <v>46090.8044064183</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>784b7953-0cb8-4573-b0dc-f0092bfb94b7</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>2200.53</v>
+      </c>
+      <c r="D919" t="n">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="n">
+        <v>46066.80440642161</v>
+      </c>
+      <c r="I919" s="2" t="n">
+        <v>46071.80440642161</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>205343d9-57cb-43b7-b9d3-bb5bba7f02d3</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>2827.14</v>
+      </c>
+      <c r="D920" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="n">
+        <v>46075.80440642474</v>
+      </c>
+      <c r="I920" s="2" t="n">
+        <v>46080.80440642474</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>cf32270a-6acc-4a50-8afc-9a8bbaaf5776</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>8147.08</v>
+      </c>
+      <c r="D921" t="n">
+        <v>86.33</v>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="n">
+        <v>46072.80440642796</v>
+      </c>
+      <c r="I921" s="2" t="n">
+        <v>46077.80440642796</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>278420f9-a71d-4ff9-bf8e-36c42d011f66</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>5530.47</v>
+      </c>
+      <c r="D922" t="n">
+        <v>85.76000000000001</v>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="n">
+        <v>46070.80440643107</v>
+      </c>
+      <c r="I922" s="2" t="n">
+        <v>46075.80440643107</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>1996a631-8c6c-47a2-bf95-71a3790c1ba9</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>7704.52</v>
+      </c>
+      <c r="D923" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H923" s="2" t="n">
+        <v>46066.80440643505</v>
+      </c>
+      <c r="I923" s="2" t="n">
+        <v>46071.80440643505</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>79ae80d8-a741-408a-b426-1045dd5f901f</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>3996.1</v>
+      </c>
+      <c r="D924" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H924" s="2" t="n">
+        <v>46065.80440643826</v>
+      </c>
+      <c r="I924" s="2" t="n">
+        <v>46070.80440643826</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>cc6cb5f9-497e-4ae2-8243-025efb78c913</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>6261.8</v>
+      </c>
+      <c r="D925" t="n">
+        <v>96.51000000000001</v>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="n">
+        <v>46059.80440644147</v>
+      </c>
+      <c r="I925" s="2" t="n">
+        <v>46064.80440644147</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>a244c00d-80aa-4979-a99e-de973e1f385d</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>5435.8</v>
+      </c>
+      <c r="D926" t="n">
+        <v>88.54000000000001</v>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H926" s="2" t="n">
+        <v>46088.80440644494</v>
+      </c>
+      <c r="I926" s="2" t="n">
+        <v>46093.80440644494</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>6404c7eb-8486-484f-9cd3-f6c05f20ab1e</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>5167.64</v>
+      </c>
+      <c r="D927" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H927" s="2" t="n">
+        <v>46069.80440644809</v>
+      </c>
+      <c r="I927" s="2" t="n">
+        <v>46074.80440644809</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>c101efbf-9d21-440d-acee-14718f324e41</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>7000.05</v>
+      </c>
+      <c r="D928" t="n">
+        <v>97.28</v>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H928" s="2" t="n">
+        <v>46067.80440645119</v>
+      </c>
+      <c r="I928" s="2" t="n">
+        <v>46072.80440645119</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>d813f0b1-a2bc-4704-a01a-dcfac48ecdc8</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>1811.24</v>
+      </c>
+      <c r="D929" t="n">
+        <v>89.88</v>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H929" s="2" t="n">
+        <v>46076.80440645434</v>
+      </c>
+      <c r="I929" s="2" t="n">
+        <v>46081.80440645434</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>4b5dcbfe-17f1-4847-bcf4-683026e1371d</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>4442.21</v>
+      </c>
+      <c r="D930" t="n">
+        <v>95.01000000000001</v>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H930" s="2" t="n">
+        <v>46081.80440645762</v>
+      </c>
+      <c r="I930" s="2" t="n">
+        <v>46086.80440645762</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>9272b8f7-149d-47b4-b746-9551e91eca22</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>2122.87</v>
+      </c>
+      <c r="D931" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H931" s="2" t="n">
+        <v>46087.80440646079</v>
+      </c>
+      <c r="I931" s="2" t="n">
+        <v>46092.80440646079</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>122ed255-e344-4d28-bfc5-f984cdd5896d</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>5018</v>
+      </c>
+      <c r="D932" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H932" s="2" t="n">
+        <v>46068.80440646412</v>
+      </c>
+      <c r="I932" s="2" t="n">
+        <v>46073.80440646412</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>4fe6469b-0aed-486c-a504-ad08459d70a6</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>6322.54</v>
+      </c>
+      <c r="D933" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H933" s="2" t="n">
+        <v>46079.80440646742</v>
+      </c>
+      <c r="I933" s="2" t="n">
+        <v>46084.80440646742</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>fee0bceb-82a6-4201-94e4-42d1aa3dc818</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>7068.05</v>
+      </c>
+      <c r="D934" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H934" s="2" t="n">
+        <v>46088.80440647055</v>
+      </c>
+      <c r="I934" s="2" t="n">
+        <v>46093.80440647055</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>6768216a-3cea-4658-9583-8910e44fd9d8</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>8485.34</v>
+      </c>
+      <c r="D935" t="n">
+        <v>94.89</v>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H935" s="2" t="n">
+        <v>46062.80440647375</v>
+      </c>
+      <c r="I935" s="2" t="n">
+        <v>46067.80440647375</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>e976e11c-07e0-468a-bfe0-393a35101eb6</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>4363.12</v>
+      </c>
+      <c r="D936" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H936" s="2" t="n">
+        <v>46083.80440647683</v>
+      </c>
+      <c r="I936" s="2" t="n">
+        <v>46088.80440647683</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>823c63ea-d079-4cc1-b547-51c3bc93dcac</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>7945.87</v>
+      </c>
+      <c r="D937" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H937" s="2" t="n">
+        <v>46077.80440648029</v>
+      </c>
+      <c r="I937" s="2" t="n">
+        <v>46082.80440648029</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>26083769-e9c1-45a4-9c19-a02cec237d0a</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>4074.83</v>
+      </c>
+      <c r="D938" t="n">
+        <v>93.11</v>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H938" s="2" t="n">
+        <v>46060.80440648388</v>
+      </c>
+      <c r="I938" s="2" t="n">
+        <v>46065.80440648388</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>21718b80-07fc-441e-883b-38f0ffc958a8</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>2138.91</v>
+      </c>
+      <c r="D939" t="n">
+        <v>95.87</v>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="n">
+        <v>46063.80440648715</v>
+      </c>
+      <c r="I939" s="2" t="n">
+        <v>46068.80440648715</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>98e8ecd1-d581-41c6-b608-802dab97fc82</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>8633.17</v>
+      </c>
+      <c r="D940" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H940" s="2" t="n">
+        <v>46074.80440649046</v>
+      </c>
+      <c r="I940" s="2" t="n">
+        <v>46079.80440649046</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>3a5f7e93-03e2-4ffd-b905-f58e1a57fc99</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>9799.91</v>
+      </c>
+      <c r="D941" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H941" s="2" t="n">
+        <v>46064.80440649367</v>
+      </c>
+      <c r="I941" s="2" t="n">
+        <v>46069.80440649367</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>391956ce-a1c5-4e36-844e-9a756b23c3d7</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>2124.97</v>
+      </c>
+      <c r="D942" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H942" s="2" t="n">
+        <v>46060.80440649675</v>
+      </c>
+      <c r="I942" s="2" t="n">
+        <v>46065.80440649675</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2a4dadd3-7f75-4936-abe0-e52ee0bd42b2</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>1339.63</v>
+      </c>
+      <c r="D943" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H943" s="2" t="n">
+        <v>46077.80440650001</v>
+      </c>
+      <c r="I943" s="2" t="n">
+        <v>46082.80440650001</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2d01e1ee-28b0-4ef1-bda4-21d336441ccd</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>9889.91</v>
+      </c>
+      <c r="D944" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H944" s="2" t="n">
+        <v>46064.80440650333</v>
+      </c>
+      <c r="I944" s="2" t="n">
+        <v>46069.80440650333</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>d837b880-4ea0-42da-97b5-0c3a078fdd43</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>5404.01</v>
+      </c>
+      <c r="D945" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H945" s="2" t="n">
+        <v>46084.80440650639</v>
+      </c>
+      <c r="I945" s="2" t="n">
+        <v>46089.80440650639</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>c6f7006f-f43a-461c-ad47-e41b19c1f14d</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>2704.67</v>
+      </c>
+      <c r="D946" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H946" s="2" t="n">
+        <v>46061.80440650963</v>
+      </c>
+      <c r="I946" s="2" t="n">
+        <v>46066.80440650963</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>760239e4-e7af-4e92-86c9-53c238f76eef</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>6264.43</v>
+      </c>
+      <c r="D947" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H947" s="2" t="n">
+        <v>46080.80440651299</v>
+      </c>
+      <c r="I947" s="2" t="n">
+        <v>46085.80440651299</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2eca3f95-9c63-498f-8b10-3506a12aa77b</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>3719.75</v>
+      </c>
+      <c r="D948" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H948" s="2" t="n">
+        <v>46084.80440651625</v>
+      </c>
+      <c r="I948" s="2" t="n">
+        <v>46089.80440651625</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>827ec653-76d9-4241-89e5-3a14d915a1cf</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>6593.89</v>
+      </c>
+      <c r="D949" t="n">
+        <v>97.95</v>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H949" s="2" t="n">
+        <v>46086.8044065195</v>
+      </c>
+      <c r="I949" s="2" t="n">
+        <v>46091.8044065195</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>b08d9958-573f-49f6-85f9-807f938ba9ca</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>1865.92</v>
+      </c>
+      <c r="D950" t="n">
+        <v>89.67</v>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H950" s="2" t="n">
+        <v>46076.80440652255</v>
+      </c>
+      <c r="I950" s="2" t="n">
+        <v>46081.80440652255</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>c0cfba62-af52-4eec-89d9-a6b32cbc6829</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>3283.28</v>
+      </c>
+      <c r="D951" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H951" s="2" t="n">
+        <v>46069.80440652594</v>
+      </c>
+      <c r="I951" s="2" t="n">
+        <v>46074.80440652594</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I951"/>
+  <dimension ref="A1:I1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35612,10 +35612,10 @@
         </is>
       </c>
       <c r="H902" s="2" t="n">
-        <v>46086.80440636374</v>
+        <v>46086.80440636574</v>
       </c>
       <c r="I902" s="2" t="n">
-        <v>46091.80440636374</v>
+        <v>46091.80440636574</v>
       </c>
     </row>
     <row r="903">
@@ -35651,10 +35651,10 @@
         </is>
       </c>
       <c r="H903" s="2" t="n">
-        <v>46074.80440636795</v>
+        <v>46074.80440636574</v>
       </c>
       <c r="I903" s="2" t="n">
-        <v>46079.80440636795</v>
+        <v>46079.80440636574</v>
       </c>
     </row>
     <row r="904">
@@ -35690,10 +35690,10 @@
         </is>
       </c>
       <c r="H904" s="2" t="n">
-        <v>46059.80440637137</v>
+        <v>46059.80440636574</v>
       </c>
       <c r="I904" s="2" t="n">
-        <v>46064.80440637137</v>
+        <v>46064.80440636574</v>
       </c>
     </row>
     <row r="905">
@@ -35729,10 +35729,10 @@
         </is>
       </c>
       <c r="H905" s="2" t="n">
-        <v>46064.8044063749</v>
+        <v>46064.80440637731</v>
       </c>
       <c r="I905" s="2" t="n">
-        <v>46069.8044063749</v>
+        <v>46069.80440637731</v>
       </c>
     </row>
     <row r="906">
@@ -35768,10 +35768,10 @@
         </is>
       </c>
       <c r="H906" s="2" t="n">
-        <v>46081.80440637823</v>
+        <v>46081.80440637731</v>
       </c>
       <c r="I906" s="2" t="n">
-        <v>46086.80440637823</v>
+        <v>46086.80440637731</v>
       </c>
     </row>
     <row r="907">
@@ -35807,10 +35807,10 @@
         </is>
       </c>
       <c r="H907" s="2" t="n">
-        <v>46060.8044063816</v>
+        <v>46060.80440637731</v>
       </c>
       <c r="I907" s="2" t="n">
-        <v>46065.8044063816</v>
+        <v>46065.80440637731</v>
       </c>
     </row>
     <row r="908">
@@ -35846,10 +35846,10 @@
         </is>
       </c>
       <c r="H908" s="2" t="n">
-        <v>46063.80440638468</v>
+        <v>46063.80440638889</v>
       </c>
       <c r="I908" s="2" t="n">
-        <v>46068.80440638468</v>
+        <v>46068.80440638889</v>
       </c>
     </row>
     <row r="909">
@@ -35885,10 +35885,10 @@
         </is>
       </c>
       <c r="H909" s="2" t="n">
-        <v>46088.80440638823</v>
+        <v>46088.80440638889</v>
       </c>
       <c r="I909" s="2" t="n">
-        <v>46093.80440638823</v>
+        <v>46093.80440638889</v>
       </c>
     </row>
     <row r="910">
@@ -35924,10 +35924,10 @@
         </is>
       </c>
       <c r="H910" s="2" t="n">
-        <v>46075.80440639157</v>
+        <v>46075.80440638889</v>
       </c>
       <c r="I910" s="2" t="n">
-        <v>46080.80440639157</v>
+        <v>46080.80440638889</v>
       </c>
     </row>
     <row r="911">
@@ -35963,10 +35963,10 @@
         </is>
       </c>
       <c r="H911" s="2" t="n">
-        <v>46083.80440639487</v>
+        <v>46083.80440640046</v>
       </c>
       <c r="I911" s="2" t="n">
-        <v>46088.80440639487</v>
+        <v>46088.80440640046</v>
       </c>
     </row>
     <row r="912">
@@ -36002,10 +36002,10 @@
         </is>
       </c>
       <c r="H912" s="2" t="n">
-        <v>46085.80440639866</v>
+        <v>46085.80440640046</v>
       </c>
       <c r="I912" s="2" t="n">
-        <v>46090.80440639866</v>
+        <v>46090.80440640046</v>
       </c>
     </row>
     <row r="913">
@@ -36041,10 +36041,10 @@
         </is>
       </c>
       <c r="H913" s="2" t="n">
-        <v>46069.80440640193</v>
+        <v>46069.80440640046</v>
       </c>
       <c r="I913" s="2" t="n">
-        <v>46074.80440640193</v>
+        <v>46074.80440640046</v>
       </c>
     </row>
     <row r="914">
@@ -36080,10 +36080,10 @@
         </is>
       </c>
       <c r="H914" s="2" t="n">
-        <v>46072.80440640528</v>
+        <v>46072.80440640046</v>
       </c>
       <c r="I914" s="2" t="n">
-        <v>46077.80440640528</v>
+        <v>46077.80440640046</v>
       </c>
     </row>
     <row r="915">
@@ -36119,10 +36119,10 @@
         </is>
       </c>
       <c r="H915" s="2" t="n">
-        <v>46064.80440640861</v>
+        <v>46064.80440641204</v>
       </c>
       <c r="I915" s="2" t="n">
-        <v>46069.80440640861</v>
+        <v>46069.80440641204</v>
       </c>
     </row>
     <row r="916">
@@ -36158,10 +36158,10 @@
         </is>
       </c>
       <c r="H916" s="2" t="n">
-        <v>46060.80440641173</v>
+        <v>46060.80440641204</v>
       </c>
       <c r="I916" s="2" t="n">
-        <v>46065.80440641173</v>
+        <v>46065.80440641204</v>
       </c>
     </row>
     <row r="917">
@@ -36197,10 +36197,10 @@
         </is>
       </c>
       <c r="H917" s="2" t="n">
-        <v>46087.80440641504</v>
+        <v>46087.80440641204</v>
       </c>
       <c r="I917" s="2" t="n">
-        <v>46092.80440641504</v>
+        <v>46092.80440641204</v>
       </c>
     </row>
     <row r="918">
@@ -36236,10 +36236,10 @@
         </is>
       </c>
       <c r="H918" s="2" t="n">
-        <v>46085.8044064183</v>
+        <v>46085.80440642361</v>
       </c>
       <c r="I918" s="2" t="n">
-        <v>46090.8044064183</v>
+        <v>46090.80440642361</v>
       </c>
     </row>
     <row r="919">
@@ -36275,10 +36275,10 @@
         </is>
       </c>
       <c r="H919" s="2" t="n">
-        <v>46066.80440642161</v>
+        <v>46066.80440642361</v>
       </c>
       <c r="I919" s="2" t="n">
-        <v>46071.80440642161</v>
+        <v>46071.80440642361</v>
       </c>
     </row>
     <row r="920">
@@ -36314,10 +36314,10 @@
         </is>
       </c>
       <c r="H920" s="2" t="n">
-        <v>46075.80440642474</v>
+        <v>46075.80440642361</v>
       </c>
       <c r="I920" s="2" t="n">
-        <v>46080.80440642474</v>
+        <v>46080.80440642361</v>
       </c>
     </row>
     <row r="921">
@@ -36353,10 +36353,10 @@
         </is>
       </c>
       <c r="H921" s="2" t="n">
-        <v>46072.80440642796</v>
+        <v>46072.80440642361</v>
       </c>
       <c r="I921" s="2" t="n">
-        <v>46077.80440642796</v>
+        <v>46077.80440642361</v>
       </c>
     </row>
     <row r="922">
@@ -36392,10 +36392,10 @@
         </is>
       </c>
       <c r="H922" s="2" t="n">
-        <v>46070.80440643107</v>
+        <v>46070.80440643519</v>
       </c>
       <c r="I922" s="2" t="n">
-        <v>46075.80440643107</v>
+        <v>46075.80440643519</v>
       </c>
     </row>
     <row r="923">
@@ -36431,10 +36431,10 @@
         </is>
       </c>
       <c r="H923" s="2" t="n">
-        <v>46066.80440643505</v>
+        <v>46066.80440643519</v>
       </c>
       <c r="I923" s="2" t="n">
-        <v>46071.80440643505</v>
+        <v>46071.80440643519</v>
       </c>
     </row>
     <row r="924">
@@ -36470,10 +36470,10 @@
         </is>
       </c>
       <c r="H924" s="2" t="n">
-        <v>46065.80440643826</v>
+        <v>46065.80440643519</v>
       </c>
       <c r="I924" s="2" t="n">
-        <v>46070.80440643826</v>
+        <v>46070.80440643519</v>
       </c>
     </row>
     <row r="925">
@@ -36509,10 +36509,10 @@
         </is>
       </c>
       <c r="H925" s="2" t="n">
-        <v>46059.80440644147</v>
+        <v>46059.80440644676</v>
       </c>
       <c r="I925" s="2" t="n">
-        <v>46064.80440644147</v>
+        <v>46064.80440644676</v>
       </c>
     </row>
     <row r="926">
@@ -36548,10 +36548,10 @@
         </is>
       </c>
       <c r="H926" s="2" t="n">
-        <v>46088.80440644494</v>
+        <v>46088.80440644676</v>
       </c>
       <c r="I926" s="2" t="n">
-        <v>46093.80440644494</v>
+        <v>46093.80440644676</v>
       </c>
     </row>
     <row r="927">
@@ -36587,10 +36587,10 @@
         </is>
       </c>
       <c r="H927" s="2" t="n">
-        <v>46069.80440644809</v>
+        <v>46069.80440644676</v>
       </c>
       <c r="I927" s="2" t="n">
-        <v>46074.80440644809</v>
+        <v>46074.80440644676</v>
       </c>
     </row>
     <row r="928">
@@ -36626,10 +36626,10 @@
         </is>
       </c>
       <c r="H928" s="2" t="n">
-        <v>46067.80440645119</v>
+        <v>46067.80440644676</v>
       </c>
       <c r="I928" s="2" t="n">
-        <v>46072.80440645119</v>
+        <v>46072.80440644676</v>
       </c>
     </row>
     <row r="929">
@@ -36665,10 +36665,10 @@
         </is>
       </c>
       <c r="H929" s="2" t="n">
-        <v>46076.80440645434</v>
+        <v>46076.80440645833</v>
       </c>
       <c r="I929" s="2" t="n">
-        <v>46081.80440645434</v>
+        <v>46081.80440645833</v>
       </c>
     </row>
     <row r="930">
@@ -36704,10 +36704,10 @@
         </is>
       </c>
       <c r="H930" s="2" t="n">
-        <v>46081.80440645762</v>
+        <v>46081.80440645833</v>
       </c>
       <c r="I930" s="2" t="n">
-        <v>46086.80440645762</v>
+        <v>46086.80440645833</v>
       </c>
     </row>
     <row r="931">
@@ -36743,10 +36743,10 @@
         </is>
       </c>
       <c r="H931" s="2" t="n">
-        <v>46087.80440646079</v>
+        <v>46087.80440645833</v>
       </c>
       <c r="I931" s="2" t="n">
-        <v>46092.80440646079</v>
+        <v>46092.80440645833</v>
       </c>
     </row>
     <row r="932">
@@ -36782,10 +36782,10 @@
         </is>
       </c>
       <c r="H932" s="2" t="n">
-        <v>46068.80440646412</v>
+        <v>46068.80440646991</v>
       </c>
       <c r="I932" s="2" t="n">
-        <v>46073.80440646412</v>
+        <v>46073.80440646991</v>
       </c>
     </row>
     <row r="933">
@@ -36821,10 +36821,10 @@
         </is>
       </c>
       <c r="H933" s="2" t="n">
-        <v>46079.80440646742</v>
+        <v>46079.80440646991</v>
       </c>
       <c r="I933" s="2" t="n">
-        <v>46084.80440646742</v>
+        <v>46084.80440646991</v>
       </c>
     </row>
     <row r="934">
@@ -36860,10 +36860,10 @@
         </is>
       </c>
       <c r="H934" s="2" t="n">
-        <v>46088.80440647055</v>
+        <v>46088.80440646991</v>
       </c>
       <c r="I934" s="2" t="n">
-        <v>46093.80440647055</v>
+        <v>46093.80440646991</v>
       </c>
     </row>
     <row r="935">
@@ -36899,10 +36899,10 @@
         </is>
       </c>
       <c r="H935" s="2" t="n">
-        <v>46062.80440647375</v>
+        <v>46062.80440646991</v>
       </c>
       <c r="I935" s="2" t="n">
-        <v>46067.80440647375</v>
+        <v>46067.80440646991</v>
       </c>
     </row>
     <row r="936">
@@ -36938,10 +36938,10 @@
         </is>
       </c>
       <c r="H936" s="2" t="n">
-        <v>46083.80440647683</v>
+        <v>46083.80440648148</v>
       </c>
       <c r="I936" s="2" t="n">
-        <v>46088.80440647683</v>
+        <v>46088.80440648148</v>
       </c>
     </row>
     <row r="937">
@@ -36977,10 +36977,10 @@
         </is>
       </c>
       <c r="H937" s="2" t="n">
-        <v>46077.80440648029</v>
+        <v>46077.80440648148</v>
       </c>
       <c r="I937" s="2" t="n">
-        <v>46082.80440648029</v>
+        <v>46082.80440648148</v>
       </c>
     </row>
     <row r="938">
@@ -37016,10 +37016,10 @@
         </is>
       </c>
       <c r="H938" s="2" t="n">
-        <v>46060.80440648388</v>
+        <v>46060.80440648148</v>
       </c>
       <c r="I938" s="2" t="n">
-        <v>46065.80440648388</v>
+        <v>46065.80440648148</v>
       </c>
     </row>
     <row r="939">
@@ -37055,10 +37055,10 @@
         </is>
       </c>
       <c r="H939" s="2" t="n">
-        <v>46063.80440648715</v>
+        <v>46063.80440648148</v>
       </c>
       <c r="I939" s="2" t="n">
-        <v>46068.80440648715</v>
+        <v>46068.80440648148</v>
       </c>
     </row>
     <row r="940">
@@ -37094,10 +37094,10 @@
         </is>
       </c>
       <c r="H940" s="2" t="n">
-        <v>46074.80440649046</v>
+        <v>46074.80440649306</v>
       </c>
       <c r="I940" s="2" t="n">
-        <v>46079.80440649046</v>
+        <v>46079.80440649306</v>
       </c>
     </row>
     <row r="941">
@@ -37133,10 +37133,10 @@
         </is>
       </c>
       <c r="H941" s="2" t="n">
-        <v>46064.80440649367</v>
+        <v>46064.80440649306</v>
       </c>
       <c r="I941" s="2" t="n">
-        <v>46069.80440649367</v>
+        <v>46069.80440649306</v>
       </c>
     </row>
     <row r="942">
@@ -37172,10 +37172,10 @@
         </is>
       </c>
       <c r="H942" s="2" t="n">
-        <v>46060.80440649675</v>
+        <v>46060.80440649306</v>
       </c>
       <c r="I942" s="2" t="n">
-        <v>46065.80440649675</v>
+        <v>46065.80440649306</v>
       </c>
     </row>
     <row r="943">
@@ -37211,10 +37211,10 @@
         </is>
       </c>
       <c r="H943" s="2" t="n">
-        <v>46077.80440650001</v>
+        <v>46077.80440650463</v>
       </c>
       <c r="I943" s="2" t="n">
-        <v>46082.80440650001</v>
+        <v>46082.80440650463</v>
       </c>
     </row>
     <row r="944">
@@ -37250,10 +37250,10 @@
         </is>
       </c>
       <c r="H944" s="2" t="n">
-        <v>46064.80440650333</v>
+        <v>46064.80440650463</v>
       </c>
       <c r="I944" s="2" t="n">
-        <v>46069.80440650333</v>
+        <v>46069.80440650463</v>
       </c>
     </row>
     <row r="945">
@@ -37289,10 +37289,10 @@
         </is>
       </c>
       <c r="H945" s="2" t="n">
-        <v>46084.80440650639</v>
+        <v>46084.80440650463</v>
       </c>
       <c r="I945" s="2" t="n">
-        <v>46089.80440650639</v>
+        <v>46089.80440650463</v>
       </c>
     </row>
     <row r="946">
@@ -37328,10 +37328,10 @@
         </is>
       </c>
       <c r="H946" s="2" t="n">
-        <v>46061.80440650963</v>
+        <v>46061.80440650463</v>
       </c>
       <c r="I946" s="2" t="n">
-        <v>46066.80440650963</v>
+        <v>46066.80440650463</v>
       </c>
     </row>
     <row r="947">
@@ -37367,10 +37367,10 @@
         </is>
       </c>
       <c r="H947" s="2" t="n">
-        <v>46080.80440651299</v>
+        <v>46080.8044065162</v>
       </c>
       <c r="I947" s="2" t="n">
-        <v>46085.80440651299</v>
+        <v>46085.8044065162</v>
       </c>
     </row>
     <row r="948">
@@ -37406,10 +37406,10 @@
         </is>
       </c>
       <c r="H948" s="2" t="n">
-        <v>46084.80440651625</v>
+        <v>46084.8044065162</v>
       </c>
       <c r="I948" s="2" t="n">
-        <v>46089.80440651625</v>
+        <v>46089.8044065162</v>
       </c>
     </row>
     <row r="949">
@@ -37445,10 +37445,10 @@
         </is>
       </c>
       <c r="H949" s="2" t="n">
-        <v>46086.8044065195</v>
+        <v>46086.8044065162</v>
       </c>
       <c r="I949" s="2" t="n">
-        <v>46091.8044065195</v>
+        <v>46091.8044065162</v>
       </c>
     </row>
     <row r="950">
@@ -37484,10 +37484,10 @@
         </is>
       </c>
       <c r="H950" s="2" t="n">
-        <v>46076.80440652255</v>
+        <v>46076.80440652778</v>
       </c>
       <c r="I950" s="2" t="n">
-        <v>46081.80440652255</v>
+        <v>46081.80440652778</v>
       </c>
     </row>
     <row r="951">
@@ -37523,10 +37523,1960 @@
         </is>
       </c>
       <c r="H951" s="2" t="n">
-        <v>46069.80440652594</v>
+        <v>46069.80440652778</v>
       </c>
       <c r="I951" s="2" t="n">
-        <v>46074.80440652594</v>
+        <v>46074.80440652778</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>a02685a3-06d6-44f7-8ea3-dc4588f6c547</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>6195.56</v>
+      </c>
+      <c r="D952" t="n">
+        <v>93.91</v>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H952" s="2" t="n">
+        <v>46063.8449306226</v>
+      </c>
+      <c r="I952" s="2" t="n">
+        <v>46068.8449306226</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>304cf696-fdda-4cff-b693-bd08f6a45d2d</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>4005.65</v>
+      </c>
+      <c r="D953" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="n">
+        <v>46087.844930627</v>
+      </c>
+      <c r="I953" s="2" t="n">
+        <v>46092.844930627</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>b7399f78-afe6-4d4c-8b73-131fc07e692b</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>2684.09</v>
+      </c>
+      <c r="D954" t="n">
+        <v>97</v>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H954" s="2" t="n">
+        <v>46081.84493063045</v>
+      </c>
+      <c r="I954" s="2" t="n">
+        <v>46086.84493063045</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>47b425cf-bf57-45e4-8111-32e7b3face78</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>6585.81</v>
+      </c>
+      <c r="D955" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H955" s="2" t="n">
+        <v>46061.8449306342</v>
+      </c>
+      <c r="I955" s="2" t="n">
+        <v>46066.8449306342</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>965ec4c0-6e8d-48c7-a87c-f39796e78c12</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>4179.21</v>
+      </c>
+      <c r="D956" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H956" s="2" t="n">
+        <v>46076.84493063729</v>
+      </c>
+      <c r="I956" s="2" t="n">
+        <v>46081.84493063729</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>b5295492-2520-4373-bb3e-a3fb01f98a8f</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>6775.09</v>
+      </c>
+      <c r="D957" t="n">
+        <v>94.45</v>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H957" s="2" t="n">
+        <v>46060.84493064057</v>
+      </c>
+      <c r="I957" s="2" t="n">
+        <v>46065.84493064057</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>a8e216dc-a773-4d4d-b0c8-c4c52e979300</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>6480.7</v>
+      </c>
+      <c r="D958" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H958" s="2" t="n">
+        <v>46088.84493064421</v>
+      </c>
+      <c r="I958" s="2" t="n">
+        <v>46093.84493064421</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>c4ad7838-72b7-4b00-83eb-abe6019300d0</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>7159.76</v>
+      </c>
+      <c r="D959" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H959" s="2" t="n">
+        <v>46072.84493064745</v>
+      </c>
+      <c r="I959" s="2" t="n">
+        <v>46077.84493064745</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>1b2493fe-1e16-4136-a930-639e79debe08</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>1742.17</v>
+      </c>
+      <c r="D960" t="n">
+        <v>87.76000000000001</v>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H960" s="2" t="n">
+        <v>46067.8449306506</v>
+      </c>
+      <c r="I960" s="2" t="n">
+        <v>46072.8449306506</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>11a96b3b-ba33-4765-8c3d-2c27efc88d75</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>4073.04</v>
+      </c>
+      <c r="D961" t="n">
+        <v>86</v>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H961" s="2" t="n">
+        <v>46062.84493065396</v>
+      </c>
+      <c r="I961" s="2" t="n">
+        <v>46067.84493065396</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>790b43a1-147d-4da1-9c99-dfd6e10961ac</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>2902.78</v>
+      </c>
+      <c r="D962" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H962" s="2" t="n">
+        <v>46081.84493065743</v>
+      </c>
+      <c r="I962" s="2" t="n">
+        <v>46086.84493065743</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>f0d987e5-7cf8-4d53-acc8-8586c7471d51</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>7313.58</v>
+      </c>
+      <c r="D963" t="n">
+        <v>90.08</v>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H963" s="2" t="n">
+        <v>46074.84493066058</v>
+      </c>
+      <c r="I963" s="2" t="n">
+        <v>46079.84493066058</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>f33e0e7b-3c18-4892-95d1-1b9df8c2e7a7</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>1112.59</v>
+      </c>
+      <c r="D964" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H964" s="2" t="n">
+        <v>46078.84493066376</v>
+      </c>
+      <c r="I964" s="2" t="n">
+        <v>46083.84493066376</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>e0e16ca1-3de2-4638-b0a2-10a853767c26</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>3071.06</v>
+      </c>
+      <c r="D965" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H965" s="2" t="n">
+        <v>46064.84493066757</v>
+      </c>
+      <c r="I965" s="2" t="n">
+        <v>46069.84493066757</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>392bf59a-f913-4032-a826-4679f6282e07</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>8259.559999999999</v>
+      </c>
+      <c r="D966" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H966" s="2" t="n">
+        <v>46071.84493067072</v>
+      </c>
+      <c r="I966" s="2" t="n">
+        <v>46076.84493067072</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>c0d2b5f6-cbcb-4d70-8f49-9fddb9bbf7ae</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>1934.06</v>
+      </c>
+      <c r="D967" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="n">
+        <v>46074.8449306738</v>
+      </c>
+      <c r="I967" s="2" t="n">
+        <v>46079.8449306738</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>0c1f8b65-9504-405d-a705-2d026fa3c8bc</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>2815.41</v>
+      </c>
+      <c r="D968" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H968" s="2" t="n">
+        <v>46077.8449306769</v>
+      </c>
+      <c r="I968" s="2" t="n">
+        <v>46082.8449306769</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>ead207e9-1408-4986-bd6e-0e94afe16d3d</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>3914.18</v>
+      </c>
+      <c r="D969" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H969" s="2" t="n">
+        <v>46085.8449306804</v>
+      </c>
+      <c r="I969" s="2" t="n">
+        <v>46090.8449306804</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>338c6d71-a408-4308-869a-3436a0c91e83</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>7306.41</v>
+      </c>
+      <c r="D970" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H970" s="2" t="n">
+        <v>46066.84493068359</v>
+      </c>
+      <c r="I970" s="2" t="n">
+        <v>46071.84493068359</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>0a10f249-13da-4371-a199-75c2ad82d491</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>9767.530000000001</v>
+      </c>
+      <c r="D971" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H971" s="2" t="n">
+        <v>46075.84493068662</v>
+      </c>
+      <c r="I971" s="2" t="n">
+        <v>46080.84493068662</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>1fa7119d-faf3-4ffb-8b83-393a06318af2</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>1038.95</v>
+      </c>
+      <c r="D972" t="n">
+        <v>93.56999999999999</v>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H972" s="2" t="n">
+        <v>46079.84493069004</v>
+      </c>
+      <c r="I972" s="2" t="n">
+        <v>46084.84493069004</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2a21b7cc-3384-4997-8661-e6758f68394f</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>1112.03</v>
+      </c>
+      <c r="D973" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H973" s="2" t="n">
+        <v>46073.84493069317</v>
+      </c>
+      <c r="I973" s="2" t="n">
+        <v>46078.84493069317</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>a99acec5-6416-4490-a246-eb2ec8d719d7</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>2593.78</v>
+      </c>
+      <c r="D974" t="n">
+        <v>96.56999999999999</v>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H974" s="2" t="n">
+        <v>46073.84493069621</v>
+      </c>
+      <c r="I974" s="2" t="n">
+        <v>46078.84493069621</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>0f25cd74-4a8a-4231-805b-c3c7663cc5b1</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>3084.2</v>
+      </c>
+      <c r="D975" t="n">
+        <v>97.76000000000001</v>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H975" s="2" t="n">
+        <v>46088.84493069941</v>
+      </c>
+      <c r="I975" s="2" t="n">
+        <v>46093.84493069941</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>5efd4503-96f5-4fb2-824f-e667ac52c10b</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>4374.65</v>
+      </c>
+      <c r="D976" t="n">
+        <v>91.92</v>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H976" s="2" t="n">
+        <v>46084.84493070267</v>
+      </c>
+      <c r="I976" s="2" t="n">
+        <v>46089.84493070267</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>9af21df8-cd51-4502-94ce-f3553d0928a4</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>5439.22</v>
+      </c>
+      <c r="D977" t="n">
+        <v>85.73</v>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H977" s="2" t="n">
+        <v>46067.84493070588</v>
+      </c>
+      <c r="I977" s="2" t="n">
+        <v>46072.84493070588</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>8319d142-4654-4038-ae44-51c3cb160448</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>9827.07</v>
+      </c>
+      <c r="D978" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H978" s="2" t="n">
+        <v>46082.84493070896</v>
+      </c>
+      <c r="I978" s="2" t="n">
+        <v>46087.84493070896</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>135adb38-7f11-4675-965f-d978a472b278</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>6295.89</v>
+      </c>
+      <c r="D979" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H979" s="2" t="n">
+        <v>46087.84493071212</v>
+      </c>
+      <c r="I979" s="2" t="n">
+        <v>46092.84493071212</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>5f288a9f-0801-4d04-bc47-937e6ebfa0a3</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>8727.790000000001</v>
+      </c>
+      <c r="D980" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H980" s="2" t="n">
+        <v>46064.84493071572</v>
+      </c>
+      <c r="I980" s="2" t="n">
+        <v>46069.84493071572</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>079795f7-bd4d-4e1b-ae9c-d39e2ef2904b</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>5614.51</v>
+      </c>
+      <c r="D981" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H981" s="2" t="n">
+        <v>46076.84493071904</v>
+      </c>
+      <c r="I981" s="2" t="n">
+        <v>46081.84493071904</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>3b70566f-9d15-4d01-9994-1ccffe8e9f0e</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>7774.56</v>
+      </c>
+      <c r="D982" t="n">
+        <v>87.63</v>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H982" s="2" t="n">
+        <v>46062.84493072213</v>
+      </c>
+      <c r="I982" s="2" t="n">
+        <v>46067.84493072213</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>b2cd0119-099a-4406-89ca-34cbb74ffaf4</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>1595.87</v>
+      </c>
+      <c r="D983" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H983" s="2" t="n">
+        <v>46086.8449307255</v>
+      </c>
+      <c r="I983" s="2" t="n">
+        <v>46091.8449307255</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>1b415b2a-42ab-4c43-a205-2a2e67a566e4</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>1283.61</v>
+      </c>
+      <c r="D984" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H984" s="2" t="n">
+        <v>46086.8449307287</v>
+      </c>
+      <c r="I984" s="2" t="n">
+        <v>46091.8449307287</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>15589b64-caec-4170-8f0e-27ef9bcdcd14</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>7480.36</v>
+      </c>
+      <c r="D985" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H985" s="2" t="n">
+        <v>46084.84493073195</v>
+      </c>
+      <c r="I985" s="2" t="n">
+        <v>46089.84493073195</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>af9ee15b-eb37-401b-a7df-624a933df8f8</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>1005.76</v>
+      </c>
+      <c r="D986" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H986" s="2" t="n">
+        <v>46070.84493073495</v>
+      </c>
+      <c r="I986" s="2" t="n">
+        <v>46075.84493073495</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>041865dc-2220-400d-ac7e-c94b308542a3</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>3796.35</v>
+      </c>
+      <c r="D987" t="n">
+        <v>85.45999999999999</v>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H987" s="2" t="n">
+        <v>46073.84493073834</v>
+      </c>
+      <c r="I987" s="2" t="n">
+        <v>46078.84493073834</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>5bfe573b-451d-477f-bbe1-8fbe1e39daf8</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>2379.52</v>
+      </c>
+      <c r="D988" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H988" s="2" t="n">
+        <v>46082.84493074143</v>
+      </c>
+      <c r="I988" s="2" t="n">
+        <v>46087.84493074143</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>53ef4842-e00b-4f4b-8768-707b0a2a6370</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>5478.8</v>
+      </c>
+      <c r="D989" t="n">
+        <v>96.26000000000001</v>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H989" s="2" t="n">
+        <v>46066.84493074451</v>
+      </c>
+      <c r="I989" s="2" t="n">
+        <v>46071.84493074451</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>4ac33e31-b837-4db2-a3fb-818d4181dbb4</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>9903.74</v>
+      </c>
+      <c r="D990" t="n">
+        <v>88.41</v>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H990" s="2" t="n">
+        <v>46063.84493074784</v>
+      </c>
+      <c r="I990" s="2" t="n">
+        <v>46068.84493074784</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>96a62cd2-1fbb-42e7-a6c6-80117f8b68e6</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>3451.35</v>
+      </c>
+      <c r="D991" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H991" s="2" t="n">
+        <v>46066.84493075091</v>
+      </c>
+      <c r="I991" s="2" t="n">
+        <v>46071.84493075091</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>3d31088d-2f2a-4efd-9a69-b795777050d9</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>2427.44</v>
+      </c>
+      <c r="D992" t="n">
+        <v>87.16</v>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H992" s="2" t="n">
+        <v>46083.84493075535</v>
+      </c>
+      <c r="I992" s="2" t="n">
+        <v>46088.84493075535</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>7634b231-a06c-4835-a6d1-12120884b16a</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>3636.18</v>
+      </c>
+      <c r="D993" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H993" s="2" t="n">
+        <v>46085.84493075847</v>
+      </c>
+      <c r="I993" s="2" t="n">
+        <v>46090.84493075847</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>83471ce2-d99b-4d0a-8ca8-78d4573296b6</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>1607.51</v>
+      </c>
+      <c r="D994" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H994" s="2" t="n">
+        <v>46062.84493076205</v>
+      </c>
+      <c r="I994" s="2" t="n">
+        <v>46067.84493076205</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>4f6ded20-4a22-40ac-9cfd-0e734d4892f3</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>1093.68</v>
+      </c>
+      <c r="D995" t="n">
+        <v>89.95999999999999</v>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H995" s="2" t="n">
+        <v>46072.84493076512</v>
+      </c>
+      <c r="I995" s="2" t="n">
+        <v>46077.84493076512</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>be961253-cc99-42aa-8fca-b11a974c87ba</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>7568.2</v>
+      </c>
+      <c r="D996" t="n">
+        <v>87.41</v>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H996" s="2" t="n">
+        <v>46071.84493076826</v>
+      </c>
+      <c r="I996" s="2" t="n">
+        <v>46076.84493076826</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>1fb8479e-4e53-4969-900d-0172a0a877a1</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>6205.29</v>
+      </c>
+      <c r="D997" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H997" s="2" t="n">
+        <v>46077.84493077166</v>
+      </c>
+      <c r="I997" s="2" t="n">
+        <v>46082.84493077166</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>1fc1e725-31ae-4d22-b93a-45c1aa8f6f42</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>5920.11</v>
+      </c>
+      <c r="D998" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H998" s="2" t="n">
+        <v>46081.84493077474</v>
+      </c>
+      <c r="I998" s="2" t="n">
+        <v>46086.84493077474</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>809465fc-383a-4da2-81e1-852e4f415c41</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>4116.44</v>
+      </c>
+      <c r="D999" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H999" s="2" t="n">
+        <v>46061.84493077818</v>
+      </c>
+      <c r="I999" s="2" t="n">
+        <v>46066.84493077818</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>1b3b5cd2-a1c7-4e9d-97f1-950018875e4e</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>7128.83</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1000" s="2" t="n">
+        <v>46065.84493078132</v>
+      </c>
+      <c r="I1000" s="2" t="n">
+        <v>46070.84493078132</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>d316f029-e54a-4b26-bbdc-9f2b631a56a2</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>6961.63</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>97</v>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1001" s="2" t="n">
+        <v>46075.84493078457</v>
+      </c>
+      <c r="I1001" s="2" t="n">
+        <v>46080.84493078457</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:I1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37562,10 +37562,10 @@
         </is>
       </c>
       <c r="H952" s="2" t="n">
-        <v>46063.8449306226</v>
+        <v>46063.844930625</v>
       </c>
       <c r="I952" s="2" t="n">
-        <v>46068.8449306226</v>
+        <v>46068.844930625</v>
       </c>
     </row>
     <row r="953">
@@ -37601,10 +37601,10 @@
         </is>
       </c>
       <c r="H953" s="2" t="n">
-        <v>46087.844930627</v>
+        <v>46087.844930625</v>
       </c>
       <c r="I953" s="2" t="n">
-        <v>46092.844930627</v>
+        <v>46092.844930625</v>
       </c>
     </row>
     <row r="954">
@@ -37640,10 +37640,10 @@
         </is>
       </c>
       <c r="H954" s="2" t="n">
-        <v>46081.84493063045</v>
+        <v>46081.844930625</v>
       </c>
       <c r="I954" s="2" t="n">
-        <v>46086.84493063045</v>
+        <v>46086.844930625</v>
       </c>
     </row>
     <row r="955">
@@ -37679,10 +37679,10 @@
         </is>
       </c>
       <c r="H955" s="2" t="n">
-        <v>46061.8449306342</v>
+        <v>46061.84493063657</v>
       </c>
       <c r="I955" s="2" t="n">
-        <v>46066.8449306342</v>
+        <v>46066.84493063657</v>
       </c>
     </row>
     <row r="956">
@@ -37718,10 +37718,10 @@
         </is>
       </c>
       <c r="H956" s="2" t="n">
-        <v>46076.84493063729</v>
+        <v>46076.84493063657</v>
       </c>
       <c r="I956" s="2" t="n">
-        <v>46081.84493063729</v>
+        <v>46081.84493063657</v>
       </c>
     </row>
     <row r="957">
@@ -37757,10 +37757,10 @@
         </is>
       </c>
       <c r="H957" s="2" t="n">
-        <v>46060.84493064057</v>
+        <v>46060.84493063657</v>
       </c>
       <c r="I957" s="2" t="n">
-        <v>46065.84493064057</v>
+        <v>46065.84493063657</v>
       </c>
     </row>
     <row r="958">
@@ -37796,10 +37796,10 @@
         </is>
       </c>
       <c r="H958" s="2" t="n">
-        <v>46088.84493064421</v>
+        <v>46088.84493064815</v>
       </c>
       <c r="I958" s="2" t="n">
-        <v>46093.84493064421</v>
+        <v>46093.84493064815</v>
       </c>
     </row>
     <row r="959">
@@ -37835,10 +37835,10 @@
         </is>
       </c>
       <c r="H959" s="2" t="n">
-        <v>46072.84493064745</v>
+        <v>46072.84493064815</v>
       </c>
       <c r="I959" s="2" t="n">
-        <v>46077.84493064745</v>
+        <v>46077.84493064815</v>
       </c>
     </row>
     <row r="960">
@@ -37874,10 +37874,10 @@
         </is>
       </c>
       <c r="H960" s="2" t="n">
-        <v>46067.8449306506</v>
+        <v>46067.84493064815</v>
       </c>
       <c r="I960" s="2" t="n">
-        <v>46072.8449306506</v>
+        <v>46072.84493064815</v>
       </c>
     </row>
     <row r="961">
@@ -37913,10 +37913,10 @@
         </is>
       </c>
       <c r="H961" s="2" t="n">
-        <v>46062.84493065396</v>
+        <v>46062.84493065972</v>
       </c>
       <c r="I961" s="2" t="n">
-        <v>46067.84493065396</v>
+        <v>46067.84493065972</v>
       </c>
     </row>
     <row r="962">
@@ -37952,10 +37952,10 @@
         </is>
       </c>
       <c r="H962" s="2" t="n">
-        <v>46081.84493065743</v>
+        <v>46081.84493065972</v>
       </c>
       <c r="I962" s="2" t="n">
-        <v>46086.84493065743</v>
+        <v>46086.84493065972</v>
       </c>
     </row>
     <row r="963">
@@ -37991,10 +37991,10 @@
         </is>
       </c>
       <c r="H963" s="2" t="n">
-        <v>46074.84493066058</v>
+        <v>46074.84493065972</v>
       </c>
       <c r="I963" s="2" t="n">
-        <v>46079.84493066058</v>
+        <v>46079.84493065972</v>
       </c>
     </row>
     <row r="964">
@@ -38030,10 +38030,10 @@
         </is>
       </c>
       <c r="H964" s="2" t="n">
-        <v>46078.84493066376</v>
+        <v>46078.84493065972</v>
       </c>
       <c r="I964" s="2" t="n">
-        <v>46083.84493066376</v>
+        <v>46083.84493065972</v>
       </c>
     </row>
     <row r="965">
@@ -38069,10 +38069,10 @@
         </is>
       </c>
       <c r="H965" s="2" t="n">
-        <v>46064.84493066757</v>
+        <v>46064.84493067129</v>
       </c>
       <c r="I965" s="2" t="n">
-        <v>46069.84493066757</v>
+        <v>46069.84493067129</v>
       </c>
     </row>
     <row r="966">
@@ -38108,10 +38108,10 @@
         </is>
       </c>
       <c r="H966" s="2" t="n">
-        <v>46071.84493067072</v>
+        <v>46071.84493067129</v>
       </c>
       <c r="I966" s="2" t="n">
-        <v>46076.84493067072</v>
+        <v>46076.84493067129</v>
       </c>
     </row>
     <row r="967">
@@ -38147,10 +38147,10 @@
         </is>
       </c>
       <c r="H967" s="2" t="n">
-        <v>46074.8449306738</v>
+        <v>46074.84493067129</v>
       </c>
       <c r="I967" s="2" t="n">
-        <v>46079.8449306738</v>
+        <v>46079.84493067129</v>
       </c>
     </row>
     <row r="968">
@@ -38186,10 +38186,10 @@
         </is>
       </c>
       <c r="H968" s="2" t="n">
-        <v>46077.8449306769</v>
+        <v>46077.84493067129</v>
       </c>
       <c r="I968" s="2" t="n">
-        <v>46082.8449306769</v>
+        <v>46082.84493067129</v>
       </c>
     </row>
     <row r="969">
@@ -38225,10 +38225,10 @@
         </is>
       </c>
       <c r="H969" s="2" t="n">
-        <v>46085.8449306804</v>
+        <v>46085.84493068287</v>
       </c>
       <c r="I969" s="2" t="n">
-        <v>46090.8449306804</v>
+        <v>46090.84493068287</v>
       </c>
     </row>
     <row r="970">
@@ -38264,10 +38264,10 @@
         </is>
       </c>
       <c r="H970" s="2" t="n">
-        <v>46066.84493068359</v>
+        <v>46066.84493068287</v>
       </c>
       <c r="I970" s="2" t="n">
-        <v>46071.84493068359</v>
+        <v>46071.84493068287</v>
       </c>
     </row>
     <row r="971">
@@ -38303,10 +38303,10 @@
         </is>
       </c>
       <c r="H971" s="2" t="n">
-        <v>46075.84493068662</v>
+        <v>46075.84493068287</v>
       </c>
       <c r="I971" s="2" t="n">
-        <v>46080.84493068662</v>
+        <v>46080.84493068287</v>
       </c>
     </row>
     <row r="972">
@@ -38342,10 +38342,10 @@
         </is>
       </c>
       <c r="H972" s="2" t="n">
-        <v>46079.84493069004</v>
+        <v>46079.84493069445</v>
       </c>
       <c r="I972" s="2" t="n">
-        <v>46084.84493069004</v>
+        <v>46084.84493069445</v>
       </c>
     </row>
     <row r="973">
@@ -38381,10 +38381,10 @@
         </is>
       </c>
       <c r="H973" s="2" t="n">
-        <v>46073.84493069317</v>
+        <v>46073.84493069445</v>
       </c>
       <c r="I973" s="2" t="n">
-        <v>46078.84493069317</v>
+        <v>46078.84493069445</v>
       </c>
     </row>
     <row r="974">
@@ -38420,10 +38420,10 @@
         </is>
       </c>
       <c r="H974" s="2" t="n">
-        <v>46073.84493069621</v>
+        <v>46073.84493069445</v>
       </c>
       <c r="I974" s="2" t="n">
-        <v>46078.84493069621</v>
+        <v>46078.84493069445</v>
       </c>
     </row>
     <row r="975">
@@ -38459,10 +38459,10 @@
         </is>
       </c>
       <c r="H975" s="2" t="n">
-        <v>46088.84493069941</v>
+        <v>46088.84493069445</v>
       </c>
       <c r="I975" s="2" t="n">
-        <v>46093.84493069941</v>
+        <v>46093.84493069445</v>
       </c>
     </row>
     <row r="976">
@@ -38498,10 +38498,10 @@
         </is>
       </c>
       <c r="H976" s="2" t="n">
-        <v>46084.84493070267</v>
+        <v>46084.84493070602</v>
       </c>
       <c r="I976" s="2" t="n">
-        <v>46089.84493070267</v>
+        <v>46089.84493070602</v>
       </c>
     </row>
     <row r="977">
@@ -38537,10 +38537,10 @@
         </is>
       </c>
       <c r="H977" s="2" t="n">
-        <v>46067.84493070588</v>
+        <v>46067.84493070602</v>
       </c>
       <c r="I977" s="2" t="n">
-        <v>46072.84493070588</v>
+        <v>46072.84493070602</v>
       </c>
     </row>
     <row r="978">
@@ -38576,10 +38576,10 @@
         </is>
       </c>
       <c r="H978" s="2" t="n">
-        <v>46082.84493070896</v>
+        <v>46082.84493070602</v>
       </c>
       <c r="I978" s="2" t="n">
-        <v>46087.84493070896</v>
+        <v>46087.84493070602</v>
       </c>
     </row>
     <row r="979">
@@ -38615,10 +38615,10 @@
         </is>
       </c>
       <c r="H979" s="2" t="n">
-        <v>46087.84493071212</v>
+        <v>46087.84493071759</v>
       </c>
       <c r="I979" s="2" t="n">
-        <v>46092.84493071212</v>
+        <v>46092.84493071759</v>
       </c>
     </row>
     <row r="980">
@@ -38654,10 +38654,10 @@
         </is>
       </c>
       <c r="H980" s="2" t="n">
-        <v>46064.84493071572</v>
+        <v>46064.84493071759</v>
       </c>
       <c r="I980" s="2" t="n">
-        <v>46069.84493071572</v>
+        <v>46069.84493071759</v>
       </c>
     </row>
     <row r="981">
@@ -38693,10 +38693,10 @@
         </is>
       </c>
       <c r="H981" s="2" t="n">
-        <v>46076.84493071904</v>
+        <v>46076.84493071759</v>
       </c>
       <c r="I981" s="2" t="n">
-        <v>46081.84493071904</v>
+        <v>46081.84493071759</v>
       </c>
     </row>
     <row r="982">
@@ -38732,10 +38732,10 @@
         </is>
       </c>
       <c r="H982" s="2" t="n">
-        <v>46062.84493072213</v>
+        <v>46062.84493071759</v>
       </c>
       <c r="I982" s="2" t="n">
-        <v>46067.84493072213</v>
+        <v>46067.84493071759</v>
       </c>
     </row>
     <row r="983">
@@ -38771,10 +38771,10 @@
         </is>
       </c>
       <c r="H983" s="2" t="n">
-        <v>46086.8449307255</v>
+        <v>46086.84493072917</v>
       </c>
       <c r="I983" s="2" t="n">
-        <v>46091.8449307255</v>
+        <v>46091.84493072917</v>
       </c>
     </row>
     <row r="984">
@@ -38810,10 +38810,10 @@
         </is>
       </c>
       <c r="H984" s="2" t="n">
-        <v>46086.8449307287</v>
+        <v>46086.84493072917</v>
       </c>
       <c r="I984" s="2" t="n">
-        <v>46091.8449307287</v>
+        <v>46091.84493072917</v>
       </c>
     </row>
     <row r="985">
@@ -38849,10 +38849,10 @@
         </is>
       </c>
       <c r="H985" s="2" t="n">
-        <v>46084.84493073195</v>
+        <v>46084.84493072917</v>
       </c>
       <c r="I985" s="2" t="n">
-        <v>46089.84493073195</v>
+        <v>46089.84493072917</v>
       </c>
     </row>
     <row r="986">
@@ -38888,10 +38888,10 @@
         </is>
       </c>
       <c r="H986" s="2" t="n">
-        <v>46070.84493073495</v>
+        <v>46070.84493072917</v>
       </c>
       <c r="I986" s="2" t="n">
-        <v>46075.84493073495</v>
+        <v>46075.84493072917</v>
       </c>
     </row>
     <row r="987">
@@ -38927,10 +38927,10 @@
         </is>
       </c>
       <c r="H987" s="2" t="n">
-        <v>46073.84493073834</v>
+        <v>46073.84493074074</v>
       </c>
       <c r="I987" s="2" t="n">
-        <v>46078.84493073834</v>
+        <v>46078.84493074074</v>
       </c>
     </row>
     <row r="988">
@@ -38966,10 +38966,10 @@
         </is>
       </c>
       <c r="H988" s="2" t="n">
-        <v>46082.84493074143</v>
+        <v>46082.84493074074</v>
       </c>
       <c r="I988" s="2" t="n">
-        <v>46087.84493074143</v>
+        <v>46087.84493074074</v>
       </c>
     </row>
     <row r="989">
@@ -39005,10 +39005,10 @@
         </is>
       </c>
       <c r="H989" s="2" t="n">
-        <v>46066.84493074451</v>
+        <v>46066.84493074074</v>
       </c>
       <c r="I989" s="2" t="n">
-        <v>46071.84493074451</v>
+        <v>46071.84493074074</v>
       </c>
     </row>
     <row r="990">
@@ -39044,10 +39044,10 @@
         </is>
       </c>
       <c r="H990" s="2" t="n">
-        <v>46063.84493074784</v>
+        <v>46063.84493075231</v>
       </c>
       <c r="I990" s="2" t="n">
-        <v>46068.84493074784</v>
+        <v>46068.84493075231</v>
       </c>
     </row>
     <row r="991">
@@ -39083,10 +39083,10 @@
         </is>
       </c>
       <c r="H991" s="2" t="n">
-        <v>46066.84493075091</v>
+        <v>46066.84493075231</v>
       </c>
       <c r="I991" s="2" t="n">
-        <v>46071.84493075091</v>
+        <v>46071.84493075231</v>
       </c>
     </row>
     <row r="992">
@@ -39122,10 +39122,10 @@
         </is>
       </c>
       <c r="H992" s="2" t="n">
-        <v>46083.84493075535</v>
+        <v>46083.84493075231</v>
       </c>
       <c r="I992" s="2" t="n">
-        <v>46088.84493075535</v>
+        <v>46088.84493075231</v>
       </c>
     </row>
     <row r="993">
@@ -39161,10 +39161,10 @@
         </is>
       </c>
       <c r="H993" s="2" t="n">
-        <v>46085.84493075847</v>
+        <v>46085.84493076389</v>
       </c>
       <c r="I993" s="2" t="n">
-        <v>46090.84493075847</v>
+        <v>46090.84493076389</v>
       </c>
     </row>
     <row r="994">
@@ -39200,10 +39200,10 @@
         </is>
       </c>
       <c r="H994" s="2" t="n">
-        <v>46062.84493076205</v>
+        <v>46062.84493076389</v>
       </c>
       <c r="I994" s="2" t="n">
-        <v>46067.84493076205</v>
+        <v>46067.84493076389</v>
       </c>
     </row>
     <row r="995">
@@ -39239,10 +39239,10 @@
         </is>
       </c>
       <c r="H995" s="2" t="n">
-        <v>46072.84493076512</v>
+        <v>46072.84493076389</v>
       </c>
       <c r="I995" s="2" t="n">
-        <v>46077.84493076512</v>
+        <v>46077.84493076389</v>
       </c>
     </row>
     <row r="996">
@@ -39278,10 +39278,10 @@
         </is>
       </c>
       <c r="H996" s="2" t="n">
-        <v>46071.84493076826</v>
+        <v>46071.84493076389</v>
       </c>
       <c r="I996" s="2" t="n">
-        <v>46076.84493076826</v>
+        <v>46076.84493076389</v>
       </c>
     </row>
     <row r="997">
@@ -39317,10 +39317,10 @@
         </is>
       </c>
       <c r="H997" s="2" t="n">
-        <v>46077.84493077166</v>
+        <v>46077.84493077546</v>
       </c>
       <c r="I997" s="2" t="n">
-        <v>46082.84493077166</v>
+        <v>46082.84493077546</v>
       </c>
     </row>
     <row r="998">
@@ -39356,10 +39356,10 @@
         </is>
       </c>
       <c r="H998" s="2" t="n">
-        <v>46081.84493077474</v>
+        <v>46081.84493077546</v>
       </c>
       <c r="I998" s="2" t="n">
-        <v>46086.84493077474</v>
+        <v>46086.84493077546</v>
       </c>
     </row>
     <row r="999">
@@ -39395,10 +39395,10 @@
         </is>
       </c>
       <c r="H999" s="2" t="n">
-        <v>46061.84493077818</v>
+        <v>46061.84493077546</v>
       </c>
       <c r="I999" s="2" t="n">
-        <v>46066.84493077818</v>
+        <v>46066.84493077546</v>
       </c>
     </row>
     <row r="1000">
@@ -39434,10 +39434,10 @@
         </is>
       </c>
       <c r="H1000" s="2" t="n">
-        <v>46065.84493078132</v>
+        <v>46065.84493078704</v>
       </c>
       <c r="I1000" s="2" t="n">
-        <v>46070.84493078132</v>
+        <v>46070.84493078704</v>
       </c>
     </row>
     <row r="1001">
@@ -39473,10 +39473,1960 @@
         </is>
       </c>
       <c r="H1001" s="2" t="n">
-        <v>46075.84493078457</v>
+        <v>46075.84493078704</v>
       </c>
       <c r="I1001" s="2" t="n">
-        <v>46080.84493078457</v>
+        <v>46080.84493078704</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>875050a1-b0ef-4e94-86df-99e81c6c7ac8</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>2150.8</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>98.09</v>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1002" s="2" t="n">
+        <v>46064.88617045216</v>
+      </c>
+      <c r="I1002" s="2" t="n">
+        <v>46069.88617045216</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>f3362f22-aeca-4338-ba01-0fd14eab7ebc</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>5755.49</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>99.33</v>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1003" s="2" t="n">
+        <v>46059.88617045641</v>
+      </c>
+      <c r="I1003" s="2" t="n">
+        <v>46064.88617045641</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>d17de870-ea0d-4ca1-981f-7a372f1cc3ed</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>2478.39</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1004" s="2" t="n">
+        <v>46082.88617045945</v>
+      </c>
+      <c r="I1004" s="2" t="n">
+        <v>46087.88617045945</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>085d94d0-bba5-4ede-8990-ac9d7715c717</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>8785.66</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1005" s="2" t="n">
+        <v>46062.88617046311</v>
+      </c>
+      <c r="I1005" s="2" t="n">
+        <v>46067.88617046311</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>dfc41205-7812-4be0-b610-292704959829</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>90.94</v>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1006" s="2" t="n">
+        <v>46072.88617046604</v>
+      </c>
+      <c r="I1006" s="2" t="n">
+        <v>46077.88617046604</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>34e52add-1e4c-4f41-9352-cb81d8e52b35</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>6054.65</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1007" s="2" t="n">
+        <v>46077.88617046904</v>
+      </c>
+      <c r="I1007" s="2" t="n">
+        <v>46082.88617046904</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>03be5c79-3899-4ed0-8795-ce3f154a3fc3</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>2062.16</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>93.68000000000001</v>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1008" s="2" t="n">
+        <v>46075.88617047207</v>
+      </c>
+      <c r="I1008" s="2" t="n">
+        <v>46080.88617047207</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>cd51a6aa-170b-4a6e-957b-c1a47c6b694e</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>6099.19</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1009" s="2" t="n">
+        <v>46080.88617047514</v>
+      </c>
+      <c r="I1009" s="2" t="n">
+        <v>46085.88617047514</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>55eae441-a279-4cc0-85e1-b065a1b05edb</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>6872.59</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1010" s="2" t="n">
+        <v>46068.88617047802</v>
+      </c>
+      <c r="I1010" s="2" t="n">
+        <v>46073.88617047802</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>f4a7d138-c478-4311-a08b-20a94c868aec</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>6220.55</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>98.17</v>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1011" s="2" t="n">
+        <v>46070.88617048087</v>
+      </c>
+      <c r="I1011" s="2" t="n">
+        <v>46075.88617048087</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>74257408-7a9f-4c95-978a-026cadefec3e</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>7084.85</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1012" s="2" t="n">
+        <v>46067.88617048383</v>
+      </c>
+      <c r="I1012" s="2" t="n">
+        <v>46072.88617048383</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>f2bc2587-8dfc-4747-8f1b-4f93a4a4b188</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>7740.42</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>96.94</v>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1013" s="2" t="n">
+        <v>46066.88617048682</v>
+      </c>
+      <c r="I1013" s="2" t="n">
+        <v>46071.88617048682</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>45c2bb71-eb62-4e4a-9282-2cafa0d9d95a</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>2540.17</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1014" s="2" t="n">
+        <v>46087.88617048982</v>
+      </c>
+      <c r="I1014" s="2" t="n">
+        <v>46092.88617048982</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>5c13ff06-e031-42b0-9395-8136eb255c62</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>5438.97</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1015" s="2" t="n">
+        <v>46060.88617049275</v>
+      </c>
+      <c r="I1015" s="2" t="n">
+        <v>46065.88617049275</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>32f54874-ada2-4f62-8679-58e497aa4a82</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>4220.15</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1016" s="2" t="n">
+        <v>46072.88617049567</v>
+      </c>
+      <c r="I1016" s="2" t="n">
+        <v>46077.88617049567</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>54588a3b-e495-4748-a156-7f1eefb878ad</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>8370.129999999999</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1017" s="2" t="n">
+        <v>46064.88617049868</v>
+      </c>
+      <c r="I1017" s="2" t="n">
+        <v>46069.88617049868</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>e4ee32e5-7e60-45eb-a213-c679be87c8bf</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>7919.93</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1018" s="2" t="n">
+        <v>46077.88617050152</v>
+      </c>
+      <c r="I1018" s="2" t="n">
+        <v>46082.88617050152</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>3c7f8b0c-0c18-4be1-9f2a-2025c68e1257</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>7898.28</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1019" s="2" t="n">
+        <v>46087.88617050457</v>
+      </c>
+      <c r="I1019" s="2" t="n">
+        <v>46092.88617050457</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>81deb3c4-c0a5-4a5f-b5c4-3576d080737e</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>5519</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1020" s="2" t="n">
+        <v>46060.88617050766</v>
+      </c>
+      <c r="I1020" s="2" t="n">
+        <v>46065.88617050766</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>e6d9ae79-3ecf-4735-bd91-f7bb2e52b5a3</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>7388.96</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1021" s="2" t="n">
+        <v>46077.88617051047</v>
+      </c>
+      <c r="I1021" s="2" t="n">
+        <v>46082.88617051047</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>480b6348-d27b-421f-a0f2-08e1c021db70</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>2608.53</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1022" s="2" t="n">
+        <v>46074.8861705133</v>
+      </c>
+      <c r="I1022" s="2" t="n">
+        <v>46079.8861705133</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>415db6e1-e911-403d-848a-949773067834</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>2695.84</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1023" s="2" t="n">
+        <v>46069.88617051615</v>
+      </c>
+      <c r="I1023" s="2" t="n">
+        <v>46074.88617051615</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>ab24f9d3-e916-4b00-8d41-19126de3f241</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>5543.05</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1024" s="2" t="n">
+        <v>46059.88617051918</v>
+      </c>
+      <c r="I1024" s="2" t="n">
+        <v>46064.88617051918</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>a3d3aadc-5143-4b43-ac28-e76e9f4d6e06</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>6747.36</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1025" s="2" t="n">
+        <v>46079.88617052201</v>
+      </c>
+      <c r="I1025" s="2" t="n">
+        <v>46084.88617052201</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2fbdead1-9d5c-499f-af78-1bf7785c6052</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>5885.18</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1026" s="2" t="n">
+        <v>46070.88617052481</v>
+      </c>
+      <c r="I1026" s="2" t="n">
+        <v>46075.88617052481</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>7ba5b19f-ee0e-4d03-b8fd-c9107a28308e</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>2401.61</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>89.62</v>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1027" s="2" t="n">
+        <v>46066.8861705278</v>
+      </c>
+      <c r="I1027" s="2" t="n">
+        <v>46071.8861705278</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>871552f8-cbb3-463f-9db0-e3aba46857ec</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>4596.55</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1028" s="2" t="n">
+        <v>46066.88617053084</v>
+      </c>
+      <c r="I1028" s="2" t="n">
+        <v>46071.88617053084</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>32624650-aba6-436c-86dd-200e54a8f336</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>9180.959999999999</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1029" s="2" t="n">
+        <v>46079.88617053386</v>
+      </c>
+      <c r="I1029" s="2" t="n">
+        <v>46084.88617053386</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>ceb9a8fb-089a-4db7-9ecf-e7ff7bd42b95</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>2708.73</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1030" s="2" t="n">
+        <v>46071.88617053667</v>
+      </c>
+      <c r="I1030" s="2" t="n">
+        <v>46076.88617053667</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>85529bde-7020-4411-afb1-c1de2aee00a2</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>7368.08</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1031" s="2" t="n">
+        <v>46074.88617053944</v>
+      </c>
+      <c r="I1031" s="2" t="n">
+        <v>46079.88617053944</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>04993d78-9dd2-4545-b5af-6d94a67541d9</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>2784.61</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1032" s="2" t="n">
+        <v>46076.8861705426</v>
+      </c>
+      <c r="I1032" s="2" t="n">
+        <v>46081.8861705426</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>43d41146-64a8-4730-84e5-1f233298a0f2</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>2159.43</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>96.53</v>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1033" s="2" t="n">
+        <v>46059.8861705454</v>
+      </c>
+      <c r="I1033" s="2" t="n">
+        <v>46064.8861705454</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>da4fcc85-22ac-481b-addf-21e4047018ac</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>3285.57</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1034" s="2" t="n">
+        <v>46077.88617054823</v>
+      </c>
+      <c r="I1034" s="2" t="n">
+        <v>46082.88617054823</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>8c099825-0e00-42ab-aed1-9bcc3ce88c9c</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>7489</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1035" s="2" t="n">
+        <v>46087.88617055114</v>
+      </c>
+      <c r="I1035" s="2" t="n">
+        <v>46092.88617055114</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>0fa0c178-3331-4262-b3b0-2cecb4f0129f</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>4868.19</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1036" s="2" t="n">
+        <v>46064.88617055416</v>
+      </c>
+      <c r="I1036" s="2" t="n">
+        <v>46069.88617055416</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>e6b70cec-a923-431b-9ae6-3bd1d9a5012a</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>9884.110000000001</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1037" s="2" t="n">
+        <v>46087.88617055702</v>
+      </c>
+      <c r="I1037" s="2" t="n">
+        <v>46092.88617055702</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>73fc9a67-9098-4274-86cf-310aa345714e</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>1947.38</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1038" s="2" t="n">
+        <v>46076.88617055984</v>
+      </c>
+      <c r="I1038" s="2" t="n">
+        <v>46081.88617055984</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>bcc971a8-905a-4f4b-b4aa-d274c37721f4</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>3647.8</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1039" s="2" t="n">
+        <v>46074.88617056284</v>
+      </c>
+      <c r="I1039" s="2" t="n">
+        <v>46079.88617056284</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>b9d3e107-be28-4d4d-a16d-f3c09866bdb8</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>4178.11</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1040" s="2" t="n">
+        <v>46066.88617056587</v>
+      </c>
+      <c r="I1040" s="2" t="n">
+        <v>46071.88617056587</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>c206dd25-25cb-48f8-8fb2-f2e135c6db25</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>4021.07</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1041" s="2" t="n">
+        <v>46080.88617056867</v>
+      </c>
+      <c r="I1041" s="2" t="n">
+        <v>46085.88617056867</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>61cbdc40-c5de-482d-ab85-16f77a521bae</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>8656.530000000001</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>85.55</v>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1042" s="2" t="n">
+        <v>46076.88617057173</v>
+      </c>
+      <c r="I1042" s="2" t="n">
+        <v>46081.88617057173</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>90ff5adf-5551-458a-b72f-334fa6cdb1ea</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>6802.77</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1043" s="2" t="n">
+        <v>46068.88617057456</v>
+      </c>
+      <c r="I1043" s="2" t="n">
+        <v>46073.88617057456</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>45ec2436-9667-4e3c-abbd-8aee014e4f70</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>5414.75</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>90.41</v>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1044" s="2" t="n">
+        <v>46060.88617057751</v>
+      </c>
+      <c r="I1044" s="2" t="n">
+        <v>46065.88617057751</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>cd540633-7ba7-4907-9339-c0c06ee5d9af</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>5872.81</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1045" s="2" t="n">
+        <v>46070.88617058032</v>
+      </c>
+      <c r="I1045" s="2" t="n">
+        <v>46075.88617058032</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>1ce6cef6-2824-4c10-9906-cda4277265e1</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>1315.84</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>85.76000000000001</v>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1046" s="2" t="n">
+        <v>46059.88617058318</v>
+      </c>
+      <c r="I1046" s="2" t="n">
+        <v>46064.88617058318</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>ea18cdc6-44ec-4839-8a92-88e7dea25555</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>4015.67</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1047" s="2" t="n">
+        <v>46063.88617058604</v>
+      </c>
+      <c r="I1047" s="2" t="n">
+        <v>46068.88617058604</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>e3705764-7a95-4cca-9546-4cc768c99e09</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>1248.55</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1048" s="2" t="n">
+        <v>46071.88617058911</v>
+      </c>
+      <c r="I1048" s="2" t="n">
+        <v>46076.88617058911</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>514839d7-a1bd-43bf-938e-012c877db275</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>7046.42</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1049" s="2" t="n">
+        <v>46076.88617059199</v>
+      </c>
+      <c r="I1049" s="2" t="n">
+        <v>46081.88617059199</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>033f7bb8-f6c4-4624-ac08-cac683c3d702</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>1051.88</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>93.91</v>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1050" s="2" t="n">
+        <v>46072.88617059489</v>
+      </c>
+      <c r="I1050" s="2" t="n">
+        <v>46077.88617059489</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>b391d8c4-66f0-4f6a-b27d-48a27a466082</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>5074.42</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>94.64</v>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1051" s="2" t="n">
+        <v>46082.88617059783</v>
+      </c>
+      <c r="I1051" s="2" t="n">
+        <v>46087.88617059783</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1051"/>
+  <dimension ref="A1:I1101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39512,10 +39512,10 @@
         </is>
       </c>
       <c r="H1002" s="2" t="n">
-        <v>46064.88617045216</v>
+        <v>46064.88617045139</v>
       </c>
       <c r="I1002" s="2" t="n">
-        <v>46069.88617045216</v>
+        <v>46069.88617045139</v>
       </c>
     </row>
     <row r="1003">
@@ -39551,10 +39551,10 @@
         </is>
       </c>
       <c r="H1003" s="2" t="n">
-        <v>46059.88617045641</v>
+        <v>46059.88617045139</v>
       </c>
       <c r="I1003" s="2" t="n">
-        <v>46064.88617045641</v>
+        <v>46064.88617045139</v>
       </c>
     </row>
     <row r="1004">
@@ -39590,10 +39590,10 @@
         </is>
       </c>
       <c r="H1004" s="2" t="n">
-        <v>46082.88617045945</v>
+        <v>46082.88617046296</v>
       </c>
       <c r="I1004" s="2" t="n">
-        <v>46087.88617045945</v>
+        <v>46087.88617046296</v>
       </c>
     </row>
     <row r="1005">
@@ -39629,10 +39629,10 @@
         </is>
       </c>
       <c r="H1005" s="2" t="n">
-        <v>46062.88617046311</v>
+        <v>46062.88617046296</v>
       </c>
       <c r="I1005" s="2" t="n">
-        <v>46067.88617046311</v>
+        <v>46067.88617046296</v>
       </c>
     </row>
     <row r="1006">
@@ -39668,10 +39668,10 @@
         </is>
       </c>
       <c r="H1006" s="2" t="n">
-        <v>46072.88617046604</v>
+        <v>46072.88617046296</v>
       </c>
       <c r="I1006" s="2" t="n">
-        <v>46077.88617046604</v>
+        <v>46077.88617046296</v>
       </c>
     </row>
     <row r="1007">
@@ -39707,10 +39707,10 @@
         </is>
       </c>
       <c r="H1007" s="2" t="n">
-        <v>46077.88617046904</v>
+        <v>46077.88617047454</v>
       </c>
       <c r="I1007" s="2" t="n">
-        <v>46082.88617046904</v>
+        <v>46082.88617047454</v>
       </c>
     </row>
     <row r="1008">
@@ -39746,10 +39746,10 @@
         </is>
       </c>
       <c r="H1008" s="2" t="n">
-        <v>46075.88617047207</v>
+        <v>46075.88617047454</v>
       </c>
       <c r="I1008" s="2" t="n">
-        <v>46080.88617047207</v>
+        <v>46080.88617047454</v>
       </c>
     </row>
     <row r="1009">
@@ -39785,10 +39785,10 @@
         </is>
       </c>
       <c r="H1009" s="2" t="n">
-        <v>46080.88617047514</v>
+        <v>46080.88617047454</v>
       </c>
       <c r="I1009" s="2" t="n">
-        <v>46085.88617047514</v>
+        <v>46085.88617047454</v>
       </c>
     </row>
     <row r="1010">
@@ -39824,10 +39824,10 @@
         </is>
       </c>
       <c r="H1010" s="2" t="n">
-        <v>46068.88617047802</v>
+        <v>46068.88617047454</v>
       </c>
       <c r="I1010" s="2" t="n">
-        <v>46073.88617047802</v>
+        <v>46073.88617047454</v>
       </c>
     </row>
     <row r="1011">
@@ -39863,10 +39863,10 @@
         </is>
       </c>
       <c r="H1011" s="2" t="n">
-        <v>46070.88617048087</v>
+        <v>46070.88617048611</v>
       </c>
       <c r="I1011" s="2" t="n">
-        <v>46075.88617048087</v>
+        <v>46075.88617048611</v>
       </c>
     </row>
     <row r="1012">
@@ -39902,10 +39902,10 @@
         </is>
       </c>
       <c r="H1012" s="2" t="n">
-        <v>46067.88617048383</v>
+        <v>46067.88617048611</v>
       </c>
       <c r="I1012" s="2" t="n">
-        <v>46072.88617048383</v>
+        <v>46072.88617048611</v>
       </c>
     </row>
     <row r="1013">
@@ -39941,10 +39941,10 @@
         </is>
       </c>
       <c r="H1013" s="2" t="n">
-        <v>46066.88617048682</v>
+        <v>46066.88617048611</v>
       </c>
       <c r="I1013" s="2" t="n">
-        <v>46071.88617048682</v>
+        <v>46071.88617048611</v>
       </c>
     </row>
     <row r="1014">
@@ -39980,10 +39980,10 @@
         </is>
       </c>
       <c r="H1014" s="2" t="n">
-        <v>46087.88617048982</v>
+        <v>46087.88617048611</v>
       </c>
       <c r="I1014" s="2" t="n">
-        <v>46092.88617048982</v>
+        <v>46092.88617048611</v>
       </c>
     </row>
     <row r="1015">
@@ -40019,10 +40019,10 @@
         </is>
       </c>
       <c r="H1015" s="2" t="n">
-        <v>46060.88617049275</v>
+        <v>46060.88617049769</v>
       </c>
       <c r="I1015" s="2" t="n">
-        <v>46065.88617049275</v>
+        <v>46065.88617049769</v>
       </c>
     </row>
     <row r="1016">
@@ -40058,10 +40058,10 @@
         </is>
       </c>
       <c r="H1016" s="2" t="n">
-        <v>46072.88617049567</v>
+        <v>46072.88617049769</v>
       </c>
       <c r="I1016" s="2" t="n">
-        <v>46077.88617049567</v>
+        <v>46077.88617049769</v>
       </c>
     </row>
     <row r="1017">
@@ -40097,10 +40097,10 @@
         </is>
       </c>
       <c r="H1017" s="2" t="n">
-        <v>46064.88617049868</v>
+        <v>46064.88617049769</v>
       </c>
       <c r="I1017" s="2" t="n">
-        <v>46069.88617049868</v>
+        <v>46069.88617049769</v>
       </c>
     </row>
     <row r="1018">
@@ -40136,10 +40136,10 @@
         </is>
       </c>
       <c r="H1018" s="2" t="n">
-        <v>46077.88617050152</v>
+        <v>46077.88617049769</v>
       </c>
       <c r="I1018" s="2" t="n">
-        <v>46082.88617050152</v>
+        <v>46082.88617049769</v>
       </c>
     </row>
     <row r="1019">
@@ -40175,10 +40175,10 @@
         </is>
       </c>
       <c r="H1019" s="2" t="n">
-        <v>46087.88617050457</v>
+        <v>46087.88617050926</v>
       </c>
       <c r="I1019" s="2" t="n">
-        <v>46092.88617050457</v>
+        <v>46092.88617050926</v>
       </c>
     </row>
     <row r="1020">
@@ -40214,10 +40214,10 @@
         </is>
       </c>
       <c r="H1020" s="2" t="n">
-        <v>46060.88617050766</v>
+        <v>46060.88617050926</v>
       </c>
       <c r="I1020" s="2" t="n">
-        <v>46065.88617050766</v>
+        <v>46065.88617050926</v>
       </c>
     </row>
     <row r="1021">
@@ -40253,10 +40253,10 @@
         </is>
       </c>
       <c r="H1021" s="2" t="n">
-        <v>46077.88617051047</v>
+        <v>46077.88617050926</v>
       </c>
       <c r="I1021" s="2" t="n">
-        <v>46082.88617051047</v>
+        <v>46082.88617050926</v>
       </c>
     </row>
     <row r="1022">
@@ -40292,10 +40292,10 @@
         </is>
       </c>
       <c r="H1022" s="2" t="n">
-        <v>46074.8861705133</v>
+        <v>46074.88617050926</v>
       </c>
       <c r="I1022" s="2" t="n">
-        <v>46079.8861705133</v>
+        <v>46079.88617050926</v>
       </c>
     </row>
     <row r="1023">
@@ -40331,10 +40331,10 @@
         </is>
       </c>
       <c r="H1023" s="2" t="n">
-        <v>46069.88617051615</v>
+        <v>46069.88617052083</v>
       </c>
       <c r="I1023" s="2" t="n">
-        <v>46074.88617051615</v>
+        <v>46074.88617052083</v>
       </c>
     </row>
     <row r="1024">
@@ -40370,10 +40370,10 @@
         </is>
       </c>
       <c r="H1024" s="2" t="n">
-        <v>46059.88617051918</v>
+        <v>46059.88617052083</v>
       </c>
       <c r="I1024" s="2" t="n">
-        <v>46064.88617051918</v>
+        <v>46064.88617052083</v>
       </c>
     </row>
     <row r="1025">
@@ -40409,10 +40409,10 @@
         </is>
       </c>
       <c r="H1025" s="2" t="n">
-        <v>46079.88617052201</v>
+        <v>46079.88617052083</v>
       </c>
       <c r="I1025" s="2" t="n">
-        <v>46084.88617052201</v>
+        <v>46084.88617052083</v>
       </c>
     </row>
     <row r="1026">
@@ -40448,10 +40448,10 @@
         </is>
       </c>
       <c r="H1026" s="2" t="n">
-        <v>46070.88617052481</v>
+        <v>46070.88617052083</v>
       </c>
       <c r="I1026" s="2" t="n">
-        <v>46075.88617052481</v>
+        <v>46075.88617052083</v>
       </c>
     </row>
     <row r="1027">
@@ -40487,10 +40487,10 @@
         </is>
       </c>
       <c r="H1027" s="2" t="n">
-        <v>46066.8861705278</v>
+        <v>46066.88617053241</v>
       </c>
       <c r="I1027" s="2" t="n">
-        <v>46071.8861705278</v>
+        <v>46071.88617053241</v>
       </c>
     </row>
     <row r="1028">
@@ -40526,10 +40526,10 @@
         </is>
       </c>
       <c r="H1028" s="2" t="n">
-        <v>46066.88617053084</v>
+        <v>46066.88617053241</v>
       </c>
       <c r="I1028" s="2" t="n">
-        <v>46071.88617053084</v>
+        <v>46071.88617053241</v>
       </c>
     </row>
     <row r="1029">
@@ -40565,10 +40565,10 @@
         </is>
       </c>
       <c r="H1029" s="2" t="n">
-        <v>46079.88617053386</v>
+        <v>46079.88617053241</v>
       </c>
       <c r="I1029" s="2" t="n">
-        <v>46084.88617053386</v>
+        <v>46084.88617053241</v>
       </c>
     </row>
     <row r="1030">
@@ -40604,10 +40604,10 @@
         </is>
       </c>
       <c r="H1030" s="2" t="n">
-        <v>46071.88617053667</v>
+        <v>46071.88617053241</v>
       </c>
       <c r="I1030" s="2" t="n">
-        <v>46076.88617053667</v>
+        <v>46076.88617053241</v>
       </c>
     </row>
     <row r="1031">
@@ -40643,10 +40643,10 @@
         </is>
       </c>
       <c r="H1031" s="2" t="n">
-        <v>46074.88617053944</v>
+        <v>46074.88617054398</v>
       </c>
       <c r="I1031" s="2" t="n">
-        <v>46079.88617053944</v>
+        <v>46079.88617054398</v>
       </c>
     </row>
     <row r="1032">
@@ -40682,10 +40682,10 @@
         </is>
       </c>
       <c r="H1032" s="2" t="n">
-        <v>46076.8861705426</v>
+        <v>46076.88617054398</v>
       </c>
       <c r="I1032" s="2" t="n">
-        <v>46081.8861705426</v>
+        <v>46081.88617054398</v>
       </c>
     </row>
     <row r="1033">
@@ -40721,10 +40721,10 @@
         </is>
       </c>
       <c r="H1033" s="2" t="n">
-        <v>46059.8861705454</v>
+        <v>46059.88617054398</v>
       </c>
       <c r="I1033" s="2" t="n">
-        <v>46064.8861705454</v>
+        <v>46064.88617054398</v>
       </c>
     </row>
     <row r="1034">
@@ -40760,10 +40760,10 @@
         </is>
       </c>
       <c r="H1034" s="2" t="n">
-        <v>46077.88617054823</v>
+        <v>46077.88617054398</v>
       </c>
       <c r="I1034" s="2" t="n">
-        <v>46082.88617054823</v>
+        <v>46082.88617054398</v>
       </c>
     </row>
     <row r="1035">
@@ -40799,10 +40799,10 @@
         </is>
       </c>
       <c r="H1035" s="2" t="n">
-        <v>46087.88617055114</v>
+        <v>46087.88617055555</v>
       </c>
       <c r="I1035" s="2" t="n">
-        <v>46092.88617055114</v>
+        <v>46092.88617055555</v>
       </c>
     </row>
     <row r="1036">
@@ -40838,10 +40838,10 @@
         </is>
       </c>
       <c r="H1036" s="2" t="n">
-        <v>46064.88617055416</v>
+        <v>46064.88617055555</v>
       </c>
       <c r="I1036" s="2" t="n">
-        <v>46069.88617055416</v>
+        <v>46069.88617055555</v>
       </c>
     </row>
     <row r="1037">
@@ -40877,10 +40877,10 @@
         </is>
       </c>
       <c r="H1037" s="2" t="n">
-        <v>46087.88617055702</v>
+        <v>46087.88617055555</v>
       </c>
       <c r="I1037" s="2" t="n">
-        <v>46092.88617055702</v>
+        <v>46092.88617055555</v>
       </c>
     </row>
     <row r="1038">
@@ -40916,10 +40916,10 @@
         </is>
       </c>
       <c r="H1038" s="2" t="n">
-        <v>46076.88617055984</v>
+        <v>46076.88617055555</v>
       </c>
       <c r="I1038" s="2" t="n">
-        <v>46081.88617055984</v>
+        <v>46081.88617055555</v>
       </c>
     </row>
     <row r="1039">
@@ -40955,10 +40955,10 @@
         </is>
       </c>
       <c r="H1039" s="2" t="n">
-        <v>46074.88617056284</v>
+        <v>46074.88617056713</v>
       </c>
       <c r="I1039" s="2" t="n">
-        <v>46079.88617056284</v>
+        <v>46079.88617056713</v>
       </c>
     </row>
     <row r="1040">
@@ -40994,10 +40994,10 @@
         </is>
       </c>
       <c r="H1040" s="2" t="n">
-        <v>46066.88617056587</v>
+        <v>46066.88617056713</v>
       </c>
       <c r="I1040" s="2" t="n">
-        <v>46071.88617056587</v>
+        <v>46071.88617056713</v>
       </c>
     </row>
     <row r="1041">
@@ -41033,10 +41033,10 @@
         </is>
       </c>
       <c r="H1041" s="2" t="n">
-        <v>46080.88617056867</v>
+        <v>46080.88617056713</v>
       </c>
       <c r="I1041" s="2" t="n">
-        <v>46085.88617056867</v>
+        <v>46085.88617056713</v>
       </c>
     </row>
     <row r="1042">
@@ -41072,10 +41072,10 @@
         </is>
       </c>
       <c r="H1042" s="2" t="n">
-        <v>46076.88617057173</v>
+        <v>46076.88617056713</v>
       </c>
       <c r="I1042" s="2" t="n">
-        <v>46081.88617057173</v>
+        <v>46081.88617056713</v>
       </c>
     </row>
     <row r="1043">
@@ -41111,10 +41111,10 @@
         </is>
       </c>
       <c r="H1043" s="2" t="n">
-        <v>46068.88617057456</v>
+        <v>46068.88617057871</v>
       </c>
       <c r="I1043" s="2" t="n">
-        <v>46073.88617057456</v>
+        <v>46073.88617057871</v>
       </c>
     </row>
     <row r="1044">
@@ -41150,10 +41150,10 @@
         </is>
       </c>
       <c r="H1044" s="2" t="n">
-        <v>46060.88617057751</v>
+        <v>46060.88617057871</v>
       </c>
       <c r="I1044" s="2" t="n">
-        <v>46065.88617057751</v>
+        <v>46065.88617057871</v>
       </c>
     </row>
     <row r="1045">
@@ -41189,10 +41189,10 @@
         </is>
       </c>
       <c r="H1045" s="2" t="n">
-        <v>46070.88617058032</v>
+        <v>46070.88617057871</v>
       </c>
       <c r="I1045" s="2" t="n">
-        <v>46075.88617058032</v>
+        <v>46075.88617057871</v>
       </c>
     </row>
     <row r="1046">
@@ -41228,10 +41228,10 @@
         </is>
       </c>
       <c r="H1046" s="2" t="n">
-        <v>46059.88617058318</v>
+        <v>46059.88617057871</v>
       </c>
       <c r="I1046" s="2" t="n">
-        <v>46064.88617058318</v>
+        <v>46064.88617057871</v>
       </c>
     </row>
     <row r="1047">
@@ -41267,10 +41267,10 @@
         </is>
       </c>
       <c r="H1047" s="2" t="n">
-        <v>46063.88617058604</v>
+        <v>46063.88617059027</v>
       </c>
       <c r="I1047" s="2" t="n">
-        <v>46068.88617058604</v>
+        <v>46068.88617059027</v>
       </c>
     </row>
     <row r="1048">
@@ -41306,10 +41306,10 @@
         </is>
       </c>
       <c r="H1048" s="2" t="n">
-        <v>46071.88617058911</v>
+        <v>46071.88617059027</v>
       </c>
       <c r="I1048" s="2" t="n">
-        <v>46076.88617058911</v>
+        <v>46076.88617059027</v>
       </c>
     </row>
     <row r="1049">
@@ -41345,10 +41345,10 @@
         </is>
       </c>
       <c r="H1049" s="2" t="n">
-        <v>46076.88617059199</v>
+        <v>46076.88617059027</v>
       </c>
       <c r="I1049" s="2" t="n">
-        <v>46081.88617059199</v>
+        <v>46081.88617059027</v>
       </c>
     </row>
     <row r="1050">
@@ -41384,10 +41384,10 @@
         </is>
       </c>
       <c r="H1050" s="2" t="n">
-        <v>46072.88617059489</v>
+        <v>46072.88617059027</v>
       </c>
       <c r="I1050" s="2" t="n">
-        <v>46077.88617059489</v>
+        <v>46077.88617059027</v>
       </c>
     </row>
     <row r="1051">
@@ -41423,10 +41423,1960 @@
         </is>
       </c>
       <c r="H1051" s="2" t="n">
-        <v>46082.88617059783</v>
+        <v>46082.88617060185</v>
       </c>
       <c r="I1051" s="2" t="n">
-        <v>46087.88617059783</v>
+        <v>46087.88617060185</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>e16dabbd-1d2f-4339-b1cc-80a62f94afdf</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>5864.03</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1052" s="2" t="n">
+        <v>46087.92765186141</v>
+      </c>
+      <c r="I1052" s="2" t="n">
+        <v>46092.92765186141</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>8f839f88-f48b-488a-a964-44395f0703cf</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>1686.73</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1053" s="2" t="n">
+        <v>46075.92765186596</v>
+      </c>
+      <c r="I1053" s="2" t="n">
+        <v>46080.92765186596</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>75590bbb-a494-4465-808f-fb6b375fdadc</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>6017.72</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1054" s="2" t="n">
+        <v>46064.92765186915</v>
+      </c>
+      <c r="I1054" s="2" t="n">
+        <v>46069.92765186915</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>c05580c4-7618-4be4-bd64-e4761cfbd829</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>1166.94</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1055" s="2" t="n">
+        <v>46078.92765187251</v>
+      </c>
+      <c r="I1055" s="2" t="n">
+        <v>46083.92765187251</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>5c262d93-398c-47a2-aaec-f5b18e59b71c</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>9174.719999999999</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1056" s="2" t="n">
+        <v>46073.92765187576</v>
+      </c>
+      <c r="I1056" s="2" t="n">
+        <v>46078.92765187576</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>3a1e969f-61d3-4dfb-af1d-5f71b64e4e69</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>6672.59</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1057" s="2" t="n">
+        <v>46063.92765187928</v>
+      </c>
+      <c r="I1057" s="2" t="n">
+        <v>46068.92765187928</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>4c69d7c4-4f6b-494a-a86f-5c2db622892c</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>2707.91</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1058" s="2" t="n">
+        <v>46061.9276518825</v>
+      </c>
+      <c r="I1058" s="2" t="n">
+        <v>46066.9276518825</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>a1a0e509-e7f5-4cfa-ac65-796dee233ff3</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>4029.89</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1059" s="2" t="n">
+        <v>46065.9276518856</v>
+      </c>
+      <c r="I1059" s="2" t="n">
+        <v>46070.9276518856</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>7e5f596b-c489-4bd7-bfc2-a71c88138893</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>8690.6</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1060" s="2" t="n">
+        <v>46068.92765188897</v>
+      </c>
+      <c r="I1060" s="2" t="n">
+        <v>46073.92765188897</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>a5f22db9-f22c-48bf-8821-f090f0715fdc</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>3938.14</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1061" s="2" t="n">
+        <v>46063.92765189202</v>
+      </c>
+      <c r="I1061" s="2" t="n">
+        <v>46068.92765189202</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>a0fc3a9a-6d1d-4ceb-a400-06e51faa868d</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>9442.440000000001</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1062" s="2" t="n">
+        <v>46072.92765189547</v>
+      </c>
+      <c r="I1062" s="2" t="n">
+        <v>46077.92765189547</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>94a7a421-2c32-4eba-b98f-00028e8790ec</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>7883.93</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1063" s="2" t="n">
+        <v>46069.9276518987</v>
+      </c>
+      <c r="I1063" s="2" t="n">
+        <v>46074.9276518987</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>e2bf5eb7-0b52-4bfb-bd7c-6f9307596561</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>4015.67</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1064" s="2" t="n">
+        <v>46078.92765190226</v>
+      </c>
+      <c r="I1064" s="2" t="n">
+        <v>46083.92765190226</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2462299b-6b78-4a77-a0c9-eb548d12cbd8</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>3789.33</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>87.04000000000001</v>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1065" s="2" t="n">
+        <v>46084.92765190562</v>
+      </c>
+      <c r="I1065" s="2" t="n">
+        <v>46089.92765190562</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2a80a252-8f36-4a58-b2a7-12b46645d3dc</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>5913.7</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1066" s="2" t="n">
+        <v>46062.92765190881</v>
+      </c>
+      <c r="I1066" s="2" t="n">
+        <v>46067.92765190881</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>93cdd32c-822a-41a4-9bca-2ca6611ee24e</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>2154.96</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1067" s="2" t="n">
+        <v>46069.92765191213</v>
+      </c>
+      <c r="I1067" s="2" t="n">
+        <v>46074.92765191213</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>50bfdb89-c1b3-496e-9e23-7255dffdd35c</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>8055.64</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1068" s="2" t="n">
+        <v>46060.92765191532</v>
+      </c>
+      <c r="I1068" s="2" t="n">
+        <v>46065.92765191532</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2a4f75df-ddc8-4388-a4a0-3580f3b3bc3e</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>3641.29</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>91.17</v>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1069" s="2" t="n">
+        <v>46076.92765191841</v>
+      </c>
+      <c r="I1069" s="2" t="n">
+        <v>46081.92765191841</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>fa54045f-c307-44c2-9cb2-4da9b00ace67</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>5946.39</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>89.22</v>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1070" s="2" t="n">
+        <v>46076.92765192151</v>
+      </c>
+      <c r="I1070" s="2" t="n">
+        <v>46081.92765192151</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>d95cb3e8-2d42-4707-bf30-ba372af93d33</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>2447.98</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1071" s="2" t="n">
+        <v>46064.92765192471</v>
+      </c>
+      <c r="I1071" s="2" t="n">
+        <v>46069.92765192471</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>fd7e06d8-23a0-49fa-85f5-bf223431a177</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>7586.51</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1072" s="2" t="n">
+        <v>46079.92765192778</v>
+      </c>
+      <c r="I1072" s="2" t="n">
+        <v>46084.92765192778</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>8bf7ce47-f41d-4170-aab9-3483db575959</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>5898.13</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1073" s="2" t="n">
+        <v>46071.92765193082</v>
+      </c>
+      <c r="I1073" s="2" t="n">
+        <v>46076.92765193082</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>d75a70de-9895-4467-9f7a-1bdbe489d936</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>5853.33</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1074" s="2" t="n">
+        <v>46081.92765193393</v>
+      </c>
+      <c r="I1074" s="2" t="n">
+        <v>46086.92765193393</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>1d50234b-0f7f-410c-8b0e-74ac6adae46b</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>2207.62</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1075" s="2" t="n">
+        <v>46078.92765193714</v>
+      </c>
+      <c r="I1075" s="2" t="n">
+        <v>46083.92765193714</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>93c7e2e9-e4c5-45dd-8616-427bf268accb</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>5092.29</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1076" s="2" t="n">
+        <v>46082.92765194014</v>
+      </c>
+      <c r="I1076" s="2" t="n">
+        <v>46087.92765194014</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>3d654124-fe83-462a-b82d-21e7a83e7995</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>5537.03</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1077" s="2" t="n">
+        <v>46081.92765194343</v>
+      </c>
+      <c r="I1077" s="2" t="n">
+        <v>46086.92765194343</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>b2374eb8-5dca-4d23-86d0-74ec5777924d</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>4777.3</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1078" s="2" t="n">
+        <v>46080.92765194691</v>
+      </c>
+      <c r="I1078" s="2" t="n">
+        <v>46085.92765194691</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>0ea8d3dc-64a0-4309-ac80-8bc1f52c869e</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>9089.35</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1079" s="2" t="n">
+        <v>46063.92765195003</v>
+      </c>
+      <c r="I1079" s="2" t="n">
+        <v>46068.92765195003</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>c7bbcccf-4817-4cce-a4d4-edb90dedd086</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>8066.69</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1080" s="2" t="n">
+        <v>46061.92765195309</v>
+      </c>
+      <c r="I1080" s="2" t="n">
+        <v>46066.92765195309</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>1ef489b9-c0a7-4c55-802a-cf1b486c0db6</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>4414.65</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>91.48999999999999</v>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1081" s="2" t="n">
+        <v>46073.92765195615</v>
+      </c>
+      <c r="I1081" s="2" t="n">
+        <v>46078.92765195615</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>84d4c225-14b3-4210-a713-ce6c3e0fadee</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>1931.12</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1082" s="2" t="n">
+        <v>46079.92765195961</v>
+      </c>
+      <c r="I1082" s="2" t="n">
+        <v>46084.92765195961</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>63a26f9a-9e9b-4368-9f9b-bd08332ec7a8</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>7611.41</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1083" s="2" t="n">
+        <v>46073.92765196475</v>
+      </c>
+      <c r="I1083" s="2" t="n">
+        <v>46078.92765196475</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>60b90ee6-b3ae-40ef-bdab-ec0bdd121f56</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>6413.29</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1084" s="2" t="n">
+        <v>46071.9276519681</v>
+      </c>
+      <c r="I1084" s="2" t="n">
+        <v>46076.9276519681</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>43687e84-6d98-4596-94cb-826f028b3542</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>7285.37</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1085" s="2" t="n">
+        <v>46088.9276519718</v>
+      </c>
+      <c r="I1085" s="2" t="n">
+        <v>46093.9276519718</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>55b1e94d-9df6-4841-b5ee-5b412113e0bf</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1086" t="n">
+        <v>5171.08</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1086" s="2" t="n">
+        <v>46069.92765197485</v>
+      </c>
+      <c r="I1086" s="2" t="n">
+        <v>46074.92765197485</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>28d1062a-61f9-4818-8c75-4d8bee485c68</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1087" t="n">
+        <v>3024.52</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1087" s="2" t="n">
+        <v>46070.92765197808</v>
+      </c>
+      <c r="I1087" s="2" t="n">
+        <v>46075.92765197808</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>1f8b29aa-a9bd-4f76-b8d7-833c35008aaa</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1088" t="n">
+        <v>6906.59</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1088" s="2" t="n">
+        <v>46074.92765198134</v>
+      </c>
+      <c r="I1088" s="2" t="n">
+        <v>46079.92765198134</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>eb796adf-6fff-4250-9bce-7f3a9570c6de</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1089" t="n">
+        <v>6962.2</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1089" s="2" t="n">
+        <v>46060.92765198461</v>
+      </c>
+      <c r="I1089" s="2" t="n">
+        <v>46065.92765198461</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>1a87ac9c-baa7-406b-9aff-83ff08e44c5c</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1090" t="n">
+        <v>9692.84</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>93.09</v>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1090" s="2" t="n">
+        <v>46068.9276519878</v>
+      </c>
+      <c r="I1090" s="2" t="n">
+        <v>46073.9276519878</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>a3f4c2da-40ae-41fd-9ffe-4936e50fb01f</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1091" t="n">
+        <v>5888.05</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1091" s="2" t="n">
+        <v>46070.92765199098</v>
+      </c>
+      <c r="I1091" s="2" t="n">
+        <v>46075.92765199098</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>3a903d55-0e13-45e3-8d8d-e28bbe73d6b6</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>9784.85</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1092" s="2" t="n">
+        <v>46081.92765199434</v>
+      </c>
+      <c r="I1092" s="2" t="n">
+        <v>46086.92765199434</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>b2c3c351-caf6-4ce5-9fc6-2d9a8d2e6d46</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>3854.13</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>89.76000000000001</v>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1093" s="2" t="n">
+        <v>46081.92765199759</v>
+      </c>
+      <c r="I1093" s="2" t="n">
+        <v>46086.92765199759</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>93b274b8-690e-4871-a1c3-36862a74250c</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>3146.87</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>94.31</v>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1094" s="2" t="n">
+        <v>46061.92765200089</v>
+      </c>
+      <c r="I1094" s="2" t="n">
+        <v>46066.92765200089</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>355c8edc-4a3f-47a4-91ba-28bdbe68d261</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>2674.89</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1095" s="2" t="n">
+        <v>46059.92765200423</v>
+      </c>
+      <c r="I1095" s="2" t="n">
+        <v>46064.92765200423</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>ef4e1cc5-1f3e-4126-bc4f-0c0a79bf15c4</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>9188.379999999999</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1096" s="2" t="n">
+        <v>46061.92765200746</v>
+      </c>
+      <c r="I1096" s="2" t="n">
+        <v>46066.92765200746</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>71e58d7e-5dad-4317-a9ee-e67e85c09a63</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>8898.99</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>85.91</v>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1097" s="2" t="n">
+        <v>46076.92765201065</v>
+      </c>
+      <c r="I1097" s="2" t="n">
+        <v>46081.92765201065</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>c0dae086-5d8b-49e4-a166-551828cb440d</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>1211.5</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1098" s="2" t="n">
+        <v>46059.92765201374</v>
+      </c>
+      <c r="I1098" s="2" t="n">
+        <v>46064.92765201374</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>6a5abde0-66d5-4855-bdcf-adfda2dd7fa9</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>3174.55</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>91.81999999999999</v>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1099" s="2" t="n">
+        <v>46067.9276520173</v>
+      </c>
+      <c r="I1099" s="2" t="n">
+        <v>46072.9276520173</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>6a356440-8ea9-4a73-90c3-1051799f93dd</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>4737.61</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1100" s="2" t="n">
+        <v>46063.92765202047</v>
+      </c>
+      <c r="I1100" s="2" t="n">
+        <v>46068.92765202047</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>f514f02e-5ac1-4e8f-b47b-3a1cf2c2a90c</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>6185.22</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>87.04000000000001</v>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1101" s="2" t="n">
+        <v>46075.92765202355</v>
+      </c>
+      <c r="I1101" s="2" t="n">
+        <v>46080.92765202355</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1101"/>
+  <dimension ref="A1:I1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41462,10 +41462,10 @@
         </is>
       </c>
       <c r="H1052" s="2" t="n">
-        <v>46087.92765186141</v>
+        <v>46087.92765186343</v>
       </c>
       <c r="I1052" s="2" t="n">
-        <v>46092.92765186141</v>
+        <v>46092.92765186343</v>
       </c>
     </row>
     <row r="1053">
@@ -41501,10 +41501,10 @@
         </is>
       </c>
       <c r="H1053" s="2" t="n">
-        <v>46075.92765186596</v>
+        <v>46075.92765186343</v>
       </c>
       <c r="I1053" s="2" t="n">
-        <v>46080.92765186596</v>
+        <v>46080.92765186343</v>
       </c>
     </row>
     <row r="1054">
@@ -41540,10 +41540,10 @@
         </is>
       </c>
       <c r="H1054" s="2" t="n">
-        <v>46064.92765186915</v>
+        <v>46064.92765186343</v>
       </c>
       <c r="I1054" s="2" t="n">
-        <v>46069.92765186915</v>
+        <v>46069.92765186343</v>
       </c>
     </row>
     <row r="1055">
@@ -41579,10 +41579,10 @@
         </is>
       </c>
       <c r="H1055" s="2" t="n">
-        <v>46078.92765187251</v>
+        <v>46078.927651875</v>
       </c>
       <c r="I1055" s="2" t="n">
-        <v>46083.92765187251</v>
+        <v>46083.927651875</v>
       </c>
     </row>
     <row r="1056">
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="H1056" s="2" t="n">
-        <v>46073.92765187576</v>
+        <v>46073.927651875</v>
       </c>
       <c r="I1056" s="2" t="n">
-        <v>46078.92765187576</v>
+        <v>46078.927651875</v>
       </c>
     </row>
     <row r="1057">
@@ -41657,10 +41657,10 @@
         </is>
       </c>
       <c r="H1057" s="2" t="n">
-        <v>46063.92765187928</v>
+        <v>46063.927651875</v>
       </c>
       <c r="I1057" s="2" t="n">
-        <v>46068.92765187928</v>
+        <v>46068.927651875</v>
       </c>
     </row>
     <row r="1058">
@@ -41696,10 +41696,10 @@
         </is>
       </c>
       <c r="H1058" s="2" t="n">
-        <v>46061.9276518825</v>
+        <v>46061.92765188657</v>
       </c>
       <c r="I1058" s="2" t="n">
-        <v>46066.9276518825</v>
+        <v>46066.92765188657</v>
       </c>
     </row>
     <row r="1059">
@@ -41735,10 +41735,10 @@
         </is>
       </c>
       <c r="H1059" s="2" t="n">
-        <v>46065.9276518856</v>
+        <v>46065.92765188657</v>
       </c>
       <c r="I1059" s="2" t="n">
-        <v>46070.9276518856</v>
+        <v>46070.92765188657</v>
       </c>
     </row>
     <row r="1060">
@@ -41774,10 +41774,10 @@
         </is>
       </c>
       <c r="H1060" s="2" t="n">
-        <v>46068.92765188897</v>
+        <v>46068.92765188657</v>
       </c>
       <c r="I1060" s="2" t="n">
-        <v>46073.92765188897</v>
+        <v>46073.92765188657</v>
       </c>
     </row>
     <row r="1061">
@@ -41813,10 +41813,10 @@
         </is>
       </c>
       <c r="H1061" s="2" t="n">
-        <v>46063.92765189202</v>
+        <v>46063.92765188657</v>
       </c>
       <c r="I1061" s="2" t="n">
-        <v>46068.92765189202</v>
+        <v>46068.92765188657</v>
       </c>
     </row>
     <row r="1062">
@@ -41852,10 +41852,10 @@
         </is>
       </c>
       <c r="H1062" s="2" t="n">
-        <v>46072.92765189547</v>
+        <v>46072.92765189815</v>
       </c>
       <c r="I1062" s="2" t="n">
-        <v>46077.92765189547</v>
+        <v>46077.92765189815</v>
       </c>
     </row>
     <row r="1063">
@@ -41891,10 +41891,10 @@
         </is>
       </c>
       <c r="H1063" s="2" t="n">
-        <v>46069.9276518987</v>
+        <v>46069.92765189815</v>
       </c>
       <c r="I1063" s="2" t="n">
-        <v>46074.9276518987</v>
+        <v>46074.92765189815</v>
       </c>
     </row>
     <row r="1064">
@@ -41930,10 +41930,10 @@
         </is>
       </c>
       <c r="H1064" s="2" t="n">
-        <v>46078.92765190226</v>
+        <v>46078.92765189815</v>
       </c>
       <c r="I1064" s="2" t="n">
-        <v>46083.92765190226</v>
+        <v>46083.92765189815</v>
       </c>
     </row>
     <row r="1065">
@@ -41969,10 +41969,10 @@
         </is>
       </c>
       <c r="H1065" s="2" t="n">
-        <v>46084.92765190562</v>
+        <v>46084.92765190973</v>
       </c>
       <c r="I1065" s="2" t="n">
-        <v>46089.92765190562</v>
+        <v>46089.92765190973</v>
       </c>
     </row>
     <row r="1066">
@@ -42008,10 +42008,10 @@
         </is>
       </c>
       <c r="H1066" s="2" t="n">
-        <v>46062.92765190881</v>
+        <v>46062.92765190973</v>
       </c>
       <c r="I1066" s="2" t="n">
-        <v>46067.92765190881</v>
+        <v>46067.92765190973</v>
       </c>
     </row>
     <row r="1067">
@@ -42047,10 +42047,10 @@
         </is>
       </c>
       <c r="H1067" s="2" t="n">
-        <v>46069.92765191213</v>
+        <v>46069.92765190973</v>
       </c>
       <c r="I1067" s="2" t="n">
-        <v>46074.92765191213</v>
+        <v>46074.92765190973</v>
       </c>
     </row>
     <row r="1068">
@@ -42086,10 +42086,10 @@
         </is>
       </c>
       <c r="H1068" s="2" t="n">
-        <v>46060.92765191532</v>
+        <v>46060.92765190973</v>
       </c>
       <c r="I1068" s="2" t="n">
-        <v>46065.92765191532</v>
+        <v>46065.92765190973</v>
       </c>
     </row>
     <row r="1069">
@@ -42125,10 +42125,10 @@
         </is>
       </c>
       <c r="H1069" s="2" t="n">
-        <v>46076.92765191841</v>
+        <v>46076.92765192129</v>
       </c>
       <c r="I1069" s="2" t="n">
-        <v>46081.92765191841</v>
+        <v>46081.92765192129</v>
       </c>
     </row>
     <row r="1070">
@@ -42164,10 +42164,10 @@
         </is>
       </c>
       <c r="H1070" s="2" t="n">
-        <v>46076.92765192151</v>
+        <v>46076.92765192129</v>
       </c>
       <c r="I1070" s="2" t="n">
-        <v>46081.92765192151</v>
+        <v>46081.92765192129</v>
       </c>
     </row>
     <row r="1071">
@@ -42203,10 +42203,10 @@
         </is>
       </c>
       <c r="H1071" s="2" t="n">
-        <v>46064.92765192471</v>
+        <v>46064.92765192129</v>
       </c>
       <c r="I1071" s="2" t="n">
-        <v>46069.92765192471</v>
+        <v>46069.92765192129</v>
       </c>
     </row>
     <row r="1072">
@@ -42242,10 +42242,10 @@
         </is>
       </c>
       <c r="H1072" s="2" t="n">
-        <v>46079.92765192778</v>
+        <v>46079.92765193287</v>
       </c>
       <c r="I1072" s="2" t="n">
-        <v>46084.92765192778</v>
+        <v>46084.92765193287</v>
       </c>
     </row>
     <row r="1073">
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="H1073" s="2" t="n">
-        <v>46071.92765193082</v>
+        <v>46071.92765193287</v>
       </c>
       <c r="I1073" s="2" t="n">
-        <v>46076.92765193082</v>
+        <v>46076.92765193287</v>
       </c>
     </row>
     <row r="1074">
@@ -42320,10 +42320,10 @@
         </is>
       </c>
       <c r="H1074" s="2" t="n">
-        <v>46081.92765193393</v>
+        <v>46081.92765193287</v>
       </c>
       <c r="I1074" s="2" t="n">
-        <v>46086.92765193393</v>
+        <v>46086.92765193287</v>
       </c>
     </row>
     <row r="1075">
@@ -42359,10 +42359,10 @@
         </is>
       </c>
       <c r="H1075" s="2" t="n">
-        <v>46078.92765193714</v>
+        <v>46078.92765193287</v>
       </c>
       <c r="I1075" s="2" t="n">
-        <v>46083.92765193714</v>
+        <v>46083.92765193287</v>
       </c>
     </row>
     <row r="1076">
@@ -42398,10 +42398,10 @@
         </is>
       </c>
       <c r="H1076" s="2" t="n">
-        <v>46082.92765194014</v>
+        <v>46082.92765194445</v>
       </c>
       <c r="I1076" s="2" t="n">
-        <v>46087.92765194014</v>
+        <v>46087.92765194445</v>
       </c>
     </row>
     <row r="1077">
@@ -42437,10 +42437,10 @@
         </is>
       </c>
       <c r="H1077" s="2" t="n">
-        <v>46081.92765194343</v>
+        <v>46081.92765194445</v>
       </c>
       <c r="I1077" s="2" t="n">
-        <v>46086.92765194343</v>
+        <v>46086.92765194445</v>
       </c>
     </row>
     <row r="1078">
@@ -42476,10 +42476,10 @@
         </is>
       </c>
       <c r="H1078" s="2" t="n">
-        <v>46080.92765194691</v>
+        <v>46080.92765194445</v>
       </c>
       <c r="I1078" s="2" t="n">
-        <v>46085.92765194691</v>
+        <v>46085.92765194445</v>
       </c>
     </row>
     <row r="1079">
@@ -42515,10 +42515,10 @@
         </is>
       </c>
       <c r="H1079" s="2" t="n">
-        <v>46063.92765195003</v>
+        <v>46063.92765194445</v>
       </c>
       <c r="I1079" s="2" t="n">
-        <v>46068.92765195003</v>
+        <v>46068.92765194445</v>
       </c>
     </row>
     <row r="1080">
@@ -42554,10 +42554,10 @@
         </is>
       </c>
       <c r="H1080" s="2" t="n">
-        <v>46061.92765195309</v>
+        <v>46061.92765195602</v>
       </c>
       <c r="I1080" s="2" t="n">
-        <v>46066.92765195309</v>
+        <v>46066.92765195602</v>
       </c>
     </row>
     <row r="1081">
@@ -42593,10 +42593,10 @@
         </is>
       </c>
       <c r="H1081" s="2" t="n">
-        <v>46073.92765195615</v>
+        <v>46073.92765195602</v>
       </c>
       <c r="I1081" s="2" t="n">
-        <v>46078.92765195615</v>
+        <v>46078.92765195602</v>
       </c>
     </row>
     <row r="1082">
@@ -42632,10 +42632,10 @@
         </is>
       </c>
       <c r="H1082" s="2" t="n">
-        <v>46079.92765195961</v>
+        <v>46079.92765195602</v>
       </c>
       <c r="I1082" s="2" t="n">
-        <v>46084.92765195961</v>
+        <v>46084.92765195602</v>
       </c>
     </row>
     <row r="1083">
@@ -42671,10 +42671,10 @@
         </is>
       </c>
       <c r="H1083" s="2" t="n">
-        <v>46073.92765196475</v>
+        <v>46073.92765196759</v>
       </c>
       <c r="I1083" s="2" t="n">
-        <v>46078.92765196475</v>
+        <v>46078.92765196759</v>
       </c>
     </row>
     <row r="1084">
@@ -42710,10 +42710,10 @@
         </is>
       </c>
       <c r="H1084" s="2" t="n">
-        <v>46071.9276519681</v>
+        <v>46071.92765196759</v>
       </c>
       <c r="I1084" s="2" t="n">
-        <v>46076.9276519681</v>
+        <v>46076.92765196759</v>
       </c>
     </row>
     <row r="1085">
@@ -42749,10 +42749,10 @@
         </is>
       </c>
       <c r="H1085" s="2" t="n">
-        <v>46088.9276519718</v>
+        <v>46088.92765196759</v>
       </c>
       <c r="I1085" s="2" t="n">
-        <v>46093.9276519718</v>
+        <v>46093.92765196759</v>
       </c>
     </row>
     <row r="1086">
@@ -42788,10 +42788,10 @@
         </is>
       </c>
       <c r="H1086" s="2" t="n">
-        <v>46069.92765197485</v>
+        <v>46069.92765197917</v>
       </c>
       <c r="I1086" s="2" t="n">
-        <v>46074.92765197485</v>
+        <v>46074.92765197917</v>
       </c>
     </row>
     <row r="1087">
@@ -42827,10 +42827,10 @@
         </is>
       </c>
       <c r="H1087" s="2" t="n">
-        <v>46070.92765197808</v>
+        <v>46070.92765197917</v>
       </c>
       <c r="I1087" s="2" t="n">
-        <v>46075.92765197808</v>
+        <v>46075.92765197917</v>
       </c>
     </row>
     <row r="1088">
@@ -42866,10 +42866,10 @@
         </is>
       </c>
       <c r="H1088" s="2" t="n">
-        <v>46074.92765198134</v>
+        <v>46074.92765197917</v>
       </c>
       <c r="I1088" s="2" t="n">
-        <v>46079.92765198134</v>
+        <v>46079.92765197917</v>
       </c>
     </row>
     <row r="1089">
@@ -42905,10 +42905,10 @@
         </is>
       </c>
       <c r="H1089" s="2" t="n">
-        <v>46060.92765198461</v>
+        <v>46060.92765197917</v>
       </c>
       <c r="I1089" s="2" t="n">
-        <v>46065.92765198461</v>
+        <v>46065.92765197917</v>
       </c>
     </row>
     <row r="1090">
@@ -42944,10 +42944,10 @@
         </is>
       </c>
       <c r="H1090" s="2" t="n">
-        <v>46068.9276519878</v>
+        <v>46068.92765199074</v>
       </c>
       <c r="I1090" s="2" t="n">
-        <v>46073.9276519878</v>
+        <v>46073.92765199074</v>
       </c>
     </row>
     <row r="1091">
@@ -42983,10 +42983,10 @@
         </is>
       </c>
       <c r="H1091" s="2" t="n">
-        <v>46070.92765199098</v>
+        <v>46070.92765199074</v>
       </c>
       <c r="I1091" s="2" t="n">
-        <v>46075.92765199098</v>
+        <v>46075.92765199074</v>
       </c>
     </row>
     <row r="1092">
@@ -43022,10 +43022,10 @@
         </is>
       </c>
       <c r="H1092" s="2" t="n">
-        <v>46081.92765199434</v>
+        <v>46081.92765199074</v>
       </c>
       <c r="I1092" s="2" t="n">
-        <v>46086.92765199434</v>
+        <v>46086.92765199074</v>
       </c>
     </row>
     <row r="1093">
@@ -43061,10 +43061,10 @@
         </is>
       </c>
       <c r="H1093" s="2" t="n">
-        <v>46081.92765199759</v>
+        <v>46081.92765200231</v>
       </c>
       <c r="I1093" s="2" t="n">
-        <v>46086.92765199759</v>
+        <v>46086.92765200231</v>
       </c>
     </row>
     <row r="1094">
@@ -43100,10 +43100,10 @@
         </is>
       </c>
       <c r="H1094" s="2" t="n">
-        <v>46061.92765200089</v>
+        <v>46061.92765200231</v>
       </c>
       <c r="I1094" s="2" t="n">
-        <v>46066.92765200089</v>
+        <v>46066.92765200231</v>
       </c>
     </row>
     <row r="1095">
@@ -43139,10 +43139,10 @@
         </is>
       </c>
       <c r="H1095" s="2" t="n">
-        <v>46059.92765200423</v>
+        <v>46059.92765200231</v>
       </c>
       <c r="I1095" s="2" t="n">
-        <v>46064.92765200423</v>
+        <v>46064.92765200231</v>
       </c>
     </row>
     <row r="1096">
@@ -43178,10 +43178,10 @@
         </is>
       </c>
       <c r="H1096" s="2" t="n">
-        <v>46061.92765200746</v>
+        <v>46061.92765200231</v>
       </c>
       <c r="I1096" s="2" t="n">
-        <v>46066.92765200746</v>
+        <v>46066.92765200231</v>
       </c>
     </row>
     <row r="1097">
@@ -43217,10 +43217,10 @@
         </is>
       </c>
       <c r="H1097" s="2" t="n">
-        <v>46076.92765201065</v>
+        <v>46076.92765201389</v>
       </c>
       <c r="I1097" s="2" t="n">
-        <v>46081.92765201065</v>
+        <v>46081.92765201389</v>
       </c>
     </row>
     <row r="1098">
@@ -43256,10 +43256,10 @@
         </is>
       </c>
       <c r="H1098" s="2" t="n">
-        <v>46059.92765201374</v>
+        <v>46059.92765201389</v>
       </c>
       <c r="I1098" s="2" t="n">
-        <v>46064.92765201374</v>
+        <v>46064.92765201389</v>
       </c>
     </row>
     <row r="1099">
@@ -43295,10 +43295,10 @@
         </is>
       </c>
       <c r="H1099" s="2" t="n">
-        <v>46067.9276520173</v>
+        <v>46067.92765201389</v>
       </c>
       <c r="I1099" s="2" t="n">
-        <v>46072.9276520173</v>
+        <v>46072.92765201389</v>
       </c>
     </row>
     <row r="1100">
@@ -43334,10 +43334,10 @@
         </is>
       </c>
       <c r="H1100" s="2" t="n">
-        <v>46063.92765202047</v>
+        <v>46063.92765202546</v>
       </c>
       <c r="I1100" s="2" t="n">
-        <v>46068.92765202047</v>
+        <v>46068.92765202546</v>
       </c>
     </row>
     <row r="1101">
@@ -43373,10 +43373,1960 @@
         </is>
       </c>
       <c r="H1101" s="2" t="n">
-        <v>46075.92765202355</v>
+        <v>46075.92765202546</v>
       </c>
       <c r="I1101" s="2" t="n">
-        <v>46080.92765202355</v>
+        <v>46080.92765202546</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>d2ccf7f0-9de1-443e-b26f-285a4a5c9f4e</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>7664.8</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>96.06</v>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1102" s="2" t="n">
+        <v>46071.96951588426</v>
+      </c>
+      <c r="I1102" s="2" t="n">
+        <v>46076.96951588426</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>625f52a0-1520-4bd3-97b6-b0c003143539</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>2372.22</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1103" s="2" t="n">
+        <v>46062.96951588847</v>
+      </c>
+      <c r="I1103" s="2" t="n">
+        <v>46067.96951588847</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>791d9521-49ea-412f-94ec-3f834affd71a</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>7204.8</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1104" s="2" t="n">
+        <v>46066.96951589212</v>
+      </c>
+      <c r="I1104" s="2" t="n">
+        <v>46071.96951589212</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>07b46a48-c32d-491a-9210-a12786071a4a</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>1603.34</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1105" s="2" t="n">
+        <v>46074.96951589531</v>
+      </c>
+      <c r="I1105" s="2" t="n">
+        <v>46079.96951589531</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>21597957-c0db-41d6-bb3f-ac139cb59066</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>9866.870000000001</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1106" s="2" t="n">
+        <v>46062.96951589861</v>
+      </c>
+      <c r="I1106" s="2" t="n">
+        <v>46067.96951589861</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>5b0af28d-a0bc-4436-bd85-97ebd102ca81</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>8269.049999999999</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>87.37</v>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1107" s="2" t="n">
+        <v>46067.96951590214</v>
+      </c>
+      <c r="I1107" s="2" t="n">
+        <v>46072.96951590214</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>8ed4a7ac-c2b0-4df3-8f21-fd1cd62b1d69</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>7745.72</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1108" s="2" t="n">
+        <v>46067.96951590518</v>
+      </c>
+      <c r="I1108" s="2" t="n">
+        <v>46072.96951590518</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>1fc9a28b-19ff-4118-a7c0-cd9d3c1d62be</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>7703.33</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>96.64</v>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1109" s="2" t="n">
+        <v>46082.96951590843</v>
+      </c>
+      <c r="I1109" s="2" t="n">
+        <v>46087.96951590843</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>97b54d8b-aa2b-4bef-bc40-1356eeb269a8</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>6644</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1110" s="2" t="n">
+        <v>46087.96951591153</v>
+      </c>
+      <c r="I1110" s="2" t="n">
+        <v>46092.96951591153</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>c21bb342-4ef3-496e-8d68-0524a60aff18</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>1968.04</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1111" s="2" t="n">
+        <v>46081.96951591499</v>
+      </c>
+      <c r="I1111" s="2" t="n">
+        <v>46086.96951591499</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>b458fe90-081c-4487-9d3c-18c13a5ba00c</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>4852.61</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1112" s="2" t="n">
+        <v>46062.96951591835</v>
+      </c>
+      <c r="I1112" s="2" t="n">
+        <v>46067.96951591835</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>5ddc5d20-f011-4602-96f7-97fea21579ca</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>7515.55</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1113" s="2" t="n">
+        <v>46071.96951592155</v>
+      </c>
+      <c r="I1113" s="2" t="n">
+        <v>46076.96951592155</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>7247395f-ae70-4d17-869d-ba90f4071ca3</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>6871.66</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1114" s="2" t="n">
+        <v>46065.96951592538</v>
+      </c>
+      <c r="I1114" s="2" t="n">
+        <v>46070.96951592538</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>8e5661d9-114a-41c9-aefd-06f82e213f68</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>6524.27</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1115" s="2" t="n">
+        <v>46083.96951592866</v>
+      </c>
+      <c r="I1115" s="2" t="n">
+        <v>46088.96951592866</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>cf206d23-9f64-404c-993c-d06f37941bf4</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>9673.459999999999</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1116" s="2" t="n">
+        <v>46065.96951593187</v>
+      </c>
+      <c r="I1116" s="2" t="n">
+        <v>46070.96951593187</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>4120ab62-081e-46e2-841a-b1c488ff23a1</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>1712.23</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1117" s="2" t="n">
+        <v>46085.96951593523</v>
+      </c>
+      <c r="I1117" s="2" t="n">
+        <v>46090.96951593523</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>5b982147-9f97-4af5-a031-6330dd1e6fa3</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>8531.49</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1118" s="2" t="n">
+        <v>46071.96951593849</v>
+      </c>
+      <c r="I1118" s="2" t="n">
+        <v>46076.96951593849</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2a7e856a-a4d4-4689-9fb8-5b8ba31b3756</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>3329.23</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>94.98999999999999</v>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1119" s="2" t="n">
+        <v>46076.96951594149</v>
+      </c>
+      <c r="I1119" s="2" t="n">
+        <v>46081.96951594149</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>a1229b92-505f-4ab9-b33d-c478f6308440</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>7472.58</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1120" s="2" t="n">
+        <v>46082.96951594476</v>
+      </c>
+      <c r="I1120" s="2" t="n">
+        <v>46087.96951594476</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>e14b5a01-a9d3-494e-8a27-25ba8b85ee8e</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>6125.02</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>96.64</v>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1121" s="2" t="n">
+        <v>46077.96951594825</v>
+      </c>
+      <c r="I1121" s="2" t="n">
+        <v>46082.96951594825</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2e65af93-0eae-451b-9fb3-7912b544f47d</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>3392.4</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>96.81999999999999</v>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1122" s="2" t="n">
+        <v>46072.96951595152</v>
+      </c>
+      <c r="I1122" s="2" t="n">
+        <v>46077.96951595152</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>1947735c-99fb-4591-8515-4199ab7ae856</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>4922.82</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1123" s="2" t="n">
+        <v>46069.96951595478</v>
+      </c>
+      <c r="I1123" s="2" t="n">
+        <v>46074.96951595478</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>05cb4225-a92a-4b1c-ad0e-e6b4530089e8</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1124" t="n">
+        <v>6524.62</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1124" s="2" t="n">
+        <v>46083.96951595787</v>
+      </c>
+      <c r="I1124" s="2" t="n">
+        <v>46088.96951595787</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>b4ddff6e-c535-4e12-85ba-f6b94c9ddddc</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1125" t="n">
+        <v>7693.3</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1125" s="2" t="n">
+        <v>46080.9695159614</v>
+      </c>
+      <c r="I1125" s="2" t="n">
+        <v>46085.9695159614</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>ab22b40c-6d45-4e73-a538-89c7cf7d755b</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1126" t="n">
+        <v>2983.81</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1126" s="2" t="n">
+        <v>46085.96951596445</v>
+      </c>
+      <c r="I1126" s="2" t="n">
+        <v>46090.96951596445</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>6dc962e0-af41-4d57-8529-0ebf8d4b407f</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>8485.99</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1127" s="2" t="n">
+        <v>46060.9695159677</v>
+      </c>
+      <c r="I1127" s="2" t="n">
+        <v>46065.9695159677</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>0fcdccd1-01f3-4b93-a474-c9848e91901d</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>5533.78</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1128" s="2" t="n">
+        <v>46060.96951597147</v>
+      </c>
+      <c r="I1128" s="2" t="n">
+        <v>46065.96951597147</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>443d6df9-8566-47a9-824d-5d34e62427cb</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>6365.45</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>90.93000000000001</v>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1129" s="2" t="n">
+        <v>46070.96951597472</v>
+      </c>
+      <c r="I1129" s="2" t="n">
+        <v>46075.96951597472</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>c62bf95e-c6c8-439b-b4cb-6e309c8411e4</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>9817.51</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1130" s="2" t="n">
+        <v>46072.96951597797</v>
+      </c>
+      <c r="I1130" s="2" t="n">
+        <v>46077.96951597797</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>83a0780e-a8b1-466f-97ca-bb74c956ea67</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>4807.7</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1131" s="2" t="n">
+        <v>46077.96951598113</v>
+      </c>
+      <c r="I1131" s="2" t="n">
+        <v>46082.96951598113</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>72575689-3a34-4a48-99e6-dc1d5ae8ef7d</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>5013.76</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1132" s="2" t="n">
+        <v>46080.96951598463</v>
+      </c>
+      <c r="I1132" s="2" t="n">
+        <v>46085.96951598463</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>9b20e40b-700b-4b39-a46b-ab9c2b223a71</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>5859.95</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1133" s="2" t="n">
+        <v>46074.96951598772</v>
+      </c>
+      <c r="I1133" s="2" t="n">
+        <v>46079.96951598772</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>129b97e9-ebb1-4bf0-b2f4-0eb5ccb772b6</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>7765.59</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1134" s="2" t="n">
+        <v>46061.96951599094</v>
+      </c>
+      <c r="I1134" s="2" t="n">
+        <v>46066.96951599094</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>57d32540-b995-4982-b7e5-1a21fcfeda45</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>5364.31</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1135" s="2" t="n">
+        <v>46066.96951599439</v>
+      </c>
+      <c r="I1135" s="2" t="n">
+        <v>46071.96951599439</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>6c145f29-0bab-49d8-9a4b-334f4c9d20b3</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>2307.78</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1136" s="2" t="n">
+        <v>46061.96951599737</v>
+      </c>
+      <c r="I1136" s="2" t="n">
+        <v>46066.96951599737</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>ba3e8f8c-a625-4c79-9af0-ade85a184a53</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>2492.4</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>92.53</v>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1137" s="2" t="n">
+        <v>46065.96951600048</v>
+      </c>
+      <c r="I1137" s="2" t="n">
+        <v>46070.96951600048</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>7b860a4a-3b9d-44d3-8d59-89a0019578da</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>9854.49</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1138" s="2" t="n">
+        <v>46083.96951600353</v>
+      </c>
+      <c r="I1138" s="2" t="n">
+        <v>46088.96951600353</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>e31a35e5-4a85-45f3-9102-4681e89d57f7</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>9116.52</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>85.13</v>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1139" s="2" t="n">
+        <v>46070.96951600706</v>
+      </c>
+      <c r="I1139" s="2" t="n">
+        <v>46075.96951600706</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2d4f2c47-efb3-405c-961e-8222f25fe1f9</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>5148.12</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1140" s="2" t="n">
+        <v>46064.96951601026</v>
+      </c>
+      <c r="I1140" s="2" t="n">
+        <v>46069.96951601026</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>e0a0e00e-d2cd-4ef6-8f55-04489fbd210b</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>5667.17</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>92.16</v>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1141" s="2" t="n">
+        <v>46064.96951601349</v>
+      </c>
+      <c r="I1141" s="2" t="n">
+        <v>46069.96951601349</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>4f9bd536-2a22-48f1-b5f7-81168938ffa5</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>2611.67</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1142" s="2" t="n">
+        <v>46062.96951601723</v>
+      </c>
+      <c r="I1142" s="2" t="n">
+        <v>46067.96951601723</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>982e3ed0-02c7-4a05-a41e-bc7c5473beba</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>2315.09</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1143" s="2" t="n">
+        <v>46072.96951602052</v>
+      </c>
+      <c r="I1143" s="2" t="n">
+        <v>46077.96951602052</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>acf8f7b3-e498-4c4e-b99f-6f2aae17caf3</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>9343.65</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>94.17</v>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1144" s="2" t="n">
+        <v>46082.96951602366</v>
+      </c>
+      <c r="I1144" s="2" t="n">
+        <v>46087.96951602366</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2202438b-1dff-42c1-9b7b-7c61b98889fc</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>9122.9</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1145" s="2" t="n">
+        <v>46066.96951602664</v>
+      </c>
+      <c r="I1145" s="2" t="n">
+        <v>46071.96951602664</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>89576101-332f-4f69-939f-096d83372f1e</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>9363.280000000001</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>90.45999999999999</v>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1146" s="2" t="n">
+        <v>46059.96951603019</v>
+      </c>
+      <c r="I1146" s="2" t="n">
+        <v>46064.96951603019</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>b73e16af-cad5-4701-aca0-c9ffb38a9fee</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>3113.52</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1147" s="2" t="n">
+        <v>46070.96951603334</v>
+      </c>
+      <c r="I1147" s="2" t="n">
+        <v>46075.96951603334</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>3b59f533-a9a2-4c4e-b5a8-0da877858b8d</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>2609.73</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1148" s="2" t="n">
+        <v>46067.96951603642</v>
+      </c>
+      <c r="I1148" s="2" t="n">
+        <v>46072.96951603642</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>f1c14c1a-2da4-4d81-aae1-924627ac801c</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>1890.73</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1149" s="2" t="n">
+        <v>46066.9695160398</v>
+      </c>
+      <c r="I1149" s="2" t="n">
+        <v>46071.9695160398</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2672a97f-59d8-4e78-bf25-a674091cded1</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>9838.219999999999</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>87.56999999999999</v>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1150" s="2" t="n">
+        <v>46083.96951604296</v>
+      </c>
+      <c r="I1150" s="2" t="n">
+        <v>46088.96951604296</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>d26d6c86-f71f-43f1-9755-3fdfea12200a</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>9665.58</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>90.27</v>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1151" s="2" t="n">
+        <v>46065.969516046</v>
+      </c>
+      <c r="I1151" s="2" t="n">
+        <v>46070.969516046</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1151"/>
+  <dimension ref="A1:I1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43412,10 +43412,10 @@
         </is>
       </c>
       <c r="H1102" s="2" t="n">
-        <v>46071.96951588426</v>
+        <v>46071.96951587963</v>
       </c>
       <c r="I1102" s="2" t="n">
-        <v>46076.96951588426</v>
+        <v>46076.96951587963</v>
       </c>
     </row>
     <row r="1103">
@@ -43451,10 +43451,10 @@
         </is>
       </c>
       <c r="H1103" s="2" t="n">
-        <v>46062.96951588847</v>
+        <v>46062.96951589121</v>
       </c>
       <c r="I1103" s="2" t="n">
-        <v>46067.96951588847</v>
+        <v>46067.96951589121</v>
       </c>
     </row>
     <row r="1104">
@@ -43490,10 +43490,10 @@
         </is>
       </c>
       <c r="H1104" s="2" t="n">
-        <v>46066.96951589212</v>
+        <v>46066.96951589121</v>
       </c>
       <c r="I1104" s="2" t="n">
-        <v>46071.96951589212</v>
+        <v>46071.96951589121</v>
       </c>
     </row>
     <row r="1105">
@@ -43529,10 +43529,10 @@
         </is>
       </c>
       <c r="H1105" s="2" t="n">
-        <v>46074.96951589531</v>
+        <v>46074.96951589121</v>
       </c>
       <c r="I1105" s="2" t="n">
-        <v>46079.96951589531</v>
+        <v>46079.96951589121</v>
       </c>
     </row>
     <row r="1106">
@@ -43568,10 +43568,10 @@
         </is>
       </c>
       <c r="H1106" s="2" t="n">
-        <v>46062.96951589861</v>
+        <v>46062.96951590278</v>
       </c>
       <c r="I1106" s="2" t="n">
-        <v>46067.96951589861</v>
+        <v>46067.96951590278</v>
       </c>
     </row>
     <row r="1107">
@@ -43607,10 +43607,10 @@
         </is>
       </c>
       <c r="H1107" s="2" t="n">
-        <v>46067.96951590214</v>
+        <v>46067.96951590278</v>
       </c>
       <c r="I1107" s="2" t="n">
-        <v>46072.96951590214</v>
+        <v>46072.96951590278</v>
       </c>
     </row>
     <row r="1108">
@@ -43646,10 +43646,10 @@
         </is>
       </c>
       <c r="H1108" s="2" t="n">
-        <v>46067.96951590518</v>
+        <v>46067.96951590278</v>
       </c>
       <c r="I1108" s="2" t="n">
-        <v>46072.96951590518</v>
+        <v>46072.96951590278</v>
       </c>
     </row>
     <row r="1109">
@@ -43685,10 +43685,10 @@
         </is>
       </c>
       <c r="H1109" s="2" t="n">
-        <v>46082.96951590843</v>
+        <v>46082.96951590278</v>
       </c>
       <c r="I1109" s="2" t="n">
-        <v>46087.96951590843</v>
+        <v>46087.96951590278</v>
       </c>
     </row>
     <row r="1110">
@@ -43724,10 +43724,10 @@
         </is>
       </c>
       <c r="H1110" s="2" t="n">
-        <v>46087.96951591153</v>
+        <v>46087.96951591435</v>
       </c>
       <c r="I1110" s="2" t="n">
-        <v>46092.96951591153</v>
+        <v>46092.96951591435</v>
       </c>
     </row>
     <row r="1111">
@@ -43763,10 +43763,10 @@
         </is>
       </c>
       <c r="H1111" s="2" t="n">
-        <v>46081.96951591499</v>
+        <v>46081.96951591435</v>
       </c>
       <c r="I1111" s="2" t="n">
-        <v>46086.96951591499</v>
+        <v>46086.96951591435</v>
       </c>
     </row>
     <row r="1112">
@@ -43802,10 +43802,10 @@
         </is>
       </c>
       <c r="H1112" s="2" t="n">
-        <v>46062.96951591835</v>
+        <v>46062.96951591435</v>
       </c>
       <c r="I1112" s="2" t="n">
-        <v>46067.96951591835</v>
+        <v>46067.96951591435</v>
       </c>
     </row>
     <row r="1113">
@@ -43841,10 +43841,10 @@
         </is>
       </c>
       <c r="H1113" s="2" t="n">
-        <v>46071.96951592155</v>
+        <v>46071.96951592593</v>
       </c>
       <c r="I1113" s="2" t="n">
-        <v>46076.96951592155</v>
+        <v>46076.96951592593</v>
       </c>
     </row>
     <row r="1114">
@@ -43880,10 +43880,10 @@
         </is>
       </c>
       <c r="H1114" s="2" t="n">
-        <v>46065.96951592538</v>
+        <v>46065.96951592593</v>
       </c>
       <c r="I1114" s="2" t="n">
-        <v>46070.96951592538</v>
+        <v>46070.96951592593</v>
       </c>
     </row>
     <row r="1115">
@@ -43919,10 +43919,10 @@
         </is>
       </c>
       <c r="H1115" s="2" t="n">
-        <v>46083.96951592866</v>
+        <v>46083.96951592593</v>
       </c>
       <c r="I1115" s="2" t="n">
-        <v>46088.96951592866</v>
+        <v>46088.96951592593</v>
       </c>
     </row>
     <row r="1116">
@@ -43958,10 +43958,10 @@
         </is>
       </c>
       <c r="H1116" s="2" t="n">
-        <v>46065.96951593187</v>
+        <v>46065.9695159375</v>
       </c>
       <c r="I1116" s="2" t="n">
-        <v>46070.96951593187</v>
+        <v>46070.9695159375</v>
       </c>
     </row>
     <row r="1117">
@@ -43997,10 +43997,10 @@
         </is>
       </c>
       <c r="H1117" s="2" t="n">
-        <v>46085.96951593523</v>
+        <v>46085.9695159375</v>
       </c>
       <c r="I1117" s="2" t="n">
-        <v>46090.96951593523</v>
+        <v>46090.9695159375</v>
       </c>
     </row>
     <row r="1118">
@@ -44036,10 +44036,10 @@
         </is>
       </c>
       <c r="H1118" s="2" t="n">
-        <v>46071.96951593849</v>
+        <v>46071.9695159375</v>
       </c>
       <c r="I1118" s="2" t="n">
-        <v>46076.96951593849</v>
+        <v>46076.9695159375</v>
       </c>
     </row>
     <row r="1119">
@@ -44075,10 +44075,10 @@
         </is>
       </c>
       <c r="H1119" s="2" t="n">
-        <v>46076.96951594149</v>
+        <v>46076.9695159375</v>
       </c>
       <c r="I1119" s="2" t="n">
-        <v>46081.96951594149</v>
+        <v>46081.9695159375</v>
       </c>
     </row>
     <row r="1120">
@@ -44114,10 +44114,10 @@
         </is>
       </c>
       <c r="H1120" s="2" t="n">
-        <v>46082.96951594476</v>
+        <v>46082.96951594907</v>
       </c>
       <c r="I1120" s="2" t="n">
-        <v>46087.96951594476</v>
+        <v>46087.96951594907</v>
       </c>
     </row>
     <row r="1121">
@@ -44153,10 +44153,10 @@
         </is>
       </c>
       <c r="H1121" s="2" t="n">
-        <v>46077.96951594825</v>
+        <v>46077.96951594907</v>
       </c>
       <c r="I1121" s="2" t="n">
-        <v>46082.96951594825</v>
+        <v>46082.96951594907</v>
       </c>
     </row>
     <row r="1122">
@@ -44192,10 +44192,10 @@
         </is>
       </c>
       <c r="H1122" s="2" t="n">
-        <v>46072.96951595152</v>
+        <v>46072.96951594907</v>
       </c>
       <c r="I1122" s="2" t="n">
-        <v>46077.96951595152</v>
+        <v>46077.96951594907</v>
       </c>
     </row>
     <row r="1123">
@@ -44231,10 +44231,10 @@
         </is>
       </c>
       <c r="H1123" s="2" t="n">
-        <v>46069.96951595478</v>
+        <v>46069.96951594907</v>
       </c>
       <c r="I1123" s="2" t="n">
-        <v>46074.96951595478</v>
+        <v>46074.96951594907</v>
       </c>
     </row>
     <row r="1124">
@@ -44270,10 +44270,10 @@
         </is>
       </c>
       <c r="H1124" s="2" t="n">
-        <v>46083.96951595787</v>
+        <v>46083.96951596065</v>
       </c>
       <c r="I1124" s="2" t="n">
-        <v>46088.96951595787</v>
+        <v>46088.96951596065</v>
       </c>
     </row>
     <row r="1125">
@@ -44309,10 +44309,10 @@
         </is>
       </c>
       <c r="H1125" s="2" t="n">
-        <v>46080.9695159614</v>
+        <v>46080.96951596065</v>
       </c>
       <c r="I1125" s="2" t="n">
-        <v>46085.9695159614</v>
+        <v>46085.96951596065</v>
       </c>
     </row>
     <row r="1126">
@@ -44348,10 +44348,10 @@
         </is>
       </c>
       <c r="H1126" s="2" t="n">
-        <v>46085.96951596445</v>
+        <v>46085.96951596065</v>
       </c>
       <c r="I1126" s="2" t="n">
-        <v>46090.96951596445</v>
+        <v>46090.96951596065</v>
       </c>
     </row>
     <row r="1127">
@@ -44387,10 +44387,10 @@
         </is>
       </c>
       <c r="H1127" s="2" t="n">
-        <v>46060.9695159677</v>
+        <v>46060.96951597223</v>
       </c>
       <c r="I1127" s="2" t="n">
-        <v>46065.9695159677</v>
+        <v>46065.96951597223</v>
       </c>
     </row>
     <row r="1128">
@@ -44426,10 +44426,10 @@
         </is>
       </c>
       <c r="H1128" s="2" t="n">
-        <v>46060.96951597147</v>
+        <v>46060.96951597223</v>
       </c>
       <c r="I1128" s="2" t="n">
-        <v>46065.96951597147</v>
+        <v>46065.96951597223</v>
       </c>
     </row>
     <row r="1129">
@@ -44465,10 +44465,10 @@
         </is>
       </c>
       <c r="H1129" s="2" t="n">
-        <v>46070.96951597472</v>
+        <v>46070.96951597223</v>
       </c>
       <c r="I1129" s="2" t="n">
-        <v>46075.96951597472</v>
+        <v>46075.96951597223</v>
       </c>
     </row>
     <row r="1130">
@@ -44504,10 +44504,10 @@
         </is>
       </c>
       <c r="H1130" s="2" t="n">
-        <v>46072.96951597797</v>
+        <v>46072.96951597223</v>
       </c>
       <c r="I1130" s="2" t="n">
-        <v>46077.96951597797</v>
+        <v>46077.96951597223</v>
       </c>
     </row>
     <row r="1131">
@@ -44543,10 +44543,10 @@
         </is>
       </c>
       <c r="H1131" s="2" t="n">
-        <v>46077.96951598113</v>
+        <v>46077.96951598379</v>
       </c>
       <c r="I1131" s="2" t="n">
-        <v>46082.96951598113</v>
+        <v>46082.96951598379</v>
       </c>
     </row>
     <row r="1132">
@@ -44582,10 +44582,10 @@
         </is>
       </c>
       <c r="H1132" s="2" t="n">
-        <v>46080.96951598463</v>
+        <v>46080.96951598379</v>
       </c>
       <c r="I1132" s="2" t="n">
-        <v>46085.96951598463</v>
+        <v>46085.96951598379</v>
       </c>
     </row>
     <row r="1133">
@@ -44621,10 +44621,10 @@
         </is>
       </c>
       <c r="H1133" s="2" t="n">
-        <v>46074.96951598772</v>
+        <v>46074.96951598379</v>
       </c>
       <c r="I1133" s="2" t="n">
-        <v>46079.96951598772</v>
+        <v>46079.96951598379</v>
       </c>
     </row>
     <row r="1134">
@@ -44660,10 +44660,10 @@
         </is>
       </c>
       <c r="H1134" s="2" t="n">
-        <v>46061.96951599094</v>
+        <v>46061.96951599537</v>
       </c>
       <c r="I1134" s="2" t="n">
-        <v>46066.96951599094</v>
+        <v>46066.96951599537</v>
       </c>
     </row>
     <row r="1135">
@@ -44699,10 +44699,10 @@
         </is>
       </c>
       <c r="H1135" s="2" t="n">
-        <v>46066.96951599439</v>
+        <v>46066.96951599537</v>
       </c>
       <c r="I1135" s="2" t="n">
-        <v>46071.96951599439</v>
+        <v>46071.96951599537</v>
       </c>
     </row>
     <row r="1136">
@@ -44738,10 +44738,10 @@
         </is>
       </c>
       <c r="H1136" s="2" t="n">
-        <v>46061.96951599737</v>
+        <v>46061.96951599537</v>
       </c>
       <c r="I1136" s="2" t="n">
-        <v>46066.96951599737</v>
+        <v>46066.96951599537</v>
       </c>
     </row>
     <row r="1137">
@@ -44777,10 +44777,10 @@
         </is>
       </c>
       <c r="H1137" s="2" t="n">
-        <v>46065.96951600048</v>
+        <v>46065.96951599537</v>
       </c>
       <c r="I1137" s="2" t="n">
-        <v>46070.96951600048</v>
+        <v>46070.96951599537</v>
       </c>
     </row>
     <row r="1138">
@@ -44816,10 +44816,10 @@
         </is>
       </c>
       <c r="H1138" s="2" t="n">
-        <v>46083.96951600353</v>
+        <v>46083.96951600695</v>
       </c>
       <c r="I1138" s="2" t="n">
-        <v>46088.96951600353</v>
+        <v>46088.96951600695</v>
       </c>
     </row>
     <row r="1139">
@@ -44855,10 +44855,10 @@
         </is>
       </c>
       <c r="H1139" s="2" t="n">
-        <v>46070.96951600706</v>
+        <v>46070.96951600695</v>
       </c>
       <c r="I1139" s="2" t="n">
-        <v>46075.96951600706</v>
+        <v>46075.96951600695</v>
       </c>
     </row>
     <row r="1140">
@@ -44894,10 +44894,10 @@
         </is>
       </c>
       <c r="H1140" s="2" t="n">
-        <v>46064.96951601026</v>
+        <v>46064.96951600695</v>
       </c>
       <c r="I1140" s="2" t="n">
-        <v>46069.96951601026</v>
+        <v>46069.96951600695</v>
       </c>
     </row>
     <row r="1141">
@@ -44933,10 +44933,10 @@
         </is>
       </c>
       <c r="H1141" s="2" t="n">
-        <v>46064.96951601349</v>
+        <v>46064.96951601852</v>
       </c>
       <c r="I1141" s="2" t="n">
-        <v>46069.96951601349</v>
+        <v>46069.96951601852</v>
       </c>
     </row>
     <row r="1142">
@@ -44972,10 +44972,10 @@
         </is>
       </c>
       <c r="H1142" s="2" t="n">
-        <v>46062.96951601723</v>
+        <v>46062.96951601852</v>
       </c>
       <c r="I1142" s="2" t="n">
-        <v>46067.96951601723</v>
+        <v>46067.96951601852</v>
       </c>
     </row>
     <row r="1143">
@@ -45011,10 +45011,10 @@
         </is>
       </c>
       <c r="H1143" s="2" t="n">
-        <v>46072.96951602052</v>
+        <v>46072.96951601852</v>
       </c>
       <c r="I1143" s="2" t="n">
-        <v>46077.96951602052</v>
+        <v>46077.96951601852</v>
       </c>
     </row>
     <row r="1144">
@@ -45050,10 +45050,10 @@
         </is>
       </c>
       <c r="H1144" s="2" t="n">
-        <v>46082.96951602366</v>
+        <v>46082.96951601852</v>
       </c>
       <c r="I1144" s="2" t="n">
-        <v>46087.96951602366</v>
+        <v>46087.96951601852</v>
       </c>
     </row>
     <row r="1145">
@@ -45089,10 +45089,10 @@
         </is>
       </c>
       <c r="H1145" s="2" t="n">
-        <v>46066.96951602664</v>
+        <v>46066.96951603009</v>
       </c>
       <c r="I1145" s="2" t="n">
-        <v>46071.96951602664</v>
+        <v>46071.96951603009</v>
       </c>
     </row>
     <row r="1146">
@@ -45128,10 +45128,10 @@
         </is>
       </c>
       <c r="H1146" s="2" t="n">
-        <v>46059.96951603019</v>
+        <v>46059.96951603009</v>
       </c>
       <c r="I1146" s="2" t="n">
-        <v>46064.96951603019</v>
+        <v>46064.96951603009</v>
       </c>
     </row>
     <row r="1147">
@@ -45167,10 +45167,10 @@
         </is>
       </c>
       <c r="H1147" s="2" t="n">
-        <v>46070.96951603334</v>
+        <v>46070.96951603009</v>
       </c>
       <c r="I1147" s="2" t="n">
-        <v>46075.96951603334</v>
+        <v>46075.96951603009</v>
       </c>
     </row>
     <row r="1148">
@@ -45206,10 +45206,10 @@
         </is>
       </c>
       <c r="H1148" s="2" t="n">
-        <v>46067.96951603642</v>
+        <v>46067.96951604167</v>
       </c>
       <c r="I1148" s="2" t="n">
-        <v>46072.96951603642</v>
+        <v>46072.96951604167</v>
       </c>
     </row>
     <row r="1149">
@@ -45245,10 +45245,10 @@
         </is>
       </c>
       <c r="H1149" s="2" t="n">
-        <v>46066.9695160398</v>
+        <v>46066.96951604167</v>
       </c>
       <c r="I1149" s="2" t="n">
-        <v>46071.9695160398</v>
+        <v>46071.96951604167</v>
       </c>
     </row>
     <row r="1150">
@@ -45284,10 +45284,10 @@
         </is>
       </c>
       <c r="H1150" s="2" t="n">
-        <v>46083.96951604296</v>
+        <v>46083.96951604167</v>
       </c>
       <c r="I1150" s="2" t="n">
-        <v>46088.96951604296</v>
+        <v>46088.96951604167</v>
       </c>
     </row>
     <row r="1151">
@@ -45323,10 +45323,1960 @@
         </is>
       </c>
       <c r="H1151" s="2" t="n">
-        <v>46065.969516046</v>
+        <v>46065.96951604167</v>
       </c>
       <c r="I1151" s="2" t="n">
-        <v>46070.969516046</v>
+        <v>46070.96951604167</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>bdf4b332-0b8b-4345-8efc-5da99cba448f</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>6306.13</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1152" s="2" t="n">
+        <v>46060.05567037185</v>
+      </c>
+      <c r="I1152" s="2" t="n">
+        <v>46065.05567037185</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>19c89a45-aa5b-42a7-a4c4-f37c45aabfa6</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>7864.93</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1153" s="2" t="n">
+        <v>46082.05567037634</v>
+      </c>
+      <c r="I1153" s="2" t="n">
+        <v>46087.05567037634</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>c836f447-2e61-4e2d-93e6-40c39cb154f4</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>2626.37</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1154" s="2" t="n">
+        <v>46069.05567037963</v>
+      </c>
+      <c r="I1154" s="2" t="n">
+        <v>46074.05567037963</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>62f560a5-91f1-4f66-b3cb-9d58b6eab438</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>2853.08</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1155" s="2" t="n">
+        <v>46082.05567038291</v>
+      </c>
+      <c r="I1155" s="2" t="n">
+        <v>46087.05567038291</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>bb4bd56d-5a84-4a0c-a431-099e02ae72d8</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>8123.55</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1156" s="2" t="n">
+        <v>46061.05567038616</v>
+      </c>
+      <c r="I1156" s="2" t="n">
+        <v>46066.05567038616</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>44faa6cf-9b22-4d69-b9a2-4345a45d3352</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>6774.94</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1157" s="2" t="n">
+        <v>46068.05567038919</v>
+      </c>
+      <c r="I1157" s="2" t="n">
+        <v>46073.05567038919</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>b49d50bb-b452-432a-b4d6-91832883d3bc</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>6623.26</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>94.27</v>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1158" s="2" t="n">
+        <v>46073.05567039228</v>
+      </c>
+      <c r="I1158" s="2" t="n">
+        <v>46078.05567039228</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>71f378d4-e4cd-43fc-a31f-bef166595fa4</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>5434.61</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>88.87</v>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1159" s="2" t="n">
+        <v>46079.05567039533</v>
+      </c>
+      <c r="I1159" s="2" t="n">
+        <v>46084.05567039533</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>fcae4882-87eb-4fab-9351-03c7d2848d20</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>2466.18</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1160" s="2" t="n">
+        <v>46082.05567039894</v>
+      </c>
+      <c r="I1160" s="2" t="n">
+        <v>46087.05567039894</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>e9168ebc-7ecf-4cbe-8a98-f938355e9523</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>5205.01</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>93.63</v>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1161" s="2" t="n">
+        <v>46063.05567040199</v>
+      </c>
+      <c r="I1161" s="2" t="n">
+        <v>46068.05567040199</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>6b39cd39-e27a-4b64-aeca-4e007d2af4e1</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>3082.78</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1162" s="2" t="n">
+        <v>46080.05567040522</v>
+      </c>
+      <c r="I1162" s="2" t="n">
+        <v>46085.05567040522</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>61a1cfe8-947b-48ce-9efd-5de0790e0464</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>8751.120000000001</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1163" s="2" t="n">
+        <v>46077.0556704085</v>
+      </c>
+      <c r="I1163" s="2" t="n">
+        <v>46082.0556704085</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>781ed867-0298-4e17-b8b2-acff8967a7bf</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>4597.77</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1164" s="2" t="n">
+        <v>46073.05567041152</v>
+      </c>
+      <c r="I1164" s="2" t="n">
+        <v>46078.05567041152</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>63ddbf74-1643-45a2-9ec6-d121cb1b59a1</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>5770.53</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>88.31</v>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1165" s="2" t="n">
+        <v>46082.05567041459</v>
+      </c>
+      <c r="I1165" s="2" t="n">
+        <v>46087.05567041459</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>b4477b36-8d6b-4bfa-8342-f947487f970d</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1166" t="n">
+        <v>5463.81</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1166" s="2" t="n">
+        <v>46088.05567041774</v>
+      </c>
+      <c r="I1166" s="2" t="n">
+        <v>46093.05567041774</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>4a9cb2bb-1014-48da-9937-60401e10b680</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1167" t="n">
+        <v>8192.799999999999</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1167" s="2" t="n">
+        <v>46068.0556704211</v>
+      </c>
+      <c r="I1167" s="2" t="n">
+        <v>46073.0556704211</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>726735f7-3ea1-47ab-8022-fd30fa0f6c7f</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1168" t="n">
+        <v>6997.05</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1168" s="2" t="n">
+        <v>46075.0556704245</v>
+      </c>
+      <c r="I1168" s="2" t="n">
+        <v>46080.0556704245</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2fe930f4-2ee6-4474-a7b3-a7eff48c5025</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1169" t="n">
+        <v>7719.57</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1169" s="2" t="n">
+        <v>46081.05567042749</v>
+      </c>
+      <c r="I1169" s="2" t="n">
+        <v>46086.05567042749</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>e8d5f8dc-538a-47b8-aa19-c6efbbb15162</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1170" t="n">
+        <v>2663.43</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>88.11</v>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1170" s="2" t="n">
+        <v>46066.05567043069</v>
+      </c>
+      <c r="I1170" s="2" t="n">
+        <v>46071.05567043069</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>0d6bfacf-0d3c-4e53-8b7d-c70341d3949a</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1171" t="n">
+        <v>2715.44</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1171" s="2" t="n">
+        <v>46089.05567043377</v>
+      </c>
+      <c r="I1171" s="2" t="n">
+        <v>46094.05567043377</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>6298f79d-8fc6-4201-b04c-9e078adfbca5</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1172" t="n">
+        <v>6725.89</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>95.87</v>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1172" s="2" t="n">
+        <v>46076.0556704369</v>
+      </c>
+      <c r="I1172" s="2" t="n">
+        <v>46081.0556704369</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>771e2c3f-e781-4e76-af89-0c99cd1ff86c</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>7260.41</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1173" s="2" t="n">
+        <v>46078.05567043996</v>
+      </c>
+      <c r="I1173" s="2" t="n">
+        <v>46083.05567043996</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>6c399d03-88ad-4a26-9e67-715a2d62bf92</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>3232.98</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1174" s="2" t="n">
+        <v>46069.05567044353</v>
+      </c>
+      <c r="I1174" s="2" t="n">
+        <v>46074.05567044353</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>046b44a0-97a7-4dff-adbd-96108301e013</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>8869.870000000001</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1175" s="2" t="n">
+        <v>46070.05567044654</v>
+      </c>
+      <c r="I1175" s="2" t="n">
+        <v>46075.05567044654</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>62e0c69d-24d8-460c-a781-bb7ffe39cb94</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1176" t="n">
+        <v>9944.43</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1176" s="2" t="n">
+        <v>46066.05567044957</v>
+      </c>
+      <c r="I1176" s="2" t="n">
+        <v>46071.05567044957</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>f06f517b-cbfb-4184-a8ef-2a5dcb5b7a5d</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1177" t="n">
+        <v>4149.95</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1177" s="2" t="n">
+        <v>46061.05567045262</v>
+      </c>
+      <c r="I1177" s="2" t="n">
+        <v>46066.05567045262</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>c5ace0d9-ce34-4d25-94c8-c819aef3c171</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1178" t="n">
+        <v>6764.22</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1178" s="2" t="n">
+        <v>46064.05567045596</v>
+      </c>
+      <c r="I1178" s="2" t="n">
+        <v>46069.05567045596</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>288d828c-0f2f-407f-abb4-2c8a67d328bd</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1179" t="n">
+        <v>9556.879999999999</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>90.58</v>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1179" s="2" t="n">
+        <v>46078.05567045918</v>
+      </c>
+      <c r="I1179" s="2" t="n">
+        <v>46083.05567045918</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>c0568aea-d541-4170-ba5b-38da5ce5ae4f</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1180" t="n">
+        <v>7482.67</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1180" s="2" t="n">
+        <v>46069.05567046218</v>
+      </c>
+      <c r="I1180" s="2" t="n">
+        <v>46074.05567046218</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>3f1b1d8a-1e2c-4b9d-8dd8-936c29080361</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1181" t="n">
+        <v>7122.94</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>93.95999999999999</v>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1181" s="2" t="n">
+        <v>46070.05567046547</v>
+      </c>
+      <c r="I1181" s="2" t="n">
+        <v>46075.05567046547</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>b8c0a864-7562-46c7-894c-47370b646b8c</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>7465.86</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1182" s="2" t="n">
+        <v>46074.05567046876</v>
+      </c>
+      <c r="I1182" s="2" t="n">
+        <v>46079.05567046876</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>7f883c33-d214-4625-b546-6d594d62c7ac</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>2850.71</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>94.47</v>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1183" s="2" t="n">
+        <v>46063.05567047193</v>
+      </c>
+      <c r="I1183" s="2" t="n">
+        <v>46068.05567047193</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>1e0f76eb-e3fa-4a67-b771-555dcb1987a0</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1184" t="n">
+        <v>1048.82</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>99.27</v>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1184" s="2" t="n">
+        <v>46088.05567047513</v>
+      </c>
+      <c r="I1184" s="2" t="n">
+        <v>46093.05567047513</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>5cae1cf4-f2db-4493-aa63-af54df75d896</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1185" t="n">
+        <v>2792.68</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1185" s="2" t="n">
+        <v>46070.0556704785</v>
+      </c>
+      <c r="I1185" s="2" t="n">
+        <v>46075.0556704785</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>0bb142ac-6ba7-4e2e-acae-c5ac023342df</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1186" t="n">
+        <v>1386.83</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>96.48999999999999</v>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1186" s="2" t="n">
+        <v>46083.05567048164</v>
+      </c>
+      <c r="I1186" s="2" t="n">
+        <v>46088.05567048164</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>e3e4474e-6e98-48c2-9344-3af5ba3909e5</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1187" t="n">
+        <v>7769.98</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1187" s="2" t="n">
+        <v>46086.05567048479</v>
+      </c>
+      <c r="I1187" s="2" t="n">
+        <v>46091.05567048479</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>f712fc12-f343-4248-8ce4-8649ce06a500</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1188" t="n">
+        <v>9199.219999999999</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>92.09</v>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1188" s="2" t="n">
+        <v>46078.05567048779</v>
+      </c>
+      <c r="I1188" s="2" t="n">
+        <v>46083.05567048779</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>26b04a3b-76b1-4ffa-ba1a-982a51f09914</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1189" t="n">
+        <v>5490.6</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>96.37</v>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1189" s="2" t="n">
+        <v>46065.05567049114</v>
+      </c>
+      <c r="I1189" s="2" t="n">
+        <v>46070.05567049114</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>ed5dc14e-dbda-4b9a-8919-cda379a62979</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1190" t="n">
+        <v>2222.19</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1190" s="2" t="n">
+        <v>46082.05567049429</v>
+      </c>
+      <c r="I1190" s="2" t="n">
+        <v>46087.05567049429</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>ed88fb44-c86b-4715-a767-834c2848c74e</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1191" t="n">
+        <v>1521.36</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>86.81999999999999</v>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1191" s="2" t="n">
+        <v>46089.05567049731</v>
+      </c>
+      <c r="I1191" s="2" t="n">
+        <v>46094.05567049731</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>3f17a970-39db-4117-85be-a95d593c2536</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1192" t="n">
+        <v>7264.88</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1192" s="2" t="n">
+        <v>46075.0556705006</v>
+      </c>
+      <c r="I1192" s="2" t="n">
+        <v>46080.0556705006</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>8acd125c-97ca-40ee-a7fe-fb2143675c19</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1193" t="n">
+        <v>3725.2</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>87.88</v>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1193" s="2" t="n">
+        <v>46082.05567050374</v>
+      </c>
+      <c r="I1193" s="2" t="n">
+        <v>46087.05567050374</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>e7728085-bf72-47c0-a8cf-b4110c3548aa</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1194" t="n">
+        <v>5911.45</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1194" s="2" t="n">
+        <v>46064.05567050678</v>
+      </c>
+      <c r="I1194" s="2" t="n">
+        <v>46069.05567050678</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>843a114b-443f-4556-b73b-2876fcff2f82</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1195" t="n">
+        <v>9600.620000000001</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1195" s="2" t="n">
+        <v>46061.05567050973</v>
+      </c>
+      <c r="I1195" s="2" t="n">
+        <v>46066.05567050973</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>b5b095cb-ccec-4024-95c6-af22afb6b6f5</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1196" t="n">
+        <v>4936.38</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>91.64</v>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1196" s="2" t="n">
+        <v>46063.0556705131</v>
+      </c>
+      <c r="I1196" s="2" t="n">
+        <v>46068.0556705131</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>e55383eb-f12d-4688-ad53-c70b1cbcae49</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1197" t="n">
+        <v>1731.25</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>95.37</v>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1197" s="2" t="n">
+        <v>46068.05567051612</v>
+      </c>
+      <c r="I1197" s="2" t="n">
+        <v>46073.05567051612</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>57c46f50-a180-4588-9da7-adac5f8b862e</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1198" t="n">
+        <v>5194.14</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>85.26000000000001</v>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1198" s="2" t="n">
+        <v>46069.05567051921</v>
+      </c>
+      <c r="I1198" s="2" t="n">
+        <v>46074.05567051921</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>a54b3498-017c-4e06-977a-b50cc555b9b6</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1199" t="n">
+        <v>7266.07</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1199" s="2" t="n">
+        <v>46079.05567052276</v>
+      </c>
+      <c r="I1199" s="2" t="n">
+        <v>46084.05567052276</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>9c6e2f28-7db4-4bd1-8fce-f4b1fb405422</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1200" t="n">
+        <v>7387.06</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1200" s="2" t="n">
+        <v>46075.05567052597</v>
+      </c>
+      <c r="I1200" s="2" t="n">
+        <v>46080.05567052597</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>c86a7f02-5792-4c0d-8afb-4325fd0b98fe</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1201" t="n">
+        <v>2819.03</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>94.06999999999999</v>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1201" s="2" t="n">
+        <v>46062.05567052915</v>
+      </c>
+      <c r="I1201" s="2" t="n">
+        <v>46067.05567052915</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1201"/>
+  <dimension ref="A1:I1251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45362,10 +45362,10 @@
         </is>
       </c>
       <c r="H1152" s="2" t="n">
-        <v>46060.05567037185</v>
+        <v>46060.05567037037</v>
       </c>
       <c r="I1152" s="2" t="n">
-        <v>46065.05567037185</v>
+        <v>46065.05567037037</v>
       </c>
     </row>
     <row r="1153">
@@ -45401,10 +45401,10 @@
         </is>
       </c>
       <c r="H1153" s="2" t="n">
-        <v>46082.05567037634</v>
+        <v>46082.05567038195</v>
       </c>
       <c r="I1153" s="2" t="n">
-        <v>46087.05567037634</v>
+        <v>46087.05567038195</v>
       </c>
     </row>
     <row r="1154">
@@ -45440,10 +45440,10 @@
         </is>
       </c>
       <c r="H1154" s="2" t="n">
-        <v>46069.05567037963</v>
+        <v>46069.05567038195</v>
       </c>
       <c r="I1154" s="2" t="n">
-        <v>46074.05567037963</v>
+        <v>46074.05567038195</v>
       </c>
     </row>
     <row r="1155">
@@ -45479,10 +45479,10 @@
         </is>
       </c>
       <c r="H1155" s="2" t="n">
-        <v>46082.05567038291</v>
+        <v>46082.05567038195</v>
       </c>
       <c r="I1155" s="2" t="n">
-        <v>46087.05567038291</v>
+        <v>46087.05567038195</v>
       </c>
     </row>
     <row r="1156">
@@ -45518,10 +45518,10 @@
         </is>
       </c>
       <c r="H1156" s="2" t="n">
-        <v>46061.05567038616</v>
+        <v>46061.05567038195</v>
       </c>
       <c r="I1156" s="2" t="n">
-        <v>46066.05567038616</v>
+        <v>46066.05567038195</v>
       </c>
     </row>
     <row r="1157">
@@ -45557,10 +45557,10 @@
         </is>
       </c>
       <c r="H1157" s="2" t="n">
-        <v>46068.05567038919</v>
+        <v>46068.05567039352</v>
       </c>
       <c r="I1157" s="2" t="n">
-        <v>46073.05567038919</v>
+        <v>46073.05567039352</v>
       </c>
     </row>
     <row r="1158">
@@ -45596,10 +45596,10 @@
         </is>
       </c>
       <c r="H1158" s="2" t="n">
-        <v>46073.05567039228</v>
+        <v>46073.05567039352</v>
       </c>
       <c r="I1158" s="2" t="n">
-        <v>46078.05567039228</v>
+        <v>46078.05567039352</v>
       </c>
     </row>
     <row r="1159">
@@ -45635,10 +45635,10 @@
         </is>
       </c>
       <c r="H1159" s="2" t="n">
-        <v>46079.05567039533</v>
+        <v>46079.05567039352</v>
       </c>
       <c r="I1159" s="2" t="n">
-        <v>46084.05567039533</v>
+        <v>46084.05567039352</v>
       </c>
     </row>
     <row r="1160">
@@ -45674,10 +45674,10 @@
         </is>
       </c>
       <c r="H1160" s="2" t="n">
-        <v>46082.05567039894</v>
+        <v>46082.05567039352</v>
       </c>
       <c r="I1160" s="2" t="n">
-        <v>46087.05567039894</v>
+        <v>46087.05567039352</v>
       </c>
     </row>
     <row r="1161">
@@ -45713,10 +45713,10 @@
         </is>
       </c>
       <c r="H1161" s="2" t="n">
-        <v>46063.05567040199</v>
+        <v>46063.05567040509</v>
       </c>
       <c r="I1161" s="2" t="n">
-        <v>46068.05567040199</v>
+        <v>46068.05567040509</v>
       </c>
     </row>
     <row r="1162">
@@ -45752,10 +45752,10 @@
         </is>
       </c>
       <c r="H1162" s="2" t="n">
-        <v>46080.05567040522</v>
+        <v>46080.05567040509</v>
       </c>
       <c r="I1162" s="2" t="n">
-        <v>46085.05567040522</v>
+        <v>46085.05567040509</v>
       </c>
     </row>
     <row r="1163">
@@ -45791,10 +45791,10 @@
         </is>
       </c>
       <c r="H1163" s="2" t="n">
-        <v>46077.0556704085</v>
+        <v>46077.05567040509</v>
       </c>
       <c r="I1163" s="2" t="n">
-        <v>46082.0556704085</v>
+        <v>46082.05567040509</v>
       </c>
     </row>
     <row r="1164">
@@ -45830,10 +45830,10 @@
         </is>
       </c>
       <c r="H1164" s="2" t="n">
-        <v>46073.05567041152</v>
+        <v>46073.05567041667</v>
       </c>
       <c r="I1164" s="2" t="n">
-        <v>46078.05567041152</v>
+        <v>46078.05567041667</v>
       </c>
     </row>
     <row r="1165">
@@ -45869,10 +45869,10 @@
         </is>
       </c>
       <c r="H1165" s="2" t="n">
-        <v>46082.05567041459</v>
+        <v>46082.05567041667</v>
       </c>
       <c r="I1165" s="2" t="n">
-        <v>46087.05567041459</v>
+        <v>46087.05567041667</v>
       </c>
     </row>
     <row r="1166">
@@ -45908,10 +45908,10 @@
         </is>
       </c>
       <c r="H1166" s="2" t="n">
-        <v>46088.05567041774</v>
+        <v>46088.05567041667</v>
       </c>
       <c r="I1166" s="2" t="n">
-        <v>46093.05567041774</v>
+        <v>46093.05567041667</v>
       </c>
     </row>
     <row r="1167">
@@ -45947,10 +45947,10 @@
         </is>
       </c>
       <c r="H1167" s="2" t="n">
-        <v>46068.0556704211</v>
+        <v>46068.05567041667</v>
       </c>
       <c r="I1167" s="2" t="n">
-        <v>46073.0556704211</v>
+        <v>46073.05567041667</v>
       </c>
     </row>
     <row r="1168">
@@ -45986,10 +45986,10 @@
         </is>
       </c>
       <c r="H1168" s="2" t="n">
-        <v>46075.0556704245</v>
+        <v>46075.05567042824</v>
       </c>
       <c r="I1168" s="2" t="n">
-        <v>46080.0556704245</v>
+        <v>46080.05567042824</v>
       </c>
     </row>
     <row r="1169">
@@ -46025,10 +46025,10 @@
         </is>
       </c>
       <c r="H1169" s="2" t="n">
-        <v>46081.05567042749</v>
+        <v>46081.05567042824</v>
       </c>
       <c r="I1169" s="2" t="n">
-        <v>46086.05567042749</v>
+        <v>46086.05567042824</v>
       </c>
     </row>
     <row r="1170">
@@ -46064,10 +46064,10 @@
         </is>
       </c>
       <c r="H1170" s="2" t="n">
-        <v>46066.05567043069</v>
+        <v>46066.05567042824</v>
       </c>
       <c r="I1170" s="2" t="n">
-        <v>46071.05567043069</v>
+        <v>46071.05567042824</v>
       </c>
     </row>
     <row r="1171">
@@ -46103,10 +46103,10 @@
         </is>
       </c>
       <c r="H1171" s="2" t="n">
-        <v>46089.05567043377</v>
+        <v>46089.05567042824</v>
       </c>
       <c r="I1171" s="2" t="n">
-        <v>46094.05567043377</v>
+        <v>46094.05567042824</v>
       </c>
     </row>
     <row r="1172">
@@ -46142,10 +46142,10 @@
         </is>
       </c>
       <c r="H1172" s="2" t="n">
-        <v>46076.0556704369</v>
+        <v>46076.05567043981</v>
       </c>
       <c r="I1172" s="2" t="n">
-        <v>46081.0556704369</v>
+        <v>46081.05567043981</v>
       </c>
     </row>
     <row r="1173">
@@ -46181,10 +46181,10 @@
         </is>
       </c>
       <c r="H1173" s="2" t="n">
-        <v>46078.05567043996</v>
+        <v>46078.05567043981</v>
       </c>
       <c r="I1173" s="2" t="n">
-        <v>46083.05567043996</v>
+        <v>46083.05567043981</v>
       </c>
     </row>
     <row r="1174">
@@ -46220,10 +46220,10 @@
         </is>
       </c>
       <c r="H1174" s="2" t="n">
-        <v>46069.05567044353</v>
+        <v>46069.05567043981</v>
       </c>
       <c r="I1174" s="2" t="n">
-        <v>46074.05567044353</v>
+        <v>46074.05567043981</v>
       </c>
     </row>
     <row r="1175">
@@ -46259,10 +46259,10 @@
         </is>
       </c>
       <c r="H1175" s="2" t="n">
-        <v>46070.05567044654</v>
+        <v>46070.05567045139</v>
       </c>
       <c r="I1175" s="2" t="n">
-        <v>46075.05567044654</v>
+        <v>46075.05567045139</v>
       </c>
     </row>
     <row r="1176">
@@ -46298,10 +46298,10 @@
         </is>
       </c>
       <c r="H1176" s="2" t="n">
-        <v>46066.05567044957</v>
+        <v>46066.05567045139</v>
       </c>
       <c r="I1176" s="2" t="n">
-        <v>46071.05567044957</v>
+        <v>46071.05567045139</v>
       </c>
     </row>
     <row r="1177">
@@ -46337,10 +46337,10 @@
         </is>
       </c>
       <c r="H1177" s="2" t="n">
-        <v>46061.05567045262</v>
+        <v>46061.05567045139</v>
       </c>
       <c r="I1177" s="2" t="n">
-        <v>46066.05567045262</v>
+        <v>46066.05567045139</v>
       </c>
     </row>
     <row r="1178">
@@ -46376,10 +46376,10 @@
         </is>
       </c>
       <c r="H1178" s="2" t="n">
-        <v>46064.05567045596</v>
+        <v>46064.05567045139</v>
       </c>
       <c r="I1178" s="2" t="n">
-        <v>46069.05567045596</v>
+        <v>46069.05567045139</v>
       </c>
     </row>
     <row r="1179">
@@ -46415,10 +46415,10 @@
         </is>
       </c>
       <c r="H1179" s="2" t="n">
-        <v>46078.05567045918</v>
+        <v>46078.05567046296</v>
       </c>
       <c r="I1179" s="2" t="n">
-        <v>46083.05567045918</v>
+        <v>46083.05567046296</v>
       </c>
     </row>
     <row r="1180">
@@ -46454,10 +46454,10 @@
         </is>
       </c>
       <c r="H1180" s="2" t="n">
-        <v>46069.05567046218</v>
+        <v>46069.05567046296</v>
       </c>
       <c r="I1180" s="2" t="n">
-        <v>46074.05567046218</v>
+        <v>46074.05567046296</v>
       </c>
     </row>
     <row r="1181">
@@ -46493,10 +46493,10 @@
         </is>
       </c>
       <c r="H1181" s="2" t="n">
-        <v>46070.05567046547</v>
+        <v>46070.05567046296</v>
       </c>
       <c r="I1181" s="2" t="n">
-        <v>46075.05567046547</v>
+        <v>46075.05567046296</v>
       </c>
     </row>
     <row r="1182">
@@ -46532,10 +46532,10 @@
         </is>
       </c>
       <c r="H1182" s="2" t="n">
-        <v>46074.05567046876</v>
+        <v>46074.05567047454</v>
       </c>
       <c r="I1182" s="2" t="n">
-        <v>46079.05567046876</v>
+        <v>46079.05567047454</v>
       </c>
     </row>
     <row r="1183">
@@ -46571,10 +46571,10 @@
         </is>
       </c>
       <c r="H1183" s="2" t="n">
-        <v>46063.05567047193</v>
+        <v>46063.05567047454</v>
       </c>
       <c r="I1183" s="2" t="n">
-        <v>46068.05567047193</v>
+        <v>46068.05567047454</v>
       </c>
     </row>
     <row r="1184">
@@ -46610,10 +46610,10 @@
         </is>
       </c>
       <c r="H1184" s="2" t="n">
-        <v>46088.05567047513</v>
+        <v>46088.05567047454</v>
       </c>
       <c r="I1184" s="2" t="n">
-        <v>46093.05567047513</v>
+        <v>46093.05567047454</v>
       </c>
     </row>
     <row r="1185">
@@ -46649,10 +46649,10 @@
         </is>
       </c>
       <c r="H1185" s="2" t="n">
-        <v>46070.0556704785</v>
+        <v>46070.05567047454</v>
       </c>
       <c r="I1185" s="2" t="n">
-        <v>46075.0556704785</v>
+        <v>46075.05567047454</v>
       </c>
     </row>
     <row r="1186">
@@ -46688,10 +46688,10 @@
         </is>
       </c>
       <c r="H1186" s="2" t="n">
-        <v>46083.05567048164</v>
+        <v>46083.05567048611</v>
       </c>
       <c r="I1186" s="2" t="n">
-        <v>46088.05567048164</v>
+        <v>46088.05567048611</v>
       </c>
     </row>
     <row r="1187">
@@ -46727,10 +46727,10 @@
         </is>
       </c>
       <c r="H1187" s="2" t="n">
-        <v>46086.05567048479</v>
+        <v>46086.05567048611</v>
       </c>
       <c r="I1187" s="2" t="n">
-        <v>46091.05567048479</v>
+        <v>46091.05567048611</v>
       </c>
     </row>
     <row r="1188">
@@ -46766,10 +46766,10 @@
         </is>
       </c>
       <c r="H1188" s="2" t="n">
-        <v>46078.05567048779</v>
+        <v>46078.05567048611</v>
       </c>
       <c r="I1188" s="2" t="n">
-        <v>46083.05567048779</v>
+        <v>46083.05567048611</v>
       </c>
     </row>
     <row r="1189">
@@ -46805,10 +46805,10 @@
         </is>
       </c>
       <c r="H1189" s="2" t="n">
-        <v>46065.05567049114</v>
+        <v>46065.05567048611</v>
       </c>
       <c r="I1189" s="2" t="n">
-        <v>46070.05567049114</v>
+        <v>46070.05567048611</v>
       </c>
     </row>
     <row r="1190">
@@ -46844,10 +46844,10 @@
         </is>
       </c>
       <c r="H1190" s="2" t="n">
-        <v>46082.05567049429</v>
+        <v>46082.05567049768</v>
       </c>
       <c r="I1190" s="2" t="n">
-        <v>46087.05567049429</v>
+        <v>46087.05567049768</v>
       </c>
     </row>
     <row r="1191">
@@ -46883,10 +46883,10 @@
         </is>
       </c>
       <c r="H1191" s="2" t="n">
-        <v>46089.05567049731</v>
+        <v>46089.05567049768</v>
       </c>
       <c r="I1191" s="2" t="n">
-        <v>46094.05567049731</v>
+        <v>46094.05567049768</v>
       </c>
     </row>
     <row r="1192">
@@ -46922,10 +46922,10 @@
         </is>
       </c>
       <c r="H1192" s="2" t="n">
-        <v>46075.0556705006</v>
+        <v>46075.05567049768</v>
       </c>
       <c r="I1192" s="2" t="n">
-        <v>46080.0556705006</v>
+        <v>46080.05567049768</v>
       </c>
     </row>
     <row r="1193">
@@ -46961,10 +46961,10 @@
         </is>
       </c>
       <c r="H1193" s="2" t="n">
-        <v>46082.05567050374</v>
+        <v>46082.05567050926</v>
       </c>
       <c r="I1193" s="2" t="n">
-        <v>46087.05567050374</v>
+        <v>46087.05567050926</v>
       </c>
     </row>
     <row r="1194">
@@ -47000,10 +47000,10 @@
         </is>
       </c>
       <c r="H1194" s="2" t="n">
-        <v>46064.05567050678</v>
+        <v>46064.05567050926</v>
       </c>
       <c r="I1194" s="2" t="n">
-        <v>46069.05567050678</v>
+        <v>46069.05567050926</v>
       </c>
     </row>
     <row r="1195">
@@ -47039,10 +47039,10 @@
         </is>
       </c>
       <c r="H1195" s="2" t="n">
-        <v>46061.05567050973</v>
+        <v>46061.05567050926</v>
       </c>
       <c r="I1195" s="2" t="n">
-        <v>46066.05567050973</v>
+        <v>46066.05567050926</v>
       </c>
     </row>
     <row r="1196">
@@ -47078,10 +47078,10 @@
         </is>
       </c>
       <c r="H1196" s="2" t="n">
-        <v>46063.0556705131</v>
+        <v>46063.05567050926</v>
       </c>
       <c r="I1196" s="2" t="n">
-        <v>46068.0556705131</v>
+        <v>46068.05567050926</v>
       </c>
     </row>
     <row r="1197">
@@ -47117,10 +47117,10 @@
         </is>
       </c>
       <c r="H1197" s="2" t="n">
-        <v>46068.05567051612</v>
+        <v>46068.05567052084</v>
       </c>
       <c r="I1197" s="2" t="n">
-        <v>46073.05567051612</v>
+        <v>46073.05567052084</v>
       </c>
     </row>
     <row r="1198">
@@ -47156,10 +47156,10 @@
         </is>
       </c>
       <c r="H1198" s="2" t="n">
-        <v>46069.05567051921</v>
+        <v>46069.05567052084</v>
       </c>
       <c r="I1198" s="2" t="n">
-        <v>46074.05567051921</v>
+        <v>46074.05567052084</v>
       </c>
     </row>
     <row r="1199">
@@ -47195,10 +47195,10 @@
         </is>
       </c>
       <c r="H1199" s="2" t="n">
-        <v>46079.05567052276</v>
+        <v>46079.05567052084</v>
       </c>
       <c r="I1199" s="2" t="n">
-        <v>46084.05567052276</v>
+        <v>46084.05567052084</v>
       </c>
     </row>
     <row r="1200">
@@ -47234,10 +47234,10 @@
         </is>
       </c>
       <c r="H1200" s="2" t="n">
-        <v>46075.05567052597</v>
+        <v>46075.05567052084</v>
       </c>
       <c r="I1200" s="2" t="n">
-        <v>46080.05567052597</v>
+        <v>46080.05567052084</v>
       </c>
     </row>
     <row r="1201">
@@ -47273,10 +47273,1960 @@
         </is>
       </c>
       <c r="H1201" s="2" t="n">
-        <v>46062.05567052915</v>
+        <v>46062.05567053241</v>
       </c>
       <c r="I1201" s="2" t="n">
-        <v>46067.05567052915</v>
+        <v>46067.05567053241</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>9a8ff805-6da3-4da3-b1ef-f58c00603732</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1202" t="n">
+        <v>9040.41</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1202" s="2" t="n">
+        <v>46071.17316444519</v>
+      </c>
+      <c r="I1202" s="2" t="n">
+        <v>46076.17316444519</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>6eb81ee1-6e66-41bc-9aed-38095788779f</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1203" t="n">
+        <v>1382.67</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1203" s="2" t="n">
+        <v>46060.17316444956</v>
+      </c>
+      <c r="I1203" s="2" t="n">
+        <v>46065.17316444956</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>7cfc8e0c-02a5-4518-9d5a-7113557c184e</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1204" t="n">
+        <v>1066.45</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1204" s="2" t="n">
+        <v>46070.17316445275</v>
+      </c>
+      <c r="I1204" s="2" t="n">
+        <v>46075.17316445275</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>596693ff-c197-470c-83c5-ff193f42a5ed</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1205" t="n">
+        <v>2321.02</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1205" s="2" t="n">
+        <v>46084.17316445591</v>
+      </c>
+      <c r="I1205" s="2" t="n">
+        <v>46089.17316445591</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2dde8c4e-2466-4cf3-accf-9d2acd738fbb</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1206" t="n">
+        <v>2547.84</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1206" s="2" t="n">
+        <v>46080.17316445887</v>
+      </c>
+      <c r="I1206" s="2" t="n">
+        <v>46085.17316445887</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>f021a564-f38d-4a0a-b157-17e169e61a38</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1207" t="n">
+        <v>2178.76</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1207" s="2" t="n">
+        <v>46060.17316446183</v>
+      </c>
+      <c r="I1207" s="2" t="n">
+        <v>46065.17316446183</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>3a1d1b14-3923-45b1-b286-e485dd10740c</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1208" t="n">
+        <v>5427.77</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1208" s="2" t="n">
+        <v>46068.17316446478</v>
+      </c>
+      <c r="I1208" s="2" t="n">
+        <v>46073.17316446478</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2071a1ba-aae1-400f-aad6-a03e2c96d338</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1209" t="n">
+        <v>6131.9</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1209" s="2" t="n">
+        <v>46067.17316446762</v>
+      </c>
+      <c r="I1209" s="2" t="n">
+        <v>46072.17316446762</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>9ad3e4dc-e4d4-45a3-bd81-430fdbcf5f65</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1210" t="n">
+        <v>1728.07</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1210" s="2" t="n">
+        <v>46089.17316447046</v>
+      </c>
+      <c r="I1210" s="2" t="n">
+        <v>46094.17316447046</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>e58e06c0-083a-4911-88db-58130f90716c</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1211" t="n">
+        <v>5069.81</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1211" s="2" t="n">
+        <v>46079.17316447342</v>
+      </c>
+      <c r="I1211" s="2" t="n">
+        <v>46084.17316447342</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>ac1cc16c-c20a-4c98-827a-b36c83d66644</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1212" t="n">
+        <v>4876.52</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1212" s="2" t="n">
+        <v>46087.17316447636</v>
+      </c>
+      <c r="I1212" s="2" t="n">
+        <v>46092.17316447636</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>61ef864d-5038-4613-983f-45fc3d206e2b</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1213" t="n">
+        <v>3496.02</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1213" s="2" t="n">
+        <v>46084.17316447932</v>
+      </c>
+      <c r="I1213" s="2" t="n">
+        <v>46089.17316447932</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>dfeb839d-8703-433f-8bdd-56112e282277</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1214" t="n">
+        <v>1646.57</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1214" s="2" t="n">
+        <v>46067.17316448212</v>
+      </c>
+      <c r="I1214" s="2" t="n">
+        <v>46072.17316448212</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>91b0138d-aecb-43cc-b23d-5d29a1db951f</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1215" t="n">
+        <v>1821.46</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1215" s="2" t="n">
+        <v>46073.17316448507</v>
+      </c>
+      <c r="I1215" s="2" t="n">
+        <v>46078.17316448507</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>9c8e2496-1f1e-405e-9fa0-985b00fda461</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1216" t="n">
+        <v>5652.38</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>99.91</v>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1216" s="2" t="n">
+        <v>46064.17316448804</v>
+      </c>
+      <c r="I1216" s="2" t="n">
+        <v>46069.17316448804</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>55a1d6a0-fffd-4488-b317-a266765d87a0</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1217" t="n">
+        <v>6166.33</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1217" s="2" t="n">
+        <v>46077.17316449086</v>
+      </c>
+      <c r="I1217" s="2" t="n">
+        <v>46082.17316449086</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>177bf079-0211-4389-8503-686b1f1a1a6d</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1218" t="n">
+        <v>9917.950000000001</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1218" s="2" t="n">
+        <v>46076.17316449368</v>
+      </c>
+      <c r="I1218" s="2" t="n">
+        <v>46081.17316449368</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>9e93126b-69c6-4ad5-86c8-2bd587aa43ed</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1219" t="n">
+        <v>6580.12</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1219" s="2" t="n">
+        <v>46072.17316449668</v>
+      </c>
+      <c r="I1219" s="2" t="n">
+        <v>46077.17316449668</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>c30dcdeb-1eb3-4e45-bd5c-88e93fb3840e</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1220" t="n">
+        <v>4962.84</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1220" s="2" t="n">
+        <v>46073.17316449956</v>
+      </c>
+      <c r="I1220" s="2" t="n">
+        <v>46078.17316449956</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>be96c13b-a08f-47f8-9b98-91042f4d0095</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>3667.88</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1221" s="2" t="n">
+        <v>46075.1731645024</v>
+      </c>
+      <c r="I1221" s="2" t="n">
+        <v>46080.1731645024</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>e9cc9899-a89d-4165-9b89-8dcdbb2e5949</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>2351.36</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1222" s="2" t="n">
+        <v>46076.17316450524</v>
+      </c>
+      <c r="I1222" s="2" t="n">
+        <v>46081.17316450524</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>bfc165f5-879e-485f-a379-7a153e0cb1f7</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>4972.71</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1223" s="2" t="n">
+        <v>46080.17316450816</v>
+      </c>
+      <c r="I1223" s="2" t="n">
+        <v>46085.17316450816</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>c49fa654-d4bc-423d-9713-72190c1a1eb5</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>4228.13</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1224" s="2" t="n">
+        <v>46066.17316451106</v>
+      </c>
+      <c r="I1224" s="2" t="n">
+        <v>46071.17316451106</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>0c3b1af1-6e10-4338-b047-6ad57d99f9e2</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1225" t="n">
+        <v>9162.33</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1225" s="2" t="n">
+        <v>46062.17316451402</v>
+      </c>
+      <c r="I1225" s="2" t="n">
+        <v>46067.17316451402</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>d17e70c4-6cfb-4fcb-ab96-cf70cb5d3c51</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1226" t="n">
+        <v>3892.21</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>99.08</v>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1226" s="2" t="n">
+        <v>46080.1731645168</v>
+      </c>
+      <c r="I1226" s="2" t="n">
+        <v>46085.1731645168</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>a05239ce-9766-4939-8328-c688ce099f98</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1227" t="n">
+        <v>4145.55</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1227" s="2" t="n">
+        <v>46074.17316451982</v>
+      </c>
+      <c r="I1227" s="2" t="n">
+        <v>46079.17316451982</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>fb91054a-0ddc-449f-9813-17f721d8ed71</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1228" t="n">
+        <v>6410.37</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1228" s="2" t="n">
+        <v>46080.17316452265</v>
+      </c>
+      <c r="I1228" s="2" t="n">
+        <v>46085.17316452265</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>438e6c33-561f-40e8-8db1-dfdca7b3e896</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1229" t="n">
+        <v>9959.33</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1229" s="2" t="n">
+        <v>46061.17316452546</v>
+      </c>
+      <c r="I1229" s="2" t="n">
+        <v>46066.17316452546</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>eb675ef2-a6e8-408c-aaae-53eafb439578</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1230" t="n">
+        <v>6039.23</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1230" s="2" t="n">
+        <v>46080.17316452834</v>
+      </c>
+      <c r="I1230" s="2" t="n">
+        <v>46085.17316452834</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>9a31b5aa-4f68-4fbe-873a-0448c3f59d19</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1231" t="n">
+        <v>1590.45</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1231" s="2" t="n">
+        <v>46061.1731645313</v>
+      </c>
+      <c r="I1231" s="2" t="n">
+        <v>46066.1731645313</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>08ef3b3a-3584-40e2-ae2d-db4b7260616c</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1232" t="n">
+        <v>1190.87</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1232" s="2" t="n">
+        <v>46079.17316453414</v>
+      </c>
+      <c r="I1232" s="2" t="n">
+        <v>46084.17316453414</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>87536869-7fa6-422f-825f-36f07177e404</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1233" t="n">
+        <v>4138.78</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1233" s="2" t="n">
+        <v>46080.17316453707</v>
+      </c>
+      <c r="I1233" s="2" t="n">
+        <v>46085.17316453707</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>7e5f2b36-466e-48ab-912b-15351ead53c6</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1234" t="n">
+        <v>9334.91</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1234" s="2" t="n">
+        <v>46087.17316453999</v>
+      </c>
+      <c r="I1234" s="2" t="n">
+        <v>46092.17316453999</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>a0a624e9-5a4e-4e4e-8f0e-f5c33e9065b1</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1235" t="n">
+        <v>9604.1</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1235" s="2" t="n">
+        <v>46072.17316454306</v>
+      </c>
+      <c r="I1235" s="2" t="n">
+        <v>46077.17316454306</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>7da06451-7637-4e8e-a945-bbd0f9c4c823</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1236" t="n">
+        <v>1644.93</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1236" s="2" t="n">
+        <v>46069.17316454583</v>
+      </c>
+      <c r="I1236" s="2" t="n">
+        <v>46074.17316454583</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>70e017c0-d36d-4bb3-80dd-50cef40c261c</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1237" t="n">
+        <v>5629.57</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1237" s="2" t="n">
+        <v>46083.17316454877</v>
+      </c>
+      <c r="I1237" s="2" t="n">
+        <v>46088.17316454877</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>6748ac31-4d13-4f4f-a60e-1fdff1edf4dd</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1238" t="n">
+        <v>4698.78</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>89.13</v>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1238" s="2" t="n">
+        <v>46061.17316455154</v>
+      </c>
+      <c r="I1238" s="2" t="n">
+        <v>46066.17316455154</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>32ae9cc1-19eb-44e4-8424-4ff932fc20ce</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1239" t="n">
+        <v>7564.56</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1239" s="2" t="n">
+        <v>46088.17316455442</v>
+      </c>
+      <c r="I1239" s="2" t="n">
+        <v>46093.17316455442</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>3e2da127-51fa-4e4b-a534-c680530aac0f</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1240" t="n">
+        <v>5916.63</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1240" s="2" t="n">
+        <v>46063.17316455724</v>
+      </c>
+      <c r="I1240" s="2" t="n">
+        <v>46068.17316455724</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>03edb0d7-86ad-4298-85bb-d8383182d0e5</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1241" t="n">
+        <v>5259.11</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1241" s="2" t="n">
+        <v>46069.17316456001</v>
+      </c>
+      <c r="I1241" s="2" t="n">
+        <v>46074.17316456001</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>4c573721-54ef-44ec-b407-144c237e2596</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1242" t="n">
+        <v>6648.73</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1242" s="2" t="n">
+        <v>46061.17316456295</v>
+      </c>
+      <c r="I1242" s="2" t="n">
+        <v>46066.17316456295</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>02f6b388-0396-44af-af45-818bf41cecee</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1243" t="n">
+        <v>3782.16</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1243" s="2" t="n">
+        <v>46068.17316456592</v>
+      </c>
+      <c r="I1243" s="2" t="n">
+        <v>46073.17316456592</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>e5566647-dbd8-4d00-9f9f-bf4e8f44350f</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1244" t="n">
+        <v>4823.16</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>94.34999999999999</v>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1244" s="2" t="n">
+        <v>46071.17316456875</v>
+      </c>
+      <c r="I1244" s="2" t="n">
+        <v>46076.17316456875</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>53d03aa6-8b91-4402-afc5-18e0a2422c7d</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1245" t="n">
+        <v>9309.469999999999</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1245" s="2" t="n">
+        <v>46069.1731645716</v>
+      </c>
+      <c r="I1245" s="2" t="n">
+        <v>46074.1731645716</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>b3525334-3cb2-461b-855b-ba39faa00e6e</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1246" t="n">
+        <v>3366.38</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1246" s="2" t="n">
+        <v>46067.17316457452</v>
+      </c>
+      <c r="I1246" s="2" t="n">
+        <v>46072.17316457452</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>be6fbd69-e5c9-47ac-94c5-a6eddb3ee14c</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1247" t="n">
+        <v>5474.24</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1247" s="2" t="n">
+        <v>46082.17316457738</v>
+      </c>
+      <c r="I1247" s="2" t="n">
+        <v>46087.17316457738</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>0bdb2e56-1f52-4ed9-a45a-a0069354e994</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1248" t="n">
+        <v>2047.57</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1248" s="2" t="n">
+        <v>46066.17316458028</v>
+      </c>
+      <c r="I1248" s="2" t="n">
+        <v>46071.17316458028</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>18b55cba-6b9c-4e06-9977-e93909a1f08e</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1249" t="n">
+        <v>8592.34</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>91.31</v>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1249" s="2" t="n">
+        <v>46061.17316458326</v>
+      </c>
+      <c r="I1249" s="2" t="n">
+        <v>46066.17316458326</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>c559c979-3a78-4837-9383-c508d34515c8</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1250" t="n">
+        <v>9087.58</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1250" s="2" t="n">
+        <v>46063.17316458606</v>
+      </c>
+      <c r="I1250" s="2" t="n">
+        <v>46068.17316458606</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>db3046ee-b42d-4d8f-86d3-2f3c746bcd21</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1251" t="n">
+        <v>1925.55</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1251" s="2" t="n">
+        <v>46072.17316458908</v>
+      </c>
+      <c r="I1251" s="2" t="n">
+        <v>46077.17316458908</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1251"/>
+  <dimension ref="A1:I1301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47312,10 +47312,10 @@
         </is>
       </c>
       <c r="H1202" s="2" t="n">
-        <v>46071.17316444519</v>
+        <v>46071.17316444444</v>
       </c>
       <c r="I1202" s="2" t="n">
-        <v>46076.17316444519</v>
+        <v>46076.17316444444</v>
       </c>
     </row>
     <row r="1203">
@@ -47351,10 +47351,10 @@
         </is>
       </c>
       <c r="H1203" s="2" t="n">
-        <v>46060.17316444956</v>
+        <v>46060.17316444444</v>
       </c>
       <c r="I1203" s="2" t="n">
-        <v>46065.17316444956</v>
+        <v>46065.17316444444</v>
       </c>
     </row>
     <row r="1204">
@@ -47390,10 +47390,10 @@
         </is>
       </c>
       <c r="H1204" s="2" t="n">
-        <v>46070.17316445275</v>
+        <v>46070.17316445602</v>
       </c>
       <c r="I1204" s="2" t="n">
-        <v>46075.17316445275</v>
+        <v>46075.17316445602</v>
       </c>
     </row>
     <row r="1205">
@@ -47429,10 +47429,10 @@
         </is>
       </c>
       <c r="H1205" s="2" t="n">
-        <v>46084.17316445591</v>
+        <v>46084.17316445602</v>
       </c>
       <c r="I1205" s="2" t="n">
-        <v>46089.17316445591</v>
+        <v>46089.17316445602</v>
       </c>
     </row>
     <row r="1206">
@@ -47468,10 +47468,10 @@
         </is>
       </c>
       <c r="H1206" s="2" t="n">
-        <v>46080.17316445887</v>
+        <v>46080.17316445602</v>
       </c>
       <c r="I1206" s="2" t="n">
-        <v>46085.17316445887</v>
+        <v>46085.17316445602</v>
       </c>
     </row>
     <row r="1207">
@@ -47507,10 +47507,10 @@
         </is>
       </c>
       <c r="H1207" s="2" t="n">
-        <v>46060.17316446183</v>
+        <v>46060.17316446759</v>
       </c>
       <c r="I1207" s="2" t="n">
-        <v>46065.17316446183</v>
+        <v>46065.17316446759</v>
       </c>
     </row>
     <row r="1208">
@@ -47546,10 +47546,10 @@
         </is>
       </c>
       <c r="H1208" s="2" t="n">
-        <v>46068.17316446478</v>
+        <v>46068.17316446759</v>
       </c>
       <c r="I1208" s="2" t="n">
-        <v>46073.17316446478</v>
+        <v>46073.17316446759</v>
       </c>
     </row>
     <row r="1209">
@@ -47585,10 +47585,10 @@
         </is>
       </c>
       <c r="H1209" s="2" t="n">
-        <v>46067.17316446762</v>
+        <v>46067.17316446759</v>
       </c>
       <c r="I1209" s="2" t="n">
-        <v>46072.17316446762</v>
+        <v>46072.17316446759</v>
       </c>
     </row>
     <row r="1210">
@@ -47624,10 +47624,10 @@
         </is>
       </c>
       <c r="H1210" s="2" t="n">
-        <v>46089.17316447046</v>
+        <v>46089.17316446759</v>
       </c>
       <c r="I1210" s="2" t="n">
-        <v>46094.17316447046</v>
+        <v>46094.17316446759</v>
       </c>
     </row>
     <row r="1211">
@@ -47663,10 +47663,10 @@
         </is>
       </c>
       <c r="H1211" s="2" t="n">
-        <v>46079.17316447342</v>
+        <v>46079.17316447917</v>
       </c>
       <c r="I1211" s="2" t="n">
-        <v>46084.17316447342</v>
+        <v>46084.17316447917</v>
       </c>
     </row>
     <row r="1212">
@@ -47702,10 +47702,10 @@
         </is>
       </c>
       <c r="H1212" s="2" t="n">
-        <v>46087.17316447636</v>
+        <v>46087.17316447917</v>
       </c>
       <c r="I1212" s="2" t="n">
-        <v>46092.17316447636</v>
+        <v>46092.17316447917</v>
       </c>
     </row>
     <row r="1213">
@@ -47741,10 +47741,10 @@
         </is>
       </c>
       <c r="H1213" s="2" t="n">
-        <v>46084.17316447932</v>
+        <v>46084.17316447917</v>
       </c>
       <c r="I1213" s="2" t="n">
-        <v>46089.17316447932</v>
+        <v>46089.17316447917</v>
       </c>
     </row>
     <row r="1214">
@@ -47780,10 +47780,10 @@
         </is>
       </c>
       <c r="H1214" s="2" t="n">
-        <v>46067.17316448212</v>
+        <v>46067.17316447917</v>
       </c>
       <c r="I1214" s="2" t="n">
-        <v>46072.17316448212</v>
+        <v>46072.17316447917</v>
       </c>
     </row>
     <row r="1215">
@@ -47819,10 +47819,10 @@
         </is>
       </c>
       <c r="H1215" s="2" t="n">
-        <v>46073.17316448507</v>
+        <v>46073.17316449074</v>
       </c>
       <c r="I1215" s="2" t="n">
-        <v>46078.17316448507</v>
+        <v>46078.17316449074</v>
       </c>
     </row>
     <row r="1216">
@@ -47858,10 +47858,10 @@
         </is>
       </c>
       <c r="H1216" s="2" t="n">
-        <v>46064.17316448804</v>
+        <v>46064.17316449074</v>
       </c>
       <c r="I1216" s="2" t="n">
-        <v>46069.17316448804</v>
+        <v>46069.17316449074</v>
       </c>
     </row>
     <row r="1217">
@@ -47897,10 +47897,10 @@
         </is>
       </c>
       <c r="H1217" s="2" t="n">
-        <v>46077.17316449086</v>
+        <v>46077.17316449074</v>
       </c>
       <c r="I1217" s="2" t="n">
-        <v>46082.17316449086</v>
+        <v>46082.17316449074</v>
       </c>
     </row>
     <row r="1218">
@@ -47936,10 +47936,10 @@
         </is>
       </c>
       <c r="H1218" s="2" t="n">
-        <v>46076.17316449368</v>
+        <v>46076.17316449074</v>
       </c>
       <c r="I1218" s="2" t="n">
-        <v>46081.17316449368</v>
+        <v>46081.17316449074</v>
       </c>
     </row>
     <row r="1219">
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="H1219" s="2" t="n">
-        <v>46072.17316449668</v>
+        <v>46072.17316450232</v>
       </c>
       <c r="I1219" s="2" t="n">
-        <v>46077.17316449668</v>
+        <v>46077.17316450232</v>
       </c>
     </row>
     <row r="1220">
@@ -48014,10 +48014,10 @@
         </is>
       </c>
       <c r="H1220" s="2" t="n">
-        <v>46073.17316449956</v>
+        <v>46073.17316450232</v>
       </c>
       <c r="I1220" s="2" t="n">
-        <v>46078.17316449956</v>
+        <v>46078.17316450232</v>
       </c>
     </row>
     <row r="1221">
@@ -48053,10 +48053,10 @@
         </is>
       </c>
       <c r="H1221" s="2" t="n">
-        <v>46075.1731645024</v>
+        <v>46075.17316450232</v>
       </c>
       <c r="I1221" s="2" t="n">
-        <v>46080.1731645024</v>
+        <v>46080.17316450232</v>
       </c>
     </row>
     <row r="1222">
@@ -48092,10 +48092,10 @@
         </is>
       </c>
       <c r="H1222" s="2" t="n">
-        <v>46076.17316450524</v>
+        <v>46076.17316450232</v>
       </c>
       <c r="I1222" s="2" t="n">
-        <v>46081.17316450524</v>
+        <v>46081.17316450232</v>
       </c>
     </row>
     <row r="1223">
@@ -48131,10 +48131,10 @@
         </is>
       </c>
       <c r="H1223" s="2" t="n">
-        <v>46080.17316450816</v>
+        <v>46080.17316451389</v>
       </c>
       <c r="I1223" s="2" t="n">
-        <v>46085.17316450816</v>
+        <v>46085.17316451389</v>
       </c>
     </row>
     <row r="1224">
@@ -48170,10 +48170,10 @@
         </is>
       </c>
       <c r="H1224" s="2" t="n">
-        <v>46066.17316451106</v>
+        <v>46066.17316451389</v>
       </c>
       <c r="I1224" s="2" t="n">
-        <v>46071.17316451106</v>
+        <v>46071.17316451389</v>
       </c>
     </row>
     <row r="1225">
@@ -48209,10 +48209,10 @@
         </is>
       </c>
       <c r="H1225" s="2" t="n">
-        <v>46062.17316451402</v>
+        <v>46062.17316451389</v>
       </c>
       <c r="I1225" s="2" t="n">
-        <v>46067.17316451402</v>
+        <v>46067.17316451389</v>
       </c>
     </row>
     <row r="1226">
@@ -48248,10 +48248,10 @@
         </is>
       </c>
       <c r="H1226" s="2" t="n">
-        <v>46080.1731645168</v>
+        <v>46080.17316451389</v>
       </c>
       <c r="I1226" s="2" t="n">
-        <v>46085.1731645168</v>
+        <v>46085.17316451389</v>
       </c>
     </row>
     <row r="1227">
@@ -48287,10 +48287,10 @@
         </is>
       </c>
       <c r="H1227" s="2" t="n">
-        <v>46074.17316451982</v>
+        <v>46074.17316452546</v>
       </c>
       <c r="I1227" s="2" t="n">
-        <v>46079.17316451982</v>
+        <v>46079.17316452546</v>
       </c>
     </row>
     <row r="1228">
@@ -48326,10 +48326,10 @@
         </is>
       </c>
       <c r="H1228" s="2" t="n">
-        <v>46080.17316452265</v>
+        <v>46080.17316452546</v>
       </c>
       <c r="I1228" s="2" t="n">
-        <v>46085.17316452265</v>
+        <v>46085.17316452546</v>
       </c>
     </row>
     <row r="1229">
@@ -48404,10 +48404,10 @@
         </is>
       </c>
       <c r="H1230" s="2" t="n">
-        <v>46080.17316452834</v>
+        <v>46080.17316452546</v>
       </c>
       <c r="I1230" s="2" t="n">
-        <v>46085.17316452834</v>
+        <v>46085.17316452546</v>
       </c>
     </row>
     <row r="1231">
@@ -48443,10 +48443,10 @@
         </is>
       </c>
       <c r="H1231" s="2" t="n">
-        <v>46061.1731645313</v>
+        <v>46061.17316453704</v>
       </c>
       <c r="I1231" s="2" t="n">
-        <v>46066.1731645313</v>
+        <v>46066.17316453704</v>
       </c>
     </row>
     <row r="1232">
@@ -48482,10 +48482,10 @@
         </is>
       </c>
       <c r="H1232" s="2" t="n">
-        <v>46079.17316453414</v>
+        <v>46079.17316453704</v>
       </c>
       <c r="I1232" s="2" t="n">
-        <v>46084.17316453414</v>
+        <v>46084.17316453704</v>
       </c>
     </row>
     <row r="1233">
@@ -48521,10 +48521,10 @@
         </is>
       </c>
       <c r="H1233" s="2" t="n">
-        <v>46080.17316453707</v>
+        <v>46080.17316453704</v>
       </c>
       <c r="I1233" s="2" t="n">
-        <v>46085.17316453707</v>
+        <v>46085.17316453704</v>
       </c>
     </row>
     <row r="1234">
@@ -48560,10 +48560,10 @@
         </is>
       </c>
       <c r="H1234" s="2" t="n">
-        <v>46087.17316453999</v>
+        <v>46087.17316453704</v>
       </c>
       <c r="I1234" s="2" t="n">
-        <v>46092.17316453999</v>
+        <v>46092.17316453704</v>
       </c>
     </row>
     <row r="1235">
@@ -48599,10 +48599,10 @@
         </is>
       </c>
       <c r="H1235" s="2" t="n">
-        <v>46072.17316454306</v>
+        <v>46072.17316454861</v>
       </c>
       <c r="I1235" s="2" t="n">
-        <v>46077.17316454306</v>
+        <v>46077.17316454861</v>
       </c>
     </row>
     <row r="1236">
@@ -48638,10 +48638,10 @@
         </is>
       </c>
       <c r="H1236" s="2" t="n">
-        <v>46069.17316454583</v>
+        <v>46069.17316454861</v>
       </c>
       <c r="I1236" s="2" t="n">
-        <v>46074.17316454583</v>
+        <v>46074.17316454861</v>
       </c>
     </row>
     <row r="1237">
@@ -48677,10 +48677,10 @@
         </is>
       </c>
       <c r="H1237" s="2" t="n">
-        <v>46083.17316454877</v>
+        <v>46083.17316454861</v>
       </c>
       <c r="I1237" s="2" t="n">
-        <v>46088.17316454877</v>
+        <v>46088.17316454861</v>
       </c>
     </row>
     <row r="1238">
@@ -48716,10 +48716,10 @@
         </is>
       </c>
       <c r="H1238" s="2" t="n">
-        <v>46061.17316455154</v>
+        <v>46061.17316454861</v>
       </c>
       <c r="I1238" s="2" t="n">
-        <v>46066.17316455154</v>
+        <v>46066.17316454861</v>
       </c>
     </row>
     <row r="1239">
@@ -48755,10 +48755,10 @@
         </is>
       </c>
       <c r="H1239" s="2" t="n">
-        <v>46088.17316455442</v>
+        <v>46088.17316456018</v>
       </c>
       <c r="I1239" s="2" t="n">
-        <v>46093.17316455442</v>
+        <v>46093.17316456018</v>
       </c>
     </row>
     <row r="1240">
@@ -48794,10 +48794,10 @@
         </is>
       </c>
       <c r="H1240" s="2" t="n">
-        <v>46063.17316455724</v>
+        <v>46063.17316456018</v>
       </c>
       <c r="I1240" s="2" t="n">
-        <v>46068.17316455724</v>
+        <v>46068.17316456018</v>
       </c>
     </row>
     <row r="1241">
@@ -48833,10 +48833,10 @@
         </is>
       </c>
       <c r="H1241" s="2" t="n">
-        <v>46069.17316456001</v>
+        <v>46069.17316456018</v>
       </c>
       <c r="I1241" s="2" t="n">
-        <v>46074.17316456001</v>
+        <v>46074.17316456018</v>
       </c>
     </row>
     <row r="1242">
@@ -48872,10 +48872,10 @@
         </is>
       </c>
       <c r="H1242" s="2" t="n">
-        <v>46061.17316456295</v>
+        <v>46061.17316456018</v>
       </c>
       <c r="I1242" s="2" t="n">
-        <v>46066.17316456295</v>
+        <v>46066.17316456018</v>
       </c>
     </row>
     <row r="1243">
@@ -48911,10 +48911,10 @@
         </is>
       </c>
       <c r="H1243" s="2" t="n">
-        <v>46068.17316456592</v>
+        <v>46068.17316456018</v>
       </c>
       <c r="I1243" s="2" t="n">
-        <v>46073.17316456592</v>
+        <v>46073.17316456018</v>
       </c>
     </row>
     <row r="1244">
@@ -48950,10 +48950,10 @@
         </is>
       </c>
       <c r="H1244" s="2" t="n">
-        <v>46071.17316456875</v>
+        <v>46071.17316457176</v>
       </c>
       <c r="I1244" s="2" t="n">
-        <v>46076.17316456875</v>
+        <v>46076.17316457176</v>
       </c>
     </row>
     <row r="1245">
@@ -48989,10 +48989,10 @@
         </is>
       </c>
       <c r="H1245" s="2" t="n">
-        <v>46069.1731645716</v>
+        <v>46069.17316457176</v>
       </c>
       <c r="I1245" s="2" t="n">
-        <v>46074.1731645716</v>
+        <v>46074.17316457176</v>
       </c>
     </row>
     <row r="1246">
@@ -49028,10 +49028,10 @@
         </is>
       </c>
       <c r="H1246" s="2" t="n">
-        <v>46067.17316457452</v>
+        <v>46067.17316457176</v>
       </c>
       <c r="I1246" s="2" t="n">
-        <v>46072.17316457452</v>
+        <v>46072.17316457176</v>
       </c>
     </row>
     <row r="1247">
@@ -49067,10 +49067,10 @@
         </is>
       </c>
       <c r="H1247" s="2" t="n">
-        <v>46082.17316457738</v>
+        <v>46082.17316457176</v>
       </c>
       <c r="I1247" s="2" t="n">
-        <v>46087.17316457738</v>
+        <v>46087.17316457176</v>
       </c>
     </row>
     <row r="1248">
@@ -49106,10 +49106,10 @@
         </is>
       </c>
       <c r="H1248" s="2" t="n">
-        <v>46066.17316458028</v>
+        <v>46066.17316458334</v>
       </c>
       <c r="I1248" s="2" t="n">
-        <v>46071.17316458028</v>
+        <v>46071.17316458334</v>
       </c>
     </row>
     <row r="1249">
@@ -49145,10 +49145,10 @@
         </is>
       </c>
       <c r="H1249" s="2" t="n">
-        <v>46061.17316458326</v>
+        <v>46061.17316458334</v>
       </c>
       <c r="I1249" s="2" t="n">
-        <v>46066.17316458326</v>
+        <v>46066.17316458334</v>
       </c>
     </row>
     <row r="1250">
@@ -49184,10 +49184,10 @@
         </is>
       </c>
       <c r="H1250" s="2" t="n">
-        <v>46063.17316458606</v>
+        <v>46063.17316458334</v>
       </c>
       <c r="I1250" s="2" t="n">
-        <v>46068.17316458606</v>
+        <v>46068.17316458334</v>
       </c>
     </row>
     <row r="1251">
@@ -49223,10 +49223,1960 @@
         </is>
       </c>
       <c r="H1251" s="2" t="n">
-        <v>46072.17316458908</v>
+        <v>46072.17316458334</v>
       </c>
       <c r="I1251" s="2" t="n">
-        <v>46077.17316458908</v>
+        <v>46077.17316458334</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>c1afc87a-643f-4914-a4a9-ffc8466f3eb3</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1252" t="n">
+        <v>8950.610000000001</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1252" s="2" t="n">
+        <v>46085.24482821159</v>
+      </c>
+      <c r="I1252" s="2" t="n">
+        <v>46090.24482821159</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>c6ea2614-3a4d-4eaa-9873-dbcbbfdb9431</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1253" t="n">
+        <v>6198.25</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1253" s="2" t="n">
+        <v>46065.244828216</v>
+      </c>
+      <c r="I1253" s="2" t="n">
+        <v>46070.244828216</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>e82fe2e6-0b60-4807-bd8a-793a9b2f49fe</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1254" t="n">
+        <v>9057.1</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1254" s="2" t="n">
+        <v>46076.24482821939</v>
+      </c>
+      <c r="I1254" s="2" t="n">
+        <v>46081.24482821939</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>13273bba-d933-4a91-938a-a7f7b28e8890</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1255" t="n">
+        <v>3156.21</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1255" s="2" t="n">
+        <v>46081.24482822263</v>
+      </c>
+      <c r="I1255" s="2" t="n">
+        <v>46086.24482822263</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>234d1e42-9650-4cdf-8589-89c7e325b347</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1256" t="n">
+        <v>6782.41</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1256" s="2" t="n">
+        <v>46076.24482822619</v>
+      </c>
+      <c r="I1256" s="2" t="n">
+        <v>46081.24482822619</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>36ac80a6-9ebf-4acf-962f-0b280dabc221</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1257" t="n">
+        <v>6955.02</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>93.72</v>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1257" s="2" t="n">
+        <v>46079.2448282293</v>
+      </c>
+      <c r="I1257" s="2" t="n">
+        <v>46084.2448282293</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>d335773b-eda9-4318-9c55-8638aa61138c</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1258" t="n">
+        <v>7334.33</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1258" s="2" t="n">
+        <v>46081.2448282324</v>
+      </c>
+      <c r="I1258" s="2" t="n">
+        <v>46086.2448282324</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>09a0a469-10fd-41c9-b065-4effe35e04bb</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1259" t="n">
+        <v>9611.459999999999</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>89.77</v>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1259" s="2" t="n">
+        <v>46084.24482823582</v>
+      </c>
+      <c r="I1259" s="2" t="n">
+        <v>46089.24482823582</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>41781fb9-cd8a-47b8-9969-51c7327ca9b0</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1260" t="n">
+        <v>6794.7</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>86.58</v>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1260" s="2" t="n">
+        <v>46070.24482823911</v>
+      </c>
+      <c r="I1260" s="2" t="n">
+        <v>46075.24482823911</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2e77154a-a2df-42fc-bd9b-331b1db91f45</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1261" t="n">
+        <v>5676.54</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1261" s="2" t="n">
+        <v>46083.24482824239</v>
+      </c>
+      <c r="I1261" s="2" t="n">
+        <v>46088.24482824239</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>8508e6e9-6400-4104-bda2-c827580f5781</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1262" t="n">
+        <v>4114.04</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1262" s="2" t="n">
+        <v>46072.24482824582</v>
+      </c>
+      <c r="I1262" s="2" t="n">
+        <v>46077.24482824582</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>cbde95c0-da37-4281-9c1a-418c872be54f</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1263" t="n">
+        <v>8725.709999999999</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>85.95</v>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1263" s="2" t="n">
+        <v>46073.24482824931</v>
+      </c>
+      <c r="I1263" s="2" t="n">
+        <v>46078.24482824931</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>329535c1-3bfe-4010-8fb3-a463cc2c53c8</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1264" t="n">
+        <v>8388.389999999999</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1264" s="2" t="n">
+        <v>46063.24482825241</v>
+      </c>
+      <c r="I1264" s="2" t="n">
+        <v>46068.24482825241</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>a1c8ebe8-e479-481d-9f8d-bab0fbefd54e</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1265" t="n">
+        <v>9537.809999999999</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>99.04000000000001</v>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1265" s="2" t="n">
+        <v>46080.24482825548</v>
+      </c>
+      <c r="I1265" s="2" t="n">
+        <v>46085.24482825548</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>db49429e-66c0-4409-bca7-8b57d328aaf4</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1266" t="n">
+        <v>3635.72</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1266" s="2" t="n">
+        <v>46075.24482825883</v>
+      </c>
+      <c r="I1266" s="2" t="n">
+        <v>46080.24482825883</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>7f543c70-cc08-4b4c-a892-e33637504543</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1267" t="n">
+        <v>3804.84</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1267" s="2" t="n">
+        <v>46063.24482826194</v>
+      </c>
+      <c r="I1267" s="2" t="n">
+        <v>46068.24482826194</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>3e3e5545-d4d8-4bfa-bbfd-cd13ac788188</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1268" t="n">
+        <v>4524.7</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1268" s="2" t="n">
+        <v>46085.24482826502</v>
+      </c>
+      <c r="I1268" s="2" t="n">
+        <v>46090.24482826502</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>045557d5-41d0-419b-ac29-8031371c7565</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1269" t="n">
+        <v>2870.9</v>
+      </c>
+      <c r="D1269" t="n">
+        <v>96.33</v>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1269" s="2" t="n">
+        <v>46068.24482826816</v>
+      </c>
+      <c r="I1269" s="2" t="n">
+        <v>46073.24482826816</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>da24ee09-852a-43f6-bee2-dc6fa932d14a</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1270" t="n">
+        <v>7400.53</v>
+      </c>
+      <c r="D1270" t="n">
+        <v>92.42</v>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1270" s="2" t="n">
+        <v>46085.24482827157</v>
+      </c>
+      <c r="I1270" s="2" t="n">
+        <v>46090.24482827157</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>10924f7b-09ee-4478-bc3b-610693f8af29</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1271" t="n">
+        <v>7097.88</v>
+      </c>
+      <c r="D1271" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1271" s="2" t="n">
+        <v>46060.24482827468</v>
+      </c>
+      <c r="I1271" s="2" t="n">
+        <v>46065.24482827468</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>817f4449-3843-4f1f-9e20-196f05093068</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1272" t="n">
+        <v>5412.53</v>
+      </c>
+      <c r="D1272" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1272" s="2" t="n">
+        <v>46085.24482827791</v>
+      </c>
+      <c r="I1272" s="2" t="n">
+        <v>46090.24482827791</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>e02efd50-472d-423a-9220-99fcc0ff11e3</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1273" t="n">
+        <v>1225.49</v>
+      </c>
+      <c r="D1273" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1273" s="2" t="n">
+        <v>46079.24482828128</v>
+      </c>
+      <c r="I1273" s="2" t="n">
+        <v>46084.24482828128</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>bf19db49-3742-4d79-b413-c77141a69904</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1274" t="n">
+        <v>5089.39</v>
+      </c>
+      <c r="D1274" t="n">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1274" s="2" t="n">
+        <v>46088.24482828451</v>
+      </c>
+      <c r="I1274" s="2" t="n">
+        <v>46093.24482828451</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>8245ad66-a0ae-432a-b17a-b8ef166c9c1b</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1275" t="n">
+        <v>1075.81</v>
+      </c>
+      <c r="D1275" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1275" s="2" t="n">
+        <v>46088.24482828761</v>
+      </c>
+      <c r="I1275" s="2" t="n">
+        <v>46093.24482828761</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>eeeb64f8-db7b-4d17-a698-800ecee7442e</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1276" t="n">
+        <v>6273</v>
+      </c>
+      <c r="D1276" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1276" s="2" t="n">
+        <v>46065.24482829065</v>
+      </c>
+      <c r="I1276" s="2" t="n">
+        <v>46070.24482829065</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>4a9d71b7-ec13-4219-bfef-da5f684e346d</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>5333.72</v>
+      </c>
+      <c r="D1277" t="n">
+        <v>90.02</v>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1277" s="2" t="n">
+        <v>46076.24482829394</v>
+      </c>
+      <c r="I1277" s="2" t="n">
+        <v>46081.24482829394</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>7363adaa-9a64-4f4b-912e-34a85500526c</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>9603.389999999999</v>
+      </c>
+      <c r="D1278" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1278" s="2" t="n">
+        <v>46078.24482829705</v>
+      </c>
+      <c r="I1278" s="2" t="n">
+        <v>46083.24482829705</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>245c0e15-5690-4550-9892-abbd6587468f</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>8650.219999999999</v>
+      </c>
+      <c r="D1279" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1279" s="2" t="n">
+        <v>46067.24482830023</v>
+      </c>
+      <c r="I1279" s="2" t="n">
+        <v>46072.24482830023</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>ef291911-db07-4742-9d82-5e60fd3904de</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>9059.459999999999</v>
+      </c>
+      <c r="D1280" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1280" s="2" t="n">
+        <v>46087.24482830329</v>
+      </c>
+      <c r="I1280" s="2" t="n">
+        <v>46092.24482830329</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>d8244b87-6537-433a-955c-1acb09861283</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>2293.34</v>
+      </c>
+      <c r="D1281" t="n">
+        <v>96.68000000000001</v>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1281" s="2" t="n">
+        <v>46062.24482830654</v>
+      </c>
+      <c r="I1281" s="2" t="n">
+        <v>46067.24482830654</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>570f9ac6-f58d-4d2f-8e67-ef269695365e</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>1507.28</v>
+      </c>
+      <c r="D1282" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1282" s="2" t="n">
+        <v>46067.24482830997</v>
+      </c>
+      <c r="I1282" s="2" t="n">
+        <v>46072.24482830997</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>e4b8ea04-4e72-4fcf-9a43-a9fba34f0fa8</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>5647.03</v>
+      </c>
+      <c r="D1283" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1283" s="2" t="n">
+        <v>46086.24482831318</v>
+      </c>
+      <c r="I1283" s="2" t="n">
+        <v>46091.24482831318</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>f76d1f94-d08f-4521-a9ea-ced64a27e7ac</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>3989.68</v>
+      </c>
+      <c r="D1284" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1284" s="2" t="n">
+        <v>46068.24482831665</v>
+      </c>
+      <c r="I1284" s="2" t="n">
+        <v>46073.24482831665</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2b26ed8c-4969-4498-8154-2f577b42efb8</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>9083.57</v>
+      </c>
+      <c r="D1285" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1285" s="2" t="n">
+        <v>46078.24482831996</v>
+      </c>
+      <c r="I1285" s="2" t="n">
+        <v>46083.24482831996</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>13fdc35e-5136-46d5-adac-c7cb4199e051</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>8856.98</v>
+      </c>
+      <c r="D1286" t="n">
+        <v>89.62</v>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1286" s="2" t="n">
+        <v>46085.24482832298</v>
+      </c>
+      <c r="I1286" s="2" t="n">
+        <v>46090.24482832298</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>298736fc-77fe-447f-8feb-d01ab1a656bd</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>8809.549999999999</v>
+      </c>
+      <c r="D1287" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1287" s="2" t="n">
+        <v>46068.24482832605</v>
+      </c>
+      <c r="I1287" s="2" t="n">
+        <v>46073.24482832605</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>c3cfbebe-94a1-4102-9d49-ccc86f61d85a</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>7662.21</v>
+      </c>
+      <c r="D1288" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1288" s="2" t="n">
+        <v>46063.24482832933</v>
+      </c>
+      <c r="I1288" s="2" t="n">
+        <v>46068.24482832933</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>7ebc5a2d-c96b-47bb-8e15-ebe133d899da</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>6653.08</v>
+      </c>
+      <c r="D1289" t="n">
+        <v>95.39</v>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1289" s="2" t="n">
+        <v>46083.24482833244</v>
+      </c>
+      <c r="I1289" s="2" t="n">
+        <v>46088.24482833244</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>69a36108-4301-40fb-89af-82d0fd82c575</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>8095.26</v>
+      </c>
+      <c r="D1290" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1290" s="2" t="n">
+        <v>46073.2448283356</v>
+      </c>
+      <c r="I1290" s="2" t="n">
+        <v>46078.2448283356</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>73d3ee13-8936-43d6-bee6-e28a6201e3ab</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>2736.21</v>
+      </c>
+      <c r="D1291" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1291" s="2" t="n">
+        <v>46074.24482833887</v>
+      </c>
+      <c r="I1291" s="2" t="n">
+        <v>46079.24482833887</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>6d8619e4-69a3-4338-9b21-791a88a2b35c</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>3594.84</v>
+      </c>
+      <c r="D1292" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1292" s="2" t="n">
+        <v>46069.24482834214</v>
+      </c>
+      <c r="I1292" s="2" t="n">
+        <v>46074.24482834214</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>7bbfdca7-3ad4-46b4-9297-7f13ac39e5c8</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1293" t="n">
+        <v>3904.96</v>
+      </c>
+      <c r="D1293" t="n">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1293" s="2" t="n">
+        <v>46067.24482834578</v>
+      </c>
+      <c r="I1293" s="2" t="n">
+        <v>46072.24482834578</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>f8b4359f-457f-4743-9450-3f697c0915f0</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1294" t="n">
+        <v>9520.120000000001</v>
+      </c>
+      <c r="D1294" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1294" s="2" t="n">
+        <v>46080.24482834889</v>
+      </c>
+      <c r="I1294" s="2" t="n">
+        <v>46085.24482834889</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>eb01cbf2-e9f5-459c-b243-8768aa44172f</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1295" t="n">
+        <v>4828.24</v>
+      </c>
+      <c r="D1295" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1295" s="2" t="n">
+        <v>46064.24482835206</v>
+      </c>
+      <c r="I1295" s="2" t="n">
+        <v>46069.24482835206</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>45f7d833-ad78-4bd0-aa46-0722228363ae</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>8988.200000000001</v>
+      </c>
+      <c r="D1296" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1296" s="2" t="n">
+        <v>46086.24482835516</v>
+      </c>
+      <c r="I1296" s="2" t="n">
+        <v>46091.24482835516</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>ef79e2a1-f6c9-476b-952f-969c4cb4b643</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>6099.67</v>
+      </c>
+      <c r="D1297" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1297" s="2" t="n">
+        <v>46072.24482835824</v>
+      </c>
+      <c r="I1297" s="2" t="n">
+        <v>46077.24482835824</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2f568f3c-79b6-4786-a007-6b430fe5b2bd</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1298" t="n">
+        <v>2803.22</v>
+      </c>
+      <c r="D1298" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1298" s="2" t="n">
+        <v>46081.24482836139</v>
+      </c>
+      <c r="I1298" s="2" t="n">
+        <v>46086.24482836139</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>4f6598ee-d976-4fb2-a81d-9da12b17b329</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>4953.14</v>
+      </c>
+      <c r="D1299" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1299" s="2" t="n">
+        <v>46060.24482836478</v>
+      </c>
+      <c r="I1299" s="2" t="n">
+        <v>46065.24482836478</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>a5a0bc4a-ab0e-46d3-8297-2e0a6058aee8</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1300" t="n">
+        <v>7591.61</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>95.47</v>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1300" s="2" t="n">
+        <v>46080.24482836779</v>
+      </c>
+      <c r="I1300" s="2" t="n">
+        <v>46085.24482836779</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>6d2125d6-4fa7-4dfb-ad1a-6f00ed30bbfe</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1301" t="n">
+        <v>3527.43</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>87.91</v>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1301" s="2" t="n">
+        <v>46074.24482837086</v>
+      </c>
+      <c r="I1301" s="2" t="n">
+        <v>46079.24482837086</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1301"/>
+  <dimension ref="A1:I1351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49262,10 +49262,10 @@
         </is>
       </c>
       <c r="H1252" s="2" t="n">
-        <v>46085.24482821159</v>
+        <v>46085.24482820602</v>
       </c>
       <c r="I1252" s="2" t="n">
-        <v>46090.24482821159</v>
+        <v>46090.24482820602</v>
       </c>
     </row>
     <row r="1253">
@@ -49301,10 +49301,10 @@
         </is>
       </c>
       <c r="H1253" s="2" t="n">
-        <v>46065.244828216</v>
+        <v>46065.24482821759</v>
       </c>
       <c r="I1253" s="2" t="n">
-        <v>46070.244828216</v>
+        <v>46070.24482821759</v>
       </c>
     </row>
     <row r="1254">
@@ -49340,10 +49340,10 @@
         </is>
       </c>
       <c r="H1254" s="2" t="n">
-        <v>46076.24482821939</v>
+        <v>46076.24482821759</v>
       </c>
       <c r="I1254" s="2" t="n">
-        <v>46081.24482821939</v>
+        <v>46081.24482821759</v>
       </c>
     </row>
     <row r="1255">
@@ -49379,10 +49379,10 @@
         </is>
       </c>
       <c r="H1255" s="2" t="n">
-        <v>46081.24482822263</v>
+        <v>46081.24482821759</v>
       </c>
       <c r="I1255" s="2" t="n">
-        <v>46086.24482822263</v>
+        <v>46086.24482821759</v>
       </c>
     </row>
     <row r="1256">
@@ -49418,10 +49418,10 @@
         </is>
       </c>
       <c r="H1256" s="2" t="n">
-        <v>46076.24482822619</v>
+        <v>46076.24482822917</v>
       </c>
       <c r="I1256" s="2" t="n">
-        <v>46081.24482822619</v>
+        <v>46081.24482822917</v>
       </c>
     </row>
     <row r="1257">
@@ -49457,10 +49457,10 @@
         </is>
       </c>
       <c r="H1257" s="2" t="n">
-        <v>46079.2448282293</v>
+        <v>46079.24482822917</v>
       </c>
       <c r="I1257" s="2" t="n">
-        <v>46084.2448282293</v>
+        <v>46084.24482822917</v>
       </c>
     </row>
     <row r="1258">
@@ -49496,10 +49496,10 @@
         </is>
       </c>
       <c r="H1258" s="2" t="n">
-        <v>46081.2448282324</v>
+        <v>46081.24482822917</v>
       </c>
       <c r="I1258" s="2" t="n">
-        <v>46086.2448282324</v>
+        <v>46086.24482822917</v>
       </c>
     </row>
     <row r="1259">
@@ -49535,10 +49535,10 @@
         </is>
       </c>
       <c r="H1259" s="2" t="n">
-        <v>46084.24482823582</v>
+        <v>46084.24482824074</v>
       </c>
       <c r="I1259" s="2" t="n">
-        <v>46089.24482823582</v>
+        <v>46089.24482824074</v>
       </c>
     </row>
     <row r="1260">
@@ -49574,10 +49574,10 @@
         </is>
       </c>
       <c r="H1260" s="2" t="n">
-        <v>46070.24482823911</v>
+        <v>46070.24482824074</v>
       </c>
       <c r="I1260" s="2" t="n">
-        <v>46075.24482823911</v>
+        <v>46075.24482824074</v>
       </c>
     </row>
     <row r="1261">
@@ -49613,10 +49613,10 @@
         </is>
       </c>
       <c r="H1261" s="2" t="n">
-        <v>46083.24482824239</v>
+        <v>46083.24482824074</v>
       </c>
       <c r="I1261" s="2" t="n">
-        <v>46088.24482824239</v>
+        <v>46088.24482824074</v>
       </c>
     </row>
     <row r="1262">
@@ -49652,10 +49652,10 @@
         </is>
       </c>
       <c r="H1262" s="2" t="n">
-        <v>46072.24482824582</v>
+        <v>46072.24482824074</v>
       </c>
       <c r="I1262" s="2" t="n">
-        <v>46077.24482824582</v>
+        <v>46077.24482824074</v>
       </c>
     </row>
     <row r="1263">
@@ -49691,10 +49691,10 @@
         </is>
       </c>
       <c r="H1263" s="2" t="n">
-        <v>46073.24482824931</v>
+        <v>46073.24482825232</v>
       </c>
       <c r="I1263" s="2" t="n">
-        <v>46078.24482824931</v>
+        <v>46078.24482825232</v>
       </c>
     </row>
     <row r="1264">
@@ -49730,10 +49730,10 @@
         </is>
       </c>
       <c r="H1264" s="2" t="n">
-        <v>46063.24482825241</v>
+        <v>46063.24482825232</v>
       </c>
       <c r="I1264" s="2" t="n">
-        <v>46068.24482825241</v>
+        <v>46068.24482825232</v>
       </c>
     </row>
     <row r="1265">
@@ -49769,10 +49769,10 @@
         </is>
       </c>
       <c r="H1265" s="2" t="n">
-        <v>46080.24482825548</v>
+        <v>46080.24482825232</v>
       </c>
       <c r="I1265" s="2" t="n">
-        <v>46085.24482825548</v>
+        <v>46085.24482825232</v>
       </c>
     </row>
     <row r="1266">
@@ -49808,10 +49808,10 @@
         </is>
       </c>
       <c r="H1266" s="2" t="n">
-        <v>46075.24482825883</v>
+        <v>46075.24482826389</v>
       </c>
       <c r="I1266" s="2" t="n">
-        <v>46080.24482825883</v>
+        <v>46080.24482826389</v>
       </c>
     </row>
     <row r="1267">
@@ -49847,10 +49847,10 @@
         </is>
       </c>
       <c r="H1267" s="2" t="n">
-        <v>46063.24482826194</v>
+        <v>46063.24482826389</v>
       </c>
       <c r="I1267" s="2" t="n">
-        <v>46068.24482826194</v>
+        <v>46068.24482826389</v>
       </c>
     </row>
     <row r="1268">
@@ -49886,10 +49886,10 @@
         </is>
       </c>
       <c r="H1268" s="2" t="n">
-        <v>46085.24482826502</v>
+        <v>46085.24482826389</v>
       </c>
       <c r="I1268" s="2" t="n">
-        <v>46090.24482826502</v>
+        <v>46090.24482826389</v>
       </c>
     </row>
     <row r="1269">
@@ -49925,10 +49925,10 @@
         </is>
       </c>
       <c r="H1269" s="2" t="n">
-        <v>46068.24482826816</v>
+        <v>46068.24482826389</v>
       </c>
       <c r="I1269" s="2" t="n">
-        <v>46073.24482826816</v>
+        <v>46073.24482826389</v>
       </c>
     </row>
     <row r="1270">
@@ -49964,10 +49964,10 @@
         </is>
       </c>
       <c r="H1270" s="2" t="n">
-        <v>46085.24482827157</v>
+        <v>46085.24482827546</v>
       </c>
       <c r="I1270" s="2" t="n">
-        <v>46090.24482827157</v>
+        <v>46090.24482827546</v>
       </c>
     </row>
     <row r="1271">
@@ -50003,10 +50003,10 @@
         </is>
       </c>
       <c r="H1271" s="2" t="n">
-        <v>46060.24482827468</v>
+        <v>46060.24482827546</v>
       </c>
       <c r="I1271" s="2" t="n">
-        <v>46065.24482827468</v>
+        <v>46065.24482827546</v>
       </c>
     </row>
     <row r="1272">
@@ -50042,10 +50042,10 @@
         </is>
       </c>
       <c r="H1272" s="2" t="n">
-        <v>46085.24482827791</v>
+        <v>46085.24482827546</v>
       </c>
       <c r="I1272" s="2" t="n">
-        <v>46090.24482827791</v>
+        <v>46090.24482827546</v>
       </c>
     </row>
     <row r="1273">
@@ -50081,10 +50081,10 @@
         </is>
       </c>
       <c r="H1273" s="2" t="n">
-        <v>46079.24482828128</v>
+        <v>46079.24482828704</v>
       </c>
       <c r="I1273" s="2" t="n">
-        <v>46084.24482828128</v>
+        <v>46084.24482828704</v>
       </c>
     </row>
     <row r="1274">
@@ -50120,10 +50120,10 @@
         </is>
       </c>
       <c r="H1274" s="2" t="n">
-        <v>46088.24482828451</v>
+        <v>46088.24482828704</v>
       </c>
       <c r="I1274" s="2" t="n">
-        <v>46093.24482828451</v>
+        <v>46093.24482828704</v>
       </c>
     </row>
     <row r="1275">
@@ -50159,10 +50159,10 @@
         </is>
       </c>
       <c r="H1275" s="2" t="n">
-        <v>46088.24482828761</v>
+        <v>46088.24482828704</v>
       </c>
       <c r="I1275" s="2" t="n">
-        <v>46093.24482828761</v>
+        <v>46093.24482828704</v>
       </c>
     </row>
     <row r="1276">
@@ -50198,10 +50198,10 @@
         </is>
       </c>
       <c r="H1276" s="2" t="n">
-        <v>46065.24482829065</v>
+        <v>46065.24482828704</v>
       </c>
       <c r="I1276" s="2" t="n">
-        <v>46070.24482829065</v>
+        <v>46070.24482828704</v>
       </c>
     </row>
     <row r="1277">
@@ -50237,10 +50237,10 @@
         </is>
       </c>
       <c r="H1277" s="2" t="n">
-        <v>46076.24482829394</v>
+        <v>46076.24482829861</v>
       </c>
       <c r="I1277" s="2" t="n">
-        <v>46081.24482829394</v>
+        <v>46081.24482829861</v>
       </c>
     </row>
     <row r="1278">
@@ -50276,10 +50276,10 @@
         </is>
       </c>
       <c r="H1278" s="2" t="n">
-        <v>46078.24482829705</v>
+        <v>46078.24482829861</v>
       </c>
       <c r="I1278" s="2" t="n">
-        <v>46083.24482829705</v>
+        <v>46083.24482829861</v>
       </c>
     </row>
     <row r="1279">
@@ -50315,10 +50315,10 @@
         </is>
       </c>
       <c r="H1279" s="2" t="n">
-        <v>46067.24482830023</v>
+        <v>46067.24482829861</v>
       </c>
       <c r="I1279" s="2" t="n">
-        <v>46072.24482830023</v>
+        <v>46072.24482829861</v>
       </c>
     </row>
     <row r="1280">
@@ -50354,10 +50354,10 @@
         </is>
       </c>
       <c r="H1280" s="2" t="n">
-        <v>46087.24482830329</v>
+        <v>46087.24482829861</v>
       </c>
       <c r="I1280" s="2" t="n">
-        <v>46092.24482830329</v>
+        <v>46092.24482829861</v>
       </c>
     </row>
     <row r="1281">
@@ -50393,10 +50393,10 @@
         </is>
       </c>
       <c r="H1281" s="2" t="n">
-        <v>46062.24482830654</v>
+        <v>46062.24482831018</v>
       </c>
       <c r="I1281" s="2" t="n">
-        <v>46067.24482830654</v>
+        <v>46067.24482831018</v>
       </c>
     </row>
     <row r="1282">
@@ -50432,10 +50432,10 @@
         </is>
       </c>
       <c r="H1282" s="2" t="n">
-        <v>46067.24482830997</v>
+        <v>46067.24482831018</v>
       </c>
       <c r="I1282" s="2" t="n">
-        <v>46072.24482830997</v>
+        <v>46072.24482831018</v>
       </c>
     </row>
     <row r="1283">
@@ -50471,10 +50471,10 @@
         </is>
       </c>
       <c r="H1283" s="2" t="n">
-        <v>46086.24482831318</v>
+        <v>46086.24482831018</v>
       </c>
       <c r="I1283" s="2" t="n">
-        <v>46091.24482831318</v>
+        <v>46091.24482831018</v>
       </c>
     </row>
     <row r="1284">
@@ -50510,10 +50510,10 @@
         </is>
       </c>
       <c r="H1284" s="2" t="n">
-        <v>46068.24482831665</v>
+        <v>46068.24482832176</v>
       </c>
       <c r="I1284" s="2" t="n">
-        <v>46073.24482831665</v>
+        <v>46073.24482832176</v>
       </c>
     </row>
     <row r="1285">
@@ -50549,10 +50549,10 @@
         </is>
       </c>
       <c r="H1285" s="2" t="n">
-        <v>46078.24482831996</v>
+        <v>46078.24482832176</v>
       </c>
       <c r="I1285" s="2" t="n">
-        <v>46083.24482831996</v>
+        <v>46083.24482832176</v>
       </c>
     </row>
     <row r="1286">
@@ -50588,10 +50588,10 @@
         </is>
       </c>
       <c r="H1286" s="2" t="n">
-        <v>46085.24482832298</v>
+        <v>46085.24482832176</v>
       </c>
       <c r="I1286" s="2" t="n">
-        <v>46090.24482832298</v>
+        <v>46090.24482832176</v>
       </c>
     </row>
     <row r="1287">
@@ -50627,10 +50627,10 @@
         </is>
       </c>
       <c r="H1287" s="2" t="n">
-        <v>46068.24482832605</v>
+        <v>46068.24482832176</v>
       </c>
       <c r="I1287" s="2" t="n">
-        <v>46073.24482832605</v>
+        <v>46073.24482832176</v>
       </c>
     </row>
     <row r="1288">
@@ -50666,10 +50666,10 @@
         </is>
       </c>
       <c r="H1288" s="2" t="n">
-        <v>46063.24482832933</v>
+        <v>46063.24482833334</v>
       </c>
       <c r="I1288" s="2" t="n">
-        <v>46068.24482832933</v>
+        <v>46068.24482833334</v>
       </c>
     </row>
     <row r="1289">
@@ -50705,10 +50705,10 @@
         </is>
       </c>
       <c r="H1289" s="2" t="n">
-        <v>46083.24482833244</v>
+        <v>46083.24482833334</v>
       </c>
       <c r="I1289" s="2" t="n">
-        <v>46088.24482833244</v>
+        <v>46088.24482833334</v>
       </c>
     </row>
     <row r="1290">
@@ -50744,10 +50744,10 @@
         </is>
       </c>
       <c r="H1290" s="2" t="n">
-        <v>46073.2448283356</v>
+        <v>46073.24482833334</v>
       </c>
       <c r="I1290" s="2" t="n">
-        <v>46078.2448283356</v>
+        <v>46078.24482833334</v>
       </c>
     </row>
     <row r="1291">
@@ -50783,10 +50783,10 @@
         </is>
       </c>
       <c r="H1291" s="2" t="n">
-        <v>46074.24482833887</v>
+        <v>46074.24482833334</v>
       </c>
       <c r="I1291" s="2" t="n">
-        <v>46079.24482833887</v>
+        <v>46079.24482833334</v>
       </c>
     </row>
     <row r="1292">
@@ -50822,10 +50822,10 @@
         </is>
       </c>
       <c r="H1292" s="2" t="n">
-        <v>46069.24482834214</v>
+        <v>46069.2448283449</v>
       </c>
       <c r="I1292" s="2" t="n">
-        <v>46074.24482834214</v>
+        <v>46074.2448283449</v>
       </c>
     </row>
     <row r="1293">
@@ -50861,10 +50861,10 @@
         </is>
       </c>
       <c r="H1293" s="2" t="n">
-        <v>46067.24482834578</v>
+        <v>46067.2448283449</v>
       </c>
       <c r="I1293" s="2" t="n">
-        <v>46072.24482834578</v>
+        <v>46072.2448283449</v>
       </c>
     </row>
     <row r="1294">
@@ -50900,10 +50900,10 @@
         </is>
       </c>
       <c r="H1294" s="2" t="n">
-        <v>46080.24482834889</v>
+        <v>46080.2448283449</v>
       </c>
       <c r="I1294" s="2" t="n">
-        <v>46085.24482834889</v>
+        <v>46085.2448283449</v>
       </c>
     </row>
     <row r="1295">
@@ -50939,10 +50939,10 @@
         </is>
       </c>
       <c r="H1295" s="2" t="n">
-        <v>46064.24482835206</v>
+        <v>46064.24482835648</v>
       </c>
       <c r="I1295" s="2" t="n">
-        <v>46069.24482835206</v>
+        <v>46069.24482835648</v>
       </c>
     </row>
     <row r="1296">
@@ -50978,10 +50978,10 @@
         </is>
       </c>
       <c r="H1296" s="2" t="n">
-        <v>46086.24482835516</v>
+        <v>46086.24482835648</v>
       </c>
       <c r="I1296" s="2" t="n">
-        <v>46091.24482835516</v>
+        <v>46091.24482835648</v>
       </c>
     </row>
     <row r="1297">
@@ -51017,10 +51017,10 @@
         </is>
       </c>
       <c r="H1297" s="2" t="n">
-        <v>46072.24482835824</v>
+        <v>46072.24482835648</v>
       </c>
       <c r="I1297" s="2" t="n">
-        <v>46077.24482835824</v>
+        <v>46077.24482835648</v>
       </c>
     </row>
     <row r="1298">
@@ -51056,10 +51056,10 @@
         </is>
       </c>
       <c r="H1298" s="2" t="n">
-        <v>46081.24482836139</v>
+        <v>46081.24482835648</v>
       </c>
       <c r="I1298" s="2" t="n">
-        <v>46086.24482836139</v>
+        <v>46086.24482835648</v>
       </c>
     </row>
     <row r="1299">
@@ -51095,10 +51095,10 @@
         </is>
       </c>
       <c r="H1299" s="2" t="n">
-        <v>46060.24482836478</v>
+        <v>46060.24482836806</v>
       </c>
       <c r="I1299" s="2" t="n">
-        <v>46065.24482836478</v>
+        <v>46065.24482836806</v>
       </c>
     </row>
     <row r="1300">
@@ -51134,10 +51134,10 @@
         </is>
       </c>
       <c r="H1300" s="2" t="n">
-        <v>46080.24482836779</v>
+        <v>46080.24482836806</v>
       </c>
       <c r="I1300" s="2" t="n">
-        <v>46085.24482836779</v>
+        <v>46085.24482836806</v>
       </c>
     </row>
     <row r="1301">
@@ -51173,10 +51173,1960 @@
         </is>
       </c>
       <c r="H1301" s="2" t="n">
-        <v>46074.24482837086</v>
+        <v>46074.24482836806</v>
       </c>
       <c r="I1301" s="2" t="n">
-        <v>46079.24482837086</v>
+        <v>46079.24482836806</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>803c794c-abad-44c9-af7c-ca5cc9e6da48</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>1892.03</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>86.34999999999999</v>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1302" s="2" t="n">
+        <v>46060.28641161769</v>
+      </c>
+      <c r="I1302" s="2" t="n">
+        <v>46065.28641161769</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>9b2fe321-2c99-4766-bf76-030845ae0a1d</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>3661.89</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1303" s="2" t="n">
+        <v>46062.28641162244</v>
+      </c>
+      <c r="I1303" s="2" t="n">
+        <v>46067.28641162244</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>19acb1fc-9efc-4a37-a12c-049ffbbea276</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>3874.12</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1304" s="2" t="n">
+        <v>46079.28641162608</v>
+      </c>
+      <c r="I1304" s="2" t="n">
+        <v>46084.28641162608</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>1fc39a69-26aa-4602-a7d0-3a2763eaa2b9</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1305" t="n">
+        <v>3962.8</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1305" s="2" t="n">
+        <v>46070.2864116292</v>
+      </c>
+      <c r="I1305" s="2" t="n">
+        <v>46075.2864116292</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>9d84f1d3-9ade-4269-b2ae-7c452cf014fd</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>8071.3</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1306" s="2" t="n">
+        <v>46089.28641163242</v>
+      </c>
+      <c r="I1306" s="2" t="n">
+        <v>46094.28641163242</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>7c4e7a82-1f01-46ad-96d0-56f9ef7ae577</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>4537.44</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1307" s="2" t="n">
+        <v>46062.28641163577</v>
+      </c>
+      <c r="I1307" s="2" t="n">
+        <v>46067.28641163577</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>3f4421ff-1261-427e-944e-2671b034212e</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>1843.24</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>92.67</v>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1308" s="2" t="n">
+        <v>46071.28641163898</v>
+      </c>
+      <c r="I1308" s="2" t="n">
+        <v>46076.28641163898</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>4af20b6a-3945-44ce-903a-613eca25acdb</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>9482.540000000001</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1309" s="2" t="n">
+        <v>46070.28641164256</v>
+      </c>
+      <c r="I1309" s="2" t="n">
+        <v>46075.28641164256</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>b0dac955-6769-4d1f-b623-491b7e33dcb0</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>8127.09</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1310" s="2" t="n">
+        <v>46060.28641164579</v>
+      </c>
+      <c r="I1310" s="2" t="n">
+        <v>46065.28641164579</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>014902fb-6dee-40fe-87c8-882e3172cf74</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>9202.110000000001</v>
+      </c>
+      <c r="D1311" t="n">
+        <v>87.92</v>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1311" s="2" t="n">
+        <v>46081.28641164896</v>
+      </c>
+      <c r="I1311" s="2" t="n">
+        <v>46086.28641164896</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>dc4e4b8b-f4f6-4d98-bd2e-3b5c404b0764</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>3441.76</v>
+      </c>
+      <c r="D1312" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1312" s="2" t="n">
+        <v>46074.28641165234</v>
+      </c>
+      <c r="I1312" s="2" t="n">
+        <v>46079.28641165234</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>20b2a01d-fbea-4e99-b06f-9f0225766fc9</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>7352.01</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1313" s="2" t="n">
+        <v>46074.28641165568</v>
+      </c>
+      <c r="I1313" s="2" t="n">
+        <v>46079.28641165568</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>14af815e-0b83-4a49-8a3b-497794c1e6ed</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>6292.58</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>96.81999999999999</v>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1314" s="2" t="n">
+        <v>46071.28641165879</v>
+      </c>
+      <c r="I1314" s="2" t="n">
+        <v>46076.28641165879</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>0458c646-6470-4be2-b304-40de35f43fdb</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>8761.540000000001</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1315" s="2" t="n">
+        <v>46077.28641166181</v>
+      </c>
+      <c r="I1315" s="2" t="n">
+        <v>46082.28641166181</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>86418913-14b6-44cb-a8af-87109b9e0d46</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>5622.94</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1316" s="2" t="n">
+        <v>46089.28641166523</v>
+      </c>
+      <c r="I1316" s="2" t="n">
+        <v>46094.28641166523</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>9311be89-f97f-4b07-86e3-ca6f88abf3c1</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>3446.76</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1317" s="2" t="n">
+        <v>46066.28641166844</v>
+      </c>
+      <c r="I1317" s="2" t="n">
+        <v>46071.28641166844</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>ab708a6c-697e-4ca9-b36f-95faf07403a8</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>6926.55</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1318" s="2" t="n">
+        <v>46089.28641167151</v>
+      </c>
+      <c r="I1318" s="2" t="n">
+        <v>46094.28641167151</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>91302732-2aa5-486d-bb0e-69526d06c573</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>5495.6</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1319" s="2" t="n">
+        <v>46085.28641167469</v>
+      </c>
+      <c r="I1319" s="2" t="n">
+        <v>46090.28641167469</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>32761a91-cda4-4b00-87f6-2607f212de2e</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>1020.53</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1320" s="2" t="n">
+        <v>46071.28641167788</v>
+      </c>
+      <c r="I1320" s="2" t="n">
+        <v>46076.28641167788</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>5d569967-0717-4da5-a164-dd10978bcd76</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>2997.87</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>86.12</v>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1321" s="2" t="n">
+        <v>46074.28641168105</v>
+      </c>
+      <c r="I1321" s="2" t="n">
+        <v>46079.28641168105</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>ea9c5664-f75b-4a88-bd7e-2f74275746ba</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>8725.360000000001</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1322" s="2" t="n">
+        <v>46063.28641168415</v>
+      </c>
+      <c r="I1322" s="2" t="n">
+        <v>46068.28641168415</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>b2bb4ac7-06a7-42db-b132-a871e334a877</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>9295.200000000001</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1323" s="2" t="n">
+        <v>46067.28641168836</v>
+      </c>
+      <c r="I1323" s="2" t="n">
+        <v>46072.28641168836</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>ae2124e8-b55d-4db4-bdf5-8a53283b062b</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>6128.82</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1324" s="2" t="n">
+        <v>46085.28641169161</v>
+      </c>
+      <c r="I1324" s="2" t="n">
+        <v>46090.28641169161</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>c6e0c488-1d90-4d67-aa47-6af90217e633</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>3095.3</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1325" s="2" t="n">
+        <v>46080.28641169467</v>
+      </c>
+      <c r="I1325" s="2" t="n">
+        <v>46085.28641169467</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>6c69b523-65b3-46c3-a792-c6ac665b3114</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>6165.13</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1326" s="2" t="n">
+        <v>46073.28641169773</v>
+      </c>
+      <c r="I1326" s="2" t="n">
+        <v>46078.28641169773</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>49f28af4-1cb9-47b6-9c10-b4ac3cc1fece</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>1039.3</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1327" s="2" t="n">
+        <v>46087.28641170112</v>
+      </c>
+      <c r="I1327" s="2" t="n">
+        <v>46092.28641170112</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>00dfaaad-0ab4-4d0a-93f1-61ce2b4b0f84</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>9411.040000000001</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>89.31</v>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1328" s="2" t="n">
+        <v>46069.28641170433</v>
+      </c>
+      <c r="I1328" s="2" t="n">
+        <v>46074.28641170433</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>3e30eee4-0eaa-4b65-a121-1ba9d2501417</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>9405.549999999999</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1329" s="2" t="n">
+        <v>46063.28641170741</v>
+      </c>
+      <c r="I1329" s="2" t="n">
+        <v>46068.28641170741</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>0682c165-3967-4c80-854d-3d7e4e158fbe</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>1386.3</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1330" s="2" t="n">
+        <v>46061.28641171058</v>
+      </c>
+      <c r="I1330" s="2" t="n">
+        <v>46066.28641171058</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>15f2ec6e-3f14-41f8-9570-7155c28f11e1</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>97.23999999999999</v>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1331" s="2" t="n">
+        <v>46080.28641171393</v>
+      </c>
+      <c r="I1331" s="2" t="n">
+        <v>46085.28641171393</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>472cded4-4ab1-46fe-a32d-dff5d0472b1b</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>1750.79</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1332" s="2" t="n">
+        <v>46083.28641171727</v>
+      </c>
+      <c r="I1332" s="2" t="n">
+        <v>46088.28641171727</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>1bd9a9d6-6554-4986-ba99-c3c3f1e77fbf</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>4755.59</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1333" s="2" t="n">
+        <v>46074.2864117203</v>
+      </c>
+      <c r="I1333" s="2" t="n">
+        <v>46079.2864117203</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>eecb0e7d-3672-4af6-9b8a-836dfc7b4222</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>7764.66</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1334" s="2" t="n">
+        <v>46065.28641172357</v>
+      </c>
+      <c r="I1334" s="2" t="n">
+        <v>46070.28641172357</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>159082a5-2306-483a-b4e9-74f021151a87</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>9322.16</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>92.84</v>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1335" s="2" t="n">
+        <v>46085.28641172659</v>
+      </c>
+      <c r="I1335" s="2" t="n">
+        <v>46090.28641172659</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>cc9693d7-3843-4f40-b387-625ace8642ec</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>8538.93</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>88.20999999999999</v>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1336" s="2" t="n">
+        <v>46074.28641172958</v>
+      </c>
+      <c r="I1336" s="2" t="n">
+        <v>46079.28641172958</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>f75fa40f-8655-45c6-b5b8-c5357845776b</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>9455.92</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1337" s="2" t="n">
+        <v>46069.2864117327</v>
+      </c>
+      <c r="I1337" s="2" t="n">
+        <v>46074.2864117327</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>4ee705b5-1b9e-4056-8963-991087f303a8</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>3194.35</v>
+      </c>
+      <c r="D1338" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1338" s="2" t="n">
+        <v>46064.28641173617</v>
+      </c>
+      <c r="I1338" s="2" t="n">
+        <v>46069.28641173617</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>46b96833-2ac3-4f5b-9f92-afbf42061e0d</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>5266.23</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1339" s="2" t="n">
+        <v>46084.28641173925</v>
+      </c>
+      <c r="I1339" s="2" t="n">
+        <v>46089.28641173925</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>ebe49ddf-36a6-40d6-9d18-5fe71107e8f2</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>5520.88</v>
+      </c>
+      <c r="D1340" t="n">
+        <v>96.04000000000001</v>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1340" s="2" t="n">
+        <v>46070.28641174226</v>
+      </c>
+      <c r="I1340" s="2" t="n">
+        <v>46075.28641174226</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>e2daa030-a550-4b12-aadb-ddc1a4c36032</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>9315.950000000001</v>
+      </c>
+      <c r="D1341" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1341" s="2" t="n">
+        <v>46068.28641174528</v>
+      </c>
+      <c r="I1341" s="2" t="n">
+        <v>46073.28641174528</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>8239e330-26a6-4cfe-b592-0f782f98a731</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>9843.389999999999</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>91.43000000000001</v>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1342" s="2" t="n">
+        <v>46066.28641174863</v>
+      </c>
+      <c r="I1342" s="2" t="n">
+        <v>46071.28641174863</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>bcd812ef-db00-4a21-b1af-76d28a7cf8cf</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>7468.64</v>
+      </c>
+      <c r="D1343" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1343" s="2" t="n">
+        <v>46084.28641175186</v>
+      </c>
+      <c r="I1343" s="2" t="n">
+        <v>46089.28641175186</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>e9f4f7bb-f29c-479c-8729-dd71ab1729b7</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>5263.53</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1344" s="2" t="n">
+        <v>46084.28641175497</v>
+      </c>
+      <c r="I1344" s="2" t="n">
+        <v>46089.28641175497</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>1987d7dd-e960-4872-babc-c54f3e81ba88</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>7551.71</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>98.72</v>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1345" s="2" t="n">
+        <v>46067.28641175831</v>
+      </c>
+      <c r="I1345" s="2" t="n">
+        <v>46072.28641175831</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2a840d95-cabe-49f5-ab28-4c51ea88fdcc</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>5012.39</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1346" s="2" t="n">
+        <v>46074.2864117615</v>
+      </c>
+      <c r="I1346" s="2" t="n">
+        <v>46079.2864117615</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>b8b8a080-ebee-4b4e-987c-611dfb3353a1</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>6866.66</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1347" s="2" t="n">
+        <v>46087.28641176457</v>
+      </c>
+      <c r="I1347" s="2" t="n">
+        <v>46092.28641176457</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>c36cf6ac-c8e5-4282-b820-2757f763f03c</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>5690.99</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1348" s="2" t="n">
+        <v>46089.28641176772</v>
+      </c>
+      <c r="I1348" s="2" t="n">
+        <v>46094.28641176772</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>ab43e0bd-22ed-4136-a721-ea7d489fccbe</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>8298.77</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1349" s="2" t="n">
+        <v>46081.28641177102</v>
+      </c>
+      <c r="I1349" s="2" t="n">
+        <v>46086.28641177102</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>c59a1917-59f1-4042-b2ea-18e6965a90fa</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>6238.03</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1350" s="2" t="n">
+        <v>46061.28641177412</v>
+      </c>
+      <c r="I1350" s="2" t="n">
+        <v>46066.28641177412</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>0f5dca8e-067c-425d-b7bc-42ae7a8e4374</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>2697.75</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1351" s="2" t="n">
+        <v>46082.28641177717</v>
+      </c>
+      <c r="I1351" s="2" t="n">
+        <v>46087.28641177717</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1351"/>
+  <dimension ref="A1:I1401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51212,10 +51212,10 @@
         </is>
       </c>
       <c r="H1302" s="2" t="n">
-        <v>46060.28641161769</v>
+        <v>46060.28641162037</v>
       </c>
       <c r="I1302" s="2" t="n">
-        <v>46065.28641161769</v>
+        <v>46065.28641162037</v>
       </c>
     </row>
     <row r="1303">
@@ -51251,10 +51251,10 @@
         </is>
       </c>
       <c r="H1303" s="2" t="n">
-        <v>46062.28641162244</v>
+        <v>46062.28641162037</v>
       </c>
       <c r="I1303" s="2" t="n">
-        <v>46067.28641162244</v>
+        <v>46067.28641162037</v>
       </c>
     </row>
     <row r="1304">
@@ -51290,10 +51290,10 @@
         </is>
       </c>
       <c r="H1304" s="2" t="n">
-        <v>46079.28641162608</v>
+        <v>46079.28641162037</v>
       </c>
       <c r="I1304" s="2" t="n">
-        <v>46084.28641162608</v>
+        <v>46084.28641162037</v>
       </c>
     </row>
     <row r="1305">
@@ -51329,10 +51329,10 @@
         </is>
       </c>
       <c r="H1305" s="2" t="n">
-        <v>46070.2864116292</v>
+        <v>46070.28641163195</v>
       </c>
       <c r="I1305" s="2" t="n">
-        <v>46075.2864116292</v>
+        <v>46075.28641163195</v>
       </c>
     </row>
     <row r="1306">
@@ -51368,10 +51368,10 @@
         </is>
       </c>
       <c r="H1306" s="2" t="n">
-        <v>46089.28641163242</v>
+        <v>46089.28641163195</v>
       </c>
       <c r="I1306" s="2" t="n">
-        <v>46094.28641163242</v>
+        <v>46094.28641163195</v>
       </c>
     </row>
     <row r="1307">
@@ -51407,10 +51407,10 @@
         </is>
       </c>
       <c r="H1307" s="2" t="n">
-        <v>46062.28641163577</v>
+        <v>46062.28641163195</v>
       </c>
       <c r="I1307" s="2" t="n">
-        <v>46067.28641163577</v>
+        <v>46067.28641163195</v>
       </c>
     </row>
     <row r="1308">
@@ -51446,10 +51446,10 @@
         </is>
       </c>
       <c r="H1308" s="2" t="n">
-        <v>46071.28641163898</v>
+        <v>46071.28641164352</v>
       </c>
       <c r="I1308" s="2" t="n">
-        <v>46076.28641163898</v>
+        <v>46076.28641164352</v>
       </c>
     </row>
     <row r="1309">
@@ -51485,10 +51485,10 @@
         </is>
       </c>
       <c r="H1309" s="2" t="n">
-        <v>46070.28641164256</v>
+        <v>46070.28641164352</v>
       </c>
       <c r="I1309" s="2" t="n">
-        <v>46075.28641164256</v>
+        <v>46075.28641164352</v>
       </c>
     </row>
     <row r="1310">
@@ -51524,10 +51524,10 @@
         </is>
       </c>
       <c r="H1310" s="2" t="n">
-        <v>46060.28641164579</v>
+        <v>46060.28641164352</v>
       </c>
       <c r="I1310" s="2" t="n">
-        <v>46065.28641164579</v>
+        <v>46065.28641164352</v>
       </c>
     </row>
     <row r="1311">
@@ -51563,10 +51563,10 @@
         </is>
       </c>
       <c r="H1311" s="2" t="n">
-        <v>46081.28641164896</v>
+        <v>46081.28641164352</v>
       </c>
       <c r="I1311" s="2" t="n">
-        <v>46086.28641164896</v>
+        <v>46086.28641164352</v>
       </c>
     </row>
     <row r="1312">
@@ -51602,10 +51602,10 @@
         </is>
       </c>
       <c r="H1312" s="2" t="n">
-        <v>46074.28641165234</v>
+        <v>46074.28641165509</v>
       </c>
       <c r="I1312" s="2" t="n">
-        <v>46079.28641165234</v>
+        <v>46079.28641165509</v>
       </c>
     </row>
     <row r="1313">
@@ -51641,10 +51641,10 @@
         </is>
       </c>
       <c r="H1313" s="2" t="n">
-        <v>46074.28641165568</v>
+        <v>46074.28641165509</v>
       </c>
       <c r="I1313" s="2" t="n">
-        <v>46079.28641165568</v>
+        <v>46079.28641165509</v>
       </c>
     </row>
     <row r="1314">
@@ -51680,10 +51680,10 @@
         </is>
       </c>
       <c r="H1314" s="2" t="n">
-        <v>46071.28641165879</v>
+        <v>46071.28641165509</v>
       </c>
       <c r="I1314" s="2" t="n">
-        <v>46076.28641165879</v>
+        <v>46076.28641165509</v>
       </c>
     </row>
     <row r="1315">
@@ -51719,10 +51719,10 @@
         </is>
       </c>
       <c r="H1315" s="2" t="n">
-        <v>46077.28641166181</v>
+        <v>46077.28641166667</v>
       </c>
       <c r="I1315" s="2" t="n">
-        <v>46082.28641166181</v>
+        <v>46082.28641166667</v>
       </c>
     </row>
     <row r="1316">
@@ -51758,10 +51758,10 @@
         </is>
       </c>
       <c r="H1316" s="2" t="n">
-        <v>46089.28641166523</v>
+        <v>46089.28641166667</v>
       </c>
       <c r="I1316" s="2" t="n">
-        <v>46094.28641166523</v>
+        <v>46094.28641166667</v>
       </c>
     </row>
     <row r="1317">
@@ -51797,10 +51797,10 @@
         </is>
       </c>
       <c r="H1317" s="2" t="n">
-        <v>46066.28641166844</v>
+        <v>46066.28641166667</v>
       </c>
       <c r="I1317" s="2" t="n">
-        <v>46071.28641166844</v>
+        <v>46071.28641166667</v>
       </c>
     </row>
     <row r="1318">
@@ -51836,10 +51836,10 @@
         </is>
       </c>
       <c r="H1318" s="2" t="n">
-        <v>46089.28641167151</v>
+        <v>46089.28641166667</v>
       </c>
       <c r="I1318" s="2" t="n">
-        <v>46094.28641167151</v>
+        <v>46094.28641166667</v>
       </c>
     </row>
     <row r="1319">
@@ -51875,10 +51875,10 @@
         </is>
       </c>
       <c r="H1319" s="2" t="n">
-        <v>46085.28641167469</v>
+        <v>46085.28641167824</v>
       </c>
       <c r="I1319" s="2" t="n">
-        <v>46090.28641167469</v>
+        <v>46090.28641167824</v>
       </c>
     </row>
     <row r="1320">
@@ -51914,10 +51914,10 @@
         </is>
       </c>
       <c r="H1320" s="2" t="n">
-        <v>46071.28641167788</v>
+        <v>46071.28641167824</v>
       </c>
       <c r="I1320" s="2" t="n">
-        <v>46076.28641167788</v>
+        <v>46076.28641167824</v>
       </c>
     </row>
     <row r="1321">
@@ -51953,10 +51953,10 @@
         </is>
       </c>
       <c r="H1321" s="2" t="n">
-        <v>46074.28641168105</v>
+        <v>46074.28641167824</v>
       </c>
       <c r="I1321" s="2" t="n">
-        <v>46079.28641168105</v>
+        <v>46079.28641167824</v>
       </c>
     </row>
     <row r="1322">
@@ -51992,10 +51992,10 @@
         </is>
       </c>
       <c r="H1322" s="2" t="n">
-        <v>46063.28641168415</v>
+        <v>46063.28641168981</v>
       </c>
       <c r="I1322" s="2" t="n">
-        <v>46068.28641168415</v>
+        <v>46068.28641168981</v>
       </c>
     </row>
     <row r="1323">
@@ -52031,10 +52031,10 @@
         </is>
       </c>
       <c r="H1323" s="2" t="n">
-        <v>46067.28641168836</v>
+        <v>46067.28641168981</v>
       </c>
       <c r="I1323" s="2" t="n">
-        <v>46072.28641168836</v>
+        <v>46072.28641168981</v>
       </c>
     </row>
     <row r="1324">
@@ -52070,10 +52070,10 @@
         </is>
       </c>
       <c r="H1324" s="2" t="n">
-        <v>46085.28641169161</v>
+        <v>46085.28641168981</v>
       </c>
       <c r="I1324" s="2" t="n">
-        <v>46090.28641169161</v>
+        <v>46090.28641168981</v>
       </c>
     </row>
     <row r="1325">
@@ -52109,10 +52109,10 @@
         </is>
       </c>
       <c r="H1325" s="2" t="n">
-        <v>46080.28641169467</v>
+        <v>46080.28641168981</v>
       </c>
       <c r="I1325" s="2" t="n">
-        <v>46085.28641169467</v>
+        <v>46085.28641168981</v>
       </c>
     </row>
     <row r="1326">
@@ -52148,10 +52148,10 @@
         </is>
       </c>
       <c r="H1326" s="2" t="n">
-        <v>46073.28641169773</v>
+        <v>46073.28641170139</v>
       </c>
       <c r="I1326" s="2" t="n">
-        <v>46078.28641169773</v>
+        <v>46078.28641170139</v>
       </c>
     </row>
     <row r="1327">
@@ -52187,10 +52187,10 @@
         </is>
       </c>
       <c r="H1327" s="2" t="n">
-        <v>46087.28641170112</v>
+        <v>46087.28641170139</v>
       </c>
       <c r="I1327" s="2" t="n">
-        <v>46092.28641170112</v>
+        <v>46092.28641170139</v>
       </c>
     </row>
     <row r="1328">
@@ -52226,10 +52226,10 @@
         </is>
       </c>
       <c r="H1328" s="2" t="n">
-        <v>46069.28641170433</v>
+        <v>46069.28641170139</v>
       </c>
       <c r="I1328" s="2" t="n">
-        <v>46074.28641170433</v>
+        <v>46074.28641170139</v>
       </c>
     </row>
     <row r="1329">
@@ -52265,10 +52265,10 @@
         </is>
       </c>
       <c r="H1329" s="2" t="n">
-        <v>46063.28641170741</v>
+        <v>46063.28641171296</v>
       </c>
       <c r="I1329" s="2" t="n">
-        <v>46068.28641170741</v>
+        <v>46068.28641171296</v>
       </c>
     </row>
     <row r="1330">
@@ -52304,10 +52304,10 @@
         </is>
       </c>
       <c r="H1330" s="2" t="n">
-        <v>46061.28641171058</v>
+        <v>46061.28641171296</v>
       </c>
       <c r="I1330" s="2" t="n">
-        <v>46066.28641171058</v>
+        <v>46066.28641171296</v>
       </c>
     </row>
     <row r="1331">
@@ -52343,10 +52343,10 @@
         </is>
       </c>
       <c r="H1331" s="2" t="n">
-        <v>46080.28641171393</v>
+        <v>46080.28641171296</v>
       </c>
       <c r="I1331" s="2" t="n">
-        <v>46085.28641171393</v>
+        <v>46085.28641171296</v>
       </c>
     </row>
     <row r="1332">
@@ -52382,10 +52382,10 @@
         </is>
       </c>
       <c r="H1332" s="2" t="n">
-        <v>46083.28641171727</v>
+        <v>46083.28641171296</v>
       </c>
       <c r="I1332" s="2" t="n">
-        <v>46088.28641171727</v>
+        <v>46088.28641171296</v>
       </c>
     </row>
     <row r="1333">
@@ -52421,10 +52421,10 @@
         </is>
       </c>
       <c r="H1333" s="2" t="n">
-        <v>46074.2864117203</v>
+        <v>46074.28641172453</v>
       </c>
       <c r="I1333" s="2" t="n">
-        <v>46079.2864117203</v>
+        <v>46079.28641172453</v>
       </c>
     </row>
     <row r="1334">
@@ -52460,10 +52460,10 @@
         </is>
       </c>
       <c r="H1334" s="2" t="n">
-        <v>46065.28641172357</v>
+        <v>46065.28641172453</v>
       </c>
       <c r="I1334" s="2" t="n">
-        <v>46070.28641172357</v>
+        <v>46070.28641172453</v>
       </c>
     </row>
     <row r="1335">
@@ -52499,10 +52499,10 @@
         </is>
       </c>
       <c r="H1335" s="2" t="n">
-        <v>46085.28641172659</v>
+        <v>46085.28641172453</v>
       </c>
       <c r="I1335" s="2" t="n">
-        <v>46090.28641172659</v>
+        <v>46090.28641172453</v>
       </c>
     </row>
     <row r="1336">
@@ -52538,10 +52538,10 @@
         </is>
       </c>
       <c r="H1336" s="2" t="n">
-        <v>46074.28641172958</v>
+        <v>46074.28641172453</v>
       </c>
       <c r="I1336" s="2" t="n">
-        <v>46079.28641172958</v>
+        <v>46079.28641172453</v>
       </c>
     </row>
     <row r="1337">
@@ -52577,10 +52577,10 @@
         </is>
       </c>
       <c r="H1337" s="2" t="n">
-        <v>46069.2864117327</v>
+        <v>46069.28641173611</v>
       </c>
       <c r="I1337" s="2" t="n">
-        <v>46074.2864117327</v>
+        <v>46074.28641173611</v>
       </c>
     </row>
     <row r="1338">
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="H1338" s="2" t="n">
-        <v>46064.28641173617</v>
+        <v>46064.28641173611</v>
       </c>
       <c r="I1338" s="2" t="n">
-        <v>46069.28641173617</v>
+        <v>46069.28641173611</v>
       </c>
     </row>
     <row r="1339">
@@ -52655,10 +52655,10 @@
         </is>
       </c>
       <c r="H1339" s="2" t="n">
-        <v>46084.28641173925</v>
+        <v>46084.28641173611</v>
       </c>
       <c r="I1339" s="2" t="n">
-        <v>46089.28641173925</v>
+        <v>46089.28641173611</v>
       </c>
     </row>
     <row r="1340">
@@ -52694,10 +52694,10 @@
         </is>
       </c>
       <c r="H1340" s="2" t="n">
-        <v>46070.28641174226</v>
+        <v>46070.28641174769</v>
       </c>
       <c r="I1340" s="2" t="n">
-        <v>46075.28641174226</v>
+        <v>46075.28641174769</v>
       </c>
     </row>
     <row r="1341">
@@ -52733,10 +52733,10 @@
         </is>
       </c>
       <c r="H1341" s="2" t="n">
-        <v>46068.28641174528</v>
+        <v>46068.28641174769</v>
       </c>
       <c r="I1341" s="2" t="n">
-        <v>46073.28641174528</v>
+        <v>46073.28641174769</v>
       </c>
     </row>
     <row r="1342">
@@ -52772,10 +52772,10 @@
         </is>
       </c>
       <c r="H1342" s="2" t="n">
-        <v>46066.28641174863</v>
+        <v>46066.28641174769</v>
       </c>
       <c r="I1342" s="2" t="n">
-        <v>46071.28641174863</v>
+        <v>46071.28641174769</v>
       </c>
     </row>
     <row r="1343">
@@ -52811,10 +52811,10 @@
         </is>
       </c>
       <c r="H1343" s="2" t="n">
-        <v>46084.28641175186</v>
+        <v>46084.28641174769</v>
       </c>
       <c r="I1343" s="2" t="n">
-        <v>46089.28641175186</v>
+        <v>46089.28641174769</v>
       </c>
     </row>
     <row r="1344">
@@ -52850,10 +52850,10 @@
         </is>
       </c>
       <c r="H1344" s="2" t="n">
-        <v>46084.28641175497</v>
+        <v>46084.28641175926</v>
       </c>
       <c r="I1344" s="2" t="n">
-        <v>46089.28641175497</v>
+        <v>46089.28641175926</v>
       </c>
     </row>
     <row r="1345">
@@ -52889,10 +52889,10 @@
         </is>
       </c>
       <c r="H1345" s="2" t="n">
-        <v>46067.28641175831</v>
+        <v>46067.28641175926</v>
       </c>
       <c r="I1345" s="2" t="n">
-        <v>46072.28641175831</v>
+        <v>46072.28641175926</v>
       </c>
     </row>
     <row r="1346">
@@ -52928,10 +52928,10 @@
         </is>
       </c>
       <c r="H1346" s="2" t="n">
-        <v>46074.2864117615</v>
+        <v>46074.28641175926</v>
       </c>
       <c r="I1346" s="2" t="n">
-        <v>46079.2864117615</v>
+        <v>46079.28641175926</v>
       </c>
     </row>
     <row r="1347">
@@ -52967,10 +52967,10 @@
         </is>
       </c>
       <c r="H1347" s="2" t="n">
-        <v>46087.28641176457</v>
+        <v>46087.28641175926</v>
       </c>
       <c r="I1347" s="2" t="n">
-        <v>46092.28641176457</v>
+        <v>46092.28641175926</v>
       </c>
     </row>
     <row r="1348">
@@ -53006,10 +53006,10 @@
         </is>
       </c>
       <c r="H1348" s="2" t="n">
-        <v>46089.28641176772</v>
+        <v>46089.28641177083</v>
       </c>
       <c r="I1348" s="2" t="n">
-        <v>46094.28641176772</v>
+        <v>46094.28641177083</v>
       </c>
     </row>
     <row r="1349">
@@ -53045,10 +53045,10 @@
         </is>
       </c>
       <c r="H1349" s="2" t="n">
-        <v>46081.28641177102</v>
+        <v>46081.28641177083</v>
       </c>
       <c r="I1349" s="2" t="n">
-        <v>46086.28641177102</v>
+        <v>46086.28641177083</v>
       </c>
     </row>
     <row r="1350">
@@ -53084,10 +53084,10 @@
         </is>
       </c>
       <c r="H1350" s="2" t="n">
-        <v>46061.28641177412</v>
+        <v>46061.28641177083</v>
       </c>
       <c r="I1350" s="2" t="n">
-        <v>46066.28641177412</v>
+        <v>46066.28641177083</v>
       </c>
     </row>
     <row r="1351">
@@ -53123,10 +53123,1960 @@
         </is>
       </c>
       <c r="H1351" s="2" t="n">
-        <v>46082.28641177717</v>
+        <v>46082.28641178241</v>
       </c>
       <c r="I1351" s="2" t="n">
-        <v>46087.28641177717</v>
+        <v>46087.28641178241</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>042c0172-287c-41a9-aa2b-35d24bed17cb</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>5262</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>95.13</v>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1352" s="2" t="n">
+        <v>46078.32285992507</v>
+      </c>
+      <c r="I1352" s="2" t="n">
+        <v>46083.32285992507</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>d89801b1-f7ce-452a-9967-c9e0646f5f20</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>1164.8</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1353" s="2" t="n">
+        <v>46060.32285992941</v>
+      </c>
+      <c r="I1353" s="2" t="n">
+        <v>46065.32285992941</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>07f0b4c3-3055-4059-bfc8-e5982f74dd40</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>6218.51</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1354" s="2" t="n">
+        <v>46077.32285993282</v>
+      </c>
+      <c r="I1354" s="2" t="n">
+        <v>46082.32285993282</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>6226717f-afae-405c-b543-aaaca372a881</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>8001.46</v>
+      </c>
+      <c r="D1355" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1355" s="2" t="n">
+        <v>46080.32285993652</v>
+      </c>
+      <c r="I1355" s="2" t="n">
+        <v>46085.32285993652</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2bd5f778-63a7-41fe-b7ed-e7c08ef1a386</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>5795.24</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>98.28</v>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1356" s="2" t="n">
+        <v>46077.32285993961</v>
+      </c>
+      <c r="I1356" s="2" t="n">
+        <v>46082.32285993961</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>bcaa84f3-497f-494a-87bc-ab1188aae3fc</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>4692.69</v>
+      </c>
+      <c r="D1357" t="n">
+        <v>90.11</v>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1357" s="2" t="n">
+        <v>46073.32285994302</v>
+      </c>
+      <c r="I1357" s="2" t="n">
+        <v>46078.32285994302</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>61e49900-8e22-41cd-81d6-a8881bf76446</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>5860.88</v>
+      </c>
+      <c r="D1358" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1358" s="2" t="n">
+        <v>46085.3228599463</v>
+      </c>
+      <c r="I1358" s="2" t="n">
+        <v>46090.3228599463</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>61189384-2783-44be-8198-bc01b2ee5878</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>8126.52</v>
+      </c>
+      <c r="D1359" t="n">
+        <v>87.91</v>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1359" s="2" t="n">
+        <v>46075.32285994949</v>
+      </c>
+      <c r="I1359" s="2" t="n">
+        <v>46080.32285994949</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>53ffd795-6564-453d-b63b-0a499fbb0ad1</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>4383.58</v>
+      </c>
+      <c r="D1360" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1360" s="2" t="n">
+        <v>46086.3228599526</v>
+      </c>
+      <c r="I1360" s="2" t="n">
+        <v>46091.3228599526</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>9681db5e-f4df-44ee-8c27-d53df6f5df80</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>1042.11</v>
+      </c>
+      <c r="D1361" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1361" s="2" t="n">
+        <v>46072.32285995584</v>
+      </c>
+      <c r="I1361" s="2" t="n">
+        <v>46077.32285995584</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>eeba8993-98e2-4388-b4b6-e59f9469684b</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>9237.66</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1362" s="2" t="n">
+        <v>46089.32285995917</v>
+      </c>
+      <c r="I1362" s="2" t="n">
+        <v>46094.32285995917</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>d413c626-7ec8-4ad4-9674-c399a597c62c</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>1978.68</v>
+      </c>
+      <c r="D1363" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1363" s="2" t="n">
+        <v>46080.3228599624</v>
+      </c>
+      <c r="I1363" s="2" t="n">
+        <v>46085.3228599624</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>86cc4417-25d9-4744-9627-df6a177b79ac</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>2771.95</v>
+      </c>
+      <c r="D1364" t="n">
+        <v>92.52</v>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1364" s="2" t="n">
+        <v>46075.32285996567</v>
+      </c>
+      <c r="I1364" s="2" t="n">
+        <v>46080.32285996567</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>6ccfe209-ab8a-4ce9-987f-9783fe5e957c</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>7639.62</v>
+      </c>
+      <c r="D1365" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1365" s="2" t="n">
+        <v>46065.32285996973</v>
+      </c>
+      <c r="I1365" s="2" t="n">
+        <v>46070.32285996973</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>7cf7806f-dce3-429d-97a8-e0b9bd41b8ed</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>4641.74</v>
+      </c>
+      <c r="D1366" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1366" s="2" t="n">
+        <v>46062.32285997286</v>
+      </c>
+      <c r="I1366" s="2" t="n">
+        <v>46067.32285997286</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>87e9a731-54a2-4375-a2e9-1e437e5c7b11</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>4680.25</v>
+      </c>
+      <c r="D1367" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1367" s="2" t="n">
+        <v>46067.32285997614</v>
+      </c>
+      <c r="I1367" s="2" t="n">
+        <v>46072.32285997614</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>f1264bd0-b226-4918-b8cd-33df7c1d66c6</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>7864.09</v>
+      </c>
+      <c r="D1368" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1368" s="2" t="n">
+        <v>46065.32285997931</v>
+      </c>
+      <c r="I1368" s="2" t="n">
+        <v>46070.32285997931</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>a9c1bb20-6bb7-4b54-9b8e-2c47eb726682</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>3935.98</v>
+      </c>
+      <c r="D1369" t="n">
+        <v>97.03</v>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1369" s="2" t="n">
+        <v>46085.32285998268</v>
+      </c>
+      <c r="I1369" s="2" t="n">
+        <v>46090.32285998268</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>b659833e-9aaf-46f8-9a4a-8f61f6e12efa</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>4011.41</v>
+      </c>
+      <c r="D1370" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1370" s="2" t="n">
+        <v>46081.32285998595</v>
+      </c>
+      <c r="I1370" s="2" t="n">
+        <v>46086.32285998595</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>e7923e10-72de-4366-acae-0293dac6674e</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>7809.41</v>
+      </c>
+      <c r="D1371" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1371" s="2" t="n">
+        <v>46060.32285998904</v>
+      </c>
+      <c r="I1371" s="2" t="n">
+        <v>46065.32285998904</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>371953eb-61c5-415a-ba30-92c60efc9059</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>4791.87</v>
+      </c>
+      <c r="D1372" t="n">
+        <v>94.61</v>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1372" s="2" t="n">
+        <v>46082.3228599925</v>
+      </c>
+      <c r="I1372" s="2" t="n">
+        <v>46087.3228599925</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>96a1a977-9b51-417f-99ed-aae66d9a89d9</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>1652.48</v>
+      </c>
+      <c r="D1373" t="n">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1373" s="2" t="n">
+        <v>46069.32285999559</v>
+      </c>
+      <c r="I1373" s="2" t="n">
+        <v>46074.32285999559</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>799033ac-761f-48e0-8324-c5f6b3d92ec5</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>6650.62</v>
+      </c>
+      <c r="D1374" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1374" s="2" t="n">
+        <v>46066.32285999883</v>
+      </c>
+      <c r="I1374" s="2" t="n">
+        <v>46071.32285999883</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>09c88e58-ca09-454c-8de9-9820434f10e1</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>4859.88</v>
+      </c>
+      <c r="D1375" t="n">
+        <v>92.48999999999999</v>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1375" s="2" t="n">
+        <v>46060.32286000184</v>
+      </c>
+      <c r="I1375" s="2" t="n">
+        <v>46065.32286000184</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>b2b466d4-7975-4ff3-99ce-87742466c525</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>6979.41</v>
+      </c>
+      <c r="D1376" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1376" s="2" t="n">
+        <v>46072.32286000525</v>
+      </c>
+      <c r="I1376" s="2" t="n">
+        <v>46077.32286000525</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>531462a2-3085-4d1f-9780-eaebcdaaf18b</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>4026.25</v>
+      </c>
+      <c r="D1377" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1377" s="2" t="n">
+        <v>46077.32286000862</v>
+      </c>
+      <c r="I1377" s="2" t="n">
+        <v>46082.32286000862</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2b4799c4-3670-4808-8778-eae82aeb1763</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>9042.33</v>
+      </c>
+      <c r="D1378" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1378" s="2" t="n">
+        <v>46064.32286001185</v>
+      </c>
+      <c r="I1378" s="2" t="n">
+        <v>46069.32286001185</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>b6779d9f-5466-47a5-a68d-ad3a1ad73103</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>6500.39</v>
+      </c>
+      <c r="D1379" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1379" s="2" t="n">
+        <v>46080.32286001596</v>
+      </c>
+      <c r="I1379" s="2" t="n">
+        <v>46085.32286001596</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>5dc3c061-fc4c-478e-b42e-7fc97d9c1057</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>2673.41</v>
+      </c>
+      <c r="D1380" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1380" s="2" t="n">
+        <v>46060.32286001905</v>
+      </c>
+      <c r="I1380" s="2" t="n">
+        <v>46065.32286001905</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>11057573-f394-479c-a800-c397fa82254b</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>1514.42</v>
+      </c>
+      <c r="D1381" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1381" s="2" t="n">
+        <v>46085.32286002226</v>
+      </c>
+      <c r="I1381" s="2" t="n">
+        <v>46090.32286002226</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>e33248c9-dd6a-4a57-adfb-42e950332c81</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>8053.74</v>
+      </c>
+      <c r="D1382" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1382" s="2" t="n">
+        <v>46072.32286002535</v>
+      </c>
+      <c r="I1382" s="2" t="n">
+        <v>46077.32286002535</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>b202a867-d31d-487b-8ec5-5ca805a2f47b</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>9673.809999999999</v>
+      </c>
+      <c r="D1383" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1383" s="2" t="n">
+        <v>46087.32286002857</v>
+      </c>
+      <c r="I1383" s="2" t="n">
+        <v>46092.32286002857</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>a9ca00f1-bf17-46b7-8242-b5544f40e24e</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>1850.26</v>
+      </c>
+      <c r="D1384" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1384" s="2" t="n">
+        <v>46089.3228600318</v>
+      </c>
+      <c r="I1384" s="2" t="n">
+        <v>46094.3228600318</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>a14edb41-93ce-4614-a48e-79d6f7af4eb2</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>3351.65</v>
+      </c>
+      <c r="D1385" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1385" s="2" t="n">
+        <v>46079.32286003488</v>
+      </c>
+      <c r="I1385" s="2" t="n">
+        <v>46084.32286003488</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>f5f9551a-34e9-4e7e-aac2-e00976b9d675</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>2946.26</v>
+      </c>
+      <c r="D1386" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1386" s="2" t="n">
+        <v>46086.32286003864</v>
+      </c>
+      <c r="I1386" s="2" t="n">
+        <v>46091.32286003864</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>09129bc0-e031-451a-ba2c-557552e4613a</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>1610.47</v>
+      </c>
+      <c r="D1387" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1387" s="2" t="n">
+        <v>46078.32286004175</v>
+      </c>
+      <c r="I1387" s="2" t="n">
+        <v>46083.32286004175</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>d55e95ca-f146-4db6-bd4a-cd8a295f0757</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>6616.77</v>
+      </c>
+      <c r="D1388" t="n">
+        <v>92.03</v>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1388" s="2" t="n">
+        <v>46078.32286004492</v>
+      </c>
+      <c r="I1388" s="2" t="n">
+        <v>46083.32286004492</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>dbebf4b9-63ac-4758-b20c-73da260347ee</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>6149.41</v>
+      </c>
+      <c r="D1389" t="n">
+        <v>91.03</v>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1389" s="2" t="n">
+        <v>46075.32286004804</v>
+      </c>
+      <c r="I1389" s="2" t="n">
+        <v>46080.32286004804</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>f97556a6-39e3-4c1c-99f9-89869070319b</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>1304.95</v>
+      </c>
+      <c r="D1390" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1390" s="2" t="n">
+        <v>46076.32286005131</v>
+      </c>
+      <c r="I1390" s="2" t="n">
+        <v>46081.32286005131</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>79e97a7c-b334-4834-b507-a7fffdc05c30</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>1363.61</v>
+      </c>
+      <c r="D1391" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1391" s="2" t="n">
+        <v>46077.32286005449</v>
+      </c>
+      <c r="I1391" s="2" t="n">
+        <v>46082.32286005449</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>f8516c87-be83-4455-8d74-15fbca730b80</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>5165.76</v>
+      </c>
+      <c r="D1392" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1392" s="2" t="n">
+        <v>46088.32286005755</v>
+      </c>
+      <c r="I1392" s="2" t="n">
+        <v>46093.32286005755</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>ea5c9ae0-192e-4bad-8096-51f2b9a8ebc3</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>9732.08</v>
+      </c>
+      <c r="D1393" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1393" s="2" t="n">
+        <v>46070.3228600606</v>
+      </c>
+      <c r="I1393" s="2" t="n">
+        <v>46075.3228600606</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>784fa69c-0ef3-4ef4-977b-2be19f7ba08d</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>7451.17</v>
+      </c>
+      <c r="D1394" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1394" s="2" t="n">
+        <v>46063.32286006435</v>
+      </c>
+      <c r="I1394" s="2" t="n">
+        <v>46068.32286006435</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>6195dead-f130-41dd-a558-02f38456b2cc</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>9518.190000000001</v>
+      </c>
+      <c r="D1395" t="n">
+        <v>86.33</v>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1395" s="2" t="n">
+        <v>46069.32286006756</v>
+      </c>
+      <c r="I1395" s="2" t="n">
+        <v>46074.32286006756</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>95cf1499-f773-433f-aa0f-c1e1d7a809af</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>9759.860000000001</v>
+      </c>
+      <c r="D1396" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1396" s="2" t="n">
+        <v>46079.32286007085</v>
+      </c>
+      <c r="I1396" s="2" t="n">
+        <v>46084.32286007085</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>9c6e90b1-dff2-4b78-ae67-cf32817d5df4</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>3045.08</v>
+      </c>
+      <c r="D1397" t="n">
+        <v>89.91</v>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1397" s="2" t="n">
+        <v>46073.3228600743</v>
+      </c>
+      <c r="I1397" s="2" t="n">
+        <v>46078.3228600743</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>6c608919-9b21-4924-8ffa-05693147aed7</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>4187.43</v>
+      </c>
+      <c r="D1398" t="n">
+        <v>91.47</v>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1398" s="2" t="n">
+        <v>46087.32286007755</v>
+      </c>
+      <c r="I1398" s="2" t="n">
+        <v>46092.32286007755</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>45ac5b49-4ae9-40ba-816a-20f768a2d408</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>4527.3</v>
+      </c>
+      <c r="D1399" t="n">
+        <v>98.87</v>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1399" s="2" t="n">
+        <v>46089.32286008081</v>
+      </c>
+      <c r="I1399" s="2" t="n">
+        <v>46094.32286008081</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>d66a44be-271b-4e19-b4fa-fb2b86a67062</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>5842.52</v>
+      </c>
+      <c r="D1400" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1400" s="2" t="n">
+        <v>46068.32286008428</v>
+      </c>
+      <c r="I1400" s="2" t="n">
+        <v>46073.32286008428</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>3e97200b-aff4-476f-9ae6-ad2ce4d611a1</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>9014.200000000001</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1401" s="2" t="n">
+        <v>46064.32286008786</v>
+      </c>
+      <c r="I1401" s="2" t="n">
+        <v>46069.32286008786</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1401"/>
+  <dimension ref="A1:I1451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53162,10 +53162,10 @@
         </is>
       </c>
       <c r="H1352" s="2" t="n">
-        <v>46078.32285992507</v>
+        <v>46078.32285993056</v>
       </c>
       <c r="I1352" s="2" t="n">
-        <v>46083.32285992507</v>
+        <v>46083.32285993056</v>
       </c>
     </row>
     <row r="1353">
@@ -53201,10 +53201,10 @@
         </is>
       </c>
       <c r="H1353" s="2" t="n">
-        <v>46060.32285992941</v>
+        <v>46060.32285993056</v>
       </c>
       <c r="I1353" s="2" t="n">
-        <v>46065.32285992941</v>
+        <v>46065.32285993056</v>
       </c>
     </row>
     <row r="1354">
@@ -53240,10 +53240,10 @@
         </is>
       </c>
       <c r="H1354" s="2" t="n">
-        <v>46077.32285993282</v>
+        <v>46077.32285993056</v>
       </c>
       <c r="I1354" s="2" t="n">
-        <v>46082.32285993282</v>
+        <v>46082.32285993056</v>
       </c>
     </row>
     <row r="1355">
@@ -53279,10 +53279,10 @@
         </is>
       </c>
       <c r="H1355" s="2" t="n">
-        <v>46080.32285993652</v>
+        <v>46080.32285994213</v>
       </c>
       <c r="I1355" s="2" t="n">
-        <v>46085.32285993652</v>
+        <v>46085.32285994213</v>
       </c>
     </row>
     <row r="1356">
@@ -53318,10 +53318,10 @@
         </is>
       </c>
       <c r="H1356" s="2" t="n">
-        <v>46077.32285993961</v>
+        <v>46077.32285994213</v>
       </c>
       <c r="I1356" s="2" t="n">
-        <v>46082.32285993961</v>
+        <v>46082.32285994213</v>
       </c>
     </row>
     <row r="1357">
@@ -53357,10 +53357,10 @@
         </is>
       </c>
       <c r="H1357" s="2" t="n">
-        <v>46073.32285994302</v>
+        <v>46073.32285994213</v>
       </c>
       <c r="I1357" s="2" t="n">
-        <v>46078.32285994302</v>
+        <v>46078.32285994213</v>
       </c>
     </row>
     <row r="1358">
@@ -53396,10 +53396,10 @@
         </is>
       </c>
       <c r="H1358" s="2" t="n">
-        <v>46085.3228599463</v>
+        <v>46085.32285994213</v>
       </c>
       <c r="I1358" s="2" t="n">
-        <v>46090.3228599463</v>
+        <v>46090.32285994213</v>
       </c>
     </row>
     <row r="1359">
@@ -53435,10 +53435,10 @@
         </is>
       </c>
       <c r="H1359" s="2" t="n">
-        <v>46075.32285994949</v>
+        <v>46075.3228599537</v>
       </c>
       <c r="I1359" s="2" t="n">
-        <v>46080.32285994949</v>
+        <v>46080.3228599537</v>
       </c>
     </row>
     <row r="1360">
@@ -53474,10 +53474,10 @@
         </is>
       </c>
       <c r="H1360" s="2" t="n">
-        <v>46086.3228599526</v>
+        <v>46086.3228599537</v>
       </c>
       <c r="I1360" s="2" t="n">
-        <v>46091.3228599526</v>
+        <v>46091.3228599537</v>
       </c>
     </row>
     <row r="1361">
@@ -53513,10 +53513,10 @@
         </is>
       </c>
       <c r="H1361" s="2" t="n">
-        <v>46072.32285995584</v>
+        <v>46072.3228599537</v>
       </c>
       <c r="I1361" s="2" t="n">
-        <v>46077.32285995584</v>
+        <v>46077.3228599537</v>
       </c>
     </row>
     <row r="1362">
@@ -53552,10 +53552,10 @@
         </is>
       </c>
       <c r="H1362" s="2" t="n">
-        <v>46089.32285995917</v>
+        <v>46089.3228599537</v>
       </c>
       <c r="I1362" s="2" t="n">
-        <v>46094.32285995917</v>
+        <v>46094.3228599537</v>
       </c>
     </row>
     <row r="1363">
@@ -53591,10 +53591,10 @@
         </is>
       </c>
       <c r="H1363" s="2" t="n">
-        <v>46080.3228599624</v>
+        <v>46080.32285996528</v>
       </c>
       <c r="I1363" s="2" t="n">
-        <v>46085.3228599624</v>
+        <v>46085.32285996528</v>
       </c>
     </row>
     <row r="1364">
@@ -53630,10 +53630,10 @@
         </is>
       </c>
       <c r="H1364" s="2" t="n">
-        <v>46075.32285996567</v>
+        <v>46075.32285996528</v>
       </c>
       <c r="I1364" s="2" t="n">
-        <v>46080.32285996567</v>
+        <v>46080.32285996528</v>
       </c>
     </row>
     <row r="1365">
@@ -53669,10 +53669,10 @@
         </is>
       </c>
       <c r="H1365" s="2" t="n">
-        <v>46065.32285996973</v>
+        <v>46065.32285996528</v>
       </c>
       <c r="I1365" s="2" t="n">
-        <v>46070.32285996973</v>
+        <v>46070.32285996528</v>
       </c>
     </row>
     <row r="1366">
@@ -53708,10 +53708,10 @@
         </is>
       </c>
       <c r="H1366" s="2" t="n">
-        <v>46062.32285997286</v>
+        <v>46062.32285997686</v>
       </c>
       <c r="I1366" s="2" t="n">
-        <v>46067.32285997286</v>
+        <v>46067.32285997686</v>
       </c>
     </row>
     <row r="1367">
@@ -53747,10 +53747,10 @@
         </is>
       </c>
       <c r="H1367" s="2" t="n">
-        <v>46067.32285997614</v>
+        <v>46067.32285997686</v>
       </c>
       <c r="I1367" s="2" t="n">
-        <v>46072.32285997614</v>
+        <v>46072.32285997686</v>
       </c>
     </row>
     <row r="1368">
@@ -53786,10 +53786,10 @@
         </is>
       </c>
       <c r="H1368" s="2" t="n">
-        <v>46065.32285997931</v>
+        <v>46065.32285997686</v>
       </c>
       <c r="I1368" s="2" t="n">
-        <v>46070.32285997931</v>
+        <v>46070.32285997686</v>
       </c>
     </row>
     <row r="1369">
@@ -53825,10 +53825,10 @@
         </is>
       </c>
       <c r="H1369" s="2" t="n">
-        <v>46085.32285998268</v>
+        <v>46085.32285998842</v>
       </c>
       <c r="I1369" s="2" t="n">
-        <v>46090.32285998268</v>
+        <v>46090.32285998842</v>
       </c>
     </row>
     <row r="1370">
@@ -53864,10 +53864,10 @@
         </is>
       </c>
       <c r="H1370" s="2" t="n">
-        <v>46081.32285998595</v>
+        <v>46081.32285998842</v>
       </c>
       <c r="I1370" s="2" t="n">
-        <v>46086.32285998595</v>
+        <v>46086.32285998842</v>
       </c>
     </row>
     <row r="1371">
@@ -53903,10 +53903,10 @@
         </is>
       </c>
       <c r="H1371" s="2" t="n">
-        <v>46060.32285998904</v>
+        <v>46060.32285998842</v>
       </c>
       <c r="I1371" s="2" t="n">
-        <v>46065.32285998904</v>
+        <v>46065.32285998842</v>
       </c>
     </row>
     <row r="1372">
@@ -53942,10 +53942,10 @@
         </is>
       </c>
       <c r="H1372" s="2" t="n">
-        <v>46082.3228599925</v>
+        <v>46082.32285998842</v>
       </c>
       <c r="I1372" s="2" t="n">
-        <v>46087.3228599925</v>
+        <v>46087.32285998842</v>
       </c>
     </row>
     <row r="1373">
@@ -53981,10 +53981,10 @@
         </is>
       </c>
       <c r="H1373" s="2" t="n">
-        <v>46069.32285999559</v>
+        <v>46069.32286</v>
       </c>
       <c r="I1373" s="2" t="n">
-        <v>46074.32285999559</v>
+        <v>46074.32286</v>
       </c>
     </row>
     <row r="1374">
@@ -54020,10 +54020,10 @@
         </is>
       </c>
       <c r="H1374" s="2" t="n">
-        <v>46066.32285999883</v>
+        <v>46066.32286</v>
       </c>
       <c r="I1374" s="2" t="n">
-        <v>46071.32285999883</v>
+        <v>46071.32286</v>
       </c>
     </row>
     <row r="1375">
@@ -54059,10 +54059,10 @@
         </is>
       </c>
       <c r="H1375" s="2" t="n">
-        <v>46060.32286000184</v>
+        <v>46060.32286</v>
       </c>
       <c r="I1375" s="2" t="n">
-        <v>46065.32286000184</v>
+        <v>46065.32286</v>
       </c>
     </row>
     <row r="1376">
@@ -54098,10 +54098,10 @@
         </is>
       </c>
       <c r="H1376" s="2" t="n">
-        <v>46072.32286000525</v>
+        <v>46072.32286</v>
       </c>
       <c r="I1376" s="2" t="n">
-        <v>46077.32286000525</v>
+        <v>46077.32286</v>
       </c>
     </row>
     <row r="1377">
@@ -54137,10 +54137,10 @@
         </is>
       </c>
       <c r="H1377" s="2" t="n">
-        <v>46077.32286000862</v>
+        <v>46077.32286001158</v>
       </c>
       <c r="I1377" s="2" t="n">
-        <v>46082.32286000862</v>
+        <v>46082.32286001158</v>
       </c>
     </row>
     <row r="1378">
@@ -54176,10 +54176,10 @@
         </is>
       </c>
       <c r="H1378" s="2" t="n">
-        <v>46064.32286001185</v>
+        <v>46064.32286001158</v>
       </c>
       <c r="I1378" s="2" t="n">
-        <v>46069.32286001185</v>
+        <v>46069.32286001158</v>
       </c>
     </row>
     <row r="1379">
@@ -54215,10 +54215,10 @@
         </is>
       </c>
       <c r="H1379" s="2" t="n">
-        <v>46080.32286001596</v>
+        <v>46080.32286001158</v>
       </c>
       <c r="I1379" s="2" t="n">
-        <v>46085.32286001596</v>
+        <v>46085.32286001158</v>
       </c>
     </row>
     <row r="1380">
@@ -54254,10 +54254,10 @@
         </is>
       </c>
       <c r="H1380" s="2" t="n">
-        <v>46060.32286001905</v>
+        <v>46060.32286002315</v>
       </c>
       <c r="I1380" s="2" t="n">
-        <v>46065.32286001905</v>
+        <v>46065.32286002315</v>
       </c>
     </row>
     <row r="1381">
@@ -54293,10 +54293,10 @@
         </is>
       </c>
       <c r="H1381" s="2" t="n">
-        <v>46085.32286002226</v>
+        <v>46085.32286002315</v>
       </c>
       <c r="I1381" s="2" t="n">
-        <v>46090.32286002226</v>
+        <v>46090.32286002315</v>
       </c>
     </row>
     <row r="1382">
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="H1382" s="2" t="n">
-        <v>46072.32286002535</v>
+        <v>46072.32286002315</v>
       </c>
       <c r="I1382" s="2" t="n">
-        <v>46077.32286002535</v>
+        <v>46077.32286002315</v>
       </c>
     </row>
     <row r="1383">
@@ -54371,10 +54371,10 @@
         </is>
       </c>
       <c r="H1383" s="2" t="n">
-        <v>46087.32286002857</v>
+        <v>46087.32286002315</v>
       </c>
       <c r="I1383" s="2" t="n">
-        <v>46092.32286002857</v>
+        <v>46092.32286002315</v>
       </c>
     </row>
     <row r="1384">
@@ -54410,10 +54410,10 @@
         </is>
       </c>
       <c r="H1384" s="2" t="n">
-        <v>46089.3228600318</v>
+        <v>46089.32286003472</v>
       </c>
       <c r="I1384" s="2" t="n">
-        <v>46094.3228600318</v>
+        <v>46094.32286003472</v>
       </c>
     </row>
     <row r="1385">
@@ -54449,10 +54449,10 @@
         </is>
       </c>
       <c r="H1385" s="2" t="n">
-        <v>46079.32286003488</v>
+        <v>46079.32286003472</v>
       </c>
       <c r="I1385" s="2" t="n">
-        <v>46084.32286003488</v>
+        <v>46084.32286003472</v>
       </c>
     </row>
     <row r="1386">
@@ -54488,10 +54488,10 @@
         </is>
       </c>
       <c r="H1386" s="2" t="n">
-        <v>46086.32286003864</v>
+        <v>46086.32286003472</v>
       </c>
       <c r="I1386" s="2" t="n">
-        <v>46091.32286003864</v>
+        <v>46091.32286003472</v>
       </c>
     </row>
     <row r="1387">
@@ -54527,10 +54527,10 @@
         </is>
       </c>
       <c r="H1387" s="2" t="n">
-        <v>46078.32286004175</v>
+        <v>46078.3228600463</v>
       </c>
       <c r="I1387" s="2" t="n">
-        <v>46083.32286004175</v>
+        <v>46083.3228600463</v>
       </c>
     </row>
     <row r="1388">
@@ -54566,10 +54566,10 @@
         </is>
       </c>
       <c r="H1388" s="2" t="n">
-        <v>46078.32286004492</v>
+        <v>46078.3228600463</v>
       </c>
       <c r="I1388" s="2" t="n">
-        <v>46083.32286004492</v>
+        <v>46083.3228600463</v>
       </c>
     </row>
     <row r="1389">
@@ -54605,10 +54605,10 @@
         </is>
       </c>
       <c r="H1389" s="2" t="n">
-        <v>46075.32286004804</v>
+        <v>46075.3228600463</v>
       </c>
       <c r="I1389" s="2" t="n">
-        <v>46080.32286004804</v>
+        <v>46080.3228600463</v>
       </c>
     </row>
     <row r="1390">
@@ -54644,10 +54644,10 @@
         </is>
       </c>
       <c r="H1390" s="2" t="n">
-        <v>46076.32286005131</v>
+        <v>46076.3228600463</v>
       </c>
       <c r="I1390" s="2" t="n">
-        <v>46081.32286005131</v>
+        <v>46081.3228600463</v>
       </c>
     </row>
     <row r="1391">
@@ -54683,10 +54683,10 @@
         </is>
       </c>
       <c r="H1391" s="2" t="n">
-        <v>46077.32286005449</v>
+        <v>46077.32286005787</v>
       </c>
       <c r="I1391" s="2" t="n">
-        <v>46082.32286005449</v>
+        <v>46082.32286005787</v>
       </c>
     </row>
     <row r="1392">
@@ -54722,10 +54722,10 @@
         </is>
       </c>
       <c r="H1392" s="2" t="n">
-        <v>46088.32286005755</v>
+        <v>46088.32286005787</v>
       </c>
       <c r="I1392" s="2" t="n">
-        <v>46093.32286005755</v>
+        <v>46093.32286005787</v>
       </c>
     </row>
     <row r="1393">
@@ -54761,10 +54761,10 @@
         </is>
       </c>
       <c r="H1393" s="2" t="n">
-        <v>46070.3228600606</v>
+        <v>46070.32286005787</v>
       </c>
       <c r="I1393" s="2" t="n">
-        <v>46075.3228600606</v>
+        <v>46075.32286005787</v>
       </c>
     </row>
     <row r="1394">
@@ -54800,10 +54800,10 @@
         </is>
       </c>
       <c r="H1394" s="2" t="n">
-        <v>46063.32286006435</v>
+        <v>46063.32286006944</v>
       </c>
       <c r="I1394" s="2" t="n">
-        <v>46068.32286006435</v>
+        <v>46068.32286006944</v>
       </c>
     </row>
     <row r="1395">
@@ -54839,10 +54839,10 @@
         </is>
       </c>
       <c r="H1395" s="2" t="n">
-        <v>46069.32286006756</v>
+        <v>46069.32286006944</v>
       </c>
       <c r="I1395" s="2" t="n">
-        <v>46074.32286006756</v>
+        <v>46074.32286006944</v>
       </c>
     </row>
     <row r="1396">
@@ -54878,10 +54878,10 @@
         </is>
       </c>
       <c r="H1396" s="2" t="n">
-        <v>46079.32286007085</v>
+        <v>46079.32286006944</v>
       </c>
       <c r="I1396" s="2" t="n">
-        <v>46084.32286007085</v>
+        <v>46084.32286006944</v>
       </c>
     </row>
     <row r="1397">
@@ -54917,10 +54917,10 @@
         </is>
       </c>
       <c r="H1397" s="2" t="n">
-        <v>46073.3228600743</v>
+        <v>46073.32286006944</v>
       </c>
       <c r="I1397" s="2" t="n">
-        <v>46078.3228600743</v>
+        <v>46078.32286006944</v>
       </c>
     </row>
     <row r="1398">
@@ -54956,10 +54956,10 @@
         </is>
       </c>
       <c r="H1398" s="2" t="n">
-        <v>46087.32286007755</v>
+        <v>46087.32286008102</v>
       </c>
       <c r="I1398" s="2" t="n">
-        <v>46092.32286007755</v>
+        <v>46092.32286008102</v>
       </c>
     </row>
     <row r="1399">
@@ -54995,10 +54995,10 @@
         </is>
       </c>
       <c r="H1399" s="2" t="n">
-        <v>46089.32286008081</v>
+        <v>46089.32286008102</v>
       </c>
       <c r="I1399" s="2" t="n">
-        <v>46094.32286008081</v>
+        <v>46094.32286008102</v>
       </c>
     </row>
     <row r="1400">
@@ -55034,10 +55034,10 @@
         </is>
       </c>
       <c r="H1400" s="2" t="n">
-        <v>46068.32286008428</v>
+        <v>46068.32286008102</v>
       </c>
       <c r="I1400" s="2" t="n">
-        <v>46073.32286008428</v>
+        <v>46073.32286008102</v>
       </c>
     </row>
     <row r="1401">
@@ -55073,10 +55073,1960 @@
         </is>
       </c>
       <c r="H1401" s="2" t="n">
-        <v>46064.32286008786</v>
+        <v>46064.32286009259</v>
       </c>
       <c r="I1401" s="2" t="n">
-        <v>46069.32286008786</v>
+        <v>46069.32286009259</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>315233ab-de09-4dae-98c5-60b6571801ec</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>7548.74</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1402" s="2" t="n">
+        <v>46076.35787033964</v>
+      </c>
+      <c r="I1402" s="2" t="n">
+        <v>46081.35787033964</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>eab062a8-1ce4-4835-8e45-830bbc1b4f20</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>9318.620000000001</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1403" s="2" t="n">
+        <v>46073.35787034393</v>
+      </c>
+      <c r="I1403" s="2" t="n">
+        <v>46078.35787034393</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>c8cddf37-cf9c-4eb8-938d-5a84537c9fb2</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>4343.55</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1404" s="2" t="n">
+        <v>46086.35787034714</v>
+      </c>
+      <c r="I1404" s="2" t="n">
+        <v>46091.35787034714</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>9fe9a17c-a3b0-4753-9222-2375b34f844d</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>1737.33</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1405" s="2" t="n">
+        <v>46086.35787035071</v>
+      </c>
+      <c r="I1405" s="2" t="n">
+        <v>46091.35787035071</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>bc5b5ab3-fd7b-4b80-b7dd-26a1b1b369f5</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>2852.52</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1406" s="2" t="n">
+        <v>46073.35787035383</v>
+      </c>
+      <c r="I1406" s="2" t="n">
+        <v>46078.35787035383</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>380dc11e-72e7-4f87-a035-6fc7e73fcf74</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>6881</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1407" s="2" t="n">
+        <v>46089.35787035698</v>
+      </c>
+      <c r="I1407" s="2" t="n">
+        <v>46094.35787035698</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>7d49ce68-5ef4-4986-a6af-96d91692b951</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>8319.15</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1408" s="2" t="n">
+        <v>46088.35787036037</v>
+      </c>
+      <c r="I1408" s="2" t="n">
+        <v>46093.35787036037</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>c15ff324-436b-4f2d-8f6b-5f3f9986a0e7</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>8733.540000000001</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1409" s="2" t="n">
+        <v>46073.35787036354</v>
+      </c>
+      <c r="I1409" s="2" t="n">
+        <v>46078.35787036354</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>f49e7147-f99e-41ec-b4fb-f831915d9808</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>3351.08</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1410" s="2" t="n">
+        <v>46073.35787036682</v>
+      </c>
+      <c r="I1410" s="2" t="n">
+        <v>46078.35787036682</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>92ca576c-ffe6-4381-b759-c6121480811f</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>3418.87</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1411" s="2" t="n">
+        <v>46087.35787036993</v>
+      </c>
+      <c r="I1411" s="2" t="n">
+        <v>46092.35787036993</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>1fd0156d-2bea-4bbc-808c-1182cb60a55a</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>9421.25</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1412" s="2" t="n">
+        <v>46075.35787037356</v>
+      </c>
+      <c r="I1412" s="2" t="n">
+        <v>46080.35787037356</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>c632a8d6-3b22-4dce-b0b5-7306627f5148</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>9306.52</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1413" s="2" t="n">
+        <v>46083.3578703767</v>
+      </c>
+      <c r="I1413" s="2" t="n">
+        <v>46088.3578703767</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>c0dd2dfd-3ea2-4b9a-9783-bf0889f8bff1</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>7818.5</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1414" s="2" t="n">
+        <v>46073.35787037977</v>
+      </c>
+      <c r="I1414" s="2" t="n">
+        <v>46078.35787037977</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>b03112af-9a3b-459f-b875-2ecc7d9fba8c</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>9119.27</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1415" s="2" t="n">
+        <v>46085.35787038316</v>
+      </c>
+      <c r="I1415" s="2" t="n">
+        <v>46090.35787038316</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>8dcd002e-a0e7-4018-b0de-e4c4fd212841</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>9944.879999999999</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1416" s="2" t="n">
+        <v>46074.35787038643</v>
+      </c>
+      <c r="I1416" s="2" t="n">
+        <v>46079.35787038643</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>bffd4a96-12ad-4f6b-8b6a-0ca105fed16a</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>8138.21</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>91.58</v>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1417" s="2" t="n">
+        <v>46068.35787038977</v>
+      </c>
+      <c r="I1417" s="2" t="n">
+        <v>46073.35787038977</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>3af35cbb-553a-4847-b55a-cd2904c63077</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>8736.950000000001</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1418" s="2" t="n">
+        <v>46083.35787039284</v>
+      </c>
+      <c r="I1418" s="2" t="n">
+        <v>46088.35787039284</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>15022968-461a-44bb-b54b-c299deaf6bfc</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>1322.63</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1419" s="2" t="n">
+        <v>46060.35787039605</v>
+      </c>
+      <c r="I1419" s="2" t="n">
+        <v>46065.35787039605</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>09bedb2b-2ea0-4eb3-af78-bbc3c28ade61</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>5519.28</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>95.69</v>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1420" s="2" t="n">
+        <v>46067.35787039919</v>
+      </c>
+      <c r="I1420" s="2" t="n">
+        <v>46072.35787039919</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>11dffe95-811d-4e2e-9fd8-be9946cb68f8</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>7227.46</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>85.33</v>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1421" s="2" t="n">
+        <v>46063.35787040242</v>
+      </c>
+      <c r="I1421" s="2" t="n">
+        <v>46068.35787040242</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>234b7614-2114-4453-9ace-dbc32b4cb825</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>9632.24</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1422" s="2" t="n">
+        <v>46071.35787040542</v>
+      </c>
+      <c r="I1422" s="2" t="n">
+        <v>46076.35787040542</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>fdb0626c-e24c-4cf5-bdc1-a8d380425e08</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>7289.65</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1423" s="2" t="n">
+        <v>46073.35787040873</v>
+      </c>
+      <c r="I1423" s="2" t="n">
+        <v>46078.35787040873</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>f2ed00f5-36cb-478f-99be-63cead244709</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>2853.17</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1424" s="2" t="n">
+        <v>46063.35787041192</v>
+      </c>
+      <c r="I1424" s="2" t="n">
+        <v>46068.35787041192</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>d78dba12-9afe-48e4-9c3f-55269b2dc908</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>7894.95</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1425" s="2" t="n">
+        <v>46073.35787041514</v>
+      </c>
+      <c r="I1425" s="2" t="n">
+        <v>46078.35787041514</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>edc89045-64eb-47e4-b5e3-41dbe705b88d</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>8173.04</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>85.59</v>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1426" s="2" t="n">
+        <v>46080.35787041856</v>
+      </c>
+      <c r="I1426" s="2" t="n">
+        <v>46085.35787041856</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>13614c8b-a55f-44db-9bdb-f1ff61e76013</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>9437.370000000001</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1427" s="2" t="n">
+        <v>46079.35787042179</v>
+      </c>
+      <c r="I1427" s="2" t="n">
+        <v>46084.35787042179</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>b882e698-7840-4ca0-b55d-395ac2b45bf6</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1428" t="n">
+        <v>6851.82</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1428" s="2" t="n">
+        <v>46074.35787042485</v>
+      </c>
+      <c r="I1428" s="2" t="n">
+        <v>46079.35787042485</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>7d9c9c31-fd3c-479d-8024-cc236370d0e0</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1429" t="n">
+        <v>8403.049999999999</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1429" s="2" t="n">
+        <v>46084.35787042801</v>
+      </c>
+      <c r="I1429" s="2" t="n">
+        <v>46089.35787042801</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>e8e78f87-cb95-4c3e-bab2-72eee3f5b485</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1430" t="n">
+        <v>9218.299999999999</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1430" s="2" t="n">
+        <v>46072.35787043128</v>
+      </c>
+      <c r="I1430" s="2" t="n">
+        <v>46077.35787043128</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>0e415e56-3c59-4ba8-8785-cdedc6768dd6</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1431" t="n">
+        <v>6093.69</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1431" s="2" t="n">
+        <v>46076.35787043439</v>
+      </c>
+      <c r="I1431" s="2" t="n">
+        <v>46081.35787043439</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>51882319-ae87-45eb-8db4-e713ebbee69d</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1432" t="n">
+        <v>3718.83</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1432" s="2" t="n">
+        <v>46083.3578704375</v>
+      </c>
+      <c r="I1432" s="2" t="n">
+        <v>46088.3578704375</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>a227ebea-f21b-4d04-a2b7-4ab954d1d161</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1433" t="n">
+        <v>1522.97</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1433" s="2" t="n">
+        <v>46062.35787044065</v>
+      </c>
+      <c r="I1433" s="2" t="n">
+        <v>46067.35787044065</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2ea7a0ee-0b88-45b1-8f6e-10bf837d4d01</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1434" t="n">
+        <v>6310.86</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1434" s="2" t="n">
+        <v>46073.35787044399</v>
+      </c>
+      <c r="I1434" s="2" t="n">
+        <v>46078.35787044399</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>47dacfa0-4728-457b-990a-d2ef6b408eff</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1435" t="n">
+        <v>9005.85</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1435" s="2" t="n">
+        <v>46085.35787044729</v>
+      </c>
+      <c r="I1435" s="2" t="n">
+        <v>46090.35787044729</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>f53b4355-9e88-4cfb-a4ab-73c5cfadee2a</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1436" t="n">
+        <v>6757.88</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1436" s="2" t="n">
+        <v>46082.35787045035</v>
+      </c>
+      <c r="I1436" s="2" t="n">
+        <v>46087.35787045035</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>cfcc4d79-0855-42f9-a818-e9e9b139df07</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1437" t="n">
+        <v>4481.87</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1437" s="2" t="n">
+        <v>46061.3578704536</v>
+      </c>
+      <c r="I1437" s="2" t="n">
+        <v>46066.3578704536</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>83c896ed-1bc6-43fc-953b-c2ed8653c403</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1438" t="n">
+        <v>7365.76</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1438" s="2" t="n">
+        <v>46082.35787045665</v>
+      </c>
+      <c r="I1438" s="2" t="n">
+        <v>46087.35787045665</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>fe6eaa60-4df6-4912-8deb-c8d13c6186d7</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1439" t="n">
+        <v>3055.83</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1439" s="2" t="n">
+        <v>46074.35787045973</v>
+      </c>
+      <c r="I1439" s="2" t="n">
+        <v>46079.35787045973</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>99751164-e488-40f3-9872-54ccdf062bef</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1440" t="n">
+        <v>7278.1</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1440" s="2" t="n">
+        <v>46068.35787046278</v>
+      </c>
+      <c r="I1440" s="2" t="n">
+        <v>46073.35787046278</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>a9103f53-c513-45e3-a226-ab4e3265da6d</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1441" t="n">
+        <v>3691.92</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1441" s="2" t="n">
+        <v>46082.35787046605</v>
+      </c>
+      <c r="I1441" s="2" t="n">
+        <v>46087.35787046605</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>41fab8da-6513-4c74-8f8b-d27c5ef456d5</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1442" t="n">
+        <v>7591.1</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1442" s="2" t="n">
+        <v>46068.3578704692</v>
+      </c>
+      <c r="I1442" s="2" t="n">
+        <v>46073.3578704692</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>de57da4b-992c-4fb2-a357-ba21928762a4</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1443" t="n">
+        <v>2521.09</v>
+      </c>
+      <c r="D1443" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1443" s="2" t="n">
+        <v>46078.35787047241</v>
+      </c>
+      <c r="I1443" s="2" t="n">
+        <v>46083.35787047241</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>cdf7124e-bcf9-4481-818e-c51d0ee94887</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1444" t="n">
+        <v>9106.73</v>
+      </c>
+      <c r="D1444" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1444" s="2" t="n">
+        <v>46080.35787047545</v>
+      </c>
+      <c r="I1444" s="2" t="n">
+        <v>46085.35787047545</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>ffa5af68-410a-4ab4-8502-d401c1df3fee</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1445" t="n">
+        <v>4280.02</v>
+      </c>
+      <c r="D1445" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1445" s="2" t="n">
+        <v>46081.35787047885</v>
+      </c>
+      <c r="I1445" s="2" t="n">
+        <v>46086.35787047885</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>30f111ce-8dff-4556-b7b9-13a8769da80b</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1446" t="n">
+        <v>5043.28</v>
+      </c>
+      <c r="D1446" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1446" s="2" t="n">
+        <v>46062.35787048196</v>
+      </c>
+      <c r="I1446" s="2" t="n">
+        <v>46067.35787048196</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>acb5eb49-7b5e-4cae-a741-c64cc062efb1</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1447" t="n">
+        <v>1136.38</v>
+      </c>
+      <c r="D1447" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1447" s="2" t="n">
+        <v>46086.35787048502</v>
+      </c>
+      <c r="I1447" s="2" t="n">
+        <v>46091.35787048502</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>e2d13110-c4bb-41fb-bcac-078759600775</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1448" t="n">
+        <v>8961.219999999999</v>
+      </c>
+      <c r="D1448" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1448" s="2" t="n">
+        <v>46066.35787048821</v>
+      </c>
+      <c r="I1448" s="2" t="n">
+        <v>46071.35787048821</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>0ce82719-aaeb-49e8-89b3-dc1e39078a56</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1449" t="n">
+        <v>6716.06</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1449" s="2" t="n">
+        <v>46083.35787049133</v>
+      </c>
+      <c r="I1449" s="2" t="n">
+        <v>46088.35787049133</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>1976c0dc-3963-4c80-9ae1-f1e0f5f188c8</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1450" t="n">
+        <v>6736.88</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1450" s="2" t="n">
+        <v>46062.35787049436</v>
+      </c>
+      <c r="I1450" s="2" t="n">
+        <v>46067.35787049436</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>ba12dd4b-3f38-404f-9d51-6febaa1de92f</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1451" t="n">
+        <v>6731.04</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1451" s="2" t="n">
+        <v>46068.3578704974</v>
+      </c>
+      <c r="I1451" s="2" t="n">
+        <v>46073.3578704974</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1451"/>
+  <dimension ref="A1:I1501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55112,10 +55112,10 @@
         </is>
       </c>
       <c r="H1402" s="2" t="n">
-        <v>46076.35787033964</v>
+        <v>46076.35787033565</v>
       </c>
       <c r="I1402" s="2" t="n">
-        <v>46081.35787033964</v>
+        <v>46081.35787033565</v>
       </c>
     </row>
     <row r="1403">
@@ -55151,10 +55151,10 @@
         </is>
       </c>
       <c r="H1403" s="2" t="n">
-        <v>46073.35787034393</v>
+        <v>46073.35787034722</v>
       </c>
       <c r="I1403" s="2" t="n">
-        <v>46078.35787034393</v>
+        <v>46078.35787034722</v>
       </c>
     </row>
     <row r="1404">
@@ -55190,10 +55190,10 @@
         </is>
       </c>
       <c r="H1404" s="2" t="n">
-        <v>46086.35787034714</v>
+        <v>46086.35787034722</v>
       </c>
       <c r="I1404" s="2" t="n">
-        <v>46091.35787034714</v>
+        <v>46091.35787034722</v>
       </c>
     </row>
     <row r="1405">
@@ -55229,10 +55229,10 @@
         </is>
       </c>
       <c r="H1405" s="2" t="n">
-        <v>46086.35787035071</v>
+        <v>46086.35787034722</v>
       </c>
       <c r="I1405" s="2" t="n">
-        <v>46091.35787035071</v>
+        <v>46091.35787034722</v>
       </c>
     </row>
     <row r="1406">
@@ -55268,10 +55268,10 @@
         </is>
       </c>
       <c r="H1406" s="2" t="n">
-        <v>46073.35787035383</v>
+        <v>46073.3578703588</v>
       </c>
       <c r="I1406" s="2" t="n">
-        <v>46078.35787035383</v>
+        <v>46078.3578703588</v>
       </c>
     </row>
     <row r="1407">
@@ -55307,10 +55307,10 @@
         </is>
       </c>
       <c r="H1407" s="2" t="n">
-        <v>46089.35787035698</v>
+        <v>46089.3578703588</v>
       </c>
       <c r="I1407" s="2" t="n">
-        <v>46094.35787035698</v>
+        <v>46094.3578703588</v>
       </c>
     </row>
     <row r="1408">
@@ -55346,10 +55346,10 @@
         </is>
       </c>
       <c r="H1408" s="2" t="n">
-        <v>46088.35787036037</v>
+        <v>46088.3578703588</v>
       </c>
       <c r="I1408" s="2" t="n">
-        <v>46093.35787036037</v>
+        <v>46093.3578703588</v>
       </c>
     </row>
     <row r="1409">
@@ -55385,10 +55385,10 @@
         </is>
       </c>
       <c r="H1409" s="2" t="n">
-        <v>46073.35787036354</v>
+        <v>46073.3578703588</v>
       </c>
       <c r="I1409" s="2" t="n">
-        <v>46078.35787036354</v>
+        <v>46078.3578703588</v>
       </c>
     </row>
     <row r="1410">
@@ -55424,10 +55424,10 @@
         </is>
       </c>
       <c r="H1410" s="2" t="n">
-        <v>46073.35787036682</v>
+        <v>46073.35787037037</v>
       </c>
       <c r="I1410" s="2" t="n">
-        <v>46078.35787036682</v>
+        <v>46078.35787037037</v>
       </c>
     </row>
     <row r="1411">
@@ -55463,10 +55463,10 @@
         </is>
       </c>
       <c r="H1411" s="2" t="n">
-        <v>46087.35787036993</v>
+        <v>46087.35787037037</v>
       </c>
       <c r="I1411" s="2" t="n">
-        <v>46092.35787036993</v>
+        <v>46092.35787037037</v>
       </c>
     </row>
     <row r="1412">
@@ -55502,10 +55502,10 @@
         </is>
       </c>
       <c r="H1412" s="2" t="n">
-        <v>46075.35787037356</v>
+        <v>46075.35787037037</v>
       </c>
       <c r="I1412" s="2" t="n">
-        <v>46080.35787037356</v>
+        <v>46080.35787037037</v>
       </c>
     </row>
     <row r="1413">
@@ -55541,10 +55541,10 @@
         </is>
       </c>
       <c r="H1413" s="2" t="n">
-        <v>46083.3578703767</v>
+        <v>46083.35787038194</v>
       </c>
       <c r="I1413" s="2" t="n">
-        <v>46088.3578703767</v>
+        <v>46088.35787038194</v>
       </c>
     </row>
     <row r="1414">
@@ -55580,10 +55580,10 @@
         </is>
       </c>
       <c r="H1414" s="2" t="n">
-        <v>46073.35787037977</v>
+        <v>46073.35787038194</v>
       </c>
       <c r="I1414" s="2" t="n">
-        <v>46078.35787037977</v>
+        <v>46078.35787038194</v>
       </c>
     </row>
     <row r="1415">
@@ -55619,10 +55619,10 @@
         </is>
       </c>
       <c r="H1415" s="2" t="n">
-        <v>46085.35787038316</v>
+        <v>46085.35787038194</v>
       </c>
       <c r="I1415" s="2" t="n">
-        <v>46090.35787038316</v>
+        <v>46090.35787038194</v>
       </c>
     </row>
     <row r="1416">
@@ -55658,10 +55658,10 @@
         </is>
       </c>
       <c r="H1416" s="2" t="n">
-        <v>46074.35787038643</v>
+        <v>46074.35787038194</v>
       </c>
       <c r="I1416" s="2" t="n">
-        <v>46079.35787038643</v>
+        <v>46079.35787038194</v>
       </c>
     </row>
     <row r="1417">
@@ -55697,10 +55697,10 @@
         </is>
       </c>
       <c r="H1417" s="2" t="n">
-        <v>46068.35787038977</v>
+        <v>46068.35787039352</v>
       </c>
       <c r="I1417" s="2" t="n">
-        <v>46073.35787038977</v>
+        <v>46073.35787039352</v>
       </c>
     </row>
     <row r="1418">
@@ -55736,10 +55736,10 @@
         </is>
       </c>
       <c r="H1418" s="2" t="n">
-        <v>46083.35787039284</v>
+        <v>46083.35787039352</v>
       </c>
       <c r="I1418" s="2" t="n">
-        <v>46088.35787039284</v>
+        <v>46088.35787039352</v>
       </c>
     </row>
     <row r="1419">
@@ -55775,10 +55775,10 @@
         </is>
       </c>
       <c r="H1419" s="2" t="n">
-        <v>46060.35787039605</v>
+        <v>46060.35787039352</v>
       </c>
       <c r="I1419" s="2" t="n">
-        <v>46065.35787039605</v>
+        <v>46065.35787039352</v>
       </c>
     </row>
     <row r="1420">
@@ -55814,10 +55814,10 @@
         </is>
       </c>
       <c r="H1420" s="2" t="n">
-        <v>46067.35787039919</v>
+        <v>46067.35787039352</v>
       </c>
       <c r="I1420" s="2" t="n">
-        <v>46072.35787039919</v>
+        <v>46072.35787039352</v>
       </c>
     </row>
     <row r="1421">
@@ -55853,10 +55853,10 @@
         </is>
       </c>
       <c r="H1421" s="2" t="n">
-        <v>46063.35787040242</v>
+        <v>46063.3578704051</v>
       </c>
       <c r="I1421" s="2" t="n">
-        <v>46068.35787040242</v>
+        <v>46068.3578704051</v>
       </c>
     </row>
     <row r="1422">
@@ -55892,10 +55892,10 @@
         </is>
       </c>
       <c r="H1422" s="2" t="n">
-        <v>46071.35787040542</v>
+        <v>46071.3578704051</v>
       </c>
       <c r="I1422" s="2" t="n">
-        <v>46076.35787040542</v>
+        <v>46076.3578704051</v>
       </c>
     </row>
     <row r="1423">
@@ -55931,10 +55931,10 @@
         </is>
       </c>
       <c r="H1423" s="2" t="n">
-        <v>46073.35787040873</v>
+        <v>46073.3578704051</v>
       </c>
       <c r="I1423" s="2" t="n">
-        <v>46078.35787040873</v>
+        <v>46078.3578704051</v>
       </c>
     </row>
     <row r="1424">
@@ -55970,10 +55970,10 @@
         </is>
       </c>
       <c r="H1424" s="2" t="n">
-        <v>46063.35787041192</v>
+        <v>46063.35787041666</v>
       </c>
       <c r="I1424" s="2" t="n">
-        <v>46068.35787041192</v>
+        <v>46068.35787041666</v>
       </c>
     </row>
     <row r="1425">
@@ -56009,10 +56009,10 @@
         </is>
       </c>
       <c r="H1425" s="2" t="n">
-        <v>46073.35787041514</v>
+        <v>46073.35787041666</v>
       </c>
       <c r="I1425" s="2" t="n">
-        <v>46078.35787041514</v>
+        <v>46078.35787041666</v>
       </c>
     </row>
     <row r="1426">
@@ -56048,10 +56048,10 @@
         </is>
       </c>
       <c r="H1426" s="2" t="n">
-        <v>46080.35787041856</v>
+        <v>46080.35787041666</v>
       </c>
       <c r="I1426" s="2" t="n">
-        <v>46085.35787041856</v>
+        <v>46085.35787041666</v>
       </c>
     </row>
     <row r="1427">
@@ -56087,10 +56087,10 @@
         </is>
       </c>
       <c r="H1427" s="2" t="n">
-        <v>46079.35787042179</v>
+        <v>46079.35787041666</v>
       </c>
       <c r="I1427" s="2" t="n">
-        <v>46084.35787042179</v>
+        <v>46084.35787041666</v>
       </c>
     </row>
     <row r="1428">
@@ -56126,10 +56126,10 @@
         </is>
       </c>
       <c r="H1428" s="2" t="n">
-        <v>46074.35787042485</v>
+        <v>46074.35787042824</v>
       </c>
       <c r="I1428" s="2" t="n">
-        <v>46079.35787042485</v>
+        <v>46079.35787042824</v>
       </c>
     </row>
     <row r="1429">
@@ -56165,10 +56165,10 @@
         </is>
       </c>
       <c r="H1429" s="2" t="n">
-        <v>46084.35787042801</v>
+        <v>46084.35787042824</v>
       </c>
       <c r="I1429" s="2" t="n">
-        <v>46089.35787042801</v>
+        <v>46089.35787042824</v>
       </c>
     </row>
     <row r="1430">
@@ -56204,10 +56204,10 @@
         </is>
       </c>
       <c r="H1430" s="2" t="n">
-        <v>46072.35787043128</v>
+        <v>46072.35787042824</v>
       </c>
       <c r="I1430" s="2" t="n">
-        <v>46077.35787043128</v>
+        <v>46077.35787042824</v>
       </c>
     </row>
     <row r="1431">
@@ -56243,10 +56243,10 @@
         </is>
       </c>
       <c r="H1431" s="2" t="n">
-        <v>46076.35787043439</v>
+        <v>46076.35787043982</v>
       </c>
       <c r="I1431" s="2" t="n">
-        <v>46081.35787043439</v>
+        <v>46081.35787043982</v>
       </c>
     </row>
     <row r="1432">
@@ -56282,10 +56282,10 @@
         </is>
       </c>
       <c r="H1432" s="2" t="n">
-        <v>46083.3578704375</v>
+        <v>46083.35787043982</v>
       </c>
       <c r="I1432" s="2" t="n">
-        <v>46088.3578704375</v>
+        <v>46088.35787043982</v>
       </c>
     </row>
     <row r="1433">
@@ -56321,10 +56321,10 @@
         </is>
       </c>
       <c r="H1433" s="2" t="n">
-        <v>46062.35787044065</v>
+        <v>46062.35787043982</v>
       </c>
       <c r="I1433" s="2" t="n">
-        <v>46067.35787044065</v>
+        <v>46067.35787043982</v>
       </c>
     </row>
     <row r="1434">
@@ -56360,10 +56360,10 @@
         </is>
       </c>
       <c r="H1434" s="2" t="n">
-        <v>46073.35787044399</v>
+        <v>46073.35787043982</v>
       </c>
       <c r="I1434" s="2" t="n">
-        <v>46078.35787044399</v>
+        <v>46078.35787043982</v>
       </c>
     </row>
     <row r="1435">
@@ -56399,10 +56399,10 @@
         </is>
       </c>
       <c r="H1435" s="2" t="n">
-        <v>46085.35787044729</v>
+        <v>46085.35787045139</v>
       </c>
       <c r="I1435" s="2" t="n">
-        <v>46090.35787044729</v>
+        <v>46090.35787045139</v>
       </c>
     </row>
     <row r="1436">
@@ -56438,10 +56438,10 @@
         </is>
       </c>
       <c r="H1436" s="2" t="n">
-        <v>46082.35787045035</v>
+        <v>46082.35787045139</v>
       </c>
       <c r="I1436" s="2" t="n">
-        <v>46087.35787045035</v>
+        <v>46087.35787045139</v>
       </c>
     </row>
     <row r="1437">
@@ -56477,10 +56477,10 @@
         </is>
       </c>
       <c r="H1437" s="2" t="n">
-        <v>46061.3578704536</v>
+        <v>46061.35787045139</v>
       </c>
       <c r="I1437" s="2" t="n">
-        <v>46066.3578704536</v>
+        <v>46066.35787045139</v>
       </c>
     </row>
     <row r="1438">
@@ -56516,10 +56516,10 @@
         </is>
       </c>
       <c r="H1438" s="2" t="n">
-        <v>46082.35787045665</v>
+        <v>46082.35787045139</v>
       </c>
       <c r="I1438" s="2" t="n">
-        <v>46087.35787045665</v>
+        <v>46087.35787045139</v>
       </c>
     </row>
     <row r="1439">
@@ -56555,10 +56555,10 @@
         </is>
       </c>
       <c r="H1439" s="2" t="n">
-        <v>46074.35787045973</v>
+        <v>46074.35787046296</v>
       </c>
       <c r="I1439" s="2" t="n">
-        <v>46079.35787045973</v>
+        <v>46079.35787046296</v>
       </c>
     </row>
     <row r="1440">
@@ -56594,10 +56594,10 @@
         </is>
       </c>
       <c r="H1440" s="2" t="n">
-        <v>46068.35787046278</v>
+        <v>46068.35787046296</v>
       </c>
       <c r="I1440" s="2" t="n">
-        <v>46073.35787046278</v>
+        <v>46073.35787046296</v>
       </c>
     </row>
     <row r="1441">
@@ -56633,10 +56633,10 @@
         </is>
       </c>
       <c r="H1441" s="2" t="n">
-        <v>46082.35787046605</v>
+        <v>46082.35787046296</v>
       </c>
       <c r="I1441" s="2" t="n">
-        <v>46087.35787046605</v>
+        <v>46087.35787046296</v>
       </c>
     </row>
     <row r="1442">
@@ -56672,10 +56672,10 @@
         </is>
       </c>
       <c r="H1442" s="2" t="n">
-        <v>46068.3578704692</v>
+        <v>46068.35787047454</v>
       </c>
       <c r="I1442" s="2" t="n">
-        <v>46073.3578704692</v>
+        <v>46073.35787047454</v>
       </c>
     </row>
     <row r="1443">
@@ -56711,10 +56711,10 @@
         </is>
       </c>
       <c r="H1443" s="2" t="n">
-        <v>46078.35787047241</v>
+        <v>46078.35787047454</v>
       </c>
       <c r="I1443" s="2" t="n">
-        <v>46083.35787047241</v>
+        <v>46083.35787047454</v>
       </c>
     </row>
     <row r="1444">
@@ -56750,10 +56750,10 @@
         </is>
       </c>
       <c r="H1444" s="2" t="n">
-        <v>46080.35787047545</v>
+        <v>46080.35787047454</v>
       </c>
       <c r="I1444" s="2" t="n">
-        <v>46085.35787047545</v>
+        <v>46085.35787047454</v>
       </c>
     </row>
     <row r="1445">
@@ -56789,10 +56789,10 @@
         </is>
       </c>
       <c r="H1445" s="2" t="n">
-        <v>46081.35787047885</v>
+        <v>46081.35787047454</v>
       </c>
       <c r="I1445" s="2" t="n">
-        <v>46086.35787047885</v>
+        <v>46086.35787047454</v>
       </c>
     </row>
     <row r="1446">
@@ -56828,10 +56828,10 @@
         </is>
       </c>
       <c r="H1446" s="2" t="n">
-        <v>46062.35787048196</v>
+        <v>46062.35787048611</v>
       </c>
       <c r="I1446" s="2" t="n">
-        <v>46067.35787048196</v>
+        <v>46067.35787048611</v>
       </c>
     </row>
     <row r="1447">
@@ -56867,10 +56867,10 @@
         </is>
       </c>
       <c r="H1447" s="2" t="n">
-        <v>46086.35787048502</v>
+        <v>46086.35787048611</v>
       </c>
       <c r="I1447" s="2" t="n">
-        <v>46091.35787048502</v>
+        <v>46091.35787048611</v>
       </c>
     </row>
     <row r="1448">
@@ -56906,10 +56906,10 @@
         </is>
       </c>
       <c r="H1448" s="2" t="n">
-        <v>46066.35787048821</v>
+        <v>46066.35787048611</v>
       </c>
       <c r="I1448" s="2" t="n">
-        <v>46071.35787048821</v>
+        <v>46071.35787048611</v>
       </c>
     </row>
     <row r="1449">
@@ -56945,10 +56945,10 @@
         </is>
       </c>
       <c r="H1449" s="2" t="n">
-        <v>46083.35787049133</v>
+        <v>46083.35787048611</v>
       </c>
       <c r="I1449" s="2" t="n">
-        <v>46088.35787049133</v>
+        <v>46088.35787048611</v>
       </c>
     </row>
     <row r="1450">
@@ -56984,10 +56984,10 @@
         </is>
       </c>
       <c r="H1450" s="2" t="n">
-        <v>46062.35787049436</v>
+        <v>46062.35787049768</v>
       </c>
       <c r="I1450" s="2" t="n">
-        <v>46067.35787049436</v>
+        <v>46067.35787049768</v>
       </c>
     </row>
     <row r="1451">
@@ -57023,10 +57023,1960 @@
         </is>
       </c>
       <c r="H1451" s="2" t="n">
-        <v>46068.3578704974</v>
+        <v>46068.35787049768</v>
       </c>
       <c r="I1451" s="2" t="n">
-        <v>46073.3578704974</v>
+        <v>46073.35787049768</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>93a7dd36-c161-4c0b-899e-925c6aa3978d</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1452" t="n">
+        <v>2402.43</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1452" s="2" t="n">
+        <v>46079.40331800383</v>
+      </c>
+      <c r="I1452" s="2" t="n">
+        <v>46084.40331800383</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>6cef5e0a-eebb-4fc2-8f07-8993e3eaf566</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1453" t="n">
+        <v>8948.190000000001</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1453" s="2" t="n">
+        <v>46089.40331800817</v>
+      </c>
+      <c r="I1453" s="2" t="n">
+        <v>46094.40331800817</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>d0c08cf7-ce3d-4c80-ae6d-6e53d1efd26f</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1454" t="n">
+        <v>5008.21</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1454" s="2" t="n">
+        <v>46082.40331801179</v>
+      </c>
+      <c r="I1454" s="2" t="n">
+        <v>46087.40331801179</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>b7c770b6-07e3-4d03-8d78-48942e9e9f7a</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1455" t="n">
+        <v>6262.66</v>
+      </c>
+      <c r="D1455" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1455" s="2" t="n">
+        <v>46072.40331801493</v>
+      </c>
+      <c r="I1455" s="2" t="n">
+        <v>46077.40331801493</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>14e8f1c9-2069-4a38-970e-9d19d34d0c4e</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1456" t="n">
+        <v>4443.06</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1456" s="2" t="n">
+        <v>46085.40331801808</v>
+      </c>
+      <c r="I1456" s="2" t="n">
+        <v>46090.40331801808</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>1d99a719-8e52-4c22-a377-cd029face776</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1457" t="n">
+        <v>9082.9</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>88.79000000000001</v>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1457" s="2" t="n">
+        <v>46086.40331802178</v>
+      </c>
+      <c r="I1457" s="2" t="n">
+        <v>46091.40331802178</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>51777f26-2035-4552-8cb1-630a4c2c0abc</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1458" t="n">
+        <v>1156.51</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>97.87</v>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1458" s="2" t="n">
+        <v>46081.40331802499</v>
+      </c>
+      <c r="I1458" s="2" t="n">
+        <v>46086.40331802499</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>707d7704-d0a9-44c7-9be2-ded67341a1fb</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1459" t="n">
+        <v>5065.01</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1459" s="2" t="n">
+        <v>46070.40331802811</v>
+      </c>
+      <c r="I1459" s="2" t="n">
+        <v>46075.40331802811</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>b5722f70-9126-4a23-8dea-e47e792fc988</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1460" t="n">
+        <v>9220.24</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1460" s="2" t="n">
+        <v>46082.40331803136</v>
+      </c>
+      <c r="I1460" s="2" t="n">
+        <v>46087.40331803136</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>8e81bcf0-c5a6-4abf-b964-dd993289e4f2</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1461" t="n">
+        <v>6870.08</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>85.33</v>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1461" s="2" t="n">
+        <v>46068.40331803489</v>
+      </c>
+      <c r="I1461" s="2" t="n">
+        <v>46073.40331803489</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>b9721a7d-4ea7-4c5c-9064-41104bc17d22</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1462" t="n">
+        <v>5383.27</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1462" s="2" t="n">
+        <v>46069.40331803829</v>
+      </c>
+      <c r="I1462" s="2" t="n">
+        <v>46074.40331803829</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>4a84da00-71f7-46a1-9351-d2352b101a51</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1463" t="n">
+        <v>8707.370000000001</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1463" s="2" t="n">
+        <v>46066.40331804139</v>
+      </c>
+      <c r="I1463" s="2" t="n">
+        <v>46071.40331804139</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>06e26132-7517-437f-bbbf-d5ea907afb83</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1464" t="n">
+        <v>7623.48</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1464" s="2" t="n">
+        <v>46072.40331804464</v>
+      </c>
+      <c r="I1464" s="2" t="n">
+        <v>46077.40331804464</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>25abd816-b2a4-40a1-b8ae-c93b921d1530</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1465" t="n">
+        <v>6810.21</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1465" s="2" t="n">
+        <v>46074.40331804768</v>
+      </c>
+      <c r="I1465" s="2" t="n">
+        <v>46079.40331804768</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2c0cb1c6-f81a-4ab9-9e5d-e51688ca0855</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1466" t="n">
+        <v>1574.28</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1466" s="2" t="n">
+        <v>46075.40331805076</v>
+      </c>
+      <c r="I1466" s="2" t="n">
+        <v>46080.40331805076</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>a04b9c4f-2345-48ba-8ef9-e301a6e4c5d4</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1467" t="n">
+        <v>3541.18</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1467" s="2" t="n">
+        <v>46073.40331805387</v>
+      </c>
+      <c r="I1467" s="2" t="n">
+        <v>46078.40331805387</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>35c28588-998e-470a-b667-a3b5d40b79bc</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1468" t="n">
+        <v>8256.870000000001</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>88.73999999999999</v>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1468" s="2" t="n">
+        <v>46074.40331805713</v>
+      </c>
+      <c r="I1468" s="2" t="n">
+        <v>46079.40331805713</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>7bc7f9f4-dd81-49da-8f21-edafc1e67248</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1469" t="n">
+        <v>4479.97</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1469" s="2" t="n">
+        <v>46086.40331806014</v>
+      </c>
+      <c r="I1469" s="2" t="n">
+        <v>46091.40331806014</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>3bcb3e2b-3fcf-475e-b9a3-7abe86678f59</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1470" t="n">
+        <v>9982.35</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1470" s="2" t="n">
+        <v>46060.40331806317</v>
+      </c>
+      <c r="I1470" s="2" t="n">
+        <v>46065.40331806317</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>eeff5a70-0003-4a71-8fc1-ddeee2675712</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1471" t="n">
+        <v>5788.95</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1471" s="2" t="n">
+        <v>46082.40331806643</v>
+      </c>
+      <c r="I1471" s="2" t="n">
+        <v>46087.40331806643</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>e2f063a2-b65d-4b41-b0c7-fc6f17fce8d5</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1472" t="n">
+        <v>4401.89</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>86</v>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1472" s="2" t="n">
+        <v>46062.40331806963</v>
+      </c>
+      <c r="I1472" s="2" t="n">
+        <v>46067.40331806963</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>64563d3d-0a1d-4eb5-8a3e-36f31c8da6cb</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1473" t="n">
+        <v>1841.22</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>98.23</v>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1473" s="2" t="n">
+        <v>46075.40331807279</v>
+      </c>
+      <c r="I1473" s="2" t="n">
+        <v>46080.40331807279</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>870d4b67-fe2d-45d5-8b63-450adbeb9182</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1474" t="n">
+        <v>5553.22</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>96</v>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1474" s="2" t="n">
+        <v>46077.40331807599</v>
+      </c>
+      <c r="I1474" s="2" t="n">
+        <v>46082.40331807599</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>bbd79780-2130-4f69-8370-2f02731f8084</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1475" t="n">
+        <v>9262.360000000001</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1475" s="2" t="n">
+        <v>46080.4033180804</v>
+      </c>
+      <c r="I1475" s="2" t="n">
+        <v>46085.4033180804</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>b0f04673-935e-4e30-99ec-1b107bc70620</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1476" t="n">
+        <v>8303.440000000001</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1476" s="2" t="n">
+        <v>46086.40331808354</v>
+      </c>
+      <c r="I1476" s="2" t="n">
+        <v>46091.40331808354</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>ec14a453-5157-4578-9df0-17e1bbc0429b</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1477" t="n">
+        <v>8742.24</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1477" s="2" t="n">
+        <v>46075.40331808675</v>
+      </c>
+      <c r="I1477" s="2" t="n">
+        <v>46080.40331808675</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>c0b1ec6d-0ec7-481f-930d-b337447f3943</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1478" t="n">
+        <v>8114.68</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1478" s="2" t="n">
+        <v>46066.40331808994</v>
+      </c>
+      <c r="I1478" s="2" t="n">
+        <v>46071.40331808994</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>ef74ad1b-a9ef-4bb5-8aea-3aa573751659</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1479" t="n">
+        <v>9054.870000000001</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1479" s="2" t="n">
+        <v>46066.40331809341</v>
+      </c>
+      <c r="I1479" s="2" t="n">
+        <v>46071.40331809341</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>561d427b-61e5-4002-9905-ffb75c1988b9</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1480" t="n">
+        <v>9430.18</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1480" s="2" t="n">
+        <v>46061.40331809647</v>
+      </c>
+      <c r="I1480" s="2" t="n">
+        <v>46066.40331809647</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>bac436f0-1e04-4674-a401-1935af996487</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1481" t="n">
+        <v>5791.73</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>97.84</v>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1481" s="2" t="n">
+        <v>46072.40331809957</v>
+      </c>
+      <c r="I1481" s="2" t="n">
+        <v>46077.40331809957</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>b7574b04-197e-4a71-9339-47ba35108319</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1482" t="n">
+        <v>9820.01</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1482" s="2" t="n">
+        <v>46062.40331810274</v>
+      </c>
+      <c r="I1482" s="2" t="n">
+        <v>46067.40331810274</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>f44ed429-f41f-4e20-b349-351fad8f9293</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1483" t="n">
+        <v>2032.53</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1483" s="2" t="n">
+        <v>46078.40331810607</v>
+      </c>
+      <c r="I1483" s="2" t="n">
+        <v>46083.40331810607</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>73b57c8d-e51b-413f-881c-71a7dffb4179</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1484" t="n">
+        <v>7276.31</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>92.98</v>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1484" s="2" t="n">
+        <v>46071.40331810926</v>
+      </c>
+      <c r="I1484" s="2" t="n">
+        <v>46076.40331810926</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>3c99ba9e-f5a7-4ad8-b7c2-b317cdb9dd5f</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1485" t="n">
+        <v>7277.21</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>97.56999999999999</v>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1485" s="2" t="n">
+        <v>46072.40331811263</v>
+      </c>
+      <c r="I1485" s="2" t="n">
+        <v>46077.40331811263</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>05f239c7-29e5-41b4-9e85-192ea8b904d2</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1486" t="n">
+        <v>8480.59</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1486" s="2" t="n">
+        <v>46079.40331811584</v>
+      </c>
+      <c r="I1486" s="2" t="n">
+        <v>46084.40331811584</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>29df2464-ee11-4264-a02a-add31b6b7684</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1487" t="n">
+        <v>5659.04</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1487" s="2" t="n">
+        <v>46069.403318119</v>
+      </c>
+      <c r="I1487" s="2" t="n">
+        <v>46074.403318119</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>cde54da0-c63c-4291-a137-0de6b67688c5</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1488" t="n">
+        <v>5237.9</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1488" s="2" t="n">
+        <v>46066.40331812219</v>
+      </c>
+      <c r="I1488" s="2" t="n">
+        <v>46071.40331812219</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>5d71e634-193c-47be-b8b6-1c7e03146d0b</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1489" t="n">
+        <v>5188.52</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1489" s="2" t="n">
+        <v>46086.40331812551</v>
+      </c>
+      <c r="I1489" s="2" t="n">
+        <v>46091.40331812551</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>e7463096-b291-459a-bfa4-d8cea719ea12</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1490" t="n">
+        <v>8412.75</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>85.66</v>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1490" s="2" t="n">
+        <v>46074.40331812856</v>
+      </c>
+      <c r="I1490" s="2" t="n">
+        <v>46079.40331812856</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>30a4ff7d-c883-42fe-bb8d-5b5e5da4cff2</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1491" t="n">
+        <v>3575.41</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1491" s="2" t="n">
+        <v>46076.40331813162</v>
+      </c>
+      <c r="I1491" s="2" t="n">
+        <v>46081.40331813162</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>7ac6eeca-058f-46a6-b1ec-40ef22dc16de</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1492" t="n">
+        <v>3046.51</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1492" s="2" t="n">
+        <v>46069.40331813478</v>
+      </c>
+      <c r="I1492" s="2" t="n">
+        <v>46074.40331813478</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>c10197a7-2631-4208-ad01-fa12f8608570</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1493" t="n">
+        <v>9943.040000000001</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1493" s="2" t="n">
+        <v>46076.40331813797</v>
+      </c>
+      <c r="I1493" s="2" t="n">
+        <v>46081.40331813797</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>1d646589-8be6-4f5e-b24b-34b5f60ae183</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1494" t="n">
+        <v>3095.58</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1494" s="2" t="n">
+        <v>46072.4033181411</v>
+      </c>
+      <c r="I1494" s="2" t="n">
+        <v>46077.4033181411</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>1c8d9e5b-ab8a-4920-9338-cbc14d94ff67</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1495" t="n">
+        <v>5200.86</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>98.31999999999999</v>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1495" s="2" t="n">
+        <v>46071.40331814413</v>
+      </c>
+      <c r="I1495" s="2" t="n">
+        <v>46076.40331814413</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>7ae4f17e-f70a-498d-b970-245323816177</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1496" t="n">
+        <v>8307.58</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1496" s="2" t="n">
+        <v>46076.40331814719</v>
+      </c>
+      <c r="I1496" s="2" t="n">
+        <v>46081.40331814719</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>88001572-2e2d-46e2-a534-c64b08db74b8</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1497" t="n">
+        <v>4851.56</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>90.33</v>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1497" s="2" t="n">
+        <v>46070.40331815042</v>
+      </c>
+      <c r="I1497" s="2" t="n">
+        <v>46075.40331815042</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>b24f18ce-35bb-43b9-85ba-a05efcb082c3</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1498" t="n">
+        <v>7914.6</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1498" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1498" s="2" t="n">
+        <v>46068.40331815345</v>
+      </c>
+      <c r="I1498" s="2" t="n">
+        <v>46073.40331815345</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>e0b1e092-25dc-4f82-aae2-20c94e21a487</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1499" t="n">
+        <v>4918.5</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1499" s="2" t="n">
+        <v>46082.40331815654</v>
+      </c>
+      <c r="I1499" s="2" t="n">
+        <v>46087.40331815654</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>41541b51-5d3a-441e-80c4-7bc5f6f2c5fc</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1500" t="n">
+        <v>1111.62</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1500" s="2" t="n">
+        <v>46078.40331815952</v>
+      </c>
+      <c r="I1500" s="2" t="n">
+        <v>46083.40331815952</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>f7db0db1-6ccb-4f9e-a82a-35354c6aac21</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1501" t="n">
+        <v>3665.2</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1501" s="2" t="n">
+        <v>46069.40331816285</v>
+      </c>
+      <c r="I1501" s="2" t="n">
+        <v>46074.40331816285</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1501"/>
+  <dimension ref="A1:I1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57062,10 +57062,10 @@
         </is>
       </c>
       <c r="H1452" s="2" t="n">
-        <v>46079.40331800383</v>
+        <v>46079.40331800926</v>
       </c>
       <c r="I1452" s="2" t="n">
-        <v>46084.40331800383</v>
+        <v>46084.40331800926</v>
       </c>
     </row>
     <row r="1453">
@@ -57101,10 +57101,10 @@
         </is>
       </c>
       <c r="H1453" s="2" t="n">
-        <v>46089.40331800817</v>
+        <v>46089.40331800926</v>
       </c>
       <c r="I1453" s="2" t="n">
-        <v>46094.40331800817</v>
+        <v>46094.40331800926</v>
       </c>
     </row>
     <row r="1454">
@@ -57140,10 +57140,10 @@
         </is>
       </c>
       <c r="H1454" s="2" t="n">
-        <v>46082.40331801179</v>
+        <v>46082.40331800926</v>
       </c>
       <c r="I1454" s="2" t="n">
-        <v>46087.40331801179</v>
+        <v>46087.40331800926</v>
       </c>
     </row>
     <row r="1455">
@@ -57179,10 +57179,10 @@
         </is>
       </c>
       <c r="H1455" s="2" t="n">
-        <v>46072.40331801493</v>
+        <v>46072.40331800926</v>
       </c>
       <c r="I1455" s="2" t="n">
-        <v>46077.40331801493</v>
+        <v>46077.40331800926</v>
       </c>
     </row>
     <row r="1456">
@@ -57218,10 +57218,10 @@
         </is>
       </c>
       <c r="H1456" s="2" t="n">
-        <v>46085.40331801808</v>
+        <v>46085.40331802084</v>
       </c>
       <c r="I1456" s="2" t="n">
-        <v>46090.40331801808</v>
+        <v>46090.40331802084</v>
       </c>
     </row>
     <row r="1457">
@@ -57257,10 +57257,10 @@
         </is>
       </c>
       <c r="H1457" s="2" t="n">
-        <v>46086.40331802178</v>
+        <v>46086.40331802084</v>
       </c>
       <c r="I1457" s="2" t="n">
-        <v>46091.40331802178</v>
+        <v>46091.40331802084</v>
       </c>
     </row>
     <row r="1458">
@@ -57296,10 +57296,10 @@
         </is>
       </c>
       <c r="H1458" s="2" t="n">
-        <v>46081.40331802499</v>
+        <v>46081.40331802084</v>
       </c>
       <c r="I1458" s="2" t="n">
-        <v>46086.40331802499</v>
+        <v>46086.40331802084</v>
       </c>
     </row>
     <row r="1459">
@@ -57335,10 +57335,10 @@
         </is>
       </c>
       <c r="H1459" s="2" t="n">
-        <v>46070.40331802811</v>
+        <v>46070.4033180324</v>
       </c>
       <c r="I1459" s="2" t="n">
-        <v>46075.40331802811</v>
+        <v>46075.4033180324</v>
       </c>
     </row>
     <row r="1460">
@@ -57374,10 +57374,10 @@
         </is>
       </c>
       <c r="H1460" s="2" t="n">
-        <v>46082.40331803136</v>
+        <v>46082.4033180324</v>
       </c>
       <c r="I1460" s="2" t="n">
-        <v>46087.40331803136</v>
+        <v>46087.4033180324</v>
       </c>
     </row>
     <row r="1461">
@@ -57413,10 +57413,10 @@
         </is>
       </c>
       <c r="H1461" s="2" t="n">
-        <v>46068.40331803489</v>
+        <v>46068.4033180324</v>
       </c>
       <c r="I1461" s="2" t="n">
-        <v>46073.40331803489</v>
+        <v>46073.4033180324</v>
       </c>
     </row>
     <row r="1462">
@@ -57452,10 +57452,10 @@
         </is>
       </c>
       <c r="H1462" s="2" t="n">
-        <v>46069.40331803829</v>
+        <v>46069.40331804398</v>
       </c>
       <c r="I1462" s="2" t="n">
-        <v>46074.40331803829</v>
+        <v>46074.40331804398</v>
       </c>
     </row>
     <row r="1463">
@@ -57491,10 +57491,10 @@
         </is>
       </c>
       <c r="H1463" s="2" t="n">
-        <v>46066.40331804139</v>
+        <v>46066.40331804398</v>
       </c>
       <c r="I1463" s="2" t="n">
-        <v>46071.40331804139</v>
+        <v>46071.40331804398</v>
       </c>
     </row>
     <row r="1464">
@@ -57530,10 +57530,10 @@
         </is>
       </c>
       <c r="H1464" s="2" t="n">
-        <v>46072.40331804464</v>
+        <v>46072.40331804398</v>
       </c>
       <c r="I1464" s="2" t="n">
-        <v>46077.40331804464</v>
+        <v>46077.40331804398</v>
       </c>
     </row>
     <row r="1465">
@@ -57569,10 +57569,10 @@
         </is>
       </c>
       <c r="H1465" s="2" t="n">
-        <v>46074.40331804768</v>
+        <v>46074.40331804398</v>
       </c>
       <c r="I1465" s="2" t="n">
-        <v>46079.40331804768</v>
+        <v>46079.40331804398</v>
       </c>
     </row>
     <row r="1466">
@@ -57608,10 +57608,10 @@
         </is>
       </c>
       <c r="H1466" s="2" t="n">
-        <v>46075.40331805076</v>
+        <v>46075.40331805556</v>
       </c>
       <c r="I1466" s="2" t="n">
-        <v>46080.40331805076</v>
+        <v>46080.40331805556</v>
       </c>
     </row>
     <row r="1467">
@@ -57647,10 +57647,10 @@
         </is>
       </c>
       <c r="H1467" s="2" t="n">
-        <v>46073.40331805387</v>
+        <v>46073.40331805556</v>
       </c>
       <c r="I1467" s="2" t="n">
-        <v>46078.40331805387</v>
+        <v>46078.40331805556</v>
       </c>
     </row>
     <row r="1468">
@@ -57686,10 +57686,10 @@
         </is>
       </c>
       <c r="H1468" s="2" t="n">
-        <v>46074.40331805713</v>
+        <v>46074.40331805556</v>
       </c>
       <c r="I1468" s="2" t="n">
-        <v>46079.40331805713</v>
+        <v>46079.40331805556</v>
       </c>
     </row>
     <row r="1469">
@@ -57725,10 +57725,10 @@
         </is>
       </c>
       <c r="H1469" s="2" t="n">
-        <v>46086.40331806014</v>
+        <v>46086.40331805556</v>
       </c>
       <c r="I1469" s="2" t="n">
-        <v>46091.40331806014</v>
+        <v>46091.40331805556</v>
       </c>
     </row>
     <row r="1470">
@@ -57764,10 +57764,10 @@
         </is>
       </c>
       <c r="H1470" s="2" t="n">
-        <v>46060.40331806317</v>
+        <v>46060.40331806713</v>
       </c>
       <c r="I1470" s="2" t="n">
-        <v>46065.40331806317</v>
+        <v>46065.40331806713</v>
       </c>
     </row>
     <row r="1471">
@@ -57803,10 +57803,10 @@
         </is>
       </c>
       <c r="H1471" s="2" t="n">
-        <v>46082.40331806643</v>
+        <v>46082.40331806713</v>
       </c>
       <c r="I1471" s="2" t="n">
-        <v>46087.40331806643</v>
+        <v>46087.40331806713</v>
       </c>
     </row>
     <row r="1472">
@@ -57842,10 +57842,10 @@
         </is>
       </c>
       <c r="H1472" s="2" t="n">
-        <v>46062.40331806963</v>
+        <v>46062.40331806713</v>
       </c>
       <c r="I1472" s="2" t="n">
-        <v>46067.40331806963</v>
+        <v>46067.40331806713</v>
       </c>
     </row>
     <row r="1473">
@@ -57881,10 +57881,10 @@
         </is>
       </c>
       <c r="H1473" s="2" t="n">
-        <v>46075.40331807279</v>
+        <v>46075.40331806713</v>
       </c>
       <c r="I1473" s="2" t="n">
-        <v>46080.40331807279</v>
+        <v>46080.40331806713</v>
       </c>
     </row>
     <row r="1474">
@@ -57920,10 +57920,10 @@
         </is>
       </c>
       <c r="H1474" s="2" t="n">
-        <v>46077.40331807599</v>
+        <v>46077.4033180787</v>
       </c>
       <c r="I1474" s="2" t="n">
-        <v>46082.40331807599</v>
+        <v>46082.4033180787</v>
       </c>
     </row>
     <row r="1475">
@@ -57959,10 +57959,10 @@
         </is>
       </c>
       <c r="H1475" s="2" t="n">
-        <v>46080.4033180804</v>
+        <v>46080.4033180787</v>
       </c>
       <c r="I1475" s="2" t="n">
-        <v>46085.4033180804</v>
+        <v>46085.4033180787</v>
       </c>
     </row>
     <row r="1476">
@@ -57998,10 +57998,10 @@
         </is>
       </c>
       <c r="H1476" s="2" t="n">
-        <v>46086.40331808354</v>
+        <v>46086.4033180787</v>
       </c>
       <c r="I1476" s="2" t="n">
-        <v>46091.40331808354</v>
+        <v>46091.4033180787</v>
       </c>
     </row>
     <row r="1477">
@@ -58037,10 +58037,10 @@
         </is>
       </c>
       <c r="H1477" s="2" t="n">
-        <v>46075.40331808675</v>
+        <v>46075.40331809028</v>
       </c>
       <c r="I1477" s="2" t="n">
-        <v>46080.40331808675</v>
+        <v>46080.40331809028</v>
       </c>
     </row>
     <row r="1478">
@@ -58076,10 +58076,10 @@
         </is>
       </c>
       <c r="H1478" s="2" t="n">
-        <v>46066.40331808994</v>
+        <v>46066.40331809028</v>
       </c>
       <c r="I1478" s="2" t="n">
-        <v>46071.40331808994</v>
+        <v>46071.40331809028</v>
       </c>
     </row>
     <row r="1479">
@@ -58115,10 +58115,10 @@
         </is>
       </c>
       <c r="H1479" s="2" t="n">
-        <v>46066.40331809341</v>
+        <v>46066.40331809028</v>
       </c>
       <c r="I1479" s="2" t="n">
-        <v>46071.40331809341</v>
+        <v>46071.40331809028</v>
       </c>
     </row>
     <row r="1480">
@@ -58154,10 +58154,10 @@
         </is>
       </c>
       <c r="H1480" s="2" t="n">
-        <v>46061.40331809647</v>
+        <v>46061.40331810185</v>
       </c>
       <c r="I1480" s="2" t="n">
-        <v>46066.40331809647</v>
+        <v>46066.40331810185</v>
       </c>
     </row>
     <row r="1481">
@@ -58193,10 +58193,10 @@
         </is>
       </c>
       <c r="H1481" s="2" t="n">
-        <v>46072.40331809957</v>
+        <v>46072.40331810185</v>
       </c>
       <c r="I1481" s="2" t="n">
-        <v>46077.40331809957</v>
+        <v>46077.40331810185</v>
       </c>
     </row>
     <row r="1482">
@@ -58232,10 +58232,10 @@
         </is>
       </c>
       <c r="H1482" s="2" t="n">
-        <v>46062.40331810274</v>
+        <v>46062.40331810185</v>
       </c>
       <c r="I1482" s="2" t="n">
-        <v>46067.40331810274</v>
+        <v>46067.40331810185</v>
       </c>
     </row>
     <row r="1483">
@@ -58271,10 +58271,10 @@
         </is>
       </c>
       <c r="H1483" s="2" t="n">
-        <v>46078.40331810607</v>
+        <v>46078.40331810185</v>
       </c>
       <c r="I1483" s="2" t="n">
-        <v>46083.40331810607</v>
+        <v>46083.40331810185</v>
       </c>
     </row>
     <row r="1484">
@@ -58310,10 +58310,10 @@
         </is>
       </c>
       <c r="H1484" s="2" t="n">
-        <v>46071.40331810926</v>
+        <v>46071.40331811343</v>
       </c>
       <c r="I1484" s="2" t="n">
-        <v>46076.40331810926</v>
+        <v>46076.40331811343</v>
       </c>
     </row>
     <row r="1485">
@@ -58349,10 +58349,10 @@
         </is>
       </c>
       <c r="H1485" s="2" t="n">
-        <v>46072.40331811263</v>
+        <v>46072.40331811343</v>
       </c>
       <c r="I1485" s="2" t="n">
-        <v>46077.40331811263</v>
+        <v>46077.40331811343</v>
       </c>
     </row>
     <row r="1486">
@@ -58388,10 +58388,10 @@
         </is>
       </c>
       <c r="H1486" s="2" t="n">
-        <v>46079.40331811584</v>
+        <v>46079.40331811343</v>
       </c>
       <c r="I1486" s="2" t="n">
-        <v>46084.40331811584</v>
+        <v>46084.40331811343</v>
       </c>
     </row>
     <row r="1487">
@@ -58427,10 +58427,10 @@
         </is>
       </c>
       <c r="H1487" s="2" t="n">
-        <v>46069.403318119</v>
+        <v>46069.40331811343</v>
       </c>
       <c r="I1487" s="2" t="n">
-        <v>46074.403318119</v>
+        <v>46074.40331811343</v>
       </c>
     </row>
     <row r="1488">
@@ -58466,10 +58466,10 @@
         </is>
       </c>
       <c r="H1488" s="2" t="n">
-        <v>46066.40331812219</v>
+        <v>46066.403318125</v>
       </c>
       <c r="I1488" s="2" t="n">
-        <v>46071.40331812219</v>
+        <v>46071.403318125</v>
       </c>
     </row>
     <row r="1489">
@@ -58505,10 +58505,10 @@
         </is>
       </c>
       <c r="H1489" s="2" t="n">
-        <v>46086.40331812551</v>
+        <v>46086.403318125</v>
       </c>
       <c r="I1489" s="2" t="n">
-        <v>46091.40331812551</v>
+        <v>46091.403318125</v>
       </c>
     </row>
     <row r="1490">
@@ -58544,10 +58544,10 @@
         </is>
       </c>
       <c r="H1490" s="2" t="n">
-        <v>46074.40331812856</v>
+        <v>46074.403318125</v>
       </c>
       <c r="I1490" s="2" t="n">
-        <v>46079.40331812856</v>
+        <v>46079.403318125</v>
       </c>
     </row>
     <row r="1491">
@@ -58583,10 +58583,10 @@
         </is>
       </c>
       <c r="H1491" s="2" t="n">
-        <v>46076.40331813162</v>
+        <v>46076.40331813657</v>
       </c>
       <c r="I1491" s="2" t="n">
-        <v>46081.40331813162</v>
+        <v>46081.40331813657</v>
       </c>
     </row>
     <row r="1492">
@@ -58622,10 +58622,10 @@
         </is>
       </c>
       <c r="H1492" s="2" t="n">
-        <v>46069.40331813478</v>
+        <v>46069.40331813657</v>
       </c>
       <c r="I1492" s="2" t="n">
-        <v>46074.40331813478</v>
+        <v>46074.40331813657</v>
       </c>
     </row>
     <row r="1493">
@@ -58661,10 +58661,10 @@
         </is>
       </c>
       <c r="H1493" s="2" t="n">
-        <v>46076.40331813797</v>
+        <v>46076.40331813657</v>
       </c>
       <c r="I1493" s="2" t="n">
-        <v>46081.40331813797</v>
+        <v>46081.40331813657</v>
       </c>
     </row>
     <row r="1494">
@@ -58700,10 +58700,10 @@
         </is>
       </c>
       <c r="H1494" s="2" t="n">
-        <v>46072.4033181411</v>
+        <v>46072.40331813657</v>
       </c>
       <c r="I1494" s="2" t="n">
-        <v>46077.4033181411</v>
+        <v>46077.40331813657</v>
       </c>
     </row>
     <row r="1495">
@@ -58739,10 +58739,10 @@
         </is>
       </c>
       <c r="H1495" s="2" t="n">
-        <v>46071.40331814413</v>
+        <v>46071.40331814815</v>
       </c>
       <c r="I1495" s="2" t="n">
-        <v>46076.40331814413</v>
+        <v>46076.40331814815</v>
       </c>
     </row>
     <row r="1496">
@@ -58778,10 +58778,10 @@
         </is>
       </c>
       <c r="H1496" s="2" t="n">
-        <v>46076.40331814719</v>
+        <v>46076.40331814815</v>
       </c>
       <c r="I1496" s="2" t="n">
-        <v>46081.40331814719</v>
+        <v>46081.40331814815</v>
       </c>
     </row>
     <row r="1497">
@@ -58817,10 +58817,10 @@
         </is>
       </c>
       <c r="H1497" s="2" t="n">
-        <v>46070.40331815042</v>
+        <v>46070.40331814815</v>
       </c>
       <c r="I1497" s="2" t="n">
-        <v>46075.40331815042</v>
+        <v>46075.40331814815</v>
       </c>
     </row>
     <row r="1498">
@@ -58856,10 +58856,10 @@
         </is>
       </c>
       <c r="H1498" s="2" t="n">
-        <v>46068.40331815345</v>
+        <v>46068.40331814815</v>
       </c>
       <c r="I1498" s="2" t="n">
-        <v>46073.40331815345</v>
+        <v>46073.40331814815</v>
       </c>
     </row>
     <row r="1499">
@@ -58895,10 +58895,10 @@
         </is>
       </c>
       <c r="H1499" s="2" t="n">
-        <v>46082.40331815654</v>
+        <v>46082.40331815972</v>
       </c>
       <c r="I1499" s="2" t="n">
-        <v>46087.40331815654</v>
+        <v>46087.40331815972</v>
       </c>
     </row>
     <row r="1500">
@@ -58934,10 +58934,10 @@
         </is>
       </c>
       <c r="H1500" s="2" t="n">
-        <v>46078.40331815952</v>
+        <v>46078.40331815972</v>
       </c>
       <c r="I1500" s="2" t="n">
-        <v>46083.40331815952</v>
+        <v>46083.40331815972</v>
       </c>
     </row>
     <row r="1501">
@@ -58973,10 +58973,1960 @@
         </is>
       </c>
       <c r="H1501" s="2" t="n">
-        <v>46069.40331816285</v>
+        <v>46069.40331815972</v>
       </c>
       <c r="I1501" s="2" t="n">
-        <v>46074.40331816285</v>
+        <v>46074.40331815972</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>43ead498-870f-416c-b396-890889c57ea0</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1502" t="n">
+        <v>8955.92</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1502" s="2" t="n">
+        <v>46071.44312581167</v>
+      </c>
+      <c r="I1502" s="2" t="n">
+        <v>46076.44312581167</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>7c5ebdec-d583-4838-8213-68859d666c6c</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1503" t="n">
+        <v>5269.78</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1503" s="2" t="n">
+        <v>46089.44312581584</v>
+      </c>
+      <c r="I1503" s="2" t="n">
+        <v>46094.44312581584</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>ac67a1e0-8f9d-4da3-ac13-3938417523d7</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1504" t="n">
+        <v>2961.34</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>98.29000000000001</v>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1504" s="2" t="n">
+        <v>46077.44312581902</v>
+      </c>
+      <c r="I1504" s="2" t="n">
+        <v>46082.44312581902</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>e97d69e4-2c88-46e7-8cde-8199f582f5b9</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1505" t="n">
+        <v>3043.18</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1505" s="2" t="n">
+        <v>46084.44312582257</v>
+      </c>
+      <c r="I1505" s="2" t="n">
+        <v>46089.44312582257</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>460ae794-5de5-43a2-9fb7-a5ddadf804a0</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1506" t="n">
+        <v>2034.83</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1506" s="2" t="n">
+        <v>46071.44312582564</v>
+      </c>
+      <c r="I1506" s="2" t="n">
+        <v>46076.44312582564</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>0d577491-be37-4c49-9002-72d0fefc6b2d</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1507" t="n">
+        <v>2369.22</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1507" s="2" t="n">
+        <v>46064.44312582895</v>
+      </c>
+      <c r="I1507" s="2" t="n">
+        <v>46069.44312582895</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>1b17354c-f320-46b2-923c-5a3e7a807718</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1508" t="n">
+        <v>7650.73</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1508" s="2" t="n">
+        <v>46076.4431258322</v>
+      </c>
+      <c r="I1508" s="2" t="n">
+        <v>46081.4431258322</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>404f2c56-b24b-4538-86d7-660edac1076e</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1509" t="n">
+        <v>9113.07</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>90.69</v>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1509" s="2" t="n">
+        <v>46082.4431258353</v>
+      </c>
+      <c r="I1509" s="2" t="n">
+        <v>46087.4431258353</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>fbca9172-dda7-4fe7-a1e9-f0da0239e89c</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1510" t="n">
+        <v>8853.440000000001</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>89.34</v>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1510" s="2" t="n">
+        <v>46073.44312583853</v>
+      </c>
+      <c r="I1510" s="2" t="n">
+        <v>46078.44312583853</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>d4379e26-250b-46f3-918b-e3e66820d055</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1511" t="n">
+        <v>6907.88</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1511" s="2" t="n">
+        <v>46073.44312584171</v>
+      </c>
+      <c r="I1511" s="2" t="n">
+        <v>46078.44312584171</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>af909e78-6d84-4e73-95c6-7816f8f19772</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1512" t="n">
+        <v>7660.9</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>88.72</v>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1512" s="2" t="n">
+        <v>46078.44312584502</v>
+      </c>
+      <c r="I1512" s="2" t="n">
+        <v>46083.44312584502</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>f81f159b-951d-4ade-bc7d-817395085946</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1513" t="n">
+        <v>8322.799999999999</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1513" s="2" t="n">
+        <v>46065.44312584821</v>
+      </c>
+      <c r="I1513" s="2" t="n">
+        <v>46070.44312584821</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>fa8dd032-10c7-420f-bc7e-cad5db014adb</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1514" t="n">
+        <v>9766.48</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1514" s="2" t="n">
+        <v>46080.44312585129</v>
+      </c>
+      <c r="I1514" s="2" t="n">
+        <v>46085.44312585129</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>be79ec6f-f616-41ae-9692-49ebc3f17f3d</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1515" t="n">
+        <v>8513.540000000001</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>96.83</v>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1515" s="2" t="n">
+        <v>46060.44312585449</v>
+      </c>
+      <c r="I1515" s="2" t="n">
+        <v>46065.44312585449</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>fe69e734-7888-4b9e-9932-8190010df45e</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1516" t="n">
+        <v>3740.57</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1516" s="2" t="n">
+        <v>46088.44312585783</v>
+      </c>
+      <c r="I1516" s="2" t="n">
+        <v>46093.44312585783</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>c22d9f4b-48e5-4569-9e5e-15f419b34d78</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1517" t="n">
+        <v>9568.950000000001</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1517" s="2" t="n">
+        <v>46064.44312586108</v>
+      </c>
+      <c r="I1517" s="2" t="n">
+        <v>46069.44312586108</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>b2b53b75-d7e6-44bb-9c62-02c3b74eb452</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1518" t="n">
+        <v>9115.09</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1518" s="2" t="n">
+        <v>46067.44312586416</v>
+      </c>
+      <c r="I1518" s="2" t="n">
+        <v>46072.44312586416</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>967cd44a-5048-4e88-9d54-8ef465483dcb</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1519" t="n">
+        <v>6009.69</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1519" s="2" t="n">
+        <v>46067.44312586734</v>
+      </c>
+      <c r="I1519" s="2" t="n">
+        <v>46072.44312586734</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>6530f826-58e2-490e-95fe-e9a2fb8b4d5a</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1520" t="n">
+        <v>3652.25</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>95.95999999999999</v>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1520" s="2" t="n">
+        <v>46064.44312587047</v>
+      </c>
+      <c r="I1520" s="2" t="n">
+        <v>46069.44312587047</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>69a3f584-36f2-43b2-89e0-4bf3e2c00ba9</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1521" t="n">
+        <v>8615.110000000001</v>
+      </c>
+      <c r="D1521" t="n">
+        <v>86.97</v>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1521" s="2" t="n">
+        <v>46066.44312587352</v>
+      </c>
+      <c r="I1521" s="2" t="n">
+        <v>46071.44312587352</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>1836e4ae-19a2-40ff-a833-e4ae189b10b7</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1522" t="n">
+        <v>2918.36</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1522" s="2" t="n">
+        <v>46089.44312587656</v>
+      </c>
+      <c r="I1522" s="2" t="n">
+        <v>46094.44312587656</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2a60688e-379f-4b5c-915a-54da616893c8</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1523" t="n">
+        <v>9970.9</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1523" s="2" t="n">
+        <v>46076.44312587981</v>
+      </c>
+      <c r="I1523" s="2" t="n">
+        <v>46081.44312587981</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>65c4a910-295a-4f61-9265-7d4137adabdf</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1524" t="n">
+        <v>1139.82</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1524" s="2" t="n">
+        <v>46071.44312588294</v>
+      </c>
+      <c r="I1524" s="2" t="n">
+        <v>46076.44312588294</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>f95a8bcf-3bf1-4449-bcef-894d85f72918</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1525" t="n">
+        <v>8678.940000000001</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1525" s="2" t="n">
+        <v>46068.44312588588</v>
+      </c>
+      <c r="I1525" s="2" t="n">
+        <v>46073.44312588588</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>903e0975-c5bb-4cbc-bd34-5958da4c5476</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1526" t="n">
+        <v>9071.17</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>90.52</v>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1526" s="2" t="n">
+        <v>46072.44312588905</v>
+      </c>
+      <c r="I1526" s="2" t="n">
+        <v>46077.44312588905</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>ad80ecb9-1bf4-4c82-8ed6-b1f9e101e211</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1527" t="n">
+        <v>3461.29</v>
+      </c>
+      <c r="D1527" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1527" s="2" t="n">
+        <v>46061.44312589245</v>
+      </c>
+      <c r="I1527" s="2" t="n">
+        <v>46066.44312589245</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>f0239146-558d-4c14-9514-6d11280b4e2a</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1528" t="n">
+        <v>6266.01</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1528" s="2" t="n">
+        <v>46079.4431258955</v>
+      </c>
+      <c r="I1528" s="2" t="n">
+        <v>46084.4431258955</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2ad03e7e-04c9-486c-9845-fe18c3002cf8</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1529" t="n">
+        <v>3485.38</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1529" s="2" t="n">
+        <v>46086.44312589856</v>
+      </c>
+      <c r="I1529" s="2" t="n">
+        <v>46091.44312589856</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>64e76db7-cbdb-4080-9529-edd682f22665</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1530" t="n">
+        <v>8802.309999999999</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1530" s="2" t="n">
+        <v>46061.44312590175</v>
+      </c>
+      <c r="I1530" s="2" t="n">
+        <v>46066.44312590175</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>5cbec4d9-11b0-49c3-85bd-78c356084d53</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1531" t="n">
+        <v>7965.13</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1531" s="2" t="n">
+        <v>46080.44312590487</v>
+      </c>
+      <c r="I1531" s="2" t="n">
+        <v>46085.44312590487</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>075238b2-a36b-474f-9705-e6766faac0d5</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1532" t="n">
+        <v>7182.82</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1532" s="2" t="n">
+        <v>46081.44312590811</v>
+      </c>
+      <c r="I1532" s="2" t="n">
+        <v>46086.44312590811</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>a9ea206b-caea-48a4-a271-b220636b24cb</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1533" t="n">
+        <v>9442.66</v>
+      </c>
+      <c r="D1533" t="n">
+        <v>96.70999999999999</v>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1533" s="2" t="n">
+        <v>46065.44312591136</v>
+      </c>
+      <c r="I1533" s="2" t="n">
+        <v>46070.44312591136</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>4805c05d-46f5-458b-b23a-e6b6f52ecf89</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1534" t="n">
+        <v>5079.42</v>
+      </c>
+      <c r="D1534" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1534" s="2" t="n">
+        <v>46082.44312591463</v>
+      </c>
+      <c r="I1534" s="2" t="n">
+        <v>46087.44312591463</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>9ea13220-e54c-4951-8e76-d130654c4c37</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1535" t="n">
+        <v>2325.49</v>
+      </c>
+      <c r="D1535" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1535" s="2" t="n">
+        <v>46082.4431259177</v>
+      </c>
+      <c r="I1535" s="2" t="n">
+        <v>46087.4431259177</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>c1886a20-3adb-4dcd-b1cd-11a253aefda1</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1536" t="n">
+        <v>4535.58</v>
+      </c>
+      <c r="D1536" t="n">
+        <v>93</v>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1536" s="2" t="n">
+        <v>46072.44312592084</v>
+      </c>
+      <c r="I1536" s="2" t="n">
+        <v>46077.44312592084</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>def9ea47-d57e-4c3f-b8f9-38acb7611352</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1537" t="n">
+        <v>7476.13</v>
+      </c>
+      <c r="D1537" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1537" s="2" t="n">
+        <v>46069.44312592409</v>
+      </c>
+      <c r="I1537" s="2" t="n">
+        <v>46074.44312592409</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>f6751b24-dd46-4249-bae6-abcf2526741a</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1538" t="n">
+        <v>1492.91</v>
+      </c>
+      <c r="D1538" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1538" s="2" t="n">
+        <v>46082.44312592728</v>
+      </c>
+      <c r="I1538" s="2" t="n">
+        <v>46087.44312592728</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>d24bc756-3716-44b0-aa85-b07557b579c5</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1539" t="n">
+        <v>1247.6</v>
+      </c>
+      <c r="D1539" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1539" s="2" t="n">
+        <v>46088.44312593054</v>
+      </c>
+      <c r="I1539" s="2" t="n">
+        <v>46093.44312593054</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>28612b0a-bc11-4198-aec4-ad60e16c15cd</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1540" t="n">
+        <v>4847.24</v>
+      </c>
+      <c r="D1540" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1540" s="2" t="n">
+        <v>46071.44312593353</v>
+      </c>
+      <c r="I1540" s="2" t="n">
+        <v>46076.44312593353</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>1d8d0756-c8d6-4287-82e8-ff4bb3ed804b</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1541" t="n">
+        <v>9385.34</v>
+      </c>
+      <c r="D1541" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1541" s="2" t="n">
+        <v>46087.44312593693</v>
+      </c>
+      <c r="I1541" s="2" t="n">
+        <v>46092.44312593693</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>388562b1-f2ec-45d3-9a5c-4d989d6a1681</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1542" t="n">
+        <v>5139.97</v>
+      </c>
+      <c r="D1542" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1542" s="2" t="n">
+        <v>46071.44312593998</v>
+      </c>
+      <c r="I1542" s="2" t="n">
+        <v>46076.44312593998</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>cb529afb-515f-4ace-b3de-bb143aed65c5</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1543" t="n">
+        <v>2908.81</v>
+      </c>
+      <c r="D1543" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1543" s="2" t="n">
+        <v>46080.44312594321</v>
+      </c>
+      <c r="I1543" s="2" t="n">
+        <v>46085.44312594321</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>6708345b-4eaf-4bc0-852d-27808640263e</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1544" t="n">
+        <v>4004.07</v>
+      </c>
+      <c r="D1544" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1544" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1544" s="2" t="n">
+        <v>46065.44312594632</v>
+      </c>
+      <c r="I1544" s="2" t="n">
+        <v>46070.44312594632</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>a4a799ab-ceab-44ed-88f2-61159292cede</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1545" t="n">
+        <v>9742.25</v>
+      </c>
+      <c r="D1545" t="n">
+        <v>87.73</v>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1545" s="2" t="n">
+        <v>46070.44312594966</v>
+      </c>
+      <c r="I1545" s="2" t="n">
+        <v>46075.44312594966</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>789a2e54-11f1-40ab-88d9-5de9af64a414</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1546" t="n">
+        <v>5837.64</v>
+      </c>
+      <c r="D1546" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1546" s="2" t="n">
+        <v>46076.44312595276</v>
+      </c>
+      <c r="I1546" s="2" t="n">
+        <v>46081.44312595276</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>0ad01bbe-0572-45f3-8f5e-9bc5640777b7</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1547" t="n">
+        <v>2976.37</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1547" s="2" t="n">
+        <v>46067.44312595594</v>
+      </c>
+      <c r="I1547" s="2" t="n">
+        <v>46072.44312595594</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>8c3dd099-3828-4305-96c3-3bbc3f06b2c0</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1548" t="n">
+        <v>3498.89</v>
+      </c>
+      <c r="D1548" t="n">
+        <v>95.95999999999999</v>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1548" s="2" t="n">
+        <v>46089.44312595913</v>
+      </c>
+      <c r="I1548" s="2" t="n">
+        <v>46094.44312595913</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>e21b025c-9608-45b0-8548-3fd14ae75f2a</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1549" t="n">
+        <v>2154.65</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1549" s="2" t="n">
+        <v>46074.44312596234</v>
+      </c>
+      <c r="I1549" s="2" t="n">
+        <v>46079.44312596234</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>043e59f6-65ab-4ca4-bf1a-cfa6f53d27e5</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1550" t="n">
+        <v>2937.39</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>85.31</v>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1550" s="2" t="n">
+        <v>46086.44312596553</v>
+      </c>
+      <c r="I1550" s="2" t="n">
+        <v>46091.44312596553</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>3522ebf8-6440-454d-85cc-59c762d79052</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1551" t="n">
+        <v>8754.290000000001</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1551" s="2" t="n">
+        <v>46076.44312596863</v>
+      </c>
+      <c r="I1551" s="2" t="n">
+        <v>46081.44312596863</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1551"/>
+  <dimension ref="A1:I1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59012,10 +59012,10 @@
         </is>
       </c>
       <c r="H1502" s="2" t="n">
-        <v>46071.44312581167</v>
+        <v>46071.44312581018</v>
       </c>
       <c r="I1502" s="2" t="n">
-        <v>46076.44312581167</v>
+        <v>46076.44312581018</v>
       </c>
     </row>
     <row r="1503">
@@ -59051,10 +59051,10 @@
         </is>
       </c>
       <c r="H1503" s="2" t="n">
-        <v>46089.44312581584</v>
+        <v>46089.44312581018</v>
       </c>
       <c r="I1503" s="2" t="n">
-        <v>46094.44312581584</v>
+        <v>46094.44312581018</v>
       </c>
     </row>
     <row r="1504">
@@ -59090,10 +59090,10 @@
         </is>
       </c>
       <c r="H1504" s="2" t="n">
-        <v>46077.44312581902</v>
+        <v>46077.44312582176</v>
       </c>
       <c r="I1504" s="2" t="n">
-        <v>46082.44312581902</v>
+        <v>46082.44312582176</v>
       </c>
     </row>
     <row r="1505">
@@ -59129,10 +59129,10 @@
         </is>
       </c>
       <c r="H1505" s="2" t="n">
-        <v>46084.44312582257</v>
+        <v>46084.44312582176</v>
       </c>
       <c r="I1505" s="2" t="n">
-        <v>46089.44312582257</v>
+        <v>46089.44312582176</v>
       </c>
     </row>
     <row r="1506">
@@ -59168,10 +59168,10 @@
         </is>
       </c>
       <c r="H1506" s="2" t="n">
-        <v>46071.44312582564</v>
+        <v>46071.44312582176</v>
       </c>
       <c r="I1506" s="2" t="n">
-        <v>46076.44312582564</v>
+        <v>46076.44312582176</v>
       </c>
     </row>
     <row r="1507">
@@ -59207,10 +59207,10 @@
         </is>
       </c>
       <c r="H1507" s="2" t="n">
-        <v>46064.44312582895</v>
+        <v>46064.44312583334</v>
       </c>
       <c r="I1507" s="2" t="n">
-        <v>46069.44312582895</v>
+        <v>46069.44312583334</v>
       </c>
     </row>
     <row r="1508">
@@ -59246,10 +59246,10 @@
         </is>
       </c>
       <c r="H1508" s="2" t="n">
-        <v>46076.4431258322</v>
+        <v>46076.44312583334</v>
       </c>
       <c r="I1508" s="2" t="n">
-        <v>46081.4431258322</v>
+        <v>46081.44312583334</v>
       </c>
     </row>
     <row r="1509">
@@ -59285,10 +59285,10 @@
         </is>
       </c>
       <c r="H1509" s="2" t="n">
-        <v>46082.4431258353</v>
+        <v>46082.44312583334</v>
       </c>
       <c r="I1509" s="2" t="n">
-        <v>46087.4431258353</v>
+        <v>46087.44312583334</v>
       </c>
     </row>
     <row r="1510">
@@ -59324,10 +59324,10 @@
         </is>
       </c>
       <c r="H1510" s="2" t="n">
-        <v>46073.44312583853</v>
+        <v>46073.44312583334</v>
       </c>
       <c r="I1510" s="2" t="n">
-        <v>46078.44312583853</v>
+        <v>46078.44312583334</v>
       </c>
     </row>
     <row r="1511">
@@ -59363,10 +59363,10 @@
         </is>
       </c>
       <c r="H1511" s="2" t="n">
-        <v>46073.44312584171</v>
+        <v>46073.4431258449</v>
       </c>
       <c r="I1511" s="2" t="n">
-        <v>46078.44312584171</v>
+        <v>46078.4431258449</v>
       </c>
     </row>
     <row r="1512">
@@ -59402,10 +59402,10 @@
         </is>
       </c>
       <c r="H1512" s="2" t="n">
-        <v>46078.44312584502</v>
+        <v>46078.4431258449</v>
       </c>
       <c r="I1512" s="2" t="n">
-        <v>46083.44312584502</v>
+        <v>46083.4431258449</v>
       </c>
     </row>
     <row r="1513">
@@ -59441,10 +59441,10 @@
         </is>
       </c>
       <c r="H1513" s="2" t="n">
-        <v>46065.44312584821</v>
+        <v>46065.4431258449</v>
       </c>
       <c r="I1513" s="2" t="n">
-        <v>46070.44312584821</v>
+        <v>46070.4431258449</v>
       </c>
     </row>
     <row r="1514">
@@ -59480,10 +59480,10 @@
         </is>
       </c>
       <c r="H1514" s="2" t="n">
-        <v>46080.44312585129</v>
+        <v>46080.44312585648</v>
       </c>
       <c r="I1514" s="2" t="n">
-        <v>46085.44312585129</v>
+        <v>46085.44312585648</v>
       </c>
     </row>
     <row r="1515">
@@ -59519,10 +59519,10 @@
         </is>
       </c>
       <c r="H1515" s="2" t="n">
-        <v>46060.44312585449</v>
+        <v>46060.44312585648</v>
       </c>
       <c r="I1515" s="2" t="n">
-        <v>46065.44312585449</v>
+        <v>46065.44312585648</v>
       </c>
     </row>
     <row r="1516">
@@ -59558,10 +59558,10 @@
         </is>
       </c>
       <c r="H1516" s="2" t="n">
-        <v>46088.44312585783</v>
+        <v>46088.44312585648</v>
       </c>
       <c r="I1516" s="2" t="n">
-        <v>46093.44312585783</v>
+        <v>46093.44312585648</v>
       </c>
     </row>
     <row r="1517">
@@ -59597,10 +59597,10 @@
         </is>
       </c>
       <c r="H1517" s="2" t="n">
-        <v>46064.44312586108</v>
+        <v>46064.44312585648</v>
       </c>
       <c r="I1517" s="2" t="n">
-        <v>46069.44312586108</v>
+        <v>46069.44312585648</v>
       </c>
     </row>
     <row r="1518">
@@ -59636,10 +59636,10 @@
         </is>
       </c>
       <c r="H1518" s="2" t="n">
-        <v>46067.44312586416</v>
+        <v>46067.44312586806</v>
       </c>
       <c r="I1518" s="2" t="n">
-        <v>46072.44312586416</v>
+        <v>46072.44312586806</v>
       </c>
     </row>
     <row r="1519">
@@ -59675,10 +59675,10 @@
         </is>
       </c>
       <c r="H1519" s="2" t="n">
-        <v>46067.44312586734</v>
+        <v>46067.44312586806</v>
       </c>
       <c r="I1519" s="2" t="n">
-        <v>46072.44312586734</v>
+        <v>46072.44312586806</v>
       </c>
     </row>
     <row r="1520">
@@ -59714,10 +59714,10 @@
         </is>
       </c>
       <c r="H1520" s="2" t="n">
-        <v>46064.44312587047</v>
+        <v>46064.44312586806</v>
       </c>
       <c r="I1520" s="2" t="n">
-        <v>46069.44312587047</v>
+        <v>46069.44312586806</v>
       </c>
     </row>
     <row r="1521">
@@ -59753,10 +59753,10 @@
         </is>
       </c>
       <c r="H1521" s="2" t="n">
-        <v>46066.44312587352</v>
+        <v>46066.44312586806</v>
       </c>
       <c r="I1521" s="2" t="n">
-        <v>46071.44312587352</v>
+        <v>46071.44312586806</v>
       </c>
     </row>
     <row r="1522">
@@ -59792,10 +59792,10 @@
         </is>
       </c>
       <c r="H1522" s="2" t="n">
-        <v>46089.44312587656</v>
+        <v>46089.44312587963</v>
       </c>
       <c r="I1522" s="2" t="n">
-        <v>46094.44312587656</v>
+        <v>46094.44312587963</v>
       </c>
     </row>
     <row r="1523">
@@ -59831,10 +59831,10 @@
         </is>
       </c>
       <c r="H1523" s="2" t="n">
-        <v>46076.44312587981</v>
+        <v>46076.44312587963</v>
       </c>
       <c r="I1523" s="2" t="n">
-        <v>46081.44312587981</v>
+        <v>46081.44312587963</v>
       </c>
     </row>
     <row r="1524">
@@ -59870,10 +59870,10 @@
         </is>
       </c>
       <c r="H1524" s="2" t="n">
-        <v>46071.44312588294</v>
+        <v>46071.44312587963</v>
       </c>
       <c r="I1524" s="2" t="n">
-        <v>46076.44312588294</v>
+        <v>46076.44312587963</v>
       </c>
     </row>
     <row r="1525">
@@ -59909,10 +59909,10 @@
         </is>
       </c>
       <c r="H1525" s="2" t="n">
-        <v>46068.44312588588</v>
+        <v>46068.4431258912</v>
       </c>
       <c r="I1525" s="2" t="n">
-        <v>46073.44312588588</v>
+        <v>46073.4431258912</v>
       </c>
     </row>
     <row r="1526">
@@ -59948,10 +59948,10 @@
         </is>
       </c>
       <c r="H1526" s="2" t="n">
-        <v>46072.44312588905</v>
+        <v>46072.4431258912</v>
       </c>
       <c r="I1526" s="2" t="n">
-        <v>46077.44312588905</v>
+        <v>46077.4431258912</v>
       </c>
     </row>
     <row r="1527">
@@ -59987,10 +59987,10 @@
         </is>
       </c>
       <c r="H1527" s="2" t="n">
-        <v>46061.44312589245</v>
+        <v>46061.4431258912</v>
       </c>
       <c r="I1527" s="2" t="n">
-        <v>46066.44312589245</v>
+        <v>46066.4431258912</v>
       </c>
     </row>
     <row r="1528">
@@ -60026,10 +60026,10 @@
         </is>
       </c>
       <c r="H1528" s="2" t="n">
-        <v>46079.4431258955</v>
+        <v>46079.4431258912</v>
       </c>
       <c r="I1528" s="2" t="n">
-        <v>46084.4431258955</v>
+        <v>46084.4431258912</v>
       </c>
     </row>
     <row r="1529">
@@ -60065,10 +60065,10 @@
         </is>
       </c>
       <c r="H1529" s="2" t="n">
-        <v>46086.44312589856</v>
+        <v>46086.44312590278</v>
       </c>
       <c r="I1529" s="2" t="n">
-        <v>46091.44312589856</v>
+        <v>46091.44312590278</v>
       </c>
     </row>
     <row r="1530">
@@ -60104,10 +60104,10 @@
         </is>
       </c>
       <c r="H1530" s="2" t="n">
-        <v>46061.44312590175</v>
+        <v>46061.44312590278</v>
       </c>
       <c r="I1530" s="2" t="n">
-        <v>46066.44312590175</v>
+        <v>46066.44312590278</v>
       </c>
     </row>
     <row r="1531">
@@ -60143,10 +60143,10 @@
         </is>
       </c>
       <c r="H1531" s="2" t="n">
-        <v>46080.44312590487</v>
+        <v>46080.44312590278</v>
       </c>
       <c r="I1531" s="2" t="n">
-        <v>46085.44312590487</v>
+        <v>46085.44312590278</v>
       </c>
     </row>
     <row r="1532">
@@ -60182,10 +60182,10 @@
         </is>
       </c>
       <c r="H1532" s="2" t="n">
-        <v>46081.44312590811</v>
+        <v>46081.44312590278</v>
       </c>
       <c r="I1532" s="2" t="n">
-        <v>46086.44312590811</v>
+        <v>46086.44312590278</v>
       </c>
     </row>
     <row r="1533">
@@ -60221,10 +60221,10 @@
         </is>
       </c>
       <c r="H1533" s="2" t="n">
-        <v>46065.44312591136</v>
+        <v>46065.44312591435</v>
       </c>
       <c r="I1533" s="2" t="n">
-        <v>46070.44312591136</v>
+        <v>46070.44312591435</v>
       </c>
     </row>
     <row r="1534">
@@ -60260,10 +60260,10 @@
         </is>
       </c>
       <c r="H1534" s="2" t="n">
-        <v>46082.44312591463</v>
+        <v>46082.44312591435</v>
       </c>
       <c r="I1534" s="2" t="n">
-        <v>46087.44312591463</v>
+        <v>46087.44312591435</v>
       </c>
     </row>
     <row r="1535">
@@ -60299,10 +60299,10 @@
         </is>
       </c>
       <c r="H1535" s="2" t="n">
-        <v>46082.4431259177</v>
+        <v>46082.44312591435</v>
       </c>
       <c r="I1535" s="2" t="n">
-        <v>46087.4431259177</v>
+        <v>46087.44312591435</v>
       </c>
     </row>
     <row r="1536">
@@ -60338,10 +60338,10 @@
         </is>
       </c>
       <c r="H1536" s="2" t="n">
-        <v>46072.44312592084</v>
+        <v>46072.44312592593</v>
       </c>
       <c r="I1536" s="2" t="n">
-        <v>46077.44312592084</v>
+        <v>46077.44312592593</v>
       </c>
     </row>
     <row r="1537">
@@ -60377,10 +60377,10 @@
         </is>
       </c>
       <c r="H1537" s="2" t="n">
-        <v>46069.44312592409</v>
+        <v>46069.44312592593</v>
       </c>
       <c r="I1537" s="2" t="n">
-        <v>46074.44312592409</v>
+        <v>46074.44312592593</v>
       </c>
     </row>
     <row r="1538">
@@ -60416,10 +60416,10 @@
         </is>
       </c>
       <c r="H1538" s="2" t="n">
-        <v>46082.44312592728</v>
+        <v>46082.44312592593</v>
       </c>
       <c r="I1538" s="2" t="n">
-        <v>46087.44312592728</v>
+        <v>46087.44312592593</v>
       </c>
     </row>
     <row r="1539">
@@ -60455,10 +60455,10 @@
         </is>
       </c>
       <c r="H1539" s="2" t="n">
-        <v>46088.44312593054</v>
+        <v>46088.44312592593</v>
       </c>
       <c r="I1539" s="2" t="n">
-        <v>46093.44312593054</v>
+        <v>46093.44312592593</v>
       </c>
     </row>
     <row r="1540">
@@ -60494,10 +60494,10 @@
         </is>
       </c>
       <c r="H1540" s="2" t="n">
-        <v>46071.44312593353</v>
+        <v>46071.4431259375</v>
       </c>
       <c r="I1540" s="2" t="n">
-        <v>46076.44312593353</v>
+        <v>46076.4431259375</v>
       </c>
     </row>
     <row r="1541">
@@ -60533,10 +60533,10 @@
         </is>
       </c>
       <c r="H1541" s="2" t="n">
-        <v>46087.44312593693</v>
+        <v>46087.4431259375</v>
       </c>
       <c r="I1541" s="2" t="n">
-        <v>46092.44312593693</v>
+        <v>46092.4431259375</v>
       </c>
     </row>
     <row r="1542">
@@ -60572,10 +60572,10 @@
         </is>
       </c>
       <c r="H1542" s="2" t="n">
-        <v>46071.44312593998</v>
+        <v>46071.4431259375</v>
       </c>
       <c r="I1542" s="2" t="n">
-        <v>46076.44312593998</v>
+        <v>46076.4431259375</v>
       </c>
     </row>
     <row r="1543">
@@ -60611,10 +60611,10 @@
         </is>
       </c>
       <c r="H1543" s="2" t="n">
-        <v>46080.44312594321</v>
+        <v>46080.4431259375</v>
       </c>
       <c r="I1543" s="2" t="n">
-        <v>46085.44312594321</v>
+        <v>46085.4431259375</v>
       </c>
     </row>
     <row r="1544">
@@ -60650,10 +60650,10 @@
         </is>
       </c>
       <c r="H1544" s="2" t="n">
-        <v>46065.44312594632</v>
+        <v>46065.44312594907</v>
       </c>
       <c r="I1544" s="2" t="n">
-        <v>46070.44312594632</v>
+        <v>46070.44312594907</v>
       </c>
     </row>
     <row r="1545">
@@ -60689,10 +60689,10 @@
         </is>
       </c>
       <c r="H1545" s="2" t="n">
-        <v>46070.44312594966</v>
+        <v>46070.44312594907</v>
       </c>
       <c r="I1545" s="2" t="n">
-        <v>46075.44312594966</v>
+        <v>46075.44312594907</v>
       </c>
     </row>
     <row r="1546">
@@ -60728,10 +60728,10 @@
         </is>
       </c>
       <c r="H1546" s="2" t="n">
-        <v>46076.44312595276</v>
+        <v>46076.44312594907</v>
       </c>
       <c r="I1546" s="2" t="n">
-        <v>46081.44312595276</v>
+        <v>46081.44312594907</v>
       </c>
     </row>
     <row r="1547">
@@ -60767,10 +60767,10 @@
         </is>
       </c>
       <c r="H1547" s="2" t="n">
-        <v>46067.44312595594</v>
+        <v>46067.44312596065</v>
       </c>
       <c r="I1547" s="2" t="n">
-        <v>46072.44312595594</v>
+        <v>46072.44312596065</v>
       </c>
     </row>
     <row r="1548">
@@ -60806,10 +60806,10 @@
         </is>
       </c>
       <c r="H1548" s="2" t="n">
-        <v>46089.44312595913</v>
+        <v>46089.44312596065</v>
       </c>
       <c r="I1548" s="2" t="n">
-        <v>46094.44312595913</v>
+        <v>46094.44312596065</v>
       </c>
     </row>
     <row r="1549">
@@ -60845,10 +60845,10 @@
         </is>
       </c>
       <c r="H1549" s="2" t="n">
-        <v>46074.44312596234</v>
+        <v>46074.44312596065</v>
       </c>
       <c r="I1549" s="2" t="n">
-        <v>46079.44312596234</v>
+        <v>46079.44312596065</v>
       </c>
     </row>
     <row r="1550">
@@ -60884,10 +60884,10 @@
         </is>
       </c>
       <c r="H1550" s="2" t="n">
-        <v>46086.44312596553</v>
+        <v>46086.44312596065</v>
       </c>
       <c r="I1550" s="2" t="n">
-        <v>46091.44312596553</v>
+        <v>46091.44312596065</v>
       </c>
     </row>
     <row r="1551">
@@ -60923,10 +60923,1960 @@
         </is>
       </c>
       <c r="H1551" s="2" t="n">
-        <v>46076.44312596863</v>
+        <v>46076.44312597222</v>
       </c>
       <c r="I1551" s="2" t="n">
-        <v>46081.44312596863</v>
+        <v>46081.44312597222</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>82a04c67-3eb9-4673-88bf-14fe0b9482d0</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1552" t="n">
+        <v>2934.13</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>93.29000000000001</v>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1552" s="2" t="n">
+        <v>46063.47898272161</v>
+      </c>
+      <c r="I1552" s="2" t="n">
+        <v>46068.47898272161</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>bc321edc-229c-4a48-8a7a-7ccdfa5dae42</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1553" t="n">
+        <v>4965.43</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1553" s="2" t="n">
+        <v>46072.47898272613</v>
+      </c>
+      <c r="I1553" s="2" t="n">
+        <v>46077.47898272613</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>74242ec0-3458-4f01-b43e-6361481a7820</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1554" t="n">
+        <v>2168.09</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1554" s="2" t="n">
+        <v>46072.47898272962</v>
+      </c>
+      <c r="I1554" s="2" t="n">
+        <v>46077.47898272962</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>6a15ed7f-1488-43dc-9bcd-f89dc4094bb7</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1555" t="n">
+        <v>8388.290000000001</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>87.31999999999999</v>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1555" s="2" t="n">
+        <v>46077.47898273277</v>
+      </c>
+      <c r="I1555" s="2" t="n">
+        <v>46082.47898273277</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>dd7074f7-f55f-499a-9a38-baebcd56a308</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1556" t="n">
+        <v>4450.75</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1556" s="2" t="n">
+        <v>46082.47898273618</v>
+      </c>
+      <c r="I1556" s="2" t="n">
+        <v>46087.47898273618</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>719684b9-50eb-4921-8d7d-df59fbf67eb1</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1557" t="n">
+        <v>5036.83</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1557" s="2" t="n">
+        <v>46069.47898273928</v>
+      </c>
+      <c r="I1557" s="2" t="n">
+        <v>46074.47898273928</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>61bc4fe3-444b-4de9-8927-f46d060dd889</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1558" t="n">
+        <v>3457.08</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1558" s="2" t="n">
+        <v>46089.47898274247</v>
+      </c>
+      <c r="I1558" s="2" t="n">
+        <v>46094.47898274247</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2edebf3a-a0bc-471d-a3d7-6cc9e69b978a</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1559" t="n">
+        <v>1140.12</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1559" s="2" t="n">
+        <v>46081.47898274573</v>
+      </c>
+      <c r="I1559" s="2" t="n">
+        <v>46086.47898274573</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>fcf166d5-2662-4fa3-afee-125d1ccc8631</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1560" t="n">
+        <v>9717.290000000001</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1560" s="2" t="n">
+        <v>46063.47898274883</v>
+      </c>
+      <c r="I1560" s="2" t="n">
+        <v>46068.47898274883</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>e86d0ec7-ac06-486c-82e6-690e23bef1ea</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1561" t="n">
+        <v>2296.11</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>86.29000000000001</v>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1561" s="2" t="n">
+        <v>46075.47898275188</v>
+      </c>
+      <c r="I1561" s="2" t="n">
+        <v>46080.47898275188</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>0764d7a0-740e-4595-b8f4-a312b615c481</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1562" t="n">
+        <v>8840.26</v>
+      </c>
+      <c r="D1562" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1562" s="2" t="n">
+        <v>46069.47898275507</v>
+      </c>
+      <c r="I1562" s="2" t="n">
+        <v>46074.47898275507</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>cf4be5de-aebb-446f-8587-59dd8f0af58f</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1563" t="n">
+        <v>9524.370000000001</v>
+      </c>
+      <c r="D1563" t="n">
+        <v>88.02</v>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1563" s="2" t="n">
+        <v>46078.4789827586</v>
+      </c>
+      <c r="I1563" s="2" t="n">
+        <v>46083.4789827586</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>3947e43a-1719-4984-8e3b-590345bee770</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1564" t="n">
+        <v>1990.43</v>
+      </c>
+      <c r="D1564" t="n">
+        <v>92.62</v>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1564" s="2" t="n">
+        <v>46078.4789827617</v>
+      </c>
+      <c r="I1564" s="2" t="n">
+        <v>46083.4789827617</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>a31213b1-2755-4cf7-941b-a941ea08f7eb</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1565" t="n">
+        <v>6421.18</v>
+      </c>
+      <c r="D1565" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1565" s="2" t="n">
+        <v>46069.47898276475</v>
+      </c>
+      <c r="I1565" s="2" t="n">
+        <v>46074.47898276475</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>193650e0-91a8-4f3c-be49-a665fdab8769</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1566" t="n">
+        <v>4314.18</v>
+      </c>
+      <c r="D1566" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1566" s="2" t="n">
+        <v>46062.47898276781</v>
+      </c>
+      <c r="I1566" s="2" t="n">
+        <v>46067.47898276781</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>720bc1c3-dad2-4482-9965-ca1e6c36cea1</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1567" t="n">
+        <v>5991.74</v>
+      </c>
+      <c r="D1567" t="n">
+        <v>99.04000000000001</v>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1567" s="2" t="n">
+        <v>46074.47898277108</v>
+      </c>
+      <c r="I1567" s="2" t="n">
+        <v>46079.47898277108</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>4d458f3a-1eb5-4cd7-9a97-e5c9c55b53b3</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1568" t="n">
+        <v>4237.39</v>
+      </c>
+      <c r="D1568" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1568" s="2" t="n">
+        <v>46071.47898277417</v>
+      </c>
+      <c r="I1568" s="2" t="n">
+        <v>46076.47898277417</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>082aafa9-f9b3-4446-ab72-679767d04d66</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1569" t="n">
+        <v>7612.76</v>
+      </c>
+      <c r="D1569" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1569" s="2" t="n">
+        <v>46082.47898277719</v>
+      </c>
+      <c r="I1569" s="2" t="n">
+        <v>46087.47898277719</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>1c7f08a8-3072-425e-b5bf-5ff9fd546ad6</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1570" t="n">
+        <v>3359.4</v>
+      </c>
+      <c r="D1570" t="n">
+        <v>90.41</v>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1570" s="2" t="n">
+        <v>46065.4789827807</v>
+      </c>
+      <c r="I1570" s="2" t="n">
+        <v>46070.4789827807</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>7d5d970d-04cd-46e0-9ff8-4d554d8dd0ad</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1571" t="n">
+        <v>6958.89</v>
+      </c>
+      <c r="D1571" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1571" s="2" t="n">
+        <v>46068.47898278375</v>
+      </c>
+      <c r="I1571" s="2" t="n">
+        <v>46073.47898278375</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>f93b9637-5fe6-44bd-b6a6-6e35bb967566</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1572" t="n">
+        <v>4022.37</v>
+      </c>
+      <c r="D1572" t="n">
+        <v>91.45999999999999</v>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1572" s="2" t="n">
+        <v>46066.47898278677</v>
+      </c>
+      <c r="I1572" s="2" t="n">
+        <v>46071.47898278677</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2283e264-2c0c-4706-84bf-a0f47e6d5822</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1573" t="n">
+        <v>1716.55</v>
+      </c>
+      <c r="D1573" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1573" s="2" t="n">
+        <v>46068.47898278983</v>
+      </c>
+      <c r="I1573" s="2" t="n">
+        <v>46073.47898278983</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>16d47716-e177-4925-85d6-3e3b3b47f9e5</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1574" t="n">
+        <v>9843.23</v>
+      </c>
+      <c r="D1574" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1574" s="2" t="n">
+        <v>46077.47898279308</v>
+      </c>
+      <c r="I1574" s="2" t="n">
+        <v>46082.47898279308</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>502664f9-7266-48cd-90d2-f3367666cbc8</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1575" t="n">
+        <v>6803.47</v>
+      </c>
+      <c r="D1575" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1575" s="2" t="n">
+        <v>46072.47898279614</v>
+      </c>
+      <c r="I1575" s="2" t="n">
+        <v>46077.47898279614</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>8332fc06-6930-41a0-8cd7-e905465ad935</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1576" t="n">
+        <v>9052.059999999999</v>
+      </c>
+      <c r="D1576" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1576" s="2" t="n">
+        <v>46069.47898279929</v>
+      </c>
+      <c r="I1576" s="2" t="n">
+        <v>46074.47898279929</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>3d27dd1a-a56c-44c2-93ed-e25c132aba62</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1577" t="n">
+        <v>7436.01</v>
+      </c>
+      <c r="D1577" t="n">
+        <v>96.81999999999999</v>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1577" s="2" t="n">
+        <v>46082.47898280239</v>
+      </c>
+      <c r="I1577" s="2" t="n">
+        <v>46087.47898280239</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>eeb6d8a2-aca3-457c-b5a4-c9dc228e6bcb</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1578" t="n">
+        <v>5525.26</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1578" s="2" t="n">
+        <v>46070.47898280567</v>
+      </c>
+      <c r="I1578" s="2" t="n">
+        <v>46075.47898280567</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>e9d3dd75-88ee-4c15-98bf-2aa2dfcdd8a9</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1579" t="n">
+        <v>1050.74</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1579" s="2" t="n">
+        <v>46089.47898280869</v>
+      </c>
+      <c r="I1579" s="2" t="n">
+        <v>46094.47898280869</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>738cf86d-19ef-474a-81f0-90e94185d453</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1580" t="n">
+        <v>6215.04</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1580" s="2" t="n">
+        <v>46089.47898281184</v>
+      </c>
+      <c r="I1580" s="2" t="n">
+        <v>46094.47898281184</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>5290939c-4ef1-4dec-b2fd-79ecd4a0c8f4</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1581" t="n">
+        <v>2707.46</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1581" s="2" t="n">
+        <v>46066.47898281505</v>
+      </c>
+      <c r="I1581" s="2" t="n">
+        <v>46071.47898281505</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>84793907-d425-4b5f-84e1-58f5fec4d756</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1582" t="n">
+        <v>5472.6</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1582" s="2" t="n">
+        <v>46075.47898281834</v>
+      </c>
+      <c r="I1582" s="2" t="n">
+        <v>46080.47898281834</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>c9e2e540-1006-48f0-936a-c96df820744d</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1583" t="n">
+        <v>6789.37</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>98.73999999999999</v>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1583" s="2" t="n">
+        <v>46080.47898282131</v>
+      </c>
+      <c r="I1583" s="2" t="n">
+        <v>46085.47898282131</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>b91551f5-2bd3-4247-9bfc-33cd1149855d</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1584" t="n">
+        <v>9485.16</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>95.36</v>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1584" s="2" t="n">
+        <v>46070.47898282449</v>
+      </c>
+      <c r="I1584" s="2" t="n">
+        <v>46075.47898282449</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>8b635b57-5a39-4409-85a4-930bcbe379bc</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1585" t="n">
+        <v>3964.56</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1585" s="2" t="n">
+        <v>46080.47898282779</v>
+      </c>
+      <c r="I1585" s="2" t="n">
+        <v>46085.47898282779</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>96139e9b-077f-40a8-85ae-3e5a5b8a6d9e</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1586" t="n">
+        <v>4664.62</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1586" s="2" t="n">
+        <v>46082.47898283097</v>
+      </c>
+      <c r="I1586" s="2" t="n">
+        <v>46087.47898283097</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>28baa84b-0ac2-4aea-aa21-2e15271c2448</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1587" t="n">
+        <v>6572.06</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1587" s="2" t="n">
+        <v>46067.47898283407</v>
+      </c>
+      <c r="I1587" s="2" t="n">
+        <v>46072.47898283407</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>b32bc3c0-6835-47dd-aaac-ba5a8e64d1b6</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1588" t="n">
+        <v>1624.68</v>
+      </c>
+      <c r="D1588" t="n">
+        <v>91.87</v>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1588" s="2" t="n">
+        <v>46082.47898283718</v>
+      </c>
+      <c r="I1588" s="2" t="n">
+        <v>46087.47898283718</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>ec72b444-4f6f-4213-ba14-fae0813369f7</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1589" t="n">
+        <v>7903.35</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>94.72</v>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1589" s="2" t="n">
+        <v>46064.47898284043</v>
+      </c>
+      <c r="I1589" s="2" t="n">
+        <v>46069.47898284043</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>a96c54e6-05b1-41e9-b2a2-af1197dfb230</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1590" t="n">
+        <v>7149.51</v>
+      </c>
+      <c r="D1590" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1590" s="2" t="n">
+        <v>46070.47898284357</v>
+      </c>
+      <c r="I1590" s="2" t="n">
+        <v>46075.47898284357</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>0891ead1-2926-4a13-b395-b43c4eb0f483</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1591" t="n">
+        <v>5117.17</v>
+      </c>
+      <c r="D1591" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1591" s="2" t="n">
+        <v>46071.47898284667</v>
+      </c>
+      <c r="I1591" s="2" t="n">
+        <v>46076.47898284667</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>95a0cdad-0d8e-455e-aba0-20fb0e569294</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1592" t="n">
+        <v>3296.38</v>
+      </c>
+      <c r="D1592" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1592" s="2" t="n">
+        <v>46075.4789828499</v>
+      </c>
+      <c r="I1592" s="2" t="n">
+        <v>46080.4789828499</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>87009d6e-a488-4d92-8aec-f096f0c3402c</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1593" t="n">
+        <v>4765.47</v>
+      </c>
+      <c r="D1593" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1593" s="2" t="n">
+        <v>46080.47898285292</v>
+      </c>
+      <c r="I1593" s="2" t="n">
+        <v>46085.47898285292</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>8dff7b50-f382-49bc-8f61-18e5bb86a257</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1594" t="n">
+        <v>5370.16</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>93.62</v>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1594" s="2" t="n">
+        <v>46067.4789828561</v>
+      </c>
+      <c r="I1594" s="2" t="n">
+        <v>46072.4789828561</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>1797cd90-3237-4bf7-9f2d-930a28ce0af5</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1595" t="n">
+        <v>3308.7</v>
+      </c>
+      <c r="D1595" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1595" s="2" t="n">
+        <v>46086.47898285909</v>
+      </c>
+      <c r="I1595" s="2" t="n">
+        <v>46091.47898285909</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>53c97ff1-4f0f-4243-aee9-b8db6686cbc9</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1596" t="n">
+        <v>5807.53</v>
+      </c>
+      <c r="D1596" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1596" s="2" t="n">
+        <v>46076.47898286287</v>
+      </c>
+      <c r="I1596" s="2" t="n">
+        <v>46081.47898286287</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>13f88061-a8b6-4caf-b9e3-fe48dc8e0eeb</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1597" t="n">
+        <v>5946.17</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>92.16</v>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1597" s="2" t="n">
+        <v>46078.47898286609</v>
+      </c>
+      <c r="I1597" s="2" t="n">
+        <v>46083.47898286609</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>7fde1eef-84f6-412e-8763-a6e019dc7398</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1598" t="n">
+        <v>9811.799999999999</v>
+      </c>
+      <c r="D1598" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1598" s="2" t="n">
+        <v>46088.47898286908</v>
+      </c>
+      <c r="I1598" s="2" t="n">
+        <v>46093.47898286908</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>b022749b-faf7-43aa-ac2d-48ecdd214338</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1599" t="n">
+        <v>9537.08</v>
+      </c>
+      <c r="D1599" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1599" s="2" t="n">
+        <v>46076.47898287233</v>
+      </c>
+      <c r="I1599" s="2" t="n">
+        <v>46081.47898287233</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>009aab46-bbae-408d-898f-aff157ab4e90</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1600" t="n">
+        <v>3403.41</v>
+      </c>
+      <c r="D1600" t="n">
+        <v>86.97</v>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1600" s="2" t="n">
+        <v>46075.47898287535</v>
+      </c>
+      <c r="I1600" s="2" t="n">
+        <v>46080.47898287535</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>ac3cb701-ca53-445f-8bb9-7f7ceb1d846d</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1601" t="n">
+        <v>4428.22</v>
+      </c>
+      <c r="D1601" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1601" s="2" t="n">
+        <v>46083.47898287953</v>
+      </c>
+      <c r="I1601" s="2" t="n">
+        <v>46088.47898287953</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1601"/>
+  <dimension ref="A1:I1651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60962,10 +60962,10 @@
         </is>
       </c>
       <c r="H1552" s="2" t="n">
-        <v>46063.47898272161</v>
+        <v>46063.47898271991</v>
       </c>
       <c r="I1552" s="2" t="n">
-        <v>46068.47898272161</v>
+        <v>46068.47898271991</v>
       </c>
     </row>
     <row r="1553">
@@ -61001,10 +61001,10 @@
         </is>
       </c>
       <c r="H1553" s="2" t="n">
-        <v>46072.47898272613</v>
+        <v>46072.47898273148</v>
       </c>
       <c r="I1553" s="2" t="n">
-        <v>46077.47898272613</v>
+        <v>46077.47898273148</v>
       </c>
     </row>
     <row r="1554">
@@ -61040,10 +61040,10 @@
         </is>
       </c>
       <c r="H1554" s="2" t="n">
-        <v>46072.47898272962</v>
+        <v>46072.47898273148</v>
       </c>
       <c r="I1554" s="2" t="n">
-        <v>46077.47898272962</v>
+        <v>46077.47898273148</v>
       </c>
     </row>
     <row r="1555">
@@ -61079,10 +61079,10 @@
         </is>
       </c>
       <c r="H1555" s="2" t="n">
-        <v>46077.47898273277</v>
+        <v>46077.47898273148</v>
       </c>
       <c r="I1555" s="2" t="n">
-        <v>46082.47898273277</v>
+        <v>46082.47898273148</v>
       </c>
     </row>
     <row r="1556">
@@ -61118,10 +61118,10 @@
         </is>
       </c>
       <c r="H1556" s="2" t="n">
-        <v>46082.47898273618</v>
+        <v>46082.47898273148</v>
       </c>
       <c r="I1556" s="2" t="n">
-        <v>46087.47898273618</v>
+        <v>46087.47898273148</v>
       </c>
     </row>
     <row r="1557">
@@ -61157,10 +61157,10 @@
         </is>
       </c>
       <c r="H1557" s="2" t="n">
-        <v>46069.47898273928</v>
+        <v>46069.47898274306</v>
       </c>
       <c r="I1557" s="2" t="n">
-        <v>46074.47898273928</v>
+        <v>46074.47898274306</v>
       </c>
     </row>
     <row r="1558">
@@ -61196,10 +61196,10 @@
         </is>
       </c>
       <c r="H1558" s="2" t="n">
-        <v>46089.47898274247</v>
+        <v>46089.47898274306</v>
       </c>
       <c r="I1558" s="2" t="n">
-        <v>46094.47898274247</v>
+        <v>46094.47898274306</v>
       </c>
     </row>
     <row r="1559">
@@ -61235,10 +61235,10 @@
         </is>
       </c>
       <c r="H1559" s="2" t="n">
-        <v>46081.47898274573</v>
+        <v>46081.47898274306</v>
       </c>
       <c r="I1559" s="2" t="n">
-        <v>46086.47898274573</v>
+        <v>46086.47898274306</v>
       </c>
     </row>
     <row r="1560">
@@ -61274,10 +61274,10 @@
         </is>
       </c>
       <c r="H1560" s="2" t="n">
-        <v>46063.47898274883</v>
+        <v>46063.47898274306</v>
       </c>
       <c r="I1560" s="2" t="n">
-        <v>46068.47898274883</v>
+        <v>46068.47898274306</v>
       </c>
     </row>
     <row r="1561">
@@ -61313,10 +61313,10 @@
         </is>
       </c>
       <c r="H1561" s="2" t="n">
-        <v>46075.47898275188</v>
+        <v>46075.47898275463</v>
       </c>
       <c r="I1561" s="2" t="n">
-        <v>46080.47898275188</v>
+        <v>46080.47898275463</v>
       </c>
     </row>
     <row r="1562">
@@ -61352,10 +61352,10 @@
         </is>
       </c>
       <c r="H1562" s="2" t="n">
-        <v>46069.47898275507</v>
+        <v>46069.47898275463</v>
       </c>
       <c r="I1562" s="2" t="n">
-        <v>46074.47898275507</v>
+        <v>46074.47898275463</v>
       </c>
     </row>
     <row r="1563">
@@ -61391,10 +61391,10 @@
         </is>
       </c>
       <c r="H1563" s="2" t="n">
-        <v>46078.4789827586</v>
+        <v>46078.47898275463</v>
       </c>
       <c r="I1563" s="2" t="n">
-        <v>46083.4789827586</v>
+        <v>46083.47898275463</v>
       </c>
     </row>
     <row r="1564">
@@ -61430,10 +61430,10 @@
         </is>
       </c>
       <c r="H1564" s="2" t="n">
-        <v>46078.4789827617</v>
+        <v>46078.4789827662</v>
       </c>
       <c r="I1564" s="2" t="n">
-        <v>46083.4789827617</v>
+        <v>46083.4789827662</v>
       </c>
     </row>
     <row r="1565">
@@ -61469,10 +61469,10 @@
         </is>
       </c>
       <c r="H1565" s="2" t="n">
-        <v>46069.47898276475</v>
+        <v>46069.4789827662</v>
       </c>
       <c r="I1565" s="2" t="n">
-        <v>46074.47898276475</v>
+        <v>46074.4789827662</v>
       </c>
     </row>
     <row r="1566">
@@ -61508,10 +61508,10 @@
         </is>
       </c>
       <c r="H1566" s="2" t="n">
-        <v>46062.47898276781</v>
+        <v>46062.4789827662</v>
       </c>
       <c r="I1566" s="2" t="n">
-        <v>46067.47898276781</v>
+        <v>46067.4789827662</v>
       </c>
     </row>
     <row r="1567">
@@ -61547,10 +61547,10 @@
         </is>
       </c>
       <c r="H1567" s="2" t="n">
-        <v>46074.47898277108</v>
+        <v>46074.4789827662</v>
       </c>
       <c r="I1567" s="2" t="n">
-        <v>46079.47898277108</v>
+        <v>46079.4789827662</v>
       </c>
     </row>
     <row r="1568">
@@ -61586,10 +61586,10 @@
         </is>
       </c>
       <c r="H1568" s="2" t="n">
-        <v>46071.47898277417</v>
+        <v>46071.47898277778</v>
       </c>
       <c r="I1568" s="2" t="n">
-        <v>46076.47898277417</v>
+        <v>46076.47898277778</v>
       </c>
     </row>
     <row r="1569">
@@ -61625,10 +61625,10 @@
         </is>
       </c>
       <c r="H1569" s="2" t="n">
-        <v>46082.47898277719</v>
+        <v>46082.47898277778</v>
       </c>
       <c r="I1569" s="2" t="n">
-        <v>46087.47898277719</v>
+        <v>46087.47898277778</v>
       </c>
     </row>
     <row r="1570">
@@ -61664,10 +61664,10 @@
         </is>
       </c>
       <c r="H1570" s="2" t="n">
-        <v>46065.4789827807</v>
+        <v>46065.47898277778</v>
       </c>
       <c r="I1570" s="2" t="n">
-        <v>46070.4789827807</v>
+        <v>46070.47898277778</v>
       </c>
     </row>
     <row r="1571">
@@ -61703,10 +61703,10 @@
         </is>
       </c>
       <c r="H1571" s="2" t="n">
-        <v>46068.47898278375</v>
+        <v>46068.47898278935</v>
       </c>
       <c r="I1571" s="2" t="n">
-        <v>46073.47898278375</v>
+        <v>46073.47898278935</v>
       </c>
     </row>
     <row r="1572">
@@ -61742,10 +61742,10 @@
         </is>
       </c>
       <c r="H1572" s="2" t="n">
-        <v>46066.47898278677</v>
+        <v>46066.47898278935</v>
       </c>
       <c r="I1572" s="2" t="n">
-        <v>46071.47898278677</v>
+        <v>46071.47898278935</v>
       </c>
     </row>
     <row r="1573">
@@ -61781,10 +61781,10 @@
         </is>
       </c>
       <c r="H1573" s="2" t="n">
-        <v>46068.47898278983</v>
+        <v>46068.47898278935</v>
       </c>
       <c r="I1573" s="2" t="n">
-        <v>46073.47898278983</v>
+        <v>46073.47898278935</v>
       </c>
     </row>
     <row r="1574">
@@ -61820,10 +61820,10 @@
         </is>
       </c>
       <c r="H1574" s="2" t="n">
-        <v>46077.47898279308</v>
+        <v>46077.47898278935</v>
       </c>
       <c r="I1574" s="2" t="n">
-        <v>46082.47898279308</v>
+        <v>46082.47898278935</v>
       </c>
     </row>
     <row r="1575">
@@ -61859,10 +61859,10 @@
         </is>
       </c>
       <c r="H1575" s="2" t="n">
-        <v>46072.47898279614</v>
+        <v>46072.47898280092</v>
       </c>
       <c r="I1575" s="2" t="n">
-        <v>46077.47898279614</v>
+        <v>46077.47898280092</v>
       </c>
     </row>
     <row r="1576">
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="H1576" s="2" t="n">
-        <v>46069.47898279929</v>
+        <v>46069.47898280092</v>
       </c>
       <c r="I1576" s="2" t="n">
-        <v>46074.47898279929</v>
+        <v>46074.47898280092</v>
       </c>
     </row>
     <row r="1577">
@@ -61937,10 +61937,10 @@
         </is>
       </c>
       <c r="H1577" s="2" t="n">
-        <v>46082.47898280239</v>
+        <v>46082.47898280092</v>
       </c>
       <c r="I1577" s="2" t="n">
-        <v>46087.47898280239</v>
+        <v>46087.47898280092</v>
       </c>
     </row>
     <row r="1578">
@@ -61976,10 +61976,10 @@
         </is>
       </c>
       <c r="H1578" s="2" t="n">
-        <v>46070.47898280567</v>
+        <v>46070.47898280092</v>
       </c>
       <c r="I1578" s="2" t="n">
-        <v>46075.47898280567</v>
+        <v>46075.47898280092</v>
       </c>
     </row>
     <row r="1579">
@@ -62015,10 +62015,10 @@
         </is>
       </c>
       <c r="H1579" s="2" t="n">
-        <v>46089.47898280869</v>
+        <v>46089.4789828125</v>
       </c>
       <c r="I1579" s="2" t="n">
-        <v>46094.47898280869</v>
+        <v>46094.4789828125</v>
       </c>
     </row>
     <row r="1580">
@@ -62054,10 +62054,10 @@
         </is>
       </c>
       <c r="H1580" s="2" t="n">
-        <v>46089.47898281184</v>
+        <v>46089.4789828125</v>
       </c>
       <c r="I1580" s="2" t="n">
-        <v>46094.47898281184</v>
+        <v>46094.4789828125</v>
       </c>
     </row>
     <row r="1581">
@@ -62093,10 +62093,10 @@
         </is>
       </c>
       <c r="H1581" s="2" t="n">
-        <v>46066.47898281505</v>
+        <v>46066.4789828125</v>
       </c>
       <c r="I1581" s="2" t="n">
-        <v>46071.47898281505</v>
+        <v>46071.4789828125</v>
       </c>
     </row>
     <row r="1582">
@@ -62132,10 +62132,10 @@
         </is>
       </c>
       <c r="H1582" s="2" t="n">
-        <v>46075.47898281834</v>
+        <v>46075.47898282408</v>
       </c>
       <c r="I1582" s="2" t="n">
-        <v>46080.47898281834</v>
+        <v>46080.47898282408</v>
       </c>
     </row>
     <row r="1583">
@@ -62171,10 +62171,10 @@
         </is>
       </c>
       <c r="H1583" s="2" t="n">
-        <v>46080.47898282131</v>
+        <v>46080.47898282408</v>
       </c>
       <c r="I1583" s="2" t="n">
-        <v>46085.47898282131</v>
+        <v>46085.47898282408</v>
       </c>
     </row>
     <row r="1584">
@@ -62210,10 +62210,10 @@
         </is>
       </c>
       <c r="H1584" s="2" t="n">
-        <v>46070.47898282449</v>
+        <v>46070.47898282408</v>
       </c>
       <c r="I1584" s="2" t="n">
-        <v>46075.47898282449</v>
+        <v>46075.47898282408</v>
       </c>
     </row>
     <row r="1585">
@@ -62249,10 +62249,10 @@
         </is>
       </c>
       <c r="H1585" s="2" t="n">
-        <v>46080.47898282779</v>
+        <v>46080.47898282408</v>
       </c>
       <c r="I1585" s="2" t="n">
-        <v>46085.47898282779</v>
+        <v>46085.47898282408</v>
       </c>
     </row>
     <row r="1586">
@@ -62288,10 +62288,10 @@
         </is>
       </c>
       <c r="H1586" s="2" t="n">
-        <v>46082.47898283097</v>
+        <v>46082.47898283565</v>
       </c>
       <c r="I1586" s="2" t="n">
-        <v>46087.47898283097</v>
+        <v>46087.47898283565</v>
       </c>
     </row>
     <row r="1587">
@@ -62327,10 +62327,10 @@
         </is>
       </c>
       <c r="H1587" s="2" t="n">
-        <v>46067.47898283407</v>
+        <v>46067.47898283565</v>
       </c>
       <c r="I1587" s="2" t="n">
-        <v>46072.47898283407</v>
+        <v>46072.47898283565</v>
       </c>
     </row>
     <row r="1588">
@@ -62366,10 +62366,10 @@
         </is>
       </c>
       <c r="H1588" s="2" t="n">
-        <v>46082.47898283718</v>
+        <v>46082.47898283565</v>
       </c>
       <c r="I1588" s="2" t="n">
-        <v>46087.47898283718</v>
+        <v>46087.47898283565</v>
       </c>
     </row>
     <row r="1589">
@@ -62405,10 +62405,10 @@
         </is>
       </c>
       <c r="H1589" s="2" t="n">
-        <v>46064.47898284043</v>
+        <v>46064.47898283565</v>
       </c>
       <c r="I1589" s="2" t="n">
-        <v>46069.47898284043</v>
+        <v>46069.47898283565</v>
       </c>
     </row>
     <row r="1590">
@@ -62444,10 +62444,10 @@
         </is>
       </c>
       <c r="H1590" s="2" t="n">
-        <v>46070.47898284357</v>
+        <v>46070.47898284722</v>
       </c>
       <c r="I1590" s="2" t="n">
-        <v>46075.47898284357</v>
+        <v>46075.47898284722</v>
       </c>
     </row>
     <row r="1591">
@@ -62483,10 +62483,10 @@
         </is>
       </c>
       <c r="H1591" s="2" t="n">
-        <v>46071.47898284667</v>
+        <v>46071.47898284722</v>
       </c>
       <c r="I1591" s="2" t="n">
-        <v>46076.47898284667</v>
+        <v>46076.47898284722</v>
       </c>
     </row>
     <row r="1592">
@@ -62522,10 +62522,10 @@
         </is>
       </c>
       <c r="H1592" s="2" t="n">
-        <v>46075.4789828499</v>
+        <v>46075.47898284722</v>
       </c>
       <c r="I1592" s="2" t="n">
-        <v>46080.4789828499</v>
+        <v>46080.47898284722</v>
       </c>
     </row>
     <row r="1593">
@@ -62561,10 +62561,10 @@
         </is>
       </c>
       <c r="H1593" s="2" t="n">
-        <v>46080.47898285292</v>
+        <v>46080.47898284722</v>
       </c>
       <c r="I1593" s="2" t="n">
-        <v>46085.47898285292</v>
+        <v>46085.47898284722</v>
       </c>
     </row>
     <row r="1594">
@@ -62600,10 +62600,10 @@
         </is>
       </c>
       <c r="H1594" s="2" t="n">
-        <v>46067.4789828561</v>
+        <v>46067.4789828588</v>
       </c>
       <c r="I1594" s="2" t="n">
-        <v>46072.4789828561</v>
+        <v>46072.4789828588</v>
       </c>
     </row>
     <row r="1595">
@@ -62639,10 +62639,10 @@
         </is>
       </c>
       <c r="H1595" s="2" t="n">
-        <v>46086.47898285909</v>
+        <v>46086.4789828588</v>
       </c>
       <c r="I1595" s="2" t="n">
-        <v>46091.47898285909</v>
+        <v>46091.4789828588</v>
       </c>
     </row>
     <row r="1596">
@@ -62678,10 +62678,10 @@
         </is>
       </c>
       <c r="H1596" s="2" t="n">
-        <v>46076.47898286287</v>
+        <v>46076.4789828588</v>
       </c>
       <c r="I1596" s="2" t="n">
-        <v>46081.47898286287</v>
+        <v>46081.4789828588</v>
       </c>
     </row>
     <row r="1597">
@@ -62717,10 +62717,10 @@
         </is>
       </c>
       <c r="H1597" s="2" t="n">
-        <v>46078.47898286609</v>
+        <v>46078.47898287037</v>
       </c>
       <c r="I1597" s="2" t="n">
-        <v>46083.47898286609</v>
+        <v>46083.47898287037</v>
       </c>
     </row>
     <row r="1598">
@@ -62756,10 +62756,10 @@
         </is>
       </c>
       <c r="H1598" s="2" t="n">
-        <v>46088.47898286908</v>
+        <v>46088.47898287037</v>
       </c>
       <c r="I1598" s="2" t="n">
-        <v>46093.47898286908</v>
+        <v>46093.47898287037</v>
       </c>
     </row>
     <row r="1599">
@@ -62795,10 +62795,10 @@
         </is>
       </c>
       <c r="H1599" s="2" t="n">
-        <v>46076.47898287233</v>
+        <v>46076.47898287037</v>
       </c>
       <c r="I1599" s="2" t="n">
-        <v>46081.47898287233</v>
+        <v>46081.47898287037</v>
       </c>
     </row>
     <row r="1600">
@@ -62834,10 +62834,10 @@
         </is>
       </c>
       <c r="H1600" s="2" t="n">
-        <v>46075.47898287535</v>
+        <v>46075.47898287037</v>
       </c>
       <c r="I1600" s="2" t="n">
-        <v>46080.47898287535</v>
+        <v>46080.47898287037</v>
       </c>
     </row>
     <row r="1601">
@@ -62873,10 +62873,1960 @@
         </is>
       </c>
       <c r="H1601" s="2" t="n">
-        <v>46083.47898287953</v>
+        <v>46083.47898288194</v>
       </c>
       <c r="I1601" s="2" t="n">
-        <v>46088.47898287953</v>
+        <v>46088.47898288194</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>ea1ade11-e0de-457b-bd14-dba10e5b8df1</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1602" t="n">
+        <v>1996.19</v>
+      </c>
+      <c r="D1602" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1602" s="2" t="n">
+        <v>46061.52871142534</v>
+      </c>
+      <c r="I1602" s="2" t="n">
+        <v>46066.52871142534</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2f64b978-cdb5-4011-805c-affa8505dcc3</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1603" t="n">
+        <v>2551.81</v>
+      </c>
+      <c r="D1603" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1603" s="2" t="n">
+        <v>46088.52871142949</v>
+      </c>
+      <c r="I1603" s="2" t="n">
+        <v>46093.52871142949</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>f8ebd807-a83d-48ef-922f-350303dc643c</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1604" t="n">
+        <v>6021.83</v>
+      </c>
+      <c r="D1604" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1604" s="2" t="n">
+        <v>46081.52871143267</v>
+      </c>
+      <c r="I1604" s="2" t="n">
+        <v>46086.52871143267</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>d2644b10-1e36-4b4c-baea-73611e153056</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1605" t="n">
+        <v>6003.48</v>
+      </c>
+      <c r="D1605" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1605" s="2" t="n">
+        <v>46082.52871143596</v>
+      </c>
+      <c r="I1605" s="2" t="n">
+        <v>46087.52871143596</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>165c2050-dd0b-4d08-bac7-cd9b837c7876</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1606" t="n">
+        <v>5581.73</v>
+      </c>
+      <c r="D1606" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1606" s="2" t="n">
+        <v>46068.52871143886</v>
+      </c>
+      <c r="I1606" s="2" t="n">
+        <v>46073.52871143886</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2397a646-3569-4429-9221-ca160cf56935</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1607" t="n">
+        <v>8510.469999999999</v>
+      </c>
+      <c r="D1607" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1607" s="2" t="n">
+        <v>46073.52871144184</v>
+      </c>
+      <c r="I1607" s="2" t="n">
+        <v>46078.52871144184</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>4ccf7ba1-aab8-4a4f-8072-14e2df78904b</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1608" t="n">
+        <v>5102.25</v>
+      </c>
+      <c r="D1608" t="n">
+        <v>97.73999999999999</v>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1608" s="2" t="n">
+        <v>46086.52871144508</v>
+      </c>
+      <c r="I1608" s="2" t="n">
+        <v>46091.52871144508</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>aac7b5b9-d2a6-44af-a9ce-62e197ef6ba1</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1609" t="n">
+        <v>4538.53</v>
+      </c>
+      <c r="D1609" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1609" s="2" t="n">
+        <v>46084.52871144808</v>
+      </c>
+      <c r="I1609" s="2" t="n">
+        <v>46089.52871144808</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>4a8b5bcc-e2e2-4ae4-b750-f12a8a0403e3</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1610" t="n">
+        <v>9917.219999999999</v>
+      </c>
+      <c r="D1610" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1610" s="2" t="n">
+        <v>46079.52871145105</v>
+      </c>
+      <c r="I1610" s="2" t="n">
+        <v>46084.52871145105</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>4f444683-952d-4d16-9cbf-471e4f5ea548</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1611" t="n">
+        <v>7341.71</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1611" s="2" t="n">
+        <v>46081.52871145396</v>
+      </c>
+      <c r="I1611" s="2" t="n">
+        <v>46086.52871145396</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>c6ef6f80-7d7a-4c78-82ad-cdb3b898be49</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1612" t="n">
+        <v>1548.61</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1612" s="2" t="n">
+        <v>46083.52871145712</v>
+      </c>
+      <c r="I1612" s="2" t="n">
+        <v>46088.52871145712</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>324a63d0-6a77-4c68-b7fc-b0ed62bdf894</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1613" t="n">
+        <v>5158.01</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1613" s="2" t="n">
+        <v>46081.52871145992</v>
+      </c>
+      <c r="I1613" s="2" t="n">
+        <v>46086.52871145992</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>b231d7f9-304a-49b2-aa3f-26c8dc5ca713</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1614" t="n">
+        <v>3618.48</v>
+      </c>
+      <c r="D1614" t="n">
+        <v>87.59</v>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1614" s="2" t="n">
+        <v>46068.52871146292</v>
+      </c>
+      <c r="I1614" s="2" t="n">
+        <v>46073.52871146292</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>51b23182-54fe-408e-b79d-d8a6767491c5</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1615" t="n">
+        <v>5549.1</v>
+      </c>
+      <c r="D1615" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1615" s="2" t="n">
+        <v>46082.52871146572</v>
+      </c>
+      <c r="I1615" s="2" t="n">
+        <v>46087.52871146572</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>68d2577e-a351-4963-9504-73eed23780b8</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1616" t="n">
+        <v>2320.72</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1616" s="2" t="n">
+        <v>46072.5287114687</v>
+      </c>
+      <c r="I1616" s="2" t="n">
+        <v>46077.5287114687</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>5397d209-ec33-4d75-9188-edb617d2a6bd</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1617" t="n">
+        <v>7165.6</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>96.39</v>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1617" s="2" t="n">
+        <v>46068.52871147158</v>
+      </c>
+      <c r="I1617" s="2" t="n">
+        <v>46073.52871147158</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>00a450c1-b452-49f8-8ffd-44980fbab741</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1618" t="n">
+        <v>5407.32</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1618" s="2" t="n">
+        <v>46073.52871147444</v>
+      </c>
+      <c r="I1618" s="2" t="n">
+        <v>46078.52871147444</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>e5953e7c-def1-4859-9914-497d9e45a546</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1619" t="n">
+        <v>6404.31</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>94.59</v>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1619" s="2" t="n">
+        <v>46064.52871147732</v>
+      </c>
+      <c r="I1619" s="2" t="n">
+        <v>46069.52871147732</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>c8c49300-bf43-48b5-9dd4-c026dffbd8fa</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1620" t="n">
+        <v>5221.42</v>
+      </c>
+      <c r="D1620" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1620" s="2" t="n">
+        <v>46075.52871148023</v>
+      </c>
+      <c r="I1620" s="2" t="n">
+        <v>46080.52871148023</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>8d48a831-a3b9-4c65-a364-03f34843c89b</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1621" t="n">
+        <v>9681.34</v>
+      </c>
+      <c r="D1621" t="n">
+        <v>96.19</v>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1621" s="2" t="n">
+        <v>46065.52871148302</v>
+      </c>
+      <c r="I1621" s="2" t="n">
+        <v>46070.52871148302</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>062773b1-56d2-49db-b88f-9f97350a2fee</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1622" t="n">
+        <v>5597.9</v>
+      </c>
+      <c r="D1622" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1622" s="2" t="n">
+        <v>46063.5287114858</v>
+      </c>
+      <c r="I1622" s="2" t="n">
+        <v>46068.5287114858</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>cbac912c-7bac-4388-b743-45016096e1ab</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1623" t="n">
+        <v>9272.860000000001</v>
+      </c>
+      <c r="D1623" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1623" s="2" t="n">
+        <v>46087.52871148861</v>
+      </c>
+      <c r="I1623" s="2" t="n">
+        <v>46092.52871148861</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>d021f5b2-c8e6-46cc-b11f-b4a767296329</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1624" t="n">
+        <v>4850.3</v>
+      </c>
+      <c r="D1624" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1624" s="2" t="n">
+        <v>46066.52871149177</v>
+      </c>
+      <c r="I1624" s="2" t="n">
+        <v>46071.52871149177</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>749840f1-b431-4b26-9350-71270d4e85be</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1625" t="n">
+        <v>4006.5</v>
+      </c>
+      <c r="D1625" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1625" s="2" t="n">
+        <v>46065.52871149458</v>
+      </c>
+      <c r="I1625" s="2" t="n">
+        <v>46070.52871149458</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>235b0eee-0e97-4f9a-8430-ff35d8f66e2a</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1626" t="n">
+        <v>8656.700000000001</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1626" s="2" t="n">
+        <v>46066.5287114974</v>
+      </c>
+      <c r="I1626" s="2" t="n">
+        <v>46071.5287114974</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>1c55a946-2bc9-4634-8b87-664eb8bf4a22</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1627" t="n">
+        <v>6371.84</v>
+      </c>
+      <c r="D1627" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1627" s="2" t="n">
+        <v>46086.52871150037</v>
+      </c>
+      <c r="I1627" s="2" t="n">
+        <v>46091.52871150037</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>c4b2e4f1-5221-44c1-8fe7-fad95537e24c</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1628" t="n">
+        <v>5210.33</v>
+      </c>
+      <c r="D1628" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1628" s="2" t="n">
+        <v>46074.5287115035</v>
+      </c>
+      <c r="I1628" s="2" t="n">
+        <v>46079.5287115035</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>15d3c483-b65b-46bd-9541-fcf711d1c507</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1629" t="n">
+        <v>5589.86</v>
+      </c>
+      <c r="D1629" t="n">
+        <v>94.27</v>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1629" s="2" t="n">
+        <v>46087.52871150631</v>
+      </c>
+      <c r="I1629" s="2" t="n">
+        <v>46092.52871150631</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>bfaed988-53d0-48bb-8972-f6cd027f8079</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1630" t="n">
+        <v>9117.02</v>
+      </c>
+      <c r="D1630" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1630" s="2" t="n">
+        <v>46077.52871150919</v>
+      </c>
+      <c r="I1630" s="2" t="n">
+        <v>46082.52871150919</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2938f337-2cc1-4b8b-9a68-34337776f600</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1631" t="n">
+        <v>3374.58</v>
+      </c>
+      <c r="D1631" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1631" s="2" t="n">
+        <v>46073.52871151223</v>
+      </c>
+      <c r="I1631" s="2" t="n">
+        <v>46078.52871151223</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>9ef9153b-2e51-40d7-b1d4-a64e45d92077</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1632" t="n">
+        <v>2324.37</v>
+      </c>
+      <c r="D1632" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1632" s="2" t="n">
+        <v>46073.52871151535</v>
+      </c>
+      <c r="I1632" s="2" t="n">
+        <v>46078.52871151535</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>594bc6c5-c9d8-40cd-9c24-17d7a0085ab8</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1633" t="n">
+        <v>9545.24</v>
+      </c>
+      <c r="D1633" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1633" s="2" t="n">
+        <v>46088.52871151811</v>
+      </c>
+      <c r="I1633" s="2" t="n">
+        <v>46093.52871151811</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>7977ee2c-bae1-4870-8b16-eef3e094461e</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1634" t="n">
+        <v>4070.69</v>
+      </c>
+      <c r="D1634" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1634" s="2" t="n">
+        <v>46073.52871152103</v>
+      </c>
+      <c r="I1634" s="2" t="n">
+        <v>46078.52871152103</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>e2e2de27-e4b9-43d0-9ddd-802346c4d403</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1635" t="n">
+        <v>4830.04</v>
+      </c>
+      <c r="D1635" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1635" s="2" t="n">
+        <v>46069.52871152383</v>
+      </c>
+      <c r="I1635" s="2" t="n">
+        <v>46074.52871152383</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>5e3e0231-2d14-411e-9b47-bca184c4aa5d</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>1948.22</v>
+      </c>
+      <c r="D1636" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1636" s="2" t="n">
+        <v>46080.52871152671</v>
+      </c>
+      <c r="I1636" s="2" t="n">
+        <v>46085.52871152671</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>27d2ecc2-69db-4819-b606-b41d0bf486d8</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>8778.5</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1637" s="2" t="n">
+        <v>46061.52871152961</v>
+      </c>
+      <c r="I1637" s="2" t="n">
+        <v>46066.52871152961</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>91b3022c-da7f-4b4e-a964-ba8a9a2a95ef</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>7596</v>
+      </c>
+      <c r="D1638" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1638" s="2" t="n">
+        <v>46064.52871153236</v>
+      </c>
+      <c r="I1638" s="2" t="n">
+        <v>46069.52871153236</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>af96b77e-68de-48a0-82dc-fc97c9fe0e3b</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>2937.92</v>
+      </c>
+      <c r="D1639" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1639" s="2" t="n">
+        <v>46084.52871153516</v>
+      </c>
+      <c r="I1639" s="2" t="n">
+        <v>46089.52871153516</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>da937882-1298-4b84-b4fc-4964515d2ee7</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>8022.6</v>
+      </c>
+      <c r="D1640" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1640" s="2" t="n">
+        <v>46067.52871153837</v>
+      </c>
+      <c r="I1640" s="2" t="n">
+        <v>46072.52871153837</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>ff95a6ca-c245-4299-af48-ed8c1e7d27b0</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>9767.4</v>
+      </c>
+      <c r="D1641" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1641" s="2" t="n">
+        <v>46073.52871154116</v>
+      </c>
+      <c r="I1641" s="2" t="n">
+        <v>46078.52871154116</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>df7f5860-c639-4c07-aa2a-1ea062c086d4</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>9437.790000000001</v>
+      </c>
+      <c r="D1642" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1642" s="2" t="n">
+        <v>46068.52871154391</v>
+      </c>
+      <c r="I1642" s="2" t="n">
+        <v>46073.52871154391</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>9c88d087-aae5-4e0b-a32a-c2e7825f72ac</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>7688.97</v>
+      </c>
+      <c r="D1643" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1643" s="2" t="n">
+        <v>46065.52871154668</v>
+      </c>
+      <c r="I1643" s="2" t="n">
+        <v>46070.52871154668</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>e985b288-8447-478e-9c29-dee339fc3912</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>8149.56</v>
+      </c>
+      <c r="D1644" t="n">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1644" s="2" t="n">
+        <v>46081.52871154983</v>
+      </c>
+      <c r="I1644" s="2" t="n">
+        <v>46086.52871154983</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>aec046df-5801-45ed-9d71-b6210c999eeb</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>7691.32</v>
+      </c>
+      <c r="D1645" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1645" s="2" t="n">
+        <v>46071.52871155273</v>
+      </c>
+      <c r="I1645" s="2" t="n">
+        <v>46076.52871155273</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>518bf301-5c1c-48a3-b60c-60db3add2b43</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>4005.85</v>
+      </c>
+      <c r="D1646" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1646" s="2" t="n">
+        <v>46069.52871155555</v>
+      </c>
+      <c r="I1646" s="2" t="n">
+        <v>46074.52871155555</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>30f5a114-3f55-43c7-8c20-7b493195a827</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>5248.23</v>
+      </c>
+      <c r="D1647" t="n">
+        <v>91.39</v>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1647" s="2" t="n">
+        <v>46065.52871155843</v>
+      </c>
+      <c r="I1647" s="2" t="n">
+        <v>46070.52871155843</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>859f9a02-9e1c-40da-b029-149d2e1b2c24</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>6289.1</v>
+      </c>
+      <c r="D1648" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1648" s="2" t="n">
+        <v>46086.52871156127</v>
+      </c>
+      <c r="I1648" s="2" t="n">
+        <v>46091.52871156127</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>8c7dcd58-00b9-44fe-b999-e3a10c1a0d40</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>2639.53</v>
+      </c>
+      <c r="D1649" t="n">
+        <v>90.77</v>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1649" s="2" t="n">
+        <v>46075.52871156417</v>
+      </c>
+      <c r="I1649" s="2" t="n">
+        <v>46080.52871156417</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>6c1a0323-a6f9-4d7a-8282-fee59517b9fc</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>4131.95</v>
+      </c>
+      <c r="D1650" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1650" s="2" t="n">
+        <v>46083.52871156701</v>
+      </c>
+      <c r="I1650" s="2" t="n">
+        <v>46088.52871156701</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>3db46911-742e-4c93-b385-83fa04a7b668</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>7395.52</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1651" s="2" t="n">
+        <v>46061.5287115698</v>
+      </c>
+      <c r="I1651" s="2" t="n">
+        <v>46066.5287115698</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1651"/>
+  <dimension ref="A1:I1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62912,10 +62912,10 @@
         </is>
       </c>
       <c r="H1602" s="2" t="n">
-        <v>46061.52871142534</v>
+        <v>46061.52871142361</v>
       </c>
       <c r="I1602" s="2" t="n">
-        <v>46066.52871142534</v>
+        <v>46066.52871142361</v>
       </c>
     </row>
     <row r="1603">
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="H1603" s="2" t="n">
-        <v>46088.52871142949</v>
+        <v>46088.52871143519</v>
       </c>
       <c r="I1603" s="2" t="n">
-        <v>46093.52871142949</v>
+        <v>46093.52871143519</v>
       </c>
     </row>
     <row r="1604">
@@ -62990,10 +62990,10 @@
         </is>
       </c>
       <c r="H1604" s="2" t="n">
-        <v>46081.52871143267</v>
+        <v>46081.52871143519</v>
       </c>
       <c r="I1604" s="2" t="n">
-        <v>46086.52871143267</v>
+        <v>46086.52871143519</v>
       </c>
     </row>
     <row r="1605">
@@ -63029,10 +63029,10 @@
         </is>
       </c>
       <c r="H1605" s="2" t="n">
-        <v>46082.52871143596</v>
+        <v>46082.52871143519</v>
       </c>
       <c r="I1605" s="2" t="n">
-        <v>46087.52871143596</v>
+        <v>46087.52871143519</v>
       </c>
     </row>
     <row r="1606">
@@ -63068,10 +63068,10 @@
         </is>
       </c>
       <c r="H1606" s="2" t="n">
-        <v>46068.52871143886</v>
+        <v>46068.52871143519</v>
       </c>
       <c r="I1606" s="2" t="n">
-        <v>46073.52871143886</v>
+        <v>46073.52871143519</v>
       </c>
     </row>
     <row r="1607">
@@ -63107,10 +63107,10 @@
         </is>
       </c>
       <c r="H1607" s="2" t="n">
-        <v>46073.52871144184</v>
+        <v>46073.52871144676</v>
       </c>
       <c r="I1607" s="2" t="n">
-        <v>46078.52871144184</v>
+        <v>46078.52871144676</v>
       </c>
     </row>
     <row r="1608">
@@ -63146,10 +63146,10 @@
         </is>
       </c>
       <c r="H1608" s="2" t="n">
-        <v>46086.52871144508</v>
+        <v>46086.52871144676</v>
       </c>
       <c r="I1608" s="2" t="n">
-        <v>46091.52871144508</v>
+        <v>46091.52871144676</v>
       </c>
     </row>
     <row r="1609">
@@ -63185,10 +63185,10 @@
         </is>
       </c>
       <c r="H1609" s="2" t="n">
-        <v>46084.52871144808</v>
+        <v>46084.52871144676</v>
       </c>
       <c r="I1609" s="2" t="n">
-        <v>46089.52871144808</v>
+        <v>46089.52871144676</v>
       </c>
     </row>
     <row r="1610">
@@ -63224,10 +63224,10 @@
         </is>
       </c>
       <c r="H1610" s="2" t="n">
-        <v>46079.52871145105</v>
+        <v>46079.52871144676</v>
       </c>
       <c r="I1610" s="2" t="n">
-        <v>46084.52871145105</v>
+        <v>46084.52871144676</v>
       </c>
     </row>
     <row r="1611">
@@ -63263,10 +63263,10 @@
         </is>
       </c>
       <c r="H1611" s="2" t="n">
-        <v>46081.52871145396</v>
+        <v>46081.52871145833</v>
       </c>
       <c r="I1611" s="2" t="n">
-        <v>46086.52871145396</v>
+        <v>46086.52871145833</v>
       </c>
     </row>
     <row r="1612">
@@ -63302,10 +63302,10 @@
         </is>
       </c>
       <c r="H1612" s="2" t="n">
-        <v>46083.52871145712</v>
+        <v>46083.52871145833</v>
       </c>
       <c r="I1612" s="2" t="n">
-        <v>46088.52871145712</v>
+        <v>46088.52871145833</v>
       </c>
     </row>
     <row r="1613">
@@ -63341,10 +63341,10 @@
         </is>
       </c>
       <c r="H1613" s="2" t="n">
-        <v>46081.52871145992</v>
+        <v>46081.52871145833</v>
       </c>
       <c r="I1613" s="2" t="n">
-        <v>46086.52871145992</v>
+        <v>46086.52871145833</v>
       </c>
     </row>
     <row r="1614">
@@ -63380,10 +63380,10 @@
         </is>
       </c>
       <c r="H1614" s="2" t="n">
-        <v>46068.52871146292</v>
+        <v>46068.52871145833</v>
       </c>
       <c r="I1614" s="2" t="n">
-        <v>46073.52871146292</v>
+        <v>46073.52871145833</v>
       </c>
     </row>
     <row r="1615">
@@ -63419,10 +63419,10 @@
         </is>
       </c>
       <c r="H1615" s="2" t="n">
-        <v>46082.52871146572</v>
+        <v>46082.52871146991</v>
       </c>
       <c r="I1615" s="2" t="n">
-        <v>46087.52871146572</v>
+        <v>46087.52871146991</v>
       </c>
     </row>
     <row r="1616">
@@ -63458,10 +63458,10 @@
         </is>
       </c>
       <c r="H1616" s="2" t="n">
-        <v>46072.5287114687</v>
+        <v>46072.52871146991</v>
       </c>
       <c r="I1616" s="2" t="n">
-        <v>46077.5287114687</v>
+        <v>46077.52871146991</v>
       </c>
     </row>
     <row r="1617">
@@ -63497,10 +63497,10 @@
         </is>
       </c>
       <c r="H1617" s="2" t="n">
-        <v>46068.52871147158</v>
+        <v>46068.52871146991</v>
       </c>
       <c r="I1617" s="2" t="n">
-        <v>46073.52871147158</v>
+        <v>46073.52871146991</v>
       </c>
     </row>
     <row r="1618">
@@ -63536,10 +63536,10 @@
         </is>
       </c>
       <c r="H1618" s="2" t="n">
-        <v>46073.52871147444</v>
+        <v>46073.52871146991</v>
       </c>
       <c r="I1618" s="2" t="n">
-        <v>46078.52871147444</v>
+        <v>46078.52871146991</v>
       </c>
     </row>
     <row r="1619">
@@ -63575,10 +63575,10 @@
         </is>
       </c>
       <c r="H1619" s="2" t="n">
-        <v>46064.52871147732</v>
+        <v>46064.52871148148</v>
       </c>
       <c r="I1619" s="2" t="n">
-        <v>46069.52871147732</v>
+        <v>46069.52871148148</v>
       </c>
     </row>
     <row r="1620">
@@ -63614,10 +63614,10 @@
         </is>
       </c>
       <c r="H1620" s="2" t="n">
-        <v>46075.52871148023</v>
+        <v>46075.52871148148</v>
       </c>
       <c r="I1620" s="2" t="n">
-        <v>46080.52871148023</v>
+        <v>46080.52871148148</v>
       </c>
     </row>
     <row r="1621">
@@ -63653,10 +63653,10 @@
         </is>
       </c>
       <c r="H1621" s="2" t="n">
-        <v>46065.52871148302</v>
+        <v>46065.52871148148</v>
       </c>
       <c r="I1621" s="2" t="n">
-        <v>46070.52871148302</v>
+        <v>46070.52871148148</v>
       </c>
     </row>
     <row r="1622">
@@ -63692,10 +63692,10 @@
         </is>
       </c>
       <c r="H1622" s="2" t="n">
-        <v>46063.5287114858</v>
+        <v>46063.52871148148</v>
       </c>
       <c r="I1622" s="2" t="n">
-        <v>46068.5287114858</v>
+        <v>46068.52871148148</v>
       </c>
     </row>
     <row r="1623">
@@ -63731,10 +63731,10 @@
         </is>
       </c>
       <c r="H1623" s="2" t="n">
-        <v>46087.52871148861</v>
+        <v>46087.52871149305</v>
       </c>
       <c r="I1623" s="2" t="n">
-        <v>46092.52871148861</v>
+        <v>46092.52871149305</v>
       </c>
     </row>
     <row r="1624">
@@ -63770,10 +63770,10 @@
         </is>
       </c>
       <c r="H1624" s="2" t="n">
-        <v>46066.52871149177</v>
+        <v>46066.52871149305</v>
       </c>
       <c r="I1624" s="2" t="n">
-        <v>46071.52871149177</v>
+        <v>46071.52871149305</v>
       </c>
     </row>
     <row r="1625">
@@ -63809,10 +63809,10 @@
         </is>
       </c>
       <c r="H1625" s="2" t="n">
-        <v>46065.52871149458</v>
+        <v>46065.52871149305</v>
       </c>
       <c r="I1625" s="2" t="n">
-        <v>46070.52871149458</v>
+        <v>46070.52871149305</v>
       </c>
     </row>
     <row r="1626">
@@ -63848,10 +63848,10 @@
         </is>
       </c>
       <c r="H1626" s="2" t="n">
-        <v>46066.5287114974</v>
+        <v>46066.52871149305</v>
       </c>
       <c r="I1626" s="2" t="n">
-        <v>46071.5287114974</v>
+        <v>46071.52871149305</v>
       </c>
     </row>
     <row r="1627">
@@ -63887,10 +63887,10 @@
         </is>
       </c>
       <c r="H1627" s="2" t="n">
-        <v>46086.52871150037</v>
+        <v>46086.52871150463</v>
       </c>
       <c r="I1627" s="2" t="n">
-        <v>46091.52871150037</v>
+        <v>46091.52871150463</v>
       </c>
     </row>
     <row r="1628">
@@ -63926,10 +63926,10 @@
         </is>
       </c>
       <c r="H1628" s="2" t="n">
-        <v>46074.5287115035</v>
+        <v>46074.52871150463</v>
       </c>
       <c r="I1628" s="2" t="n">
-        <v>46079.5287115035</v>
+        <v>46079.52871150463</v>
       </c>
     </row>
     <row r="1629">
@@ -63965,10 +63965,10 @@
         </is>
       </c>
       <c r="H1629" s="2" t="n">
-        <v>46087.52871150631</v>
+        <v>46087.52871150463</v>
       </c>
       <c r="I1629" s="2" t="n">
-        <v>46092.52871150631</v>
+        <v>46092.52871150463</v>
       </c>
     </row>
     <row r="1630">
@@ -64004,10 +64004,10 @@
         </is>
       </c>
       <c r="H1630" s="2" t="n">
-        <v>46077.52871150919</v>
+        <v>46077.52871150463</v>
       </c>
       <c r="I1630" s="2" t="n">
-        <v>46082.52871150919</v>
+        <v>46082.52871150463</v>
       </c>
     </row>
     <row r="1631">
@@ -64043,10 +64043,10 @@
         </is>
       </c>
       <c r="H1631" s="2" t="n">
-        <v>46073.52871151223</v>
+        <v>46073.52871151621</v>
       </c>
       <c r="I1631" s="2" t="n">
-        <v>46078.52871151223</v>
+        <v>46078.52871151621</v>
       </c>
     </row>
     <row r="1632">
@@ -64082,10 +64082,10 @@
         </is>
       </c>
       <c r="H1632" s="2" t="n">
-        <v>46073.52871151535</v>
+        <v>46073.52871151621</v>
       </c>
       <c r="I1632" s="2" t="n">
-        <v>46078.52871151535</v>
+        <v>46078.52871151621</v>
       </c>
     </row>
     <row r="1633">
@@ -64121,10 +64121,10 @@
         </is>
       </c>
       <c r="H1633" s="2" t="n">
-        <v>46088.52871151811</v>
+        <v>46088.52871151621</v>
       </c>
       <c r="I1633" s="2" t="n">
-        <v>46093.52871151811</v>
+        <v>46093.52871151621</v>
       </c>
     </row>
     <row r="1634">
@@ -64160,10 +64160,10 @@
         </is>
       </c>
       <c r="H1634" s="2" t="n">
-        <v>46073.52871152103</v>
+        <v>46073.52871151621</v>
       </c>
       <c r="I1634" s="2" t="n">
-        <v>46078.52871152103</v>
+        <v>46078.52871151621</v>
       </c>
     </row>
     <row r="1635">
@@ -64199,10 +64199,10 @@
         </is>
       </c>
       <c r="H1635" s="2" t="n">
-        <v>46069.52871152383</v>
+        <v>46069.52871152778</v>
       </c>
       <c r="I1635" s="2" t="n">
-        <v>46074.52871152383</v>
+        <v>46074.52871152778</v>
       </c>
     </row>
     <row r="1636">
@@ -64238,10 +64238,10 @@
         </is>
       </c>
       <c r="H1636" s="2" t="n">
-        <v>46080.52871152671</v>
+        <v>46080.52871152778</v>
       </c>
       <c r="I1636" s="2" t="n">
-        <v>46085.52871152671</v>
+        <v>46085.52871152778</v>
       </c>
     </row>
     <row r="1637">
@@ -64277,10 +64277,10 @@
         </is>
       </c>
       <c r="H1637" s="2" t="n">
-        <v>46061.52871152961</v>
+        <v>46061.52871152778</v>
       </c>
       <c r="I1637" s="2" t="n">
-        <v>46066.52871152961</v>
+        <v>46066.52871152778</v>
       </c>
     </row>
     <row r="1638">
@@ -64316,10 +64316,10 @@
         </is>
       </c>
       <c r="H1638" s="2" t="n">
-        <v>46064.52871153236</v>
+        <v>46064.52871152778</v>
       </c>
       <c r="I1638" s="2" t="n">
-        <v>46069.52871153236</v>
+        <v>46069.52871152778</v>
       </c>
     </row>
     <row r="1639">
@@ -64355,10 +64355,10 @@
         </is>
       </c>
       <c r="H1639" s="2" t="n">
-        <v>46084.52871153516</v>
+        <v>46084.52871153935</v>
       </c>
       <c r="I1639" s="2" t="n">
-        <v>46089.52871153516</v>
+        <v>46089.52871153935</v>
       </c>
     </row>
     <row r="1640">
@@ -64394,10 +64394,10 @@
         </is>
       </c>
       <c r="H1640" s="2" t="n">
-        <v>46067.52871153837</v>
+        <v>46067.52871153935</v>
       </c>
       <c r="I1640" s="2" t="n">
-        <v>46072.52871153837</v>
+        <v>46072.52871153935</v>
       </c>
     </row>
     <row r="1641">
@@ -64433,10 +64433,10 @@
         </is>
       </c>
       <c r="H1641" s="2" t="n">
-        <v>46073.52871154116</v>
+        <v>46073.52871153935</v>
       </c>
       <c r="I1641" s="2" t="n">
-        <v>46078.52871154116</v>
+        <v>46078.52871153935</v>
       </c>
     </row>
     <row r="1642">
@@ -64472,10 +64472,10 @@
         </is>
       </c>
       <c r="H1642" s="2" t="n">
-        <v>46068.52871154391</v>
+        <v>46068.52871153935</v>
       </c>
       <c r="I1642" s="2" t="n">
-        <v>46073.52871154391</v>
+        <v>46073.52871153935</v>
       </c>
     </row>
     <row r="1643">
@@ -64511,10 +64511,10 @@
         </is>
       </c>
       <c r="H1643" s="2" t="n">
-        <v>46065.52871154668</v>
+        <v>46065.52871155093</v>
       </c>
       <c r="I1643" s="2" t="n">
-        <v>46070.52871154668</v>
+        <v>46070.52871155093</v>
       </c>
     </row>
     <row r="1644">
@@ -64550,10 +64550,10 @@
         </is>
       </c>
       <c r="H1644" s="2" t="n">
-        <v>46081.52871154983</v>
+        <v>46081.52871155093</v>
       </c>
       <c r="I1644" s="2" t="n">
-        <v>46086.52871154983</v>
+        <v>46086.52871155093</v>
       </c>
     </row>
     <row r="1645">
@@ -64589,10 +64589,10 @@
         </is>
       </c>
       <c r="H1645" s="2" t="n">
-        <v>46071.52871155273</v>
+        <v>46071.52871155093</v>
       </c>
       <c r="I1645" s="2" t="n">
-        <v>46076.52871155273</v>
+        <v>46076.52871155093</v>
       </c>
     </row>
     <row r="1646">
@@ -64628,10 +64628,10 @@
         </is>
       </c>
       <c r="H1646" s="2" t="n">
-        <v>46069.52871155555</v>
+        <v>46069.52871155093</v>
       </c>
       <c r="I1646" s="2" t="n">
-        <v>46074.52871155555</v>
+        <v>46074.52871155093</v>
       </c>
     </row>
     <row r="1647">
@@ -64667,10 +64667,10 @@
         </is>
       </c>
       <c r="H1647" s="2" t="n">
-        <v>46065.52871155843</v>
+        <v>46065.5287115625</v>
       </c>
       <c r="I1647" s="2" t="n">
-        <v>46070.52871155843</v>
+        <v>46070.5287115625</v>
       </c>
     </row>
     <row r="1648">
@@ -64706,10 +64706,10 @@
         </is>
       </c>
       <c r="H1648" s="2" t="n">
-        <v>46086.52871156127</v>
+        <v>46086.5287115625</v>
       </c>
       <c r="I1648" s="2" t="n">
-        <v>46091.52871156127</v>
+        <v>46091.5287115625</v>
       </c>
     </row>
     <row r="1649">
@@ -64745,10 +64745,10 @@
         </is>
       </c>
       <c r="H1649" s="2" t="n">
-        <v>46075.52871156417</v>
+        <v>46075.5287115625</v>
       </c>
       <c r="I1649" s="2" t="n">
-        <v>46080.52871156417</v>
+        <v>46080.5287115625</v>
       </c>
     </row>
     <row r="1650">
@@ -64784,10 +64784,10 @@
         </is>
       </c>
       <c r="H1650" s="2" t="n">
-        <v>46083.52871156701</v>
+        <v>46083.5287115625</v>
       </c>
       <c r="I1650" s="2" t="n">
-        <v>46088.52871156701</v>
+        <v>46088.5287115625</v>
       </c>
     </row>
     <row r="1651">
@@ -64823,10 +64823,1960 @@
         </is>
       </c>
       <c r="H1651" s="2" t="n">
-        <v>46061.5287115698</v>
+        <v>46061.52871157407</v>
       </c>
       <c r="I1651" s="2" t="n">
-        <v>46066.5287115698</v>
+        <v>46066.52871157407</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>57ab6d74-f2aa-4832-9eb1-6ff9d5bf8e3e</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>6461.81</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1652" s="2" t="n">
+        <v>46078.6785767574</v>
+      </c>
+      <c r="I1652" s="2" t="n">
+        <v>46083.6785767574</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>7923be07-ca5a-46e1-b54f-99074ef66e2c</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>1440.96</v>
+      </c>
+      <c r="D1653" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1653" s="2" t="n">
+        <v>46073.67857676251</v>
+      </c>
+      <c r="I1653" s="2" t="n">
+        <v>46078.67857676251</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>4d898aa9-1c65-4b1e-a54b-38b41cea9839</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>4999.68</v>
+      </c>
+      <c r="D1654" t="n">
+        <v>98.70999999999999</v>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1654" s="2" t="n">
+        <v>46081.67857676662</v>
+      </c>
+      <c r="I1654" s="2" t="n">
+        <v>46086.67857676662</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>06e330e3-42c6-473e-8b0c-5609d9c4fd34</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>8319.860000000001</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>89.47</v>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1655" s="2" t="n">
+        <v>46086.67857677013</v>
+      </c>
+      <c r="I1655" s="2" t="n">
+        <v>46091.67857677013</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>5dc314db-1ec4-4fca-a591-3f46528f9e14</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1656" t="n">
+        <v>4272.04</v>
+      </c>
+      <c r="D1656" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1656" s="2" t="n">
+        <v>46070.67857677327</v>
+      </c>
+      <c r="I1656" s="2" t="n">
+        <v>46075.67857677327</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>12e7c0d0-038c-4ca1-9dd4-1a58f374423f</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>6142.36</v>
+      </c>
+      <c r="D1657" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1657" s="2" t="n">
+        <v>46082.67857677677</v>
+      </c>
+      <c r="I1657" s="2" t="n">
+        <v>46087.67857677677</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>3320910b-fe0c-40dc-a6fa-b2621760955a</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>8661.879999999999</v>
+      </c>
+      <c r="D1658" t="n">
+        <v>87.97</v>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1658" s="2" t="n">
+        <v>46077.67857677994</v>
+      </c>
+      <c r="I1658" s="2" t="n">
+        <v>46082.67857677994</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>b85720b9-16f7-4d68-9800-f5099246c862</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1659" t="n">
+        <v>1787.65</v>
+      </c>
+      <c r="D1659" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1659" s="2" t="n">
+        <v>46087.67857678317</v>
+      </c>
+      <c r="I1659" s="2" t="n">
+        <v>46092.67857678317</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2562bd8c-c4ae-4098-af74-634b0c20a9bb</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1660" t="n">
+        <v>3887.96</v>
+      </c>
+      <c r="D1660" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1660" s="2" t="n">
+        <v>46067.67857678673</v>
+      </c>
+      <c r="I1660" s="2" t="n">
+        <v>46072.67857678673</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>b2043ac9-51b6-4436-9009-2b9441ec57c6</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1661" t="n">
+        <v>7622.72</v>
+      </c>
+      <c r="D1661" t="n">
+        <v>86.43000000000001</v>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1661" s="2" t="n">
+        <v>46060.67857678999</v>
+      </c>
+      <c r="I1661" s="2" t="n">
+        <v>46065.67857678999</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>b76145ac-2cca-45d8-8027-848e5228b265</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>1136.24</v>
+      </c>
+      <c r="D1662" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1662" s="2" t="n">
+        <v>46082.67857679319</v>
+      </c>
+      <c r="I1662" s="2" t="n">
+        <v>46087.67857679319</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>579b495e-6d4e-4dbb-83fa-211bcaafc3ed</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>2529.51</v>
+      </c>
+      <c r="D1663" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1663" s="2" t="n">
+        <v>46060.67857679647</v>
+      </c>
+      <c r="I1663" s="2" t="n">
+        <v>46065.67857679647</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>12f1af42-93ef-485d-9778-a762bc02b4ae</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1664" t="n">
+        <v>7382.88</v>
+      </c>
+      <c r="D1664" t="n">
+        <v>96.95999999999999</v>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1664" s="2" t="n">
+        <v>46078.67857679991</v>
+      </c>
+      <c r="I1664" s="2" t="n">
+        <v>46083.67857679991</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>9b060e97-5aeb-4ba9-9b1a-a0e6e69da063</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>5483.11</v>
+      </c>
+      <c r="D1665" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1665" s="2" t="n">
+        <v>46071.67857680303</v>
+      </c>
+      <c r="I1665" s="2" t="n">
+        <v>46076.67857680303</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>dfe14294-5675-4662-af29-698700b69859</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>8721.190000000001</v>
+      </c>
+      <c r="D1666" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1666" s="2" t="n">
+        <v>46074.67857680612</v>
+      </c>
+      <c r="I1666" s="2" t="n">
+        <v>46079.67857680612</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>69e7348b-c265-405c-b2f6-2dc28a3eec80</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>3789.39</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1667" s="2" t="n">
+        <v>46081.67857680971</v>
+      </c>
+      <c r="I1667" s="2" t="n">
+        <v>46086.67857680971</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>21084d39-cd0e-4b0a-8312-fe2471e2ad13</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>8023.56</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1668" s="2" t="n">
+        <v>46070.67857681295</v>
+      </c>
+      <c r="I1668" s="2" t="n">
+        <v>46075.67857681295</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>58878448-5c52-42eb-a195-866fa8bf7e52</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>4946.38</v>
+      </c>
+      <c r="D1669" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1669" s="2" t="n">
+        <v>46062.67857681617</v>
+      </c>
+      <c r="I1669" s="2" t="n">
+        <v>46067.67857681617</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>5c60f1ac-e406-4d09-8556-1b3ee905ebf8</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>9637.049999999999</v>
+      </c>
+      <c r="D1670" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1670" s="2" t="n">
+        <v>46070.67857681933</v>
+      </c>
+      <c r="I1670" s="2" t="n">
+        <v>46075.67857681933</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>ef6a45c5-4825-49f2-876f-92cb78724d7c</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>4450.38</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1671" s="2" t="n">
+        <v>46081.67857682281</v>
+      </c>
+      <c r="I1671" s="2" t="n">
+        <v>46086.67857682281</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>3ead2d53-4ccb-429b-a2a5-e7a68cee8e8a</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>8777.48</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1672" s="2" t="n">
+        <v>46070.67857682597</v>
+      </c>
+      <c r="I1672" s="2" t="n">
+        <v>46075.67857682597</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>0c5f752e-b73b-4645-bf37-c3bbfd9cb7d8</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>8805.66</v>
+      </c>
+      <c r="D1673" t="n">
+        <v>91.19</v>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1673" s="2" t="n">
+        <v>46065.67857682914</v>
+      </c>
+      <c r="I1673" s="2" t="n">
+        <v>46070.67857682914</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2449b7e5-78fc-40d4-b51c-7a641035fd87</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>2121.92</v>
+      </c>
+      <c r="D1674" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1674" s="2" t="n">
+        <v>46088.67857683254</v>
+      </c>
+      <c r="I1674" s="2" t="n">
+        <v>46093.67857683254</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>8fd0e957-b0e0-48c7-b5cb-937a005f8741</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>3001.28</v>
+      </c>
+      <c r="D1675" t="n">
+        <v>93.23999999999999</v>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1675" s="2" t="n">
+        <v>46071.67857683581</v>
+      </c>
+      <c r="I1675" s="2" t="n">
+        <v>46076.67857683581</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>c08bef1a-097c-4d6d-97ce-ace3a2036c13</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>1389.34</v>
+      </c>
+      <c r="D1676" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1676" s="2" t="n">
+        <v>46060.67857683908</v>
+      </c>
+      <c r="I1676" s="2" t="n">
+        <v>46065.67857683908</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>70dfe2fc-eeb1-43d9-929d-de1432f0debe</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>2640.45</v>
+      </c>
+      <c r="D1677" t="n">
+        <v>98.26000000000001</v>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1677" s="2" t="n">
+        <v>46061.67857684216</v>
+      </c>
+      <c r="I1677" s="2" t="n">
+        <v>46066.67857684216</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>d8df92f9-4a92-476f-b577-7ed831caf15b</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1678" t="n">
+        <v>2247.78</v>
+      </c>
+      <c r="D1678" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1678" s="2" t="n">
+        <v>46077.67857684576</v>
+      </c>
+      <c r="I1678" s="2" t="n">
+        <v>46082.67857684576</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>5e4c6806-f63b-48b6-bcb1-715e65bc82fe</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1679" t="n">
+        <v>8533.309999999999</v>
+      </c>
+      <c r="D1679" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1679" s="2" t="n">
+        <v>46072.67857684886</v>
+      </c>
+      <c r="I1679" s="2" t="n">
+        <v>46077.67857684886</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>6b6a2616-8905-478f-a523-6cc7cc7e9975</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1680" t="n">
+        <v>7284.44</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1680" s="2" t="n">
+        <v>46079.67857685211</v>
+      </c>
+      <c r="I1680" s="2" t="n">
+        <v>46084.67857685211</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>92459525-16a6-4d67-805f-6fdf96fcf29d</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1681" t="n">
+        <v>4691.67</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1681" s="2" t="n">
+        <v>46070.67857685585</v>
+      </c>
+      <c r="I1681" s="2" t="n">
+        <v>46075.67857685585</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>b063787e-7684-48c6-9c66-b68552a50c2a</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1682" t="n">
+        <v>5547.64</v>
+      </c>
+      <c r="D1682" t="n">
+        <v>93.63</v>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1682" s="2" t="n">
+        <v>46076.67857685918</v>
+      </c>
+      <c r="I1682" s="2" t="n">
+        <v>46081.67857685918</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>ef2bb356-22ba-4a69-b6bd-474dbcd2bfda</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1683" t="n">
+        <v>2539.48</v>
+      </c>
+      <c r="D1683" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1683" s="2" t="n">
+        <v>46079.67857686226</v>
+      </c>
+      <c r="I1683" s="2" t="n">
+        <v>46084.67857686226</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>c7dd6d71-5a7a-4f0d-a69b-881815587ddf</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1684" t="n">
+        <v>1922.63</v>
+      </c>
+      <c r="D1684" t="n">
+        <v>86.13</v>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1684" s="2" t="n">
+        <v>46082.67857686542</v>
+      </c>
+      <c r="I1684" s="2" t="n">
+        <v>46087.67857686542</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>1b9426e0-dc1d-49ec-bb71-5dc56c29d85d</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1685" t="n">
+        <v>1581.94</v>
+      </c>
+      <c r="D1685" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1685" s="2" t="n">
+        <v>46076.67857686911</v>
+      </c>
+      <c r="I1685" s="2" t="n">
+        <v>46081.67857686911</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>260bc29a-d52a-43f3-ab31-c7a7ef019d16</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1686" t="n">
+        <v>9614.66</v>
+      </c>
+      <c r="D1686" t="n">
+        <v>89.34</v>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1686" s="2" t="n">
+        <v>46087.67857687221</v>
+      </c>
+      <c r="I1686" s="2" t="n">
+        <v>46092.67857687221</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>06bab144-a675-4a7d-bd87-79014aedc371</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1687" t="n">
+        <v>3994.69</v>
+      </c>
+      <c r="D1687" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1687" s="2" t="n">
+        <v>46078.67857687533</v>
+      </c>
+      <c r="I1687" s="2" t="n">
+        <v>46083.67857687533</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>4a697c78-2548-4eec-be93-c019ec24998b</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1688" t="n">
+        <v>4337.76</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>86.97</v>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1688" s="2" t="n">
+        <v>46069.67857687834</v>
+      </c>
+      <c r="I1688" s="2" t="n">
+        <v>46074.67857687834</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>794b3f5d-2b87-45f8-9f5d-540c3ccbb0c9</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1689" t="n">
+        <v>8125.26</v>
+      </c>
+      <c r="D1689" t="n">
+        <v>90.56</v>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1689" s="2" t="n">
+        <v>46076.67857688169</v>
+      </c>
+      <c r="I1689" s="2" t="n">
+        <v>46081.67857688169</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>dd2423ec-5c50-4b40-8941-591a214a1726</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1690" t="n">
+        <v>4578.42</v>
+      </c>
+      <c r="D1690" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1690" s="2" t="n">
+        <v>46079.67857688489</v>
+      </c>
+      <c r="I1690" s="2" t="n">
+        <v>46084.67857688489</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>99b9ea5f-acab-42d1-a108-88ca690492f9</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1691" t="n">
+        <v>5085.58</v>
+      </c>
+      <c r="D1691" t="n">
+        <v>96.16</v>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1691" s="2" t="n">
+        <v>46080.67857688816</v>
+      </c>
+      <c r="I1691" s="2" t="n">
+        <v>46085.67857688816</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>4a4bd5ff-b415-4f34-ac73-d84b8e657757</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1692" t="n">
+        <v>6291.8</v>
+      </c>
+      <c r="D1692" t="n">
+        <v>96.41</v>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1692" s="2" t="n">
+        <v>46088.67857689153</v>
+      </c>
+      <c r="I1692" s="2" t="n">
+        <v>46093.67857689153</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>0f9bc35e-a2cd-4f1d-8d76-3e1d23bf416b</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1693" t="n">
+        <v>5052.95</v>
+      </c>
+      <c r="D1693" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1693" s="2" t="n">
+        <v>46070.67857689474</v>
+      </c>
+      <c r="I1693" s="2" t="n">
+        <v>46075.67857689474</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>1d279b40-4d75-4083-8567-f2de1634e430</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1694" t="n">
+        <v>7112.84</v>
+      </c>
+      <c r="D1694" t="n">
+        <v>89.11</v>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1694" s="2" t="n">
+        <v>46087.67857689804</v>
+      </c>
+      <c r="I1694" s="2" t="n">
+        <v>46092.67857689804</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2fb1608f-059c-42f9-8705-575d4c58a877</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1695" t="n">
+        <v>7704.7</v>
+      </c>
+      <c r="D1695" t="n">
+        <v>91.19</v>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1695" s="2" t="n">
+        <v>46075.67857690123</v>
+      </c>
+      <c r="I1695" s="2" t="n">
+        <v>46080.67857690123</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>c1eef5b2-75f6-43b0-b8e6-461d99ac512b</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1696" t="n">
+        <v>6180.46</v>
+      </c>
+      <c r="D1696" t="n">
+        <v>91.37</v>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1696" s="2" t="n">
+        <v>46065.67857690503</v>
+      </c>
+      <c r="I1696" s="2" t="n">
+        <v>46070.67857690503</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>949ebc06-2a8a-4987-a932-6fd616a8aa81</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1697" t="n">
+        <v>9639.93</v>
+      </c>
+      <c r="D1697" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1697" s="2" t="n">
+        <v>46067.67857690811</v>
+      </c>
+      <c r="I1697" s="2" t="n">
+        <v>46072.67857690811</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>6a1a7d08-fada-4ce2-a11f-5245489f4c6f</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1698" t="n">
+        <v>9215.049999999999</v>
+      </c>
+      <c r="D1698" t="n">
+        <v>98.61</v>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1698" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1698" s="2" t="n">
+        <v>46083.6785769113</v>
+      </c>
+      <c r="I1698" s="2" t="n">
+        <v>46088.6785769113</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>944c66d7-f53a-4cd6-9511-159698cd4419</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1699" t="n">
+        <v>9732</v>
+      </c>
+      <c r="D1699" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1699" s="2" t="n">
+        <v>46087.67857691492</v>
+      </c>
+      <c r="I1699" s="2" t="n">
+        <v>46092.67857691492</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>41a4f48d-0e68-4c42-9660-515a903adaa2</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1700" t="n">
+        <v>9108.360000000001</v>
+      </c>
+      <c r="D1700" t="n">
+        <v>86.83</v>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1700" s="2" t="n">
+        <v>46084.6785769181</v>
+      </c>
+      <c r="I1700" s="2" t="n">
+        <v>46089.6785769181</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>973218a7-b805-4dfb-8a1b-df529cffde50</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1701" t="n">
+        <v>9447.33</v>
+      </c>
+      <c r="D1701" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1701" s="2" t="n">
+        <v>46080.67857692132</v>
+      </c>
+      <c r="I1701" s="2" t="n">
+        <v>46085.67857692132</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1701"/>
+  <dimension ref="A1:I1751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64862,10 +64862,10 @@
         </is>
       </c>
       <c r="H1652" s="2" t="n">
-        <v>46078.6785767574</v>
+        <v>46078.67857675926</v>
       </c>
       <c r="I1652" s="2" t="n">
-        <v>46083.6785767574</v>
+        <v>46083.67857675926</v>
       </c>
     </row>
     <row r="1653">
@@ -64901,10 +64901,10 @@
         </is>
       </c>
       <c r="H1653" s="2" t="n">
-        <v>46073.67857676251</v>
+        <v>46073.67857675926</v>
       </c>
       <c r="I1653" s="2" t="n">
-        <v>46078.67857676251</v>
+        <v>46078.67857675926</v>
       </c>
     </row>
     <row r="1654">
@@ -64940,10 +64940,10 @@
         </is>
       </c>
       <c r="H1654" s="2" t="n">
-        <v>46081.67857676662</v>
+        <v>46081.67857677084</v>
       </c>
       <c r="I1654" s="2" t="n">
-        <v>46086.67857676662</v>
+        <v>46086.67857677084</v>
       </c>
     </row>
     <row r="1655">
@@ -64979,10 +64979,10 @@
         </is>
       </c>
       <c r="H1655" s="2" t="n">
-        <v>46086.67857677013</v>
+        <v>46086.67857677084</v>
       </c>
       <c r="I1655" s="2" t="n">
-        <v>46091.67857677013</v>
+        <v>46091.67857677084</v>
       </c>
     </row>
     <row r="1656">
@@ -65018,10 +65018,10 @@
         </is>
       </c>
       <c r="H1656" s="2" t="n">
-        <v>46070.67857677327</v>
+        <v>46070.67857677084</v>
       </c>
       <c r="I1656" s="2" t="n">
-        <v>46075.67857677327</v>
+        <v>46075.67857677084</v>
       </c>
     </row>
     <row r="1657">
@@ -65057,10 +65057,10 @@
         </is>
       </c>
       <c r="H1657" s="2" t="n">
-        <v>46082.67857677677</v>
+        <v>46082.6785767824</v>
       </c>
       <c r="I1657" s="2" t="n">
-        <v>46087.67857677677</v>
+        <v>46087.6785767824</v>
       </c>
     </row>
     <row r="1658">
@@ -65096,10 +65096,10 @@
         </is>
       </c>
       <c r="H1658" s="2" t="n">
-        <v>46077.67857677994</v>
+        <v>46077.6785767824</v>
       </c>
       <c r="I1658" s="2" t="n">
-        <v>46082.67857677994</v>
+        <v>46082.6785767824</v>
       </c>
     </row>
     <row r="1659">
@@ -65135,10 +65135,10 @@
         </is>
       </c>
       <c r="H1659" s="2" t="n">
-        <v>46087.67857678317</v>
+        <v>46087.6785767824</v>
       </c>
       <c r="I1659" s="2" t="n">
-        <v>46092.67857678317</v>
+        <v>46092.6785767824</v>
       </c>
     </row>
     <row r="1660">
@@ -65174,10 +65174,10 @@
         </is>
       </c>
       <c r="H1660" s="2" t="n">
-        <v>46067.67857678673</v>
+        <v>46067.6785767824</v>
       </c>
       <c r="I1660" s="2" t="n">
-        <v>46072.67857678673</v>
+        <v>46072.6785767824</v>
       </c>
     </row>
     <row r="1661">
@@ -65213,10 +65213,10 @@
         </is>
       </c>
       <c r="H1661" s="2" t="n">
-        <v>46060.67857678999</v>
+        <v>46060.67857679398</v>
       </c>
       <c r="I1661" s="2" t="n">
-        <v>46065.67857678999</v>
+        <v>46065.67857679398</v>
       </c>
     </row>
     <row r="1662">
@@ -65252,10 +65252,10 @@
         </is>
       </c>
       <c r="H1662" s="2" t="n">
-        <v>46082.67857679319</v>
+        <v>46082.67857679398</v>
       </c>
       <c r="I1662" s="2" t="n">
-        <v>46087.67857679319</v>
+        <v>46087.67857679398</v>
       </c>
     </row>
     <row r="1663">
@@ -65291,10 +65291,10 @@
         </is>
       </c>
       <c r="H1663" s="2" t="n">
-        <v>46060.67857679647</v>
+        <v>46060.67857679398</v>
       </c>
       <c r="I1663" s="2" t="n">
-        <v>46065.67857679647</v>
+        <v>46065.67857679398</v>
       </c>
     </row>
     <row r="1664">
@@ -65330,10 +65330,10 @@
         </is>
       </c>
       <c r="H1664" s="2" t="n">
-        <v>46078.67857679991</v>
+        <v>46078.67857680556</v>
       </c>
       <c r="I1664" s="2" t="n">
-        <v>46083.67857679991</v>
+        <v>46083.67857680556</v>
       </c>
     </row>
     <row r="1665">
@@ -65369,10 +65369,10 @@
         </is>
       </c>
       <c r="H1665" s="2" t="n">
-        <v>46071.67857680303</v>
+        <v>46071.67857680556</v>
       </c>
       <c r="I1665" s="2" t="n">
-        <v>46076.67857680303</v>
+        <v>46076.67857680556</v>
       </c>
     </row>
     <row r="1666">
@@ -65408,10 +65408,10 @@
         </is>
       </c>
       <c r="H1666" s="2" t="n">
-        <v>46074.67857680612</v>
+        <v>46074.67857680556</v>
       </c>
       <c r="I1666" s="2" t="n">
-        <v>46079.67857680612</v>
+        <v>46079.67857680556</v>
       </c>
     </row>
     <row r="1667">
@@ -65447,10 +65447,10 @@
         </is>
       </c>
       <c r="H1667" s="2" t="n">
-        <v>46081.67857680971</v>
+        <v>46081.67857680556</v>
       </c>
       <c r="I1667" s="2" t="n">
-        <v>46086.67857680971</v>
+        <v>46086.67857680556</v>
       </c>
     </row>
     <row r="1668">
@@ -65486,10 +65486,10 @@
         </is>
       </c>
       <c r="H1668" s="2" t="n">
-        <v>46070.67857681295</v>
+        <v>46070.67857681713</v>
       </c>
       <c r="I1668" s="2" t="n">
-        <v>46075.67857681295</v>
+        <v>46075.67857681713</v>
       </c>
     </row>
     <row r="1669">
@@ -65525,10 +65525,10 @@
         </is>
       </c>
       <c r="H1669" s="2" t="n">
-        <v>46062.67857681617</v>
+        <v>46062.67857681713</v>
       </c>
       <c r="I1669" s="2" t="n">
-        <v>46067.67857681617</v>
+        <v>46067.67857681713</v>
       </c>
     </row>
     <row r="1670">
@@ -65564,10 +65564,10 @@
         </is>
       </c>
       <c r="H1670" s="2" t="n">
-        <v>46070.67857681933</v>
+        <v>46070.67857681713</v>
       </c>
       <c r="I1670" s="2" t="n">
-        <v>46075.67857681933</v>
+        <v>46075.67857681713</v>
       </c>
     </row>
     <row r="1671">
@@ -65603,10 +65603,10 @@
         </is>
       </c>
       <c r="H1671" s="2" t="n">
-        <v>46081.67857682281</v>
+        <v>46081.67857681713</v>
       </c>
       <c r="I1671" s="2" t="n">
-        <v>46086.67857682281</v>
+        <v>46086.67857681713</v>
       </c>
     </row>
     <row r="1672">
@@ -65642,10 +65642,10 @@
         </is>
       </c>
       <c r="H1672" s="2" t="n">
-        <v>46070.67857682597</v>
+        <v>46070.6785768287</v>
       </c>
       <c r="I1672" s="2" t="n">
-        <v>46075.67857682597</v>
+        <v>46075.6785768287</v>
       </c>
     </row>
     <row r="1673">
@@ -65681,10 +65681,10 @@
         </is>
       </c>
       <c r="H1673" s="2" t="n">
-        <v>46065.67857682914</v>
+        <v>46065.6785768287</v>
       </c>
       <c r="I1673" s="2" t="n">
-        <v>46070.67857682914</v>
+        <v>46070.6785768287</v>
       </c>
     </row>
     <row r="1674">
@@ -65720,10 +65720,10 @@
         </is>
       </c>
       <c r="H1674" s="2" t="n">
-        <v>46088.67857683254</v>
+        <v>46088.6785768287</v>
       </c>
       <c r="I1674" s="2" t="n">
-        <v>46093.67857683254</v>
+        <v>46093.6785768287</v>
       </c>
     </row>
     <row r="1675">
@@ -65759,10 +65759,10 @@
         </is>
       </c>
       <c r="H1675" s="2" t="n">
-        <v>46071.67857683581</v>
+        <v>46071.67857684028</v>
       </c>
       <c r="I1675" s="2" t="n">
-        <v>46076.67857683581</v>
+        <v>46076.67857684028</v>
       </c>
     </row>
     <row r="1676">
@@ -65798,10 +65798,10 @@
         </is>
       </c>
       <c r="H1676" s="2" t="n">
-        <v>46060.67857683908</v>
+        <v>46060.67857684028</v>
       </c>
       <c r="I1676" s="2" t="n">
-        <v>46065.67857683908</v>
+        <v>46065.67857684028</v>
       </c>
     </row>
     <row r="1677">
@@ -65837,10 +65837,10 @@
         </is>
       </c>
       <c r="H1677" s="2" t="n">
-        <v>46061.67857684216</v>
+        <v>46061.67857684028</v>
       </c>
       <c r="I1677" s="2" t="n">
-        <v>46066.67857684216</v>
+        <v>46066.67857684028</v>
       </c>
     </row>
     <row r="1678">
@@ -65876,10 +65876,10 @@
         </is>
       </c>
       <c r="H1678" s="2" t="n">
-        <v>46077.67857684576</v>
+        <v>46077.67857684028</v>
       </c>
       <c r="I1678" s="2" t="n">
-        <v>46082.67857684576</v>
+        <v>46082.67857684028</v>
       </c>
     </row>
     <row r="1679">
@@ -65915,10 +65915,10 @@
         </is>
       </c>
       <c r="H1679" s="2" t="n">
-        <v>46072.67857684886</v>
+        <v>46072.67857685185</v>
       </c>
       <c r="I1679" s="2" t="n">
-        <v>46077.67857684886</v>
+        <v>46077.67857685185</v>
       </c>
     </row>
     <row r="1680">
@@ -65954,10 +65954,10 @@
         </is>
       </c>
       <c r="H1680" s="2" t="n">
-        <v>46079.67857685211</v>
+        <v>46079.67857685185</v>
       </c>
       <c r="I1680" s="2" t="n">
-        <v>46084.67857685211</v>
+        <v>46084.67857685185</v>
       </c>
     </row>
     <row r="1681">
@@ -65993,10 +65993,10 @@
         </is>
       </c>
       <c r="H1681" s="2" t="n">
-        <v>46070.67857685585</v>
+        <v>46070.67857685185</v>
       </c>
       <c r="I1681" s="2" t="n">
-        <v>46075.67857685585</v>
+        <v>46075.67857685185</v>
       </c>
     </row>
     <row r="1682">
@@ -66032,10 +66032,10 @@
         </is>
       </c>
       <c r="H1682" s="2" t="n">
-        <v>46076.67857685918</v>
+        <v>46076.67857686343</v>
       </c>
       <c r="I1682" s="2" t="n">
-        <v>46081.67857685918</v>
+        <v>46081.67857686343</v>
       </c>
     </row>
     <row r="1683">
@@ -66071,10 +66071,10 @@
         </is>
       </c>
       <c r="H1683" s="2" t="n">
-        <v>46079.67857686226</v>
+        <v>46079.67857686343</v>
       </c>
       <c r="I1683" s="2" t="n">
-        <v>46084.67857686226</v>
+        <v>46084.67857686343</v>
       </c>
     </row>
     <row r="1684">
@@ -66110,10 +66110,10 @@
         </is>
       </c>
       <c r="H1684" s="2" t="n">
-        <v>46082.67857686542</v>
+        <v>46082.67857686343</v>
       </c>
       <c r="I1684" s="2" t="n">
-        <v>46087.67857686542</v>
+        <v>46087.67857686343</v>
       </c>
     </row>
     <row r="1685">
@@ -66149,10 +66149,10 @@
         </is>
       </c>
       <c r="H1685" s="2" t="n">
-        <v>46076.67857686911</v>
+        <v>46076.67857686343</v>
       </c>
       <c r="I1685" s="2" t="n">
-        <v>46081.67857686911</v>
+        <v>46081.67857686343</v>
       </c>
     </row>
     <row r="1686">
@@ -66188,10 +66188,10 @@
         </is>
       </c>
       <c r="H1686" s="2" t="n">
-        <v>46087.67857687221</v>
+        <v>46087.678576875</v>
       </c>
       <c r="I1686" s="2" t="n">
-        <v>46092.67857687221</v>
+        <v>46092.678576875</v>
       </c>
     </row>
     <row r="1687">
@@ -66227,10 +66227,10 @@
         </is>
       </c>
       <c r="H1687" s="2" t="n">
-        <v>46078.67857687533</v>
+        <v>46078.678576875</v>
       </c>
       <c r="I1687" s="2" t="n">
-        <v>46083.67857687533</v>
+        <v>46083.678576875</v>
       </c>
     </row>
     <row r="1688">
@@ -66266,10 +66266,10 @@
         </is>
       </c>
       <c r="H1688" s="2" t="n">
-        <v>46069.67857687834</v>
+        <v>46069.678576875</v>
       </c>
       <c r="I1688" s="2" t="n">
-        <v>46074.67857687834</v>
+        <v>46074.678576875</v>
       </c>
     </row>
     <row r="1689">
@@ -66305,10 +66305,10 @@
         </is>
       </c>
       <c r="H1689" s="2" t="n">
-        <v>46076.67857688169</v>
+        <v>46076.67857688657</v>
       </c>
       <c r="I1689" s="2" t="n">
-        <v>46081.67857688169</v>
+        <v>46081.67857688657</v>
       </c>
     </row>
     <row r="1690">
@@ -66344,10 +66344,10 @@
         </is>
       </c>
       <c r="H1690" s="2" t="n">
-        <v>46079.67857688489</v>
+        <v>46079.67857688657</v>
       </c>
       <c r="I1690" s="2" t="n">
-        <v>46084.67857688489</v>
+        <v>46084.67857688657</v>
       </c>
     </row>
     <row r="1691">
@@ -66383,10 +66383,10 @@
         </is>
       </c>
       <c r="H1691" s="2" t="n">
-        <v>46080.67857688816</v>
+        <v>46080.67857688657</v>
       </c>
       <c r="I1691" s="2" t="n">
-        <v>46085.67857688816</v>
+        <v>46085.67857688657</v>
       </c>
     </row>
     <row r="1692">
@@ -66422,10 +66422,10 @@
         </is>
       </c>
       <c r="H1692" s="2" t="n">
-        <v>46088.67857689153</v>
+        <v>46088.67857688657</v>
       </c>
       <c r="I1692" s="2" t="n">
-        <v>46093.67857689153</v>
+        <v>46093.67857688657</v>
       </c>
     </row>
     <row r="1693">
@@ -66461,10 +66461,10 @@
         </is>
       </c>
       <c r="H1693" s="2" t="n">
-        <v>46070.67857689474</v>
+        <v>46070.67857689815</v>
       </c>
       <c r="I1693" s="2" t="n">
-        <v>46075.67857689474</v>
+        <v>46075.67857689815</v>
       </c>
     </row>
     <row r="1694">
@@ -66500,10 +66500,10 @@
         </is>
       </c>
       <c r="H1694" s="2" t="n">
-        <v>46087.67857689804</v>
+        <v>46087.67857689815</v>
       </c>
       <c r="I1694" s="2" t="n">
-        <v>46092.67857689804</v>
+        <v>46092.67857689815</v>
       </c>
     </row>
     <row r="1695">
@@ -66539,10 +66539,10 @@
         </is>
       </c>
       <c r="H1695" s="2" t="n">
-        <v>46075.67857690123</v>
+        <v>46075.67857689815</v>
       </c>
       <c r="I1695" s="2" t="n">
-        <v>46080.67857690123</v>
+        <v>46080.67857689815</v>
       </c>
     </row>
     <row r="1696">
@@ -66578,10 +66578,10 @@
         </is>
       </c>
       <c r="H1696" s="2" t="n">
-        <v>46065.67857690503</v>
+        <v>46065.67857690972</v>
       </c>
       <c r="I1696" s="2" t="n">
-        <v>46070.67857690503</v>
+        <v>46070.67857690972</v>
       </c>
     </row>
     <row r="1697">
@@ -66617,10 +66617,10 @@
         </is>
       </c>
       <c r="H1697" s="2" t="n">
-        <v>46067.67857690811</v>
+        <v>46067.67857690972</v>
       </c>
       <c r="I1697" s="2" t="n">
-        <v>46072.67857690811</v>
+        <v>46072.67857690972</v>
       </c>
     </row>
     <row r="1698">
@@ -66656,10 +66656,10 @@
         </is>
       </c>
       <c r="H1698" s="2" t="n">
-        <v>46083.6785769113</v>
+        <v>46083.67857690972</v>
       </c>
       <c r="I1698" s="2" t="n">
-        <v>46088.6785769113</v>
+        <v>46088.67857690972</v>
       </c>
     </row>
     <row r="1699">
@@ -66695,10 +66695,10 @@
         </is>
       </c>
       <c r="H1699" s="2" t="n">
-        <v>46087.67857691492</v>
+        <v>46087.67857690972</v>
       </c>
       <c r="I1699" s="2" t="n">
-        <v>46092.67857691492</v>
+        <v>46092.67857690972</v>
       </c>
     </row>
     <row r="1700">
@@ -66734,10 +66734,10 @@
         </is>
       </c>
       <c r="H1700" s="2" t="n">
-        <v>46084.6785769181</v>
+        <v>46084.67857692129</v>
       </c>
       <c r="I1700" s="2" t="n">
-        <v>46089.6785769181</v>
+        <v>46089.67857692129</v>
       </c>
     </row>
     <row r="1701">
@@ -66773,10 +66773,1960 @@
         </is>
       </c>
       <c r="H1701" s="2" t="n">
-        <v>46080.67857692132</v>
+        <v>46080.67857692129</v>
       </c>
       <c r="I1701" s="2" t="n">
-        <v>46085.67857692132</v>
+        <v>46085.67857692129</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>f4ddca0a-8d6e-44d0-9ee1-7a810dfa9b0e</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1702" t="n">
+        <v>3707.03</v>
+      </c>
+      <c r="D1702" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1702" s="2" t="n">
+        <v>46072.18522146757</v>
+      </c>
+      <c r="I1702" s="2" t="n">
+        <v>46077.18522146757</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2c3bb197-67e5-435f-8433-3556cab58193</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1703" t="n">
+        <v>7523.29</v>
+      </c>
+      <c r="D1703" t="n">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1703" s="2" t="n">
+        <v>46065.18522147178</v>
+      </c>
+      <c r="I1703" s="2" t="n">
+        <v>46070.18522147178</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>ff87bae6-6f31-494d-8205-180932ca4233</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1704" t="n">
+        <v>9136.9</v>
+      </c>
+      <c r="D1704" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1704" s="2" t="n">
+        <v>46064.18522147501</v>
+      </c>
+      <c r="I1704" s="2" t="n">
+        <v>46069.18522147501</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>bf74494f-051e-4574-9a1a-aec3f3e9208d</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1705" t="n">
+        <v>5157</v>
+      </c>
+      <c r="D1705" t="n">
+        <v>95.88</v>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1705" s="2" t="n">
+        <v>46075.18522147834</v>
+      </c>
+      <c r="I1705" s="2" t="n">
+        <v>46080.18522147834</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>0c8c97e3-5295-47c9-8cb1-972dd8fff04b</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1706" t="n">
+        <v>1993.37</v>
+      </c>
+      <c r="D1706" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1706" s="2" t="n">
+        <v>46074.18522148159</v>
+      </c>
+      <c r="I1706" s="2" t="n">
+        <v>46079.18522148159</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>b4ee5f9c-67a0-47e6-aa1c-a0b4bebecbbd</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1707" t="n">
+        <v>3908.22</v>
+      </c>
+      <c r="D1707" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1707" s="2" t="n">
+        <v>46065.18522148477</v>
+      </c>
+      <c r="I1707" s="2" t="n">
+        <v>46070.18522148477</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>c4453e34-7115-41a3-ac3d-cd5577a50d82</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1708" t="n">
+        <v>3371.38</v>
+      </c>
+      <c r="D1708" t="n">
+        <v>88.59</v>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1708" s="2" t="n">
+        <v>46067.18522148816</v>
+      </c>
+      <c r="I1708" s="2" t="n">
+        <v>46072.18522148816</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>b604085a-7388-40c9-ac7c-8740ca2c8fd0</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1709" t="n">
+        <v>7925.68</v>
+      </c>
+      <c r="D1709" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1709" s="2" t="n">
+        <v>46061.18522149131</v>
+      </c>
+      <c r="I1709" s="2" t="n">
+        <v>46066.18522149131</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>a1ed0d99-f814-4a34-b2aa-19694f92df1d</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1710" t="n">
+        <v>1998.46</v>
+      </c>
+      <c r="D1710" t="n">
+        <v>98.13</v>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1710" s="2" t="n">
+        <v>46087.18522149436</v>
+      </c>
+      <c r="I1710" s="2" t="n">
+        <v>46092.18522149436</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>503b913b-7f84-4634-bbee-f0de199efaf1</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1711" t="n">
+        <v>3584.71</v>
+      </c>
+      <c r="D1711" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1711" s="2" t="n">
+        <v>46078.18522149795</v>
+      </c>
+      <c r="I1711" s="2" t="n">
+        <v>46083.18522149795</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>1f0c4806-5f83-4757-843b-3ce783d94ed1</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1712" t="n">
+        <v>5432.74</v>
+      </c>
+      <c r="D1712" t="n">
+        <v>95.70999999999999</v>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1712" s="2" t="n">
+        <v>46087.1852215017</v>
+      </c>
+      <c r="I1712" s="2" t="n">
+        <v>46092.1852215017</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>90931d55-9c18-42d6-b45f-545f8c04a3c5</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1713" t="n">
+        <v>3022.04</v>
+      </c>
+      <c r="D1713" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1713" s="2" t="n">
+        <v>46075.18522150483</v>
+      </c>
+      <c r="I1713" s="2" t="n">
+        <v>46080.18522150483</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>9171a899-96a3-4b86-8007-fdf3642d883c</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1714" t="n">
+        <v>4575.58</v>
+      </c>
+      <c r="D1714" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1714" s="2" t="n">
+        <v>46080.18522150807</v>
+      </c>
+      <c r="I1714" s="2" t="n">
+        <v>46085.18522150807</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>d39a7d81-f7e2-487f-80c8-05ceb05bf1b1</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1715" t="n">
+        <v>4840.12</v>
+      </c>
+      <c r="D1715" t="n">
+        <v>98.37</v>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1715" s="2" t="n">
+        <v>46085.18522151131</v>
+      </c>
+      <c r="I1715" s="2" t="n">
+        <v>46090.18522151131</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>3283ce6f-36b6-48cd-9e89-574e38696d87</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1716" t="n">
+        <v>2538.54</v>
+      </c>
+      <c r="D1716" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1716" s="2" t="n">
+        <v>46087.18522151439</v>
+      </c>
+      <c r="I1716" s="2" t="n">
+        <v>46092.18522151439</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>3ce1a7c4-66ee-47ae-999e-98568c0308fd</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1717" t="n">
+        <v>2937.28</v>
+      </c>
+      <c r="D1717" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1717" s="2" t="n">
+        <v>46079.18522151747</v>
+      </c>
+      <c r="I1717" s="2" t="n">
+        <v>46084.18522151747</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>504a65b7-c3d6-4166-b758-bb902bd19b72</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1718" t="n">
+        <v>2751.87</v>
+      </c>
+      <c r="D1718" t="n">
+        <v>89.06</v>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1718" s="2" t="n">
+        <v>46067.18522152056</v>
+      </c>
+      <c r="I1718" s="2" t="n">
+        <v>46072.18522152056</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>d16cd225-39dc-4a14-9a3b-090e0b8e587c</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1719" t="n">
+        <v>3406.21</v>
+      </c>
+      <c r="D1719" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1719" s="2" t="n">
+        <v>46077.18522152376</v>
+      </c>
+      <c r="I1719" s="2" t="n">
+        <v>46082.18522152376</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>0d3e9a26-5073-422c-9963-0de08047c88e</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1720" t="n">
+        <v>7337.03</v>
+      </c>
+      <c r="D1720" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1720" s="2" t="n">
+        <v>46075.18522152698</v>
+      </c>
+      <c r="I1720" s="2" t="n">
+        <v>46080.18522152698</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>d1459ffa-93b9-4965-96f5-46458a9e59ef</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1721" t="n">
+        <v>3050.68</v>
+      </c>
+      <c r="D1721" t="n">
+        <v>91.13</v>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1721" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1721" s="2" t="n">
+        <v>46088.18522153005</v>
+      </c>
+      <c r="I1721" s="2" t="n">
+        <v>46093.18522153005</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>e54b6ca7-1b45-4ac2-990d-37c8a27bdd17</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1722" t="n">
+        <v>7099.06</v>
+      </c>
+      <c r="D1722" t="n">
+        <v>95.06999999999999</v>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1722" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1722" s="2" t="n">
+        <v>46072.1852215332</v>
+      </c>
+      <c r="I1722" s="2" t="n">
+        <v>46077.1852215332</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>6e126c78-b907-4ad5-b820-2dd132493ce1</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1723" t="n">
+        <v>5636.36</v>
+      </c>
+      <c r="D1723" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1723" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1723" s="2" t="n">
+        <v>46085.18522153661</v>
+      </c>
+      <c r="I1723" s="2" t="n">
+        <v>46090.18522153661</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>fa4b4209-549a-4b18-891c-a5d7517af47d</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1724" t="n">
+        <v>7134.7</v>
+      </c>
+      <c r="D1724" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1724" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1724" s="2" t="n">
+        <v>46074.1852215397</v>
+      </c>
+      <c r="I1724" s="2" t="n">
+        <v>46079.1852215397</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>4c0de839-9120-4329-8d07-e4d34a2ceed2</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1725" t="n">
+        <v>4122.63</v>
+      </c>
+      <c r="D1725" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1725" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1725" s="2" t="n">
+        <v>46078.1852215427</v>
+      </c>
+      <c r="I1725" s="2" t="n">
+        <v>46083.1852215427</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>4f22234f-0d19-418f-898e-57f2e157b85b</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1726" t="n">
+        <v>2576.93</v>
+      </c>
+      <c r="D1726" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1726" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1726" s="2" t="n">
+        <v>46066.1852215459</v>
+      </c>
+      <c r="I1726" s="2" t="n">
+        <v>46071.1852215459</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>8f46e708-fb90-4fb9-b75a-2331ddbd7ab4</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1727" t="n">
+        <v>5118.37</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1727" s="2" t="n">
+        <v>46063.18522154899</v>
+      </c>
+      <c r="I1727" s="2" t="n">
+        <v>46068.18522154899</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>b86e336f-cf03-4875-90ac-bc8c94d1abb2</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1728" t="n">
+        <v>8943.25</v>
+      </c>
+      <c r="D1728" t="n">
+        <v>89.87</v>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1728" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1728" s="2" t="n">
+        <v>46061.18522155219</v>
+      </c>
+      <c r="I1728" s="2" t="n">
+        <v>46066.18522155219</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>f2784152-1332-4324-8269-cd162b8bba8c</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1729" t="n">
+        <v>5670.02</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1729" s="2" t="n">
+        <v>46064.1852215554</v>
+      </c>
+      <c r="I1729" s="2" t="n">
+        <v>46069.1852215554</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>796c11a2-9a25-43e0-8ff9-47fa9911a9e4</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1730" t="n">
+        <v>8850.73</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>93.37</v>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1730" s="2" t="n">
+        <v>46075.18522155871</v>
+      </c>
+      <c r="I1730" s="2" t="n">
+        <v>46080.18522155871</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>8a4462d1-a0ce-4637-931e-963e3e2c0fdc</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1731" t="n">
+        <v>7808.81</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1731" s="2" t="n">
+        <v>46081.18522156178</v>
+      </c>
+      <c r="I1731" s="2" t="n">
+        <v>46086.18522156178</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>c7a05a34-fb92-492e-8386-6542e879adc1</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1732" t="n">
+        <v>8569.469999999999</v>
+      </c>
+      <c r="D1732" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1732" s="2" t="n">
+        <v>46065.18522156496</v>
+      </c>
+      <c r="I1732" s="2" t="n">
+        <v>46070.18522156496</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>154b43ad-64df-44ef-a48d-60762d0059ef</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1733" t="n">
+        <v>2740.16</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>94.61</v>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1733" s="2" t="n">
+        <v>46064.18522156811</v>
+      </c>
+      <c r="I1733" s="2" t="n">
+        <v>46069.18522156811</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>717acdea-bcd0-45e9-ab95-b3ecd58e34b0</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1734" t="n">
+        <v>5446.56</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1734" s="2" t="n">
+        <v>46089.18522157139</v>
+      </c>
+      <c r="I1734" s="2" t="n">
+        <v>46094.18522157139</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>25076df8-400f-4109-8e22-1bc52e8eccac</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1735" t="n">
+        <v>5959.72</v>
+      </c>
+      <c r="D1735" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1735" s="2" t="n">
+        <v>46068.18522157448</v>
+      </c>
+      <c r="I1735" s="2" t="n">
+        <v>46073.18522157448</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>f8dc4389-8a70-4a31-86b9-1910ce5e56d0</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1736" t="n">
+        <v>1926.28</v>
+      </c>
+      <c r="D1736" t="n">
+        <v>86.33</v>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1736" s="2" t="n">
+        <v>46078.18522157765</v>
+      </c>
+      <c r="I1736" s="2" t="n">
+        <v>46083.18522157765</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>dd112ac8-d264-499c-a23d-e018926e1a43</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1737" t="n">
+        <v>3469.66</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>98.41</v>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1737" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1737" s="2" t="n">
+        <v>46087.18522158083</v>
+      </c>
+      <c r="I1737" s="2" t="n">
+        <v>46092.18522158083</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>fc16ce42-9e10-41b8-b0d4-7e990c8eff82</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1738" t="n">
+        <v>7660.16</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1738" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1738" s="2" t="n">
+        <v>46076.18522158402</v>
+      </c>
+      <c r="I1738" s="2" t="n">
+        <v>46081.18522158402</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>1da8ac8a-e486-4869-9749-a9c6c9832700</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1739" t="n">
+        <v>3766.37</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>85.45999999999999</v>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1739" s="2" t="n">
+        <v>46078.18522158715</v>
+      </c>
+      <c r="I1739" s="2" t="n">
+        <v>46083.18522158715</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>f357bd3e-4aa3-4c35-8fa1-900d8c277bf9</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1740" t="n">
+        <v>8861.629999999999</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1740" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1740" s="2" t="n">
+        <v>46075.18522159017</v>
+      </c>
+      <c r="I1740" s="2" t="n">
+        <v>46080.18522159017</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2a0e9d17-703d-4c3b-864c-4fc6327956e5</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1741" t="n">
+        <v>1009.85</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1741" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1741" s="2" t="n">
+        <v>46086.18522159343</v>
+      </c>
+      <c r="I1741" s="2" t="n">
+        <v>46091.18522159343</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>edb13e45-57ef-4ea6-897b-b07e2be59ae8</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1742" t="n">
+        <v>2417.9</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>91.87</v>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1742" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1742" s="2" t="n">
+        <v>46085.18522159647</v>
+      </c>
+      <c r="I1742" s="2" t="n">
+        <v>46090.18522159647</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>dc90146d-128d-49b1-b4ca-57d26dce2bb3</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1743" t="n">
+        <v>3395.39</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1743" s="2" t="n">
+        <v>46083.18522159955</v>
+      </c>
+      <c r="I1743" s="2" t="n">
+        <v>46088.18522159955</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>169ee050-8624-4623-93a3-395d634a3855</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1744" t="n">
+        <v>3560.19</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1744" s="2" t="n">
+        <v>46070.18522160258</v>
+      </c>
+      <c r="I1744" s="2" t="n">
+        <v>46075.18522160258</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>a4c828a0-3afd-45ea-a4d2-c6e4a4cb86d8</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1745" t="n">
+        <v>9264.030000000001</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1745" s="2" t="n">
+        <v>46083.18522160593</v>
+      </c>
+      <c r="I1745" s="2" t="n">
+        <v>46088.18522160593</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>7d00b664-fcfe-4efe-b6af-e8841b875413</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1746" t="n">
+        <v>9413.41</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1746" s="2" t="n">
+        <v>46068.18522160903</v>
+      </c>
+      <c r="I1746" s="2" t="n">
+        <v>46073.18522160903</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>7a52e499-ed14-4bf4-b071-35aac2c3164f</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1747" t="n">
+        <v>6351.28</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1747" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1747" s="2" t="n">
+        <v>46077.18522161206</v>
+      </c>
+      <c r="I1747" s="2" t="n">
+        <v>46082.18522161206</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>b4cb8dd2-62be-478d-b2f2-24fda97dfd4d</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1748" t="n">
+        <v>6595.82</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1748" s="2" t="n">
+        <v>46061.1852216153</v>
+      </c>
+      <c r="I1748" s="2" t="n">
+        <v>46066.1852216153</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>d4e4d4e9-26c4-4407-9b5d-ebd2f6e8174c</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1749" t="n">
+        <v>2730.67</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1749" s="2" t="n">
+        <v>46066.18522161854</v>
+      </c>
+      <c r="I1749" s="2" t="n">
+        <v>46071.18522161854</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>6a86c908-e562-4056-b138-1eedc260241b</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1750" t="n">
+        <v>1135.49</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>95.91</v>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1750" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1750" s="2" t="n">
+        <v>46066.18522162154</v>
+      </c>
+      <c r="I1750" s="2" t="n">
+        <v>46071.18522162154</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>0f4a82f0-8519-481c-9026-86692b20a125</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1751" t="n">
+        <v>8240.93</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1751" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1751" s="2" t="n">
+        <v>46086.1852216246</v>
+      </c>
+      <c r="I1751" s="2" t="n">
+        <v>46091.1852216246</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1751"/>
+  <dimension ref="A1:I1801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66812,10 +66812,10 @@
         </is>
       </c>
       <c r="H1702" s="2" t="n">
-        <v>46072.18522146757</v>
+        <v>46072.18522146991</v>
       </c>
       <c r="I1702" s="2" t="n">
-        <v>46077.18522146757</v>
+        <v>46077.18522146991</v>
       </c>
     </row>
     <row r="1703">
@@ -66851,10 +66851,10 @@
         </is>
       </c>
       <c r="H1703" s="2" t="n">
-        <v>46065.18522147178</v>
+        <v>46065.18522146991</v>
       </c>
       <c r="I1703" s="2" t="n">
-        <v>46070.18522147178</v>
+        <v>46070.18522146991</v>
       </c>
     </row>
     <row r="1704">
@@ -66890,10 +66890,10 @@
         </is>
       </c>
       <c r="H1704" s="2" t="n">
-        <v>46064.18522147501</v>
+        <v>46064.18522146991</v>
       </c>
       <c r="I1704" s="2" t="n">
-        <v>46069.18522147501</v>
+        <v>46069.18522146991</v>
       </c>
     </row>
     <row r="1705">
@@ -66929,10 +66929,10 @@
         </is>
       </c>
       <c r="H1705" s="2" t="n">
-        <v>46075.18522147834</v>
+        <v>46075.18522148148</v>
       </c>
       <c r="I1705" s="2" t="n">
-        <v>46080.18522147834</v>
+        <v>46080.18522148148</v>
       </c>
     </row>
     <row r="1706">
@@ -66968,10 +66968,10 @@
         </is>
       </c>
       <c r="H1706" s="2" t="n">
-        <v>46074.18522148159</v>
+        <v>46074.18522148148</v>
       </c>
       <c r="I1706" s="2" t="n">
-        <v>46079.18522148159</v>
+        <v>46079.18522148148</v>
       </c>
     </row>
     <row r="1707">
@@ -67007,10 +67007,10 @@
         </is>
       </c>
       <c r="H1707" s="2" t="n">
-        <v>46065.18522148477</v>
+        <v>46065.18522148148</v>
       </c>
       <c r="I1707" s="2" t="n">
-        <v>46070.18522148477</v>
+        <v>46070.18522148148</v>
       </c>
     </row>
     <row r="1708">
@@ -67046,10 +67046,10 @@
         </is>
       </c>
       <c r="H1708" s="2" t="n">
-        <v>46067.18522148816</v>
+        <v>46067.18522149305</v>
       </c>
       <c r="I1708" s="2" t="n">
-        <v>46072.18522148816</v>
+        <v>46072.18522149305</v>
       </c>
     </row>
     <row r="1709">
@@ -67085,10 +67085,10 @@
         </is>
       </c>
       <c r="H1709" s="2" t="n">
-        <v>46061.18522149131</v>
+        <v>46061.18522149305</v>
       </c>
       <c r="I1709" s="2" t="n">
-        <v>46066.18522149131</v>
+        <v>46066.18522149305</v>
       </c>
     </row>
     <row r="1710">
@@ -67124,10 +67124,10 @@
         </is>
       </c>
       <c r="H1710" s="2" t="n">
-        <v>46087.18522149436</v>
+        <v>46087.18522149305</v>
       </c>
       <c r="I1710" s="2" t="n">
-        <v>46092.18522149436</v>
+        <v>46092.18522149305</v>
       </c>
     </row>
     <row r="1711">
@@ -67163,10 +67163,10 @@
         </is>
       </c>
       <c r="H1711" s="2" t="n">
-        <v>46078.18522149795</v>
+        <v>46078.18522149305</v>
       </c>
       <c r="I1711" s="2" t="n">
-        <v>46083.18522149795</v>
+        <v>46083.18522149305</v>
       </c>
     </row>
     <row r="1712">
@@ -67202,10 +67202,10 @@
         </is>
       </c>
       <c r="H1712" s="2" t="n">
-        <v>46087.1852215017</v>
+        <v>46087.18522150463</v>
       </c>
       <c r="I1712" s="2" t="n">
-        <v>46092.1852215017</v>
+        <v>46092.18522150463</v>
       </c>
     </row>
     <row r="1713">
@@ -67241,10 +67241,10 @@
         </is>
       </c>
       <c r="H1713" s="2" t="n">
-        <v>46075.18522150483</v>
+        <v>46075.18522150463</v>
       </c>
       <c r="I1713" s="2" t="n">
-        <v>46080.18522150483</v>
+        <v>46080.18522150463</v>
       </c>
     </row>
     <row r="1714">
@@ -67280,10 +67280,10 @@
         </is>
       </c>
       <c r="H1714" s="2" t="n">
-        <v>46080.18522150807</v>
+        <v>46080.18522150463</v>
       </c>
       <c r="I1714" s="2" t="n">
-        <v>46085.18522150807</v>
+        <v>46085.18522150463</v>
       </c>
     </row>
     <row r="1715">
@@ -67319,10 +67319,10 @@
         </is>
       </c>
       <c r="H1715" s="2" t="n">
-        <v>46085.18522151131</v>
+        <v>46085.18522151621</v>
       </c>
       <c r="I1715" s="2" t="n">
-        <v>46090.18522151131</v>
+        <v>46090.18522151621</v>
       </c>
     </row>
     <row r="1716">
@@ -67358,10 +67358,10 @@
         </is>
       </c>
       <c r="H1716" s="2" t="n">
-        <v>46087.18522151439</v>
+        <v>46087.18522151621</v>
       </c>
       <c r="I1716" s="2" t="n">
-        <v>46092.18522151439</v>
+        <v>46092.18522151621</v>
       </c>
     </row>
     <row r="1717">
@@ -67397,10 +67397,10 @@
         </is>
       </c>
       <c r="H1717" s="2" t="n">
-        <v>46079.18522151747</v>
+        <v>46079.18522151621</v>
       </c>
       <c r="I1717" s="2" t="n">
-        <v>46084.18522151747</v>
+        <v>46084.18522151621</v>
       </c>
     </row>
     <row r="1718">
@@ -67436,10 +67436,10 @@
         </is>
       </c>
       <c r="H1718" s="2" t="n">
-        <v>46067.18522152056</v>
+        <v>46067.18522151621</v>
       </c>
       <c r="I1718" s="2" t="n">
-        <v>46072.18522152056</v>
+        <v>46072.18522151621</v>
       </c>
     </row>
     <row r="1719">
@@ -67475,10 +67475,10 @@
         </is>
       </c>
       <c r="H1719" s="2" t="n">
-        <v>46077.18522152376</v>
+        <v>46077.18522152778</v>
       </c>
       <c r="I1719" s="2" t="n">
-        <v>46082.18522152376</v>
+        <v>46082.18522152778</v>
       </c>
     </row>
     <row r="1720">
@@ -67514,10 +67514,10 @@
         </is>
       </c>
       <c r="H1720" s="2" t="n">
-        <v>46075.18522152698</v>
+        <v>46075.18522152778</v>
       </c>
       <c r="I1720" s="2" t="n">
-        <v>46080.18522152698</v>
+        <v>46080.18522152778</v>
       </c>
     </row>
     <row r="1721">
@@ -67553,10 +67553,10 @@
         </is>
       </c>
       <c r="H1721" s="2" t="n">
-        <v>46088.18522153005</v>
+        <v>46088.18522152778</v>
       </c>
       <c r="I1721" s="2" t="n">
-        <v>46093.18522153005</v>
+        <v>46093.18522152778</v>
       </c>
     </row>
     <row r="1722">
@@ -67592,10 +67592,10 @@
         </is>
       </c>
       <c r="H1722" s="2" t="n">
-        <v>46072.1852215332</v>
+        <v>46072.18522152778</v>
       </c>
       <c r="I1722" s="2" t="n">
-        <v>46077.1852215332</v>
+        <v>46077.18522152778</v>
       </c>
     </row>
     <row r="1723">
@@ -67631,10 +67631,10 @@
         </is>
       </c>
       <c r="H1723" s="2" t="n">
-        <v>46085.18522153661</v>
+        <v>46085.18522153935</v>
       </c>
       <c r="I1723" s="2" t="n">
-        <v>46090.18522153661</v>
+        <v>46090.18522153935</v>
       </c>
     </row>
     <row r="1724">
@@ -67670,10 +67670,10 @@
         </is>
       </c>
       <c r="H1724" s="2" t="n">
-        <v>46074.1852215397</v>
+        <v>46074.18522153935</v>
       </c>
       <c r="I1724" s="2" t="n">
-        <v>46079.1852215397</v>
+        <v>46079.18522153935</v>
       </c>
     </row>
     <row r="1725">
@@ -67709,10 +67709,10 @@
         </is>
       </c>
       <c r="H1725" s="2" t="n">
-        <v>46078.1852215427</v>
+        <v>46078.18522153935</v>
       </c>
       <c r="I1725" s="2" t="n">
-        <v>46083.1852215427</v>
+        <v>46083.18522153935</v>
       </c>
     </row>
     <row r="1726">
@@ -67748,10 +67748,10 @@
         </is>
       </c>
       <c r="H1726" s="2" t="n">
-        <v>46066.1852215459</v>
+        <v>46066.18522155093</v>
       </c>
       <c r="I1726" s="2" t="n">
-        <v>46071.1852215459</v>
+        <v>46071.18522155093</v>
       </c>
     </row>
     <row r="1727">
@@ -67787,10 +67787,10 @@
         </is>
       </c>
       <c r="H1727" s="2" t="n">
-        <v>46063.18522154899</v>
+        <v>46063.18522155093</v>
       </c>
       <c r="I1727" s="2" t="n">
-        <v>46068.18522154899</v>
+        <v>46068.18522155093</v>
       </c>
     </row>
     <row r="1728">
@@ -67826,10 +67826,10 @@
         </is>
       </c>
       <c r="H1728" s="2" t="n">
-        <v>46061.18522155219</v>
+        <v>46061.18522155093</v>
       </c>
       <c r="I1728" s="2" t="n">
-        <v>46066.18522155219</v>
+        <v>46066.18522155093</v>
       </c>
     </row>
     <row r="1729">
@@ -67865,10 +67865,10 @@
         </is>
       </c>
       <c r="H1729" s="2" t="n">
-        <v>46064.1852215554</v>
+        <v>46064.18522155093</v>
       </c>
       <c r="I1729" s="2" t="n">
-        <v>46069.1852215554</v>
+        <v>46069.18522155093</v>
       </c>
     </row>
     <row r="1730">
@@ -67904,10 +67904,10 @@
         </is>
       </c>
       <c r="H1730" s="2" t="n">
-        <v>46075.18522155871</v>
+        <v>46075.1852215625</v>
       </c>
       <c r="I1730" s="2" t="n">
-        <v>46080.18522155871</v>
+        <v>46080.1852215625</v>
       </c>
     </row>
     <row r="1731">
@@ -67943,10 +67943,10 @@
         </is>
       </c>
       <c r="H1731" s="2" t="n">
-        <v>46081.18522156178</v>
+        <v>46081.1852215625</v>
       </c>
       <c r="I1731" s="2" t="n">
-        <v>46086.18522156178</v>
+        <v>46086.1852215625</v>
       </c>
     </row>
     <row r="1732">
@@ -67982,10 +67982,10 @@
         </is>
       </c>
       <c r="H1732" s="2" t="n">
-        <v>46065.18522156496</v>
+        <v>46065.1852215625</v>
       </c>
       <c r="I1732" s="2" t="n">
-        <v>46070.18522156496</v>
+        <v>46070.1852215625</v>
       </c>
     </row>
     <row r="1733">
@@ -68021,10 +68021,10 @@
         </is>
       </c>
       <c r="H1733" s="2" t="n">
-        <v>46064.18522156811</v>
+        <v>46064.1852215625</v>
       </c>
       <c r="I1733" s="2" t="n">
-        <v>46069.18522156811</v>
+        <v>46069.1852215625</v>
       </c>
     </row>
     <row r="1734">
@@ -68060,10 +68060,10 @@
         </is>
       </c>
       <c r="H1734" s="2" t="n">
-        <v>46089.18522157139</v>
+        <v>46089.18522157407</v>
       </c>
       <c r="I1734" s="2" t="n">
-        <v>46094.18522157139</v>
+        <v>46094.18522157407</v>
       </c>
     </row>
     <row r="1735">
@@ -68099,10 +68099,10 @@
         </is>
       </c>
       <c r="H1735" s="2" t="n">
-        <v>46068.18522157448</v>
+        <v>46068.18522157407</v>
       </c>
       <c r="I1735" s="2" t="n">
-        <v>46073.18522157448</v>
+        <v>46073.18522157407</v>
       </c>
     </row>
     <row r="1736">
@@ -68138,10 +68138,10 @@
         </is>
       </c>
       <c r="H1736" s="2" t="n">
-        <v>46078.18522157765</v>
+        <v>46078.18522157407</v>
       </c>
       <c r="I1736" s="2" t="n">
-        <v>46083.18522157765</v>
+        <v>46083.18522157407</v>
       </c>
     </row>
     <row r="1737">
@@ -68177,10 +68177,10 @@
         </is>
       </c>
       <c r="H1737" s="2" t="n">
-        <v>46087.18522158083</v>
+        <v>46087.18522158565</v>
       </c>
       <c r="I1737" s="2" t="n">
-        <v>46092.18522158083</v>
+        <v>46092.18522158565</v>
       </c>
     </row>
     <row r="1738">
@@ -68216,10 +68216,10 @@
         </is>
       </c>
       <c r="H1738" s="2" t="n">
-        <v>46076.18522158402</v>
+        <v>46076.18522158565</v>
       </c>
       <c r="I1738" s="2" t="n">
-        <v>46081.18522158402</v>
+        <v>46081.18522158565</v>
       </c>
     </row>
     <row r="1739">
@@ -68255,10 +68255,10 @@
         </is>
       </c>
       <c r="H1739" s="2" t="n">
-        <v>46078.18522158715</v>
+        <v>46078.18522158565</v>
       </c>
       <c r="I1739" s="2" t="n">
-        <v>46083.18522158715</v>
+        <v>46083.18522158565</v>
       </c>
     </row>
     <row r="1740">
@@ -68294,10 +68294,10 @@
         </is>
       </c>
       <c r="H1740" s="2" t="n">
-        <v>46075.18522159017</v>
+        <v>46075.18522158565</v>
       </c>
       <c r="I1740" s="2" t="n">
-        <v>46080.18522159017</v>
+        <v>46080.18522158565</v>
       </c>
     </row>
     <row r="1741">
@@ -68333,10 +68333,10 @@
         </is>
       </c>
       <c r="H1741" s="2" t="n">
-        <v>46086.18522159343</v>
+        <v>46086.18522159722</v>
       </c>
       <c r="I1741" s="2" t="n">
-        <v>46091.18522159343</v>
+        <v>46091.18522159722</v>
       </c>
     </row>
     <row r="1742">
@@ -68372,10 +68372,10 @@
         </is>
       </c>
       <c r="H1742" s="2" t="n">
-        <v>46085.18522159647</v>
+        <v>46085.18522159722</v>
       </c>
       <c r="I1742" s="2" t="n">
-        <v>46090.18522159647</v>
+        <v>46090.18522159722</v>
       </c>
     </row>
     <row r="1743">
@@ -68411,10 +68411,10 @@
         </is>
       </c>
       <c r="H1743" s="2" t="n">
-        <v>46083.18522159955</v>
+        <v>46083.18522159722</v>
       </c>
       <c r="I1743" s="2" t="n">
-        <v>46088.18522159955</v>
+        <v>46088.18522159722</v>
       </c>
     </row>
     <row r="1744">
@@ -68450,10 +68450,10 @@
         </is>
       </c>
       <c r="H1744" s="2" t="n">
-        <v>46070.18522160258</v>
+        <v>46070.18522159722</v>
       </c>
       <c r="I1744" s="2" t="n">
-        <v>46075.18522160258</v>
+        <v>46075.18522159722</v>
       </c>
     </row>
     <row r="1745">
@@ -68489,10 +68489,10 @@
         </is>
       </c>
       <c r="H1745" s="2" t="n">
-        <v>46083.18522160593</v>
+        <v>46083.18522160879</v>
       </c>
       <c r="I1745" s="2" t="n">
-        <v>46088.18522160593</v>
+        <v>46088.18522160879</v>
       </c>
     </row>
     <row r="1746">
@@ -68528,10 +68528,10 @@
         </is>
       </c>
       <c r="H1746" s="2" t="n">
-        <v>46068.18522160903</v>
+        <v>46068.18522160879</v>
       </c>
       <c r="I1746" s="2" t="n">
-        <v>46073.18522160903</v>
+        <v>46073.18522160879</v>
       </c>
     </row>
     <row r="1747">
@@ -68567,10 +68567,10 @@
         </is>
       </c>
       <c r="H1747" s="2" t="n">
-        <v>46077.18522161206</v>
+        <v>46077.18522160879</v>
       </c>
       <c r="I1747" s="2" t="n">
-        <v>46082.18522161206</v>
+        <v>46082.18522160879</v>
       </c>
     </row>
     <row r="1748">
@@ -68606,10 +68606,10 @@
         </is>
       </c>
       <c r="H1748" s="2" t="n">
-        <v>46061.1852216153</v>
+        <v>46061.18522162037</v>
       </c>
       <c r="I1748" s="2" t="n">
-        <v>46066.1852216153</v>
+        <v>46066.18522162037</v>
       </c>
     </row>
     <row r="1749">
@@ -68645,10 +68645,10 @@
         </is>
       </c>
       <c r="H1749" s="2" t="n">
-        <v>46066.18522161854</v>
+        <v>46066.18522162037</v>
       </c>
       <c r="I1749" s="2" t="n">
-        <v>46071.18522161854</v>
+        <v>46071.18522162037</v>
       </c>
     </row>
     <row r="1750">
@@ -68684,10 +68684,10 @@
         </is>
       </c>
       <c r="H1750" s="2" t="n">
-        <v>46066.18522162154</v>
+        <v>46066.18522162037</v>
       </c>
       <c r="I1750" s="2" t="n">
-        <v>46071.18522162154</v>
+        <v>46071.18522162037</v>
       </c>
     </row>
     <row r="1751">
@@ -68723,10 +68723,1960 @@
         </is>
       </c>
       <c r="H1751" s="2" t="n">
-        <v>46086.1852216246</v>
+        <v>46086.18522162037</v>
       </c>
       <c r="I1751" s="2" t="n">
-        <v>46091.1852216246</v>
+        <v>46091.18522162037</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>9170c1a3-49ac-4096-8f62-8b2343897fc3</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1752" t="n">
+        <v>5044.48</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1752" s="2" t="n">
+        <v>46082.23563889218</v>
+      </c>
+      <c r="I1752" s="2" t="n">
+        <v>46087.23563889218</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>e296c0d2-7e2d-4794-acf1-d5e4421841d5</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1753" t="n">
+        <v>7989.44</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>86.04000000000001</v>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1753" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1753" s="2" t="n">
+        <v>46084.23563889649</v>
+      </c>
+      <c r="I1753" s="2" t="n">
+        <v>46089.23563889649</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>74afb41f-0b93-40ff-a9fd-99c168e556e8</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1754" t="n">
+        <v>7225.81</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1754" s="2" t="n">
+        <v>46064.23563889977</v>
+      </c>
+      <c r="I1754" s="2" t="n">
+        <v>46069.23563889977</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>309975ad-3945-4359-ac5a-1c4708531910</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1755" t="n">
+        <v>5272.05</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>96.16</v>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1755" s="2" t="n">
+        <v>46063.23563890303</v>
+      </c>
+      <c r="I1755" s="2" t="n">
+        <v>46068.23563890303</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>3e705212-95fa-4880-9718-7c822acdfc81</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1756" t="n">
+        <v>3284.65</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1756" s="2" t="n">
+        <v>46086.2356389063</v>
+      </c>
+      <c r="I1756" s="2" t="n">
+        <v>46091.2356389063</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>93c4aec4-4b3a-4f6a-bc3e-37905c7c39fc</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1757" t="n">
+        <v>2296.84</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1757" s="2" t="n">
+        <v>46087.2356389095</v>
+      </c>
+      <c r="I1757" s="2" t="n">
+        <v>46092.2356389095</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>c0cfd944-c7cd-4ca1-9deb-08176c2352d6</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1758" t="n">
+        <v>2387.55</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1758" s="2" t="n">
+        <v>46073.23563891259</v>
+      </c>
+      <c r="I1758" s="2" t="n">
+        <v>46078.23563891259</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>bae82fd6-0baf-466c-8e7c-3ea79860b08e</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1759" t="n">
+        <v>5836.69</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1759" s="2" t="n">
+        <v>46078.23563891614</v>
+      </c>
+      <c r="I1759" s="2" t="n">
+        <v>46083.23563891614</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>25c0c2b8-392c-4765-a339-cb3086ab747b</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1760" t="n">
+        <v>4599.84</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1760" s="2" t="n">
+        <v>46079.23563891928</v>
+      </c>
+      <c r="I1760" s="2" t="n">
+        <v>46084.23563891928</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>dce08e91-42b2-4729-a4e0-5c1d7c860654</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1761" t="n">
+        <v>5575.51</v>
+      </c>
+      <c r="D1761" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1761" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1761" s="2" t="n">
+        <v>46088.23563892239</v>
+      </c>
+      <c r="I1761" s="2" t="n">
+        <v>46093.23563892239</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>12c64a62-689d-4657-9b7d-84f5ffde97c6</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1762" t="n">
+        <v>6721.79</v>
+      </c>
+      <c r="D1762" t="n">
+        <v>98.84</v>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1762" s="2" t="n">
+        <v>46068.23563892567</v>
+      </c>
+      <c r="I1762" s="2" t="n">
+        <v>46073.23563892567</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>f9d666aa-c4de-43a8-9fa3-7865d5fccc56</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1763" t="n">
+        <v>9809.32</v>
+      </c>
+      <c r="D1763" t="n">
+        <v>95.89</v>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1763" s="2" t="n">
+        <v>46089.23563892905</v>
+      </c>
+      <c r="I1763" s="2" t="n">
+        <v>46094.23563892905</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>27fe8019-fd17-4109-b75a-128ed57b18fa</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1764" t="n">
+        <v>3471.82</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1764" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1764" s="2" t="n">
+        <v>46090.23563893232</v>
+      </c>
+      <c r="I1764" s="2" t="n">
+        <v>46095.23563893232</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>17ee1e1e-5681-422b-89e0-b3484743d9fc</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1765" t="n">
+        <v>5371.28</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1765" s="2" t="n">
+        <v>46087.23563893538</v>
+      </c>
+      <c r="I1765" s="2" t="n">
+        <v>46092.23563893538</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2634c01f-3652-4f11-9402-abde766bbb0f</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1766" t="n">
+        <v>8296.18</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1766" s="2" t="n">
+        <v>46086.23563893846</v>
+      </c>
+      <c r="I1766" s="2" t="n">
+        <v>46091.23563893846</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>d4f38b3c-241b-46aa-8d95-9f7aedd15fe4</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1767" t="n">
+        <v>4542.22</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1767" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1767" s="2" t="n">
+        <v>46069.2356389419</v>
+      </c>
+      <c r="I1767" s="2" t="n">
+        <v>46074.2356389419</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>11c08e16-1dce-482f-ad40-d8be8b67cdbf</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1768" t="n">
+        <v>6732.65</v>
+      </c>
+      <c r="D1768" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1768" s="2" t="n">
+        <v>46077.23563894499</v>
+      </c>
+      <c r="I1768" s="2" t="n">
+        <v>46082.23563894499</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2d02b18a-3ade-402f-bf3b-9e23c29e5d3e</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1769" t="n">
+        <v>5698.68</v>
+      </c>
+      <c r="D1769" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1769" s="2" t="n">
+        <v>46088.23563894818</v>
+      </c>
+      <c r="I1769" s="2" t="n">
+        <v>46093.23563894818</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>bd660620-205f-4836-9c1e-2ed6c5f3abc5</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1770" t="n">
+        <v>6492.53</v>
+      </c>
+      <c r="D1770" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1770" s="2" t="n">
+        <v>46068.23563895162</v>
+      </c>
+      <c r="I1770" s="2" t="n">
+        <v>46073.23563895162</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>b110d69b-4f13-47ee-8847-fa4568bba672</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1771" t="n">
+        <v>6638</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1771" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1771" s="2" t="n">
+        <v>46079.2356389547</v>
+      </c>
+      <c r="I1771" s="2" t="n">
+        <v>46084.2356389547</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>c6e116af-5ee1-4d4a-a1b3-1118a5b9a178</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1772" t="n">
+        <v>6439.6</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1772" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1772" s="2" t="n">
+        <v>46066.23563895777</v>
+      </c>
+      <c r="I1772" s="2" t="n">
+        <v>46071.23563895777</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>7ee40d22-1f4f-4583-9500-9dcb76fe803b</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1773" t="n">
+        <v>6326.54</v>
+      </c>
+      <c r="D1773" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1773" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1773" s="2" t="n">
+        <v>46074.23563896103</v>
+      </c>
+      <c r="I1773" s="2" t="n">
+        <v>46079.23563896103</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>11be0600-7eb2-41dc-883c-5d6090a9087c</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1774" t="n">
+        <v>7903.06</v>
+      </c>
+      <c r="D1774" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1774" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1774" s="2" t="n">
+        <v>46066.23563896459</v>
+      </c>
+      <c r="I1774" s="2" t="n">
+        <v>46071.23563896459</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>7e3b4db0-f84f-4eb6-9510-e8aac1dddf25</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1775" t="n">
+        <v>1569.23</v>
+      </c>
+      <c r="D1775" t="n">
+        <v>87.64</v>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1775" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1775" s="2" t="n">
+        <v>46063.23563896763</v>
+      </c>
+      <c r="I1775" s="2" t="n">
+        <v>46068.23563896763</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>4f9aea4b-0c8d-405c-8433-600df2917004</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1776" t="n">
+        <v>8674.52</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1776" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1776" s="2" t="n">
+        <v>46063.23563897067</v>
+      </c>
+      <c r="I1776" s="2" t="n">
+        <v>46068.23563897067</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>401392e4-960b-49f7-bfdd-07258dfd613e</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1777" t="n">
+        <v>5428.68</v>
+      </c>
+      <c r="D1777" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1777" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1777" s="2" t="n">
+        <v>46064.23563897398</v>
+      </c>
+      <c r="I1777" s="2" t="n">
+        <v>46069.23563897398</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>5d5483b9-ee6e-4948-a0c2-7b561658513b</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1778" t="n">
+        <v>1779.06</v>
+      </c>
+      <c r="D1778" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1778" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1778" s="2" t="n">
+        <v>46071.23563897709</v>
+      </c>
+      <c r="I1778" s="2" t="n">
+        <v>46076.23563897709</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>ed14d143-ae93-484f-95bb-f116b5c90a01</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1779" t="n">
+        <v>5251.7</v>
+      </c>
+      <c r="D1779" t="n">
+        <v>97.66</v>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1779" s="2" t="n">
+        <v>46082.23563898017</v>
+      </c>
+      <c r="I1779" s="2" t="n">
+        <v>46087.23563898017</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>d941bab9-52f1-4092-9841-a7d35ae84bd1</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1780" t="n">
+        <v>4387.17</v>
+      </c>
+      <c r="D1780" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1780" s="2" t="n">
+        <v>46062.23563898334</v>
+      </c>
+      <c r="I1780" s="2" t="n">
+        <v>46067.23563898334</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>060cd397-9116-416f-8aa7-a068b6214d57</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1781" t="n">
+        <v>5146.19</v>
+      </c>
+      <c r="D1781" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1781" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1781" s="2" t="n">
+        <v>46072.23563898659</v>
+      </c>
+      <c r="I1781" s="2" t="n">
+        <v>46077.23563898659</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>b200f386-6524-48b2-a742-872dc159a39e</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1782" t="n">
+        <v>9810.469999999999</v>
+      </c>
+      <c r="D1782" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1782" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1782" s="2" t="n">
+        <v>46077.23563898979</v>
+      </c>
+      <c r="I1782" s="2" t="n">
+        <v>46082.23563898979</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>d0f5c278-22ae-4133-af70-2cda565a1164</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1783" t="n">
+        <v>6025.31</v>
+      </c>
+      <c r="D1783" t="n">
+        <v>88.61</v>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1783" s="2" t="n">
+        <v>46061.23563899301</v>
+      </c>
+      <c r="I1783" s="2" t="n">
+        <v>46066.23563899301</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>3a6c35cf-7172-4b73-8bcd-867ea1c5358d</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1784" t="n">
+        <v>8124.72</v>
+      </c>
+      <c r="D1784" t="n">
+        <v>92.43000000000001</v>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1784" s="2" t="n">
+        <v>46066.23563899614</v>
+      </c>
+      <c r="I1784" s="2" t="n">
+        <v>46071.23563899614</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>3ce9dee6-577f-4c46-b3f0-9459bf39048b</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1785" t="n">
+        <v>5619.76</v>
+      </c>
+      <c r="D1785" t="n">
+        <v>96.20999999999999</v>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1785" s="2" t="n">
+        <v>46063.23563899941</v>
+      </c>
+      <c r="I1785" s="2" t="n">
+        <v>46068.23563899941</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>eac6d24d-5ce9-42e5-8402-1346ecbc5adf</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1786" t="n">
+        <v>1910.26</v>
+      </c>
+      <c r="D1786" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1786" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1786" s="2" t="n">
+        <v>46063.23563900251</v>
+      </c>
+      <c r="I1786" s="2" t="n">
+        <v>46068.23563900251</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>98c9891a-f135-435f-8625-5bf2356d80d8</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1787" t="n">
+        <v>8621.280000000001</v>
+      </c>
+      <c r="D1787" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1787" s="2" t="n">
+        <v>46062.23563900564</v>
+      </c>
+      <c r="I1787" s="2" t="n">
+        <v>46067.23563900564</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>543d97e5-a22a-4276-8b0f-9ec6eb408028</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1788" t="n">
+        <v>5751.06</v>
+      </c>
+      <c r="D1788" t="n">
+        <v>97.20999999999999</v>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1788" s="2" t="n">
+        <v>46061.23563900893</v>
+      </c>
+      <c r="I1788" s="2" t="n">
+        <v>46066.23563900893</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>86a1dc05-25d8-4ed1-8c8c-f3a46379ddf2</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1789" t="n">
+        <v>6192.78</v>
+      </c>
+      <c r="D1789" t="n">
+        <v>87.16</v>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1789" s="2" t="n">
+        <v>46090.23563901213</v>
+      </c>
+      <c r="I1789" s="2" t="n">
+        <v>46095.23563901213</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>f7a792c3-13e8-46eb-b89b-6277ab4aa0a1</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1790" t="n">
+        <v>2327.14</v>
+      </c>
+      <c r="D1790" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1790" s="2" t="n">
+        <v>46067.23563901529</v>
+      </c>
+      <c r="I1790" s="2" t="n">
+        <v>46072.23563901529</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>e4d30515-7fae-41b8-ba0c-0d3f0a8bcc21</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1791" t="n">
+        <v>8863.02</v>
+      </c>
+      <c r="D1791" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1791" s="2" t="n">
+        <v>46066.23563901853</v>
+      </c>
+      <c r="I1791" s="2" t="n">
+        <v>46071.23563901853</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>d14ade62-f764-487b-be12-7082714670a2</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1792" t="n">
+        <v>3807.52</v>
+      </c>
+      <c r="D1792" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1792" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1792" s="2" t="n">
+        <v>46061.23563902177</v>
+      </c>
+      <c r="I1792" s="2" t="n">
+        <v>46066.23563902177</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>070eff3b-2627-4eb9-9830-9728777ba993</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1793" t="n">
+        <v>5617.71</v>
+      </c>
+      <c r="D1793" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1793" s="2" t="n">
+        <v>46090.23563902505</v>
+      </c>
+      <c r="I1793" s="2" t="n">
+        <v>46095.23563902505</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>067ba303-2e1f-440d-b282-609925848884</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1794" t="n">
+        <v>5045.09</v>
+      </c>
+      <c r="D1794" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1794" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1794" s="2" t="n">
+        <v>46070.2356390281</v>
+      </c>
+      <c r="I1794" s="2" t="n">
+        <v>46075.2356390281</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>c1c850de-9c05-4e3c-a681-66c9f6257780</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1795" t="n">
+        <v>6525.39</v>
+      </c>
+      <c r="D1795" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1795" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1795" s="2" t="n">
+        <v>46089.23563903131</v>
+      </c>
+      <c r="I1795" s="2" t="n">
+        <v>46094.23563903131</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>4a98c36d-6ad8-42d6-9f86-8b6bcd2bc3e8</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1796" t="n">
+        <v>3056.66</v>
+      </c>
+      <c r="D1796" t="n">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1796" s="2" t="n">
+        <v>46088.23563903548</v>
+      </c>
+      <c r="I1796" s="2" t="n">
+        <v>46093.23563903548</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>6444ecc5-7444-4971-8cfe-63fe21a8719f</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1797" t="n">
+        <v>1320.78</v>
+      </c>
+      <c r="D1797" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1797" s="2" t="n">
+        <v>46084.23563903856</v>
+      </c>
+      <c r="I1797" s="2" t="n">
+        <v>46089.23563903856</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>f1188708-c6c6-42ae-affd-e5a13c8ec51a</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1798" t="n">
+        <v>7654.82</v>
+      </c>
+      <c r="D1798" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1798" s="2" t="n">
+        <v>46066.23563904161</v>
+      </c>
+      <c r="I1798" s="2" t="n">
+        <v>46071.23563904161</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>7ea5d8ab-8fe9-4c66-9331-654bfd286b63</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1799" t="n">
+        <v>9323.360000000001</v>
+      </c>
+      <c r="D1799" t="n">
+        <v>94.48999999999999</v>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1799" s="2" t="n">
+        <v>46073.23563904529</v>
+      </c>
+      <c r="I1799" s="2" t="n">
+        <v>46078.23563904529</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>ce63100e-276e-447c-8b35-2088592499f9</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1800" t="n">
+        <v>2599.29</v>
+      </c>
+      <c r="D1800" t="n">
+        <v>89.86</v>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1800" s="2" t="n">
+        <v>46062.23563904837</v>
+      </c>
+      <c r="I1800" s="2" t="n">
+        <v>46067.23563904837</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>592cd027-c468-4054-824b-dbc7b81af69a</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1801" t="n">
+        <v>9267.74</v>
+      </c>
+      <c r="D1801" t="n">
+        <v>93.61</v>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1801" s="2" t="n">
+        <v>46062.23563905143</v>
+      </c>
+      <c r="I1801" s="2" t="n">
+        <v>46067.23563905143</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1801"/>
+  <dimension ref="A1:I1851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68762,10 +68762,10 @@
         </is>
       </c>
       <c r="H1752" s="2" t="n">
-        <v>46082.23563889218</v>
+        <v>46082.23563888889</v>
       </c>
       <c r="I1752" s="2" t="n">
-        <v>46087.23563889218</v>
+        <v>46087.23563888889</v>
       </c>
     </row>
     <row r="1753">
@@ -68801,10 +68801,10 @@
         </is>
       </c>
       <c r="H1753" s="2" t="n">
-        <v>46084.23563889649</v>
+        <v>46084.23563890046</v>
       </c>
       <c r="I1753" s="2" t="n">
-        <v>46089.23563889649</v>
+        <v>46089.23563890046</v>
       </c>
     </row>
     <row r="1754">
@@ -68840,10 +68840,10 @@
         </is>
       </c>
       <c r="H1754" s="2" t="n">
-        <v>46064.23563889977</v>
+        <v>46064.23563890046</v>
       </c>
       <c r="I1754" s="2" t="n">
-        <v>46069.23563889977</v>
+        <v>46069.23563890046</v>
       </c>
     </row>
     <row r="1755">
@@ -68879,10 +68879,10 @@
         </is>
       </c>
       <c r="H1755" s="2" t="n">
-        <v>46063.23563890303</v>
+        <v>46063.23563890046</v>
       </c>
       <c r="I1755" s="2" t="n">
-        <v>46068.23563890303</v>
+        <v>46068.23563890046</v>
       </c>
     </row>
     <row r="1756">
@@ -68918,10 +68918,10 @@
         </is>
       </c>
       <c r="H1756" s="2" t="n">
-        <v>46086.2356389063</v>
+        <v>46086.23563891204</v>
       </c>
       <c r="I1756" s="2" t="n">
-        <v>46091.2356389063</v>
+        <v>46091.23563891204</v>
       </c>
     </row>
     <row r="1757">
@@ -68957,10 +68957,10 @@
         </is>
       </c>
       <c r="H1757" s="2" t="n">
-        <v>46087.2356389095</v>
+        <v>46087.23563891204</v>
       </c>
       <c r="I1757" s="2" t="n">
-        <v>46092.2356389095</v>
+        <v>46092.23563891204</v>
       </c>
     </row>
     <row r="1758">
@@ -68996,10 +68996,10 @@
         </is>
       </c>
       <c r="H1758" s="2" t="n">
-        <v>46073.23563891259</v>
+        <v>46073.23563891204</v>
       </c>
       <c r="I1758" s="2" t="n">
-        <v>46078.23563891259</v>
+        <v>46078.23563891204</v>
       </c>
     </row>
     <row r="1759">
@@ -69035,10 +69035,10 @@
         </is>
       </c>
       <c r="H1759" s="2" t="n">
-        <v>46078.23563891614</v>
+        <v>46078.23563891204</v>
       </c>
       <c r="I1759" s="2" t="n">
-        <v>46083.23563891614</v>
+        <v>46083.23563891204</v>
       </c>
     </row>
     <row r="1760">
@@ -69074,10 +69074,10 @@
         </is>
       </c>
       <c r="H1760" s="2" t="n">
-        <v>46079.23563891928</v>
+        <v>46079.23563892361</v>
       </c>
       <c r="I1760" s="2" t="n">
-        <v>46084.23563891928</v>
+        <v>46084.23563892361</v>
       </c>
     </row>
     <row r="1761">
@@ -69113,10 +69113,10 @@
         </is>
       </c>
       <c r="H1761" s="2" t="n">
-        <v>46088.23563892239</v>
+        <v>46088.23563892361</v>
       </c>
       <c r="I1761" s="2" t="n">
-        <v>46093.23563892239</v>
+        <v>46093.23563892361</v>
       </c>
     </row>
     <row r="1762">
@@ -69152,10 +69152,10 @@
         </is>
       </c>
       <c r="H1762" s="2" t="n">
-        <v>46068.23563892567</v>
+        <v>46068.23563892361</v>
       </c>
       <c r="I1762" s="2" t="n">
-        <v>46073.23563892567</v>
+        <v>46073.23563892361</v>
       </c>
     </row>
     <row r="1763">
@@ -69191,10 +69191,10 @@
         </is>
       </c>
       <c r="H1763" s="2" t="n">
-        <v>46089.23563892905</v>
+        <v>46089.23563892361</v>
       </c>
       <c r="I1763" s="2" t="n">
-        <v>46094.23563892905</v>
+        <v>46094.23563892361</v>
       </c>
     </row>
     <row r="1764">
@@ -69230,10 +69230,10 @@
         </is>
       </c>
       <c r="H1764" s="2" t="n">
-        <v>46090.23563893232</v>
+        <v>46090.23563893518</v>
       </c>
       <c r="I1764" s="2" t="n">
-        <v>46095.23563893232</v>
+        <v>46095.23563893518</v>
       </c>
     </row>
     <row r="1765">
@@ -69269,10 +69269,10 @@
         </is>
       </c>
       <c r="H1765" s="2" t="n">
-        <v>46087.23563893538</v>
+        <v>46087.23563893518</v>
       </c>
       <c r="I1765" s="2" t="n">
-        <v>46092.23563893538</v>
+        <v>46092.23563893518</v>
       </c>
     </row>
     <row r="1766">
@@ -69308,10 +69308,10 @@
         </is>
       </c>
       <c r="H1766" s="2" t="n">
-        <v>46086.23563893846</v>
+        <v>46086.23563893518</v>
       </c>
       <c r="I1766" s="2" t="n">
-        <v>46091.23563893846</v>
+        <v>46091.23563893518</v>
       </c>
     </row>
     <row r="1767">
@@ -69347,10 +69347,10 @@
         </is>
       </c>
       <c r="H1767" s="2" t="n">
-        <v>46069.2356389419</v>
+        <v>46069.23563894676</v>
       </c>
       <c r="I1767" s="2" t="n">
-        <v>46074.2356389419</v>
+        <v>46074.23563894676</v>
       </c>
     </row>
     <row r="1768">
@@ -69386,10 +69386,10 @@
         </is>
       </c>
       <c r="H1768" s="2" t="n">
-        <v>46077.23563894499</v>
+        <v>46077.23563894676</v>
       </c>
       <c r="I1768" s="2" t="n">
-        <v>46082.23563894499</v>
+        <v>46082.23563894676</v>
       </c>
     </row>
     <row r="1769">
@@ -69425,10 +69425,10 @@
         </is>
       </c>
       <c r="H1769" s="2" t="n">
-        <v>46088.23563894818</v>
+        <v>46088.23563894676</v>
       </c>
       <c r="I1769" s="2" t="n">
-        <v>46093.23563894818</v>
+        <v>46093.23563894676</v>
       </c>
     </row>
     <row r="1770">
@@ -69464,10 +69464,10 @@
         </is>
       </c>
       <c r="H1770" s="2" t="n">
-        <v>46068.23563895162</v>
+        <v>46068.23563894676</v>
       </c>
       <c r="I1770" s="2" t="n">
-        <v>46073.23563895162</v>
+        <v>46073.23563894676</v>
       </c>
     </row>
     <row r="1771">
@@ -69503,10 +69503,10 @@
         </is>
       </c>
       <c r="H1771" s="2" t="n">
-        <v>46079.2356389547</v>
+        <v>46079.23563895834</v>
       </c>
       <c r="I1771" s="2" t="n">
-        <v>46084.2356389547</v>
+        <v>46084.23563895834</v>
       </c>
     </row>
     <row r="1772">
@@ -69542,10 +69542,10 @@
         </is>
       </c>
       <c r="H1772" s="2" t="n">
-        <v>46066.23563895777</v>
+        <v>46066.23563895834</v>
       </c>
       <c r="I1772" s="2" t="n">
-        <v>46071.23563895777</v>
+        <v>46071.23563895834</v>
       </c>
     </row>
     <row r="1773">
@@ -69581,10 +69581,10 @@
         </is>
       </c>
       <c r="H1773" s="2" t="n">
-        <v>46074.23563896103</v>
+        <v>46074.23563895834</v>
       </c>
       <c r="I1773" s="2" t="n">
-        <v>46079.23563896103</v>
+        <v>46079.23563895834</v>
       </c>
     </row>
     <row r="1774">
@@ -69620,10 +69620,10 @@
         </is>
       </c>
       <c r="H1774" s="2" t="n">
-        <v>46066.23563896459</v>
+        <v>46066.23563896991</v>
       </c>
       <c r="I1774" s="2" t="n">
-        <v>46071.23563896459</v>
+        <v>46071.23563896991</v>
       </c>
     </row>
     <row r="1775">
@@ -69659,10 +69659,10 @@
         </is>
       </c>
       <c r="H1775" s="2" t="n">
-        <v>46063.23563896763</v>
+        <v>46063.23563896991</v>
       </c>
       <c r="I1775" s="2" t="n">
-        <v>46068.23563896763</v>
+        <v>46068.23563896991</v>
       </c>
     </row>
     <row r="1776">
@@ -69698,10 +69698,10 @@
         </is>
       </c>
       <c r="H1776" s="2" t="n">
-        <v>46063.23563897067</v>
+        <v>46063.23563896991</v>
       </c>
       <c r="I1776" s="2" t="n">
-        <v>46068.23563897067</v>
+        <v>46068.23563896991</v>
       </c>
     </row>
     <row r="1777">
@@ -69737,10 +69737,10 @@
         </is>
       </c>
       <c r="H1777" s="2" t="n">
-        <v>46064.23563897398</v>
+        <v>46064.23563896991</v>
       </c>
       <c r="I1777" s="2" t="n">
-        <v>46069.23563897398</v>
+        <v>46069.23563896991</v>
       </c>
     </row>
     <row r="1778">
@@ -69776,10 +69776,10 @@
         </is>
       </c>
       <c r="H1778" s="2" t="n">
-        <v>46071.23563897709</v>
+        <v>46071.23563898148</v>
       </c>
       <c r="I1778" s="2" t="n">
-        <v>46076.23563897709</v>
+        <v>46076.23563898148</v>
       </c>
     </row>
     <row r="1779">
@@ -69815,10 +69815,10 @@
         </is>
       </c>
       <c r="H1779" s="2" t="n">
-        <v>46082.23563898017</v>
+        <v>46082.23563898148</v>
       </c>
       <c r="I1779" s="2" t="n">
-        <v>46087.23563898017</v>
+        <v>46087.23563898148</v>
       </c>
     </row>
     <row r="1780">
@@ -69854,10 +69854,10 @@
         </is>
       </c>
       <c r="H1780" s="2" t="n">
-        <v>46062.23563898334</v>
+        <v>46062.23563898148</v>
       </c>
       <c r="I1780" s="2" t="n">
-        <v>46067.23563898334</v>
+        <v>46067.23563898148</v>
       </c>
     </row>
     <row r="1781">
@@ -69893,10 +69893,10 @@
         </is>
       </c>
       <c r="H1781" s="2" t="n">
-        <v>46072.23563898659</v>
+        <v>46072.23563898148</v>
       </c>
       <c r="I1781" s="2" t="n">
-        <v>46077.23563898659</v>
+        <v>46077.23563898148</v>
       </c>
     </row>
     <row r="1782">
@@ -69932,10 +69932,10 @@
         </is>
       </c>
       <c r="H1782" s="2" t="n">
-        <v>46077.23563898979</v>
+        <v>46077.23563899306</v>
       </c>
       <c r="I1782" s="2" t="n">
-        <v>46082.23563898979</v>
+        <v>46082.23563899306</v>
       </c>
     </row>
     <row r="1783">
@@ -69971,10 +69971,10 @@
         </is>
       </c>
       <c r="H1783" s="2" t="n">
-        <v>46061.23563899301</v>
+        <v>46061.23563899306</v>
       </c>
       <c r="I1783" s="2" t="n">
-        <v>46066.23563899301</v>
+        <v>46066.23563899306</v>
       </c>
     </row>
     <row r="1784">
@@ -70010,10 +70010,10 @@
         </is>
       </c>
       <c r="H1784" s="2" t="n">
-        <v>46066.23563899614</v>
+        <v>46066.23563899306</v>
       </c>
       <c r="I1784" s="2" t="n">
-        <v>46071.23563899614</v>
+        <v>46071.23563899306</v>
       </c>
     </row>
     <row r="1785">
@@ -70049,10 +70049,10 @@
         </is>
       </c>
       <c r="H1785" s="2" t="n">
-        <v>46063.23563899941</v>
+        <v>46063.23563900463</v>
       </c>
       <c r="I1785" s="2" t="n">
-        <v>46068.23563899941</v>
+        <v>46068.23563900463</v>
       </c>
     </row>
     <row r="1786">
@@ -70088,10 +70088,10 @@
         </is>
       </c>
       <c r="H1786" s="2" t="n">
-        <v>46063.23563900251</v>
+        <v>46063.23563900463</v>
       </c>
       <c r="I1786" s="2" t="n">
-        <v>46068.23563900251</v>
+        <v>46068.23563900463</v>
       </c>
     </row>
     <row r="1787">
@@ -70127,10 +70127,10 @@
         </is>
       </c>
       <c r="H1787" s="2" t="n">
-        <v>46062.23563900564</v>
+        <v>46062.23563900463</v>
       </c>
       <c r="I1787" s="2" t="n">
-        <v>46067.23563900564</v>
+        <v>46067.23563900463</v>
       </c>
     </row>
     <row r="1788">
@@ -70166,10 +70166,10 @@
         </is>
       </c>
       <c r="H1788" s="2" t="n">
-        <v>46061.23563900893</v>
+        <v>46061.23563900463</v>
       </c>
       <c r="I1788" s="2" t="n">
-        <v>46066.23563900893</v>
+        <v>46066.23563900463</v>
       </c>
     </row>
     <row r="1789">
@@ -70205,10 +70205,10 @@
         </is>
       </c>
       <c r="H1789" s="2" t="n">
-        <v>46090.23563901213</v>
+        <v>46090.2356390162</v>
       </c>
       <c r="I1789" s="2" t="n">
-        <v>46095.23563901213</v>
+        <v>46095.2356390162</v>
       </c>
     </row>
     <row r="1790">
@@ -70244,10 +70244,10 @@
         </is>
       </c>
       <c r="H1790" s="2" t="n">
-        <v>46067.23563901529</v>
+        <v>46067.2356390162</v>
       </c>
       <c r="I1790" s="2" t="n">
-        <v>46072.23563901529</v>
+        <v>46072.2356390162</v>
       </c>
     </row>
     <row r="1791">
@@ -70283,10 +70283,10 @@
         </is>
       </c>
       <c r="H1791" s="2" t="n">
-        <v>46066.23563901853</v>
+        <v>46066.2356390162</v>
       </c>
       <c r="I1791" s="2" t="n">
-        <v>46071.23563901853</v>
+        <v>46071.2356390162</v>
       </c>
     </row>
     <row r="1792">
@@ -70322,10 +70322,10 @@
         </is>
       </c>
       <c r="H1792" s="2" t="n">
-        <v>46061.23563902177</v>
+        <v>46061.2356390162</v>
       </c>
       <c r="I1792" s="2" t="n">
-        <v>46066.23563902177</v>
+        <v>46066.2356390162</v>
       </c>
     </row>
     <row r="1793">
@@ -70361,10 +70361,10 @@
         </is>
       </c>
       <c r="H1793" s="2" t="n">
-        <v>46090.23563902505</v>
+        <v>46090.23563902778</v>
       </c>
       <c r="I1793" s="2" t="n">
-        <v>46095.23563902505</v>
+        <v>46095.23563902778</v>
       </c>
     </row>
     <row r="1794">
@@ -70400,10 +70400,10 @@
         </is>
       </c>
       <c r="H1794" s="2" t="n">
-        <v>46070.2356390281</v>
+        <v>46070.23563902778</v>
       </c>
       <c r="I1794" s="2" t="n">
-        <v>46075.2356390281</v>
+        <v>46075.23563902778</v>
       </c>
     </row>
     <row r="1795">
@@ -70439,10 +70439,10 @@
         </is>
       </c>
       <c r="H1795" s="2" t="n">
-        <v>46089.23563903131</v>
+        <v>46089.23563902778</v>
       </c>
       <c r="I1795" s="2" t="n">
-        <v>46094.23563903131</v>
+        <v>46094.23563902778</v>
       </c>
     </row>
     <row r="1796">
@@ -70478,10 +70478,10 @@
         </is>
       </c>
       <c r="H1796" s="2" t="n">
-        <v>46088.23563903548</v>
+        <v>46088.23563903935</v>
       </c>
       <c r="I1796" s="2" t="n">
-        <v>46093.23563903548</v>
+        <v>46093.23563903935</v>
       </c>
     </row>
     <row r="1797">
@@ -70517,10 +70517,10 @@
         </is>
       </c>
       <c r="H1797" s="2" t="n">
-        <v>46084.23563903856</v>
+        <v>46084.23563903935</v>
       </c>
       <c r="I1797" s="2" t="n">
-        <v>46089.23563903856</v>
+        <v>46089.23563903935</v>
       </c>
     </row>
     <row r="1798">
@@ -70556,10 +70556,10 @@
         </is>
       </c>
       <c r="H1798" s="2" t="n">
-        <v>46066.23563904161</v>
+        <v>46066.23563903935</v>
       </c>
       <c r="I1798" s="2" t="n">
-        <v>46071.23563904161</v>
+        <v>46071.23563903935</v>
       </c>
     </row>
     <row r="1799">
@@ -70595,10 +70595,10 @@
         </is>
       </c>
       <c r="H1799" s="2" t="n">
-        <v>46073.23563904529</v>
+        <v>46073.23563905092</v>
       </c>
       <c r="I1799" s="2" t="n">
-        <v>46078.23563904529</v>
+        <v>46078.23563905092</v>
       </c>
     </row>
     <row r="1800">
@@ -70634,10 +70634,10 @@
         </is>
       </c>
       <c r="H1800" s="2" t="n">
-        <v>46062.23563904837</v>
+        <v>46062.23563905092</v>
       </c>
       <c r="I1800" s="2" t="n">
-        <v>46067.23563904837</v>
+        <v>46067.23563905092</v>
       </c>
     </row>
     <row r="1801">
@@ -70673,10 +70673,1960 @@
         </is>
       </c>
       <c r="H1801" s="2" t="n">
-        <v>46062.23563905143</v>
+        <v>46062.23563905092</v>
       </c>
       <c r="I1801" s="2" t="n">
-        <v>46067.23563905143</v>
+        <v>46067.23563905092</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>235b3d11-7234-4c78-a4f7-e6cac1fa631f</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1802" t="n">
+        <v>1134.45</v>
+      </c>
+      <c r="D1802" t="n">
+        <v>89</v>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1802" s="2" t="n">
+        <v>46080.275891374</v>
+      </c>
+      <c r="I1802" s="2" t="n">
+        <v>46085.275891374</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>96e6f4b0-fd8c-4bef-8d6d-6e74c85b380a</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1803" t="n">
+        <v>9862.700000000001</v>
+      </c>
+      <c r="D1803" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1803" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1803" s="2" t="n">
+        <v>46065.27589137823</v>
+      </c>
+      <c r="I1803" s="2" t="n">
+        <v>46070.27589137823</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>66dd239a-54b2-4ce9-8a63-e24729d86c9e</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1804" t="n">
+        <v>6352.66</v>
+      </c>
+      <c r="D1804" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1804" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1804" s="2" t="n">
+        <v>46066.27589138141</v>
+      </c>
+      <c r="I1804" s="2" t="n">
+        <v>46071.27589138141</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>abba9264-795a-4643-85c0-d4701fd46654</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1805" t="n">
+        <v>2649.99</v>
+      </c>
+      <c r="D1805" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1805" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1805" s="2" t="n">
+        <v>46065.27589138494</v>
+      </c>
+      <c r="I1805" s="2" t="n">
+        <v>46070.27589138494</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>1c958d53-edeb-4f83-b7c4-e9fe07ae64ee</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1806" t="n">
+        <v>9434.74</v>
+      </c>
+      <c r="D1806" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1806" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1806" s="2" t="n">
+        <v>46063.27589138811</v>
+      </c>
+      <c r="I1806" s="2" t="n">
+        <v>46068.27589138811</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>5a91d4c6-f63b-4b05-82f0-17524733a43b</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1807" t="n">
+        <v>5076.83</v>
+      </c>
+      <c r="D1807" t="n">
+        <v>97.77</v>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1807" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1807" s="2" t="n">
+        <v>46069.27589139123</v>
+      </c>
+      <c r="I1807" s="2" t="n">
+        <v>46074.27589139123</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>3f29d64d-9c4a-4fd3-b9cf-fe8aaac6005a</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1808" t="n">
+        <v>9781.4</v>
+      </c>
+      <c r="D1808" t="n">
+        <v>98.48999999999999</v>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1808" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1808" s="2" t="n">
+        <v>46074.27589139454</v>
+      </c>
+      <c r="I1808" s="2" t="n">
+        <v>46079.27589139454</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>3b848b4e-57b3-486c-847c-bbe64e631818</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1809" t="n">
+        <v>4578.43</v>
+      </c>
+      <c r="D1809" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1809" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1809" s="2" t="n">
+        <v>46079.27589139837</v>
+      </c>
+      <c r="I1809" s="2" t="n">
+        <v>46084.27589139837</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>f110d18a-5352-4f48-9222-1aa9f22ec91a</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1810" t="n">
+        <v>8666.6</v>
+      </c>
+      <c r="D1810" t="n">
+        <v>96.51000000000001</v>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1810" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1810" s="2" t="n">
+        <v>46074.27589140169</v>
+      </c>
+      <c r="I1810" s="2" t="n">
+        <v>46079.27589140169</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>5341cd1a-f5ab-425d-8187-802e894793c4</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1811" t="n">
+        <v>4291.46</v>
+      </c>
+      <c r="D1811" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1811" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1811" s="2" t="n">
+        <v>46078.27589140482</v>
+      </c>
+      <c r="I1811" s="2" t="n">
+        <v>46083.27589140482</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>ed20c832-3148-446c-b14d-bc6ea65eb65b</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1812" t="n">
+        <v>3466.74</v>
+      </c>
+      <c r="D1812" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1812" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1812" s="2" t="n">
+        <v>46075.27589140823</v>
+      </c>
+      <c r="I1812" s="2" t="n">
+        <v>46080.27589140823</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>e689a622-3c9f-4f0c-a59d-600ffcdfa8cc</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1813" t="n">
+        <v>5745.55</v>
+      </c>
+      <c r="D1813" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1813" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1813" s="2" t="n">
+        <v>46089.27589141133</v>
+      </c>
+      <c r="I1813" s="2" t="n">
+        <v>46094.27589141133</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>6dc487af-7e77-4d23-a9b9-3db228a18371</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1814" t="n">
+        <v>2227.51</v>
+      </c>
+      <c r="D1814" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1814" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1814" s="2" t="n">
+        <v>46081.27589141442</v>
+      </c>
+      <c r="I1814" s="2" t="n">
+        <v>46086.27589141442</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>4063f34c-5c30-4c20-a67e-0177ac0aa92c</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1815" t="n">
+        <v>7428.68</v>
+      </c>
+      <c r="D1815" t="n">
+        <v>96.04000000000001</v>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1815" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1815" s="2" t="n">
+        <v>46090.27589141779</v>
+      </c>
+      <c r="I1815" s="2" t="n">
+        <v>46095.27589141779</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>c967873b-a6e3-4060-bb9f-2945774e48ea</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1816" t="n">
+        <v>8257.08</v>
+      </c>
+      <c r="D1816" t="n">
+        <v>87.06</v>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1816" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1816" s="2" t="n">
+        <v>46072.27589142094</v>
+      </c>
+      <c r="I1816" s="2" t="n">
+        <v>46077.27589142094</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>10a3fd8a-69c9-40e3-bbfb-7042f4801d01</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1817" t="n">
+        <v>4196.07</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1817" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1817" s="2" t="n">
+        <v>46073.27589142398</v>
+      </c>
+      <c r="I1817" s="2" t="n">
+        <v>46078.27589142398</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>7a01a05b-895c-498b-9ff8-4a57efa27c97</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1818" t="n">
+        <v>5744.13</v>
+      </c>
+      <c r="D1818" t="n">
+        <v>85.51000000000001</v>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1818" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1818" s="2" t="n">
+        <v>46083.27589142705</v>
+      </c>
+      <c r="I1818" s="2" t="n">
+        <v>46088.27589142705</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>f7f36eda-5a23-4f3a-91d6-c7f8880a740a</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1819" t="n">
+        <v>4753.48</v>
+      </c>
+      <c r="D1819" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1819" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1819" s="2" t="n">
+        <v>46087.27589143036</v>
+      </c>
+      <c r="I1819" s="2" t="n">
+        <v>46092.27589143036</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>c58335b4-69a7-4ca8-8099-434ee4155d62</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1820" t="n">
+        <v>4773.86</v>
+      </c>
+      <c r="D1820" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1820" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1820" s="2" t="n">
+        <v>46061.27589143366</v>
+      </c>
+      <c r="I1820" s="2" t="n">
+        <v>46066.27589143366</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>7f18fcec-46a1-45ad-be91-e91c90f37edb</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1821" t="n">
+        <v>6137.78</v>
+      </c>
+      <c r="D1821" t="n">
+        <v>94.89</v>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1821" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1821" s="2" t="n">
+        <v>46072.27589143672</v>
+      </c>
+      <c r="I1821" s="2" t="n">
+        <v>46077.27589143672</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>5f336d17-545c-4752-bc61-5f6bc5175d74</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1822" t="n">
+        <v>4130.32</v>
+      </c>
+      <c r="D1822" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1822" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1822" s="2" t="n">
+        <v>46063.27589143992</v>
+      </c>
+      <c r="I1822" s="2" t="n">
+        <v>46068.27589143992</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>1dd699b5-91b4-4bb4-bd0e-3944fbfcc136</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1823" t="n">
+        <v>1108</v>
+      </c>
+      <c r="D1823" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1823" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1823" s="2" t="n">
+        <v>46080.27589144332</v>
+      </c>
+      <c r="I1823" s="2" t="n">
+        <v>46085.27589144332</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>c6db83ed-0aa0-45c7-8454-68e4289ec1e7</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1824" t="n">
+        <v>3822.22</v>
+      </c>
+      <c r="D1824" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1824" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1824" s="2" t="n">
+        <v>46077.27589144638</v>
+      </c>
+      <c r="I1824" s="2" t="n">
+        <v>46082.27589144638</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>eff03056-3aac-4cfe-a6e8-96d378958383</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1825" t="n">
+        <v>3530.25</v>
+      </c>
+      <c r="D1825" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1825" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1825" s="2" t="n">
+        <v>46065.27589144961</v>
+      </c>
+      <c r="I1825" s="2" t="n">
+        <v>46070.27589144961</v>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>7b507908-613e-4377-ba9e-58cfdd226eb9</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1826" t="n">
+        <v>1968.28</v>
+      </c>
+      <c r="D1826" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1826" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1826" s="2" t="n">
+        <v>46066.2758914529</v>
+      </c>
+      <c r="I1826" s="2" t="n">
+        <v>46071.2758914529</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>1d6752ad-0d5d-47bf-9db6-04a2c6ce9aca</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1827" t="n">
+        <v>1709.67</v>
+      </c>
+      <c r="D1827" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1827" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1827" s="2" t="n">
+        <v>46074.275891456</v>
+      </c>
+      <c r="I1827" s="2" t="n">
+        <v>46079.275891456</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>43ffe683-6fa5-452b-9483-d24e2d8debd9</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1828" t="n">
+        <v>4373.11</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1828" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1828" s="2" t="n">
+        <v>46069.27589145905</v>
+      </c>
+      <c r="I1828" s="2" t="n">
+        <v>46074.27589145905</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2bd4c63b-92a8-44fd-9c2f-6729e6dbbb41</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1829" t="n">
+        <v>8249.65</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>90.92</v>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1829" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1829" s="2" t="n">
+        <v>46063.27589146209</v>
+      </c>
+      <c r="I1829" s="2" t="n">
+        <v>46068.27589146209</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>79b76ddc-2005-4ac6-9fc8-b4f90cd03acc</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1830" t="n">
+        <v>7371.53</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1830" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1830" s="2" t="n">
+        <v>46088.27589146548</v>
+      </c>
+      <c r="I1830" s="2" t="n">
+        <v>46093.27589146548</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>7529a0fe-c618-4ed5-92ff-0dc0af763225</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1831" t="n">
+        <v>5202.6</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1831" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1831" s="2" t="n">
+        <v>46066.2758914687</v>
+      </c>
+      <c r="I1831" s="2" t="n">
+        <v>46071.2758914687</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>356a3b0b-b08f-462b-9c33-8224cd74d953</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1832" t="n">
+        <v>4459.74</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>93.81</v>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1832" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1832" s="2" t="n">
+        <v>46064.27589147181</v>
+      </c>
+      <c r="I1832" s="2" t="n">
+        <v>46069.27589147181</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>c944edcb-9998-4cd3-9e83-f05722a1e985</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1833" t="n">
+        <v>6566.9</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>93.37</v>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1833" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1833" s="2" t="n">
+        <v>46083.27589147492</v>
+      </c>
+      <c r="I1833" s="2" t="n">
+        <v>46088.27589147492</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>9c33ba9d-eb9a-4889-9bca-c4ab31d1ca5d</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1834" t="n">
+        <v>5238.74</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1834" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1834" s="2" t="n">
+        <v>46080.27589147815</v>
+      </c>
+      <c r="I1834" s="2" t="n">
+        <v>46085.27589147815</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>71a48183-f332-4d9d-a4d9-257631c5f356</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1835" t="n">
+        <v>4177.19</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1835" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1835" s="2" t="n">
+        <v>46078.27589148129</v>
+      </c>
+      <c r="I1835" s="2" t="n">
+        <v>46083.27589148129</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>7291fc97-1f05-4c43-a91d-084fe0b37ec4</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1836" t="n">
+        <v>4988.89</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1836" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1836" s="2" t="n">
+        <v>46090.27589148443</v>
+      </c>
+      <c r="I1836" s="2" t="n">
+        <v>46095.27589148443</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>239080bb-3b80-4eb5-8368-0abf3f5618c3</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1837" t="n">
+        <v>5728.07</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>85.53</v>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1837" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1837" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1837" s="2" t="n">
+        <v>46075.27589148768</v>
+      </c>
+      <c r="I1837" s="2" t="n">
+        <v>46080.27589148768</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>6aaf2cce-13ab-48ed-9854-a6edba1c05dc</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1838" t="n">
+        <v>1854.67</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1838" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1838" s="2" t="n">
+        <v>46084.27589149073</v>
+      </c>
+      <c r="I1838" s="2" t="n">
+        <v>46089.27589149073</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>b3351198-7b92-4a8c-a751-f5b2c9812b39</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1839" t="n">
+        <v>9139.76</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1839" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1839" s="2" t="n">
+        <v>46080.2758914939</v>
+      </c>
+      <c r="I1839" s="2" t="n">
+        <v>46085.2758914939</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>6b1a44d1-55d4-44bc-9194-a185b2353f31</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1840" t="n">
+        <v>4133.52</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1840" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1840" s="2" t="n">
+        <v>46067.27589149714</v>
+      </c>
+      <c r="I1840" s="2" t="n">
+        <v>46072.27589149714</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>1a86857f-b308-4a75-aa76-57ad3b696117</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1841" t="n">
+        <v>2179.33</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1841" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1841" s="2" t="n">
+        <v>46079.27589150043</v>
+      </c>
+      <c r="I1841" s="2" t="n">
+        <v>46084.27589150043</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>21982c69-fd13-4723-b132-aa072e9bea56</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1842" t="n">
+        <v>7095.66</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1842" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1842" s="2" t="n">
+        <v>46074.27589150383</v>
+      </c>
+      <c r="I1842" s="2" t="n">
+        <v>46079.27589150383</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>cec5b577-10ad-4da2-b223-ff659c100d24</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1843" t="n">
+        <v>8122.43</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1843" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1843" s="2" t="n">
+        <v>46076.27589150686</v>
+      </c>
+      <c r="I1843" s="2" t="n">
+        <v>46081.27589150686</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>ecf78c76-b34e-48e4-8f45-d00b3d463bcf</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1844" t="n">
+        <v>1746</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1844" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1844" s="2" t="n">
+        <v>46070.27589151002</v>
+      </c>
+      <c r="I1844" s="2" t="n">
+        <v>46075.27589151002</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>9439bb2f-cd39-467f-93fe-3fc10b501b76</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1845" t="n">
+        <v>3673.48</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1845" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1845" s="2" t="n">
+        <v>46079.2758915133</v>
+      </c>
+      <c r="I1845" s="2" t="n">
+        <v>46084.2758915133</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>da2dd4dc-f657-41d8-99bf-4692bbe891c2</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1846" t="n">
+        <v>7941.65</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1846" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1846" s="2" t="n">
+        <v>46075.27589151638</v>
+      </c>
+      <c r="I1846" s="2" t="n">
+        <v>46080.27589151638</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>ec142984-bffb-4424-bfc8-841f464be685</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1847" t="n">
+        <v>9295.49</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>99.12</v>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1847" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1847" s="2" t="n">
+        <v>46064.27589151944</v>
+      </c>
+      <c r="I1847" s="2" t="n">
+        <v>46069.27589151944</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>c3392225-b4c7-46f8-ab47-62a1a5b3cd28</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1848" t="n">
+        <v>3743.26</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1848" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1848" s="2" t="n">
+        <v>46085.27589152277</v>
+      </c>
+      <c r="I1848" s="2" t="n">
+        <v>46090.27589152277</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>e928e269-a868-4aed-90ac-825c329ba67b</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1849" t="n">
+        <v>2803.24</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1849" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1849" s="2" t="n">
+        <v>46062.27589152589</v>
+      </c>
+      <c r="I1849" s="2" t="n">
+        <v>46067.27589152589</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2d1bffa1-2c30-48be-9c2c-5cbf931a1454</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1850" t="n">
+        <v>8170.9</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1850" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1850" s="2" t="n">
+        <v>46079.27589152903</v>
+      </c>
+      <c r="I1850" s="2" t="n">
+        <v>46084.27589152903</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>e839981c-6ffd-4a01-9152-89db0f32775a</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1851" t="n">
+        <v>6822.5</v>
+      </c>
+      <c r="D1851" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1851" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1851" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1851" s="2" t="n">
+        <v>46088.27589153206</v>
+      </c>
+      <c r="I1851" s="2" t="n">
+        <v>46093.27589153206</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1851"/>
+  <dimension ref="A1:I1901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70712,10 +70712,10 @@
         </is>
       </c>
       <c r="H1802" s="2" t="n">
-        <v>46080.275891374</v>
+        <v>46080.27589137731</v>
       </c>
       <c r="I1802" s="2" t="n">
-        <v>46085.275891374</v>
+        <v>46085.27589137731</v>
       </c>
     </row>
     <row r="1803">
@@ -70751,10 +70751,10 @@
         </is>
       </c>
       <c r="H1803" s="2" t="n">
-        <v>46065.27589137823</v>
+        <v>46065.27589137731</v>
       </c>
       <c r="I1803" s="2" t="n">
-        <v>46070.27589137823</v>
+        <v>46070.27589137731</v>
       </c>
     </row>
     <row r="1804">
@@ -70790,10 +70790,10 @@
         </is>
       </c>
       <c r="H1804" s="2" t="n">
-        <v>46066.27589138141</v>
+        <v>46066.27589137731</v>
       </c>
       <c r="I1804" s="2" t="n">
-        <v>46071.27589138141</v>
+        <v>46071.27589137731</v>
       </c>
     </row>
     <row r="1805">
@@ -70829,10 +70829,10 @@
         </is>
       </c>
       <c r="H1805" s="2" t="n">
-        <v>46065.27589138494</v>
+        <v>46065.27589138889</v>
       </c>
       <c r="I1805" s="2" t="n">
-        <v>46070.27589138494</v>
+        <v>46070.27589138889</v>
       </c>
     </row>
     <row r="1806">
@@ -70868,10 +70868,10 @@
         </is>
       </c>
       <c r="H1806" s="2" t="n">
-        <v>46063.27589138811</v>
+        <v>46063.27589138889</v>
       </c>
       <c r="I1806" s="2" t="n">
-        <v>46068.27589138811</v>
+        <v>46068.27589138889</v>
       </c>
     </row>
     <row r="1807">
@@ -70907,10 +70907,10 @@
         </is>
       </c>
       <c r="H1807" s="2" t="n">
-        <v>46069.27589139123</v>
+        <v>46069.27589138889</v>
       </c>
       <c r="I1807" s="2" t="n">
-        <v>46074.27589139123</v>
+        <v>46074.27589138889</v>
       </c>
     </row>
     <row r="1808">
@@ -70946,10 +70946,10 @@
         </is>
       </c>
       <c r="H1808" s="2" t="n">
-        <v>46074.27589139454</v>
+        <v>46074.27589138889</v>
       </c>
       <c r="I1808" s="2" t="n">
-        <v>46079.27589139454</v>
+        <v>46079.27589138889</v>
       </c>
     </row>
     <row r="1809">
@@ -70985,10 +70985,10 @@
         </is>
       </c>
       <c r="H1809" s="2" t="n">
-        <v>46079.27589139837</v>
+        <v>46079.27589140047</v>
       </c>
       <c r="I1809" s="2" t="n">
-        <v>46084.27589139837</v>
+        <v>46084.27589140047</v>
       </c>
     </row>
     <row r="1810">
@@ -71024,10 +71024,10 @@
         </is>
       </c>
       <c r="H1810" s="2" t="n">
-        <v>46074.27589140169</v>
+        <v>46074.27589140047</v>
       </c>
       <c r="I1810" s="2" t="n">
-        <v>46079.27589140169</v>
+        <v>46079.27589140047</v>
       </c>
     </row>
     <row r="1811">
@@ -71063,10 +71063,10 @@
         </is>
       </c>
       <c r="H1811" s="2" t="n">
-        <v>46078.27589140482</v>
+        <v>46078.27589140047</v>
       </c>
       <c r="I1811" s="2" t="n">
-        <v>46083.27589140482</v>
+        <v>46083.27589140047</v>
       </c>
     </row>
     <row r="1812">
@@ -71102,10 +71102,10 @@
         </is>
       </c>
       <c r="H1812" s="2" t="n">
-        <v>46075.27589140823</v>
+        <v>46075.27589141203</v>
       </c>
       <c r="I1812" s="2" t="n">
-        <v>46080.27589140823</v>
+        <v>46080.27589141203</v>
       </c>
     </row>
     <row r="1813">
@@ -71141,10 +71141,10 @@
         </is>
       </c>
       <c r="H1813" s="2" t="n">
-        <v>46089.27589141133</v>
+        <v>46089.27589141203</v>
       </c>
       <c r="I1813" s="2" t="n">
-        <v>46094.27589141133</v>
+        <v>46094.27589141203</v>
       </c>
     </row>
     <row r="1814">
@@ -71180,10 +71180,10 @@
         </is>
       </c>
       <c r="H1814" s="2" t="n">
-        <v>46081.27589141442</v>
+        <v>46081.27589141203</v>
       </c>
       <c r="I1814" s="2" t="n">
-        <v>46086.27589141442</v>
+        <v>46086.27589141203</v>
       </c>
     </row>
     <row r="1815">
@@ -71219,10 +71219,10 @@
         </is>
       </c>
       <c r="H1815" s="2" t="n">
-        <v>46090.27589141779</v>
+        <v>46090.27589141203</v>
       </c>
       <c r="I1815" s="2" t="n">
-        <v>46095.27589141779</v>
+        <v>46095.27589141203</v>
       </c>
     </row>
     <row r="1816">
@@ -71258,10 +71258,10 @@
         </is>
       </c>
       <c r="H1816" s="2" t="n">
-        <v>46072.27589142094</v>
+        <v>46072.27589142361</v>
       </c>
       <c r="I1816" s="2" t="n">
-        <v>46077.27589142094</v>
+        <v>46077.27589142361</v>
       </c>
     </row>
     <row r="1817">
@@ -71297,10 +71297,10 @@
         </is>
       </c>
       <c r="H1817" s="2" t="n">
-        <v>46073.27589142398</v>
+        <v>46073.27589142361</v>
       </c>
       <c r="I1817" s="2" t="n">
-        <v>46078.27589142398</v>
+        <v>46078.27589142361</v>
       </c>
     </row>
     <row r="1818">
@@ -71336,10 +71336,10 @@
         </is>
       </c>
       <c r="H1818" s="2" t="n">
-        <v>46083.27589142705</v>
+        <v>46083.27589142361</v>
       </c>
       <c r="I1818" s="2" t="n">
-        <v>46088.27589142705</v>
+        <v>46088.27589142361</v>
       </c>
     </row>
     <row r="1819">
@@ -71375,10 +71375,10 @@
         </is>
       </c>
       <c r="H1819" s="2" t="n">
-        <v>46087.27589143036</v>
+        <v>46087.27589143519</v>
       </c>
       <c r="I1819" s="2" t="n">
-        <v>46092.27589143036</v>
+        <v>46092.27589143519</v>
       </c>
     </row>
     <row r="1820">
@@ -71414,10 +71414,10 @@
         </is>
       </c>
       <c r="H1820" s="2" t="n">
-        <v>46061.27589143366</v>
+        <v>46061.27589143519</v>
       </c>
       <c r="I1820" s="2" t="n">
-        <v>46066.27589143366</v>
+        <v>46066.27589143519</v>
       </c>
     </row>
     <row r="1821">
@@ -71453,10 +71453,10 @@
         </is>
       </c>
       <c r="H1821" s="2" t="n">
-        <v>46072.27589143672</v>
+        <v>46072.27589143519</v>
       </c>
       <c r="I1821" s="2" t="n">
-        <v>46077.27589143672</v>
+        <v>46077.27589143519</v>
       </c>
     </row>
     <row r="1822">
@@ -71492,10 +71492,10 @@
         </is>
       </c>
       <c r="H1822" s="2" t="n">
-        <v>46063.27589143992</v>
+        <v>46063.27589143519</v>
       </c>
       <c r="I1822" s="2" t="n">
-        <v>46068.27589143992</v>
+        <v>46068.27589143519</v>
       </c>
     </row>
     <row r="1823">
@@ -71531,10 +71531,10 @@
         </is>
       </c>
       <c r="H1823" s="2" t="n">
-        <v>46080.27589144332</v>
+        <v>46080.27589144676</v>
       </c>
       <c r="I1823" s="2" t="n">
-        <v>46085.27589144332</v>
+        <v>46085.27589144676</v>
       </c>
     </row>
     <row r="1824">
@@ -71570,10 +71570,10 @@
         </is>
       </c>
       <c r="H1824" s="2" t="n">
-        <v>46077.27589144638</v>
+        <v>46077.27589144676</v>
       </c>
       <c r="I1824" s="2" t="n">
-        <v>46082.27589144638</v>
+        <v>46082.27589144676</v>
       </c>
     </row>
     <row r="1825">
@@ -71609,10 +71609,10 @@
         </is>
       </c>
       <c r="H1825" s="2" t="n">
-        <v>46065.27589144961</v>
+        <v>46065.27589144676</v>
       </c>
       <c r="I1825" s="2" t="n">
-        <v>46070.27589144961</v>
+        <v>46070.27589144676</v>
       </c>
     </row>
     <row r="1826">
@@ -71648,10 +71648,10 @@
         </is>
       </c>
       <c r="H1826" s="2" t="n">
-        <v>46066.2758914529</v>
+        <v>46066.27589145833</v>
       </c>
       <c r="I1826" s="2" t="n">
-        <v>46071.2758914529</v>
+        <v>46071.27589145833</v>
       </c>
     </row>
     <row r="1827">
@@ -71687,10 +71687,10 @@
         </is>
       </c>
       <c r="H1827" s="2" t="n">
-        <v>46074.275891456</v>
+        <v>46074.27589145833</v>
       </c>
       <c r="I1827" s="2" t="n">
-        <v>46079.275891456</v>
+        <v>46079.27589145833</v>
       </c>
     </row>
     <row r="1828">
@@ -71726,10 +71726,10 @@
         </is>
       </c>
       <c r="H1828" s="2" t="n">
-        <v>46069.27589145905</v>
+        <v>46069.27589145833</v>
       </c>
       <c r="I1828" s="2" t="n">
-        <v>46074.27589145905</v>
+        <v>46074.27589145833</v>
       </c>
     </row>
     <row r="1829">
@@ -71765,10 +71765,10 @@
         </is>
       </c>
       <c r="H1829" s="2" t="n">
-        <v>46063.27589146209</v>
+        <v>46063.27589145833</v>
       </c>
       <c r="I1829" s="2" t="n">
-        <v>46068.27589146209</v>
+        <v>46068.27589145833</v>
       </c>
     </row>
     <row r="1830">
@@ -71804,10 +71804,10 @@
         </is>
       </c>
       <c r="H1830" s="2" t="n">
-        <v>46088.27589146548</v>
+        <v>46088.27589146991</v>
       </c>
       <c r="I1830" s="2" t="n">
-        <v>46093.27589146548</v>
+        <v>46093.27589146991</v>
       </c>
     </row>
     <row r="1831">
@@ -71843,10 +71843,10 @@
         </is>
       </c>
       <c r="H1831" s="2" t="n">
-        <v>46066.2758914687</v>
+        <v>46066.27589146991</v>
       </c>
       <c r="I1831" s="2" t="n">
-        <v>46071.2758914687</v>
+        <v>46071.27589146991</v>
       </c>
     </row>
     <row r="1832">
@@ -71882,10 +71882,10 @@
         </is>
       </c>
       <c r="H1832" s="2" t="n">
-        <v>46064.27589147181</v>
+        <v>46064.27589146991</v>
       </c>
       <c r="I1832" s="2" t="n">
-        <v>46069.27589147181</v>
+        <v>46069.27589146991</v>
       </c>
     </row>
     <row r="1833">
@@ -71921,10 +71921,10 @@
         </is>
       </c>
       <c r="H1833" s="2" t="n">
-        <v>46083.27589147492</v>
+        <v>46083.27589146991</v>
       </c>
       <c r="I1833" s="2" t="n">
-        <v>46088.27589147492</v>
+        <v>46088.27589146991</v>
       </c>
     </row>
     <row r="1834">
@@ -71960,10 +71960,10 @@
         </is>
       </c>
       <c r="H1834" s="2" t="n">
-        <v>46080.27589147815</v>
+        <v>46080.27589148148</v>
       </c>
       <c r="I1834" s="2" t="n">
-        <v>46085.27589147815</v>
+        <v>46085.27589148148</v>
       </c>
     </row>
     <row r="1835">
@@ -71999,10 +71999,10 @@
         </is>
       </c>
       <c r="H1835" s="2" t="n">
-        <v>46078.27589148129</v>
+        <v>46078.27589148148</v>
       </c>
       <c r="I1835" s="2" t="n">
-        <v>46083.27589148129</v>
+        <v>46083.27589148148</v>
       </c>
     </row>
     <row r="1836">
@@ -72038,10 +72038,10 @@
         </is>
       </c>
       <c r="H1836" s="2" t="n">
-        <v>46090.27589148443</v>
+        <v>46090.27589148148</v>
       </c>
       <c r="I1836" s="2" t="n">
-        <v>46095.27589148443</v>
+        <v>46095.27589148148</v>
       </c>
     </row>
     <row r="1837">
@@ -72077,10 +72077,10 @@
         </is>
       </c>
       <c r="H1837" s="2" t="n">
-        <v>46075.27589148768</v>
+        <v>46075.27589149305</v>
       </c>
       <c r="I1837" s="2" t="n">
-        <v>46080.27589148768</v>
+        <v>46080.27589149305</v>
       </c>
     </row>
     <row r="1838">
@@ -72116,10 +72116,10 @@
         </is>
       </c>
       <c r="H1838" s="2" t="n">
-        <v>46084.27589149073</v>
+        <v>46084.27589149305</v>
       </c>
       <c r="I1838" s="2" t="n">
-        <v>46089.27589149073</v>
+        <v>46089.27589149305</v>
       </c>
     </row>
     <row r="1839">
@@ -72155,10 +72155,10 @@
         </is>
       </c>
       <c r="H1839" s="2" t="n">
-        <v>46080.2758914939</v>
+        <v>46080.27589149305</v>
       </c>
       <c r="I1839" s="2" t="n">
-        <v>46085.2758914939</v>
+        <v>46085.27589149305</v>
       </c>
     </row>
     <row r="1840">
@@ -72194,10 +72194,10 @@
         </is>
       </c>
       <c r="H1840" s="2" t="n">
-        <v>46067.27589149714</v>
+        <v>46067.27589149305</v>
       </c>
       <c r="I1840" s="2" t="n">
-        <v>46072.27589149714</v>
+        <v>46072.27589149305</v>
       </c>
     </row>
     <row r="1841">
@@ -72233,10 +72233,10 @@
         </is>
       </c>
       <c r="H1841" s="2" t="n">
-        <v>46079.27589150043</v>
+        <v>46079.27589150463</v>
       </c>
       <c r="I1841" s="2" t="n">
-        <v>46084.27589150043</v>
+        <v>46084.27589150463</v>
       </c>
     </row>
     <row r="1842">
@@ -72272,10 +72272,10 @@
         </is>
       </c>
       <c r="H1842" s="2" t="n">
-        <v>46074.27589150383</v>
+        <v>46074.27589150463</v>
       </c>
       <c r="I1842" s="2" t="n">
-        <v>46079.27589150383</v>
+        <v>46079.27589150463</v>
       </c>
     </row>
     <row r="1843">
@@ -72311,10 +72311,10 @@
         </is>
       </c>
       <c r="H1843" s="2" t="n">
-        <v>46076.27589150686</v>
+        <v>46076.27589150463</v>
       </c>
       <c r="I1843" s="2" t="n">
-        <v>46081.27589150686</v>
+        <v>46081.27589150463</v>
       </c>
     </row>
     <row r="1844">
@@ -72350,10 +72350,10 @@
         </is>
       </c>
       <c r="H1844" s="2" t="n">
-        <v>46070.27589151002</v>
+        <v>46070.27589150463</v>
       </c>
       <c r="I1844" s="2" t="n">
-        <v>46075.27589151002</v>
+        <v>46075.27589150463</v>
       </c>
     </row>
     <row r="1845">
@@ -72389,10 +72389,10 @@
         </is>
       </c>
       <c r="H1845" s="2" t="n">
-        <v>46079.2758915133</v>
+        <v>46079.2758915162</v>
       </c>
       <c r="I1845" s="2" t="n">
-        <v>46084.2758915133</v>
+        <v>46084.2758915162</v>
       </c>
     </row>
     <row r="1846">
@@ -72428,10 +72428,10 @@
         </is>
       </c>
       <c r="H1846" s="2" t="n">
-        <v>46075.27589151638</v>
+        <v>46075.2758915162</v>
       </c>
       <c r="I1846" s="2" t="n">
-        <v>46080.27589151638</v>
+        <v>46080.2758915162</v>
       </c>
     </row>
     <row r="1847">
@@ -72467,10 +72467,10 @@
         </is>
       </c>
       <c r="H1847" s="2" t="n">
-        <v>46064.27589151944</v>
+        <v>46064.2758915162</v>
       </c>
       <c r="I1847" s="2" t="n">
-        <v>46069.27589151944</v>
+        <v>46069.2758915162</v>
       </c>
     </row>
     <row r="1848">
@@ -72506,10 +72506,10 @@
         </is>
       </c>
       <c r="H1848" s="2" t="n">
-        <v>46085.27589152277</v>
+        <v>46085.27589152778</v>
       </c>
       <c r="I1848" s="2" t="n">
-        <v>46090.27589152277</v>
+        <v>46090.27589152778</v>
       </c>
     </row>
     <row r="1849">
@@ -72545,10 +72545,10 @@
         </is>
       </c>
       <c r="H1849" s="2" t="n">
-        <v>46062.27589152589</v>
+        <v>46062.27589152778</v>
       </c>
       <c r="I1849" s="2" t="n">
-        <v>46067.27589152589</v>
+        <v>46067.27589152778</v>
       </c>
     </row>
     <row r="1850">
@@ -72584,10 +72584,10 @@
         </is>
       </c>
       <c r="H1850" s="2" t="n">
-        <v>46079.27589152903</v>
+        <v>46079.27589152778</v>
       </c>
       <c r="I1850" s="2" t="n">
-        <v>46084.27589152903</v>
+        <v>46084.27589152778</v>
       </c>
     </row>
     <row r="1851">
@@ -72623,10 +72623,1960 @@
         </is>
       </c>
       <c r="H1851" s="2" t="n">
-        <v>46088.27589153206</v>
+        <v>46088.27589152778</v>
       </c>
       <c r="I1851" s="2" t="n">
-        <v>46093.27589153206</v>
+        <v>46093.27589152778</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>43b64f9f-f5c9-489d-bb5b-cbf80262e775</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1852" t="n">
+        <v>8365.4</v>
+      </c>
+      <c r="D1852" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1852" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1852" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1852" s="2" t="n">
+        <v>46086.31430924147</v>
+      </c>
+      <c r="I1852" s="2" t="n">
+        <v>46091.31430924147</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>e9f86acf-c571-48e4-9a94-5de571c52b7d</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1853" t="n">
+        <v>5048.07</v>
+      </c>
+      <c r="D1853" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1853" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1853" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1853" s="2" t="n">
+        <v>46063.31430924567</v>
+      </c>
+      <c r="I1853" s="2" t="n">
+        <v>46068.31430924567</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>aa84d5be-7207-428d-b3fb-f7508d8f7987</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1854" t="n">
+        <v>6465.21</v>
+      </c>
+      <c r="D1854" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1854" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1854" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1854" s="2" t="n">
+        <v>46064.31430924918</v>
+      </c>
+      <c r="I1854" s="2" t="n">
+        <v>46069.31430924918</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>0c73f1e6-6b2f-4d6f-9590-3e1f5ef81877</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1855" t="n">
+        <v>7536.11</v>
+      </c>
+      <c r="D1855" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1855" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1855" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1855" s="2" t="n">
+        <v>46066.31430925251</v>
+      </c>
+      <c r="I1855" s="2" t="n">
+        <v>46071.31430925251</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>9b764c7e-7326-4510-bf60-500fe4e3b219</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1856" t="n">
+        <v>5044.03</v>
+      </c>
+      <c r="D1856" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1856" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1856" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1856" s="2" t="n">
+        <v>46075.31430925579</v>
+      </c>
+      <c r="I1856" s="2" t="n">
+        <v>46080.31430925579</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>cd308a27-e094-4370-8bed-1c443c24eebc</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1857" t="n">
+        <v>2679.72</v>
+      </c>
+      <c r="D1857" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1857" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1857" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1857" s="2" t="n">
+        <v>46074.31430925896</v>
+      </c>
+      <c r="I1857" s="2" t="n">
+        <v>46079.31430925896</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>b983d059-f99e-4e44-9b77-e1824eeb99ef</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1858" t="n">
+        <v>5191.2</v>
+      </c>
+      <c r="D1858" t="n">
+        <v>94.17</v>
+      </c>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1858" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1858" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1858" s="2" t="n">
+        <v>46086.31430926249</v>
+      </c>
+      <c r="I1858" s="2" t="n">
+        <v>46091.31430926249</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>3b3038db-30e1-4c62-b331-4b1db6ddc522</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1859" t="n">
+        <v>9888.76</v>
+      </c>
+      <c r="D1859" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1859" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1859" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1859" s="2" t="n">
+        <v>46072.31430926573</v>
+      </c>
+      <c r="I1859" s="2" t="n">
+        <v>46077.31430926573</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>fa6c8de1-0be6-4b97-97bb-63a2ae26eecb</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1860" t="n">
+        <v>1695.54</v>
+      </c>
+      <c r="D1860" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1860" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1860" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1860" s="2" t="n">
+        <v>46078.31430926901</v>
+      </c>
+      <c r="I1860" s="2" t="n">
+        <v>46083.31430926901</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>26439b6e-e4f2-46ce-875b-58754711f0dc</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1861" t="n">
+        <v>2326.99</v>
+      </c>
+      <c r="D1861" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="E1861" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1861" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1861" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1861" s="2" t="n">
+        <v>46076.31430927227</v>
+      </c>
+      <c r="I1861" s="2" t="n">
+        <v>46081.31430927227</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>3e5fb4c3-00d7-4683-b2fa-857b14c04e28</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1862" t="n">
+        <v>8875.67</v>
+      </c>
+      <c r="D1862" t="n">
+        <v>89.48</v>
+      </c>
+      <c r="E1862" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1862" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1862" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1862" s="2" t="n">
+        <v>46068.31430927559</v>
+      </c>
+      <c r="I1862" s="2" t="n">
+        <v>46073.31430927559</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>9a50a567-91d5-4ed1-b8d9-5c7bd4a13547</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1863" t="n">
+        <v>6381.51</v>
+      </c>
+      <c r="D1863" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="E1863" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1863" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1863" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1863" s="2" t="n">
+        <v>46089.31430927875</v>
+      </c>
+      <c r="I1863" s="2" t="n">
+        <v>46094.31430927875</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>09d010bd-2d49-46a0-b8e7-be71b05928e8</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1864" t="n">
+        <v>2056.73</v>
+      </c>
+      <c r="D1864" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1864" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1864" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1864" s="2" t="n">
+        <v>46070.31430928207</v>
+      </c>
+      <c r="I1864" s="2" t="n">
+        <v>46075.31430928207</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>f3b95691-fecc-446f-8c91-ea92d7cac5c2</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1865" t="n">
+        <v>7244.88</v>
+      </c>
+      <c r="D1865" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1865" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1865" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1865" s="2" t="n">
+        <v>46072.31430928535</v>
+      </c>
+      <c r="I1865" s="2" t="n">
+        <v>46077.31430928535</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>7c918f57-9203-406e-b7ba-ee20a5b8d84d</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1866" t="n">
+        <v>2904.58</v>
+      </c>
+      <c r="D1866" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1866" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1866" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1866" s="2" t="n">
+        <v>46082.31430928847</v>
+      </c>
+      <c r="I1866" s="2" t="n">
+        <v>46087.31430928847</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>74c79a26-6731-4fca-a084-8c7c9c1701a5</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1867" t="n">
+        <v>8459.74</v>
+      </c>
+      <c r="D1867" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="E1867" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1867" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1867" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1867" s="2" t="n">
+        <v>46086.31430929169</v>
+      </c>
+      <c r="I1867" s="2" t="n">
+        <v>46091.31430929169</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>fd6bf766-6321-4f31-917e-b3d2c343054b</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1868" t="n">
+        <v>8813.719999999999</v>
+      </c>
+      <c r="D1868" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1868" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1868" s="2" t="n">
+        <v>46083.31430929509</v>
+      </c>
+      <c r="I1868" s="2" t="n">
+        <v>46088.31430929509</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>5932932e-ef1e-4b81-9b4b-5289219a1071</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1869" t="n">
+        <v>4575.84</v>
+      </c>
+      <c r="D1869" t="n">
+        <v>91</v>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1869" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1869" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1869" s="2" t="n">
+        <v>46081.31430929821</v>
+      </c>
+      <c r="I1869" s="2" t="n">
+        <v>46086.31430929821</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>756643db-664f-4470-a33d-bea53aae3173</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1870" t="n">
+        <v>7306.16</v>
+      </c>
+      <c r="D1870" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1870" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1870" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1870" s="2" t="n">
+        <v>46087.3143093013</v>
+      </c>
+      <c r="I1870" s="2" t="n">
+        <v>46092.3143093013</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>95dc1b07-7f01-450f-9f0c-99921409053d</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1871" t="n">
+        <v>3535.49</v>
+      </c>
+      <c r="D1871" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1871" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1871" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1871" s="2" t="n">
+        <v>46063.31430930436</v>
+      </c>
+      <c r="I1871" s="2" t="n">
+        <v>46068.31430930436</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>f6252cc0-7331-4e30-9955-0ddc9bdc33be</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1872" t="n">
+        <v>3351.57</v>
+      </c>
+      <c r="D1872" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1872" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1872" s="2" t="n">
+        <v>46073.31430930771</v>
+      </c>
+      <c r="I1872" s="2" t="n">
+        <v>46078.31430930771</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>5ffa703c-e429-4c82-9c3c-2b418eac78d5</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1873" t="n">
+        <v>3974.61</v>
+      </c>
+      <c r="D1873" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1873" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1873" s="2" t="n">
+        <v>46068.31430931124</v>
+      </c>
+      <c r="I1873" s="2" t="n">
+        <v>46073.31430931124</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>0a3adaf2-1cb7-4baf-9683-26086f06f87a</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1874" t="n">
+        <v>2697.01</v>
+      </c>
+      <c r="D1874" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1874" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1874" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1874" s="2" t="n">
+        <v>46070.31430931453</v>
+      </c>
+      <c r="I1874" s="2" t="n">
+        <v>46075.31430931453</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>b176f2f9-d443-4b5e-92bf-def333af20bd</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1875" t="n">
+        <v>1509.6</v>
+      </c>
+      <c r="D1875" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1875" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1875" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1875" s="2" t="n">
+        <v>46075.31430931774</v>
+      </c>
+      <c r="I1875" s="2" t="n">
+        <v>46080.31430931774</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>e125722d-bdbc-4a8d-bd32-a5f8f99b3d39</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1876" t="n">
+        <v>8066.25</v>
+      </c>
+      <c r="D1876" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1876" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1876" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1876" s="2" t="n">
+        <v>46069.31430932119</v>
+      </c>
+      <c r="I1876" s="2" t="n">
+        <v>46074.31430932119</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>bca107da-44b5-400a-b221-c7ef40300feb</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1877" t="n">
+        <v>7071.64</v>
+      </c>
+      <c r="D1877" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1877" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1877" s="2" t="n">
+        <v>46085.31430932444</v>
+      </c>
+      <c r="I1877" s="2" t="n">
+        <v>46090.31430932444</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>a197b98f-a68d-4efb-a4e7-4227bb78b6fd</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1878" t="n">
+        <v>9796.58</v>
+      </c>
+      <c r="D1878" t="n">
+        <v>95.09</v>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1878" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1878" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1878" s="2" t="n">
+        <v>46080.31430932754</v>
+      </c>
+      <c r="I1878" s="2" t="n">
+        <v>46085.31430932754</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>dce50cc6-d29d-4188-a3ce-983e09f7636c</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1879" t="n">
+        <v>3692.4</v>
+      </c>
+      <c r="D1879" t="n">
+        <v>88.28</v>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1879" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1879" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1879" s="2" t="n">
+        <v>46067.31430933083</v>
+      </c>
+      <c r="I1879" s="2" t="n">
+        <v>46072.31430933083</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>c79c2fd7-1198-45d3-8ed9-a1b14d9750db</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1880" t="n">
+        <v>2364.92</v>
+      </c>
+      <c r="D1880" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1880" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1880" s="2" t="n">
+        <v>46083.31430933387</v>
+      </c>
+      <c r="I1880" s="2" t="n">
+        <v>46088.31430933387</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>48ddbc7e-0e46-426f-80f2-baf4958622c1</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1881" t="n">
+        <v>5164.81</v>
+      </c>
+      <c r="D1881" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1881" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1881" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1881" s="2" t="n">
+        <v>46080.31430933707</v>
+      </c>
+      <c r="I1881" s="2" t="n">
+        <v>46085.31430933707</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>333699c3-a5da-4b49-b799-44896039da54</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1882" t="n">
+        <v>1222.68</v>
+      </c>
+      <c r="D1882" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1882" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1882" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1882" s="2" t="n">
+        <v>46085.31430934039</v>
+      </c>
+      <c r="I1882" s="2" t="n">
+        <v>46090.31430934039</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>e92811c2-b197-43cf-ae14-6669da8505b4</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1883" t="n">
+        <v>8446.299999999999</v>
+      </c>
+      <c r="D1883" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1883" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1883" s="2" t="n">
+        <v>46070.31430934368</v>
+      </c>
+      <c r="I1883" s="2" t="n">
+        <v>46075.31430934368</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>809e2c02-375b-48c7-a936-5546992c5cac</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1884" t="n">
+        <v>2723.39</v>
+      </c>
+      <c r="D1884" t="n">
+        <v>87.05</v>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1884" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1884" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1884" s="2" t="n">
+        <v>46069.31430934693</v>
+      </c>
+      <c r="I1884" s="2" t="n">
+        <v>46074.31430934693</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>b639f2d9-717e-469f-bfd9-c09163492753</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1885" t="n">
+        <v>9196.360000000001</v>
+      </c>
+      <c r="D1885" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1885" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1885" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1885" s="2" t="n">
+        <v>46065.31430935</v>
+      </c>
+      <c r="I1885" s="2" t="n">
+        <v>46070.31430935</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>437dde84-2a87-48e1-b135-a4faca60d0cb</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1886" t="n">
+        <v>5148.04</v>
+      </c>
+      <c r="D1886" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1886" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1886" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1886" s="2" t="n">
+        <v>46065.31430935318</v>
+      </c>
+      <c r="I1886" s="2" t="n">
+        <v>46070.31430935318</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>feaafd77-9dc3-4fd6-b588-fa3836d8f985</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1887" t="n">
+        <v>9227.290000000001</v>
+      </c>
+      <c r="D1887" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1887" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1887" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1887" s="2" t="n">
+        <v>46090.31430935644</v>
+      </c>
+      <c r="I1887" s="2" t="n">
+        <v>46095.31430935644</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>5dca3b0f-add6-4da1-9107-636410c0b346</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1888" t="n">
+        <v>2003.78</v>
+      </c>
+      <c r="D1888" t="n">
+        <v>95.39</v>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1888" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1888" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1888" s="2" t="n">
+        <v>46066.31430935964</v>
+      </c>
+      <c r="I1888" s="2" t="n">
+        <v>46071.31430935964</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>f5316215-15aa-4efa-81ac-773dcf4b432a</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1889" t="n">
+        <v>2827.56</v>
+      </c>
+      <c r="D1889" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1889" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1889" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1889" s="2" t="n">
+        <v>46080.31430936286</v>
+      </c>
+      <c r="I1889" s="2" t="n">
+        <v>46085.31430936286</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>6f1ed5cb-330a-41b8-a25a-3d350154da7b</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1890" t="n">
+        <v>8680.030000000001</v>
+      </c>
+      <c r="D1890" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1890" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1890" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1890" s="2" t="n">
+        <v>46063.3143093661</v>
+      </c>
+      <c r="I1890" s="2" t="n">
+        <v>46068.3143093661</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>1f87cd5a-9d9e-4f19-a16b-49c8ca56faca</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1891" t="n">
+        <v>7451.38</v>
+      </c>
+      <c r="D1891" t="n">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1891" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1891" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1891" s="2" t="n">
+        <v>46073.31430936919</v>
+      </c>
+      <c r="I1891" s="2" t="n">
+        <v>46078.31430936919</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>5956ca8e-84c4-45da-8106-da48ed12f4d7</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1892" t="n">
+        <v>6518.24</v>
+      </c>
+      <c r="D1892" t="n">
+        <v>97.09</v>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1892" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1892" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1892" s="2" t="n">
+        <v>46087.31430937217</v>
+      </c>
+      <c r="I1892" s="2" t="n">
+        <v>46092.31430937217</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>3fdd2900-5e75-4f54-889f-12b01b20554c</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1893" t="n">
+        <v>2442.77</v>
+      </c>
+      <c r="D1893" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="E1893" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1893" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1893" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1893" s="2" t="n">
+        <v>46064.31430937523</v>
+      </c>
+      <c r="I1893" s="2" t="n">
+        <v>46069.31430937523</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>a7eae0fd-f5f9-481d-9934-3b8eed490fcb</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1894" t="n">
+        <v>2223.56</v>
+      </c>
+      <c r="D1894" t="n">
+        <v>92.33</v>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1894" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1894" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1894" s="2" t="n">
+        <v>46083.31430937852</v>
+      </c>
+      <c r="I1894" s="2" t="n">
+        <v>46088.31430937852</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>83f1637e-02e2-46fe-ae19-73cfd90ac1c8</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1895" t="n">
+        <v>2188.85</v>
+      </c>
+      <c r="D1895" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="E1895" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1895" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1895" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1895" s="2" t="n">
+        <v>46090.3143093817</v>
+      </c>
+      <c r="I1895" s="2" t="n">
+        <v>46095.3143093817</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>8142865f-248c-47ce-81a0-fce6cc17bafc</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1896" t="n">
+        <v>6217.76</v>
+      </c>
+      <c r="D1896" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1896" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1896" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1896" s="2" t="n">
+        <v>46062.31430938493</v>
+      </c>
+      <c r="I1896" s="2" t="n">
+        <v>46067.31430938493</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>4f9639c8-42b2-4f56-af7e-10e6bcc81300</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1897" t="n">
+        <v>6783.51</v>
+      </c>
+      <c r="D1897" t="n">
+        <v>99.11</v>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1897" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1897" s="2" t="n">
+        <v>46063.31430938818</v>
+      </c>
+      <c r="I1897" s="2" t="n">
+        <v>46068.31430938818</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>0ade1855-d0eb-49ec-8326-4c13b86baff1</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1898" t="n">
+        <v>2306.93</v>
+      </c>
+      <c r="D1898" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1898" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1898" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1898" s="2" t="n">
+        <v>46063.3143093914</v>
+      </c>
+      <c r="I1898" s="2" t="n">
+        <v>46068.3143093914</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>72659455-a52c-48c8-a612-9792a3679b00</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1899" t="n">
+        <v>4626.12</v>
+      </c>
+      <c r="D1899" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="E1899" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1899" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1899" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1899" s="2" t="n">
+        <v>46083.31430939458</v>
+      </c>
+      <c r="I1899" s="2" t="n">
+        <v>46088.31430939458</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>77e5ea7c-4a29-4cd6-8d5b-202de0bdd09c</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1900" t="n">
+        <v>3703.26</v>
+      </c>
+      <c r="D1900" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1900" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1900" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1900" s="2" t="n">
+        <v>46090.31430939762</v>
+      </c>
+      <c r="I1900" s="2" t="n">
+        <v>46095.31430939762</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>790b9a5d-f145-4d81-85d8-a60f7acb03b2</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1901" t="n">
+        <v>8828.23</v>
+      </c>
+      <c r="D1901" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1901" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1901" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1901" s="2" t="n">
+        <v>46090.31430940087</v>
+      </c>
+      <c r="I1901" s="2" t="n">
+        <v>46095.31430940087</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1901"/>
+  <dimension ref="A1:I1951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72662,10 +72662,10 @@
         </is>
       </c>
       <c r="H1852" s="2" t="n">
-        <v>46086.31430924147</v>
+        <v>46086.31430923611</v>
       </c>
       <c r="I1852" s="2" t="n">
-        <v>46091.31430924147</v>
+        <v>46091.31430923611</v>
       </c>
     </row>
     <row r="1853">
@@ -72701,10 +72701,10 @@
         </is>
       </c>
       <c r="H1853" s="2" t="n">
-        <v>46063.31430924567</v>
+        <v>46063.31430924768</v>
       </c>
       <c r="I1853" s="2" t="n">
-        <v>46068.31430924567</v>
+        <v>46068.31430924768</v>
       </c>
     </row>
     <row r="1854">
@@ -72740,10 +72740,10 @@
         </is>
       </c>
       <c r="H1854" s="2" t="n">
-        <v>46064.31430924918</v>
+        <v>46064.31430924768</v>
       </c>
       <c r="I1854" s="2" t="n">
-        <v>46069.31430924918</v>
+        <v>46069.31430924768</v>
       </c>
     </row>
     <row r="1855">
@@ -72779,10 +72779,10 @@
         </is>
       </c>
       <c r="H1855" s="2" t="n">
-        <v>46066.31430925251</v>
+        <v>46066.31430924768</v>
       </c>
       <c r="I1855" s="2" t="n">
-        <v>46071.31430925251</v>
+        <v>46071.31430924768</v>
       </c>
     </row>
     <row r="1856">
@@ -72818,10 +72818,10 @@
         </is>
       </c>
       <c r="H1856" s="2" t="n">
-        <v>46075.31430925579</v>
+        <v>46075.31430925926</v>
       </c>
       <c r="I1856" s="2" t="n">
-        <v>46080.31430925579</v>
+        <v>46080.31430925926</v>
       </c>
     </row>
     <row r="1857">
@@ -72857,10 +72857,10 @@
         </is>
       </c>
       <c r="H1857" s="2" t="n">
-        <v>46074.31430925896</v>
+        <v>46074.31430925926</v>
       </c>
       <c r="I1857" s="2" t="n">
-        <v>46079.31430925896</v>
+        <v>46079.31430925926</v>
       </c>
     </row>
     <row r="1858">
@@ -72896,10 +72896,10 @@
         </is>
       </c>
       <c r="H1858" s="2" t="n">
-        <v>46086.31430926249</v>
+        <v>46086.31430925926</v>
       </c>
       <c r="I1858" s="2" t="n">
-        <v>46091.31430926249</v>
+        <v>46091.31430925926</v>
       </c>
     </row>
     <row r="1859">
@@ -72935,10 +72935,10 @@
         </is>
       </c>
       <c r="H1859" s="2" t="n">
-        <v>46072.31430926573</v>
+        <v>46072.31430927083</v>
       </c>
       <c r="I1859" s="2" t="n">
-        <v>46077.31430926573</v>
+        <v>46077.31430927083</v>
       </c>
     </row>
     <row r="1860">
@@ -72974,10 +72974,10 @@
         </is>
       </c>
       <c r="H1860" s="2" t="n">
-        <v>46078.31430926901</v>
+        <v>46078.31430927083</v>
       </c>
       <c r="I1860" s="2" t="n">
-        <v>46083.31430926901</v>
+        <v>46083.31430927083</v>
       </c>
     </row>
     <row r="1861">
@@ -73013,10 +73013,10 @@
         </is>
       </c>
       <c r="H1861" s="2" t="n">
-        <v>46076.31430927227</v>
+        <v>46076.31430927083</v>
       </c>
       <c r="I1861" s="2" t="n">
-        <v>46081.31430927227</v>
+        <v>46081.31430927083</v>
       </c>
     </row>
     <row r="1862">
@@ -73052,10 +73052,10 @@
         </is>
       </c>
       <c r="H1862" s="2" t="n">
-        <v>46068.31430927559</v>
+        <v>46068.31430927083</v>
       </c>
       <c r="I1862" s="2" t="n">
-        <v>46073.31430927559</v>
+        <v>46073.31430927083</v>
       </c>
     </row>
     <row r="1863">
@@ -73091,10 +73091,10 @@
         </is>
       </c>
       <c r="H1863" s="2" t="n">
-        <v>46089.31430927875</v>
+        <v>46089.31430928241</v>
       </c>
       <c r="I1863" s="2" t="n">
-        <v>46094.31430927875</v>
+        <v>46094.31430928241</v>
       </c>
     </row>
     <row r="1864">
@@ -73130,10 +73130,10 @@
         </is>
       </c>
       <c r="H1864" s="2" t="n">
-        <v>46070.31430928207</v>
+        <v>46070.31430928241</v>
       </c>
       <c r="I1864" s="2" t="n">
-        <v>46075.31430928207</v>
+        <v>46075.31430928241</v>
       </c>
     </row>
     <row r="1865">
@@ -73169,10 +73169,10 @@
         </is>
       </c>
       <c r="H1865" s="2" t="n">
-        <v>46072.31430928535</v>
+        <v>46072.31430928241</v>
       </c>
       <c r="I1865" s="2" t="n">
-        <v>46077.31430928535</v>
+        <v>46077.31430928241</v>
       </c>
     </row>
     <row r="1866">
@@ -73208,10 +73208,10 @@
         </is>
       </c>
       <c r="H1866" s="2" t="n">
-        <v>46082.31430928847</v>
+        <v>46082.31430929398</v>
       </c>
       <c r="I1866" s="2" t="n">
-        <v>46087.31430928847</v>
+        <v>46087.31430929398</v>
       </c>
     </row>
     <row r="1867">
@@ -73247,10 +73247,10 @@
         </is>
       </c>
       <c r="H1867" s="2" t="n">
-        <v>46086.31430929169</v>
+        <v>46086.31430929398</v>
       </c>
       <c r="I1867" s="2" t="n">
-        <v>46091.31430929169</v>
+        <v>46091.31430929398</v>
       </c>
     </row>
     <row r="1868">
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="H1868" s="2" t="n">
-        <v>46083.31430929509</v>
+        <v>46083.31430929398</v>
       </c>
       <c r="I1868" s="2" t="n">
-        <v>46088.31430929509</v>
+        <v>46088.31430929398</v>
       </c>
     </row>
     <row r="1869">
@@ -73325,10 +73325,10 @@
         </is>
       </c>
       <c r="H1869" s="2" t="n">
-        <v>46081.31430929821</v>
+        <v>46081.31430929398</v>
       </c>
       <c r="I1869" s="2" t="n">
-        <v>46086.31430929821</v>
+        <v>46086.31430929398</v>
       </c>
     </row>
     <row r="1870">
@@ -73364,10 +73364,10 @@
         </is>
       </c>
       <c r="H1870" s="2" t="n">
-        <v>46087.3143093013</v>
+        <v>46087.31430930556</v>
       </c>
       <c r="I1870" s="2" t="n">
-        <v>46092.3143093013</v>
+        <v>46092.31430930556</v>
       </c>
     </row>
     <row r="1871">
@@ -73403,10 +73403,10 @@
         </is>
       </c>
       <c r="H1871" s="2" t="n">
-        <v>46063.31430930436</v>
+        <v>46063.31430930556</v>
       </c>
       <c r="I1871" s="2" t="n">
-        <v>46068.31430930436</v>
+        <v>46068.31430930556</v>
       </c>
     </row>
     <row r="1872">
@@ -73442,10 +73442,10 @@
         </is>
       </c>
       <c r="H1872" s="2" t="n">
-        <v>46073.31430930771</v>
+        <v>46073.31430930556</v>
       </c>
       <c r="I1872" s="2" t="n">
-        <v>46078.31430930771</v>
+        <v>46078.31430930556</v>
       </c>
     </row>
     <row r="1873">
@@ -73481,10 +73481,10 @@
         </is>
       </c>
       <c r="H1873" s="2" t="n">
-        <v>46068.31430931124</v>
+        <v>46068.31430930556</v>
       </c>
       <c r="I1873" s="2" t="n">
-        <v>46073.31430931124</v>
+        <v>46073.31430930556</v>
       </c>
     </row>
     <row r="1874">
@@ -73520,10 +73520,10 @@
         </is>
       </c>
       <c r="H1874" s="2" t="n">
-        <v>46070.31430931453</v>
+        <v>46070.31430931713</v>
       </c>
       <c r="I1874" s="2" t="n">
-        <v>46075.31430931453</v>
+        <v>46075.31430931713</v>
       </c>
     </row>
     <row r="1875">
@@ -73559,10 +73559,10 @@
         </is>
       </c>
       <c r="H1875" s="2" t="n">
-        <v>46075.31430931774</v>
+        <v>46075.31430931713</v>
       </c>
       <c r="I1875" s="2" t="n">
-        <v>46080.31430931774</v>
+        <v>46080.31430931713</v>
       </c>
     </row>
     <row r="1876">
@@ -73598,10 +73598,10 @@
         </is>
       </c>
       <c r="H1876" s="2" t="n">
-        <v>46069.31430932119</v>
+        <v>46069.31430931713</v>
       </c>
       <c r="I1876" s="2" t="n">
-        <v>46074.31430932119</v>
+        <v>46074.31430931713</v>
       </c>
     </row>
     <row r="1877">
@@ -73637,10 +73637,10 @@
         </is>
       </c>
       <c r="H1877" s="2" t="n">
-        <v>46085.31430932444</v>
+        <v>46085.31430932871</v>
       </c>
       <c r="I1877" s="2" t="n">
-        <v>46090.31430932444</v>
+        <v>46090.31430932871</v>
       </c>
     </row>
     <row r="1878">
@@ -73676,10 +73676,10 @@
         </is>
       </c>
       <c r="H1878" s="2" t="n">
-        <v>46080.31430932754</v>
+        <v>46080.31430932871</v>
       </c>
       <c r="I1878" s="2" t="n">
-        <v>46085.31430932754</v>
+        <v>46085.31430932871</v>
       </c>
     </row>
     <row r="1879">
@@ -73715,10 +73715,10 @@
         </is>
       </c>
       <c r="H1879" s="2" t="n">
-        <v>46067.31430933083</v>
+        <v>46067.31430932871</v>
       </c>
       <c r="I1879" s="2" t="n">
-        <v>46072.31430933083</v>
+        <v>46072.31430932871</v>
       </c>
     </row>
     <row r="1880">
@@ -73754,10 +73754,10 @@
         </is>
       </c>
       <c r="H1880" s="2" t="n">
-        <v>46083.31430933387</v>
+        <v>46083.31430932871</v>
       </c>
       <c r="I1880" s="2" t="n">
-        <v>46088.31430933387</v>
+        <v>46088.31430932871</v>
       </c>
     </row>
     <row r="1881">
@@ -73793,10 +73793,10 @@
         </is>
       </c>
       <c r="H1881" s="2" t="n">
-        <v>46080.31430933707</v>
+        <v>46080.31430934028</v>
       </c>
       <c r="I1881" s="2" t="n">
-        <v>46085.31430933707</v>
+        <v>46085.31430934028</v>
       </c>
     </row>
     <row r="1882">
@@ -73832,10 +73832,10 @@
         </is>
       </c>
       <c r="H1882" s="2" t="n">
-        <v>46085.31430934039</v>
+        <v>46085.31430934028</v>
       </c>
       <c r="I1882" s="2" t="n">
-        <v>46090.31430934039</v>
+        <v>46090.31430934028</v>
       </c>
     </row>
     <row r="1883">
@@ -73871,10 +73871,10 @@
         </is>
       </c>
       <c r="H1883" s="2" t="n">
-        <v>46070.31430934368</v>
+        <v>46070.31430934028</v>
       </c>
       <c r="I1883" s="2" t="n">
-        <v>46075.31430934368</v>
+        <v>46075.31430934028</v>
       </c>
     </row>
     <row r="1884">
@@ -73910,10 +73910,10 @@
         </is>
       </c>
       <c r="H1884" s="2" t="n">
-        <v>46069.31430934693</v>
+        <v>46069.31430935185</v>
       </c>
       <c r="I1884" s="2" t="n">
-        <v>46074.31430934693</v>
+        <v>46074.31430935185</v>
       </c>
     </row>
     <row r="1885">
@@ -73949,10 +73949,10 @@
         </is>
       </c>
       <c r="H1885" s="2" t="n">
-        <v>46065.31430935</v>
+        <v>46065.31430935185</v>
       </c>
       <c r="I1885" s="2" t="n">
-        <v>46070.31430935</v>
+        <v>46070.31430935185</v>
       </c>
     </row>
     <row r="1886">
@@ -73988,10 +73988,10 @@
         </is>
       </c>
       <c r="H1886" s="2" t="n">
-        <v>46065.31430935318</v>
+        <v>46065.31430935185</v>
       </c>
       <c r="I1886" s="2" t="n">
-        <v>46070.31430935318</v>
+        <v>46070.31430935185</v>
       </c>
     </row>
     <row r="1887">
@@ -74027,10 +74027,10 @@
         </is>
       </c>
       <c r="H1887" s="2" t="n">
-        <v>46090.31430935644</v>
+        <v>46090.31430935185</v>
       </c>
       <c r="I1887" s="2" t="n">
-        <v>46095.31430935644</v>
+        <v>46095.31430935185</v>
       </c>
     </row>
     <row r="1888">
@@ -74066,10 +74066,10 @@
         </is>
       </c>
       <c r="H1888" s="2" t="n">
-        <v>46066.31430935964</v>
+        <v>46066.31430936343</v>
       </c>
       <c r="I1888" s="2" t="n">
-        <v>46071.31430935964</v>
+        <v>46071.31430936343</v>
       </c>
     </row>
     <row r="1889">
@@ -74105,10 +74105,10 @@
         </is>
       </c>
       <c r="H1889" s="2" t="n">
-        <v>46080.31430936286</v>
+        <v>46080.31430936343</v>
       </c>
       <c r="I1889" s="2" t="n">
-        <v>46085.31430936286</v>
+        <v>46085.31430936343</v>
       </c>
     </row>
     <row r="1890">
@@ -74144,10 +74144,10 @@
         </is>
       </c>
       <c r="H1890" s="2" t="n">
-        <v>46063.3143093661</v>
+        <v>46063.31430936343</v>
       </c>
       <c r="I1890" s="2" t="n">
-        <v>46068.3143093661</v>
+        <v>46068.31430936343</v>
       </c>
     </row>
     <row r="1891">
@@ -74183,10 +74183,10 @@
         </is>
       </c>
       <c r="H1891" s="2" t="n">
-        <v>46073.31430936919</v>
+        <v>46073.31430936343</v>
       </c>
       <c r="I1891" s="2" t="n">
-        <v>46078.31430936919</v>
+        <v>46078.31430936343</v>
       </c>
     </row>
     <row r="1892">
@@ -74222,10 +74222,10 @@
         </is>
       </c>
       <c r="H1892" s="2" t="n">
-        <v>46087.31430937217</v>
+        <v>46087.314309375</v>
       </c>
       <c r="I1892" s="2" t="n">
-        <v>46092.31430937217</v>
+        <v>46092.314309375</v>
       </c>
     </row>
     <row r="1893">
@@ -74261,10 +74261,10 @@
         </is>
       </c>
       <c r="H1893" s="2" t="n">
-        <v>46064.31430937523</v>
+        <v>46064.314309375</v>
       </c>
       <c r="I1893" s="2" t="n">
-        <v>46069.31430937523</v>
+        <v>46069.314309375</v>
       </c>
     </row>
     <row r="1894">
@@ -74300,10 +74300,10 @@
         </is>
       </c>
       <c r="H1894" s="2" t="n">
-        <v>46083.31430937852</v>
+        <v>46083.314309375</v>
       </c>
       <c r="I1894" s="2" t="n">
-        <v>46088.31430937852</v>
+        <v>46088.314309375</v>
       </c>
     </row>
     <row r="1895">
@@ -74339,10 +74339,10 @@
         </is>
       </c>
       <c r="H1895" s="2" t="n">
-        <v>46090.3143093817</v>
+        <v>46090.31430938657</v>
       </c>
       <c r="I1895" s="2" t="n">
-        <v>46095.3143093817</v>
+        <v>46095.31430938657</v>
       </c>
     </row>
     <row r="1896">
@@ -74378,10 +74378,10 @@
         </is>
       </c>
       <c r="H1896" s="2" t="n">
-        <v>46062.31430938493</v>
+        <v>46062.31430938657</v>
       </c>
       <c r="I1896" s="2" t="n">
-        <v>46067.31430938493</v>
+        <v>46067.31430938657</v>
       </c>
     </row>
     <row r="1897">
@@ -74417,10 +74417,10 @@
         </is>
       </c>
       <c r="H1897" s="2" t="n">
-        <v>46063.31430938818</v>
+        <v>46063.31430938657</v>
       </c>
       <c r="I1897" s="2" t="n">
-        <v>46068.31430938818</v>
+        <v>46068.31430938657</v>
       </c>
     </row>
     <row r="1898">
@@ -74456,10 +74456,10 @@
         </is>
       </c>
       <c r="H1898" s="2" t="n">
-        <v>46063.3143093914</v>
+        <v>46063.31430938657</v>
       </c>
       <c r="I1898" s="2" t="n">
-        <v>46068.3143093914</v>
+        <v>46068.31430938657</v>
       </c>
     </row>
     <row r="1899">
@@ -74495,10 +74495,10 @@
         </is>
       </c>
       <c r="H1899" s="2" t="n">
-        <v>46083.31430939458</v>
+        <v>46083.31430939815</v>
       </c>
       <c r="I1899" s="2" t="n">
-        <v>46088.31430939458</v>
+        <v>46088.31430939815</v>
       </c>
     </row>
     <row r="1900">
@@ -74534,10 +74534,10 @@
         </is>
       </c>
       <c r="H1900" s="2" t="n">
-        <v>46090.31430939762</v>
+        <v>46090.31430939815</v>
       </c>
       <c r="I1900" s="2" t="n">
-        <v>46095.31430939762</v>
+        <v>46095.31430939815</v>
       </c>
     </row>
     <row r="1901">
@@ -74573,10 +74573,1960 @@
         </is>
       </c>
       <c r="H1901" s="2" t="n">
-        <v>46090.31430940087</v>
+        <v>46090.31430939815</v>
       </c>
       <c r="I1901" s="2" t="n">
-        <v>46095.31430940087</v>
+        <v>46095.31430939815</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>9cae9438-2d6f-475f-8908-724a90753160</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1902" t="n">
+        <v>2235.56</v>
+      </c>
+      <c r="D1902" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="E1902" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1902" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1902" s="2" t="n">
+        <v>46076.35469825191</v>
+      </c>
+      <c r="I1902" s="2" t="n">
+        <v>46081.35469825191</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>9c24f17e-af0a-4e0a-9486-25ae791f16d0</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1903" t="n">
+        <v>9030.74</v>
+      </c>
+      <c r="D1903" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1903" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1903" s="2" t="n">
+        <v>46072.35469825636</v>
+      </c>
+      <c r="I1903" s="2" t="n">
+        <v>46077.35469825636</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>c6890bc8-fada-4330-b73f-4402e62cbf91</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1904" t="n">
+        <v>3668.56</v>
+      </c>
+      <c r="D1904" t="n">
+        <v>88.63</v>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1904" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1904" s="2" t="n">
+        <v>46085.35469825958</v>
+      </c>
+      <c r="I1904" s="2" t="n">
+        <v>46090.35469825958</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>bfd81a3f-2944-4fd7-8f99-444ed362f2b8</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1905" t="n">
+        <v>6399.93</v>
+      </c>
+      <c r="D1905" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1905" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1905" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1905" s="2" t="n">
+        <v>46075.35469826269</v>
+      </c>
+      <c r="I1905" s="2" t="n">
+        <v>46080.35469826269</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>74f57041-a63e-4da3-b80d-9279f182590e</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1906" t="n">
+        <v>4974.7</v>
+      </c>
+      <c r="D1906" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1906" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1906" s="2" t="n">
+        <v>46065.35469826573</v>
+      </c>
+      <c r="I1906" s="2" t="n">
+        <v>46070.35469826573</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>3a5b84b3-f5f0-4964-9fde-58aaddeb58ff</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1907" t="n">
+        <v>2994.4</v>
+      </c>
+      <c r="D1907" t="n">
+        <v>91.11</v>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1907" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1907" s="2" t="n">
+        <v>46084.35469826905</v>
+      </c>
+      <c r="I1907" s="2" t="n">
+        <v>46089.35469826905</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>7d26f32e-f1fa-4816-b839-b0afb8b90511</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1908" t="n">
+        <v>6408.64</v>
+      </c>
+      <c r="D1908" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1908" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1908" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1908" s="2" t="n">
+        <v>46066.35469827223</v>
+      </c>
+      <c r="I1908" s="2" t="n">
+        <v>46071.35469827223</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>b865e09d-4db0-4f4c-999a-144f911fd47d</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1909" t="n">
+        <v>9068.870000000001</v>
+      </c>
+      <c r="D1909" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1909" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1909" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1909" s="2" t="n">
+        <v>46068.3546982753</v>
+      </c>
+      <c r="I1909" s="2" t="n">
+        <v>46073.3546982753</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>4e318a22-fc25-4c5d-9c37-4bae546b4e24</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1910" t="n">
+        <v>3659.7</v>
+      </c>
+      <c r="D1910" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="E1910" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1910" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1910" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1910" s="2" t="n">
+        <v>46085.3546982789</v>
+      </c>
+      <c r="I1910" s="2" t="n">
+        <v>46090.3546982789</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>ef185591-63f5-49a9-996f-fdd38619119d</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1911" t="n">
+        <v>5395.59</v>
+      </c>
+      <c r="D1911" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="E1911" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1911" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1911" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1911" s="2" t="n">
+        <v>46066.35469828203</v>
+      </c>
+      <c r="I1911" s="2" t="n">
+        <v>46071.35469828203</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>5fa317e1-d049-4166-9cf7-69f6691b9b71</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1912" t="n">
+        <v>5144.11</v>
+      </c>
+      <c r="D1912" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1912" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1912" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1912" s="2" t="n">
+        <v>46077.35469828514</v>
+      </c>
+      <c r="I1912" s="2" t="n">
+        <v>46082.35469828514</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>f05ccbe4-3fe7-492c-9114-6949390dc786</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1913" t="n">
+        <v>1510.69</v>
+      </c>
+      <c r="D1913" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1913" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1913" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1913" s="2" t="n">
+        <v>46062.3546982883</v>
+      </c>
+      <c r="I1913" s="2" t="n">
+        <v>46067.3546982883</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>568beb64-60e7-4f4e-99ea-42b12486381c</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1914" t="n">
+        <v>8878.83</v>
+      </c>
+      <c r="D1914" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1914" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1914" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1914" s="2" t="n">
+        <v>46066.35469829199</v>
+      </c>
+      <c r="I1914" s="2" t="n">
+        <v>46071.35469829199</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>0c9d115e-173a-42e8-bb62-7b29209da711</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1915" t="n">
+        <v>7699.48</v>
+      </c>
+      <c r="D1915" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1915" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1915" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1915" s="2" t="n">
+        <v>46078.35469829508</v>
+      </c>
+      <c r="I1915" s="2" t="n">
+        <v>46083.35469829508</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>b5e8660a-cd9b-4730-aa01-88a641a347ee</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1916" t="n">
+        <v>5093.54</v>
+      </c>
+      <c r="D1916" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1916" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1916" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1916" s="2" t="n">
+        <v>46074.35469829809</v>
+      </c>
+      <c r="I1916" s="2" t="n">
+        <v>46079.35469829809</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>ed3bfa9a-8c76-4c23-9333-413aa1909c70</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1917" t="n">
+        <v>8038.64</v>
+      </c>
+      <c r="D1917" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1917" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1917" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1917" s="2" t="n">
+        <v>46084.35469830127</v>
+      </c>
+      <c r="I1917" s="2" t="n">
+        <v>46089.35469830127</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>2d3e6f5b-9550-4a29-bee8-189496eb6796</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1918" t="n">
+        <v>4749.46</v>
+      </c>
+      <c r="D1918" t="n">
+        <v>87.73</v>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1918" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1918" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1918" s="2" t="n">
+        <v>46087.35469830448</v>
+      </c>
+      <c r="I1918" s="2" t="n">
+        <v>46092.35469830448</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>cb618713-04a0-4d21-994f-81fc9714e19f</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1919" t="n">
+        <v>6259.7</v>
+      </c>
+      <c r="D1919" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1919" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1919" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1919" s="2" t="n">
+        <v>46073.35469830758</v>
+      </c>
+      <c r="I1919" s="2" t="n">
+        <v>46078.35469830758</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>77f95eb5-e8d3-4b4c-b00e-a6055d80b6bc</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1920" t="n">
+        <v>7664.68</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>92.23</v>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1920" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1920" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1920" s="2" t="n">
+        <v>46084.35469831073</v>
+      </c>
+      <c r="I1920" s="2" t="n">
+        <v>46089.35469831073</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>1f562e3f-de12-49a6-9ec8-07cc11c47bec</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1921" t="n">
+        <v>1526.49</v>
+      </c>
+      <c r="D1921" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1921" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1921" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1921" s="2" t="n">
+        <v>46085.35469831404</v>
+      </c>
+      <c r="I1921" s="2" t="n">
+        <v>46090.35469831404</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>5a91b0fc-6197-41a7-9126-f071451f217f</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1922" t="n">
+        <v>8887.620000000001</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1922" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1922" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1922" s="2" t="n">
+        <v>46063.35469831715</v>
+      </c>
+      <c r="I1922" s="2" t="n">
+        <v>46068.35469831715</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>143bee5e-aaf9-4472-8171-2fa76ad95d34</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1923" t="n">
+        <v>1039.2</v>
+      </c>
+      <c r="D1923" t="n">
+        <v>97.58</v>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1923" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1923" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1923" s="2" t="n">
+        <v>46079.35469832031</v>
+      </c>
+      <c r="I1923" s="2" t="n">
+        <v>46084.35469832031</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>21b4d5e0-8d14-4bcd-a53a-9547f24f3abc</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1924" t="n">
+        <v>2671.5</v>
+      </c>
+      <c r="D1924" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1924" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1924" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1924" s="2" t="n">
+        <v>46073.35469832335</v>
+      </c>
+      <c r="I1924" s="2" t="n">
+        <v>46078.35469832335</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>6f5e44e5-b572-4335-bf1f-24886df14045</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1925" t="n">
+        <v>4314.43</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1925" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1925" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1925" s="2" t="n">
+        <v>46089.35469832653</v>
+      </c>
+      <c r="I1925" s="2" t="n">
+        <v>46094.35469832653</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>da8d9990-bcf5-4346-b382-458d688af1ca</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1926" t="n">
+        <v>1346.97</v>
+      </c>
+      <c r="D1926" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1926" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1926" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1926" s="2" t="n">
+        <v>46079.35469832952</v>
+      </c>
+      <c r="I1926" s="2" t="n">
+        <v>46084.35469832952</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>80a89430-4d89-478c-83af-33922193c816</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1927" t="n">
+        <v>9179.959999999999</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1927" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1927" s="2" t="n">
+        <v>46070.35469833275</v>
+      </c>
+      <c r="I1927" s="2" t="n">
+        <v>46075.35469833275</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>a69f9295-2385-4682-8e4a-e39936a92d43</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1928" t="n">
+        <v>3840.93</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1928" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1928" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1928" s="2" t="n">
+        <v>46072.35469833589</v>
+      </c>
+      <c r="I1928" s="2" t="n">
+        <v>46077.35469833589</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>3e13df0c-b27a-4d2c-bc43-6f39de5eb52f</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1929" t="n">
+        <v>3965.9</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1929" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1929" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1929" s="2" t="n">
+        <v>46088.35469833962</v>
+      </c>
+      <c r="I1929" s="2" t="n">
+        <v>46093.35469833962</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>6426e88b-fdd4-453a-bbce-5542cc62c14f</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1930" t="n">
+        <v>9211.120000000001</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1930" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1930" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1930" s="2" t="n">
+        <v>46090.35469834265</v>
+      </c>
+      <c r="I1930" s="2" t="n">
+        <v>46095.35469834265</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>ba69fe65-61a7-4401-811f-2fcc6bf7704e</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1931" t="n">
+        <v>9638.190000000001</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1931" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1931" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1931" s="2" t="n">
+        <v>46077.35469834563</v>
+      </c>
+      <c r="I1931" s="2" t="n">
+        <v>46082.35469834563</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2d6d13e1-f550-43df-94e2-13ced3971dfd</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1932" t="n">
+        <v>5032.36</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1932" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1932" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1932" s="2" t="n">
+        <v>46089.35469834894</v>
+      </c>
+      <c r="I1932" s="2" t="n">
+        <v>46094.35469834894</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>3d9826ae-2d38-4b9c-9753-0a9ba9e313c5</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1933" t="n">
+        <v>8260.889999999999</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1933" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1933" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1933" s="2" t="n">
+        <v>46063.35469835192</v>
+      </c>
+      <c r="I1933" s="2" t="n">
+        <v>46068.35469835192</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>b77be1bb-2a94-4004-9c28-01d029717973</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1934" t="n">
+        <v>4637.77</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1934" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1934" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1934" s="2" t="n">
+        <v>46074.35469835497</v>
+      </c>
+      <c r="I1934" s="2" t="n">
+        <v>46079.35469835497</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>673846e0-80d0-4f80-84d2-6d198710c084</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1935" t="n">
+        <v>9654.700000000001</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>88.76000000000001</v>
+      </c>
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1935" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1935" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1935" s="2" t="n">
+        <v>46071.3546983581</v>
+      </c>
+      <c r="I1935" s="2" t="n">
+        <v>46076.3546983581</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>9a0a784e-81cb-4f9c-b01d-64f3af6c87f7</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1936" t="n">
+        <v>3298.55</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1936" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1936" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1936" s="2" t="n">
+        <v>46073.35469836125</v>
+      </c>
+      <c r="I1936" s="2" t="n">
+        <v>46078.35469836125</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>fde4fbcc-af3d-4687-a8a1-51eb5cb99240</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1937" t="n">
+        <v>4073.42</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1937" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1937" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1937" s="2" t="n">
+        <v>46089.3546983643</v>
+      </c>
+      <c r="I1937" s="2" t="n">
+        <v>46094.3546983643</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>9bc121cb-ccc2-49b7-bf81-80b8b8e941d0</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1938" t="n">
+        <v>7716.15</v>
+      </c>
+      <c r="D1938" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1938" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1938" s="2" t="n">
+        <v>46081.3546983674</v>
+      </c>
+      <c r="I1938" s="2" t="n">
+        <v>46086.3546983674</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2426081c-5d3a-4ec2-9624-854b733cbc09</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1939" t="n">
+        <v>6341.62</v>
+      </c>
+      <c r="D1939" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1939" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1939" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1939" s="2" t="n">
+        <v>46070.35469837041</v>
+      </c>
+      <c r="I1939" s="2" t="n">
+        <v>46075.35469837041</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>e50a79b9-ac0a-43ea-9819-720ce550a2d3</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1940" t="n">
+        <v>8465.01</v>
+      </c>
+      <c r="D1940" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1940" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1940" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1940" s="2" t="n">
+        <v>46084.35469837364</v>
+      </c>
+      <c r="I1940" s="2" t="n">
+        <v>46089.35469837364</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>49443ecb-b3eb-4a0f-8114-33f471474506</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1941" t="n">
+        <v>5268.99</v>
+      </c>
+      <c r="D1941" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1941" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1941" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1941" s="2" t="n">
+        <v>46071.35469837664</v>
+      </c>
+      <c r="I1941" s="2" t="n">
+        <v>46076.35469837664</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>e180db79-68e3-4631-be8d-4acb76deda21</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1942" t="n">
+        <v>4216.4</v>
+      </c>
+      <c r="D1942" t="n">
+        <v>88.68000000000001</v>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1942" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1942" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1942" s="2" t="n">
+        <v>46063.35469837979</v>
+      </c>
+      <c r="I1942" s="2" t="n">
+        <v>46068.35469837979</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>fbf4fe0c-8655-4890-bba9-d5f93acfce28</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1943" t="n">
+        <v>2339.04</v>
+      </c>
+      <c r="D1943" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1943" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1943" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1943" s="2" t="n">
+        <v>46070.35469838334</v>
+      </c>
+      <c r="I1943" s="2" t="n">
+        <v>46075.35469838334</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>5197fdba-c03e-4b53-9840-7cdf5649e5f1</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1944" t="n">
+        <v>5749.89</v>
+      </c>
+      <c r="D1944" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1944" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1944" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1944" s="2" t="n">
+        <v>46062.35469838638</v>
+      </c>
+      <c r="I1944" s="2" t="n">
+        <v>46067.35469838638</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>674aa5de-d4ed-47fc-99b8-56b3388eb056</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1945" t="n">
+        <v>9093.200000000001</v>
+      </c>
+      <c r="D1945" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1945" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1945" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1945" s="2" t="n">
+        <v>46080.35469838942</v>
+      </c>
+      <c r="I1945" s="2" t="n">
+        <v>46085.35469838942</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>59fdcdd0-c519-42d6-b48a-3fad7f372bef</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1946" t="n">
+        <v>8869.67</v>
+      </c>
+      <c r="D1946" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1946" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1946" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1946" s="2" t="n">
+        <v>46074.35469839242</v>
+      </c>
+      <c r="I1946" s="2" t="n">
+        <v>46079.35469839242</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>e02808a6-6ac0-4e2e-b966-d1ec6ff7ed5a</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1947" t="n">
+        <v>7818.41</v>
+      </c>
+      <c r="D1947" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1947" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1947" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1947" s="2" t="n">
+        <v>46061.3546983958</v>
+      </c>
+      <c r="I1947" s="2" t="n">
+        <v>46066.3546983958</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>cf424325-bb0a-470c-9761-365d80be8d84</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1948" t="n">
+        <v>7269.27</v>
+      </c>
+      <c r="D1948" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1948" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1948" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1948" s="2" t="n">
+        <v>46075.35469839891</v>
+      </c>
+      <c r="I1948" s="2" t="n">
+        <v>46080.35469839891</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2cf1c7b2-8580-407b-a13e-cc263bec6411</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1949" t="n">
+        <v>4323.66</v>
+      </c>
+      <c r="D1949" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1949" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1949" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1949" s="2" t="n">
+        <v>46080.35469840227</v>
+      </c>
+      <c r="I1949" s="2" t="n">
+        <v>46085.35469840227</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>d6abbb41-2f57-45fc-85c3-12dbf5ae7f21</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1950" t="n">
+        <v>1752.3</v>
+      </c>
+      <c r="D1950" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1950" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1950" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1950" s="2" t="n">
+        <v>46090.35469840537</v>
+      </c>
+      <c r="I1950" s="2" t="n">
+        <v>46095.35469840537</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>091a525b-b19f-4dd3-915e-49690fa3958b</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1951" t="n">
+        <v>3107.16</v>
+      </c>
+      <c r="D1951" t="n">
+        <v>98.08</v>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1951" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1951" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1951" s="2" t="n">
+        <v>46079.35469840858</v>
+      </c>
+      <c r="I1951" s="2" t="n">
+        <v>46084.35469840858</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1951"/>
+  <dimension ref="A1:I2001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74612,10 +74612,10 @@
         </is>
       </c>
       <c r="H1902" s="2" t="n">
-        <v>46076.35469825191</v>
+        <v>46076.35469825231</v>
       </c>
       <c r="I1902" s="2" t="n">
-        <v>46081.35469825191</v>
+        <v>46081.35469825231</v>
       </c>
     </row>
     <row r="1903">
@@ -74651,10 +74651,10 @@
         </is>
       </c>
       <c r="H1903" s="2" t="n">
-        <v>46072.35469825636</v>
+        <v>46072.35469825231</v>
       </c>
       <c r="I1903" s="2" t="n">
-        <v>46077.35469825636</v>
+        <v>46077.35469825231</v>
       </c>
     </row>
     <row r="1904">
@@ -74690,10 +74690,10 @@
         </is>
       </c>
       <c r="H1904" s="2" t="n">
-        <v>46085.35469825958</v>
+        <v>46085.35469826389</v>
       </c>
       <c r="I1904" s="2" t="n">
-        <v>46090.35469825958</v>
+        <v>46090.35469826389</v>
       </c>
     </row>
     <row r="1905">
@@ -74729,10 +74729,10 @@
         </is>
       </c>
       <c r="H1905" s="2" t="n">
-        <v>46075.35469826269</v>
+        <v>46075.35469826389</v>
       </c>
       <c r="I1905" s="2" t="n">
-        <v>46080.35469826269</v>
+        <v>46080.35469826389</v>
       </c>
     </row>
     <row r="1906">
@@ -74768,10 +74768,10 @@
         </is>
       </c>
       <c r="H1906" s="2" t="n">
-        <v>46065.35469826573</v>
+        <v>46065.35469826389</v>
       </c>
       <c r="I1906" s="2" t="n">
-        <v>46070.35469826573</v>
+        <v>46070.35469826389</v>
       </c>
     </row>
     <row r="1907">
@@ -74807,10 +74807,10 @@
         </is>
       </c>
       <c r="H1907" s="2" t="n">
-        <v>46084.35469826905</v>
+        <v>46084.35469826389</v>
       </c>
       <c r="I1907" s="2" t="n">
-        <v>46089.35469826905</v>
+        <v>46089.35469826389</v>
       </c>
     </row>
     <row r="1908">
@@ -74846,10 +74846,10 @@
         </is>
       </c>
       <c r="H1908" s="2" t="n">
-        <v>46066.35469827223</v>
+        <v>46066.35469827546</v>
       </c>
       <c r="I1908" s="2" t="n">
-        <v>46071.35469827223</v>
+        <v>46071.35469827546</v>
       </c>
     </row>
     <row r="1909">
@@ -74885,10 +74885,10 @@
         </is>
       </c>
       <c r="H1909" s="2" t="n">
-        <v>46068.3546982753</v>
+        <v>46068.35469827546</v>
       </c>
       <c r="I1909" s="2" t="n">
-        <v>46073.3546982753</v>
+        <v>46073.35469827546</v>
       </c>
     </row>
     <row r="1910">
@@ -74924,10 +74924,10 @@
         </is>
       </c>
       <c r="H1910" s="2" t="n">
-        <v>46085.3546982789</v>
+        <v>46085.35469827546</v>
       </c>
       <c r="I1910" s="2" t="n">
-        <v>46090.3546982789</v>
+        <v>46090.35469827546</v>
       </c>
     </row>
     <row r="1911">
@@ -74963,10 +74963,10 @@
         </is>
       </c>
       <c r="H1911" s="2" t="n">
-        <v>46066.35469828203</v>
+        <v>46066.35469828704</v>
       </c>
       <c r="I1911" s="2" t="n">
-        <v>46071.35469828203</v>
+        <v>46071.35469828704</v>
       </c>
     </row>
     <row r="1912">
@@ -75002,10 +75002,10 @@
         </is>
       </c>
       <c r="H1912" s="2" t="n">
-        <v>46077.35469828514</v>
+        <v>46077.35469828704</v>
       </c>
       <c r="I1912" s="2" t="n">
-        <v>46082.35469828514</v>
+        <v>46082.35469828704</v>
       </c>
     </row>
     <row r="1913">
@@ -75041,10 +75041,10 @@
         </is>
       </c>
       <c r="H1913" s="2" t="n">
-        <v>46062.3546982883</v>
+        <v>46062.35469828704</v>
       </c>
       <c r="I1913" s="2" t="n">
-        <v>46067.3546982883</v>
+        <v>46067.35469828704</v>
       </c>
     </row>
     <row r="1914">
@@ -75080,10 +75080,10 @@
         </is>
       </c>
       <c r="H1914" s="2" t="n">
-        <v>46066.35469829199</v>
+        <v>46066.35469828704</v>
       </c>
       <c r="I1914" s="2" t="n">
-        <v>46071.35469829199</v>
+        <v>46071.35469828704</v>
       </c>
     </row>
     <row r="1915">
@@ -75119,10 +75119,10 @@
         </is>
       </c>
       <c r="H1915" s="2" t="n">
-        <v>46078.35469829508</v>
+        <v>46078.35469829861</v>
       </c>
       <c r="I1915" s="2" t="n">
-        <v>46083.35469829508</v>
+        <v>46083.35469829861</v>
       </c>
     </row>
     <row r="1916">
@@ -75158,10 +75158,10 @@
         </is>
       </c>
       <c r="H1916" s="2" t="n">
-        <v>46074.35469829809</v>
+        <v>46074.35469829861</v>
       </c>
       <c r="I1916" s="2" t="n">
-        <v>46079.35469829809</v>
+        <v>46079.35469829861</v>
       </c>
     </row>
     <row r="1917">
@@ -75197,10 +75197,10 @@
         </is>
       </c>
       <c r="H1917" s="2" t="n">
-        <v>46084.35469830127</v>
+        <v>46084.35469829861</v>
       </c>
       <c r="I1917" s="2" t="n">
-        <v>46089.35469830127</v>
+        <v>46089.35469829861</v>
       </c>
     </row>
     <row r="1918">
@@ -75236,10 +75236,10 @@
         </is>
       </c>
       <c r="H1918" s="2" t="n">
-        <v>46087.35469830448</v>
+        <v>46087.35469831018</v>
       </c>
       <c r="I1918" s="2" t="n">
-        <v>46092.35469830448</v>
+        <v>46092.35469831018</v>
       </c>
     </row>
     <row r="1919">
@@ -75275,10 +75275,10 @@
         </is>
       </c>
       <c r="H1919" s="2" t="n">
-        <v>46073.35469830758</v>
+        <v>46073.35469831018</v>
       </c>
       <c r="I1919" s="2" t="n">
-        <v>46078.35469830758</v>
+        <v>46078.35469831018</v>
       </c>
     </row>
     <row r="1920">
@@ -75314,10 +75314,10 @@
         </is>
       </c>
       <c r="H1920" s="2" t="n">
-        <v>46084.35469831073</v>
+        <v>46084.35469831018</v>
       </c>
       <c r="I1920" s="2" t="n">
-        <v>46089.35469831073</v>
+        <v>46089.35469831018</v>
       </c>
     </row>
     <row r="1921">
@@ -75353,10 +75353,10 @@
         </is>
       </c>
       <c r="H1921" s="2" t="n">
-        <v>46085.35469831404</v>
+        <v>46085.35469831018</v>
       </c>
       <c r="I1921" s="2" t="n">
-        <v>46090.35469831404</v>
+        <v>46090.35469831018</v>
       </c>
     </row>
     <row r="1922">
@@ -75392,10 +75392,10 @@
         </is>
       </c>
       <c r="H1922" s="2" t="n">
-        <v>46063.35469831715</v>
+        <v>46063.35469832176</v>
       </c>
       <c r="I1922" s="2" t="n">
-        <v>46068.35469831715</v>
+        <v>46068.35469832176</v>
       </c>
     </row>
     <row r="1923">
@@ -75431,10 +75431,10 @@
         </is>
       </c>
       <c r="H1923" s="2" t="n">
-        <v>46079.35469832031</v>
+        <v>46079.35469832176</v>
       </c>
       <c r="I1923" s="2" t="n">
-        <v>46084.35469832031</v>
+        <v>46084.35469832176</v>
       </c>
     </row>
     <row r="1924">
@@ -75470,10 +75470,10 @@
         </is>
       </c>
       <c r="H1924" s="2" t="n">
-        <v>46073.35469832335</v>
+        <v>46073.35469832176</v>
       </c>
       <c r="I1924" s="2" t="n">
-        <v>46078.35469832335</v>
+        <v>46078.35469832176</v>
       </c>
     </row>
     <row r="1925">
@@ -75509,10 +75509,10 @@
         </is>
       </c>
       <c r="H1925" s="2" t="n">
-        <v>46089.35469832653</v>
+        <v>46089.35469832176</v>
       </c>
       <c r="I1925" s="2" t="n">
-        <v>46094.35469832653</v>
+        <v>46094.35469832176</v>
       </c>
     </row>
     <row r="1926">
@@ -75548,10 +75548,10 @@
         </is>
       </c>
       <c r="H1926" s="2" t="n">
-        <v>46079.35469832952</v>
+        <v>46079.35469833334</v>
       </c>
       <c r="I1926" s="2" t="n">
-        <v>46084.35469832952</v>
+        <v>46084.35469833334</v>
       </c>
     </row>
     <row r="1927">
@@ -75587,10 +75587,10 @@
         </is>
       </c>
       <c r="H1927" s="2" t="n">
-        <v>46070.35469833275</v>
+        <v>46070.35469833334</v>
       </c>
       <c r="I1927" s="2" t="n">
-        <v>46075.35469833275</v>
+        <v>46075.35469833334</v>
       </c>
     </row>
     <row r="1928">
@@ -75626,10 +75626,10 @@
         </is>
       </c>
       <c r="H1928" s="2" t="n">
-        <v>46072.35469833589</v>
+        <v>46072.35469833334</v>
       </c>
       <c r="I1928" s="2" t="n">
-        <v>46077.35469833589</v>
+        <v>46077.35469833334</v>
       </c>
     </row>
     <row r="1929">
@@ -75665,10 +75665,10 @@
         </is>
       </c>
       <c r="H1929" s="2" t="n">
-        <v>46088.35469833962</v>
+        <v>46088.35469834491</v>
       </c>
       <c r="I1929" s="2" t="n">
-        <v>46093.35469833962</v>
+        <v>46093.35469834491</v>
       </c>
     </row>
     <row r="1930">
@@ -75704,10 +75704,10 @@
         </is>
       </c>
       <c r="H1930" s="2" t="n">
-        <v>46090.35469834265</v>
+        <v>46090.35469834491</v>
       </c>
       <c r="I1930" s="2" t="n">
-        <v>46095.35469834265</v>
+        <v>46095.35469834491</v>
       </c>
     </row>
     <row r="1931">
@@ -75743,10 +75743,10 @@
         </is>
       </c>
       <c r="H1931" s="2" t="n">
-        <v>46077.35469834563</v>
+        <v>46077.35469834491</v>
       </c>
       <c r="I1931" s="2" t="n">
-        <v>46082.35469834563</v>
+        <v>46082.35469834491</v>
       </c>
     </row>
     <row r="1932">
@@ -75782,10 +75782,10 @@
         </is>
       </c>
       <c r="H1932" s="2" t="n">
-        <v>46089.35469834894</v>
+        <v>46089.35469834491</v>
       </c>
       <c r="I1932" s="2" t="n">
-        <v>46094.35469834894</v>
+        <v>46094.35469834491</v>
       </c>
     </row>
     <row r="1933">
@@ -75821,10 +75821,10 @@
         </is>
       </c>
       <c r="H1933" s="2" t="n">
-        <v>46063.35469835192</v>
+        <v>46063.35469835648</v>
       </c>
       <c r="I1933" s="2" t="n">
-        <v>46068.35469835192</v>
+        <v>46068.35469835648</v>
       </c>
     </row>
     <row r="1934">
@@ -75860,10 +75860,10 @@
         </is>
       </c>
       <c r="H1934" s="2" t="n">
-        <v>46074.35469835497</v>
+        <v>46074.35469835648</v>
       </c>
       <c r="I1934" s="2" t="n">
-        <v>46079.35469835497</v>
+        <v>46079.35469835648</v>
       </c>
     </row>
     <row r="1935">
@@ -75899,10 +75899,10 @@
         </is>
       </c>
       <c r="H1935" s="2" t="n">
-        <v>46071.3546983581</v>
+        <v>46071.35469835648</v>
       </c>
       <c r="I1935" s="2" t="n">
-        <v>46076.3546983581</v>
+        <v>46076.35469835648</v>
       </c>
     </row>
     <row r="1936">
@@ -75938,10 +75938,10 @@
         </is>
       </c>
       <c r="H1936" s="2" t="n">
-        <v>46073.35469836125</v>
+        <v>46073.35469835648</v>
       </c>
       <c r="I1936" s="2" t="n">
-        <v>46078.35469836125</v>
+        <v>46078.35469835648</v>
       </c>
     </row>
     <row r="1937">
@@ -75977,10 +75977,10 @@
         </is>
       </c>
       <c r="H1937" s="2" t="n">
-        <v>46089.3546983643</v>
+        <v>46089.35469836806</v>
       </c>
       <c r="I1937" s="2" t="n">
-        <v>46094.3546983643</v>
+        <v>46094.35469836806</v>
       </c>
     </row>
     <row r="1938">
@@ -76016,10 +76016,10 @@
         </is>
       </c>
       <c r="H1938" s="2" t="n">
-        <v>46081.3546983674</v>
+        <v>46081.35469836806</v>
       </c>
       <c r="I1938" s="2" t="n">
-        <v>46086.3546983674</v>
+        <v>46086.35469836806</v>
       </c>
     </row>
     <row r="1939">
@@ -76055,10 +76055,10 @@
         </is>
       </c>
       <c r="H1939" s="2" t="n">
-        <v>46070.35469837041</v>
+        <v>46070.35469836806</v>
       </c>
       <c r="I1939" s="2" t="n">
-        <v>46075.35469837041</v>
+        <v>46075.35469836806</v>
       </c>
     </row>
     <row r="1940">
@@ -76094,10 +76094,10 @@
         </is>
       </c>
       <c r="H1940" s="2" t="n">
-        <v>46084.35469837364</v>
+        <v>46084.35469836806</v>
       </c>
       <c r="I1940" s="2" t="n">
-        <v>46089.35469837364</v>
+        <v>46089.35469836806</v>
       </c>
     </row>
     <row r="1941">
@@ -76133,10 +76133,10 @@
         </is>
       </c>
       <c r="H1941" s="2" t="n">
-        <v>46071.35469837664</v>
+        <v>46071.35469837963</v>
       </c>
       <c r="I1941" s="2" t="n">
-        <v>46076.35469837664</v>
+        <v>46076.35469837963</v>
       </c>
     </row>
     <row r="1942">
@@ -76172,10 +76172,10 @@
         </is>
       </c>
       <c r="H1942" s="2" t="n">
-        <v>46063.35469837979</v>
+        <v>46063.35469837963</v>
       </c>
       <c r="I1942" s="2" t="n">
-        <v>46068.35469837979</v>
+        <v>46068.35469837963</v>
       </c>
     </row>
     <row r="1943">
@@ -76211,10 +76211,10 @@
         </is>
       </c>
       <c r="H1943" s="2" t="n">
-        <v>46070.35469838334</v>
+        <v>46070.35469837963</v>
       </c>
       <c r="I1943" s="2" t="n">
-        <v>46075.35469838334</v>
+        <v>46075.35469837963</v>
       </c>
     </row>
     <row r="1944">
@@ -76250,10 +76250,10 @@
         </is>
       </c>
       <c r="H1944" s="2" t="n">
-        <v>46062.35469838638</v>
+        <v>46062.3546983912</v>
       </c>
       <c r="I1944" s="2" t="n">
-        <v>46067.35469838638</v>
+        <v>46067.3546983912</v>
       </c>
     </row>
     <row r="1945">
@@ -76289,10 +76289,10 @@
         </is>
       </c>
       <c r="H1945" s="2" t="n">
-        <v>46080.35469838942</v>
+        <v>46080.3546983912</v>
       </c>
       <c r="I1945" s="2" t="n">
-        <v>46085.35469838942</v>
+        <v>46085.3546983912</v>
       </c>
     </row>
     <row r="1946">
@@ -76328,10 +76328,10 @@
         </is>
       </c>
       <c r="H1946" s="2" t="n">
-        <v>46074.35469839242</v>
+        <v>46074.3546983912</v>
       </c>
       <c r="I1946" s="2" t="n">
-        <v>46079.35469839242</v>
+        <v>46079.3546983912</v>
       </c>
     </row>
     <row r="1947">
@@ -76367,10 +76367,10 @@
         </is>
       </c>
       <c r="H1947" s="2" t="n">
-        <v>46061.3546983958</v>
+        <v>46061.3546983912</v>
       </c>
       <c r="I1947" s="2" t="n">
-        <v>46066.3546983958</v>
+        <v>46066.3546983912</v>
       </c>
     </row>
     <row r="1948">
@@ -76406,10 +76406,10 @@
         </is>
       </c>
       <c r="H1948" s="2" t="n">
-        <v>46075.35469839891</v>
+        <v>46075.35469840278</v>
       </c>
       <c r="I1948" s="2" t="n">
-        <v>46080.35469839891</v>
+        <v>46080.35469840278</v>
       </c>
     </row>
     <row r="1949">
@@ -76445,10 +76445,10 @@
         </is>
       </c>
       <c r="H1949" s="2" t="n">
-        <v>46080.35469840227</v>
+        <v>46080.35469840278</v>
       </c>
       <c r="I1949" s="2" t="n">
-        <v>46085.35469840227</v>
+        <v>46085.35469840278</v>
       </c>
     </row>
     <row r="1950">
@@ -76484,10 +76484,10 @@
         </is>
       </c>
       <c r="H1950" s="2" t="n">
-        <v>46090.35469840537</v>
+        <v>46090.35469840278</v>
       </c>
       <c r="I1950" s="2" t="n">
-        <v>46095.35469840537</v>
+        <v>46095.35469840278</v>
       </c>
     </row>
     <row r="1951">
@@ -76523,10 +76523,1960 @@
         </is>
       </c>
       <c r="H1951" s="2" t="n">
-        <v>46079.35469840858</v>
+        <v>46079.35469841435</v>
       </c>
       <c r="I1951" s="2" t="n">
-        <v>46084.35469840858</v>
+        <v>46084.35469841435</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>e8df55ff-27fd-43a3-98ae-604f4c60bf41</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1952" t="n">
+        <v>1194.78</v>
+      </c>
+      <c r="D1952" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1952" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1952" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1952" s="2" t="n">
+        <v>46066.39949894831</v>
+      </c>
+      <c r="I1952" s="2" t="n">
+        <v>46071.39949894831</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>8ec13404-c2ae-4e62-b157-d661c95e956d</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1953" t="n">
+        <v>4592.18</v>
+      </c>
+      <c r="D1953" t="n">
+        <v>91.81</v>
+      </c>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1953" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1953" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1953" s="2" t="n">
+        <v>46062.39949895244</v>
+      </c>
+      <c r="I1953" s="2" t="n">
+        <v>46067.39949895244</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>3920277a-4eca-44f6-a078-cc5deed7c2e1</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1954" t="n">
+        <v>5437.44</v>
+      </c>
+      <c r="D1954" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1954" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1954" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1954" s="2" t="n">
+        <v>46090.39949895548</v>
+      </c>
+      <c r="I1954" s="2" t="n">
+        <v>46095.39949895548</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>a35f2ff8-5cab-48e7-9761-fd41fa4f300b</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1955" t="n">
+        <v>5233.53</v>
+      </c>
+      <c r="D1955" t="n">
+        <v>99.48999999999999</v>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1955" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1955" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1955" s="2" t="n">
+        <v>46083.39949895888</v>
+      </c>
+      <c r="I1955" s="2" t="n">
+        <v>46088.39949895888</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>fb7bbd5d-7616-4a33-bc2f-edff28c235a9</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1956" t="n">
+        <v>2065.27</v>
+      </c>
+      <c r="D1956" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1956" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1956" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1956" s="2" t="n">
+        <v>46072.39949896192</v>
+      </c>
+      <c r="I1956" s="2" t="n">
+        <v>46077.39949896192</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>541347c8-d8e5-462d-8a85-9565a13bc23d</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1957" t="n">
+        <v>8547.75</v>
+      </c>
+      <c r="D1957" t="n">
+        <v>98.98</v>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1957" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1957" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1957" s="2" t="n">
+        <v>46078.39949896483</v>
+      </c>
+      <c r="I1957" s="2" t="n">
+        <v>46083.39949896483</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>ed27e6eb-be26-4ae7-ac2d-a4872b07d39d</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1958" t="n">
+        <v>8587.790000000001</v>
+      </c>
+      <c r="D1958" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1958" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1958" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1958" s="2" t="n">
+        <v>46063.39949896766</v>
+      </c>
+      <c r="I1958" s="2" t="n">
+        <v>46068.39949896766</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>e7525ac4-356b-4426-9660-aa84ffcac4ca</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1959" t="n">
+        <v>4409.01</v>
+      </c>
+      <c r="D1959" t="n">
+        <v>96.53</v>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1959" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1959" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1959" s="2" t="n">
+        <v>46067.39949897063</v>
+      </c>
+      <c r="I1959" s="2" t="n">
+        <v>46072.39949897063</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>7243cab6-5d8f-47cb-a027-8ba269247d74</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1960" t="n">
+        <v>8259.040000000001</v>
+      </c>
+      <c r="D1960" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1960" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1960" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1960" s="2" t="n">
+        <v>46067.39949897349</v>
+      </c>
+      <c r="I1960" s="2" t="n">
+        <v>46072.39949897349</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>ed7c587c-d84e-4b60-8409-a91c56f95ac2</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1961" t="n">
+        <v>3218.65</v>
+      </c>
+      <c r="D1961" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1961" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1961" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1961" s="2" t="n">
+        <v>46083.39949897646</v>
+      </c>
+      <c r="I1961" s="2" t="n">
+        <v>46088.39949897646</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>f4b8e19c-adc9-4a42-926a-b701b967ad15</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1962" t="n">
+        <v>1873.42</v>
+      </c>
+      <c r="D1962" t="n">
+        <v>96.34</v>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1962" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1962" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1962" s="2" t="n">
+        <v>46090.39949897966</v>
+      </c>
+      <c r="I1962" s="2" t="n">
+        <v>46095.39949897966</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>d8b3a84c-ebe3-4f7d-a9ee-11c921b7a51c</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1963" t="n">
+        <v>6785.15</v>
+      </c>
+      <c r="D1963" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1963" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1963" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1963" s="2" t="n">
+        <v>46072.39949898252</v>
+      </c>
+      <c r="I1963" s="2" t="n">
+        <v>46077.39949898252</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>60a7116f-f5bf-487b-bbaf-b87391334bad</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1964" t="n">
+        <v>1755.11</v>
+      </c>
+      <c r="D1964" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1964" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1964" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1964" s="2" t="n">
+        <v>46081.39949898548</v>
+      </c>
+      <c r="I1964" s="2" t="n">
+        <v>46086.39949898548</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>1263ef02-e612-430a-8b57-ef00790ca2a4</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1965" t="n">
+        <v>9329.440000000001</v>
+      </c>
+      <c r="D1965" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1965" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1965" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1965" s="2" t="n">
+        <v>46073.39949898839</v>
+      </c>
+      <c r="I1965" s="2" t="n">
+        <v>46078.39949898839</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>1a49dc48-c949-430c-8803-e49a95ad41b4</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1966" t="n">
+        <v>6265.07</v>
+      </c>
+      <c r="D1966" t="n">
+        <v>89.14</v>
+      </c>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1966" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1966" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1966" s="2" t="n">
+        <v>46069.39949899139</v>
+      </c>
+      <c r="I1966" s="2" t="n">
+        <v>46074.39949899139</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>6f21c631-712b-4e8c-8d2b-8eda4d9d0b4f</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1967" t="n">
+        <v>9624.73</v>
+      </c>
+      <c r="D1967" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1967" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1967" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1967" s="2" t="n">
+        <v>46080.39949899426</v>
+      </c>
+      <c r="I1967" s="2" t="n">
+        <v>46085.39949899426</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>cd795b4a-2522-439b-aa80-bec36333313a</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1968" t="n">
+        <v>8028.84</v>
+      </c>
+      <c r="D1968" t="n">
+        <v>85.08</v>
+      </c>
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1968" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1968" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1968" s="2" t="n">
+        <v>46089.39949899706</v>
+      </c>
+      <c r="I1968" s="2" t="n">
+        <v>46094.39949899706</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2325aa40-69c2-41a8-922b-8a0bda2ad7ed</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1969" t="n">
+        <v>4947.32</v>
+      </c>
+      <c r="D1969" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1969" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1969" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1969" s="2" t="n">
+        <v>46089.39949899985</v>
+      </c>
+      <c r="I1969" s="2" t="n">
+        <v>46094.39949899985</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>63ab935b-948d-4476-868a-9f88da018472</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1970" t="n">
+        <v>7171.93</v>
+      </c>
+      <c r="D1970" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1970" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1970" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1970" s="2" t="n">
+        <v>46084.39949900293</v>
+      </c>
+      <c r="I1970" s="2" t="n">
+        <v>46089.39949900293</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>9e12a349-d062-4e18-ac97-8922fd728020</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1971" t="n">
+        <v>2036.72</v>
+      </c>
+      <c r="D1971" t="n">
+        <v>96.04000000000001</v>
+      </c>
+      <c r="E1971" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1971" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1971" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1971" s="2" t="n">
+        <v>46070.39949900575</v>
+      </c>
+      <c r="I1971" s="2" t="n">
+        <v>46075.39949900575</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>7b0651a5-24ed-4635-9c20-42e8226ad2d0</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1972" t="n">
+        <v>1557.12</v>
+      </c>
+      <c r="D1972" t="n">
+        <v>90.73</v>
+      </c>
+      <c r="E1972" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1972" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1972" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1972" s="2" t="n">
+        <v>46088.3994990086</v>
+      </c>
+      <c r="I1972" s="2" t="n">
+        <v>46093.3994990086</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>90c6355f-4946-4b87-a9d7-3f4ed71fbe0b</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1973" t="n">
+        <v>3441.77</v>
+      </c>
+      <c r="D1973" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="E1973" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1973" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1973" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1973" s="2" t="n">
+        <v>46079.39949901148</v>
+      </c>
+      <c r="I1973" s="2" t="n">
+        <v>46084.39949901148</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>5bbc5c66-07d8-4110-a2ae-7567871dc643</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1974" t="n">
+        <v>2868.63</v>
+      </c>
+      <c r="D1974" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1974" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1974" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1974" s="2" t="n">
+        <v>46085.39949901441</v>
+      </c>
+      <c r="I1974" s="2" t="n">
+        <v>46090.39949901441</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2753f472-9f03-49c3-a7ed-0102cff1539a</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1975" t="n">
+        <v>7204.93</v>
+      </c>
+      <c r="D1975" t="n">
+        <v>92.63</v>
+      </c>
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1975" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1975" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1975" s="2" t="n">
+        <v>46089.39949901721</v>
+      </c>
+      <c r="I1975" s="2" t="n">
+        <v>46094.39949901721</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>ae56f9ea-e16a-4b3e-8b8b-3ca2cfd5ab97</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1976" t="n">
+        <v>7598.82</v>
+      </c>
+      <c r="D1976" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="E1976" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1976" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1976" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1976" s="2" t="n">
+        <v>46084.39949902004</v>
+      </c>
+      <c r="I1976" s="2" t="n">
+        <v>46089.39949902004</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>27b61076-ce80-48ab-a16a-d7e5f7789397</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1977" t="n">
+        <v>4658.86</v>
+      </c>
+      <c r="D1977" t="n">
+        <v>98.38</v>
+      </c>
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1977" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1977" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1977" s="2" t="n">
+        <v>46065.39949902306</v>
+      </c>
+      <c r="I1977" s="2" t="n">
+        <v>46070.39949902306</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>800a7a7c-043c-4beb-bb1f-c5eb62d717ae</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1978" t="n">
+        <v>9851.98</v>
+      </c>
+      <c r="D1978" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="E1978" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1978" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1978" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1978" s="2" t="n">
+        <v>46065.3994990261</v>
+      </c>
+      <c r="I1978" s="2" t="n">
+        <v>46070.3994990261</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>a729c4d0-2dda-4137-bd98-a76ed12e09c3</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1979" t="n">
+        <v>1166.25</v>
+      </c>
+      <c r="D1979" t="n">
+        <v>90.63</v>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1979" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1979" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1979" s="2" t="n">
+        <v>46074.39949902906</v>
+      </c>
+      <c r="I1979" s="2" t="n">
+        <v>46079.39949902906</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>34006e11-eb4d-4a75-bfac-12b7b1441bce</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1980" t="n">
+        <v>5862.39</v>
+      </c>
+      <c r="D1980" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1980" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1980" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1980" s="2" t="n">
+        <v>46077.3994990319</v>
+      </c>
+      <c r="I1980" s="2" t="n">
+        <v>46082.3994990319</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>b448bccd-e187-4f92-b931-31a650dba3e2</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1981" t="n">
+        <v>6649.09</v>
+      </c>
+      <c r="D1981" t="n">
+        <v>88.78</v>
+      </c>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1981" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1981" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1981" s="2" t="n">
+        <v>46061.39949903472</v>
+      </c>
+      <c r="I1981" s="2" t="n">
+        <v>46066.39949903472</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>7992cbbf-8169-422c-acca-cc9b2ccbedf1</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1982" t="n">
+        <v>6965.95</v>
+      </c>
+      <c r="D1982" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1982" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1982" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1982" s="2" t="n">
+        <v>46076.39949903785</v>
+      </c>
+      <c r="I1982" s="2" t="n">
+        <v>46081.39949903785</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>224ee8a3-4d7b-4de2-85d0-d56b94d263a2</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1983" t="n">
+        <v>9685.530000000001</v>
+      </c>
+      <c r="D1983" t="n">
+        <v>98.83</v>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1983" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1983" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1983" s="2" t="n">
+        <v>46082.39949904069</v>
+      </c>
+      <c r="I1983" s="2" t="n">
+        <v>46087.39949904069</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>ea7c0426-b996-45cc-a465-1077bb17cb8a</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1984" t="n">
+        <v>6614.88</v>
+      </c>
+      <c r="D1984" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1984" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1984" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1984" s="2" t="n">
+        <v>46088.3994990436</v>
+      </c>
+      <c r="I1984" s="2" t="n">
+        <v>46093.3994990436</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>7be97863-8971-4afa-b811-1cabcda9b6a7</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1985" t="n">
+        <v>2407.06</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1985" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1985" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1985" s="2" t="n">
+        <v>46069.39949904659</v>
+      </c>
+      <c r="I1985" s="2" t="n">
+        <v>46074.39949904659</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>d600776c-0197-46c8-8b60-62b89d332466</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1986" t="n">
+        <v>1229.85</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1986" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1986" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1986" s="2" t="n">
+        <v>46074.39949904947</v>
+      </c>
+      <c r="I1986" s="2" t="n">
+        <v>46079.39949904947</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>55939fd7-813f-4b53-97be-260fc5ea18e5</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1987" t="n">
+        <v>8606.450000000001</v>
+      </c>
+      <c r="D1987" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1987" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1987" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1987" s="2" t="n">
+        <v>46063.39949905243</v>
+      </c>
+      <c r="I1987" s="2" t="n">
+        <v>46068.39949905243</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>1345e873-4cab-426a-825f-f3af3e0d3f75</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1988" t="n">
+        <v>4136.23</v>
+      </c>
+      <c r="D1988" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1988" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1988" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1988" s="2" t="n">
+        <v>46075.39949905523</v>
+      </c>
+      <c r="I1988" s="2" t="n">
+        <v>46080.39949905523</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>c04f8cbb-e9e4-4fcd-a8f9-2a07f19f6c59</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1989" t="n">
+        <v>7199.69</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>95.26000000000001</v>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1989" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1989" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1989" s="2" t="n">
+        <v>46067.39949905807</v>
+      </c>
+      <c r="I1989" s="2" t="n">
+        <v>46072.39949905807</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>dbcf8f2b-abf3-4a0e-940d-74d8b053c70b</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1990" t="n">
+        <v>3009.98</v>
+      </c>
+      <c r="D1990" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1990" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1990" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1990" s="2" t="n">
+        <v>46088.39949906095</v>
+      </c>
+      <c r="I1990" s="2" t="n">
+        <v>46093.39949906095</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>5ce56817-2b12-4814-9fa4-e9b9d59e8412</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C1991" t="n">
+        <v>1673.35</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1991" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1991" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1991" s="2" t="n">
+        <v>46069.39949906385</v>
+      </c>
+      <c r="I1991" s="2" t="n">
+        <v>46074.39949906385</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>18b97689-8265-4500-82bf-c1c9a5fb0001</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1992" t="n">
+        <v>6099.26</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>96.63</v>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1992" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1992" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1992" s="2" t="n">
+        <v>46068.3994990667</v>
+      </c>
+      <c r="I1992" s="2" t="n">
+        <v>46073.3994990667</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>48a0c40d-5036-4684-af47-d344ed1a85e1</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1993" t="n">
+        <v>3252.94</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>89.47</v>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1993" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1993" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1993" s="2" t="n">
+        <v>46075.39949906961</v>
+      </c>
+      <c r="I1993" s="2" t="n">
+        <v>46080.39949906961</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>e220f895-7e66-4d4c-9064-89814e079e0c</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1994" t="n">
+        <v>4950</v>
+      </c>
+      <c r="D1994" t="n">
+        <v>96.19</v>
+      </c>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1994" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1994" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1994" s="2" t="n">
+        <v>46065.39949907256</v>
+      </c>
+      <c r="I1994" s="2" t="n">
+        <v>46070.39949907256</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>f572e262-7cbb-476a-bc5e-df82699b0347</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1995" t="n">
+        <v>4450.99</v>
+      </c>
+      <c r="D1995" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1995" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1995" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1995" s="2" t="n">
+        <v>46068.39949907553</v>
+      </c>
+      <c r="I1995" s="2" t="n">
+        <v>46073.39949907553</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>acdc337c-712a-4d83-b41f-2b1d839258f0</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1996" t="n">
+        <v>7109.77</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1996" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1996" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H1996" s="2" t="n">
+        <v>46076.39949907839</v>
+      </c>
+      <c r="I1996" s="2" t="n">
+        <v>46081.39949907839</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>318e3450-d48a-4a75-bf6d-51783234c03b</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1997" t="n">
+        <v>2673.89</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>89.34999999999999</v>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1997" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1997" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1997" s="2" t="n">
+        <v>46068.39949908133</v>
+      </c>
+      <c r="I1997" s="2" t="n">
+        <v>46073.39949908133</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>a7df247c-43ed-4a2f-875f-3a270546003d</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C1998" t="n">
+        <v>3490.94</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1998" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1998" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H1998" s="2" t="n">
+        <v>46077.3994990844</v>
+      </c>
+      <c r="I1998" s="2" t="n">
+        <v>46082.3994990844</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>5c5d9819-ee15-4849-b212-a393a9794699</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C1999" t="n">
+        <v>4797.74</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F1999" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G1999" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H1999" s="2" t="n">
+        <v>46077.39949908742</v>
+      </c>
+      <c r="I1999" s="2" t="n">
+        <v>46082.39949908742</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>f3f6d821-b359-41f2-9cb0-c9ffb72a2b7d</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C2000" t="n">
+        <v>7224.83</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2000" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2000" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H2000" s="2" t="n">
+        <v>46063.39949909023</v>
+      </c>
+      <c r="I2000" s="2" t="n">
+        <v>46068.39949909023</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>aac3da22-cd33-49bc-96a2-39507718f78f</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="C2001" t="n">
+        <v>5535.16</v>
+      </c>
+      <c r="D2001" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2001" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2001" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H2001" s="2" t="n">
+        <v>46089.39949909318</v>
+      </c>
+      <c r="I2001" s="2" t="n">
+        <v>46094.39949909318</v>
       </c>
     </row>
   </sheetData>

--- a/shipments.xlsx
+++ b/shipments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2001"/>
+  <dimension ref="A1:I2051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76562,10 +76562,10 @@
         </is>
       </c>
       <c r="H1952" s="2" t="n">
-        <v>46066.39949894831</v>
+        <v>46066.39949894676</v>
       </c>
       <c r="I1952" s="2" t="n">
-        <v>46071.39949894831</v>
+        <v>46071.39949894676</v>
       </c>
     </row>
     <row r="1953">
@@ -76601,10 +76601,10 @@
         </is>
       </c>
       <c r="H1953" s="2" t="n">
-        <v>46062.39949895244</v>
+        <v>46062.39949894676</v>
       </c>
       <c r="I1953" s="2" t="n">
-        <v>46067.39949895244</v>
+        <v>46067.39949894676</v>
       </c>
     </row>
     <row r="1954">
@@ -76640,10 +76640,10 @@
         </is>
       </c>
       <c r="H1954" s="2" t="n">
-        <v>46090.39949895548</v>
+        <v>46090.39949895833</v>
       </c>
       <c r="I1954" s="2" t="n">
-        <v>46095.39949895548</v>
+        <v>46095.39949895833</v>
       </c>
     </row>
     <row r="1955">
@@ -76679,10 +76679,10 @@
         </is>
       </c>
       <c r="H1955" s="2" t="n">
-        <v>46083.39949895888</v>
+        <v>46083.39949895833</v>
       </c>
       <c r="I1955" s="2" t="n">
-        <v>46088.39949895888</v>
+        <v>46088.39949895833</v>
       </c>
     </row>
     <row r="1956">
@@ -76718,10 +76718,10 @@
         </is>
       </c>
       <c r="H1956" s="2" t="n">
-        <v>46072.39949896192</v>
+        <v>46072.39949895833</v>
       </c>
       <c r="I1956" s="2" t="n">
-        <v>46077.39949896192</v>
+        <v>46077.39949895833</v>
       </c>
     </row>
     <row r="1957">
@@ -76757,10 +76757,10 @@
         </is>
       </c>
       <c r="H1957" s="2" t="n">
-        <v>46078.39949896483</v>
+        <v>46078.39949896991</v>
       </c>
       <c r="I1957" s="2" t="n">
-        <v>46083.39949896483</v>
+        <v>46083.39949896991</v>
       </c>
     </row>
     <row r="1958">
@@ -76796,10 +76796,10 @@
         </is>
       </c>
       <c r="H1958" s="2" t="n">
-        <v>46063.39949896766</v>
+        <v>46063.39949896991</v>
       </c>
       <c r="I1958" s="2" t="n">
-        <v>46068.39949896766</v>
+        <v>46068.39949896991</v>
       </c>
     </row>
     <row r="1959">
@@ -76835,10 +76835,10 @@
         </is>
       </c>
       <c r="H1959" s="2" t="n">
-        <v>46067.39949897063</v>
+        <v>46067.39949896991</v>
       </c>
       <c r="I1959" s="2" t="n">
-        <v>46072.39949897063</v>
+        <v>46072.39949896991</v>
       </c>
     </row>
     <row r="1960">
@@ -76874,10 +76874,10 @@
         </is>
       </c>
       <c r="H1960" s="2" t="n">
-        <v>46067.39949897349</v>
+        <v>46067.39949896991</v>
       </c>
       <c r="I1960" s="2" t="n">
-        <v>46072.39949897349</v>
+        <v>46072.39949896991</v>
       </c>
     </row>
     <row r="1961">
@@ -76913,10 +76913,10 @@
         </is>
       </c>
       <c r="H1961" s="2" t="n">
-        <v>46083.39949897646</v>
+        <v>46083.39949898148</v>
       </c>
       <c r="I1961" s="2" t="n">
-        <v>46088.39949897646</v>
+        <v>46088.39949898148</v>
       </c>
     </row>
     <row r="1962">
@@ -76952,10 +76952,10 @@
         </is>
       </c>
       <c r="H1962" s="2" t="n">
-        <v>46090.39949897966</v>
+        <v>46090.39949898148</v>
       </c>
       <c r="I1962" s="2" t="n">
-        <v>46095.39949897966</v>
+        <v>46095.39949898148</v>
       </c>
     </row>
     <row r="1963">
@@ -76991,10 +76991,10 @@
         </is>
       </c>
       <c r="H1963" s="2" t="n">
-        <v>46072.39949898252</v>
+        <v>46072.39949898148</v>
       </c>
       <c r="I1963" s="2" t="n">
-        <v>46077.39949898252</v>
+        <v>46077.39949898148</v>
       </c>
     </row>
     <row r="1964">
@@ -77030,10 +77030,10 @@
         </is>
       </c>
       <c r="H1964" s="2" t="n">
-        <v>46081.39949898548</v>
+        <v>46081.39949898148</v>
       </c>
       <c r="I1964" s="2" t="n">
-        <v>46086.39949898548</v>
+        <v>46086.39949898148</v>
       </c>
     </row>
     <row r="1965">
@@ -77069,10 +77069,10 @@
         </is>
       </c>
       <c r="H1965" s="2" t="n">
-        <v>46073.39949898839</v>
+        <v>46073.39949899306</v>
       </c>
       <c r="I1965" s="2" t="n">
-        <v>46078.39949898839</v>
+        <v>46078.39949899306</v>
       </c>
     </row>
     <row r="1966">
@@ -77108,10 +77108,10 @@
         </is>
       </c>
       <c r="H1966" s="2" t="n">
-        <v>46069.39949899139</v>
+        <v>46069.39949899306</v>
       </c>
       <c r="I1966" s="2" t="n">
-        <v>46074.39949899139</v>
+        <v>46074.39949899306</v>
       </c>
     </row>
     <row r="1967">
@@ -77147,10 +77147,10 @@
         </is>
       </c>
       <c r="H1967" s="2" t="n">
-        <v>46080.39949899426</v>
+        <v>46080.39949899306</v>
       </c>
       <c r="I1967" s="2" t="n">
-        <v>46085.39949899426</v>
+        <v>46085.39949899306</v>
       </c>
     </row>
     <row r="1968">
@@ -77186,10 +77186,10 @@
         </is>
       </c>
       <c r="H1968" s="2" t="n">
-        <v>46089.39949899706</v>
+        <v>46089.39949899306</v>
       </c>
       <c r="I1968" s="2" t="n">
-        <v>46094.39949899706</v>
+        <v>46094.39949899306</v>
       </c>
     </row>
     <row r="1969">
@@ -77225,10 +77225,10 @@
         </is>
       </c>
       <c r="H1969" s="2" t="n">
-        <v>46089.39949899985</v>
+        <v>46089.39949900463</v>
       </c>
       <c r="I1969" s="2" t="n">
-        <v>46094.39949899985</v>
+        <v>46094.39949900463</v>
       </c>
     </row>
     <row r="1970">
@@ -77264,10 +77264,10 @@
         </is>
       </c>
       <c r="H1970" s="2" t="n">
-        <v>46084.39949900293</v>
+        <v>46084.39949900463</v>
       </c>
       <c r="I1970" s="2" t="n">
-        <v>46089.39949900293</v>
+        <v>46089.39949900463</v>
       </c>
     </row>
     <row r="1971">
@@ -77303,10 +77303,10 @@
         </is>
       </c>
       <c r="H1971" s="2" t="n">
-        <v>46070.39949900575</v>
+        <v>46070.39949900463</v>
       </c>
       <c r="I1971" s="2" t="n">
-        <v>46075.39949900575</v>
+        <v>46075.39949900463</v>
       </c>
     </row>
     <row r="1972">
@@ -77342,10 +77342,10 @@
         </is>
       </c>
       <c r="H1972" s="2" t="n">
-        <v>46088.3994990086</v>
+        <v>46088.39949900463</v>
       </c>
       <c r="I1972" s="2" t="n">
-        <v>46093.3994990086</v>
+        <v>46093.39949900463</v>
       </c>
     </row>
     <row r="1973">
@@ -77381,10 +77381,10 @@
         </is>
       </c>
       <c r="H1973" s="2" t="n">
-        <v>46079.39949901148</v>
+        <v>46079.3994990162</v>
       </c>
       <c r="I1973" s="2" t="n">
-        <v>46084.39949901148</v>
+        <v>46084.3994990162</v>
       </c>
     </row>
     <row r="1974">
@@ -77420,10 +77420,10 @@
         </is>
       </c>
       <c r="H1974" s="2" t="n">
-        <v>46085.39949901441</v>
+        <v>46085.3994990162</v>
       </c>
       <c r="I1974" s="2" t="n">
-        <v>46090.39949901441</v>
+        <v>46090.3994990162</v>
       </c>
     </row>
     <row r="1975">
@@ -77459,10 +77459,10 @@
         </is>
       </c>
       <c r="H1975" s="2" t="n">
-        <v>46089.39949901721</v>
+        <v>46089.3994990162</v>
       </c>
       <c r="I1975" s="2" t="n">
-        <v>46094.39949901721</v>
+        <v>46094.3994990162</v>
       </c>
     </row>
     <row r="1976">
@@ -77498,10 +77498,10 @@
         </is>
       </c>
       <c r="H1976" s="2" t="n">
-        <v>46084.39949902004</v>
+        <v>46084.3994990162</v>
       </c>
       <c r="I1976" s="2" t="n">
-        <v>46089.39949902004</v>
+        <v>46089.3994990162</v>
       </c>
     </row>
     <row r="1977">
@@ -77537,10 +77537,10 @@
         </is>
       </c>
       <c r="H1977" s="2" t="n">
-        <v>46065.39949902306</v>
+        <v>46065.39949902778</v>
       </c>
       <c r="I1977" s="2" t="n">
-        <v>46070.39949902306</v>
+        <v>46070.39949902778</v>
       </c>
     </row>
     <row r="1978">
@@ -77576,10 +77576,10 @@
         </is>
       </c>
       <c r="H1978" s="2" t="n">
-        <v>46065.3994990261</v>
+        <v>46065.39949902778</v>
       </c>
       <c r="I1978" s="2" t="n">
-        <v>46070.3994990261</v>
+        <v>46070.39949902778</v>
       </c>
     </row>
     <row r="1979">
@@ -77615,10 +77615,10 @@
         </is>
       </c>
       <c r="H1979" s="2" t="n">
-        <v>46074.39949902906</v>
+        <v>46074.39949902778</v>
       </c>
       <c r="I1979" s="2" t="n">
-        <v>46079.39949902906</v>
+        <v>46079.39949902778</v>
       </c>
     </row>
     <row r="1980">
@@ -77654,10 +77654,10 @@
         </is>
       </c>
       <c r="H1980" s="2" t="n">
-        <v>46077.3994990319</v>
+        <v>46077.39949902778</v>
       </c>
       <c r="I1980" s="2" t="n">
-        <v>46082.3994990319</v>
+        <v>46082.39949902778</v>
       </c>
     </row>
     <row r="1981">
@@ -77693,10 +77693,10 @@
         </is>
       </c>
       <c r="H1981" s="2" t="n">
-        <v>46061.39949903472</v>
+        <v>46061.39949903935</v>
       </c>
       <c r="I1981" s="2" t="n">
-        <v>46066.39949903472</v>
+        <v>46066.39949903935</v>
       </c>
     </row>
     <row r="1982">
@@ -77732,10 +77732,10 @@
         </is>
       </c>
       <c r="H1982" s="2" t="n">
-        <v>46076.39949903785</v>
+        <v>46076.39949903935</v>
       </c>
       <c r="I1982" s="2" t="n">
-        <v>46081.39949903785</v>
+        <v>46081.39949903935</v>
       </c>
     </row>
     <row r="1983">
@@ -77771,10 +77771,10 @@
         </is>
       </c>
       <c r="H1983" s="2" t="n">
-        <v>46082.39949904069</v>
+        <v>46082.39949903935</v>
       </c>
       <c r="I1983" s="2" t="n">
-        <v>46087.39949904069</v>
+        <v>46087.39949903935</v>
       </c>
     </row>
     <row r="1984">
@@ -77810,10 +77810,10 @@
         </is>
       </c>
       <c r="H1984" s="2" t="n">
-        <v>46088.3994990436</v>
+        <v>46088.39949903935</v>
       </c>
       <c r="I1984" s="2" t="n">
-        <v>46093.3994990436</v>
+        <v>46093.39949903935</v>
       </c>
     </row>
     <row r="1985">
@@ -77849,10 +77849,10 @@
         </is>
       </c>
       <c r="H1985" s="2" t="n">
-        <v>46069.39949904659</v>
+        <v>46069.39949905092</v>
       </c>
       <c r="I1985" s="2" t="n">
-        <v>46074.39949904659</v>
+        <v>46074.39949905092</v>
       </c>
     </row>
     <row r="1986">
@@ -77888,10 +77888,10 @@
         </is>
       </c>
       <c r="H1986" s="2" t="n">
-        <v>46074.39949904947</v>
+        <v>46074.39949905092</v>
       </c>
       <c r="I1986" s="2" t="n">
-        <v>46079.39949904947</v>
+        <v>46079.39949905092</v>
       </c>
     </row>
     <row r="1987">
@@ -77927,10 +77927,10 @@
         </is>
       </c>
       <c r="H1987" s="2" t="n">
-        <v>46063.39949905243</v>
+        <v>46063.39949905092</v>
       </c>
       <c r="I1987" s="2" t="n">
-        <v>46068.39949905243</v>
+        <v>46068.39949905092</v>
       </c>
     </row>
     <row r="1988">
@@ -77966,10 +77966,10 @@
         </is>
       </c>
       <c r="H1988" s="2" t="n">
-        <v>46075.39949905523</v>
+        <v>46075.39949905092</v>
       </c>
       <c r="I1988" s="2" t="n">
-        <v>46080.39949905523</v>
+        <v>46080.39949905092</v>
       </c>
     </row>
     <row r="1989">
@@ -78005,10 +78005,10 @@
         </is>
       </c>
       <c r="H1989" s="2" t="n">
-        <v>46067.39949905807</v>
+        <v>46067.3994990625</v>
       </c>
       <c r="I1989" s="2" t="n">
-        <v>46072.39949905807</v>
+        <v>46072.3994990625</v>
       </c>
     </row>
     <row r="1990">
@@ -78044,10 +78044,10 @@
         </is>
       </c>
       <c r="H1990" s="2" t="n">
-        <v>46088.39949906095</v>
+        <v>46088.3994990625</v>
       </c>
       <c r="I1990" s="2" t="n">
-        <v>46093.39949906095</v>
+        <v>46093.3994990625</v>
       </c>
     </row>
     <row r="1991">
@@ -78083,10 +78083,10 @@
         </is>
       </c>
       <c r="H1991" s="2" t="n">
-        <v>46069.39949906385</v>
+        <v>46069.3994990625</v>
       </c>
       <c r="I1991" s="2" t="n">
-        <v>46074.39949906385</v>
+        <v>46074.3994990625</v>
       </c>
     </row>
     <row r="1992">
@@ -78122,10 +78122,10 @@
         </is>
       </c>
       <c r="H1992" s="2" t="n">
-        <v>46068.3994990667</v>
+        <v>46068.3994990625</v>
       </c>
       <c r="I1992" s="2" t="n">
-        <v>46073.3994990667</v>
+        <v>46073.3994990625</v>
       </c>
     </row>
     <row r="1993">
@@ -78161,10 +78161,10 @@
         </is>
       </c>
       <c r="H1993" s="2" t="n">
-        <v>46075.39949906961</v>
+        <v>46075.39949907408</v>
       </c>
       <c r="I1993" s="2" t="n">
-        <v>46080.39949906961</v>
+        <v>46080.39949907408</v>
       </c>
     </row>
     <row r="1994">
@@ -78200,10 +78200,10 @@
         </is>
       </c>
       <c r="H1994" s="2" t="n">
-        <v>46065.39949907256</v>
+        <v>46065.39949907408</v>
       </c>
       <c r="I1994" s="2" t="n">
-        <v>46070.39949907256</v>
+        <v>46070.39949907408</v>
       </c>
     </row>
     <row r="1995">
@@ -78239,10 +78239,10 @@
         </is>
       </c>
       <c r="H1995" s="2" t="n">
-        <v>46068.39949907553</v>
+        <v>46068.39949907408</v>
       </c>
       <c r="I1995" s="2" t="n">
-        <v>46073.39949907553</v>
+        <v>46073.39949907408</v>
       </c>
     </row>
     <row r="1996">
@@ -78278,10 +78278,10 @@
         </is>
       </c>
       <c r="H1996" s="2" t="n">
-        <v>46076.39949907839</v>
+        <v>46076.39949907408</v>
       </c>
       <c r="I1996" s="2" t="n">
-        <v>46081.39949907839</v>
+        <v>46081.39949907408</v>
       </c>
     </row>
     <row r="1997">
@@ -78317,10 +78317,10 @@
         </is>
       </c>
       <c r="H1997" s="2" t="n">
-        <v>46068.39949908133</v>
+        <v>46068.39949908565</v>
       </c>
       <c r="I1997" s="2" t="n">
-        <v>46073.39949908133</v>
+        <v>46073.39949908565</v>
       </c>
     </row>
     <row r="1998">
@@ -78356,10 +78356,10 @@
         </is>
       </c>
       <c r="H1998" s="2" t="n">
-        <v>46077.3994990844</v>
+        <v>46077.39949908565</v>
       </c>
       <c r="I1998" s="2" t="n">
-        <v>46082.3994990844</v>
+        <v>46082.39949908565</v>
       </c>
     </row>
     <row r="1999">
@@ -78395,10 +78395,10 @@
         </is>
       </c>
       <c r="H1999" s="2" t="n">
-        <v>46077.39949908742</v>
+        <v>46077.39949908565</v>
       </c>
       <c r="I1999" s="2" t="n">
-        <v>46082.39949908742</v>
+        <v>46082.39949908565</v>
       </c>
     </row>
     <row r="2000">
@@ -78434,10 +78434,10 @@
         </is>
       </c>
       <c r="H2000" s="2" t="n">
-        <v>46063.39949909023</v>
+        <v>46063.39949908565</v>
       </c>
       <c r="I2000" s="2" t="n">
-        <v>46068.39949909023</v>
+        <v>46068.39949908565</v>
       </c>
     </row>
     <row r="2001">
@@ -78473,10 +78473,1960 @@
         </is>
       </c>
       <c r="H2001" s="2" t="n">
-        <v>46089.39949909318</v>
+        <v>46089.39949909722</v>
       </c>
       <c r="I2001" s="2" t="n">
-        <v>46094.39949909318</v>
+        <v>46094.39949909722</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>d6962470-d22a-46dc-94b9-ad2a8e1973b9</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C2002" t="n">
+        <v>4895.51</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2002" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2002" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H2002" s="2" t="n">
+        <v>46069.4378169697</v>
+      </c>
+      <c r="I2002" s="2" t="n">
+        <v>46074.4378169697</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>0babc8de-4663-47fd-b7d1-3cb47da498fb</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C2003" t="n">
+        <v>7847.23</v>
+      </c>
+      <c r="D2003" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2003" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2003" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H2003" s="2" t="n">
+        <v>46083.43781697456</v>
+      </c>
+      <c r="I2003" s="2" t="n">
+        <v>46088.43781697456</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>4a33b787-ee7a-4d0f-af55-78e55f54edb5</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C2004" t="n">
+        <v>1739.98</v>
+      </c>
+      <c r="D2004" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2004" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2004" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H2004" s="2" t="n">
+        <v>46081.43781697774</v>
+      </c>
+      <c r="I2004" s="2" t="n">
+        <v>46086.43781697774</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>14b2b5f9-882d-4910-be44-a5ce08d66961</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>Grape</t>
+        </is>
+      </c>
+      <c r="C2005" t="n">
+        <v>6061.8</v>
+      </c>
+      <c r="D2005" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2005" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2005" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H2005" s="2" t="n">
+        <v>46082.43781698091</v>
+      </c>
+      <c r="I2005" s="2" t="n">
+        <v>46087.43781698091</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>fdf52d98-33f3-42ac-8081-5d94db6b0927</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C2006" t="n">
+        <v>4001.21</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2006" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2006" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="H2006" s="2" t="n">
+        <v>46070.43781698418</v>
+      </c>
+      <c r="I2006" s="2" t="n">
+        <v>46075.43781698418</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>cfb9efd0-36c2-471f-baaf-7c4f8e9ddee2</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C2007" t="n">
+        <v>1840.04</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>98.44</v>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2007" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2007" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H2007" s="2" t="n">
+        <v>46084.4378169873</v>
+      </c>
+      <c r="I2007" s="2" t="n">
+        <v>46089.4378169873</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>9dbd4538-1945-485b-a2cf-92b03461af10</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C2008" t="n">
+        <v>1612.11</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>India Packhouse</t>
+        </is>
+      </c>
+      <c r="F2008" t="inlineStr">
+        <is>
+          <t>US Distribution Center</t>
+        </is>
+      </c>
+      <c r="G2008" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H2008" s="2" t="n">
+        <v>46084.43781699042</v>
+      </c>
+      <c r="I2008" s="2" t="n">
+        <v>46089.43781699042</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>f909aeaf-5210-4c7d-98d4-8f2bb3dfd37f</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="C2009" t="n">
+        <v>1793.79</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="E2009" t="inlineStr">
+   